--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normal" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -179,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,6 +207,7 @@
     <xf numFmtId="169" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2119,6 +2121,586 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Normal distribution: probabilities, values, μ ± kσ, σ or mean from a tail fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 16-19, 26; ___1.1 Ztable.pdf; ___1.2 statistische functionaliteit in excel.pdf p. 1-3; __NormVerdeling Excel functies.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Excel's normal functions as the course uses them (NORM.DIST = NORM.VERD, NORM.INV); probabilities are fractions shown as %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: tested against course worked examples S06-WE09 (NORM.INV / NORM.VERD workbook) and S06-WE10 (deck p. 19 notes), the 68-95-99.7 rule (deck p. 18) and the course Z table</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. The distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Mean μ</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>standard normal Z (as in the Z table): μ = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Standard deviation σ</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>standard normal Z: σ = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2. Probability below and above a value x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Value x</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>z = (x − μ) / σ</t>
+        </is>
+      </c>
+      <c r="B14" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B13)),(B13-B9)/B10,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 18; Excel NORMALISEREN (STANDARDIZE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>P(X &lt; x)</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>IF(ISNUMBER(B14),_xlfn.NORM.S.DIST(B14,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Excel NORM.VERD(x; μ; σ; WAAR) = NORM.DIST(..., TRUE); Z table ___1.1 Ztable.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>P(X &gt; x)</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <f>IF(ISNUMBER(B14),_xlfn.NORM.S.DIST(-B14,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>1 − P(X &lt; x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>3. Probability between two values a &lt; b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Lower value a</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Upper value b</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>must be above a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>P(a &lt; X &lt; b)</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B19),ISNUMBER(B20),B20&gt;B19),_xlfn.NORM.DIST(B20,B9,B10,TRUE)-_xlfn.NORM.DIST(B19,B9,B10,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>P(X &lt; a or X &gt; b)</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B19),ISNUMBER(B20),B20&gt;B19),_xlfn.NORM.DIST(B19,B9,B10,TRUE)+_xlfn.NORM.S.DIST(-(B20-B9)/B10,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>4. Value x for a probability p</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Probability p (as a fraction: 0.01 = 1 %)</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>between 0 and 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>x with P(X &lt; x) = p  (lower limit for p below it)</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B25),B25&gt;0,B25&lt;1),_xlfn.NORM.INV(B25,B9,B10),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Excel NORM.INV(p; μ; σ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>x with P(X &gt; x) = p  (upper limit for p above it)</t>
+        </is>
+      </c>
+      <c r="B27" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B25),B25&gt;0,B25&lt;1),_xlfn.NORM.INV(1-B25,B9,B10),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 1 % afkeur bovengrens: NORM.INV(0,99; 20; 0,5) (__NormVerdeling Excel functies.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Central interval with p split over both tails: lower end</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B25),B25&gt;0,B25&lt;1),_xlfn.NORM.INV(B25/2,B9,B10),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>holds 1 − p of the values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Central interval with p split over both tails: upper end</t>
+        </is>
+      </c>
+      <c r="B29" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B25),B25&gt;0,B25&lt;1),_xlfn.NORM.INV(1-B25/2,B9,B10),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>5. μ ± kσ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>k (number of standard deviations)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>μ − kσ</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B32)),B9-B32*B10,"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 19 notes: shoe sizes 42,5 − 3·2,5 = 35</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>μ + kσ</t>
+        </is>
+      </c>
+      <c r="B34" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),ISNUMBER(B32)),B9+B32*B10,"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>42,5 + 3·2,5 = 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Fraction inside μ ± kσ</t>
+        </is>
+      </c>
+      <c r="B35" s="14">
+        <f>IF(ISNUMBER(B32),1-2*_xlfn.NORM.S.DIST(-ABS(B32),TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Fraction outside μ ± kσ</t>
+        </is>
+      </c>
+      <c r="B36" s="14">
+        <f>IF(ISNUMBER(B32),2*_xlfn.NORM.S.DIST(-ABS(B32),TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>6. The 68 - 95 - 99.7 rule (deck p. 18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>within μ ± 1σ</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="14">
+        <f>1-2*_xlfn.NORM.S.DIST(-B39,TRUE)</f>
+        <v/>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 18: ≈ 68 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>within μ ± 2σ</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="14">
+        <f>1-2*_xlfn.NORM.S.DIST(-B40,TRUE)</f>
+        <v/>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 18: ≈ 95 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>within μ ± 3σ</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="14">
+        <f>1-2*_xlfn.NORM.S.DIST(-B41,TRUE)</f>
+        <v/>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 18: ≈ 99.7 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>7. σ from a tail fraction, mean known (e.g. '2 in 40 below 720, mean 820')</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Limit L</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>uses the mean μ from section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Fraction f beyond L (as a fraction: 2/40 = 0.05)</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>σ if f lies BELOW L</t>
+        </is>
+      </c>
+      <c r="B46" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B44),ISNUMBER(B45),B45&gt;0,B45&lt;1,B45&lt;&gt;0.5),IF((B44-B9)/_xlfn.NORM.S.INV(B45)&gt;0,(B44-B9)/_xlfn.NORM.S.INV(B45),"not possible: L is on the other side"),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>(L − μ) / NORM.S.INV(f)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>σ if f lies ABOVE L</t>
+        </is>
+      </c>
+      <c r="B47" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B44),ISNUMBER(B45),B45&gt;0,B45&lt;1,B45&lt;&gt;0.5),IF((B44-B9)/_xlfn.NORM.S.INV(1-B45)&gt;0,(B44-B9)/_xlfn.NORM.S.INV(1-B45),"not possible: L is on the other side"),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>(L − μ) / NORM.S.INV(1 − f)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Variance σ² (f below L)</t>
+        </is>
+      </c>
+      <c r="B48" s="11">
+        <f>IF(ISNUMBER(B46),B46^2,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Variance σ² (f above L)</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(ISNUMBER(B47),B47^2,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>8. Mean from a tail fraction, σ known (uses σ from section 1, L and f from section 7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>μ if f lies BELOW L</t>
+        </is>
+      </c>
+      <c r="B52" s="11">
+        <f>IF(AND(ISNUMBER(B10),ISNUMBER(B44),ISNUMBER(B45),B45&gt;0,B45&lt;1),B44-B10*_xlfn.NORM.S.INV(B45),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>L − σ · NORM.S.INV(f)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>μ if f lies ABOVE L</t>
+        </is>
+      </c>
+      <c r="B53" s="11">
+        <f>IF(AND(ISNUMBER(B10),ISNUMBER(B44),ISNUMBER(B45),B45&gt;0,B45&lt;1),B44-B10*_xlfn.NORM.S.INV(1-B45),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>L − σ · NORM.S.INV(1 − f)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B25 B45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Probability" error="Type a fraction between 0 and 1, e.g. 0.01 for 1 %." type="decimal" operator="between">
+      <formula1>0.0000000001</formula1>
+      <formula2>0.9999999999</formula2>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="σ" error="σ must be greater than 0." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2218,7 +2800,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Table 18 - Factors for Computing Control-Chart Lines</t>
         </is>
@@ -2232,7 +2814,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>USED by the calculators (the lecturer's exercise workbooks use these values).</t>
         </is>
@@ -2326,1330 +2908,1330 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B14" s="23" t="n">
         <v>2.121</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <v>3.76</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <v>3.76</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="23" t="n">
         <v>1.88</v>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="24" t="n">
         <v>0.5642</v>
       </c>
-      <c r="G14" s="23" t="n">
+      <c r="G14" s="24" t="n">
         <v>1.7725</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="23" t="n">
         <v>1.843</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="23" t="n">
         <v>3.267</v>
       </c>
-      <c r="L14" s="22" t="n">
+      <c r="L14" s="23" t="n">
         <v>1.128</v>
       </c>
-      <c r="M14" s="23" t="n">
+      <c r="M14" s="24" t="n">
         <v>0.8865</v>
       </c>
-      <c r="N14" s="21" t="n">
+      <c r="N14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="22" t="n">
+      <c r="O14" s="23" t="n">
         <v>3.686</v>
       </c>
-      <c r="P14" s="21" t="n">
+      <c r="P14" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="22" t="n">
+      <c r="Q14" s="23" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B15" s="23" t="n">
         <v>1.732</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>3.07</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <v>2.394</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="23" t="n">
         <v>1.023</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="F15" s="24" t="n">
         <v>0.7236</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="24" t="n">
         <v>1.382</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="23" t="n">
         <v>1.858</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="22" t="n">
+      <c r="K15" s="23" t="n">
         <v>2.568</v>
       </c>
-      <c r="L15" s="22" t="n">
+      <c r="L15" s="23" t="n">
         <v>1.693</v>
       </c>
-      <c r="M15" s="23" t="n">
+      <c r="M15" s="24" t="n">
         <v>0.5907</v>
       </c>
-      <c r="N15" s="21" t="n">
+      <c r="N15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="22" t="n">
+      <c r="O15" s="23" t="n">
         <v>4.358</v>
       </c>
-      <c r="P15" s="21" t="n">
+      <c r="P15" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="24" t="n">
+      <c r="Q15" s="25" t="n">
         <v>2.575</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>2.914</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>1.88</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <v>0.729</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="24" t="n">
         <v>1.2533</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="23" t="n">
         <v>1.808</v>
       </c>
-      <c r="J16" s="21" t="n">
+      <c r="J16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="23" t="n">
         <v>2.266</v>
       </c>
-      <c r="L16" s="22" t="n">
+      <c r="L16" s="23" t="n">
         <v>2.059</v>
       </c>
-      <c r="M16" s="23" t="n">
+      <c r="M16" s="24" t="n">
         <v>0.4857</v>
       </c>
-      <c r="N16" s="21" t="n">
+      <c r="N16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="22" t="n">
+      <c r="O16" s="23" t="n">
         <v>4.698</v>
       </c>
-      <c r="P16" s="21" t="n">
+      <c r="P16" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="22" t="n">
+      <c r="Q16" s="23" t="n">
         <v>2.282</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="23" t="n">
         <v>1.342</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="23" t="n">
         <v>2.884</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="23" t="n">
         <v>1.596</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="23" t="n">
         <v>0.577</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="24" t="n">
         <v>0.8407</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="24" t="n">
         <v>1.1894</v>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="H17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="23" t="n">
         <v>1.756</v>
       </c>
-      <c r="J17" s="21" t="n">
+      <c r="J17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="K17" s="23" t="n">
         <v>2.089</v>
       </c>
-      <c r="L17" s="22" t="n">
+      <c r="L17" s="23" t="n">
         <v>2.326</v>
       </c>
-      <c r="M17" s="23" t="n">
+      <c r="M17" s="24" t="n">
         <v>0.4299</v>
       </c>
-      <c r="N17" s="21" t="n">
+      <c r="N17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="22" t="n">
+      <c r="O17" s="23" t="n">
         <v>4.918</v>
       </c>
-      <c r="P17" s="21" t="n">
+      <c r="P17" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="24" t="n">
+      <c r="Q17" s="25" t="n">
         <v>2.115</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="n">
+      <c r="A18" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B18" s="23" t="n">
         <v>1.225</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="23" t="n">
         <v>2.899</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>1.41</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="23" t="n">
         <v>0.483</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="24" t="n">
         <v>0.8686</v>
       </c>
-      <c r="G18" s="23" t="n">
+      <c r="G18" s="24" t="n">
         <v>1.1512</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="23" t="n">
         <v>0.026</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="23" t="n">
         <v>1.711</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" s="22" t="n">
+      <c r="K18" s="23" t="n">
         <v>1.97</v>
       </c>
-      <c r="L18" s="22" t="n">
+      <c r="L18" s="23" t="n">
         <v>2.534</v>
       </c>
-      <c r="M18" s="23" t="n">
+      <c r="M18" s="24" t="n">
         <v>0.3946</v>
       </c>
-      <c r="N18" s="21" t="n">
+      <c r="N18" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="22" t="n">
+      <c r="O18" s="23" t="n">
         <v>5.078</v>
       </c>
-      <c r="P18" s="21" t="n">
+      <c r="P18" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="22" t="n">
+      <c r="Q18" s="23" t="n">
         <v>2.004</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="23" t="n">
         <v>1.134</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="23" t="n">
         <v>2.935</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="23" t="n">
         <v>1.277</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="23" t="n">
         <v>0.419</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="24" t="n">
         <v>0.8882</v>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="24" t="n">
         <v>1.1259</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="23" t="n">
         <v>0.105</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="I19" s="23" t="n">
         <v>1.672</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="23" t="n">
         <v>0.118</v>
       </c>
-      <c r="K19" s="22" t="n">
+      <c r="K19" s="23" t="n">
         <v>1.882</v>
       </c>
-      <c r="L19" s="22" t="n">
+      <c r="L19" s="23" t="n">
         <v>2.704</v>
       </c>
-      <c r="M19" s="23" t="n">
+      <c r="M19" s="24" t="n">
         <v>0.3698</v>
       </c>
-      <c r="N19" s="24" t="n">
+      <c r="N19" s="25" t="n">
         <v>0.205</v>
       </c>
-      <c r="O19" s="24" t="n">
+      <c r="O19" s="25" t="n">
         <v>5.203</v>
       </c>
-      <c r="P19" s="22" t="n">
+      <c r="P19" s="23" t="n">
         <v>0.076</v>
       </c>
-      <c r="Q19" s="22" t="n">
+      <c r="Q19" s="23" t="n">
         <v>1.924</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="23" t="n">
         <v>1.061</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="23" t="n">
         <v>2.98</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>1.175</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.373</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="24" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="24" t="n">
         <v>1.1078</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="23" t="n">
         <v>0.167</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="23" t="n">
         <v>1.638</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J20" s="23" t="n">
         <v>0.185</v>
       </c>
-      <c r="K20" s="22" t="n">
+      <c r="K20" s="23" t="n">
         <v>1.815</v>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="L20" s="23" t="n">
         <v>2.847</v>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="24" t="n">
         <v>0.3512</v>
       </c>
-      <c r="N20" s="24" t="n">
+      <c r="N20" s="25" t="n">
         <v>0.387</v>
       </c>
-      <c r="O20" s="24" t="n">
+      <c r="O20" s="25" t="n">
         <v>5.307</v>
       </c>
-      <c r="P20" s="22" t="n">
+      <c r="P20" s="23" t="n">
         <v>0.136</v>
       </c>
-      <c r="Q20" s="22" t="n">
+      <c r="Q20" s="23" t="n">
         <v>1.864</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="n">
+      <c r="A21" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="23" t="n">
         <v>3.03</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="23" t="n">
         <v>1.094</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="23" t="n">
         <v>0.337</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="24" t="n">
         <v>0.9139</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="24" t="n">
         <v>1.0942</v>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="23" t="n">
         <v>0.219</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="23" t="n">
         <v>1.609</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="23" t="n">
         <v>0.239</v>
       </c>
-      <c r="K21" s="22" t="n">
+      <c r="K21" s="23" t="n">
         <v>1.761</v>
       </c>
-      <c r="L21" s="22" t="n">
+      <c r="L21" s="23" t="n">
         <v>2.97</v>
       </c>
-      <c r="M21" s="23" t="n">
+      <c r="M21" s="24" t="n">
         <v>0.3367</v>
       </c>
-      <c r="N21" s="24" t="n">
+      <c r="N21" s="25" t="n">
         <v>0.546</v>
       </c>
-      <c r="O21" s="24" t="n">
+      <c r="O21" s="25" t="n">
         <v>5.394</v>
       </c>
-      <c r="P21" s="22" t="n">
+      <c r="P21" s="23" t="n">
         <v>0.184</v>
       </c>
-      <c r="Q21" s="22" t="n">
+      <c r="Q21" s="23" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="n">
+      <c r="A22" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="23" t="n">
         <v>0.949</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="23" t="n">
         <v>3.085</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>1.028</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.308</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F22" s="24" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="24" t="n">
         <v>1.0837</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="23" t="n">
         <v>0.262</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="23" t="n">
         <v>1.584</v>
       </c>
-      <c r="J22" s="22" t="n">
+      <c r="J22" s="23" t="n">
         <v>0.284</v>
       </c>
-      <c r="K22" s="22" t="n">
+      <c r="K22" s="23" t="n">
         <v>1.716</v>
       </c>
-      <c r="L22" s="22" t="n">
+      <c r="L22" s="23" t="n">
         <v>3.078</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="M22" s="24" t="n">
         <v>0.3249</v>
       </c>
-      <c r="N22" s="22" t="n">
+      <c r="N22" s="23" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="O22" s="22" t="n">
+      <c r="O22" s="23" t="n">
         <v>5.469</v>
       </c>
-      <c r="P22" s="22" t="n">
+      <c r="P22" s="23" t="n">
         <v>0.223</v>
       </c>
-      <c r="Q22" s="22" t="n">
+      <c r="Q22" s="23" t="n">
         <v>1.777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n">
+      <c r="A23" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="23" t="n">
         <v>0.905</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="23" t="n">
         <v>3.136</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <v>0.973</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="23" t="n">
         <v>0.285</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="24" t="n">
         <v>0.93</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="24" t="n">
         <v>1.0753</v>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="H23" s="23" t="n">
         <v>0.299</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="23" t="n">
         <v>1.561</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="J23" s="23" t="n">
         <v>0.321</v>
       </c>
-      <c r="K23" s="22" t="n">
+      <c r="K23" s="23" t="n">
         <v>1.679</v>
       </c>
-      <c r="L23" s="22" t="n">
+      <c r="L23" s="23" t="n">
         <v>3.173</v>
       </c>
-      <c r="M23" s="23" t="n">
+      <c r="M23" s="24" t="n">
         <v>0.3152</v>
       </c>
-      <c r="N23" s="24" t="n">
+      <c r="N23" s="25" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="O23" s="24" t="n">
+      <c r="O23" s="25" t="n">
         <v>5.534</v>
       </c>
-      <c r="P23" s="22" t="n">
+      <c r="P23" s="23" t="n">
         <v>0.256</v>
       </c>
-      <c r="Q23" s="22" t="n">
+      <c r="Q23" s="23" t="n">
         <v>1.744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="n">
+      <c r="A24" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="23" t="n">
         <v>0.866</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="23" t="n">
         <v>3.189</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.925</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="23" t="n">
         <v>0.266</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="24" t="n">
         <v>0.9359</v>
       </c>
-      <c r="G24" s="23" t="n">
+      <c r="G24" s="24" t="n">
         <v>1.0684</v>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="H24" s="23" t="n">
         <v>0.331</v>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="I24" s="23" t="n">
         <v>1.541</v>
       </c>
-      <c r="J24" s="22" t="n">
+      <c r="J24" s="23" t="n">
         <v>0.354</v>
       </c>
-      <c r="K24" s="22" t="n">
+      <c r="K24" s="23" t="n">
         <v>1.646</v>
       </c>
-      <c r="L24" s="22" t="n">
+      <c r="L24" s="23" t="n">
         <v>3.258</v>
       </c>
-      <c r="M24" s="23" t="n">
+      <c r="M24" s="24" t="n">
         <v>0.3069</v>
       </c>
-      <c r="N24" s="24" t="n">
+      <c r="N24" s="25" t="n">
         <v>0.924</v>
       </c>
-      <c r="O24" s="24" t="n">
+      <c r="O24" s="25" t="n">
         <v>5.592</v>
       </c>
-      <c r="P24" s="24" t="n">
+      <c r="P24" s="25" t="n">
         <v>0.284</v>
       </c>
-      <c r="Q24" s="24" t="n">
+      <c r="Q24" s="25" t="n">
         <v>1.716</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="22" t="n">
+      <c r="B25" s="23" t="n">
         <v>0.832</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="23" t="n">
         <v>3.242</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="23" t="n">
         <v>0.884</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="23" t="n">
         <v>0.249</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="24" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="G25" s="23" t="n">
+      <c r="G25" s="24" t="n">
         <v>1.0627</v>
       </c>
-      <c r="H25" s="22" t="n">
+      <c r="H25" s="23" t="n">
         <v>0.359</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="I25" s="23" t="n">
         <v>1.523</v>
       </c>
-      <c r="J25" s="22" t="n">
+      <c r="J25" s="23" t="n">
         <v>0.382</v>
       </c>
-      <c r="K25" s="22" t="n">
+      <c r="K25" s="23" t="n">
         <v>1.618</v>
       </c>
-      <c r="L25" s="22" t="n">
+      <c r="L25" s="23" t="n">
         <v>3.336</v>
       </c>
-      <c r="M25" s="23" t="n">
+      <c r="M25" s="24" t="n">
         <v>0.2998</v>
       </c>
-      <c r="N25" s="24" t="n">
+      <c r="N25" s="25" t="n">
         <v>1.026</v>
       </c>
-      <c r="O25" s="24" t="n">
+      <c r="O25" s="25" t="n">
         <v>5.646</v>
       </c>
-      <c r="P25" s="24" t="n">
+      <c r="P25" s="25" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q25" s="24" t="n">
+      <c r="Q25" s="25" t="n">
         <v>1.692</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="n">
+      <c r="A26" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="22" t="n">
+      <c r="B26" s="23" t="n">
         <v>0.802</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="23" t="n">
         <v>3.295</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <v>0.848</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="23" t="n">
         <v>0.235</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="24" t="n">
         <v>0.9453</v>
       </c>
-      <c r="G26" s="23" t="n">
+      <c r="G26" s="24" t="n">
         <v>1.0579</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="23" t="n">
         <v>0.384</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="23" t="n">
         <v>1.507</v>
       </c>
-      <c r="J26" s="22" t="n">
+      <c r="J26" s="23" t="n">
         <v>0.406</v>
       </c>
-      <c r="K26" s="22" t="n">
+      <c r="K26" s="23" t="n">
         <v>1.594</v>
       </c>
-      <c r="L26" s="22" t="n">
+      <c r="L26" s="23" t="n">
         <v>3.407</v>
       </c>
-      <c r="M26" s="23" t="n">
+      <c r="M26" s="24" t="n">
         <v>0.2935</v>
       </c>
-      <c r="N26" s="24" t="n">
+      <c r="N26" s="25" t="n">
         <v>1.121</v>
       </c>
-      <c r="O26" s="24" t="n">
+      <c r="O26" s="25" t="n">
         <v>5.693</v>
       </c>
-      <c r="P26" s="24" t="n">
+      <c r="P26" s="25" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q26" s="24" t="n">
+      <c r="Q26" s="25" t="n">
         <v>1.671</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n">
+      <c r="A27" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="22" t="n">
+      <c r="B27" s="23" t="n">
         <v>0.775</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="23" t="n">
         <v>3.347</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="23" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="23" t="n">
         <v>0.223</v>
       </c>
-      <c r="F27" s="23" t="n">
+      <c r="F27" s="24" t="n">
         <v>0.949</v>
       </c>
-      <c r="G27" s="23" t="n">
+      <c r="G27" s="24" t="n">
         <v>1.0537</v>
       </c>
-      <c r="H27" s="22" t="n">
+      <c r="H27" s="23" t="n">
         <v>0.406</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="23" t="n">
         <v>1.492</v>
       </c>
-      <c r="J27" s="22" t="n">
+      <c r="J27" s="23" t="n">
         <v>0.428</v>
       </c>
-      <c r="K27" s="22" t="n">
+      <c r="K27" s="23" t="n">
         <v>1.572</v>
       </c>
-      <c r="L27" s="22" t="n">
+      <c r="L27" s="23" t="n">
         <v>3.472</v>
       </c>
-      <c r="M27" s="23" t="n">
+      <c r="M27" s="24" t="n">
         <v>0.288</v>
       </c>
-      <c r="N27" s="24" t="n">
+      <c r="N27" s="25" t="n">
         <v>1.207</v>
       </c>
-      <c r="O27" s="24" t="n">
+      <c r="O27" s="25" t="n">
         <v>5.737</v>
       </c>
-      <c r="P27" s="24" t="n">
+      <c r="P27" s="25" t="n">
         <v>0.348</v>
       </c>
-      <c r="Q27" s="24" t="n">
+      <c r="Q27" s="25" t="n">
         <v>1.652</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="n">
+      <c r="A28" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="22" t="n">
+      <c r="B28" s="23" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="23" t="n">
         <v>3.398</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>0.788</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="23" t="n">
         <v>0.212</v>
       </c>
-      <c r="F28" s="23" t="n">
+      <c r="F28" s="24" t="n">
         <v>0.9523</v>
       </c>
-      <c r="G28" s="23" t="n">
+      <c r="G28" s="24" t="n">
         <v>1.0501</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="H28" s="23" t="n">
         <v>0.427</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="I28" s="23" t="n">
         <v>1.478</v>
       </c>
-      <c r="J28" s="22" t="n">
+      <c r="J28" s="23" t="n">
         <v>0.448</v>
       </c>
-      <c r="K28" s="22" t="n">
+      <c r="K28" s="23" t="n">
         <v>1.552</v>
       </c>
-      <c r="L28" s="22" t="n">
+      <c r="L28" s="23" t="n">
         <v>3.532</v>
       </c>
-      <c r="M28" s="23" t="n">
+      <c r="M28" s="24" t="n">
         <v>0.2831</v>
       </c>
-      <c r="N28" s="24" t="n">
+      <c r="N28" s="25" t="n">
         <v>1.285</v>
       </c>
-      <c r="O28" s="24" t="n">
+      <c r="O28" s="25" t="n">
         <v>5.779</v>
       </c>
-      <c r="P28" s="24" t="n">
+      <c r="P28" s="25" t="n">
         <v>0.364</v>
       </c>
-      <c r="Q28" s="24" t="n">
+      <c r="Q28" s="25" t="n">
         <v>1.636</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="n">
+      <c r="A29" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="22" t="n">
+      <c r="B29" s="23" t="n">
         <v>0.728</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="23" t="n">
         <v>3.448</v>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="23" t="n">
         <v>0.762</v>
       </c>
-      <c r="E29" s="22" t="n">
+      <c r="E29" s="23" t="n">
         <v>0.203</v>
       </c>
-      <c r="F29" s="23" t="n">
+      <c r="F29" s="24" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="G29" s="23" t="n">
+      <c r="G29" s="24" t="n">
         <v>1.047</v>
       </c>
-      <c r="H29" s="22" t="n">
+      <c r="H29" s="23" t="n">
         <v>0.445</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I29" s="23" t="n">
         <v>1.465</v>
       </c>
-      <c r="J29" s="22" t="n">
+      <c r="J29" s="23" t="n">
         <v>0.466</v>
       </c>
-      <c r="K29" s="22" t="n">
+      <c r="K29" s="23" t="n">
         <v>1.534</v>
       </c>
-      <c r="L29" s="22" t="n">
+      <c r="L29" s="23" t="n">
         <v>3.588</v>
       </c>
-      <c r="M29" s="23" t="n">
+      <c r="M29" s="24" t="n">
         <v>0.2787</v>
       </c>
-      <c r="N29" s="24" t="n">
+      <c r="N29" s="25" t="n">
         <v>1.359</v>
       </c>
-      <c r="O29" s="24" t="n">
+      <c r="O29" s="25" t="n">
         <v>5.817</v>
       </c>
-      <c r="P29" s="24" t="n">
+      <c r="P29" s="25" t="n">
         <v>0.379</v>
       </c>
-      <c r="Q29" s="24" t="n">
+      <c r="Q29" s="25" t="n">
         <v>1.621</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="n">
+      <c r="A30" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="22" t="n">
+      <c r="B30" s="23" t="n">
         <v>0.707</v>
       </c>
-      <c r="C30" s="22" t="n">
+      <c r="C30" s="23" t="n">
         <v>3.497</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.738</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.194</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F30" s="24" t="n">
         <v>0.9576</v>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="24" t="n">
         <v>1.0442</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="23" t="n">
         <v>0.461</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="I30" s="23" t="n">
         <v>1.454</v>
       </c>
-      <c r="J30" s="22" t="n">
+      <c r="J30" s="23" t="n">
         <v>0.482</v>
       </c>
-      <c r="K30" s="22" t="n">
+      <c r="K30" s="23" t="n">
         <v>1.518</v>
       </c>
-      <c r="L30" s="22" t="n">
+      <c r="L30" s="23" t="n">
         <v>3.64</v>
       </c>
-      <c r="M30" s="23" t="n">
+      <c r="M30" s="24" t="n">
         <v>0.2747</v>
       </c>
-      <c r="N30" s="24" t="n">
+      <c r="N30" s="25" t="n">
         <v>1.426</v>
       </c>
-      <c r="O30" s="24" t="n">
+      <c r="O30" s="25" t="n">
         <v>5.854</v>
       </c>
-      <c r="P30" s="24" t="n">
+      <c r="P30" s="25" t="n">
         <v>0.392</v>
       </c>
-      <c r="Q30" s="22" t="n">
+      <c r="Q30" s="23" t="n">
         <v>1.608</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="n">
+      <c r="A31" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="23" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="23" t="n">
         <v>3.545</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="23" t="n">
         <v>0.717</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="23" t="n">
         <v>0.187</v>
       </c>
-      <c r="F31" s="23" t="n">
+      <c r="F31" s="24" t="n">
         <v>0.9599</v>
       </c>
-      <c r="G31" s="23" t="n">
+      <c r="G31" s="24" t="n">
         <v>1.0418</v>
       </c>
-      <c r="H31" s="22" t="n">
+      <c r="H31" s="23" t="n">
         <v>0.477</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="I31" s="23" t="n">
         <v>1.443</v>
       </c>
-      <c r="J31" s="22" t="n">
+      <c r="J31" s="23" t="n">
         <v>0.497</v>
       </c>
-      <c r="K31" s="22" t="n">
+      <c r="K31" s="23" t="n">
         <v>1.503</v>
       </c>
-      <c r="L31" s="22" t="n">
+      <c r="L31" s="23" t="n">
         <v>3.689</v>
       </c>
-      <c r="M31" s="23" t="n">
+      <c r="M31" s="24" t="n">
         <v>0.2711</v>
       </c>
-      <c r="N31" s="24" t="n">
+      <c r="N31" s="25" t="n">
         <v>1.49</v>
       </c>
-      <c r="O31" s="24" t="n">
+      <c r="O31" s="25" t="n">
         <v>5.888</v>
       </c>
-      <c r="P31" s="24" t="n">
+      <c r="P31" s="25" t="n">
         <v>0.404</v>
       </c>
-      <c r="Q31" s="24" t="n">
+      <c r="Q31" s="25" t="n">
         <v>1.596</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="n">
+      <c r="A32" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="23" t="n">
         <v>0.671</v>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="23" t="n">
         <v>3.592</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="23" t="n">
         <v>0.697</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="F32" s="23" t="n">
+      <c r="F32" s="24" t="n">
         <v>0.9619</v>
       </c>
-      <c r="G32" s="23" t="n">
+      <c r="G32" s="24" t="n">
         <v>1.0396</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="H32" s="23" t="n">
         <v>0.491</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="I32" s="23" t="n">
         <v>1.433</v>
       </c>
-      <c r="J32" s="22" t="n">
+      <c r="J32" s="23" t="n">
         <v>0.51</v>
       </c>
-      <c r="K32" s="22" t="n">
+      <c r="K32" s="23" t="n">
         <v>1.49</v>
       </c>
-      <c r="L32" s="22" t="n">
+      <c r="L32" s="23" t="n">
         <v>3.735</v>
       </c>
-      <c r="M32" s="23" t="n">
+      <c r="M32" s="24" t="n">
         <v>0.2677</v>
       </c>
-      <c r="N32" s="24" t="n">
+      <c r="N32" s="25" t="n">
         <v>1.548</v>
       </c>
-      <c r="O32" s="24" t="n">
+      <c r="O32" s="25" t="n">
         <v>5.922</v>
       </c>
-      <c r="P32" s="24" t="n">
+      <c r="P32" s="25" t="n">
         <v>0.414</v>
       </c>
-      <c r="Q32" s="24" t="n">
+      <c r="Q32" s="25" t="n">
         <v>1.586</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n">
+      <c r="A33" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="23" t="n">
         <v>0.655</v>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>3.639</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="23" t="n">
         <v>0.679</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="23" t="n">
         <v>0.173</v>
       </c>
-      <c r="F33" s="23" t="n">
+      <c r="F33" s="24" t="n">
         <v>0.9638</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="24" t="n">
         <v>1.0376</v>
       </c>
-      <c r="H33" s="22" t="n">
+      <c r="H33" s="23" t="n">
         <v>0.504</v>
       </c>
-      <c r="I33" s="22" t="n">
+      <c r="I33" s="23" t="n">
         <v>1.424</v>
       </c>
-      <c r="J33" s="22" t="n">
+      <c r="J33" s="23" t="n">
         <v>0.523</v>
       </c>
-      <c r="K33" s="22" t="n">
+      <c r="K33" s="23" t="n">
         <v>1.477</v>
       </c>
-      <c r="L33" s="22" t="n">
+      <c r="L33" s="23" t="n">
         <v>3.778</v>
       </c>
-      <c r="M33" s="23" t="n">
+      <c r="M33" s="24" t="n">
         <v>0.2647</v>
       </c>
-      <c r="N33" s="24" t="n">
+      <c r="N33" s="25" t="n">
         <v>1.606</v>
       </c>
-      <c r="O33" s="24" t="n">
+      <c r="O33" s="25" t="n">
         <v>5.95</v>
       </c>
-      <c r="P33" s="22" t="n">
+      <c r="P33" s="23" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q33" s="22" t="n">
+      <c r="Q33" s="23" t="n">
         <v>1.575</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="n">
+      <c r="A34" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="23" t="n">
         <v>0.64</v>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="23" t="n">
         <v>3.684</v>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="23" t="n">
         <v>0.662</v>
       </c>
-      <c r="E34" s="22" t="n">
+      <c r="E34" s="23" t="n">
         <v>0.167</v>
       </c>
-      <c r="F34" s="23" t="n">
+      <c r="F34" s="24" t="n">
         <v>0.9655</v>
       </c>
-      <c r="G34" s="23" t="n">
+      <c r="G34" s="24" t="n">
         <v>1.0358</v>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="H34" s="23" t="n">
         <v>0.516</v>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="I34" s="23" t="n">
         <v>1.415</v>
       </c>
-      <c r="J34" s="22" t="n">
+      <c r="J34" s="23" t="n">
         <v>0.534</v>
       </c>
-      <c r="K34" s="22" t="n">
+      <c r="K34" s="23" t="n">
         <v>1.466</v>
       </c>
-      <c r="L34" s="22" t="n">
+      <c r="L34" s="23" t="n">
         <v>3.819</v>
       </c>
-      <c r="M34" s="23" t="n">
+      <c r="M34" s="24" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N34" s="22" t="n">
+      <c r="N34" s="23" t="n">
         <v>1.659</v>
       </c>
-      <c r="O34" s="22" t="n">
+      <c r="O34" s="23" t="n">
         <v>5.979</v>
       </c>
-      <c r="P34" s="22" t="n">
+      <c r="P34" s="23" t="n">
         <v>0.434</v>
       </c>
-      <c r="Q34" s="22" t="n">
+      <c r="Q34" s="23" t="n">
         <v>1.566</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="n">
+      <c r="A35" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="23" t="n">
         <v>0.626</v>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="23" t="n">
         <v>3.729</v>
       </c>
-      <c r="D35" s="22" t="n">
+      <c r="D35" s="23" t="n">
         <v>0.647</v>
       </c>
-      <c r="E35" s="22" t="n">
+      <c r="E35" s="23" t="n">
         <v>0.162</v>
       </c>
-      <c r="F35" s="23" t="n">
+      <c r="F35" s="24" t="n">
         <v>0.967</v>
       </c>
-      <c r="G35" s="23" t="n">
+      <c r="G35" s="24" t="n">
         <v>1.0342</v>
       </c>
-      <c r="H35" s="22" t="n">
+      <c r="H35" s="23" t="n">
         <v>0.527</v>
       </c>
-      <c r="I35" s="22" t="n">
+      <c r="I35" s="23" t="n">
         <v>1.407</v>
       </c>
-      <c r="J35" s="22" t="n">
+      <c r="J35" s="23" t="n">
         <v>0.545</v>
       </c>
-      <c r="K35" s="22" t="n">
+      <c r="K35" s="23" t="n">
         <v>1.455</v>
       </c>
-      <c r="L35" s="22" t="n">
+      <c r="L35" s="23" t="n">
         <v>3.858</v>
       </c>
-      <c r="M35" s="23" t="n">
+      <c r="M35" s="24" t="n">
         <v>0.2592</v>
       </c>
-      <c r="N35" s="22" t="n">
+      <c r="N35" s="23" t="n">
         <v>1.71</v>
       </c>
-      <c r="O35" s="22" t="n">
+      <c r="O35" s="23" t="n">
         <v>6.006</v>
       </c>
-      <c r="P35" s="22" t="n">
+      <c r="P35" s="23" t="n">
         <v>0.443</v>
       </c>
-      <c r="Q35" s="22" t="n">
+      <c r="Q35" s="23" t="n">
         <v>1.557</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="n">
+      <c r="A36" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="22" t="n">
+      <c r="B36" s="23" t="n">
         <v>0.612</v>
       </c>
-      <c r="C36" s="22" t="n">
+      <c r="C36" s="23" t="n">
         <v>3.773</v>
       </c>
-      <c r="D36" s="22" t="n">
+      <c r="D36" s="23" t="n">
         <v>0.632</v>
       </c>
-      <c r="E36" s="22" t="n">
+      <c r="E36" s="23" t="n">
         <v>0.157</v>
       </c>
-      <c r="F36" s="23" t="n">
+      <c r="F36" s="24" t="n">
         <v>0.9684</v>
       </c>
-      <c r="G36" s="23" t="n">
+      <c r="G36" s="24" t="n">
         <v>1.0327</v>
       </c>
-      <c r="H36" s="22" t="n">
+      <c r="H36" s="23" t="n">
         <v>0.538</v>
       </c>
-      <c r="I36" s="22" t="n">
+      <c r="I36" s="23" t="n">
         <v>1.399</v>
       </c>
-      <c r="J36" s="22" t="n">
+      <c r="J36" s="23" t="n">
         <v>0.555</v>
       </c>
-      <c r="K36" s="22" t="n">
+      <c r="K36" s="23" t="n">
         <v>1.445</v>
       </c>
-      <c r="L36" s="22" t="n">
+      <c r="L36" s="23" t="n">
         <v>3.895</v>
       </c>
-      <c r="M36" s="23" t="n">
+      <c r="M36" s="24" t="n">
         <v>0.2567</v>
       </c>
-      <c r="N36" s="22" t="n">
+      <c r="N36" s="23" t="n">
         <v>1.759</v>
       </c>
-      <c r="O36" s="22" t="n">
+      <c r="O36" s="23" t="n">
         <v>6.031</v>
       </c>
-      <c r="P36" s="24" t="n">
+      <c r="P36" s="25" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q36" s="22" t="n">
+      <c r="Q36" s="23" t="n">
         <v>1.548</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="n">
+      <c r="A37" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="22" t="n">
+      <c r="B37" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="C37" s="22" t="n">
+      <c r="C37" s="23" t="n">
         <v>3.816</v>
       </c>
-      <c r="D37" s="22" t="n">
+      <c r="D37" s="23" t="n">
         <v>0.619</v>
       </c>
-      <c r="E37" s="22" t="n">
+      <c r="E37" s="23" t="n">
         <v>0.153</v>
       </c>
-      <c r="F37" s="25" t="n">
+      <c r="F37" s="26" t="n">
         <v>0.9696</v>
       </c>
-      <c r="G37" s="23" t="n">
+      <c r="G37" s="24" t="n">
         <v>1.0313</v>
       </c>
-      <c r="H37" s="22" t="n">
+      <c r="H37" s="23" t="n">
         <v>0.548</v>
       </c>
-      <c r="I37" s="22" t="n">
+      <c r="I37" s="23" t="n">
         <v>1.392</v>
       </c>
-      <c r="J37" s="22" t="n">
+      <c r="J37" s="23" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="K37" s="22" t="n">
+      <c r="K37" s="23" t="n">
         <v>1.435</v>
       </c>
-      <c r="L37" s="22" t="n">
+      <c r="L37" s="23" t="n">
         <v>3.931</v>
       </c>
-      <c r="M37" s="23" t="n">
+      <c r="M37" s="24" t="n">
         <v>0.2544</v>
       </c>
-      <c r="N37" s="24" t="n">
+      <c r="N37" s="25" t="n">
         <v>1.804</v>
       </c>
-      <c r="O37" s="24" t="n">
+      <c r="O37" s="25" t="n">
         <v>6.058</v>
       </c>
-      <c r="P37" s="22" t="n">
+      <c r="P37" s="23" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q37" s="22" t="n">
+      <c r="Q37" s="23" t="n">
         <v>1.541</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>&gt;25</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr"/>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr"/>
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr"/>
-      <c r="F38" s="23" t="n">
+      <c r="E38" s="27" t="inlineStr"/>
+      <c r="F38" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="23" t="n">
+      <c r="G38" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="H38" s="27" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="I38" s="26" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="J38" s="26" t="inlineStr">
+      <c r="J38" s="27" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="K38" s="26" t="inlineStr">
+      <c r="K38" s="27" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L38" s="26" t="inlineStr"/>
-      <c r="M38" s="26" t="inlineStr"/>
-      <c r="N38" s="26" t="inlineStr"/>
-      <c r="O38" s="26" t="inlineStr"/>
-      <c r="P38" s="26" t="inlineStr"/>
-      <c r="Q38" s="26" t="inlineStr"/>
+      <c r="L38" s="27" t="inlineStr"/>
+      <c r="M38" s="27" t="inlineStr"/>
+      <c r="N38" s="27" t="inlineStr"/>
+      <c r="O38" s="27" t="inlineStr"/>
+      <c r="P38" s="27" t="inlineStr"/>
+      <c r="Q38" s="27" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Table A - Bias Correction Factors For Estimating Standard Deviations</t>
         </is>
@@ -3663,7 +4245,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>USED for c4 and d3 (Table 18 does not give them). Reference for d2 and c2.</t>
         </is>
@@ -3697,585 +4279,585 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="n">
+      <c r="A44" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="23" t="n">
         <v>1.128</v>
       </c>
-      <c r="C44" s="23" t="n">
+      <c r="C44" s="24" t="n">
         <v>0.5642</v>
       </c>
-      <c r="D44" s="23" t="n">
+      <c r="D44" s="24" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="E44" s="23" t="n">
+      <c r="E44" s="24" t="n">
         <v>0.8525</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="n">
+      <c r="A45" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="22" t="n">
+      <c r="B45" s="23" t="n">
         <v>1.693</v>
       </c>
-      <c r="C45" s="23" t="n">
+      <c r="C45" s="24" t="n">
         <v>0.7236</v>
       </c>
-      <c r="D45" s="23" t="n">
+      <c r="D45" s="24" t="n">
         <v>0.8862</v>
       </c>
-      <c r="E45" s="23" t="n">
+      <c r="E45" s="24" t="n">
         <v>0.8884</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="n">
+      <c r="A46" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="22" t="n">
+      <c r="B46" s="23" t="n">
         <v>2.059</v>
       </c>
-      <c r="C46" s="23" t="n">
+      <c r="C46" s="24" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="D46" s="23" t="n">
+      <c r="D46" s="24" t="n">
         <v>0.9213</v>
       </c>
-      <c r="E46" s="23" t="n">
+      <c r="E46" s="24" t="n">
         <v>0.8798</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="n">
+      <c r="A47" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="22" t="n">
+      <c r="B47" s="23" t="n">
         <v>2.326</v>
       </c>
-      <c r="C47" s="23" t="n">
+      <c r="C47" s="24" t="n">
         <v>0.8407</v>
       </c>
-      <c r="D47" s="23" t="n">
+      <c r="D47" s="24" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E47" s="23" t="n">
+      <c r="E47" s="24" t="n">
         <v>0.8641</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="n">
+      <c r="A48" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="22" t="n">
+      <c r="B48" s="23" t="n">
         <v>2.534</v>
       </c>
-      <c r="C48" s="23" t="n">
+      <c r="C48" s="24" t="n">
         <v>0.8686</v>
       </c>
-      <c r="D48" s="23" t="n">
+      <c r="D48" s="24" t="n">
         <v>0.9515</v>
       </c>
-      <c r="E48" s="23" t="n">
+      <c r="E48" s="24" t="n">
         <v>0.848</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="n">
+      <c r="A49" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="22" t="n">
+      <c r="B49" s="23" t="n">
         <v>2.704</v>
       </c>
-      <c r="C49" s="23" t="n">
+      <c r="C49" s="24" t="n">
         <v>0.8882</v>
       </c>
-      <c r="D49" s="23" t="n">
+      <c r="D49" s="24" t="n">
         <v>0.9594</v>
       </c>
-      <c r="E49" s="23" t="n">
+      <c r="E49" s="24" t="n">
         <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="n">
+      <c r="A50" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="22" t="n">
+      <c r="B50" s="23" t="n">
         <v>2.847</v>
       </c>
-      <c r="C50" s="23" t="n">
+      <c r="C50" s="24" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="D50" s="23" t="n">
+      <c r="D50" s="24" t="n">
         <v>0.965</v>
       </c>
-      <c r="E50" s="23" t="n">
+      <c r="E50" s="24" t="n">
         <v>0.8198</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="n">
+      <c r="A51" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="22" t="n">
+      <c r="B51" s="23" t="n">
         <v>2.97</v>
       </c>
-      <c r="C51" s="23" t="n">
+      <c r="C51" s="24" t="n">
         <v>0.9139</v>
       </c>
-      <c r="D51" s="23" t="n">
+      <c r="D51" s="24" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="E51" s="23" t="n">
+      <c r="E51" s="24" t="n">
         <v>0.8078</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="n">
+      <c r="A52" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="22" t="n">
+      <c r="B52" s="23" t="n">
         <v>3.078</v>
       </c>
-      <c r="C52" s="23" t="n">
+      <c r="C52" s="24" t="n">
         <v>0.9227</v>
       </c>
-      <c r="D52" s="23" t="n">
+      <c r="D52" s="24" t="n">
         <v>0.9727</v>
       </c>
-      <c r="E52" s="23" t="n">
+      <c r="E52" s="24" t="n">
         <v>0.7971</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="n">
+      <c r="A53" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="22" t="n">
+      <c r="B53" s="23" t="n">
         <v>3.173</v>
       </c>
-      <c r="C53" s="23" t="n">
+      <c r="C53" s="24" t="n">
         <v>0.93</v>
       </c>
-      <c r="D53" s="23" t="n">
+      <c r="D53" s="24" t="n">
         <v>0.9754</v>
       </c>
-      <c r="E53" s="23" t="n">
+      <c r="E53" s="24" t="n">
         <v>0.7873</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="n">
+      <c r="A54" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="22" t="n">
+      <c r="B54" s="23" t="n">
         <v>3.258</v>
       </c>
-      <c r="C54" s="23" t="n">
+      <c r="C54" s="24" t="n">
         <v>0.9359</v>
       </c>
-      <c r="D54" s="23" t="n">
+      <c r="D54" s="24" t="n">
         <v>0.9776</v>
       </c>
-      <c r="E54" s="25" t="n">
+      <c r="E54" s="26" t="n">
         <v>0.7785</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="n">
+      <c r="A55" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="22" t="n">
+      <c r="B55" s="23" t="n">
         <v>3.336</v>
       </c>
-      <c r="C55" s="23" t="n">
+      <c r="C55" s="24" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="D55" s="23" t="n">
+      <c r="D55" s="24" t="n">
         <v>0.9794</v>
       </c>
-      <c r="E55" s="23" t="n">
+      <c r="E55" s="24" t="n">
         <v>0.7704</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="n">
+      <c r="A56" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="22" t="n">
+      <c r="B56" s="23" t="n">
         <v>3.407</v>
       </c>
-      <c r="C56" s="23" t="n">
+      <c r="C56" s="24" t="n">
         <v>0.9453</v>
       </c>
-      <c r="D56" s="23" t="n">
+      <c r="D56" s="24" t="n">
         <v>0.981</v>
       </c>
-      <c r="E56" s="23" t="n">
+      <c r="E56" s="24" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="n">
+      <c r="A57" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="22" t="n">
+      <c r="B57" s="23" t="n">
         <v>3.472</v>
       </c>
-      <c r="C57" s="23" t="n">
+      <c r="C57" s="24" t="n">
         <v>0.949</v>
       </c>
-      <c r="D57" s="23" t="n">
+      <c r="D57" s="24" t="n">
         <v>0.9823</v>
       </c>
-      <c r="E57" s="23" t="n">
+      <c r="E57" s="24" t="n">
         <v>0.7562</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="n">
+      <c r="A58" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B58" s="22" t="n">
+      <c r="B58" s="23" t="n">
         <v>3.532</v>
       </c>
-      <c r="C58" s="23" t="n">
+      <c r="C58" s="24" t="n">
         <v>0.9523</v>
       </c>
-      <c r="D58" s="23" t="n">
+      <c r="D58" s="24" t="n">
         <v>0.9835</v>
       </c>
-      <c r="E58" s="23" t="n">
+      <c r="E58" s="24" t="n">
         <v>0.7499</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="n">
+      <c r="A59" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B59" s="22" t="n">
+      <c r="B59" s="23" t="n">
         <v>3.588</v>
       </c>
-      <c r="C59" s="23" t="n">
+      <c r="C59" s="24" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="D59" s="23" t="n">
+      <c r="D59" s="24" t="n">
         <v>0.9845</v>
       </c>
-      <c r="E59" s="23" t="n">
+      <c r="E59" s="24" t="n">
         <v>0.7441</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="n">
+      <c r="A60" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B60" s="22" t="n">
+      <c r="B60" s="23" t="n">
         <v>3.64</v>
       </c>
-      <c r="C60" s="23" t="n">
+      <c r="C60" s="24" t="n">
         <v>0.9576</v>
       </c>
-      <c r="D60" s="23" t="n">
+      <c r="D60" s="24" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="E60" s="23" t="n">
+      <c r="E60" s="24" t="n">
         <v>0.7386</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="21" t="n">
+      <c r="A61" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B61" s="22" t="n">
+      <c r="B61" s="23" t="n">
         <v>3.689</v>
       </c>
-      <c r="C61" s="23" t="n">
+      <c r="C61" s="24" t="n">
         <v>0.9599</v>
       </c>
-      <c r="D61" s="23" t="n">
+      <c r="D61" s="24" t="n">
         <v>0.9862</v>
       </c>
-      <c r="E61" s="23" t="n">
+      <c r="E61" s="24" t="n">
         <v>0.7335</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="21" t="n">
+      <c r="A62" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B62" s="22" t="n">
+      <c r="B62" s="23" t="n">
         <v>3.735</v>
       </c>
-      <c r="C62" s="23" t="n">
+      <c r="C62" s="24" t="n">
         <v>0.9619</v>
       </c>
-      <c r="D62" s="23" t="n">
+      <c r="D62" s="24" t="n">
         <v>0.9869</v>
       </c>
-      <c r="E62" s="23" t="n">
+      <c r="E62" s="24" t="n">
         <v>0.7287</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="n">
+      <c r="A63" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="22" t="n">
+      <c r="B63" s="23" t="n">
         <v>3.778</v>
       </c>
-      <c r="C63" s="23" t="n">
+      <c r="C63" s="24" t="n">
         <v>0.9638</v>
       </c>
-      <c r="D63" s="23" t="n">
+      <c r="D63" s="24" t="n">
         <v>0.9876</v>
       </c>
-      <c r="E63" s="25" t="n">
+      <c r="E63" s="26" t="n">
         <v>0.7272</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="21" t="n">
+      <c r="A64" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B64" s="22" t="n">
+      <c r="B64" s="23" t="n">
         <v>3.819</v>
       </c>
-      <c r="C64" s="23" t="n">
+      <c r="C64" s="24" t="n">
         <v>0.9655</v>
       </c>
-      <c r="D64" s="23" t="n">
+      <c r="D64" s="24" t="n">
         <v>0.9882</v>
       </c>
-      <c r="E64" s="23" t="n">
+      <c r="E64" s="24" t="n">
         <v>0.7199</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="21" t="n">
+      <c r="A65" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="22" t="n">
+      <c r="B65" s="23" t="n">
         <v>3.858</v>
       </c>
-      <c r="C65" s="23" t="n">
+      <c r="C65" s="24" t="n">
         <v>0.967</v>
       </c>
-      <c r="D65" s="23" t="n">
+      <c r="D65" s="24" t="n">
         <v>0.9887</v>
       </c>
-      <c r="E65" s="23" t="n">
+      <c r="E65" s="24" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="n">
+      <c r="A66" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="22" t="n">
+      <c r="B66" s="23" t="n">
         <v>3.895</v>
       </c>
-      <c r="C66" s="23" t="n">
+      <c r="C66" s="24" t="n">
         <v>0.9684</v>
       </c>
-      <c r="D66" s="23" t="n">
+      <c r="D66" s="24" t="n">
         <v>0.9892</v>
       </c>
-      <c r="E66" s="23" t="n">
+      <c r="E66" s="24" t="n">
         <v>0.7121</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="21" t="n">
+      <c r="A67" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B67" s="22" t="n">
+      <c r="B67" s="23" t="n">
         <v>3.931</v>
       </c>
-      <c r="C67" s="25" t="n">
+      <c r="C67" s="26" t="n">
         <v>0.9695</v>
       </c>
-      <c r="D67" s="23" t="n">
+      <c r="D67" s="24" t="n">
         <v>0.9896</v>
       </c>
-      <c r="E67" s="23" t="n">
+      <c r="E67" s="24" t="n">
         <v>0.7084</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="21" t="n">
+      <c r="A68" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="B68" s="22" t="n">
+      <c r="B68" s="23" t="n">
         <v>4.086</v>
       </c>
-      <c r="C68" s="23" t="n">
+      <c r="C68" s="24" t="n">
         <v>0.9748</v>
       </c>
-      <c r="D68" s="23" t="n">
+      <c r="D68" s="24" t="n">
         <v>0.9915</v>
       </c>
-      <c r="E68" s="23" t="n">
+      <c r="E68" s="24" t="n">
         <v>0.6927</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="21" t="n">
+      <c r="A69" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="B69" s="22" t="n">
+      <c r="B69" s="23" t="n">
         <v>4.213</v>
       </c>
-      <c r="C69" s="23" t="n">
+      <c r="C69" s="24" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D69" s="23" t="n">
+      <c r="D69" s="24" t="n">
         <v>0.9927</v>
       </c>
-      <c r="E69" s="23" t="n">
+      <c r="E69" s="24" t="n">
         <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="21" t="n">
+      <c r="A70" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="B70" s="22" t="n">
+      <c r="B70" s="23" t="n">
         <v>4.322</v>
       </c>
-      <c r="C70" s="23" t="n">
+      <c r="C70" s="24" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D70" s="23" t="n">
+      <c r="D70" s="24" t="n">
         <v>0.9936</v>
       </c>
-      <c r="E70" s="23" t="n">
+      <c r="E70" s="24" t="n">
         <v>0.6692</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="21" t="n">
+      <c r="A71" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="B71" s="22" t="n">
+      <c r="B71" s="23" t="n">
         <v>4.415</v>
       </c>
-      <c r="C71" s="23" t="n">
+      <c r="C71" s="24" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D71" s="23" t="n">
+      <c r="D71" s="24" t="n">
         <v>0.9943</v>
       </c>
-      <c r="E71" s="23" t="n">
+      <c r="E71" s="24" t="n">
         <v>0.6601</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="21" t="n">
+      <c r="A72" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="B72" s="22" t="n">
+      <c r="B72" s="23" t="n">
         <v>4.498</v>
       </c>
-      <c r="C72" s="23" t="n">
+      <c r="C72" s="24" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D72" s="23" t="n">
+      <c r="D72" s="24" t="n">
         <v>0.9949</v>
       </c>
-      <c r="E72" s="23" t="n">
+      <c r="E72" s="24" t="n">
         <v>0.6521</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="21" t="n">
+      <c r="A73" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="B73" s="22" t="n">
+      <c r="B73" s="23" t="n">
         <v>4.639</v>
       </c>
-      <c r="C73" s="23" t="n">
+      <c r="C73" s="24" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D73" s="23" t="n">
+      <c r="D73" s="24" t="n">
         <v>0.9957</v>
       </c>
-      <c r="E73" s="23" t="n">
+      <c r="E73" s="24" t="n">
         <v>0.6389</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="21" t="n">
+      <c r="A74" s="22" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="22" t="n">
+      <c r="B74" s="23" t="n">
         <v>4.755</v>
       </c>
-      <c r="C74" s="23" t="n">
+      <c r="C74" s="24" t="n">
         <v>0.9892</v>
       </c>
-      <c r="D74" s="23" t="n">
+      <c r="D74" s="24" t="n">
         <v>0.9963</v>
       </c>
-      <c r="E74" s="23" t="n">
+      <c r="E74" s="24" t="n">
         <v>0.6283</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="21" t="n">
+      <c r="A75" s="22" t="n">
         <v>80</v>
       </c>
-      <c r="B75" s="22" t="n">
+      <c r="B75" s="23" t="n">
         <v>4.854</v>
       </c>
-      <c r="C75" s="23" t="n">
+      <c r="C75" s="24" t="n">
         <v>0.9906</v>
       </c>
-      <c r="D75" s="23" t="n">
+      <c r="D75" s="24" t="n">
         <v>0.9968</v>
       </c>
-      <c r="E75" s="23" t="n">
+      <c r="E75" s="24" t="n">
         <v>0.6194</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="21" t="n">
+      <c r="A76" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="B76" s="22" t="n">
+      <c r="B76" s="23" t="n">
         <v>4.939</v>
       </c>
-      <c r="C76" s="23" t="n">
+      <c r="C76" s="24" t="n">
         <v>0.9916</v>
       </c>
-      <c r="D76" s="23" t="n">
+      <c r="D76" s="24" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E76" s="23" t="n">
+      <c r="E76" s="24" t="n">
         <v>0.6118</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="21" t="n">
+      <c r="A77" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="B77" s="22" t="n">
+      <c r="B77" s="23" t="n">
         <v>5.015</v>
       </c>
-      <c r="C77" s="23" t="n">
+      <c r="C77" s="24" t="n">
         <v>0.9925</v>
       </c>
-      <c r="D77" s="23" t="n">
+      <c r="D77" s="24" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="E77" s="23" t="n">
+      <c r="E77" s="24" t="n">
         <v>0.6052</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>Control Chart Constants - Chart for Average &amp; Chart for Standard Deviations (Six Sigma Demystified, 2nd ed.)</t>
         </is>
@@ -4289,7 +4871,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="20" t="inlineStr">
+      <c r="A81" s="21" t="inlineStr">
         <is>
           <t>USED for A3, B5 and B6 (Table 18 and Table A do not give them). Reference otherwise.</t>
         </is>
@@ -4348,791 +4930,791 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="21" t="n">
+      <c r="A83" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="22" t="n">
+      <c r="B83" s="23" t="n">
         <v>2.121</v>
       </c>
-      <c r="C83" s="22" t="n">
+      <c r="C83" s="23" t="n">
         <v>1.88</v>
       </c>
-      <c r="D83" s="22" t="n">
+      <c r="D83" s="23" t="n">
         <v>2.659</v>
       </c>
-      <c r="E83" s="23" t="n">
+      <c r="E83" s="24" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="F83" s="23" t="n">
+      <c r="F83" s="24" t="n">
         <v>1.2533</v>
       </c>
-      <c r="G83" s="21" t="n">
+      <c r="G83" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="22" t="n">
+      <c r="H83" s="23" t="n">
         <v>3.267</v>
       </c>
-      <c r="I83" s="21" t="n">
+      <c r="I83" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="22" t="n">
+      <c r="J83" s="23" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="21" t="n">
+      <c r="A84" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="B84" s="22" t="n">
+      <c r="B84" s="23" t="n">
         <v>2.606</v>
       </c>
-      <c r="C84" s="26" t="inlineStr"/>
-      <c r="D84" s="26" t="inlineStr"/>
-      <c r="E84" s="26" t="inlineStr"/>
-      <c r="F84" s="26" t="inlineStr"/>
-      <c r="G84" s="26" t="inlineStr"/>
-      <c r="H84" s="26" t="inlineStr"/>
-      <c r="I84" s="26" t="inlineStr"/>
-      <c r="J84" s="26" t="inlineStr"/>
+      <c r="C84" s="27" t="inlineStr"/>
+      <c r="D84" s="27" t="inlineStr"/>
+      <c r="E84" s="27" t="inlineStr"/>
+      <c r="F84" s="27" t="inlineStr"/>
+      <c r="G84" s="27" t="inlineStr"/>
+      <c r="H84" s="27" t="inlineStr"/>
+      <c r="I84" s="27" t="inlineStr"/>
+      <c r="J84" s="27" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="21" t="n">
+      <c r="A85" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="22" t="n">
+      <c r="B85" s="23" t="n">
         <v>1.732</v>
       </c>
-      <c r="C85" s="22" t="n">
+      <c r="C85" s="23" t="n">
         <v>1.023</v>
       </c>
-      <c r="D85" s="22" t="n">
+      <c r="D85" s="23" t="n">
         <v>1.954</v>
       </c>
-      <c r="E85" s="23" t="n">
+      <c r="E85" s="24" t="n">
         <v>0.8862</v>
       </c>
-      <c r="F85" s="23" t="n">
+      <c r="F85" s="24" t="n">
         <v>1.1284</v>
       </c>
-      <c r="G85" s="21" t="n">
+      <c r="G85" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="22" t="n">
+      <c r="H85" s="23" t="n">
         <v>2.568</v>
       </c>
-      <c r="I85" s="21" t="n">
+      <c r="I85" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="22" t="n">
+      <c r="J85" s="23" t="n">
         <v>2.276</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="21" t="n">
+      <c r="A86" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="22" t="n">
+      <c r="B86" s="23" t="n">
         <v>1.5</v>
       </c>
-      <c r="C86" s="22" t="n">
+      <c r="C86" s="23" t="n">
         <v>0.729</v>
       </c>
-      <c r="D86" s="22" t="n">
+      <c r="D86" s="23" t="n">
         <v>1.628</v>
       </c>
-      <c r="E86" s="23" t="n">
+      <c r="E86" s="24" t="n">
         <v>0.9213</v>
       </c>
-      <c r="F86" s="23" t="n">
+      <c r="F86" s="24" t="n">
         <v>1.0854</v>
       </c>
-      <c r="G86" s="21" t="n">
+      <c r="G86" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="22" t="n">
+      <c r="H86" s="23" t="n">
         <v>2.266</v>
       </c>
-      <c r="I86" s="21" t="n">
+      <c r="I86" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="22" t="n">
+      <c r="J86" s="23" t="n">
         <v>2.088</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="21" t="n">
+      <c r="A87" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="22" t="n">
+      <c r="B87" s="23" t="n">
         <v>1.342</v>
       </c>
-      <c r="C87" s="22" t="n">
+      <c r="C87" s="23" t="n">
         <v>0.577</v>
       </c>
-      <c r="D87" s="22" t="n">
+      <c r="D87" s="23" t="n">
         <v>1.427</v>
       </c>
-      <c r="E87" s="23" t="n">
+      <c r="E87" s="24" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F87" s="23" t="n">
+      <c r="F87" s="24" t="n">
         <v>1.0638</v>
       </c>
-      <c r="G87" s="21" t="n">
+      <c r="G87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="22" t="n">
+      <c r="H87" s="23" t="n">
         <v>2.089</v>
       </c>
-      <c r="I87" s="21" t="n">
+      <c r="I87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="22" t="n">
+      <c r="J87" s="23" t="n">
         <v>1.964</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="21" t="n">
+      <c r="A88" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B88" s="22" t="n">
+      <c r="B88" s="23" t="n">
         <v>1.225</v>
       </c>
-      <c r="C88" s="22" t="n">
+      <c r="C88" s="23" t="n">
         <v>0.483</v>
       </c>
-      <c r="D88" s="22" t="n">
+      <c r="D88" s="23" t="n">
         <v>1.287</v>
       </c>
-      <c r="E88" s="23" t="n">
+      <c r="E88" s="24" t="n">
         <v>0.9515</v>
       </c>
-      <c r="F88" s="23" t="n">
+      <c r="F88" s="24" t="n">
         <v>1.051</v>
       </c>
-      <c r="G88" s="22" t="n">
+      <c r="G88" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="H88" s="22" t="n">
+      <c r="H88" s="23" t="n">
         <v>1.97</v>
       </c>
-      <c r="I88" s="22" t="n">
+      <c r="I88" s="23" t="n">
         <v>0.029</v>
       </c>
-      <c r="J88" s="22" t="n">
+      <c r="J88" s="23" t="n">
         <v>1.874</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="21" t="n">
+      <c r="A89" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B89" s="22" t="n">
+      <c r="B89" s="23" t="n">
         <v>1.134</v>
       </c>
-      <c r="C89" s="22" t="n">
+      <c r="C89" s="23" t="n">
         <v>0.419</v>
       </c>
-      <c r="D89" s="22" t="n">
+      <c r="D89" s="23" t="n">
         <v>1.182</v>
       </c>
-      <c r="E89" s="23" t="n">
+      <c r="E89" s="24" t="n">
         <v>0.9594</v>
       </c>
-      <c r="F89" s="23" t="n">
+      <c r="F89" s="24" t="n">
         <v>1.0423</v>
       </c>
-      <c r="G89" s="22" t="n">
+      <c r="G89" s="23" t="n">
         <v>0.118</v>
       </c>
-      <c r="H89" s="22" t="n">
+      <c r="H89" s="23" t="n">
         <v>1.882</v>
       </c>
-      <c r="I89" s="22" t="n">
+      <c r="I89" s="23" t="n">
         <v>0.113</v>
       </c>
-      <c r="J89" s="22" t="n">
+      <c r="J89" s="23" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="21" t="n">
+      <c r="A90" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="22" t="n">
+      <c r="B90" s="23" t="n">
         <v>1.061</v>
       </c>
-      <c r="C90" s="22" t="n">
+      <c r="C90" s="23" t="n">
         <v>0.373</v>
       </c>
-      <c r="D90" s="22" t="n">
+      <c r="D90" s="23" t="n">
         <v>1.099</v>
       </c>
-      <c r="E90" s="23" t="n">
+      <c r="E90" s="24" t="n">
         <v>0.965</v>
       </c>
-      <c r="F90" s="23" t="n">
+      <c r="F90" s="24" t="n">
         <v>1.0363</v>
       </c>
-      <c r="G90" s="22" t="n">
+      <c r="G90" s="23" t="n">
         <v>0.185</v>
       </c>
-      <c r="H90" s="22" t="n">
+      <c r="H90" s="23" t="n">
         <v>1.815</v>
       </c>
-      <c r="I90" s="22" t="n">
+      <c r="I90" s="23" t="n">
         <v>0.179</v>
       </c>
-      <c r="J90" s="22" t="n">
+      <c r="J90" s="23" t="n">
         <v>1.751</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="21" t="n">
+      <c r="A91" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="22" t="n">
+      <c r="B91" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="22" t="n">
+      <c r="C91" s="23" t="n">
         <v>0.337</v>
       </c>
-      <c r="D91" s="22" t="n">
+      <c r="D91" s="23" t="n">
         <v>1.032</v>
       </c>
-      <c r="E91" s="23" t="n">
+      <c r="E91" s="24" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="F91" s="23" t="n">
+      <c r="F91" s="24" t="n">
         <v>1.0317</v>
       </c>
-      <c r="G91" s="22" t="n">
+      <c r="G91" s="23" t="n">
         <v>0.239</v>
       </c>
-      <c r="H91" s="22" t="n">
+      <c r="H91" s="23" t="n">
         <v>1.761</v>
       </c>
-      <c r="I91" s="22" t="n">
+      <c r="I91" s="23" t="n">
         <v>0.232</v>
       </c>
-      <c r="J91" s="22" t="n">
+      <c r="J91" s="23" t="n">
         <v>1.707</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="21" t="n">
+      <c r="A92" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B92" s="22" t="n">
+      <c r="B92" s="23" t="n">
         <v>0.949</v>
       </c>
-      <c r="C92" s="22" t="n">
+      <c r="C92" s="23" t="n">
         <v>0.308</v>
       </c>
-      <c r="D92" s="22" t="n">
+      <c r="D92" s="23" t="n">
         <v>0.975</v>
       </c>
-      <c r="E92" s="23" t="n">
+      <c r="E92" s="24" t="n">
         <v>0.9727</v>
       </c>
-      <c r="F92" s="23" t="n">
+      <c r="F92" s="24" t="n">
         <v>1.0281</v>
       </c>
-      <c r="G92" s="22" t="n">
+      <c r="G92" s="23" t="n">
         <v>0.284</v>
       </c>
-      <c r="H92" s="22" t="n">
+      <c r="H92" s="23" t="n">
         <v>1.716</v>
       </c>
-      <c r="I92" s="22" t="n">
+      <c r="I92" s="23" t="n">
         <v>0.276</v>
       </c>
-      <c r="J92" s="22" t="n">
+      <c r="J92" s="23" t="n">
         <v>1.669</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="21" t="n">
+      <c r="A93" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B93" s="22" t="n">
+      <c r="B93" s="23" t="n">
         <v>0.905</v>
       </c>
-      <c r="C93" s="22" t="n">
+      <c r="C93" s="23" t="n">
         <v>0.285</v>
       </c>
-      <c r="D93" s="22" t="n">
+      <c r="D93" s="23" t="n">
         <v>0.927</v>
       </c>
-      <c r="E93" s="23" t="n">
+      <c r="E93" s="24" t="n">
         <v>0.9754</v>
       </c>
-      <c r="F93" s="23" t="n">
+      <c r="F93" s="24" t="n">
         <v>1.0252</v>
       </c>
-      <c r="G93" s="22" t="n">
+      <c r="G93" s="23" t="n">
         <v>0.321</v>
       </c>
-      <c r="H93" s="22" t="n">
+      <c r="H93" s="23" t="n">
         <v>1.679</v>
       </c>
-      <c r="I93" s="22" t="n">
+      <c r="I93" s="23" t="n">
         <v>0.313</v>
       </c>
-      <c r="J93" s="22" t="n">
+      <c r="J93" s="23" t="n">
         <v>1.637</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="21" t="n">
+      <c r="A94" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B94" s="22" t="n">
+      <c r="B94" s="23" t="n">
         <v>0.866</v>
       </c>
-      <c r="C94" s="22" t="n">
+      <c r="C94" s="23" t="n">
         <v>0.266</v>
       </c>
-      <c r="D94" s="22" t="n">
+      <c r="D94" s="23" t="n">
         <v>0.886</v>
       </c>
-      <c r="E94" s="23" t="n">
+      <c r="E94" s="24" t="n">
         <v>0.9776</v>
       </c>
-      <c r="F94" s="23" t="n">
+      <c r="F94" s="24" t="n">
         <v>1.0229</v>
       </c>
-      <c r="G94" s="22" t="n">
+      <c r="G94" s="23" t="n">
         <v>0.354</v>
       </c>
-      <c r="H94" s="22" t="n">
+      <c r="H94" s="23" t="n">
         <v>1.646</v>
       </c>
-      <c r="I94" s="22" t="n">
+      <c r="I94" s="23" t="n">
         <v>0.346</v>
       </c>
-      <c r="J94" s="22" t="n">
+      <c r="J94" s="23" t="n">
         <v>1.61</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="21" t="n">
+      <c r="A95" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B95" s="22" t="n">
+      <c r="B95" s="23" t="n">
         <v>0.832</v>
       </c>
-      <c r="C95" s="22" t="n">
+      <c r="C95" s="23" t="n">
         <v>0.249</v>
       </c>
-      <c r="D95" s="22" t="n">
+      <c r="D95" s="23" t="n">
         <v>0.85</v>
       </c>
-      <c r="E95" s="23" t="n">
+      <c r="E95" s="24" t="n">
         <v>0.9794</v>
       </c>
-      <c r="F95" s="23" t="n">
+      <c r="F95" s="24" t="n">
         <v>1.021</v>
       </c>
-      <c r="G95" s="22" t="n">
+      <c r="G95" s="23" t="n">
         <v>0.382</v>
       </c>
-      <c r="H95" s="22" t="n">
+      <c r="H95" s="23" t="n">
         <v>1.618</v>
       </c>
-      <c r="I95" s="22" t="n">
+      <c r="I95" s="23" t="n">
         <v>0.374</v>
       </c>
-      <c r="J95" s="22" t="n">
+      <c r="J95" s="23" t="n">
         <v>1.585</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="21" t="n">
+      <c r="A96" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B96" s="22" t="n">
+      <c r="B96" s="23" t="n">
         <v>0.802</v>
       </c>
-      <c r="C96" s="22" t="n">
+      <c r="C96" s="23" t="n">
         <v>0.235</v>
       </c>
-      <c r="D96" s="22" t="n">
+      <c r="D96" s="23" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E96" s="23" t="n">
+      <c r="E96" s="24" t="n">
         <v>0.981</v>
       </c>
-      <c r="F96" s="23" t="n">
+      <c r="F96" s="24" t="n">
         <v>1.0194</v>
       </c>
-      <c r="G96" s="22" t="n">
+      <c r="G96" s="23" t="n">
         <v>0.406</v>
       </c>
-      <c r="H96" s="22" t="n">
+      <c r="H96" s="23" t="n">
         <v>1.594</v>
       </c>
-      <c r="I96" s="22" t="n">
+      <c r="I96" s="23" t="n">
         <v>0.399</v>
       </c>
-      <c r="J96" s="22" t="n">
+      <c r="J96" s="23" t="n">
         <v>1.563</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="21" t="n">
+      <c r="A97" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B97" s="22" t="n">
+      <c r="B97" s="23" t="n">
         <v>0.775</v>
       </c>
-      <c r="C97" s="22" t="n">
+      <c r="C97" s="23" t="n">
         <v>0.223</v>
       </c>
-      <c r="D97" s="22" t="n">
+      <c r="D97" s="23" t="n">
         <v>0.789</v>
       </c>
-      <c r="E97" s="23" t="n">
+      <c r="E97" s="24" t="n">
         <v>0.9823</v>
       </c>
-      <c r="F97" s="23" t="n">
+      <c r="F97" s="24" t="n">
         <v>1.018</v>
       </c>
-      <c r="G97" s="22" t="n">
+      <c r="G97" s="23" t="n">
         <v>0.428</v>
       </c>
-      <c r="H97" s="22" t="n">
+      <c r="H97" s="23" t="n">
         <v>1.572</v>
       </c>
-      <c r="I97" s="22" t="n">
+      <c r="I97" s="23" t="n">
         <v>0.421</v>
       </c>
-      <c r="J97" s="22" t="n">
+      <c r="J97" s="23" t="n">
         <v>1.544</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="21" t="n">
+      <c r="A98" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B98" s="22" t="n">
+      <c r="B98" s="23" t="n">
         <v>0.75</v>
       </c>
-      <c r="C98" s="22" t="n">
+      <c r="C98" s="23" t="n">
         <v>0.212</v>
       </c>
-      <c r="D98" s="22" t="n">
+      <c r="D98" s="23" t="n">
         <v>0.763</v>
       </c>
-      <c r="E98" s="23" t="n">
+      <c r="E98" s="24" t="n">
         <v>0.9835</v>
       </c>
-      <c r="F98" s="23" t="n">
+      <c r="F98" s="24" t="n">
         <v>1.0168</v>
       </c>
-      <c r="G98" s="22" t="n">
+      <c r="G98" s="23" t="n">
         <v>0.448</v>
       </c>
-      <c r="H98" s="22" t="n">
+      <c r="H98" s="23" t="n">
         <v>1.552</v>
       </c>
-      <c r="I98" s="22" t="n">
+      <c r="I98" s="23" t="n">
         <v>0.44</v>
       </c>
-      <c r="J98" s="22" t="n">
+      <c r="J98" s="23" t="n">
         <v>1.526</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="21" t="n">
+      <c r="A99" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="22" t="n">
+      <c r="B99" s="23" t="n">
         <v>0.728</v>
       </c>
-      <c r="C99" s="22" t="n">
+      <c r="C99" s="23" t="n">
         <v>0.203</v>
       </c>
-      <c r="D99" s="22" t="n">
+      <c r="D99" s="23" t="n">
         <v>0.739</v>
       </c>
-      <c r="E99" s="23" t="n">
+      <c r="E99" s="24" t="n">
         <v>0.9845</v>
       </c>
-      <c r="F99" s="23" t="n">
+      <c r="F99" s="24" t="n">
         <v>1.0157</v>
       </c>
-      <c r="G99" s="22" t="n">
+      <c r="G99" s="23" t="n">
         <v>0.466</v>
       </c>
-      <c r="H99" s="22" t="n">
+      <c r="H99" s="23" t="n">
         <v>1.534</v>
       </c>
-      <c r="I99" s="22" t="n">
+      <c r="I99" s="23" t="n">
         <v>0.458</v>
       </c>
-      <c r="J99" s="22" t="n">
+      <c r="J99" s="23" t="n">
         <v>1.511</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="21" t="n">
+      <c r="A100" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B100" s="22" t="n">
+      <c r="B100" s="23" t="n">
         <v>0.707</v>
       </c>
-      <c r="C100" s="22" t="n">
+      <c r="C100" s="23" t="n">
         <v>0.194</v>
       </c>
-      <c r="D100" s="22" t="n">
+      <c r="D100" s="23" t="n">
         <v>0.718</v>
       </c>
-      <c r="E100" s="23" t="n">
+      <c r="E100" s="24" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="F100" s="23" t="n">
+      <c r="F100" s="24" t="n">
         <v>1.0148</v>
       </c>
-      <c r="G100" s="22" t="n">
+      <c r="G100" s="23" t="n">
         <v>0.482</v>
       </c>
-      <c r="H100" s="22" t="n">
+      <c r="H100" s="23" t="n">
         <v>1.518</v>
       </c>
-      <c r="I100" s="22" t="n">
+      <c r="I100" s="23" t="n">
         <v>0.475</v>
       </c>
-      <c r="J100" s="22" t="n">
+      <c r="J100" s="23" t="n">
         <v>1.496</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="21" t="n">
+      <c r="A101" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B101" s="22" t="n">
+      <c r="B101" s="23" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C101" s="22" t="n">
+      <c r="C101" s="23" t="n">
         <v>0.187</v>
       </c>
-      <c r="D101" s="22" t="n">
+      <c r="D101" s="23" t="n">
         <v>0.698</v>
       </c>
-      <c r="E101" s="23" t="n">
+      <c r="E101" s="24" t="n">
         <v>0.9862</v>
       </c>
-      <c r="F101" s="23" t="n">
+      <c r="F101" s="24" t="n">
         <v>1.014</v>
       </c>
-      <c r="G101" s="22" t="n">
+      <c r="G101" s="23" t="n">
         <v>0.497</v>
       </c>
-      <c r="H101" s="22" t="n">
+      <c r="H101" s="23" t="n">
         <v>1.503</v>
       </c>
-      <c r="I101" s="22" t="n">
+      <c r="I101" s="23" t="n">
         <v>0.49</v>
       </c>
-      <c r="J101" s="22" t="n">
+      <c r="J101" s="23" t="n">
         <v>1.483</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="21" t="n">
+      <c r="A102" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B102" s="22" t="n">
+      <c r="B102" s="23" t="n">
         <v>0.671</v>
       </c>
-      <c r="C102" s="22" t="n">
+      <c r="C102" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="D102" s="22" t="n">
+      <c r="D102" s="23" t="n">
         <v>0.68</v>
       </c>
-      <c r="E102" s="23" t="n">
+      <c r="E102" s="24" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F102" s="23" t="n">
+      <c r="F102" s="24" t="n">
         <v>1.0133</v>
       </c>
-      <c r="G102" s="22" t="n">
+      <c r="G102" s="23" t="n">
         <v>0.51</v>
       </c>
-      <c r="H102" s="22" t="n">
+      <c r="H102" s="23" t="n">
         <v>1.49</v>
       </c>
-      <c r="I102" s="22" t="n">
+      <c r="I102" s="23" t="n">
         <v>0.504</v>
       </c>
-      <c r="J102" s="22" t="n">
+      <c r="J102" s="23" t="n">
         <v>1.47</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="21" t="n">
+      <c r="A103" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B103" s="22" t="n">
+      <c r="B103" s="23" t="n">
         <v>0.655</v>
       </c>
-      <c r="C103" s="22" t="n">
+      <c r="C103" s="23" t="n">
         <v>0.173</v>
       </c>
-      <c r="D103" s="22" t="n">
+      <c r="D103" s="23" t="n">
         <v>0.663</v>
       </c>
-      <c r="E103" s="23" t="n">
+      <c r="E103" s="24" t="n">
         <v>0.9876</v>
       </c>
-      <c r="F103" s="23" t="n">
+      <c r="F103" s="24" t="n">
         <v>1.0126</v>
       </c>
-      <c r="G103" s="22" t="n">
+      <c r="G103" s="23" t="n">
         <v>0.523</v>
       </c>
-      <c r="H103" s="22" t="n">
+      <c r="H103" s="23" t="n">
         <v>1.477</v>
       </c>
-      <c r="I103" s="22" t="n">
+      <c r="I103" s="23" t="n">
         <v>0.516</v>
       </c>
-      <c r="J103" s="22" t="n">
+      <c r="J103" s="23" t="n">
         <v>1.459</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="21" t="n">
+      <c r="A104" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B104" s="22" t="n">
+      <c r="B104" s="23" t="n">
         <v>0.64</v>
       </c>
-      <c r="C104" s="22" t="n">
+      <c r="C104" s="23" t="n">
         <v>0.167</v>
       </c>
-      <c r="D104" s="22" t="n">
+      <c r="D104" s="23" t="n">
         <v>0.647</v>
       </c>
-      <c r="E104" s="23" t="n">
+      <c r="E104" s="24" t="n">
         <v>0.9882</v>
       </c>
-      <c r="F104" s="23" t="n">
+      <c r="F104" s="24" t="n">
         <v>1.0119</v>
       </c>
-      <c r="G104" s="22" t="n">
+      <c r="G104" s="23" t="n">
         <v>0.534</v>
       </c>
-      <c r="H104" s="22" t="n">
+      <c r="H104" s="23" t="n">
         <v>1.466</v>
       </c>
-      <c r="I104" s="22" t="n">
+      <c r="I104" s="23" t="n">
         <v>0.528</v>
       </c>
-      <c r="J104" s="22" t="n">
+      <c r="J104" s="23" t="n">
         <v>1.448</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="21" t="n">
+      <c r="A105" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="B105" s="22" t="n">
+      <c r="B105" s="23" t="n">
         <v>0.626</v>
       </c>
-      <c r="C105" s="22" t="n">
+      <c r="C105" s="23" t="n">
         <v>0.162</v>
       </c>
-      <c r="D105" s="22" t="n">
+      <c r="D105" s="23" t="n">
         <v>0.633</v>
       </c>
-      <c r="E105" s="23" t="n">
+      <c r="E105" s="24" t="n">
         <v>0.9887</v>
       </c>
-      <c r="F105" s="23" t="n">
+      <c r="F105" s="24" t="n">
         <v>1.0114</v>
       </c>
-      <c r="G105" s="22" t="n">
+      <c r="G105" s="23" t="n">
         <v>0.545</v>
       </c>
-      <c r="H105" s="22" t="n">
+      <c r="H105" s="23" t="n">
         <v>1.455</v>
       </c>
-      <c r="I105" s="22" t="n">
+      <c r="I105" s="23" t="n">
         <v>0.539</v>
       </c>
-      <c r="J105" s="22" t="n">
+      <c r="J105" s="23" t="n">
         <v>1.438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="21" t="n">
+      <c r="A106" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B106" s="22" t="n">
+      <c r="B106" s="23" t="n">
         <v>0.612</v>
       </c>
-      <c r="C106" s="22" t="n">
+      <c r="C106" s="23" t="n">
         <v>0.157</v>
       </c>
-      <c r="D106" s="22" t="n">
+      <c r="D106" s="23" t="n">
         <v>0.619</v>
       </c>
-      <c r="E106" s="23" t="n">
+      <c r="E106" s="24" t="n">
         <v>0.9892</v>
       </c>
-      <c r="F106" s="23" t="n">
+      <c r="F106" s="24" t="n">
         <v>1.0109</v>
       </c>
-      <c r="G106" s="22" t="n">
+      <c r="G106" s="23" t="n">
         <v>0.555</v>
       </c>
-      <c r="H106" s="22" t="n">
+      <c r="H106" s="23" t="n">
         <v>1.445</v>
       </c>
-      <c r="I106" s="22" t="n">
+      <c r="I106" s="23" t="n">
         <v>0.549</v>
       </c>
-      <c r="J106" s="22" t="n">
+      <c r="J106" s="23" t="n">
         <v>1.429</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="21" t="n">
+      <c r="A107" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B107" s="22" t="n">
+      <c r="B107" s="23" t="n">
         <v>0.6</v>
       </c>
-      <c r="C107" s="22" t="n">
+      <c r="C107" s="23" t="n">
         <v>0.153</v>
       </c>
-      <c r="D107" s="22" t="n">
+      <c r="D107" s="23" t="n">
         <v>0.606</v>
       </c>
-      <c r="E107" s="23" t="n">
+      <c r="E107" s="24" t="n">
         <v>0.9896</v>
       </c>
-      <c r="F107" s="23" t="n">
+      <c r="F107" s="24" t="n">
         <v>1.0105</v>
       </c>
-      <c r="G107" s="22" t="n">
+      <c r="G107" s="23" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H107" s="22" t="n">
+      <c r="H107" s="23" t="n">
         <v>1.435</v>
       </c>
-      <c r="I107" s="22" t="n">
+      <c r="I107" s="23" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J107" s="22" t="n">
+      <c r="J107" s="23" t="n">
         <v>1.42</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="20" t="inlineStr">
+      <c r="A109" s="21" t="inlineStr">
         <is>
           <t>Control Chart Constants - Chart for Ranges &amp; X Charts (Six Sigma Demystified, 2nd ed.)</t>
         </is>
@@ -5146,7 +5728,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="inlineStr">
+      <c r="A111" s="21" t="inlineStr">
         <is>
           <t>USED for E2 (Table 18 and Table A do not give it). Reference otherwise.</t>
         </is>
@@ -5200,703 +5782,703 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="21" t="n">
+      <c r="A113" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="22" t="n">
+      <c r="B113" s="23" t="n">
         <v>1.128</v>
       </c>
-      <c r="C113" s="23" t="n">
+      <c r="C113" s="24" t="n">
         <v>0.8865</v>
       </c>
-      <c r="D113" s="22" t="n">
+      <c r="D113" s="23" t="n">
         <v>0.853</v>
       </c>
-      <c r="E113" s="21" t="n">
+      <c r="E113" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="22" t="n">
+      <c r="F113" s="23" t="n">
         <v>3.686</v>
       </c>
-      <c r="G113" s="21" t="n">
+      <c r="G113" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="22" t="n">
+      <c r="H113" s="23" t="n">
         <v>3.267</v>
       </c>
-      <c r="I113" s="24" t="n">
+      <c r="I113" s="25" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="21" t="n">
+      <c r="A114" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="22" t="n">
+      <c r="B114" s="23" t="n">
         <v>1.693</v>
       </c>
-      <c r="C114" s="23" t="n">
+      <c r="C114" s="24" t="n">
         <v>0.5907</v>
       </c>
-      <c r="D114" s="22" t="n">
+      <c r="D114" s="23" t="n">
         <v>0.888</v>
       </c>
-      <c r="E114" s="21" t="n">
+      <c r="E114" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="22" t="n">
+      <c r="F114" s="23" t="n">
         <v>4.358</v>
       </c>
-      <c r="G114" s="21" t="n">
+      <c r="G114" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="24" t="n">
+      <c r="H114" s="25" t="n">
         <v>2.574</v>
       </c>
-      <c r="I114" s="22" t="n">
+      <c r="I114" s="23" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="21" t="n">
+      <c r="A115" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B115" s="22" t="n">
+      <c r="B115" s="23" t="n">
         <v>2.059</v>
       </c>
-      <c r="C115" s="23" t="n">
+      <c r="C115" s="24" t="n">
         <v>0.4857</v>
       </c>
-      <c r="D115" s="22" t="n">
+      <c r="D115" s="23" t="n">
         <v>0.88</v>
       </c>
-      <c r="E115" s="21" t="n">
+      <c r="E115" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="22" t="n">
+      <c r="F115" s="23" t="n">
         <v>4.698</v>
       </c>
-      <c r="G115" s="21" t="n">
+      <c r="G115" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="22" t="n">
+      <c r="H115" s="23" t="n">
         <v>2.282</v>
       </c>
-      <c r="I115" s="22" t="n">
+      <c r="I115" s="23" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="21" t="n">
+      <c r="A116" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="22" t="n">
+      <c r="B116" s="23" t="n">
         <v>2.326</v>
       </c>
-      <c r="C116" s="23" t="n">
+      <c r="C116" s="24" t="n">
         <v>0.4299</v>
       </c>
-      <c r="D116" s="22" t="n">
+      <c r="D116" s="23" t="n">
         <v>0.864</v>
       </c>
-      <c r="E116" s="21" t="n">
+      <c r="E116" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="22" t="n">
+      <c r="F116" s="23" t="n">
         <v>4.918</v>
       </c>
-      <c r="G116" s="21" t="n">
+      <c r="G116" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="24" t="n">
+      <c r="H116" s="25" t="n">
         <v>2.114</v>
       </c>
-      <c r="I116" s="22" t="n">
+      <c r="I116" s="23" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="21" t="n">
+      <c r="A117" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B117" s="22" t="n">
+      <c r="B117" s="23" t="n">
         <v>2.534</v>
       </c>
-      <c r="C117" s="23" t="n">
+      <c r="C117" s="24" t="n">
         <v>0.3946</v>
       </c>
-      <c r="D117" s="22" t="n">
+      <c r="D117" s="23" t="n">
         <v>0.848</v>
       </c>
-      <c r="E117" s="21" t="n">
+      <c r="E117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="22" t="n">
+      <c r="F117" s="23" t="n">
         <v>5.078</v>
       </c>
-      <c r="G117" s="21" t="n">
+      <c r="G117" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="22" t="n">
+      <c r="H117" s="23" t="n">
         <v>2.004</v>
       </c>
-      <c r="I117" s="22" t="n">
+      <c r="I117" s="23" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="21" t="n">
+      <c r="A118" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="22" t="n">
+      <c r="B118" s="23" t="n">
         <v>2.704</v>
       </c>
-      <c r="C118" s="23" t="n">
+      <c r="C118" s="24" t="n">
         <v>0.3698</v>
       </c>
-      <c r="D118" s="22" t="n">
+      <c r="D118" s="23" t="n">
         <v>0.833</v>
       </c>
-      <c r="E118" s="24" t="n">
+      <c r="E118" s="25" t="n">
         <v>0.204</v>
       </c>
-      <c r="F118" s="24" t="n">
+      <c r="F118" s="25" t="n">
         <v>5.204</v>
       </c>
-      <c r="G118" s="22" t="n">
+      <c r="G118" s="23" t="n">
         <v>0.076</v>
       </c>
-      <c r="H118" s="22" t="n">
+      <c r="H118" s="23" t="n">
         <v>1.924</v>
       </c>
-      <c r="I118" s="22" t="n">
+      <c r="I118" s="23" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="21" t="n">
+      <c r="A119" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B119" s="22" t="n">
+      <c r="B119" s="23" t="n">
         <v>2.847</v>
       </c>
-      <c r="C119" s="23" t="n">
+      <c r="C119" s="24" t="n">
         <v>0.3512</v>
       </c>
-      <c r="D119" s="22" t="n">
+      <c r="D119" s="23" t="n">
         <v>0.82</v>
       </c>
-      <c r="E119" s="24" t="n">
+      <c r="E119" s="25" t="n">
         <v>0.388</v>
       </c>
-      <c r="F119" s="24" t="n">
+      <c r="F119" s="25" t="n">
         <v>5.306</v>
       </c>
-      <c r="G119" s="22" t="n">
+      <c r="G119" s="23" t="n">
         <v>0.136</v>
       </c>
-      <c r="H119" s="22" t="n">
+      <c r="H119" s="23" t="n">
         <v>1.864</v>
       </c>
-      <c r="I119" s="22" t="n">
+      <c r="I119" s="23" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="21" t="n">
+      <c r="A120" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="22" t="n">
+      <c r="B120" s="23" t="n">
         <v>2.97</v>
       </c>
-      <c r="C120" s="23" t="n">
+      <c r="C120" s="24" t="n">
         <v>0.3367</v>
       </c>
-      <c r="D120" s="22" t="n">
+      <c r="D120" s="23" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E120" s="24" t="n">
+      <c r="E120" s="25" t="n">
         <v>0.547</v>
       </c>
-      <c r="F120" s="24" t="n">
+      <c r="F120" s="25" t="n">
         <v>5.393</v>
       </c>
-      <c r="G120" s="22" t="n">
+      <c r="G120" s="23" t="n">
         <v>0.184</v>
       </c>
-      <c r="H120" s="22" t="n">
+      <c r="H120" s="23" t="n">
         <v>1.816</v>
       </c>
-      <c r="I120" s="22" t="n">
+      <c r="I120" s="23" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="21" t="n">
+      <c r="A121" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B121" s="22" t="n">
+      <c r="B121" s="23" t="n">
         <v>3.078</v>
       </c>
-      <c r="C121" s="23" t="n">
+      <c r="C121" s="24" t="n">
         <v>0.3249</v>
       </c>
-      <c r="D121" s="22" t="n">
+      <c r="D121" s="23" t="n">
         <v>0.797</v>
       </c>
-      <c r="E121" s="22" t="n">
+      <c r="E121" s="23" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F121" s="22" t="n">
+      <c r="F121" s="23" t="n">
         <v>5.469</v>
       </c>
-      <c r="G121" s="22" t="n">
+      <c r="G121" s="23" t="n">
         <v>0.223</v>
       </c>
-      <c r="H121" s="22" t="n">
+      <c r="H121" s="23" t="n">
         <v>1.777</v>
       </c>
-      <c r="I121" s="22" t="n">
+      <c r="I121" s="23" t="n">
         <v>0.975</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="21" t="n">
+      <c r="A122" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B122" s="22" t="n">
+      <c r="B122" s="23" t="n">
         <v>3.173</v>
       </c>
-      <c r="C122" s="23" t="n">
+      <c r="C122" s="24" t="n">
         <v>0.3152</v>
       </c>
-      <c r="D122" s="22" t="n">
+      <c r="D122" s="23" t="n">
         <v>0.787</v>
       </c>
-      <c r="E122" s="24" t="n">
+      <c r="E122" s="25" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F122" s="24" t="n">
+      <c r="F122" s="25" t="n">
         <v>5.535</v>
       </c>
-      <c r="G122" s="22" t="n">
+      <c r="G122" s="23" t="n">
         <v>0.256</v>
       </c>
-      <c r="H122" s="22" t="n">
+      <c r="H122" s="23" t="n">
         <v>1.744</v>
       </c>
-      <c r="I122" s="22" t="n">
+      <c r="I122" s="23" t="n">
         <v>0.945</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="21" t="n">
+      <c r="A123" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="22" t="n">
+      <c r="B123" s="23" t="n">
         <v>3.258</v>
       </c>
-      <c r="C123" s="23" t="n">
+      <c r="C123" s="24" t="n">
         <v>0.3069</v>
       </c>
-      <c r="D123" s="24" t="n">
+      <c r="D123" s="25" t="n">
         <v>0.778</v>
       </c>
-      <c r="E123" s="24" t="n">
+      <c r="E123" s="25" t="n">
         <v>0.922</v>
       </c>
-      <c r="F123" s="24" t="n">
+      <c r="F123" s="25" t="n">
         <v>5.594</v>
       </c>
-      <c r="G123" s="24" t="n">
+      <c r="G123" s="25" t="n">
         <v>0.283</v>
       </c>
-      <c r="H123" s="24" t="n">
+      <c r="H123" s="25" t="n">
         <v>1.717</v>
       </c>
-      <c r="I123" s="22" t="n">
+      <c r="I123" s="23" t="n">
         <v>0.921</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="21" t="n">
+      <c r="A124" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B124" s="22" t="n">
+      <c r="B124" s="23" t="n">
         <v>3.336</v>
       </c>
-      <c r="C124" s="23" t="n">
+      <c r="C124" s="24" t="n">
         <v>0.2998</v>
       </c>
-      <c r="D124" s="22" t="n">
+      <c r="D124" s="23" t="n">
         <v>0.77</v>
       </c>
-      <c r="E124" s="24" t="n">
+      <c r="E124" s="25" t="n">
         <v>1.025</v>
       </c>
-      <c r="F124" s="24" t="n">
+      <c r="F124" s="25" t="n">
         <v>5.647</v>
       </c>
-      <c r="G124" s="24" t="n">
+      <c r="G124" s="25" t="n">
         <v>0.307</v>
       </c>
-      <c r="H124" s="24" t="n">
+      <c r="H124" s="25" t="n">
         <v>1.693</v>
       </c>
-      <c r="I124" s="22" t="n">
+      <c r="I124" s="23" t="n">
         <v>0.899</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="21" t="n">
+      <c r="A125" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B125" s="22" t="n">
+      <c r="B125" s="23" t="n">
         <v>3.407</v>
       </c>
-      <c r="C125" s="23" t="n">
+      <c r="C125" s="24" t="n">
         <v>0.2935</v>
       </c>
-      <c r="D125" s="22" t="n">
+      <c r="D125" s="23" t="n">
         <v>0.763</v>
       </c>
-      <c r="E125" s="24" t="n">
+      <c r="E125" s="25" t="n">
         <v>1.118</v>
       </c>
-      <c r="F125" s="24" t="n">
+      <c r="F125" s="25" t="n">
         <v>5.696</v>
       </c>
-      <c r="G125" s="24" t="n">
+      <c r="G125" s="25" t="n">
         <v>0.328</v>
       </c>
-      <c r="H125" s="24" t="n">
+      <c r="H125" s="25" t="n">
         <v>1.672</v>
       </c>
-      <c r="I125" s="22" t="n">
+      <c r="I125" s="23" t="n">
         <v>0.881</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="21" t="n">
+      <c r="A126" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B126" s="22" t="n">
+      <c r="B126" s="23" t="n">
         <v>3.472</v>
       </c>
-      <c r="C126" s="23" t="n">
+      <c r="C126" s="24" t="n">
         <v>0.288</v>
       </c>
-      <c r="D126" s="22" t="n">
+      <c r="D126" s="23" t="n">
         <v>0.756</v>
       </c>
-      <c r="E126" s="24" t="n">
+      <c r="E126" s="25" t="n">
         <v>1.203</v>
       </c>
-      <c r="F126" s="24" t="n">
+      <c r="F126" s="25" t="n">
         <v>5.741</v>
       </c>
-      <c r="G126" s="24" t="n">
+      <c r="G126" s="25" t="n">
         <v>0.347</v>
       </c>
-      <c r="H126" s="24" t="n">
+      <c r="H126" s="25" t="n">
         <v>1.653</v>
       </c>
-      <c r="I126" s="22" t="n">
+      <c r="I126" s="23" t="n">
         <v>0.864</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="21" t="n">
+      <c r="A127" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B127" s="22" t="n">
+      <c r="B127" s="23" t="n">
         <v>3.532</v>
       </c>
-      <c r="C127" s="23" t="n">
+      <c r="C127" s="24" t="n">
         <v>0.2831</v>
       </c>
-      <c r="D127" s="22" t="n">
+      <c r="D127" s="23" t="n">
         <v>0.75</v>
       </c>
-      <c r="E127" s="24" t="n">
+      <c r="E127" s="25" t="n">
         <v>1.282</v>
       </c>
-      <c r="F127" s="24" t="n">
+      <c r="F127" s="25" t="n">
         <v>5.782</v>
       </c>
-      <c r="G127" s="24" t="n">
+      <c r="G127" s="25" t="n">
         <v>0.363</v>
       </c>
-      <c r="H127" s="24" t="n">
+      <c r="H127" s="25" t="n">
         <v>1.637</v>
       </c>
-      <c r="I127" s="22" t="n">
+      <c r="I127" s="23" t="n">
         <v>0.849</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="21" t="n">
+      <c r="A128" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B128" s="22" t="n">
+      <c r="B128" s="23" t="n">
         <v>3.588</v>
       </c>
-      <c r="C128" s="23" t="n">
+      <c r="C128" s="24" t="n">
         <v>0.2787</v>
       </c>
-      <c r="D128" s="22" t="n">
+      <c r="D128" s="23" t="n">
         <v>0.744</v>
       </c>
-      <c r="E128" s="24" t="n">
+      <c r="E128" s="25" t="n">
         <v>1.356</v>
       </c>
-      <c r="F128" s="24" t="n">
+      <c r="F128" s="25" t="n">
         <v>5.82</v>
       </c>
-      <c r="G128" s="24" t="n">
+      <c r="G128" s="25" t="n">
         <v>0.378</v>
       </c>
-      <c r="H128" s="24" t="n">
+      <c r="H128" s="25" t="n">
         <v>1.622</v>
       </c>
-      <c r="I128" s="22" t="n">
+      <c r="I128" s="23" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="21" t="n">
+      <c r="A129" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B129" s="22" t="n">
+      <c r="B129" s="23" t="n">
         <v>3.64</v>
       </c>
-      <c r="C129" s="23" t="n">
+      <c r="C129" s="24" t="n">
         <v>0.2747</v>
       </c>
-      <c r="D129" s="22" t="n">
+      <c r="D129" s="23" t="n">
         <v>0.739</v>
       </c>
-      <c r="E129" s="24" t="n">
+      <c r="E129" s="25" t="n">
         <v>1.424</v>
       </c>
-      <c r="F129" s="24" t="n">
+      <c r="F129" s="25" t="n">
         <v>5.856</v>
       </c>
-      <c r="G129" s="24" t="n">
+      <c r="G129" s="25" t="n">
         <v>0.391</v>
       </c>
-      <c r="H129" s="22" t="n">
+      <c r="H129" s="23" t="n">
         <v>1.608</v>
       </c>
-      <c r="I129" s="22" t="n">
+      <c r="I129" s="23" t="n">
         <v>0.824</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="21" t="n">
+      <c r="A130" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B130" s="22" t="n">
+      <c r="B130" s="23" t="n">
         <v>3.689</v>
       </c>
-      <c r="C130" s="23" t="n">
+      <c r="C130" s="24" t="n">
         <v>0.2711</v>
       </c>
-      <c r="D130" s="22" t="n">
+      <c r="D130" s="23" t="n">
         <v>0.734</v>
       </c>
-      <c r="E130" s="24" t="n">
+      <c r="E130" s="25" t="n">
         <v>1.487</v>
       </c>
-      <c r="F130" s="24" t="n">
+      <c r="F130" s="25" t="n">
         <v>5.891</v>
       </c>
-      <c r="G130" s="24" t="n">
+      <c r="G130" s="25" t="n">
         <v>0.403</v>
       </c>
-      <c r="H130" s="24" t="n">
+      <c r="H130" s="25" t="n">
         <v>1.597</v>
       </c>
-      <c r="I130" s="22" t="n">
+      <c r="I130" s="23" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="21" t="n">
+      <c r="A131" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="22" t="n">
+      <c r="B131" s="23" t="n">
         <v>3.735</v>
       </c>
-      <c r="C131" s="23" t="n">
+      <c r="C131" s="24" t="n">
         <v>0.2677</v>
       </c>
-      <c r="D131" s="22" t="n">
+      <c r="D131" s="23" t="n">
         <v>0.729</v>
       </c>
-      <c r="E131" s="24" t="n">
+      <c r="E131" s="25" t="n">
         <v>1.549</v>
       </c>
-      <c r="F131" s="24" t="n">
+      <c r="F131" s="25" t="n">
         <v>5.921</v>
       </c>
-      <c r="G131" s="24" t="n">
+      <c r="G131" s="25" t="n">
         <v>0.415</v>
       </c>
-      <c r="H131" s="24" t="n">
+      <c r="H131" s="25" t="n">
         <v>1.585</v>
       </c>
-      <c r="I131" s="22" t="n">
+      <c r="I131" s="23" t="n">
         <v>0.803</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="21" t="n">
+      <c r="A132" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B132" s="22" t="n">
+      <c r="B132" s="23" t="n">
         <v>3.778</v>
       </c>
-      <c r="C132" s="23" t="n">
+      <c r="C132" s="24" t="n">
         <v>0.2647</v>
       </c>
-      <c r="D132" s="24" t="n">
+      <c r="D132" s="25" t="n">
         <v>0.724</v>
       </c>
-      <c r="E132" s="24" t="n">
+      <c r="E132" s="25" t="n">
         <v>1.605</v>
       </c>
-      <c r="F132" s="24" t="n">
+      <c r="F132" s="25" t="n">
         <v>5.951</v>
       </c>
-      <c r="G132" s="22" t="n">
+      <c r="G132" s="23" t="n">
         <v>0.425</v>
       </c>
-      <c r="H132" s="22" t="n">
+      <c r="H132" s="23" t="n">
         <v>1.575</v>
       </c>
-      <c r="I132" s="22" t="n">
+      <c r="I132" s="23" t="n">
         <v>0.794</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="21" t="n">
+      <c r="A133" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B133" s="22" t="n">
+      <c r="B133" s="23" t="n">
         <v>3.819</v>
       </c>
-      <c r="C133" s="23" t="n">
+      <c r="C133" s="24" t="n">
         <v>0.2618</v>
       </c>
-      <c r="D133" s="22" t="n">
+      <c r="D133" s="23" t="n">
         <v>0.72</v>
       </c>
-      <c r="E133" s="22" t="n">
+      <c r="E133" s="23" t="n">
         <v>1.659</v>
       </c>
-      <c r="F133" s="22" t="n">
+      <c r="F133" s="23" t="n">
         <v>5.979</v>
       </c>
-      <c r="G133" s="22" t="n">
+      <c r="G133" s="23" t="n">
         <v>0.434</v>
       </c>
-      <c r="H133" s="22" t="n">
+      <c r="H133" s="23" t="n">
         <v>1.566</v>
       </c>
-      <c r="I133" s="22" t="n">
+      <c r="I133" s="23" t="n">
         <v>0.786</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="21" t="n">
+      <c r="A134" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="B134" s="22" t="n">
+      <c r="B134" s="23" t="n">
         <v>3.858</v>
       </c>
-      <c r="C134" s="23" t="n">
+      <c r="C134" s="24" t="n">
         <v>0.2592</v>
       </c>
-      <c r="D134" s="22" t="n">
+      <c r="D134" s="23" t="n">
         <v>0.716</v>
       </c>
-      <c r="E134" s="22" t="n">
+      <c r="E134" s="23" t="n">
         <v>1.71</v>
       </c>
-      <c r="F134" s="22" t="n">
+      <c r="F134" s="23" t="n">
         <v>6.006</v>
       </c>
-      <c r="G134" s="22" t="n">
+      <c r="G134" s="23" t="n">
         <v>0.443</v>
       </c>
-      <c r="H134" s="22" t="n">
+      <c r="H134" s="23" t="n">
         <v>1.557</v>
       </c>
-      <c r="I134" s="22" t="n">
+      <c r="I134" s="23" t="n">
         <v>0.778</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="21" t="n">
+      <c r="A135" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B135" s="22" t="n">
+      <c r="B135" s="23" t="n">
         <v>3.895</v>
       </c>
-      <c r="C135" s="23" t="n">
+      <c r="C135" s="24" t="n">
         <v>0.2567</v>
       </c>
-      <c r="D135" s="22" t="n">
+      <c r="D135" s="23" t="n">
         <v>0.712</v>
       </c>
-      <c r="E135" s="22" t="n">
+      <c r="E135" s="23" t="n">
         <v>1.759</v>
       </c>
-      <c r="F135" s="22" t="n">
+      <c r="F135" s="23" t="n">
         <v>6.031</v>
       </c>
-      <c r="G135" s="24" t="n">
+      <c r="G135" s="25" t="n">
         <v>0.451</v>
       </c>
-      <c r="H135" s="22" t="n">
+      <c r="H135" s="23" t="n">
         <v>1.548</v>
       </c>
-      <c r="I135" s="22" t="n">
+      <c r="I135" s="23" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="21" t="n">
+      <c r="A136" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B136" s="22" t="n">
+      <c r="B136" s="23" t="n">
         <v>3.931</v>
       </c>
-      <c r="C136" s="23" t="n">
+      <c r="C136" s="24" t="n">
         <v>0.2544</v>
       </c>
-      <c r="D136" s="22" t="n">
+      <c r="D136" s="23" t="n">
         <v>0.708</v>
       </c>
-      <c r="E136" s="24" t="n">
+      <c r="E136" s="25" t="n">
         <v>1.806</v>
       </c>
-      <c r="F136" s="24" t="n">
+      <c r="F136" s="25" t="n">
         <v>6.056</v>
       </c>
-      <c r="G136" s="22" t="n">
+      <c r="G136" s="23" t="n">
         <v>0.459</v>
       </c>
-      <c r="H136" s="22" t="n">
+      <c r="H136" s="23" t="n">
         <v>1.541</v>
       </c>
-      <c r="I136" s="22" t="n">
+      <c r="I136" s="23" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="20" t="inlineStr">
+      <c r="A138" s="21" t="inlineStr">
         <is>
           <t>Table 10-2: Continuous Data Control Chart constants (A2, A3, B3, B4, D3, D4, E2)</t>
         </is>
@@ -5910,7 +6492,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="20" t="inlineStr">
+      <c r="A140" s="21" t="inlineStr">
         <is>
           <t>Reference only.</t>
         </is>
@@ -5959,236 +6541,236 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="21" t="n">
+      <c r="A142" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B142" s="22" t="n">
+      <c r="B142" s="23" t="n">
         <v>1.88</v>
       </c>
-      <c r="C142" s="22" t="n">
+      <c r="C142" s="23" t="n">
         <v>2.659</v>
       </c>
-      <c r="D142" s="21" t="n">
+      <c r="D142" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="22" t="n">
+      <c r="E142" s="23" t="n">
         <v>3.267</v>
       </c>
-      <c r="F142" s="21" t="n">
+      <c r="F142" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="22" t="n">
+      <c r="G142" s="23" t="n">
         <v>3.267</v>
       </c>
-      <c r="H142" s="24" t="n">
+      <c r="H142" s="25" t="n">
         <v>2.659</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="21" t="n">
+      <c r="A143" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="22" t="n">
+      <c r="B143" s="23" t="n">
         <v>1.023</v>
       </c>
-      <c r="C143" s="22" t="n">
+      <c r="C143" s="23" t="n">
         <v>1.954</v>
       </c>
-      <c r="D143" s="21" t="n">
+      <c r="D143" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="22" t="n">
+      <c r="E143" s="23" t="n">
         <v>2.568</v>
       </c>
-      <c r="F143" s="21" t="n">
+      <c r="F143" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="24" t="n">
+      <c r="G143" s="25" t="n">
         <v>2.574</v>
       </c>
-      <c r="H143" s="22" t="n">
+      <c r="H143" s="23" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="21" t="n">
+      <c r="A144" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B144" s="22" t="n">
+      <c r="B144" s="23" t="n">
         <v>0.729</v>
       </c>
-      <c r="C144" s="22" t="n">
+      <c r="C144" s="23" t="n">
         <v>1.628</v>
       </c>
-      <c r="D144" s="21" t="n">
+      <c r="D144" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="22" t="n">
+      <c r="E144" s="23" t="n">
         <v>2.266</v>
       </c>
-      <c r="F144" s="21" t="n">
+      <c r="F144" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="22" t="n">
+      <c r="G144" s="23" t="n">
         <v>2.282</v>
       </c>
-      <c r="H144" s="22" t="n">
+      <c r="H144" s="23" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="21" t="n">
+      <c r="A145" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B145" s="22" t="n">
+      <c r="B145" s="23" t="n">
         <v>0.577</v>
       </c>
-      <c r="C145" s="22" t="n">
+      <c r="C145" s="23" t="n">
         <v>1.427</v>
       </c>
-      <c r="D145" s="21" t="n">
+      <c r="D145" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E145" s="22" t="n">
+      <c r="E145" s="23" t="n">
         <v>2.089</v>
       </c>
-      <c r="F145" s="21" t="n">
+      <c r="F145" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="24" t="n">
+      <c r="G145" s="25" t="n">
         <v>2.114</v>
       </c>
-      <c r="H145" s="22" t="n">
+      <c r="H145" s="23" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="21" t="n">
+      <c r="A146" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B146" s="22" t="n">
+      <c r="B146" s="23" t="n">
         <v>0.483</v>
       </c>
-      <c r="C146" s="22" t="n">
+      <c r="C146" s="23" t="n">
         <v>1.287</v>
       </c>
-      <c r="D146" s="22" t="n">
+      <c r="D146" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="E146" s="22" t="n">
+      <c r="E146" s="23" t="n">
         <v>1.97</v>
       </c>
-      <c r="F146" s="21" t="n">
+      <c r="F146" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="22" t="n">
+      <c r="G146" s="23" t="n">
         <v>2.004</v>
       </c>
-      <c r="H146" s="22" t="n">
+      <c r="H146" s="23" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="21" t="n">
+      <c r="A147" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B147" s="22" t="n">
+      <c r="B147" s="23" t="n">
         <v>0.419</v>
       </c>
-      <c r="C147" s="22" t="n">
+      <c r="C147" s="23" t="n">
         <v>1.182</v>
       </c>
-      <c r="D147" s="22" t="n">
+      <c r="D147" s="23" t="n">
         <v>0.118</v>
       </c>
-      <c r="E147" s="22" t="n">
+      <c r="E147" s="23" t="n">
         <v>1.882</v>
       </c>
-      <c r="F147" s="22" t="n">
+      <c r="F147" s="23" t="n">
         <v>0.076</v>
       </c>
-      <c r="G147" s="22" t="n">
+      <c r="G147" s="23" t="n">
         <v>1.924</v>
       </c>
-      <c r="H147" s="22" t="n">
+      <c r="H147" s="23" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="21" t="n">
+      <c r="A148" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B148" s="22" t="n">
+      <c r="B148" s="23" t="n">
         <v>0.373</v>
       </c>
-      <c r="C148" s="22" t="n">
+      <c r="C148" s="23" t="n">
         <v>1.099</v>
       </c>
-      <c r="D148" s="22" t="n">
+      <c r="D148" s="23" t="n">
         <v>0.185</v>
       </c>
-      <c r="E148" s="22" t="n">
+      <c r="E148" s="23" t="n">
         <v>1.815</v>
       </c>
-      <c r="F148" s="22" t="n">
+      <c r="F148" s="23" t="n">
         <v>0.136</v>
       </c>
-      <c r="G148" s="22" t="n">
+      <c r="G148" s="23" t="n">
         <v>1.864</v>
       </c>
-      <c r="H148" s="22" t="n">
+      <c r="H148" s="23" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="21" t="n">
+      <c r="A149" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B149" s="22" t="n">
+      <c r="B149" s="23" t="n">
         <v>0.337</v>
       </c>
-      <c r="C149" s="22" t="n">
+      <c r="C149" s="23" t="n">
         <v>1.032</v>
       </c>
-      <c r="D149" s="22" t="n">
+      <c r="D149" s="23" t="n">
         <v>0.239</v>
       </c>
-      <c r="E149" s="22" t="n">
+      <c r="E149" s="23" t="n">
         <v>1.761</v>
       </c>
-      <c r="F149" s="22" t="n">
+      <c r="F149" s="23" t="n">
         <v>0.184</v>
       </c>
-      <c r="G149" s="22" t="n">
+      <c r="G149" s="23" t="n">
         <v>1.816</v>
       </c>
-      <c r="H149" s="22" t="n">
+      <c r="H149" s="23" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="21" t="n">
+      <c r="A150" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B150" s="22" t="n">
+      <c r="B150" s="23" t="n">
         <v>0.308</v>
       </c>
-      <c r="C150" s="22" t="n">
+      <c r="C150" s="23" t="n">
         <v>0.975</v>
       </c>
-      <c r="D150" s="22" t="n">
+      <c r="D150" s="23" t="n">
         <v>0.284</v>
       </c>
-      <c r="E150" s="22" t="n">
+      <c r="E150" s="23" t="n">
         <v>1.716</v>
       </c>
-      <c r="F150" s="22" t="n">
+      <c r="F150" s="23" t="n">
         <v>0.223</v>
       </c>
-      <c r="G150" s="22" t="n">
+      <c r="G150" s="23" t="n">
         <v>1.777</v>
       </c>
-      <c r="H150" s="22" t="n">
+      <c r="H150" s="23" t="n">
         <v>0.975</v>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normal" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sigma &amp; DPMO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -68,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
@@ -76,6 +77,9 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.00000%"/>
     <numFmt numFmtId="170" formatCode="0.0000000%"/>
+    <numFmt numFmtId="171" formatCode="0.000000000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.000"/>
+    <numFmt numFmtId="173" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -180,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -208,6 +212,11 @@
     <xf numFmtId="170" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2701,6 +2710,881 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sigma level, DPMO and yield: DPU, DPO, DPMO, Z with and without 1.5σ shift, Y, FTY, RTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 19-20, 36-39; Six Sigma For Dummies.pdf p. 42, 147-161; Six-Sigma Mikel Harry - Richard Schroeder.pdf p. 3-5; 20260521_van volsem.pdf p. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Decision 3: sigma level ↔ DPMO shown both with the 1.5σ shift (as in every course table) and without.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: tested against course worked examples S07-WE01, S08-WE01 to S08-WE08, S09-WE01, S09-WE03 to S09-WE06 and the course sigma tables; a few printed values disagree (listed in build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. Defects, units and opportunities (discrete data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>D = number of defects observed</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>N = number of units inspected</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>for one item with many opportunities: N = 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>O = opportunities (CTQs) per unit</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1 if every unit is one opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>DPU = D / N</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>IF(AND(ISNUMBER(B9),ISNUMBER(B10),B10&gt;0),B9/B10,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 152; Harry &amp; Schroeder p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>DPO = D / (N · O)</t>
+        </is>
+      </c>
+      <c r="B13" s="21">
+        <f>IF(AND(AND(ISNUMBER(B9),ISNUMBER(B10),B10&gt;0),ISNUMBER(B11),B11&gt;0),B9/(B10*B11),"")</f>
+        <v/>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 19; Dummies p. 153</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>DPMO = DPO · 1 000 000</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <f>IF(ISNUMBER(B13),B13*1000000,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 19; Dummies p. 155</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Yield per opportunity = 1 − DPO</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>IF(ISNUMBER(B13),1-B13,"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Throughput yield TY = 1 − DPU</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <f>IF(ISNUMBER(B12),1-B12,"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 5 (defects/unit 5 % -&gt; TY 95 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>RTY ≈ e^(−DPU)</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <f>IF(ISNUMBER(B12),EXP(-B12),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 156 (valid when DPU is small, e.g. &lt; 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2. From DPMO to sigma level (both course readings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>DPMO</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>leave empty to use the DPMO of section 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>DPMO used</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <f>IF(ISNUMBER(B20),B20,IF(ISNUMBER(B14),B14,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Yield = 1 − DPMO / 1 000 000</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <f>IF(AND(ISNUMBER(B21),B21&gt;0,B21&lt;1000000),1-B21/1000000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Z without shift (one tail beyond Z)</t>
+        </is>
+      </c>
+      <c r="B23" s="12">
+        <f>IF(AND(ISNUMBER(B21),B21&gt;0,B21&lt;1000000),_xlfn.NORM.S.INV(1-B21/1000000),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 158 (Z_LT); Harry &amp; Schroeder p. 3 reads sigma this way</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Sigma level with the 1.5σ shift = Z + 1.5  (course tables)</t>
+        </is>
+      </c>
+      <c r="B24" s="12">
+        <f>IF(ISNUMBER(B23),B23+B83,"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 20; Dummies Table 6-3 p. 160 ('long-term DPMO, short-term Z'); Harry &amp; Schroeder p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>3. From sigma level to DPMO (both course readings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Sigma level Z</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>DPMO with the 1.5σ shift (one tail beyond Z − 1.5)  (course tables)</t>
+        </is>
+      </c>
+      <c r="B28" s="23">
+        <f>IF(ISNUMBER(B27),1000000*_xlfn.NORM.S.DIST(-(B27-B83),TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 20; Dummies p. 42, 160; Van Volsem p. 7: 6 -&gt; 3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>DPMO without shift, one tail beyond Z</t>
+        </is>
+      </c>
+      <c r="B29" s="23">
+        <f>IF(ISNUMBER(B27),1000000*_xlfn.NORM.S.DIST(-B27,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>DPMO without shift, both tails beyond ±Z (centred, Cp = Z / 3)</t>
+        </is>
+      </c>
+      <c r="B30" s="23">
+        <f>IF(ISNUMBER(B27),2*1000000*_xlfn.NORM.S.DIST(-B27,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 39: Cp = 2 (Z = 6) -&gt; 2 per billion</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Yield with the 1.5σ shift</t>
+        </is>
+      </c>
+      <c r="B31" s="17">
+        <f>IF(ISNUMBER(B27),1-B28/1000000,"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 20; Van Volsem p. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>4. Traditional yield and first-time yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Units in</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Units out (good at the end, after rework)</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Units scrapped</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Units reworked (and then good)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Traditional yield Y = out / in</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>IF(AND(AND(ISNUMBER(B34),B34&gt;0),ISNUMBER(B35)),B35/B34,"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 147, 151</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>First-time yield FTY = (in − scrap − rework) / in</t>
+        </is>
+      </c>
+      <c r="B39" s="14">
+        <f>IF(AND(AND(ISNUMBER(B34),B34&gt;0),ISNUMBER(B36),ISNUMBER(B37)),(B34-B36-B37)/B34,"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 148, 151</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Hidden factory = Y − FTY</t>
+        </is>
+      </c>
+      <c r="B40" s="14">
+        <f>IF(AND(ISNUMBER(B38),ISNUMBER(B39)),B38-B39,"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 148; Harry &amp; Schroeder p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>5. Rolled throughput yield from the yield of each step (up to 10 steps, as fractions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 1</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 0.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 2</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 3</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 4</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 5</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 6</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 7</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 8</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 9</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Yield of step 10</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Number of steps k</t>
+        </is>
+      </c>
+      <c r="B53" s="24">
+        <f>IF(COUNT(B43:B52)&gt;0,COUNT(B43:B52),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>RTY = product of the step yields</t>
+        </is>
+      </c>
+      <c r="B54" s="14">
+        <f>IF(COUNT(B43:B52)&gt;0,PRODUCT(B43:B52),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 150; Harry &amp; Schroeder p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Normalized yield NY = k-th root of RTY</t>
+        </is>
+      </c>
+      <c r="B55" s="14">
+        <f>IF(ISNUMBER(B54),B54^(1/B53),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>6. From a known RTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>leave empty to use the RTY of section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Number of steps k</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>leave empty to use k of section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>RTY used</t>
+        </is>
+      </c>
+      <c r="B63" s="14">
+        <f>IF(ISNUMBER(B61),B61,IF(ISNUMBER(B54),B54,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>k used</t>
+        </is>
+      </c>
+      <c r="B64" s="24">
+        <f>IF(ISNUMBER(B62),B62,IF(ISNUMBER(B53),B53,""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Normalized yield NY = RTY^(1/k)</t>
+        </is>
+      </c>
+      <c r="B65" s="14">
+        <f>IF(AND(AND(ISNUMBER(B63),B63&gt;0,B63&lt;=1),ISNUMBER(B64),B64&gt;0),B63^(1/B64),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 5 ('kth root of RTY')</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>DPU = −ln(RTY)</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>IF(AND(ISNUMBER(B63),B63&gt;0,B63&lt;=1),-LN(B63),"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 156</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Units needed per defect-free unit, defects repairable: 1 + (1 − RTY)</t>
+        </is>
+      </c>
+      <c r="B67" s="12">
+        <f>IF(AND(ISNUMBER(B63),B63&gt;0,B63&lt;=1),1+(1-B63),"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Units needed per defect-free unit, defectives scrapped: 1 / RTY</t>
+        </is>
+      </c>
+      <c r="B68" s="12">
+        <f>IF(AND(ISNUMBER(B63),B63&gt;0,B63&lt;=1),1/B63,"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>7. k identical steps (e.g. dice: 5/6 chance per die of no '1')</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Yield of one step (fraction)</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Number of steps k</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>RTY = yield^k</t>
+        </is>
+      </c>
+      <c r="B72" s="25">
+        <f>IF(AND(ISNUMBER(B70),ISNUMBER(B71)),B70^B71,"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 38-39 (dice example)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>That is one in … (1 / RTY)</t>
+        </is>
+      </c>
+      <c r="B73" s="15">
+        <f>IF(AND(ISNUMBER(B72),B72&gt;0),1/B72,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>8. Average yield per defect opportunity (compare products of different complexity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Final yield of the product (fraction)</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Number of defect opportunities</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 600</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Yield per opportunity = yield^(1 / opportunities)</t>
+        </is>
+      </c>
+      <c r="B78" s="14">
+        <f>IF(AND(ISNUMBER(B76),B76&gt;0,B76&lt;=1,ISNUMBER(B77),B77&gt;0),B76^(1/B77),"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>DPMO = (1 − yield per opportunity) · 1 000 000</t>
+        </is>
+      </c>
+      <c r="B79" s="15">
+        <f>IF(ISNUMBER(B78),(1-B78)*1000000,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Z without shift</t>
+        </is>
+      </c>
+      <c r="B80" s="12">
+        <f>IF(AND(ISNUMBER(B78),B78&lt;1),_xlfn.NORM.S.INV(B78),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Harry &amp; Schroeder p. 3 quotes this reading ('about 3.5 sigma')</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Sigma level with the 1.5σ shift</t>
+        </is>
+      </c>
+      <c r="B81" s="12">
+        <f>IF(ISNUMBER(B80),B80+B83,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Shift assumed by the course (σ)</t>
+        </is>
+      </c>
+      <c r="B83" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 36; Dummies p. 159-160 ('Zlt = Zst - 1.5')</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B61 B70 B76" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Yield" error="Type a yield as a fraction, 0 to 1." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2800,7 +3684,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Table 18 - Factors for Computing Control-Chart Lines</t>
         </is>
@@ -2814,7 +3698,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>USED by the calculators (the lecturer's exercise workbooks use these values).</t>
         </is>
@@ -2908,1330 +3792,1330 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="28" t="n">
         <v>2.121</v>
       </c>
-      <c r="C14" s="23" t="n">
+      <c r="C14" s="28" t="n">
         <v>3.76</v>
       </c>
-      <c r="D14" s="23" t="n">
+      <c r="D14" s="28" t="n">
         <v>3.76</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="28" t="n">
         <v>1.88</v>
       </c>
-      <c r="F14" s="24" t="n">
+      <c r="F14" s="29" t="n">
         <v>0.5642</v>
       </c>
-      <c r="G14" s="24" t="n">
+      <c r="G14" s="29" t="n">
         <v>1.7725</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="23" t="n">
+      <c r="I14" s="28" t="n">
         <v>1.843</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="23" t="n">
+      <c r="K14" s="28" t="n">
         <v>3.267</v>
       </c>
-      <c r="L14" s="23" t="n">
+      <c r="L14" s="28" t="n">
         <v>1.128</v>
       </c>
-      <c r="M14" s="24" t="n">
+      <c r="M14" s="29" t="n">
         <v>0.8865</v>
       </c>
-      <c r="N14" s="22" t="n">
+      <c r="N14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="23" t="n">
+      <c r="O14" s="28" t="n">
         <v>3.686</v>
       </c>
-      <c r="P14" s="22" t="n">
+      <c r="P14" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="23" t="n">
+      <c r="Q14" s="28" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="28" t="n">
         <v>1.732</v>
       </c>
-      <c r="C15" s="23" t="n">
+      <c r="C15" s="28" t="n">
         <v>3.07</v>
       </c>
-      <c r="D15" s="23" t="n">
+      <c r="D15" s="28" t="n">
         <v>2.394</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="28" t="n">
         <v>1.023</v>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="29" t="n">
         <v>0.7236</v>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="29" t="n">
         <v>1.382</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="28" t="n">
         <v>1.858</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="28" t="n">
         <v>2.568</v>
       </c>
-      <c r="L15" s="23" t="n">
+      <c r="L15" s="28" t="n">
         <v>1.693</v>
       </c>
-      <c r="M15" s="24" t="n">
+      <c r="M15" s="29" t="n">
         <v>0.5907</v>
       </c>
-      <c r="N15" s="22" t="n">
+      <c r="N15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="23" t="n">
+      <c r="O15" s="28" t="n">
         <v>4.358</v>
       </c>
-      <c r="P15" s="22" t="n">
+      <c r="P15" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="25" t="n">
+      <c r="Q15" s="30" t="n">
         <v>2.575</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="28" t="n">
         <v>2.914</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="28" t="n">
         <v>1.88</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="28" t="n">
         <v>0.729</v>
       </c>
-      <c r="F16" s="24" t="n">
+      <c r="F16" s="29" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="G16" s="24" t="n">
+      <c r="G16" s="29" t="n">
         <v>1.2533</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="28" t="n">
         <v>1.808</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="28" t="n">
         <v>2.266</v>
       </c>
-      <c r="L16" s="23" t="n">
+      <c r="L16" s="28" t="n">
         <v>2.059</v>
       </c>
-      <c r="M16" s="24" t="n">
+      <c r="M16" s="29" t="n">
         <v>0.4857</v>
       </c>
-      <c r="N16" s="22" t="n">
+      <c r="N16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="23" t="n">
+      <c r="O16" s="28" t="n">
         <v>4.698</v>
       </c>
-      <c r="P16" s="22" t="n">
+      <c r="P16" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="23" t="n">
+      <c r="Q16" s="28" t="n">
         <v>2.282</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="28" t="n">
         <v>1.342</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="28" t="n">
         <v>2.884</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="28" t="n">
         <v>1.596</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="28" t="n">
         <v>0.577</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="29" t="n">
         <v>0.8407</v>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="29" t="n">
         <v>1.1894</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I17" s="28" t="n">
         <v>1.756</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K17" s="28" t="n">
         <v>2.089</v>
       </c>
-      <c r="L17" s="23" t="n">
+      <c r="L17" s="28" t="n">
         <v>2.326</v>
       </c>
-      <c r="M17" s="24" t="n">
+      <c r="M17" s="29" t="n">
         <v>0.4299</v>
       </c>
-      <c r="N17" s="22" t="n">
+      <c r="N17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="23" t="n">
+      <c r="O17" s="28" t="n">
         <v>4.918</v>
       </c>
-      <c r="P17" s="22" t="n">
+      <c r="P17" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="25" t="n">
+      <c r="Q17" s="30" t="n">
         <v>2.115</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n">
+      <c r="A18" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="23" t="n">
+      <c r="B18" s="28" t="n">
         <v>1.225</v>
       </c>
-      <c r="C18" s="23" t="n">
+      <c r="C18" s="28" t="n">
         <v>2.899</v>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="28" t="n">
         <v>1.41</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="28" t="n">
         <v>0.483</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="29" t="n">
         <v>0.8686</v>
       </c>
-      <c r="G18" s="24" t="n">
+      <c r="G18" s="29" t="n">
         <v>1.1512</v>
       </c>
-      <c r="H18" s="23" t="n">
+      <c r="H18" s="28" t="n">
         <v>0.026</v>
       </c>
-      <c r="I18" s="23" t="n">
+      <c r="I18" s="28" t="n">
         <v>1.711</v>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="J18" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="28" t="n">
         <v>1.97</v>
       </c>
-      <c r="L18" s="23" t="n">
+      <c r="L18" s="28" t="n">
         <v>2.534</v>
       </c>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="29" t="n">
         <v>0.3946</v>
       </c>
-      <c r="N18" s="22" t="n">
+      <c r="N18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="23" t="n">
+      <c r="O18" s="28" t="n">
         <v>5.078</v>
       </c>
-      <c r="P18" s="22" t="n">
+      <c r="P18" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="23" t="n">
+      <c r="Q18" s="28" t="n">
         <v>2.004</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="n">
+      <c r="A19" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="23" t="n">
+      <c r="B19" s="28" t="n">
         <v>1.134</v>
       </c>
-      <c r="C19" s="23" t="n">
+      <c r="C19" s="28" t="n">
         <v>2.935</v>
       </c>
-      <c r="D19" s="23" t="n">
+      <c r="D19" s="28" t="n">
         <v>1.277</v>
       </c>
-      <c r="E19" s="23" t="n">
+      <c r="E19" s="28" t="n">
         <v>0.419</v>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="29" t="n">
         <v>0.8882</v>
       </c>
-      <c r="G19" s="24" t="n">
+      <c r="G19" s="29" t="n">
         <v>1.1259</v>
       </c>
-      <c r="H19" s="23" t="n">
+      <c r="H19" s="28" t="n">
         <v>0.105</v>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="28" t="n">
         <v>1.672</v>
       </c>
-      <c r="J19" s="23" t="n">
+      <c r="J19" s="28" t="n">
         <v>0.118</v>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="28" t="n">
         <v>1.882</v>
       </c>
-      <c r="L19" s="23" t="n">
+      <c r="L19" s="28" t="n">
         <v>2.704</v>
       </c>
-      <c r="M19" s="24" t="n">
+      <c r="M19" s="29" t="n">
         <v>0.3698</v>
       </c>
-      <c r="N19" s="25" t="n">
+      <c r="N19" s="30" t="n">
         <v>0.205</v>
       </c>
-      <c r="O19" s="25" t="n">
+      <c r="O19" s="30" t="n">
         <v>5.203</v>
       </c>
-      <c r="P19" s="23" t="n">
+      <c r="P19" s="28" t="n">
         <v>0.076</v>
       </c>
-      <c r="Q19" s="23" t="n">
+      <c r="Q19" s="28" t="n">
         <v>1.924</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="n">
+      <c r="A20" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="28" t="n">
         <v>1.061</v>
       </c>
-      <c r="C20" s="23" t="n">
+      <c r="C20" s="28" t="n">
         <v>2.98</v>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="28" t="n">
         <v>1.175</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="28" t="n">
         <v>0.373</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="29" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="29" t="n">
         <v>1.1078</v>
       </c>
-      <c r="H20" s="23" t="n">
+      <c r="H20" s="28" t="n">
         <v>0.167</v>
       </c>
-      <c r="I20" s="23" t="n">
+      <c r="I20" s="28" t="n">
         <v>1.638</v>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="J20" s="28" t="n">
         <v>0.185</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="28" t="n">
         <v>1.815</v>
       </c>
-      <c r="L20" s="23" t="n">
+      <c r="L20" s="28" t="n">
         <v>2.847</v>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M20" s="29" t="n">
         <v>0.3512</v>
       </c>
-      <c r="N20" s="25" t="n">
+      <c r="N20" s="30" t="n">
         <v>0.387</v>
       </c>
-      <c r="O20" s="25" t="n">
+      <c r="O20" s="30" t="n">
         <v>5.307</v>
       </c>
-      <c r="P20" s="23" t="n">
+      <c r="P20" s="28" t="n">
         <v>0.136</v>
       </c>
-      <c r="Q20" s="23" t="n">
+      <c r="Q20" s="28" t="n">
         <v>1.864</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="n">
+      <c r="A21" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="23" t="n">
+      <c r="B21" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="23" t="n">
+      <c r="C21" s="28" t="n">
         <v>3.03</v>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="28" t="n">
         <v>1.094</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="28" t="n">
         <v>0.337</v>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="29" t="n">
         <v>0.9139</v>
       </c>
-      <c r="G21" s="24" t="n">
+      <c r="G21" s="29" t="n">
         <v>1.0942</v>
       </c>
-      <c r="H21" s="23" t="n">
+      <c r="H21" s="28" t="n">
         <v>0.219</v>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="28" t="n">
         <v>1.609</v>
       </c>
-      <c r="J21" s="23" t="n">
+      <c r="J21" s="28" t="n">
         <v>0.239</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="28" t="n">
         <v>1.761</v>
       </c>
-      <c r="L21" s="23" t="n">
+      <c r="L21" s="28" t="n">
         <v>2.97</v>
       </c>
-      <c r="M21" s="24" t="n">
+      <c r="M21" s="29" t="n">
         <v>0.3367</v>
       </c>
-      <c r="N21" s="25" t="n">
+      <c r="N21" s="30" t="n">
         <v>0.546</v>
       </c>
-      <c r="O21" s="25" t="n">
+      <c r="O21" s="30" t="n">
         <v>5.394</v>
       </c>
-      <c r="P21" s="23" t="n">
+      <c r="P21" s="28" t="n">
         <v>0.184</v>
       </c>
-      <c r="Q21" s="23" t="n">
+      <c r="Q21" s="28" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="n">
+      <c r="A22" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B22" s="28" t="n">
         <v>0.949</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C22" s="28" t="n">
         <v>3.085</v>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="28" t="n">
         <v>1.028</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="28" t="n">
         <v>0.308</v>
       </c>
-      <c r="F22" s="24" t="n">
+      <c r="F22" s="29" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G22" s="24" t="n">
+      <c r="G22" s="29" t="n">
         <v>1.0837</v>
       </c>
-      <c r="H22" s="23" t="n">
+      <c r="H22" s="28" t="n">
         <v>0.262</v>
       </c>
-      <c r="I22" s="23" t="n">
+      <c r="I22" s="28" t="n">
         <v>1.584</v>
       </c>
-      <c r="J22" s="23" t="n">
+      <c r="J22" s="28" t="n">
         <v>0.284</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="28" t="n">
         <v>1.716</v>
       </c>
-      <c r="L22" s="23" t="n">
+      <c r="L22" s="28" t="n">
         <v>3.078</v>
       </c>
-      <c r="M22" s="24" t="n">
+      <c r="M22" s="29" t="n">
         <v>0.3249</v>
       </c>
-      <c r="N22" s="23" t="n">
+      <c r="N22" s="28" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="O22" s="23" t="n">
+      <c r="O22" s="28" t="n">
         <v>5.469</v>
       </c>
-      <c r="P22" s="23" t="n">
+      <c r="P22" s="28" t="n">
         <v>0.223</v>
       </c>
-      <c r="Q22" s="23" t="n">
+      <c r="Q22" s="28" t="n">
         <v>1.777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="n">
+      <c r="A23" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="28" t="n">
         <v>0.905</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="28" t="n">
         <v>3.136</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="28" t="n">
         <v>0.973</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="28" t="n">
         <v>0.285</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="29" t="n">
         <v>0.93</v>
       </c>
-      <c r="G23" s="24" t="n">
+      <c r="G23" s="29" t="n">
         <v>1.0753</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="28" t="n">
         <v>0.299</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="28" t="n">
         <v>1.561</v>
       </c>
-      <c r="J23" s="23" t="n">
+      <c r="J23" s="28" t="n">
         <v>0.321</v>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K23" s="28" t="n">
         <v>1.679</v>
       </c>
-      <c r="L23" s="23" t="n">
+      <c r="L23" s="28" t="n">
         <v>3.173</v>
       </c>
-      <c r="M23" s="24" t="n">
+      <c r="M23" s="29" t="n">
         <v>0.3152</v>
       </c>
-      <c r="N23" s="25" t="n">
+      <c r="N23" s="30" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="O23" s="25" t="n">
+      <c r="O23" s="30" t="n">
         <v>5.534</v>
       </c>
-      <c r="P23" s="23" t="n">
+      <c r="P23" s="28" t="n">
         <v>0.256</v>
       </c>
-      <c r="Q23" s="23" t="n">
+      <c r="Q23" s="28" t="n">
         <v>1.744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="n">
+      <c r="A24" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="23" t="n">
+      <c r="B24" s="28" t="n">
         <v>0.866</v>
       </c>
-      <c r="C24" s="23" t="n">
+      <c r="C24" s="28" t="n">
         <v>3.189</v>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="28" t="n">
         <v>0.925</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="28" t="n">
         <v>0.266</v>
       </c>
-      <c r="F24" s="24" t="n">
+      <c r="F24" s="29" t="n">
         <v>0.9359</v>
       </c>
-      <c r="G24" s="24" t="n">
+      <c r="G24" s="29" t="n">
         <v>1.0684</v>
       </c>
-      <c r="H24" s="23" t="n">
+      <c r="H24" s="28" t="n">
         <v>0.331</v>
       </c>
-      <c r="I24" s="23" t="n">
+      <c r="I24" s="28" t="n">
         <v>1.541</v>
       </c>
-      <c r="J24" s="23" t="n">
+      <c r="J24" s="28" t="n">
         <v>0.354</v>
       </c>
-      <c r="K24" s="23" t="n">
+      <c r="K24" s="28" t="n">
         <v>1.646</v>
       </c>
-      <c r="L24" s="23" t="n">
+      <c r="L24" s="28" t="n">
         <v>3.258</v>
       </c>
-      <c r="M24" s="24" t="n">
+      <c r="M24" s="29" t="n">
         <v>0.3069</v>
       </c>
-      <c r="N24" s="25" t="n">
+      <c r="N24" s="30" t="n">
         <v>0.924</v>
       </c>
-      <c r="O24" s="25" t="n">
+      <c r="O24" s="30" t="n">
         <v>5.592</v>
       </c>
-      <c r="P24" s="25" t="n">
+      <c r="P24" s="30" t="n">
         <v>0.284</v>
       </c>
-      <c r="Q24" s="25" t="n">
+      <c r="Q24" s="30" t="n">
         <v>1.716</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="n">
+      <c r="A25" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B25" s="28" t="n">
         <v>0.832</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C25" s="28" t="n">
         <v>3.242</v>
       </c>
-      <c r="D25" s="23" t="n">
+      <c r="D25" s="28" t="n">
         <v>0.884</v>
       </c>
-      <c r="E25" s="23" t="n">
+      <c r="E25" s="28" t="n">
         <v>0.249</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="29" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="29" t="n">
         <v>1.0627</v>
       </c>
-      <c r="H25" s="23" t="n">
+      <c r="H25" s="28" t="n">
         <v>0.359</v>
       </c>
-      <c r="I25" s="23" t="n">
+      <c r="I25" s="28" t="n">
         <v>1.523</v>
       </c>
-      <c r="J25" s="23" t="n">
+      <c r="J25" s="28" t="n">
         <v>0.382</v>
       </c>
-      <c r="K25" s="23" t="n">
+      <c r="K25" s="28" t="n">
         <v>1.618</v>
       </c>
-      <c r="L25" s="23" t="n">
+      <c r="L25" s="28" t="n">
         <v>3.336</v>
       </c>
-      <c r="M25" s="24" t="n">
+      <c r="M25" s="29" t="n">
         <v>0.2998</v>
       </c>
-      <c r="N25" s="25" t="n">
+      <c r="N25" s="30" t="n">
         <v>1.026</v>
       </c>
-      <c r="O25" s="25" t="n">
+      <c r="O25" s="30" t="n">
         <v>5.646</v>
       </c>
-      <c r="P25" s="25" t="n">
+      <c r="P25" s="30" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q25" s="25" t="n">
+      <c r="Q25" s="30" t="n">
         <v>1.692</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="n">
+      <c r="A26" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="28" t="n">
         <v>0.802</v>
       </c>
-      <c r="C26" s="23" t="n">
+      <c r="C26" s="28" t="n">
         <v>3.295</v>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="28" t="n">
         <v>0.848</v>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="28" t="n">
         <v>0.235</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="29" t="n">
         <v>0.9453</v>
       </c>
-      <c r="G26" s="24" t="n">
+      <c r="G26" s="29" t="n">
         <v>1.0579</v>
       </c>
-      <c r="H26" s="23" t="n">
+      <c r="H26" s="28" t="n">
         <v>0.384</v>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="28" t="n">
         <v>1.507</v>
       </c>
-      <c r="J26" s="23" t="n">
+      <c r="J26" s="28" t="n">
         <v>0.406</v>
       </c>
-      <c r="K26" s="23" t="n">
+      <c r="K26" s="28" t="n">
         <v>1.594</v>
       </c>
-      <c r="L26" s="23" t="n">
+      <c r="L26" s="28" t="n">
         <v>3.407</v>
       </c>
-      <c r="M26" s="24" t="n">
+      <c r="M26" s="29" t="n">
         <v>0.2935</v>
       </c>
-      <c r="N26" s="25" t="n">
+      <c r="N26" s="30" t="n">
         <v>1.121</v>
       </c>
-      <c r="O26" s="25" t="n">
+      <c r="O26" s="30" t="n">
         <v>5.693</v>
       </c>
-      <c r="P26" s="25" t="n">
+      <c r="P26" s="30" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q26" s="25" t="n">
+      <c r="Q26" s="30" t="n">
         <v>1.671</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n">
+      <c r="A27" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="23" t="n">
+      <c r="B27" s="28" t="n">
         <v>0.775</v>
       </c>
-      <c r="C27" s="23" t="n">
+      <c r="C27" s="28" t="n">
         <v>3.347</v>
       </c>
-      <c r="D27" s="23" t="n">
+      <c r="D27" s="28" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="E27" s="23" t="n">
+      <c r="E27" s="28" t="n">
         <v>0.223</v>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="29" t="n">
         <v>0.949</v>
       </c>
-      <c r="G27" s="24" t="n">
+      <c r="G27" s="29" t="n">
         <v>1.0537</v>
       </c>
-      <c r="H27" s="23" t="n">
+      <c r="H27" s="28" t="n">
         <v>0.406</v>
       </c>
-      <c r="I27" s="23" t="n">
+      <c r="I27" s="28" t="n">
         <v>1.492</v>
       </c>
-      <c r="J27" s="23" t="n">
+      <c r="J27" s="28" t="n">
         <v>0.428</v>
       </c>
-      <c r="K27" s="23" t="n">
+      <c r="K27" s="28" t="n">
         <v>1.572</v>
       </c>
-      <c r="L27" s="23" t="n">
+      <c r="L27" s="28" t="n">
         <v>3.472</v>
       </c>
-      <c r="M27" s="24" t="n">
+      <c r="M27" s="29" t="n">
         <v>0.288</v>
       </c>
-      <c r="N27" s="25" t="n">
+      <c r="N27" s="30" t="n">
         <v>1.207</v>
       </c>
-      <c r="O27" s="25" t="n">
+      <c r="O27" s="30" t="n">
         <v>5.737</v>
       </c>
-      <c r="P27" s="25" t="n">
+      <c r="P27" s="30" t="n">
         <v>0.348</v>
       </c>
-      <c r="Q27" s="25" t="n">
+      <c r="Q27" s="30" t="n">
         <v>1.652</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n">
+      <c r="A28" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="23" t="n">
+      <c r="B28" s="28" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="28" t="n">
         <v>3.398</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="28" t="n">
         <v>0.788</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="28" t="n">
         <v>0.212</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="29" t="n">
         <v>0.9523</v>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="29" t="n">
         <v>1.0501</v>
       </c>
-      <c r="H28" s="23" t="n">
+      <c r="H28" s="28" t="n">
         <v>0.427</v>
       </c>
-      <c r="I28" s="23" t="n">
+      <c r="I28" s="28" t="n">
         <v>1.478</v>
       </c>
-      <c r="J28" s="23" t="n">
+      <c r="J28" s="28" t="n">
         <v>0.448</v>
       </c>
-      <c r="K28" s="23" t="n">
+      <c r="K28" s="28" t="n">
         <v>1.552</v>
       </c>
-      <c r="L28" s="23" t="n">
+      <c r="L28" s="28" t="n">
         <v>3.532</v>
       </c>
-      <c r="M28" s="24" t="n">
+      <c r="M28" s="29" t="n">
         <v>0.2831</v>
       </c>
-      <c r="N28" s="25" t="n">
+      <c r="N28" s="30" t="n">
         <v>1.285</v>
       </c>
-      <c r="O28" s="25" t="n">
+      <c r="O28" s="30" t="n">
         <v>5.779</v>
       </c>
-      <c r="P28" s="25" t="n">
+      <c r="P28" s="30" t="n">
         <v>0.364</v>
       </c>
-      <c r="Q28" s="25" t="n">
+      <c r="Q28" s="30" t="n">
         <v>1.636</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="n">
+      <c r="A29" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="23" t="n">
+      <c r="B29" s="28" t="n">
         <v>0.728</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="28" t="n">
         <v>3.448</v>
       </c>
-      <c r="D29" s="23" t="n">
+      <c r="D29" s="28" t="n">
         <v>0.762</v>
       </c>
-      <c r="E29" s="23" t="n">
+      <c r="E29" s="28" t="n">
         <v>0.203</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="29" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G29" s="29" t="n">
         <v>1.047</v>
       </c>
-      <c r="H29" s="23" t="n">
+      <c r="H29" s="28" t="n">
         <v>0.445</v>
       </c>
-      <c r="I29" s="23" t="n">
+      <c r="I29" s="28" t="n">
         <v>1.465</v>
       </c>
-      <c r="J29" s="23" t="n">
+      <c r="J29" s="28" t="n">
         <v>0.466</v>
       </c>
-      <c r="K29" s="23" t="n">
+      <c r="K29" s="28" t="n">
         <v>1.534</v>
       </c>
-      <c r="L29" s="23" t="n">
+      <c r="L29" s="28" t="n">
         <v>3.588</v>
       </c>
-      <c r="M29" s="24" t="n">
+      <c r="M29" s="29" t="n">
         <v>0.2787</v>
       </c>
-      <c r="N29" s="25" t="n">
+      <c r="N29" s="30" t="n">
         <v>1.359</v>
       </c>
-      <c r="O29" s="25" t="n">
+      <c r="O29" s="30" t="n">
         <v>5.817</v>
       </c>
-      <c r="P29" s="25" t="n">
+      <c r="P29" s="30" t="n">
         <v>0.379</v>
       </c>
-      <c r="Q29" s="25" t="n">
+      <c r="Q29" s="30" t="n">
         <v>1.621</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="n">
+      <c r="A30" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="23" t="n">
+      <c r="B30" s="28" t="n">
         <v>0.707</v>
       </c>
-      <c r="C30" s="23" t="n">
+      <c r="C30" s="28" t="n">
         <v>3.497</v>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="28" t="n">
         <v>0.738</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="28" t="n">
         <v>0.194</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="29" t="n">
         <v>0.9576</v>
       </c>
-      <c r="G30" s="24" t="n">
+      <c r="G30" s="29" t="n">
         <v>1.0442</v>
       </c>
-      <c r="H30" s="23" t="n">
+      <c r="H30" s="28" t="n">
         <v>0.461</v>
       </c>
-      <c r="I30" s="23" t="n">
+      <c r="I30" s="28" t="n">
         <v>1.454</v>
       </c>
-      <c r="J30" s="23" t="n">
+      <c r="J30" s="28" t="n">
         <v>0.482</v>
       </c>
-      <c r="K30" s="23" t="n">
+      <c r="K30" s="28" t="n">
         <v>1.518</v>
       </c>
-      <c r="L30" s="23" t="n">
+      <c r="L30" s="28" t="n">
         <v>3.64</v>
       </c>
-      <c r="M30" s="24" t="n">
+      <c r="M30" s="29" t="n">
         <v>0.2747</v>
       </c>
-      <c r="N30" s="25" t="n">
+      <c r="N30" s="30" t="n">
         <v>1.426</v>
       </c>
-      <c r="O30" s="25" t="n">
+      <c r="O30" s="30" t="n">
         <v>5.854</v>
       </c>
-      <c r="P30" s="25" t="n">
+      <c r="P30" s="30" t="n">
         <v>0.392</v>
       </c>
-      <c r="Q30" s="23" t="n">
+      <c r="Q30" s="28" t="n">
         <v>1.608</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="n">
+      <c r="A31" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="23" t="n">
+      <c r="B31" s="28" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C31" s="28" t="n">
         <v>3.545</v>
       </c>
-      <c r="D31" s="23" t="n">
+      <c r="D31" s="28" t="n">
         <v>0.717</v>
       </c>
-      <c r="E31" s="23" t="n">
+      <c r="E31" s="28" t="n">
         <v>0.187</v>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="29" t="n">
         <v>0.9599</v>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G31" s="29" t="n">
         <v>1.0418</v>
       </c>
-      <c r="H31" s="23" t="n">
+      <c r="H31" s="28" t="n">
         <v>0.477</v>
       </c>
-      <c r="I31" s="23" t="n">
+      <c r="I31" s="28" t="n">
         <v>1.443</v>
       </c>
-      <c r="J31" s="23" t="n">
+      <c r="J31" s="28" t="n">
         <v>0.497</v>
       </c>
-      <c r="K31" s="23" t="n">
+      <c r="K31" s="28" t="n">
         <v>1.503</v>
       </c>
-      <c r="L31" s="23" t="n">
+      <c r="L31" s="28" t="n">
         <v>3.689</v>
       </c>
-      <c r="M31" s="24" t="n">
+      <c r="M31" s="29" t="n">
         <v>0.2711</v>
       </c>
-      <c r="N31" s="25" t="n">
+      <c r="N31" s="30" t="n">
         <v>1.49</v>
       </c>
-      <c r="O31" s="25" t="n">
+      <c r="O31" s="30" t="n">
         <v>5.888</v>
       </c>
-      <c r="P31" s="25" t="n">
+      <c r="P31" s="30" t="n">
         <v>0.404</v>
       </c>
-      <c r="Q31" s="25" t="n">
+      <c r="Q31" s="30" t="n">
         <v>1.596</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n">
+      <c r="A32" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="23" t="n">
+      <c r="B32" s="28" t="n">
         <v>0.671</v>
       </c>
-      <c r="C32" s="23" t="n">
+      <c r="C32" s="28" t="n">
         <v>3.592</v>
       </c>
-      <c r="D32" s="23" t="n">
+      <c r="D32" s="28" t="n">
         <v>0.697</v>
       </c>
-      <c r="E32" s="23" t="n">
+      <c r="E32" s="28" t="n">
         <v>0.18</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="29" t="n">
         <v>0.9619</v>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="29" t="n">
         <v>1.0396</v>
       </c>
-      <c r="H32" s="23" t="n">
+      <c r="H32" s="28" t="n">
         <v>0.491</v>
       </c>
-      <c r="I32" s="23" t="n">
+      <c r="I32" s="28" t="n">
         <v>1.433</v>
       </c>
-      <c r="J32" s="23" t="n">
+      <c r="J32" s="28" t="n">
         <v>0.51</v>
       </c>
-      <c r="K32" s="23" t="n">
+      <c r="K32" s="28" t="n">
         <v>1.49</v>
       </c>
-      <c r="L32" s="23" t="n">
+      <c r="L32" s="28" t="n">
         <v>3.735</v>
       </c>
-      <c r="M32" s="24" t="n">
+      <c r="M32" s="29" t="n">
         <v>0.2677</v>
       </c>
-      <c r="N32" s="25" t="n">
+      <c r="N32" s="30" t="n">
         <v>1.548</v>
       </c>
-      <c r="O32" s="25" t="n">
+      <c r="O32" s="30" t="n">
         <v>5.922</v>
       </c>
-      <c r="P32" s="25" t="n">
+      <c r="P32" s="30" t="n">
         <v>0.414</v>
       </c>
-      <c r="Q32" s="25" t="n">
+      <c r="Q32" s="30" t="n">
         <v>1.586</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="n">
+      <c r="A33" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="28" t="n">
         <v>0.655</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="28" t="n">
         <v>3.639</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="28" t="n">
         <v>0.679</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="28" t="n">
         <v>0.173</v>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="29" t="n">
         <v>0.9638</v>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="29" t="n">
         <v>1.0376</v>
       </c>
-      <c r="H33" s="23" t="n">
+      <c r="H33" s="28" t="n">
         <v>0.504</v>
       </c>
-      <c r="I33" s="23" t="n">
+      <c r="I33" s="28" t="n">
         <v>1.424</v>
       </c>
-      <c r="J33" s="23" t="n">
+      <c r="J33" s="28" t="n">
         <v>0.523</v>
       </c>
-      <c r="K33" s="23" t="n">
+      <c r="K33" s="28" t="n">
         <v>1.477</v>
       </c>
-      <c r="L33" s="23" t="n">
+      <c r="L33" s="28" t="n">
         <v>3.778</v>
       </c>
-      <c r="M33" s="24" t="n">
+      <c r="M33" s="29" t="n">
         <v>0.2647</v>
       </c>
-      <c r="N33" s="25" t="n">
+      <c r="N33" s="30" t="n">
         <v>1.606</v>
       </c>
-      <c r="O33" s="25" t="n">
+      <c r="O33" s="30" t="n">
         <v>5.95</v>
       </c>
-      <c r="P33" s="23" t="n">
+      <c r="P33" s="28" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q33" s="23" t="n">
+      <c r="Q33" s="28" t="n">
         <v>1.575</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n">
+      <c r="A34" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="28" t="n">
         <v>0.64</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="28" t="n">
         <v>3.684</v>
       </c>
-      <c r="D34" s="23" t="n">
+      <c r="D34" s="28" t="n">
         <v>0.662</v>
       </c>
-      <c r="E34" s="23" t="n">
+      <c r="E34" s="28" t="n">
         <v>0.167</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="29" t="n">
         <v>0.9655</v>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G34" s="29" t="n">
         <v>1.0358</v>
       </c>
-      <c r="H34" s="23" t="n">
+      <c r="H34" s="28" t="n">
         <v>0.516</v>
       </c>
-      <c r="I34" s="23" t="n">
+      <c r="I34" s="28" t="n">
         <v>1.415</v>
       </c>
-      <c r="J34" s="23" t="n">
+      <c r="J34" s="28" t="n">
         <v>0.534</v>
       </c>
-      <c r="K34" s="23" t="n">
+      <c r="K34" s="28" t="n">
         <v>1.466</v>
       </c>
-      <c r="L34" s="23" t="n">
+      <c r="L34" s="28" t="n">
         <v>3.819</v>
       </c>
-      <c r="M34" s="24" t="n">
+      <c r="M34" s="29" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N34" s="23" t="n">
+      <c r="N34" s="28" t="n">
         <v>1.659</v>
       </c>
-      <c r="O34" s="23" t="n">
+      <c r="O34" s="28" t="n">
         <v>5.979</v>
       </c>
-      <c r="P34" s="23" t="n">
+      <c r="P34" s="28" t="n">
         <v>0.434</v>
       </c>
-      <c r="Q34" s="23" t="n">
+      <c r="Q34" s="28" t="n">
         <v>1.566</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="n">
+      <c r="A35" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="28" t="n">
         <v>0.626</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="28" t="n">
         <v>3.729</v>
       </c>
-      <c r="D35" s="23" t="n">
+      <c r="D35" s="28" t="n">
         <v>0.647</v>
       </c>
-      <c r="E35" s="23" t="n">
+      <c r="E35" s="28" t="n">
         <v>0.162</v>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="29" t="n">
         <v>0.967</v>
       </c>
-      <c r="G35" s="24" t="n">
+      <c r="G35" s="29" t="n">
         <v>1.0342</v>
       </c>
-      <c r="H35" s="23" t="n">
+      <c r="H35" s="28" t="n">
         <v>0.527</v>
       </c>
-      <c r="I35" s="23" t="n">
+      <c r="I35" s="28" t="n">
         <v>1.407</v>
       </c>
-      <c r="J35" s="23" t="n">
+      <c r="J35" s="28" t="n">
         <v>0.545</v>
       </c>
-      <c r="K35" s="23" t="n">
+      <c r="K35" s="28" t="n">
         <v>1.455</v>
       </c>
-      <c r="L35" s="23" t="n">
+      <c r="L35" s="28" t="n">
         <v>3.858</v>
       </c>
-      <c r="M35" s="24" t="n">
+      <c r="M35" s="29" t="n">
         <v>0.2592</v>
       </c>
-      <c r="N35" s="23" t="n">
+      <c r="N35" s="28" t="n">
         <v>1.71</v>
       </c>
-      <c r="O35" s="23" t="n">
+      <c r="O35" s="28" t="n">
         <v>6.006</v>
       </c>
-      <c r="P35" s="23" t="n">
+      <c r="P35" s="28" t="n">
         <v>0.443</v>
       </c>
-      <c r="Q35" s="23" t="n">
+      <c r="Q35" s="28" t="n">
         <v>1.557</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="n">
+      <c r="A36" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="28" t="n">
         <v>0.612</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="28" t="n">
         <v>3.773</v>
       </c>
-      <c r="D36" s="23" t="n">
+      <c r="D36" s="28" t="n">
         <v>0.632</v>
       </c>
-      <c r="E36" s="23" t="n">
+      <c r="E36" s="28" t="n">
         <v>0.157</v>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="29" t="n">
         <v>0.9684</v>
       </c>
-      <c r="G36" s="24" t="n">
+      <c r="G36" s="29" t="n">
         <v>1.0327</v>
       </c>
-      <c r="H36" s="23" t="n">
+      <c r="H36" s="28" t="n">
         <v>0.538</v>
       </c>
-      <c r="I36" s="23" t="n">
+      <c r="I36" s="28" t="n">
         <v>1.399</v>
       </c>
-      <c r="J36" s="23" t="n">
+      <c r="J36" s="28" t="n">
         <v>0.555</v>
       </c>
-      <c r="K36" s="23" t="n">
+      <c r="K36" s="28" t="n">
         <v>1.445</v>
       </c>
-      <c r="L36" s="23" t="n">
+      <c r="L36" s="28" t="n">
         <v>3.895</v>
       </c>
-      <c r="M36" s="24" t="n">
+      <c r="M36" s="29" t="n">
         <v>0.2567</v>
       </c>
-      <c r="N36" s="23" t="n">
+      <c r="N36" s="28" t="n">
         <v>1.759</v>
       </c>
-      <c r="O36" s="23" t="n">
+      <c r="O36" s="28" t="n">
         <v>6.031</v>
       </c>
-      <c r="P36" s="25" t="n">
+      <c r="P36" s="30" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q36" s="23" t="n">
+      <c r="Q36" s="28" t="n">
         <v>1.548</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="n">
+      <c r="A37" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="28" t="n">
         <v>0.6</v>
       </c>
-      <c r="C37" s="23" t="n">
+      <c r="C37" s="28" t="n">
         <v>3.816</v>
       </c>
-      <c r="D37" s="23" t="n">
+      <c r="D37" s="28" t="n">
         <v>0.619</v>
       </c>
-      <c r="E37" s="23" t="n">
+      <c r="E37" s="28" t="n">
         <v>0.153</v>
       </c>
-      <c r="F37" s="26" t="n">
+      <c r="F37" s="31" t="n">
         <v>0.9696</v>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="29" t="n">
         <v>1.0313</v>
       </c>
-      <c r="H37" s="23" t="n">
+      <c r="H37" s="28" t="n">
         <v>0.548</v>
       </c>
-      <c r="I37" s="23" t="n">
+      <c r="I37" s="28" t="n">
         <v>1.392</v>
       </c>
-      <c r="J37" s="23" t="n">
+      <c r="J37" s="28" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="K37" s="23" t="n">
+      <c r="K37" s="28" t="n">
         <v>1.435</v>
       </c>
-      <c r="L37" s="23" t="n">
+      <c r="L37" s="28" t="n">
         <v>3.931</v>
       </c>
-      <c r="M37" s="24" t="n">
+      <c r="M37" s="29" t="n">
         <v>0.2544</v>
       </c>
-      <c r="N37" s="25" t="n">
+      <c r="N37" s="30" t="n">
         <v>1.804</v>
       </c>
-      <c r="O37" s="25" t="n">
+      <c r="O37" s="30" t="n">
         <v>6.058</v>
       </c>
-      <c r="P37" s="23" t="n">
+      <c r="P37" s="28" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q37" s="23" t="n">
+      <c r="Q37" s="28" t="n">
         <v>1.541</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>&gt;25</t>
         </is>
       </c>
-      <c r="B38" s="27" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr"/>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr"/>
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr"/>
-      <c r="F38" s="24" t="n">
+      <c r="E38" s="32" t="inlineStr"/>
+      <c r="F38" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G38" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="27" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="I38" s="27" t="inlineStr">
+      <c r="I38" s="32" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="J38" s="27" t="inlineStr">
+      <c r="J38" s="32" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="K38" s="27" t="inlineStr">
+      <c r="K38" s="32" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L38" s="27" t="inlineStr"/>
-      <c r="M38" s="27" t="inlineStr"/>
-      <c r="N38" s="27" t="inlineStr"/>
-      <c r="O38" s="27" t="inlineStr"/>
-      <c r="P38" s="27" t="inlineStr"/>
-      <c r="Q38" s="27" t="inlineStr"/>
+      <c r="L38" s="32" t="inlineStr"/>
+      <c r="M38" s="32" t="inlineStr"/>
+      <c r="N38" s="32" t="inlineStr"/>
+      <c r="O38" s="32" t="inlineStr"/>
+      <c r="P38" s="32" t="inlineStr"/>
+      <c r="Q38" s="32" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>Table A - Bias Correction Factors For Estimating Standard Deviations</t>
         </is>
@@ -4245,7 +5129,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>USED for c4 and d3 (Table 18 does not give them). Reference for d2 and c2.</t>
         </is>
@@ -4279,585 +5163,585 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="n">
+      <c r="A44" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="23" t="n">
+      <c r="B44" s="28" t="n">
         <v>1.128</v>
       </c>
-      <c r="C44" s="24" t="n">
+      <c r="C44" s="29" t="n">
         <v>0.5642</v>
       </c>
-      <c r="D44" s="24" t="n">
+      <c r="D44" s="29" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="29" t="n">
         <v>0.8525</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="n">
+      <c r="A45" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="23" t="n">
+      <c r="B45" s="28" t="n">
         <v>1.693</v>
       </c>
-      <c r="C45" s="24" t="n">
+      <c r="C45" s="29" t="n">
         <v>0.7236</v>
       </c>
-      <c r="D45" s="24" t="n">
+      <c r="D45" s="29" t="n">
         <v>0.8862</v>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="29" t="n">
         <v>0.8884</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="n">
+      <c r="A46" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="23" t="n">
+      <c r="B46" s="28" t="n">
         <v>2.059</v>
       </c>
-      <c r="C46" s="24" t="n">
+      <c r="C46" s="29" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="D46" s="24" t="n">
+      <c r="D46" s="29" t="n">
         <v>0.9213</v>
       </c>
-      <c r="E46" s="24" t="n">
+      <c r="E46" s="29" t="n">
         <v>0.8798</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="n">
+      <c r="A47" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="23" t="n">
+      <c r="B47" s="28" t="n">
         <v>2.326</v>
       </c>
-      <c r="C47" s="24" t="n">
+      <c r="C47" s="29" t="n">
         <v>0.8407</v>
       </c>
-      <c r="D47" s="24" t="n">
+      <c r="D47" s="29" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E47" s="24" t="n">
+      <c r="E47" s="29" t="n">
         <v>0.8641</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="n">
+      <c r="A48" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="23" t="n">
+      <c r="B48" s="28" t="n">
         <v>2.534</v>
       </c>
-      <c r="C48" s="24" t="n">
+      <c r="C48" s="29" t="n">
         <v>0.8686</v>
       </c>
-      <c r="D48" s="24" t="n">
+      <c r="D48" s="29" t="n">
         <v>0.9515</v>
       </c>
-      <c r="E48" s="24" t="n">
+      <c r="E48" s="29" t="n">
         <v>0.848</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n">
+      <c r="A49" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="23" t="n">
+      <c r="B49" s="28" t="n">
         <v>2.704</v>
       </c>
-      <c r="C49" s="24" t="n">
+      <c r="C49" s="29" t="n">
         <v>0.8882</v>
       </c>
-      <c r="D49" s="24" t="n">
+      <c r="D49" s="29" t="n">
         <v>0.9594</v>
       </c>
-      <c r="E49" s="24" t="n">
+      <c r="E49" s="29" t="n">
         <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="n">
+      <c r="A50" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="23" t="n">
+      <c r="B50" s="28" t="n">
         <v>2.847</v>
       </c>
-      <c r="C50" s="24" t="n">
+      <c r="C50" s="29" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="D50" s="24" t="n">
+      <c r="D50" s="29" t="n">
         <v>0.965</v>
       </c>
-      <c r="E50" s="24" t="n">
+      <c r="E50" s="29" t="n">
         <v>0.8198</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="n">
+      <c r="A51" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="23" t="n">
+      <c r="B51" s="28" t="n">
         <v>2.97</v>
       </c>
-      <c r="C51" s="24" t="n">
+      <c r="C51" s="29" t="n">
         <v>0.9139</v>
       </c>
-      <c r="D51" s="24" t="n">
+      <c r="D51" s="29" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E51" s="29" t="n">
         <v>0.8078</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="n">
+      <c r="A52" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="23" t="n">
+      <c r="B52" s="28" t="n">
         <v>3.078</v>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="29" t="n">
         <v>0.9227</v>
       </c>
-      <c r="D52" s="24" t="n">
+      <c r="D52" s="29" t="n">
         <v>0.9727</v>
       </c>
-      <c r="E52" s="24" t="n">
+      <c r="E52" s="29" t="n">
         <v>0.7971</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="n">
+      <c r="A53" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="23" t="n">
+      <c r="B53" s="28" t="n">
         <v>3.173</v>
       </c>
-      <c r="C53" s="24" t="n">
+      <c r="C53" s="29" t="n">
         <v>0.93</v>
       </c>
-      <c r="D53" s="24" t="n">
+      <c r="D53" s="29" t="n">
         <v>0.9754</v>
       </c>
-      <c r="E53" s="24" t="n">
+      <c r="E53" s="29" t="n">
         <v>0.7873</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="n">
+      <c r="A54" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="23" t="n">
+      <c r="B54" s="28" t="n">
         <v>3.258</v>
       </c>
-      <c r="C54" s="24" t="n">
+      <c r="C54" s="29" t="n">
         <v>0.9359</v>
       </c>
-      <c r="D54" s="24" t="n">
+      <c r="D54" s="29" t="n">
         <v>0.9776</v>
       </c>
-      <c r="E54" s="26" t="n">
+      <c r="E54" s="31" t="n">
         <v>0.7785</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="n">
+      <c r="A55" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="23" t="n">
+      <c r="B55" s="28" t="n">
         <v>3.336</v>
       </c>
-      <c r="C55" s="24" t="n">
+      <c r="C55" s="29" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="D55" s="24" t="n">
+      <c r="D55" s="29" t="n">
         <v>0.9794</v>
       </c>
-      <c r="E55" s="24" t="n">
+      <c r="E55" s="29" t="n">
         <v>0.7704</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="n">
+      <c r="A56" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="23" t="n">
+      <c r="B56" s="28" t="n">
         <v>3.407</v>
       </c>
-      <c r="C56" s="24" t="n">
+      <c r="C56" s="29" t="n">
         <v>0.9453</v>
       </c>
-      <c r="D56" s="24" t="n">
+      <c r="D56" s="29" t="n">
         <v>0.981</v>
       </c>
-      <c r="E56" s="24" t="n">
+      <c r="E56" s="29" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n">
+      <c r="A57" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="23" t="n">
+      <c r="B57" s="28" t="n">
         <v>3.472</v>
       </c>
-      <c r="C57" s="24" t="n">
+      <c r="C57" s="29" t="n">
         <v>0.949</v>
       </c>
-      <c r="D57" s="24" t="n">
+      <c r="D57" s="29" t="n">
         <v>0.9823</v>
       </c>
-      <c r="E57" s="24" t="n">
+      <c r="E57" s="29" t="n">
         <v>0.7562</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="n">
+      <c r="A58" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B58" s="23" t="n">
+      <c r="B58" s="28" t="n">
         <v>3.532</v>
       </c>
-      <c r="C58" s="24" t="n">
+      <c r="C58" s="29" t="n">
         <v>0.9523</v>
       </c>
-      <c r="D58" s="24" t="n">
+      <c r="D58" s="29" t="n">
         <v>0.9835</v>
       </c>
-      <c r="E58" s="24" t="n">
+      <c r="E58" s="29" t="n">
         <v>0.7499</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="n">
+      <c r="A59" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B59" s="23" t="n">
+      <c r="B59" s="28" t="n">
         <v>3.588</v>
       </c>
-      <c r="C59" s="24" t="n">
+      <c r="C59" s="29" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="D59" s="24" t="n">
+      <c r="D59" s="29" t="n">
         <v>0.9845</v>
       </c>
-      <c r="E59" s="24" t="n">
+      <c r="E59" s="29" t="n">
         <v>0.7441</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="n">
+      <c r="A60" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B60" s="23" t="n">
+      <c r="B60" s="28" t="n">
         <v>3.64</v>
       </c>
-      <c r="C60" s="24" t="n">
+      <c r="C60" s="29" t="n">
         <v>0.9576</v>
       </c>
-      <c r="D60" s="24" t="n">
+      <c r="D60" s="29" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="E60" s="24" t="n">
+      <c r="E60" s="29" t="n">
         <v>0.7386</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="n">
+      <c r="A61" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B61" s="23" t="n">
+      <c r="B61" s="28" t="n">
         <v>3.689</v>
       </c>
-      <c r="C61" s="24" t="n">
+      <c r="C61" s="29" t="n">
         <v>0.9599</v>
       </c>
-      <c r="D61" s="24" t="n">
+      <c r="D61" s="29" t="n">
         <v>0.9862</v>
       </c>
-      <c r="E61" s="24" t="n">
+      <c r="E61" s="29" t="n">
         <v>0.7335</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="n">
+      <c r="A62" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B62" s="23" t="n">
+      <c r="B62" s="28" t="n">
         <v>3.735</v>
       </c>
-      <c r="C62" s="24" t="n">
+      <c r="C62" s="29" t="n">
         <v>0.9619</v>
       </c>
-      <c r="D62" s="24" t="n">
+      <c r="D62" s="29" t="n">
         <v>0.9869</v>
       </c>
-      <c r="E62" s="24" t="n">
+      <c r="E62" s="29" t="n">
         <v>0.7287</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="22" t="n">
+      <c r="A63" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="23" t="n">
+      <c r="B63" s="28" t="n">
         <v>3.778</v>
       </c>
-      <c r="C63" s="24" t="n">
+      <c r="C63" s="29" t="n">
         <v>0.9638</v>
       </c>
-      <c r="D63" s="24" t="n">
+      <c r="D63" s="29" t="n">
         <v>0.9876</v>
       </c>
-      <c r="E63" s="26" t="n">
+      <c r="E63" s="31" t="n">
         <v>0.7272</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="n">
+      <c r="A64" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="B64" s="23" t="n">
+      <c r="B64" s="28" t="n">
         <v>3.819</v>
       </c>
-      <c r="C64" s="24" t="n">
+      <c r="C64" s="29" t="n">
         <v>0.9655</v>
       </c>
-      <c r="D64" s="24" t="n">
+      <c r="D64" s="29" t="n">
         <v>0.9882</v>
       </c>
-      <c r="E64" s="24" t="n">
+      <c r="E64" s="29" t="n">
         <v>0.7199</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="22" t="n">
+      <c r="A65" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="23" t="n">
+      <c r="B65" s="28" t="n">
         <v>3.858</v>
       </c>
-      <c r="C65" s="24" t="n">
+      <c r="C65" s="29" t="n">
         <v>0.967</v>
       </c>
-      <c r="D65" s="24" t="n">
+      <c r="D65" s="29" t="n">
         <v>0.9887</v>
       </c>
-      <c r="E65" s="24" t="n">
+      <c r="E65" s="29" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="n">
+      <c r="A66" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="23" t="n">
+      <c r="B66" s="28" t="n">
         <v>3.895</v>
       </c>
-      <c r="C66" s="24" t="n">
+      <c r="C66" s="29" t="n">
         <v>0.9684</v>
       </c>
-      <c r="D66" s="24" t="n">
+      <c r="D66" s="29" t="n">
         <v>0.9892</v>
       </c>
-      <c r="E66" s="24" t="n">
+      <c r="E66" s="29" t="n">
         <v>0.7121</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="22" t="n">
+      <c r="A67" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="B67" s="23" t="n">
+      <c r="B67" s="28" t="n">
         <v>3.931</v>
       </c>
-      <c r="C67" s="26" t="n">
+      <c r="C67" s="31" t="n">
         <v>0.9695</v>
       </c>
-      <c r="D67" s="24" t="n">
+      <c r="D67" s="29" t="n">
         <v>0.9896</v>
       </c>
-      <c r="E67" s="24" t="n">
+      <c r="E67" s="29" t="n">
         <v>0.7084</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="22" t="n">
+      <c r="A68" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="B68" s="23" t="n">
+      <c r="B68" s="28" t="n">
         <v>4.086</v>
       </c>
-      <c r="C68" s="24" t="n">
+      <c r="C68" s="29" t="n">
         <v>0.9748</v>
       </c>
-      <c r="D68" s="24" t="n">
+      <c r="D68" s="29" t="n">
         <v>0.9915</v>
       </c>
-      <c r="E68" s="24" t="n">
+      <c r="E68" s="29" t="n">
         <v>0.6927</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="22" t="n">
+      <c r="A69" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="B69" s="23" t="n">
+      <c r="B69" s="28" t="n">
         <v>4.213</v>
       </c>
-      <c r="C69" s="24" t="n">
+      <c r="C69" s="29" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D69" s="24" t="n">
+      <c r="D69" s="29" t="n">
         <v>0.9927</v>
       </c>
-      <c r="E69" s="24" t="n">
+      <c r="E69" s="29" t="n">
         <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="22" t="n">
+      <c r="A70" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="B70" s="23" t="n">
+      <c r="B70" s="28" t="n">
         <v>4.322</v>
       </c>
-      <c r="C70" s="24" t="n">
+      <c r="C70" s="29" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D70" s="24" t="n">
+      <c r="D70" s="29" t="n">
         <v>0.9936</v>
       </c>
-      <c r="E70" s="24" t="n">
+      <c r="E70" s="29" t="n">
         <v>0.6692</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="22" t="n">
+      <c r="A71" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="B71" s="23" t="n">
+      <c r="B71" s="28" t="n">
         <v>4.415</v>
       </c>
-      <c r="C71" s="24" t="n">
+      <c r="C71" s="29" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D71" s="24" t="n">
+      <c r="D71" s="29" t="n">
         <v>0.9943</v>
       </c>
-      <c r="E71" s="24" t="n">
+      <c r="E71" s="29" t="n">
         <v>0.6601</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="22" t="n">
+      <c r="A72" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="B72" s="23" t="n">
+      <c r="B72" s="28" t="n">
         <v>4.498</v>
       </c>
-      <c r="C72" s="24" t="n">
+      <c r="C72" s="29" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D72" s="24" t="n">
+      <c r="D72" s="29" t="n">
         <v>0.9949</v>
       </c>
-      <c r="E72" s="24" t="n">
+      <c r="E72" s="29" t="n">
         <v>0.6521</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="22" t="n">
+      <c r="A73" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="B73" s="23" t="n">
+      <c r="B73" s="28" t="n">
         <v>4.639</v>
       </c>
-      <c r="C73" s="24" t="n">
+      <c r="C73" s="29" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D73" s="24" t="n">
+      <c r="D73" s="29" t="n">
         <v>0.9957</v>
       </c>
-      <c r="E73" s="24" t="n">
+      <c r="E73" s="29" t="n">
         <v>0.6389</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="22" t="n">
+      <c r="A74" s="27" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="23" t="n">
+      <c r="B74" s="28" t="n">
         <v>4.755</v>
       </c>
-      <c r="C74" s="24" t="n">
+      <c r="C74" s="29" t="n">
         <v>0.9892</v>
       </c>
-      <c r="D74" s="24" t="n">
+      <c r="D74" s="29" t="n">
         <v>0.9963</v>
       </c>
-      <c r="E74" s="24" t="n">
+      <c r="E74" s="29" t="n">
         <v>0.6283</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="22" t="n">
+      <c r="A75" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="B75" s="23" t="n">
+      <c r="B75" s="28" t="n">
         <v>4.854</v>
       </c>
-      <c r="C75" s="24" t="n">
+      <c r="C75" s="29" t="n">
         <v>0.9906</v>
       </c>
-      <c r="D75" s="24" t="n">
+      <c r="D75" s="29" t="n">
         <v>0.9968</v>
       </c>
-      <c r="E75" s="24" t="n">
+      <c r="E75" s="29" t="n">
         <v>0.6194</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="22" t="n">
+      <c r="A76" s="27" t="n">
         <v>90</v>
       </c>
-      <c r="B76" s="23" t="n">
+      <c r="B76" s="28" t="n">
         <v>4.939</v>
       </c>
-      <c r="C76" s="24" t="n">
+      <c r="C76" s="29" t="n">
         <v>0.9916</v>
       </c>
-      <c r="D76" s="24" t="n">
+      <c r="D76" s="29" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E76" s="24" t="n">
+      <c r="E76" s="29" t="n">
         <v>0.6118</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="22" t="n">
+      <c r="A77" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="B77" s="23" t="n">
+      <c r="B77" s="28" t="n">
         <v>5.015</v>
       </c>
-      <c r="C77" s="24" t="n">
+      <c r="C77" s="29" t="n">
         <v>0.9925</v>
       </c>
-      <c r="D77" s="24" t="n">
+      <c r="D77" s="29" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="E77" s="24" t="n">
+      <c r="E77" s="29" t="n">
         <v>0.6052</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="21" t="inlineStr">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>Control Chart Constants - Chart for Average &amp; Chart for Standard Deviations (Six Sigma Demystified, 2nd ed.)</t>
         </is>
@@ -4871,7 +5755,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="21" t="inlineStr">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>USED for A3, B5 and B6 (Table 18 and Table A do not give them). Reference otherwise.</t>
         </is>
@@ -4930,791 +5814,791 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="22" t="n">
+      <c r="A83" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="23" t="n">
+      <c r="B83" s="28" t="n">
         <v>2.121</v>
       </c>
-      <c r="C83" s="23" t="n">
+      <c r="C83" s="28" t="n">
         <v>1.88</v>
       </c>
-      <c r="D83" s="23" t="n">
+      <c r="D83" s="28" t="n">
         <v>2.659</v>
       </c>
-      <c r="E83" s="24" t="n">
+      <c r="E83" s="29" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="F83" s="24" t="n">
+      <c r="F83" s="29" t="n">
         <v>1.2533</v>
       </c>
-      <c r="G83" s="22" t="n">
+      <c r="G83" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="23" t="n">
+      <c r="H83" s="28" t="n">
         <v>3.267</v>
       </c>
-      <c r="I83" s="22" t="n">
+      <c r="I83" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="23" t="n">
+      <c r="J83" s="28" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="22" t="n">
+      <c r="A84" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="B84" s="23" t="n">
+      <c r="B84" s="28" t="n">
         <v>2.606</v>
       </c>
-      <c r="C84" s="27" t="inlineStr"/>
-      <c r="D84" s="27" t="inlineStr"/>
-      <c r="E84" s="27" t="inlineStr"/>
-      <c r="F84" s="27" t="inlineStr"/>
-      <c r="G84" s="27" t="inlineStr"/>
-      <c r="H84" s="27" t="inlineStr"/>
-      <c r="I84" s="27" t="inlineStr"/>
-      <c r="J84" s="27" t="inlineStr"/>
+      <c r="C84" s="32" t="inlineStr"/>
+      <c r="D84" s="32" t="inlineStr"/>
+      <c r="E84" s="32" t="inlineStr"/>
+      <c r="F84" s="32" t="inlineStr"/>
+      <c r="G84" s="32" t="inlineStr"/>
+      <c r="H84" s="32" t="inlineStr"/>
+      <c r="I84" s="32" t="inlineStr"/>
+      <c r="J84" s="32" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="22" t="n">
+      <c r="A85" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="23" t="n">
+      <c r="B85" s="28" t="n">
         <v>1.732</v>
       </c>
-      <c r="C85" s="23" t="n">
+      <c r="C85" s="28" t="n">
         <v>1.023</v>
       </c>
-      <c r="D85" s="23" t="n">
+      <c r="D85" s="28" t="n">
         <v>1.954</v>
       </c>
-      <c r="E85" s="24" t="n">
+      <c r="E85" s="29" t="n">
         <v>0.8862</v>
       </c>
-      <c r="F85" s="24" t="n">
+      <c r="F85" s="29" t="n">
         <v>1.1284</v>
       </c>
-      <c r="G85" s="22" t="n">
+      <c r="G85" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="23" t="n">
+      <c r="H85" s="28" t="n">
         <v>2.568</v>
       </c>
-      <c r="I85" s="22" t="n">
+      <c r="I85" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="23" t="n">
+      <c r="J85" s="28" t="n">
         <v>2.276</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="22" t="n">
+      <c r="A86" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="23" t="n">
+      <c r="B86" s="28" t="n">
         <v>1.5</v>
       </c>
-      <c r="C86" s="23" t="n">
+      <c r="C86" s="28" t="n">
         <v>0.729</v>
       </c>
-      <c r="D86" s="23" t="n">
+      <c r="D86" s="28" t="n">
         <v>1.628</v>
       </c>
-      <c r="E86" s="24" t="n">
+      <c r="E86" s="29" t="n">
         <v>0.9213</v>
       </c>
-      <c r="F86" s="24" t="n">
+      <c r="F86" s="29" t="n">
         <v>1.0854</v>
       </c>
-      <c r="G86" s="22" t="n">
+      <c r="G86" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="23" t="n">
+      <c r="H86" s="28" t="n">
         <v>2.266</v>
       </c>
-      <c r="I86" s="22" t="n">
+      <c r="I86" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="23" t="n">
+      <c r="J86" s="28" t="n">
         <v>2.088</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="22" t="n">
+      <c r="A87" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="23" t="n">
+      <c r="B87" s="28" t="n">
         <v>1.342</v>
       </c>
-      <c r="C87" s="23" t="n">
+      <c r="C87" s="28" t="n">
         <v>0.577</v>
       </c>
-      <c r="D87" s="23" t="n">
+      <c r="D87" s="28" t="n">
         <v>1.427</v>
       </c>
-      <c r="E87" s="24" t="n">
+      <c r="E87" s="29" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F87" s="24" t="n">
+      <c r="F87" s="29" t="n">
         <v>1.0638</v>
       </c>
-      <c r="G87" s="22" t="n">
+      <c r="G87" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="23" t="n">
+      <c r="H87" s="28" t="n">
         <v>2.089</v>
       </c>
-      <c r="I87" s="22" t="n">
+      <c r="I87" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="23" t="n">
+      <c r="J87" s="28" t="n">
         <v>1.964</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="22" t="n">
+      <c r="A88" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B88" s="23" t="n">
+      <c r="B88" s="28" t="n">
         <v>1.225</v>
       </c>
-      <c r="C88" s="23" t="n">
+      <c r="C88" s="28" t="n">
         <v>0.483</v>
       </c>
-      <c r="D88" s="23" t="n">
+      <c r="D88" s="28" t="n">
         <v>1.287</v>
       </c>
-      <c r="E88" s="24" t="n">
+      <c r="E88" s="29" t="n">
         <v>0.9515</v>
       </c>
-      <c r="F88" s="24" t="n">
+      <c r="F88" s="29" t="n">
         <v>1.051</v>
       </c>
-      <c r="G88" s="23" t="n">
+      <c r="G88" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="H88" s="23" t="n">
+      <c r="H88" s="28" t="n">
         <v>1.97</v>
       </c>
-      <c r="I88" s="23" t="n">
+      <c r="I88" s="28" t="n">
         <v>0.029</v>
       </c>
-      <c r="J88" s="23" t="n">
+      <c r="J88" s="28" t="n">
         <v>1.874</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="22" t="n">
+      <c r="A89" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B89" s="23" t="n">
+      <c r="B89" s="28" t="n">
         <v>1.134</v>
       </c>
-      <c r="C89" s="23" t="n">
+      <c r="C89" s="28" t="n">
         <v>0.419</v>
       </c>
-      <c r="D89" s="23" t="n">
+      <c r="D89" s="28" t="n">
         <v>1.182</v>
       </c>
-      <c r="E89" s="24" t="n">
+      <c r="E89" s="29" t="n">
         <v>0.9594</v>
       </c>
-      <c r="F89" s="24" t="n">
+      <c r="F89" s="29" t="n">
         <v>1.0423</v>
       </c>
-      <c r="G89" s="23" t="n">
+      <c r="G89" s="28" t="n">
         <v>0.118</v>
       </c>
-      <c r="H89" s="23" t="n">
+      <c r="H89" s="28" t="n">
         <v>1.882</v>
       </c>
-      <c r="I89" s="23" t="n">
+      <c r="I89" s="28" t="n">
         <v>0.113</v>
       </c>
-      <c r="J89" s="23" t="n">
+      <c r="J89" s="28" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="22" t="n">
+      <c r="A90" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="23" t="n">
+      <c r="B90" s="28" t="n">
         <v>1.061</v>
       </c>
-      <c r="C90" s="23" t="n">
+      <c r="C90" s="28" t="n">
         <v>0.373</v>
       </c>
-      <c r="D90" s="23" t="n">
+      <c r="D90" s="28" t="n">
         <v>1.099</v>
       </c>
-      <c r="E90" s="24" t="n">
+      <c r="E90" s="29" t="n">
         <v>0.965</v>
       </c>
-      <c r="F90" s="24" t="n">
+      <c r="F90" s="29" t="n">
         <v>1.0363</v>
       </c>
-      <c r="G90" s="23" t="n">
+      <c r="G90" s="28" t="n">
         <v>0.185</v>
       </c>
-      <c r="H90" s="23" t="n">
+      <c r="H90" s="28" t="n">
         <v>1.815</v>
       </c>
-      <c r="I90" s="23" t="n">
+      <c r="I90" s="28" t="n">
         <v>0.179</v>
       </c>
-      <c r="J90" s="23" t="n">
+      <c r="J90" s="28" t="n">
         <v>1.751</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="22" t="n">
+      <c r="A91" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="23" t="n">
+      <c r="B91" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="23" t="n">
+      <c r="C91" s="28" t="n">
         <v>0.337</v>
       </c>
-      <c r="D91" s="23" t="n">
+      <c r="D91" s="28" t="n">
         <v>1.032</v>
       </c>
-      <c r="E91" s="24" t="n">
+      <c r="E91" s="29" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="F91" s="24" t="n">
+      <c r="F91" s="29" t="n">
         <v>1.0317</v>
       </c>
-      <c r="G91" s="23" t="n">
+      <c r="G91" s="28" t="n">
         <v>0.239</v>
       </c>
-      <c r="H91" s="23" t="n">
+      <c r="H91" s="28" t="n">
         <v>1.761</v>
       </c>
-      <c r="I91" s="23" t="n">
+      <c r="I91" s="28" t="n">
         <v>0.232</v>
       </c>
-      <c r="J91" s="23" t="n">
+      <c r="J91" s="28" t="n">
         <v>1.707</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="22" t="n">
+      <c r="A92" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B92" s="23" t="n">
+      <c r="B92" s="28" t="n">
         <v>0.949</v>
       </c>
-      <c r="C92" s="23" t="n">
+      <c r="C92" s="28" t="n">
         <v>0.308</v>
       </c>
-      <c r="D92" s="23" t="n">
+      <c r="D92" s="28" t="n">
         <v>0.975</v>
       </c>
-      <c r="E92" s="24" t="n">
+      <c r="E92" s="29" t="n">
         <v>0.9727</v>
       </c>
-      <c r="F92" s="24" t="n">
+      <c r="F92" s="29" t="n">
         <v>1.0281</v>
       </c>
-      <c r="G92" s="23" t="n">
+      <c r="G92" s="28" t="n">
         <v>0.284</v>
       </c>
-      <c r="H92" s="23" t="n">
+      <c r="H92" s="28" t="n">
         <v>1.716</v>
       </c>
-      <c r="I92" s="23" t="n">
+      <c r="I92" s="28" t="n">
         <v>0.276</v>
       </c>
-      <c r="J92" s="23" t="n">
+      <c r="J92" s="28" t="n">
         <v>1.669</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="22" t="n">
+      <c r="A93" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B93" s="23" t="n">
+      <c r="B93" s="28" t="n">
         <v>0.905</v>
       </c>
-      <c r="C93" s="23" t="n">
+      <c r="C93" s="28" t="n">
         <v>0.285</v>
       </c>
-      <c r="D93" s="23" t="n">
+      <c r="D93" s="28" t="n">
         <v>0.927</v>
       </c>
-      <c r="E93" s="24" t="n">
+      <c r="E93" s="29" t="n">
         <v>0.9754</v>
       </c>
-      <c r="F93" s="24" t="n">
+      <c r="F93" s="29" t="n">
         <v>1.0252</v>
       </c>
-      <c r="G93" s="23" t="n">
+      <c r="G93" s="28" t="n">
         <v>0.321</v>
       </c>
-      <c r="H93" s="23" t="n">
+      <c r="H93" s="28" t="n">
         <v>1.679</v>
       </c>
-      <c r="I93" s="23" t="n">
+      <c r="I93" s="28" t="n">
         <v>0.313</v>
       </c>
-      <c r="J93" s="23" t="n">
+      <c r="J93" s="28" t="n">
         <v>1.637</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="22" t="n">
+      <c r="A94" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B94" s="23" t="n">
+      <c r="B94" s="28" t="n">
         <v>0.866</v>
       </c>
-      <c r="C94" s="23" t="n">
+      <c r="C94" s="28" t="n">
         <v>0.266</v>
       </c>
-      <c r="D94" s="23" t="n">
+      <c r="D94" s="28" t="n">
         <v>0.886</v>
       </c>
-      <c r="E94" s="24" t="n">
+      <c r="E94" s="29" t="n">
         <v>0.9776</v>
       </c>
-      <c r="F94" s="24" t="n">
+      <c r="F94" s="29" t="n">
         <v>1.0229</v>
       </c>
-      <c r="G94" s="23" t="n">
+      <c r="G94" s="28" t="n">
         <v>0.354</v>
       </c>
-      <c r="H94" s="23" t="n">
+      <c r="H94" s="28" t="n">
         <v>1.646</v>
       </c>
-      <c r="I94" s="23" t="n">
+      <c r="I94" s="28" t="n">
         <v>0.346</v>
       </c>
-      <c r="J94" s="23" t="n">
+      <c r="J94" s="28" t="n">
         <v>1.61</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="22" t="n">
+      <c r="A95" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B95" s="23" t="n">
+      <c r="B95" s="28" t="n">
         <v>0.832</v>
       </c>
-      <c r="C95" s="23" t="n">
+      <c r="C95" s="28" t="n">
         <v>0.249</v>
       </c>
-      <c r="D95" s="23" t="n">
+      <c r="D95" s="28" t="n">
         <v>0.85</v>
       </c>
-      <c r="E95" s="24" t="n">
+      <c r="E95" s="29" t="n">
         <v>0.9794</v>
       </c>
-      <c r="F95" s="24" t="n">
+      <c r="F95" s="29" t="n">
         <v>1.021</v>
       </c>
-      <c r="G95" s="23" t="n">
+      <c r="G95" s="28" t="n">
         <v>0.382</v>
       </c>
-      <c r="H95" s="23" t="n">
+      <c r="H95" s="28" t="n">
         <v>1.618</v>
       </c>
-      <c r="I95" s="23" t="n">
+      <c r="I95" s="28" t="n">
         <v>0.374</v>
       </c>
-      <c r="J95" s="23" t="n">
+      <c r="J95" s="28" t="n">
         <v>1.585</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="22" t="n">
+      <c r="A96" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B96" s="23" t="n">
+      <c r="B96" s="28" t="n">
         <v>0.802</v>
       </c>
-      <c r="C96" s="23" t="n">
+      <c r="C96" s="28" t="n">
         <v>0.235</v>
       </c>
-      <c r="D96" s="23" t="n">
+      <c r="D96" s="28" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E96" s="24" t="n">
+      <c r="E96" s="29" t="n">
         <v>0.981</v>
       </c>
-      <c r="F96" s="24" t="n">
+      <c r="F96" s="29" t="n">
         <v>1.0194</v>
       </c>
-      <c r="G96" s="23" t="n">
+      <c r="G96" s="28" t="n">
         <v>0.406</v>
       </c>
-      <c r="H96" s="23" t="n">
+      <c r="H96" s="28" t="n">
         <v>1.594</v>
       </c>
-      <c r="I96" s="23" t="n">
+      <c r="I96" s="28" t="n">
         <v>0.399</v>
       </c>
-      <c r="J96" s="23" t="n">
+      <c r="J96" s="28" t="n">
         <v>1.563</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="22" t="n">
+      <c r="A97" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B97" s="23" t="n">
+      <c r="B97" s="28" t="n">
         <v>0.775</v>
       </c>
-      <c r="C97" s="23" t="n">
+      <c r="C97" s="28" t="n">
         <v>0.223</v>
       </c>
-      <c r="D97" s="23" t="n">
+      <c r="D97" s="28" t="n">
         <v>0.789</v>
       </c>
-      <c r="E97" s="24" t="n">
+      <c r="E97" s="29" t="n">
         <v>0.9823</v>
       </c>
-      <c r="F97" s="24" t="n">
+      <c r="F97" s="29" t="n">
         <v>1.018</v>
       </c>
-      <c r="G97" s="23" t="n">
+      <c r="G97" s="28" t="n">
         <v>0.428</v>
       </c>
-      <c r="H97" s="23" t="n">
+      <c r="H97" s="28" t="n">
         <v>1.572</v>
       </c>
-      <c r="I97" s="23" t="n">
+      <c r="I97" s="28" t="n">
         <v>0.421</v>
       </c>
-      <c r="J97" s="23" t="n">
+      <c r="J97" s="28" t="n">
         <v>1.544</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="22" t="n">
+      <c r="A98" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B98" s="23" t="n">
+      <c r="B98" s="28" t="n">
         <v>0.75</v>
       </c>
-      <c r="C98" s="23" t="n">
+      <c r="C98" s="28" t="n">
         <v>0.212</v>
       </c>
-      <c r="D98" s="23" t="n">
+      <c r="D98" s="28" t="n">
         <v>0.763</v>
       </c>
-      <c r="E98" s="24" t="n">
+      <c r="E98" s="29" t="n">
         <v>0.9835</v>
       </c>
-      <c r="F98" s="24" t="n">
+      <c r="F98" s="29" t="n">
         <v>1.0168</v>
       </c>
-      <c r="G98" s="23" t="n">
+      <c r="G98" s="28" t="n">
         <v>0.448</v>
       </c>
-      <c r="H98" s="23" t="n">
+      <c r="H98" s="28" t="n">
         <v>1.552</v>
       </c>
-      <c r="I98" s="23" t="n">
+      <c r="I98" s="28" t="n">
         <v>0.44</v>
       </c>
-      <c r="J98" s="23" t="n">
+      <c r="J98" s="28" t="n">
         <v>1.526</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="22" t="n">
+      <c r="A99" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="23" t="n">
+      <c r="B99" s="28" t="n">
         <v>0.728</v>
       </c>
-      <c r="C99" s="23" t="n">
+      <c r="C99" s="28" t="n">
         <v>0.203</v>
       </c>
-      <c r="D99" s="23" t="n">
+      <c r="D99" s="28" t="n">
         <v>0.739</v>
       </c>
-      <c r="E99" s="24" t="n">
+      <c r="E99" s="29" t="n">
         <v>0.9845</v>
       </c>
-      <c r="F99" s="24" t="n">
+      <c r="F99" s="29" t="n">
         <v>1.0157</v>
       </c>
-      <c r="G99" s="23" t="n">
+      <c r="G99" s="28" t="n">
         <v>0.466</v>
       </c>
-      <c r="H99" s="23" t="n">
+      <c r="H99" s="28" t="n">
         <v>1.534</v>
       </c>
-      <c r="I99" s="23" t="n">
+      <c r="I99" s="28" t="n">
         <v>0.458</v>
       </c>
-      <c r="J99" s="23" t="n">
+      <c r="J99" s="28" t="n">
         <v>1.511</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="22" t="n">
+      <c r="A100" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B100" s="23" t="n">
+      <c r="B100" s="28" t="n">
         <v>0.707</v>
       </c>
-      <c r="C100" s="23" t="n">
+      <c r="C100" s="28" t="n">
         <v>0.194</v>
       </c>
-      <c r="D100" s="23" t="n">
+      <c r="D100" s="28" t="n">
         <v>0.718</v>
       </c>
-      <c r="E100" s="24" t="n">
+      <c r="E100" s="29" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="F100" s="24" t="n">
+      <c r="F100" s="29" t="n">
         <v>1.0148</v>
       </c>
-      <c r="G100" s="23" t="n">
+      <c r="G100" s="28" t="n">
         <v>0.482</v>
       </c>
-      <c r="H100" s="23" t="n">
+      <c r="H100" s="28" t="n">
         <v>1.518</v>
       </c>
-      <c r="I100" s="23" t="n">
+      <c r="I100" s="28" t="n">
         <v>0.475</v>
       </c>
-      <c r="J100" s="23" t="n">
+      <c r="J100" s="28" t="n">
         <v>1.496</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="22" t="n">
+      <c r="A101" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B101" s="23" t="n">
+      <c r="B101" s="28" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C101" s="23" t="n">
+      <c r="C101" s="28" t="n">
         <v>0.187</v>
       </c>
-      <c r="D101" s="23" t="n">
+      <c r="D101" s="28" t="n">
         <v>0.698</v>
       </c>
-      <c r="E101" s="24" t="n">
+      <c r="E101" s="29" t="n">
         <v>0.9862</v>
       </c>
-      <c r="F101" s="24" t="n">
+      <c r="F101" s="29" t="n">
         <v>1.014</v>
       </c>
-      <c r="G101" s="23" t="n">
+      <c r="G101" s="28" t="n">
         <v>0.497</v>
       </c>
-      <c r="H101" s="23" t="n">
+      <c r="H101" s="28" t="n">
         <v>1.503</v>
       </c>
-      <c r="I101" s="23" t="n">
+      <c r="I101" s="28" t="n">
         <v>0.49</v>
       </c>
-      <c r="J101" s="23" t="n">
+      <c r="J101" s="28" t="n">
         <v>1.483</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="22" t="n">
+      <c r="A102" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B102" s="23" t="n">
+      <c r="B102" s="28" t="n">
         <v>0.671</v>
       </c>
-      <c r="C102" s="23" t="n">
+      <c r="C102" s="28" t="n">
         <v>0.18</v>
       </c>
-      <c r="D102" s="23" t="n">
+      <c r="D102" s="28" t="n">
         <v>0.68</v>
       </c>
-      <c r="E102" s="24" t="n">
+      <c r="E102" s="29" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F102" s="24" t="n">
+      <c r="F102" s="29" t="n">
         <v>1.0133</v>
       </c>
-      <c r="G102" s="23" t="n">
+      <c r="G102" s="28" t="n">
         <v>0.51</v>
       </c>
-      <c r="H102" s="23" t="n">
+      <c r="H102" s="28" t="n">
         <v>1.49</v>
       </c>
-      <c r="I102" s="23" t="n">
+      <c r="I102" s="28" t="n">
         <v>0.504</v>
       </c>
-      <c r="J102" s="23" t="n">
+      <c r="J102" s="28" t="n">
         <v>1.47</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="22" t="n">
+      <c r="A103" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="B103" s="23" t="n">
+      <c r="B103" s="28" t="n">
         <v>0.655</v>
       </c>
-      <c r="C103" s="23" t="n">
+      <c r="C103" s="28" t="n">
         <v>0.173</v>
       </c>
-      <c r="D103" s="23" t="n">
+      <c r="D103" s="28" t="n">
         <v>0.663</v>
       </c>
-      <c r="E103" s="24" t="n">
+      <c r="E103" s="29" t="n">
         <v>0.9876</v>
       </c>
-      <c r="F103" s="24" t="n">
+      <c r="F103" s="29" t="n">
         <v>1.0126</v>
       </c>
-      <c r="G103" s="23" t="n">
+      <c r="G103" s="28" t="n">
         <v>0.523</v>
       </c>
-      <c r="H103" s="23" t="n">
+      <c r="H103" s="28" t="n">
         <v>1.477</v>
       </c>
-      <c r="I103" s="23" t="n">
+      <c r="I103" s="28" t="n">
         <v>0.516</v>
       </c>
-      <c r="J103" s="23" t="n">
+      <c r="J103" s="28" t="n">
         <v>1.459</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="22" t="n">
+      <c r="A104" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="B104" s="23" t="n">
+      <c r="B104" s="28" t="n">
         <v>0.64</v>
       </c>
-      <c r="C104" s="23" t="n">
+      <c r="C104" s="28" t="n">
         <v>0.167</v>
       </c>
-      <c r="D104" s="23" t="n">
+      <c r="D104" s="28" t="n">
         <v>0.647</v>
       </c>
-      <c r="E104" s="24" t="n">
+      <c r="E104" s="29" t="n">
         <v>0.9882</v>
       </c>
-      <c r="F104" s="24" t="n">
+      <c r="F104" s="29" t="n">
         <v>1.0119</v>
       </c>
-      <c r="G104" s="23" t="n">
+      <c r="G104" s="28" t="n">
         <v>0.534</v>
       </c>
-      <c r="H104" s="23" t="n">
+      <c r="H104" s="28" t="n">
         <v>1.466</v>
       </c>
-      <c r="I104" s="23" t="n">
+      <c r="I104" s="28" t="n">
         <v>0.528</v>
       </c>
-      <c r="J104" s="23" t="n">
+      <c r="J104" s="28" t="n">
         <v>1.448</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="22" t="n">
+      <c r="A105" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="B105" s="23" t="n">
+      <c r="B105" s="28" t="n">
         <v>0.626</v>
       </c>
-      <c r="C105" s="23" t="n">
+      <c r="C105" s="28" t="n">
         <v>0.162</v>
       </c>
-      <c r="D105" s="23" t="n">
+      <c r="D105" s="28" t="n">
         <v>0.633</v>
       </c>
-      <c r="E105" s="24" t="n">
+      <c r="E105" s="29" t="n">
         <v>0.9887</v>
       </c>
-      <c r="F105" s="24" t="n">
+      <c r="F105" s="29" t="n">
         <v>1.0114</v>
       </c>
-      <c r="G105" s="23" t="n">
+      <c r="G105" s="28" t="n">
         <v>0.545</v>
       </c>
-      <c r="H105" s="23" t="n">
+      <c r="H105" s="28" t="n">
         <v>1.455</v>
       </c>
-      <c r="I105" s="23" t="n">
+      <c r="I105" s="28" t="n">
         <v>0.539</v>
       </c>
-      <c r="J105" s="23" t="n">
+      <c r="J105" s="28" t="n">
         <v>1.438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="22" t="n">
+      <c r="A106" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="B106" s="23" t="n">
+      <c r="B106" s="28" t="n">
         <v>0.612</v>
       </c>
-      <c r="C106" s="23" t="n">
+      <c r="C106" s="28" t="n">
         <v>0.157</v>
       </c>
-      <c r="D106" s="23" t="n">
+      <c r="D106" s="28" t="n">
         <v>0.619</v>
       </c>
-      <c r="E106" s="24" t="n">
+      <c r="E106" s="29" t="n">
         <v>0.9892</v>
       </c>
-      <c r="F106" s="24" t="n">
+      <c r="F106" s="29" t="n">
         <v>1.0109</v>
       </c>
-      <c r="G106" s="23" t="n">
+      <c r="G106" s="28" t="n">
         <v>0.555</v>
       </c>
-      <c r="H106" s="23" t="n">
+      <c r="H106" s="28" t="n">
         <v>1.445</v>
       </c>
-      <c r="I106" s="23" t="n">
+      <c r="I106" s="28" t="n">
         <v>0.549</v>
       </c>
-      <c r="J106" s="23" t="n">
+      <c r="J106" s="28" t="n">
         <v>1.429</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="22" t="n">
+      <c r="A107" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="B107" s="23" t="n">
+      <c r="B107" s="28" t="n">
         <v>0.6</v>
       </c>
-      <c r="C107" s="23" t="n">
+      <c r="C107" s="28" t="n">
         <v>0.153</v>
       </c>
-      <c r="D107" s="23" t="n">
+      <c r="D107" s="28" t="n">
         <v>0.606</v>
       </c>
-      <c r="E107" s="24" t="n">
+      <c r="E107" s="29" t="n">
         <v>0.9896</v>
       </c>
-      <c r="F107" s="24" t="n">
+      <c r="F107" s="29" t="n">
         <v>1.0105</v>
       </c>
-      <c r="G107" s="23" t="n">
+      <c r="G107" s="28" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H107" s="23" t="n">
+      <c r="H107" s="28" t="n">
         <v>1.435</v>
       </c>
-      <c r="I107" s="23" t="n">
+      <c r="I107" s="28" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J107" s="23" t="n">
+      <c r="J107" s="28" t="n">
         <v>1.42</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="21" t="inlineStr">
+      <c r="A109" s="26" t="inlineStr">
         <is>
           <t>Control Chart Constants - Chart for Ranges &amp; X Charts (Six Sigma Demystified, 2nd ed.)</t>
         </is>
@@ -5728,7 +6612,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="21" t="inlineStr">
+      <c r="A111" s="26" t="inlineStr">
         <is>
           <t>USED for E2 (Table 18 and Table A do not give it). Reference otherwise.</t>
         </is>
@@ -5782,703 +6666,703 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="22" t="n">
+      <c r="A113" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="23" t="n">
+      <c r="B113" s="28" t="n">
         <v>1.128</v>
       </c>
-      <c r="C113" s="24" t="n">
+      <c r="C113" s="29" t="n">
         <v>0.8865</v>
       </c>
-      <c r="D113" s="23" t="n">
+      <c r="D113" s="28" t="n">
         <v>0.853</v>
       </c>
-      <c r="E113" s="22" t="n">
+      <c r="E113" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="23" t="n">
+      <c r="F113" s="28" t="n">
         <v>3.686</v>
       </c>
-      <c r="G113" s="22" t="n">
+      <c r="G113" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="23" t="n">
+      <c r="H113" s="28" t="n">
         <v>3.267</v>
       </c>
-      <c r="I113" s="25" t="n">
+      <c r="I113" s="30" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="22" t="n">
+      <c r="A114" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="23" t="n">
+      <c r="B114" s="28" t="n">
         <v>1.693</v>
       </c>
-      <c r="C114" s="24" t="n">
+      <c r="C114" s="29" t="n">
         <v>0.5907</v>
       </c>
-      <c r="D114" s="23" t="n">
+      <c r="D114" s="28" t="n">
         <v>0.888</v>
       </c>
-      <c r="E114" s="22" t="n">
+      <c r="E114" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="23" t="n">
+      <c r="F114" s="28" t="n">
         <v>4.358</v>
       </c>
-      <c r="G114" s="22" t="n">
+      <c r="G114" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="25" t="n">
+      <c r="H114" s="30" t="n">
         <v>2.574</v>
       </c>
-      <c r="I114" s="23" t="n">
+      <c r="I114" s="28" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="22" t="n">
+      <c r="A115" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B115" s="23" t="n">
+      <c r="B115" s="28" t="n">
         <v>2.059</v>
       </c>
-      <c r="C115" s="24" t="n">
+      <c r="C115" s="29" t="n">
         <v>0.4857</v>
       </c>
-      <c r="D115" s="23" t="n">
+      <c r="D115" s="28" t="n">
         <v>0.88</v>
       </c>
-      <c r="E115" s="22" t="n">
+      <c r="E115" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="23" t="n">
+      <c r="F115" s="28" t="n">
         <v>4.698</v>
       </c>
-      <c r="G115" s="22" t="n">
+      <c r="G115" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="23" t="n">
+      <c r="H115" s="28" t="n">
         <v>2.282</v>
       </c>
-      <c r="I115" s="23" t="n">
+      <c r="I115" s="28" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="22" t="n">
+      <c r="A116" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="23" t="n">
+      <c r="B116" s="28" t="n">
         <v>2.326</v>
       </c>
-      <c r="C116" s="24" t="n">
+      <c r="C116" s="29" t="n">
         <v>0.4299</v>
       </c>
-      <c r="D116" s="23" t="n">
+      <c r="D116" s="28" t="n">
         <v>0.864</v>
       </c>
-      <c r="E116" s="22" t="n">
+      <c r="E116" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="23" t="n">
+      <c r="F116" s="28" t="n">
         <v>4.918</v>
       </c>
-      <c r="G116" s="22" t="n">
+      <c r="G116" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="25" t="n">
+      <c r="H116" s="30" t="n">
         <v>2.114</v>
       </c>
-      <c r="I116" s="23" t="n">
+      <c r="I116" s="28" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="22" t="n">
+      <c r="A117" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B117" s="23" t="n">
+      <c r="B117" s="28" t="n">
         <v>2.534</v>
       </c>
-      <c r="C117" s="24" t="n">
+      <c r="C117" s="29" t="n">
         <v>0.3946</v>
       </c>
-      <c r="D117" s="23" t="n">
+      <c r="D117" s="28" t="n">
         <v>0.848</v>
       </c>
-      <c r="E117" s="22" t="n">
+      <c r="E117" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="23" t="n">
+      <c r="F117" s="28" t="n">
         <v>5.078</v>
       </c>
-      <c r="G117" s="22" t="n">
+      <c r="G117" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="23" t="n">
+      <c r="H117" s="28" t="n">
         <v>2.004</v>
       </c>
-      <c r="I117" s="23" t="n">
+      <c r="I117" s="28" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="22" t="n">
+      <c r="A118" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="23" t="n">
+      <c r="B118" s="28" t="n">
         <v>2.704</v>
       </c>
-      <c r="C118" s="24" t="n">
+      <c r="C118" s="29" t="n">
         <v>0.3698</v>
       </c>
-      <c r="D118" s="23" t="n">
+      <c r="D118" s="28" t="n">
         <v>0.833</v>
       </c>
-      <c r="E118" s="25" t="n">
+      <c r="E118" s="30" t="n">
         <v>0.204</v>
       </c>
-      <c r="F118" s="25" t="n">
+      <c r="F118" s="30" t="n">
         <v>5.204</v>
       </c>
-      <c r="G118" s="23" t="n">
+      <c r="G118" s="28" t="n">
         <v>0.076</v>
       </c>
-      <c r="H118" s="23" t="n">
+      <c r="H118" s="28" t="n">
         <v>1.924</v>
       </c>
-      <c r="I118" s="23" t="n">
+      <c r="I118" s="28" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="22" t="n">
+      <c r="A119" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B119" s="23" t="n">
+      <c r="B119" s="28" t="n">
         <v>2.847</v>
       </c>
-      <c r="C119" s="24" t="n">
+      <c r="C119" s="29" t="n">
         <v>0.3512</v>
       </c>
-      <c r="D119" s="23" t="n">
+      <c r="D119" s="28" t="n">
         <v>0.82</v>
       </c>
-      <c r="E119" s="25" t="n">
+      <c r="E119" s="30" t="n">
         <v>0.388</v>
       </c>
-      <c r="F119" s="25" t="n">
+      <c r="F119" s="30" t="n">
         <v>5.306</v>
       </c>
-      <c r="G119" s="23" t="n">
+      <c r="G119" s="28" t="n">
         <v>0.136</v>
       </c>
-      <c r="H119" s="23" t="n">
+      <c r="H119" s="28" t="n">
         <v>1.864</v>
       </c>
-      <c r="I119" s="23" t="n">
+      <c r="I119" s="28" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="22" t="n">
+      <c r="A120" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="23" t="n">
+      <c r="B120" s="28" t="n">
         <v>2.97</v>
       </c>
-      <c r="C120" s="24" t="n">
+      <c r="C120" s="29" t="n">
         <v>0.3367</v>
       </c>
-      <c r="D120" s="23" t="n">
+      <c r="D120" s="28" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E120" s="25" t="n">
+      <c r="E120" s="30" t="n">
         <v>0.547</v>
       </c>
-      <c r="F120" s="25" t="n">
+      <c r="F120" s="30" t="n">
         <v>5.393</v>
       </c>
-      <c r="G120" s="23" t="n">
+      <c r="G120" s="28" t="n">
         <v>0.184</v>
       </c>
-      <c r="H120" s="23" t="n">
+      <c r="H120" s="28" t="n">
         <v>1.816</v>
       </c>
-      <c r="I120" s="23" t="n">
+      <c r="I120" s="28" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="22" t="n">
+      <c r="A121" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B121" s="23" t="n">
+      <c r="B121" s="28" t="n">
         <v>3.078</v>
       </c>
-      <c r="C121" s="24" t="n">
+      <c r="C121" s="29" t="n">
         <v>0.3249</v>
       </c>
-      <c r="D121" s="23" t="n">
+      <c r="D121" s="28" t="n">
         <v>0.797</v>
       </c>
-      <c r="E121" s="23" t="n">
+      <c r="E121" s="28" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F121" s="23" t="n">
+      <c r="F121" s="28" t="n">
         <v>5.469</v>
       </c>
-      <c r="G121" s="23" t="n">
+      <c r="G121" s="28" t="n">
         <v>0.223</v>
       </c>
-      <c r="H121" s="23" t="n">
+      <c r="H121" s="28" t="n">
         <v>1.777</v>
       </c>
-      <c r="I121" s="23" t="n">
+      <c r="I121" s="28" t="n">
         <v>0.975</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="n">
+      <c r="A122" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="B122" s="23" t="n">
+      <c r="B122" s="28" t="n">
         <v>3.173</v>
       </c>
-      <c r="C122" s="24" t="n">
+      <c r="C122" s="29" t="n">
         <v>0.3152</v>
       </c>
-      <c r="D122" s="23" t="n">
+      <c r="D122" s="28" t="n">
         <v>0.787</v>
       </c>
-      <c r="E122" s="25" t="n">
+      <c r="E122" s="30" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F122" s="25" t="n">
+      <c r="F122" s="30" t="n">
         <v>5.535</v>
       </c>
-      <c r="G122" s="23" t="n">
+      <c r="G122" s="28" t="n">
         <v>0.256</v>
       </c>
-      <c r="H122" s="23" t="n">
+      <c r="H122" s="28" t="n">
         <v>1.744</v>
       </c>
-      <c r="I122" s="23" t="n">
+      <c r="I122" s="28" t="n">
         <v>0.945</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="22" t="n">
+      <c r="A123" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="23" t="n">
+      <c r="B123" s="28" t="n">
         <v>3.258</v>
       </c>
-      <c r="C123" s="24" t="n">
+      <c r="C123" s="29" t="n">
         <v>0.3069</v>
       </c>
-      <c r="D123" s="25" t="n">
+      <c r="D123" s="30" t="n">
         <v>0.778</v>
       </c>
-      <c r="E123" s="25" t="n">
+      <c r="E123" s="30" t="n">
         <v>0.922</v>
       </c>
-      <c r="F123" s="25" t="n">
+      <c r="F123" s="30" t="n">
         <v>5.594</v>
       </c>
-      <c r="G123" s="25" t="n">
+      <c r="G123" s="30" t="n">
         <v>0.283</v>
       </c>
-      <c r="H123" s="25" t="n">
+      <c r="H123" s="30" t="n">
         <v>1.717</v>
       </c>
-      <c r="I123" s="23" t="n">
+      <c r="I123" s="28" t="n">
         <v>0.921</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="22" t="n">
+      <c r="A124" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="B124" s="23" t="n">
+      <c r="B124" s="28" t="n">
         <v>3.336</v>
       </c>
-      <c r="C124" s="24" t="n">
+      <c r="C124" s="29" t="n">
         <v>0.2998</v>
       </c>
-      <c r="D124" s="23" t="n">
+      <c r="D124" s="28" t="n">
         <v>0.77</v>
       </c>
-      <c r="E124" s="25" t="n">
+      <c r="E124" s="30" t="n">
         <v>1.025</v>
       </c>
-      <c r="F124" s="25" t="n">
+      <c r="F124" s="30" t="n">
         <v>5.647</v>
       </c>
-      <c r="G124" s="25" t="n">
+      <c r="G124" s="30" t="n">
         <v>0.307</v>
       </c>
-      <c r="H124" s="25" t="n">
+      <c r="H124" s="30" t="n">
         <v>1.693</v>
       </c>
-      <c r="I124" s="23" t="n">
+      <c r="I124" s="28" t="n">
         <v>0.899</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="22" t="n">
+      <c r="A125" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="B125" s="23" t="n">
+      <c r="B125" s="28" t="n">
         <v>3.407</v>
       </c>
-      <c r="C125" s="24" t="n">
+      <c r="C125" s="29" t="n">
         <v>0.2935</v>
       </c>
-      <c r="D125" s="23" t="n">
+      <c r="D125" s="28" t="n">
         <v>0.763</v>
       </c>
-      <c r="E125" s="25" t="n">
+      <c r="E125" s="30" t="n">
         <v>1.118</v>
       </c>
-      <c r="F125" s="25" t="n">
+      <c r="F125" s="30" t="n">
         <v>5.696</v>
       </c>
-      <c r="G125" s="25" t="n">
+      <c r="G125" s="30" t="n">
         <v>0.328</v>
       </c>
-      <c r="H125" s="25" t="n">
+      <c r="H125" s="30" t="n">
         <v>1.672</v>
       </c>
-      <c r="I125" s="23" t="n">
+      <c r="I125" s="28" t="n">
         <v>0.881</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="22" t="n">
+      <c r="A126" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B126" s="23" t="n">
+      <c r="B126" s="28" t="n">
         <v>3.472</v>
       </c>
-      <c r="C126" s="24" t="n">
+      <c r="C126" s="29" t="n">
         <v>0.288</v>
       </c>
-      <c r="D126" s="23" t="n">
+      <c r="D126" s="28" t="n">
         <v>0.756</v>
       </c>
-      <c r="E126" s="25" t="n">
+      <c r="E126" s="30" t="n">
         <v>1.203</v>
       </c>
-      <c r="F126" s="25" t="n">
+      <c r="F126" s="30" t="n">
         <v>5.741</v>
       </c>
-      <c r="G126" s="25" t="n">
+      <c r="G126" s="30" t="n">
         <v>0.347</v>
       </c>
-      <c r="H126" s="25" t="n">
+      <c r="H126" s="30" t="n">
         <v>1.653</v>
       </c>
-      <c r="I126" s="23" t="n">
+      <c r="I126" s="28" t="n">
         <v>0.864</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="22" t="n">
+      <c r="A127" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B127" s="23" t="n">
+      <c r="B127" s="28" t="n">
         <v>3.532</v>
       </c>
-      <c r="C127" s="24" t="n">
+      <c r="C127" s="29" t="n">
         <v>0.2831</v>
       </c>
-      <c r="D127" s="23" t="n">
+      <c r="D127" s="28" t="n">
         <v>0.75</v>
       </c>
-      <c r="E127" s="25" t="n">
+      <c r="E127" s="30" t="n">
         <v>1.282</v>
       </c>
-      <c r="F127" s="25" t="n">
+      <c r="F127" s="30" t="n">
         <v>5.782</v>
       </c>
-      <c r="G127" s="25" t="n">
+      <c r="G127" s="30" t="n">
         <v>0.363</v>
       </c>
-      <c r="H127" s="25" t="n">
+      <c r="H127" s="30" t="n">
         <v>1.637</v>
       </c>
-      <c r="I127" s="23" t="n">
+      <c r="I127" s="28" t="n">
         <v>0.849</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="22" t="n">
+      <c r="A128" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="B128" s="23" t="n">
+      <c r="B128" s="28" t="n">
         <v>3.588</v>
       </c>
-      <c r="C128" s="24" t="n">
+      <c r="C128" s="29" t="n">
         <v>0.2787</v>
       </c>
-      <c r="D128" s="23" t="n">
+      <c r="D128" s="28" t="n">
         <v>0.744</v>
       </c>
-      <c r="E128" s="25" t="n">
+      <c r="E128" s="30" t="n">
         <v>1.356</v>
       </c>
-      <c r="F128" s="25" t="n">
+      <c r="F128" s="30" t="n">
         <v>5.82</v>
       </c>
-      <c r="G128" s="25" t="n">
+      <c r="G128" s="30" t="n">
         <v>0.378</v>
       </c>
-      <c r="H128" s="25" t="n">
+      <c r="H128" s="30" t="n">
         <v>1.622</v>
       </c>
-      <c r="I128" s="23" t="n">
+      <c r="I128" s="28" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="22" t="n">
+      <c r="A129" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="B129" s="23" t="n">
+      <c r="B129" s="28" t="n">
         <v>3.64</v>
       </c>
-      <c r="C129" s="24" t="n">
+      <c r="C129" s="29" t="n">
         <v>0.2747</v>
       </c>
-      <c r="D129" s="23" t="n">
+      <c r="D129" s="28" t="n">
         <v>0.739</v>
       </c>
-      <c r="E129" s="25" t="n">
+      <c r="E129" s="30" t="n">
         <v>1.424</v>
       </c>
-      <c r="F129" s="25" t="n">
+      <c r="F129" s="30" t="n">
         <v>5.856</v>
       </c>
-      <c r="G129" s="25" t="n">
+      <c r="G129" s="30" t="n">
         <v>0.391</v>
       </c>
-      <c r="H129" s="23" t="n">
+      <c r="H129" s="28" t="n">
         <v>1.608</v>
       </c>
-      <c r="I129" s="23" t="n">
+      <c r="I129" s="28" t="n">
         <v>0.824</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="22" t="n">
+      <c r="A130" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="B130" s="23" t="n">
+      <c r="B130" s="28" t="n">
         <v>3.689</v>
       </c>
-      <c r="C130" s="24" t="n">
+      <c r="C130" s="29" t="n">
         <v>0.2711</v>
       </c>
-      <c r="D130" s="23" t="n">
+      <c r="D130" s="28" t="n">
         <v>0.734</v>
       </c>
-      <c r="E130" s="25" t="n">
+      <c r="E130" s="30" t="n">
         <v>1.487</v>
       </c>
-      <c r="F130" s="25" t="n">
+      <c r="F130" s="30" t="n">
         <v>5.891</v>
       </c>
-      <c r="G130" s="25" t="n">
+      <c r="G130" s="30" t="n">
         <v>0.403</v>
       </c>
-      <c r="H130" s="25" t="n">
+      <c r="H130" s="30" t="n">
         <v>1.597</v>
       </c>
-      <c r="I130" s="23" t="n">
+      <c r="I130" s="28" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="22" t="n">
+      <c r="A131" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="23" t="n">
+      <c r="B131" s="28" t="n">
         <v>3.735</v>
       </c>
-      <c r="C131" s="24" t="n">
+      <c r="C131" s="29" t="n">
         <v>0.2677</v>
       </c>
-      <c r="D131" s="23" t="n">
+      <c r="D131" s="28" t="n">
         <v>0.729</v>
       </c>
-      <c r="E131" s="25" t="n">
+      <c r="E131" s="30" t="n">
         <v>1.549</v>
       </c>
-      <c r="F131" s="25" t="n">
+      <c r="F131" s="30" t="n">
         <v>5.921</v>
       </c>
-      <c r="G131" s="25" t="n">
+      <c r="G131" s="30" t="n">
         <v>0.415</v>
       </c>
-      <c r="H131" s="25" t="n">
+      <c r="H131" s="30" t="n">
         <v>1.585</v>
       </c>
-      <c r="I131" s="23" t="n">
+      <c r="I131" s="28" t="n">
         <v>0.803</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="22" t="n">
+      <c r="A132" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="B132" s="23" t="n">
+      <c r="B132" s="28" t="n">
         <v>3.778</v>
       </c>
-      <c r="C132" s="24" t="n">
+      <c r="C132" s="29" t="n">
         <v>0.2647</v>
       </c>
-      <c r="D132" s="25" t="n">
+      <c r="D132" s="30" t="n">
         <v>0.724</v>
       </c>
-      <c r="E132" s="25" t="n">
+      <c r="E132" s="30" t="n">
         <v>1.605</v>
       </c>
-      <c r="F132" s="25" t="n">
+      <c r="F132" s="30" t="n">
         <v>5.951</v>
       </c>
-      <c r="G132" s="23" t="n">
+      <c r="G132" s="28" t="n">
         <v>0.425</v>
       </c>
-      <c r="H132" s="23" t="n">
+      <c r="H132" s="28" t="n">
         <v>1.575</v>
       </c>
-      <c r="I132" s="23" t="n">
+      <c r="I132" s="28" t="n">
         <v>0.794</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="22" t="n">
+      <c r="A133" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="B133" s="23" t="n">
+      <c r="B133" s="28" t="n">
         <v>3.819</v>
       </c>
-      <c r="C133" s="24" t="n">
+      <c r="C133" s="29" t="n">
         <v>0.2618</v>
       </c>
-      <c r="D133" s="23" t="n">
+      <c r="D133" s="28" t="n">
         <v>0.72</v>
       </c>
-      <c r="E133" s="23" t="n">
+      <c r="E133" s="28" t="n">
         <v>1.659</v>
       </c>
-      <c r="F133" s="23" t="n">
+      <c r="F133" s="28" t="n">
         <v>5.979</v>
       </c>
-      <c r="G133" s="23" t="n">
+      <c r="G133" s="28" t="n">
         <v>0.434</v>
       </c>
-      <c r="H133" s="23" t="n">
+      <c r="H133" s="28" t="n">
         <v>1.566</v>
       </c>
-      <c r="I133" s="23" t="n">
+      <c r="I133" s="28" t="n">
         <v>0.786</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="22" t="n">
+      <c r="A134" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="B134" s="23" t="n">
+      <c r="B134" s="28" t="n">
         <v>3.858</v>
       </c>
-      <c r="C134" s="24" t="n">
+      <c r="C134" s="29" t="n">
         <v>0.2592</v>
       </c>
-      <c r="D134" s="23" t="n">
+      <c r="D134" s="28" t="n">
         <v>0.716</v>
       </c>
-      <c r="E134" s="23" t="n">
+      <c r="E134" s="28" t="n">
         <v>1.71</v>
       </c>
-      <c r="F134" s="23" t="n">
+      <c r="F134" s="28" t="n">
         <v>6.006</v>
       </c>
-      <c r="G134" s="23" t="n">
+      <c r="G134" s="28" t="n">
         <v>0.443</v>
       </c>
-      <c r="H134" s="23" t="n">
+      <c r="H134" s="28" t="n">
         <v>1.557</v>
       </c>
-      <c r="I134" s="23" t="n">
+      <c r="I134" s="28" t="n">
         <v>0.778</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="22" t="n">
+      <c r="A135" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="B135" s="23" t="n">
+      <c r="B135" s="28" t="n">
         <v>3.895</v>
       </c>
-      <c r="C135" s="24" t="n">
+      <c r="C135" s="29" t="n">
         <v>0.2567</v>
       </c>
-      <c r="D135" s="23" t="n">
+      <c r="D135" s="28" t="n">
         <v>0.712</v>
       </c>
-      <c r="E135" s="23" t="n">
+      <c r="E135" s="28" t="n">
         <v>1.759</v>
       </c>
-      <c r="F135" s="23" t="n">
+      <c r="F135" s="28" t="n">
         <v>6.031</v>
       </c>
-      <c r="G135" s="25" t="n">
+      <c r="G135" s="30" t="n">
         <v>0.451</v>
       </c>
-      <c r="H135" s="23" t="n">
+      <c r="H135" s="28" t="n">
         <v>1.548</v>
       </c>
-      <c r="I135" s="23" t="n">
+      <c r="I135" s="28" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="22" t="n">
+      <c r="A136" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="B136" s="23" t="n">
+      <c r="B136" s="28" t="n">
         <v>3.931</v>
       </c>
-      <c r="C136" s="24" t="n">
+      <c r="C136" s="29" t="n">
         <v>0.2544</v>
       </c>
-      <c r="D136" s="23" t="n">
+      <c r="D136" s="28" t="n">
         <v>0.708</v>
       </c>
-      <c r="E136" s="25" t="n">
+      <c r="E136" s="30" t="n">
         <v>1.806</v>
       </c>
-      <c r="F136" s="25" t="n">
+      <c r="F136" s="30" t="n">
         <v>6.056</v>
       </c>
-      <c r="G136" s="23" t="n">
+      <c r="G136" s="28" t="n">
         <v>0.459</v>
       </c>
-      <c r="H136" s="23" t="n">
+      <c r="H136" s="28" t="n">
         <v>1.541</v>
       </c>
-      <c r="I136" s="23" t="n">
+      <c r="I136" s="28" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="21" t="inlineStr">
+      <c r="A138" s="26" t="inlineStr">
         <is>
           <t>Table 10-2: Continuous Data Control Chart constants (A2, A3, B3, B4, D3, D4, E2)</t>
         </is>
@@ -6492,7 +7376,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="21" t="inlineStr">
+      <c r="A140" s="26" t="inlineStr">
         <is>
           <t>Reference only.</t>
         </is>
@@ -6541,236 +7425,236 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="22" t="n">
+      <c r="A142" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="B142" s="23" t="n">
+      <c r="B142" s="28" t="n">
         <v>1.88</v>
       </c>
-      <c r="C142" s="23" t="n">
+      <c r="C142" s="28" t="n">
         <v>2.659</v>
       </c>
-      <c r="D142" s="22" t="n">
+      <c r="D142" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="23" t="n">
+      <c r="E142" s="28" t="n">
         <v>3.267</v>
       </c>
-      <c r="F142" s="22" t="n">
+      <c r="F142" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="23" t="n">
+      <c r="G142" s="28" t="n">
         <v>3.267</v>
       </c>
-      <c r="H142" s="25" t="n">
+      <c r="H142" s="30" t="n">
         <v>2.659</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="22" t="n">
+      <c r="A143" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="23" t="n">
+      <c r="B143" s="28" t="n">
         <v>1.023</v>
       </c>
-      <c r="C143" s="23" t="n">
+      <c r="C143" s="28" t="n">
         <v>1.954</v>
       </c>
-      <c r="D143" s="22" t="n">
+      <c r="D143" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="23" t="n">
+      <c r="E143" s="28" t="n">
         <v>2.568</v>
       </c>
-      <c r="F143" s="22" t="n">
+      <c r="F143" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="25" t="n">
+      <c r="G143" s="30" t="n">
         <v>2.574</v>
       </c>
-      <c r="H143" s="23" t="n">
+      <c r="H143" s="28" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="22" t="n">
+      <c r="A144" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="B144" s="23" t="n">
+      <c r="B144" s="28" t="n">
         <v>0.729</v>
       </c>
-      <c r="C144" s="23" t="n">
+      <c r="C144" s="28" t="n">
         <v>1.628</v>
       </c>
-      <c r="D144" s="22" t="n">
+      <c r="D144" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="23" t="n">
+      <c r="E144" s="28" t="n">
         <v>2.266</v>
       </c>
-      <c r="F144" s="22" t="n">
+      <c r="F144" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="23" t="n">
+      <c r="G144" s="28" t="n">
         <v>2.282</v>
       </c>
-      <c r="H144" s="23" t="n">
+      <c r="H144" s="28" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="22" t="n">
+      <c r="A145" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="B145" s="23" t="n">
+      <c r="B145" s="28" t="n">
         <v>0.577</v>
       </c>
-      <c r="C145" s="23" t="n">
+      <c r="C145" s="28" t="n">
         <v>1.427</v>
       </c>
-      <c r="D145" s="22" t="n">
+      <c r="D145" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="E145" s="23" t="n">
+      <c r="E145" s="28" t="n">
         <v>2.089</v>
       </c>
-      <c r="F145" s="22" t="n">
+      <c r="F145" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="25" t="n">
+      <c r="G145" s="30" t="n">
         <v>2.114</v>
       </c>
-      <c r="H145" s="23" t="n">
+      <c r="H145" s="28" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="22" t="n">
+      <c r="A146" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="B146" s="23" t="n">
+      <c r="B146" s="28" t="n">
         <v>0.483</v>
       </c>
-      <c r="C146" s="23" t="n">
+      <c r="C146" s="28" t="n">
         <v>1.287</v>
       </c>
-      <c r="D146" s="23" t="n">
+      <c r="D146" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="E146" s="23" t="n">
+      <c r="E146" s="28" t="n">
         <v>1.97</v>
       </c>
-      <c r="F146" s="22" t="n">
+      <c r="F146" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="23" t="n">
+      <c r="G146" s="28" t="n">
         <v>2.004</v>
       </c>
-      <c r="H146" s="23" t="n">
+      <c r="H146" s="28" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="22" t="n">
+      <c r="A147" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="B147" s="23" t="n">
+      <c r="B147" s="28" t="n">
         <v>0.419</v>
       </c>
-      <c r="C147" s="23" t="n">
+      <c r="C147" s="28" t="n">
         <v>1.182</v>
       </c>
-      <c r="D147" s="23" t="n">
+      <c r="D147" s="28" t="n">
         <v>0.118</v>
       </c>
-      <c r="E147" s="23" t="n">
+      <c r="E147" s="28" t="n">
         <v>1.882</v>
       </c>
-      <c r="F147" s="23" t="n">
+      <c r="F147" s="28" t="n">
         <v>0.076</v>
       </c>
-      <c r="G147" s="23" t="n">
+      <c r="G147" s="28" t="n">
         <v>1.924</v>
       </c>
-      <c r="H147" s="23" t="n">
+      <c r="H147" s="28" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="22" t="n">
+      <c r="A148" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="B148" s="23" t="n">
+      <c r="B148" s="28" t="n">
         <v>0.373</v>
       </c>
-      <c r="C148" s="23" t="n">
+      <c r="C148" s="28" t="n">
         <v>1.099</v>
       </c>
-      <c r="D148" s="23" t="n">
+      <c r="D148" s="28" t="n">
         <v>0.185</v>
       </c>
-      <c r="E148" s="23" t="n">
+      <c r="E148" s="28" t="n">
         <v>1.815</v>
       </c>
-      <c r="F148" s="23" t="n">
+      <c r="F148" s="28" t="n">
         <v>0.136</v>
       </c>
-      <c r="G148" s="23" t="n">
+      <c r="G148" s="28" t="n">
         <v>1.864</v>
       </c>
-      <c r="H148" s="23" t="n">
+      <c r="H148" s="28" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="22" t="n">
+      <c r="A149" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="B149" s="23" t="n">
+      <c r="B149" s="28" t="n">
         <v>0.337</v>
       </c>
-      <c r="C149" s="23" t="n">
+      <c r="C149" s="28" t="n">
         <v>1.032</v>
       </c>
-      <c r="D149" s="23" t="n">
+      <c r="D149" s="28" t="n">
         <v>0.239</v>
       </c>
-      <c r="E149" s="23" t="n">
+      <c r="E149" s="28" t="n">
         <v>1.761</v>
       </c>
-      <c r="F149" s="23" t="n">
+      <c r="F149" s="28" t="n">
         <v>0.184</v>
       </c>
-      <c r="G149" s="23" t="n">
+      <c r="G149" s="28" t="n">
         <v>1.816</v>
       </c>
-      <c r="H149" s="23" t="n">
+      <c r="H149" s="28" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="22" t="n">
+      <c r="A150" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B150" s="23" t="n">
+      <c r="B150" s="28" t="n">
         <v>0.308</v>
       </c>
-      <c r="C150" s="23" t="n">
+      <c r="C150" s="28" t="n">
         <v>0.975</v>
       </c>
-      <c r="D150" s="23" t="n">
+      <c r="D150" s="28" t="n">
         <v>0.284</v>
       </c>
-      <c r="E150" s="23" t="n">
+      <c r="E150" s="28" t="n">
         <v>1.716</v>
       </c>
-      <c r="F150" s="23" t="n">
+      <c r="F150" s="28" t="n">
         <v>0.223</v>
       </c>
-      <c r="G150" s="23" t="n">
+      <c r="G150" s="28" t="n">
         <v>1.777</v>
       </c>
-      <c r="H150" s="23" t="n">
+      <c r="H150" s="28" t="n">
         <v>0.975</v>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capability" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sigma &amp; DPMO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance CI &amp; tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -69,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
@@ -80,6 +81,8 @@
     <numFmt numFmtId="171" formatCode="0.000000000"/>
     <numFmt numFmtId="172" formatCode="#,##0.000"/>
     <numFmt numFmtId="173" formatCode="0.0000000000%"/>
+    <numFmt numFmtId="174" formatCode="0.000000"/>
+    <numFmt numFmtId="175" formatCode="0.0000000000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -184,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -218,6 +221,9 @@
     <xf numFmtId="1" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3585,6 +3591,2777 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I509"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variances: CI and test for σ² and σ (χ²), CI and test for a ratio of two variances (F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 2/20260529_ottoy_Confidence Intervals - Further Reading (Dutch).pdf p. 21; Confidence Intervals.pdf p. 16; Testing of Hypotheses.pdf p. 13; Test Recipes - Further Reading (Dutch).pdf p. 11-14; Six Sigma For Dummies.pdf p. 192-196</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Decisions 5-7: α input prefilled 0.05; two-sided, lower-only and upper-only side by side; F from F.INV / F.INV.RT, both σ1²/σ2² and σ2²/σ1².</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: tested against course worked examples S03-WE03, S03-WE05, S08-WE10 and the Dummies χ² and F tables (p. 194, 196); the Dummies F-interval example S08-WE11 disagrees (build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. Settings</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Optional: paste raw values below; n and s are then computed from them</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Significance α (confidence = 1 − α)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>course has no default; most course examples use 5 %; use the value the question gives</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Sample 1 data</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>Sample 2 data</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2. One sample: σ² and σ</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>n (sample size)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>or paste the data in column H</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>s (sample standard deviation, STDEV.S)</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>σ0 for the test (the claimed σ)</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 0.01</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>n used</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>IF(COUNT(H10:H509)&gt;1,COUNT(H10:H509),IF(ISNUMBER(B12),B12,""))</f>
+        <v/>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>from column H if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>s used</t>
+        </is>
+      </c>
+      <c r="B16" s="28">
+        <f>IF(COUNT(H10:H509)&gt;1,_xlfn.STDEV.S(H10:H509),IF(ISNUMBER(B13),B13,""))</f>
+        <v/>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>from column H if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>s² used</t>
+        </is>
+      </c>
+      <c r="B17" s="29">
+        <f>IF(ISNUMBER(B16),B16^2,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>degrees of freedom n − 1</t>
+        </is>
+      </c>
+      <c r="B18" s="24">
+        <f>IF(ISNUMBER(B15),B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Confidence interval (1 − α)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>σ² from</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>σ² to</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>σ from</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>σ to</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B21" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),B18*B17/_xlfn.CHISQ.INV.RT(B9/2,B18),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),B18*B17/_xlfn.CHISQ.INV(B9/2,B18),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="28">
+        <f>IF(ISNUMBER(B21),SQRT(B21),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>IF(ISNUMBER(C21),SQRT(C21),C21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>CI Further Reading (Dutch) p. 21</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>lower bound only (σ at least …; goes with HA: σ &gt; σ0)</t>
+        </is>
+      </c>
+      <c r="B22" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),B18*B17/_xlfn.CHISQ.INV.RT(B9,B18),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>IF(ISNUMBER(B22),SQRT(B22),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>IF(ISNUMBER(C22),SQRT(C22),C22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Confidence Intervals.pdf p. 16 ('one-sided 98 %-CI ]0.0088, +∞[')</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>upper bound only (σ at most …; goes with HA: σ &lt; σ0)</t>
+        </is>
+      </c>
+      <c r="B23" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),0,"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),B18*B17/_xlfn.CHISQ.INV(B9,B18),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>IF(ISNUMBER(B23),SQRT(B23),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>IF(ISNUMBER(C23),SQRT(C23),C23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>χ²-test of H0: σ = σ0</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Statistic (n−1)s²/σ0²</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Critical value</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical value</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>HA: σ ≠ σ0 (two-sided)</t>
+        </is>
+      </c>
+      <c r="B27" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),B18*B17/B14^2,"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),_xlfn.CHISQ.INV(B9/2,B18),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),_xlfn.CHISQ.INV.RT(B9/2,B18),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),2*MIN(_xlfn.CHISQ.DIST(B27,B18,TRUE),_xlfn.CHISQ.DIST.RT(B27,B18)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="13">
+        <f>IF(ISNUMBER(E27),IF(E27&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>HA: σ &gt; σ0 (e.g. 'more erratic')</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),B18*B17/B14^2,"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),_xlfn.CHISQ.INV.RT(B9,B18),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),_xlfn.CHISQ.DIST.RT(B28,B18),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="13">
+        <f>IF(ISNUMBER(E28),IF(E28&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>HA: σ &lt; σ0</t>
+        </is>
+      </c>
+      <c r="B29" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),B18*B17/B14^2,"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="11">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),_xlfn.CHISQ.INV(B9,B18),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E29" s="14">
+        <f>IF(AND(AND(ISNUMBER(B17),ISNUMBER(B18),B18&gt;0,ISNUMBER(B9)),ISNUMBER(B14),B14&gt;0),_xlfn.CHISQ.DIST(B29,B18,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="13">
+        <f>IF(ISNUMBER(E29),IF(E29&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Source: Test Recipes - Further Reading (Dutch) p. 11; Testing of Hypotheses.pdf p. 13</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>3. Two samples: ratio of variances (F)   e.g. exam Q2: is machine M1 more precise than M2?</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>n1 (sample 1)</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>or paste sample 1 in column H</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>n2 (sample 2)</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>or paste sample 2 in column I</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>n1 used</t>
+        </is>
+      </c>
+      <c r="B36" s="24">
+        <f>IF(COUNT(H10:H509)&gt;1,COUNT(H10:H509),IF(ISNUMBER(B32),B32,""))</f>
+        <v/>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>from column H if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>s1 used</t>
+        </is>
+      </c>
+      <c r="B37" s="28">
+        <f>IF(COUNT(H10:H509)&gt;1,_xlfn.STDEV.S(H10:H509),IF(ISNUMBER(B33),B33,""))</f>
+        <v/>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>from column H if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>n2 used</t>
+        </is>
+      </c>
+      <c r="B38" s="24">
+        <f>IF(COUNT(I10:I509)&gt;1,COUNT(I10:I509),IF(ISNUMBER(B34),B34,""))</f>
+        <v/>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>from column I if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>s2 used</t>
+        </is>
+      </c>
+      <c r="B39" s="28">
+        <f>IF(COUNT(I10:I509)&gt;1,_xlfn.STDEV.S(I10:I509),IF(ISNUMBER(B35),B35,""))</f>
+        <v/>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>from column I if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>F = s1² / s2²</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B37^2/B39^2,"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Test Recipes p. 12-13: (s1²/σ1²)/(s2²/σ2²) ~ F(n1 − 1, n2 − 1)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>degrees of freedom (numerator n1 − 1, denominator n2 − 1)</t>
+        </is>
+      </c>
+      <c r="B41" s="24">
+        <f>IF(ISNUMBER(B36),B36-1,"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="24">
+        <f>IF(ISNUMBER(B38),B38-1,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Confidence interval (1 − α)</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>σ1²/σ2² from</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>σ1²/σ2² to</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>σ2²/σ1² from</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>σ2²/σ1² to</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B44" s="28">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40/_xlfn.F.INV.RT(B9/2,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="28">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40/_xlfn.F.INV(B9/2,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="28">
+        <f>IF(ISNUMBER(C44),1/C44,IF(C44="+∞",0,""))</f>
+        <v/>
+      </c>
+      <c r="E44" s="28">
+        <f>IF(ISNUMBER(B44),IF(B44=0,"+∞",1/B44),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>exam Q2 hint; Test Recipes p. 12</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>one-sided: σ1²/σ2² at least … (σ2²/σ1² at most …)</t>
+        </is>
+      </c>
+      <c r="B45" s="28">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40/_xlfn.F.INV.RT(B9,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="28">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D45" s="28">
+        <f>IF(ISNUMBER(C45),1/C45,IF(C45="+∞",0,""))</f>
+        <v/>
+      </c>
+      <c r="E45" s="28">
+        <f>IF(ISNUMBER(B45),IF(B45=0,"+∞",1/B45),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>goes with HA: σ1 &gt; σ2</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>one-sided: σ1²/σ2² at most … (σ2²/σ1² at least …)</t>
+        </is>
+      </c>
+      <c r="B46" s="28">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),0,"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="28">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40/_xlfn.F.INV(B9,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="28">
+        <f>IF(ISNUMBER(C46),1/C46,IF(C46="+∞",0,""))</f>
+        <v/>
+      </c>
+      <c r="E46" s="28">
+        <f>IF(ISNUMBER(B46),IF(B46=0,"+∞",1/B46),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>goes with HA: σ1 &lt; σ2 (e.g. M1 more precise)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>F-test of H0: σ1 = σ2</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Statistic F = s1²/s2²</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Critical value</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical value</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>HA: σ1 ≠ σ2 (two-sided)</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40,"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),_xlfn.F.INV(B9/2,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),_xlfn.F.INV.RT(B9/2,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="14">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),2*MIN(_xlfn.F.DIST(B49,B41,C41,TRUE),_xlfn.F.DIST.RT(B49,B41,C41)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="13">
+        <f>IF(ISNUMBER(E49),IF(E49&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>HA: σ1 &gt; σ2</t>
+        </is>
+      </c>
+      <c r="B50" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40,"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),_xlfn.F.INV.RT(B9,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),_xlfn.F.DIST.RT(B50,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="13">
+        <f>IF(ISNUMBER(E50),IF(E50&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>HA: σ1 &lt; σ2</t>
+        </is>
+      </c>
+      <c r="B51" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),B40,"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),_xlfn.F.INV(B9,B41,C41),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E51" s="14">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(B37),ISNUMBER(B38),ISNUMBER(B39),B36&gt;1,B38&gt;1,B39&gt;0,ISNUMBER(B9)),_xlfn.F.DIST(B51,B41,C41,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="13">
+        <f>IF(ISNUMBER(E51),IF(E51&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Source: Test Recipes - Further Reading (Dutch) p. 13-14; Dummies Table 8-3 p. 196 (5 % upper-tail F values)</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+    </row>
+    <row r="64">
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+    </row>
+    <row r="74">
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="H76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+    </row>
+    <row r="79">
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+    </row>
+    <row r="80">
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+    </row>
+    <row r="82">
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
+    </row>
+    <row r="84">
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
+    </row>
+    <row r="85">
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
+    </row>
+    <row r="86">
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+    </row>
+    <row r="88">
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="H94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="H95" s="7" t="n"/>
+      <c r="I95" s="7" t="n"/>
+    </row>
+    <row r="96">
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+    </row>
+    <row r="98">
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+    </row>
+    <row r="99">
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
+    </row>
+    <row r="100">
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="H101" s="7" t="n"/>
+      <c r="I101" s="7" t="n"/>
+    </row>
+    <row r="102">
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="H103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
+    </row>
+    <row r="104">
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
+    </row>
+    <row r="105">
+      <c r="H105" s="7" t="n"/>
+      <c r="I105" s="7" t="n"/>
+    </row>
+    <row r="106">
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="H109" s="7" t="n"/>
+      <c r="I109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="H110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="H111" s="7" t="n"/>
+      <c r="I111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
+    </row>
+    <row r="113">
+      <c r="H113" s="7" t="n"/>
+      <c r="I113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="H114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="H115" s="7" t="n"/>
+      <c r="I115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
+    </row>
+    <row r="117">
+      <c r="H117" s="7" t="n"/>
+      <c r="I117" s="7" t="n"/>
+    </row>
+    <row r="118">
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
+    </row>
+    <row r="119">
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
+    </row>
+    <row r="120">
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="H121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
+    </row>
+    <row r="122">
+      <c r="H122" s="7" t="n"/>
+      <c r="I122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="H123" s="7" t="n"/>
+      <c r="I123" s="7" t="n"/>
+    </row>
+    <row r="124">
+      <c r="H124" s="7" t="n"/>
+      <c r="I124" s="7" t="n"/>
+    </row>
+    <row r="125">
+      <c r="H125" s="7" t="n"/>
+      <c r="I125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="H126" s="7" t="n"/>
+      <c r="I126" s="7" t="n"/>
+    </row>
+    <row r="127">
+      <c r="H127" s="7" t="n"/>
+      <c r="I127" s="7" t="n"/>
+    </row>
+    <row r="128">
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
+    </row>
+    <row r="129">
+      <c r="H129" s="7" t="n"/>
+      <c r="I129" s="7" t="n"/>
+    </row>
+    <row r="130">
+      <c r="H130" s="7" t="n"/>
+      <c r="I130" s="7" t="n"/>
+    </row>
+    <row r="131">
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
+    </row>
+    <row r="132">
+      <c r="H132" s="7" t="n"/>
+      <c r="I132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="H133" s="7" t="n"/>
+      <c r="I133" s="7" t="n"/>
+    </row>
+    <row r="134">
+      <c r="H134" s="7" t="n"/>
+      <c r="I134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="H135" s="7" t="n"/>
+      <c r="I135" s="7" t="n"/>
+    </row>
+    <row r="136">
+      <c r="H136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
+    </row>
+    <row r="137">
+      <c r="H137" s="7" t="n"/>
+      <c r="I137" s="7" t="n"/>
+    </row>
+    <row r="138">
+      <c r="H138" s="7" t="n"/>
+      <c r="I138" s="7" t="n"/>
+    </row>
+    <row r="139">
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="H140" s="7" t="n"/>
+      <c r="I140" s="7" t="n"/>
+    </row>
+    <row r="141">
+      <c r="H141" s="7" t="n"/>
+      <c r="I141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="H142" s="7" t="n"/>
+      <c r="I142" s="7" t="n"/>
+    </row>
+    <row r="143">
+      <c r="H143" s="7" t="n"/>
+      <c r="I143" s="7" t="n"/>
+    </row>
+    <row r="144">
+      <c r="H144" s="7" t="n"/>
+      <c r="I144" s="7" t="n"/>
+    </row>
+    <row r="145">
+      <c r="H145" s="7" t="n"/>
+      <c r="I145" s="7" t="n"/>
+    </row>
+    <row r="146">
+      <c r="H146" s="7" t="n"/>
+      <c r="I146" s="7" t="n"/>
+    </row>
+    <row r="147">
+      <c r="H147" s="7" t="n"/>
+      <c r="I147" s="7" t="n"/>
+    </row>
+    <row r="148">
+      <c r="H148" s="7" t="n"/>
+      <c r="I148" s="7" t="n"/>
+    </row>
+    <row r="149">
+      <c r="H149" s="7" t="n"/>
+      <c r="I149" s="7" t="n"/>
+    </row>
+    <row r="150">
+      <c r="H150" s="7" t="n"/>
+      <c r="I150" s="7" t="n"/>
+    </row>
+    <row r="151">
+      <c r="H151" s="7" t="n"/>
+      <c r="I151" s="7" t="n"/>
+    </row>
+    <row r="152">
+      <c r="H152" s="7" t="n"/>
+      <c r="I152" s="7" t="n"/>
+    </row>
+    <row r="153">
+      <c r="H153" s="7" t="n"/>
+      <c r="I153" s="7" t="n"/>
+    </row>
+    <row r="154">
+      <c r="H154" s="7" t="n"/>
+      <c r="I154" s="7" t="n"/>
+    </row>
+    <row r="155">
+      <c r="H155" s="7" t="n"/>
+      <c r="I155" s="7" t="n"/>
+    </row>
+    <row r="156">
+      <c r="H156" s="7" t="n"/>
+      <c r="I156" s="7" t="n"/>
+    </row>
+    <row r="157">
+      <c r="H157" s="7" t="n"/>
+      <c r="I157" s="7" t="n"/>
+    </row>
+    <row r="158">
+      <c r="H158" s="7" t="n"/>
+      <c r="I158" s="7" t="n"/>
+    </row>
+    <row r="159">
+      <c r="H159" s="7" t="n"/>
+      <c r="I159" s="7" t="n"/>
+    </row>
+    <row r="160">
+      <c r="H160" s="7" t="n"/>
+      <c r="I160" s="7" t="n"/>
+    </row>
+    <row r="161">
+      <c r="H161" s="7" t="n"/>
+      <c r="I161" s="7" t="n"/>
+    </row>
+    <row r="162">
+      <c r="H162" s="7" t="n"/>
+      <c r="I162" s="7" t="n"/>
+    </row>
+    <row r="163">
+      <c r="H163" s="7" t="n"/>
+      <c r="I163" s="7" t="n"/>
+    </row>
+    <row r="164">
+      <c r="H164" s="7" t="n"/>
+      <c r="I164" s="7" t="n"/>
+    </row>
+    <row r="165">
+      <c r="H165" s="7" t="n"/>
+      <c r="I165" s="7" t="n"/>
+    </row>
+    <row r="166">
+      <c r="H166" s="7" t="n"/>
+      <c r="I166" s="7" t="n"/>
+    </row>
+    <row r="167">
+      <c r="H167" s="7" t="n"/>
+      <c r="I167" s="7" t="n"/>
+    </row>
+    <row r="168">
+      <c r="H168" s="7" t="n"/>
+      <c r="I168" s="7" t="n"/>
+    </row>
+    <row r="169">
+      <c r="H169" s="7" t="n"/>
+      <c r="I169" s="7" t="n"/>
+    </row>
+    <row r="170">
+      <c r="H170" s="7" t="n"/>
+      <c r="I170" s="7" t="n"/>
+    </row>
+    <row r="171">
+      <c r="H171" s="7" t="n"/>
+      <c r="I171" s="7" t="n"/>
+    </row>
+    <row r="172">
+      <c r="H172" s="7" t="n"/>
+      <c r="I172" s="7" t="n"/>
+    </row>
+    <row r="173">
+      <c r="H173" s="7" t="n"/>
+      <c r="I173" s="7" t="n"/>
+    </row>
+    <row r="174">
+      <c r="H174" s="7" t="n"/>
+      <c r="I174" s="7" t="n"/>
+    </row>
+    <row r="175">
+      <c r="H175" s="7" t="n"/>
+      <c r="I175" s="7" t="n"/>
+    </row>
+    <row r="176">
+      <c r="H176" s="7" t="n"/>
+      <c r="I176" s="7" t="n"/>
+    </row>
+    <row r="177">
+      <c r="H177" s="7" t="n"/>
+      <c r="I177" s="7" t="n"/>
+    </row>
+    <row r="178">
+      <c r="H178" s="7" t="n"/>
+      <c r="I178" s="7" t="n"/>
+    </row>
+    <row r="179">
+      <c r="H179" s="7" t="n"/>
+      <c r="I179" s="7" t="n"/>
+    </row>
+    <row r="180">
+      <c r="H180" s="7" t="n"/>
+      <c r="I180" s="7" t="n"/>
+    </row>
+    <row r="181">
+      <c r="H181" s="7" t="n"/>
+      <c r="I181" s="7" t="n"/>
+    </row>
+    <row r="182">
+      <c r="H182" s="7" t="n"/>
+      <c r="I182" s="7" t="n"/>
+    </row>
+    <row r="183">
+      <c r="H183" s="7" t="n"/>
+      <c r="I183" s="7" t="n"/>
+    </row>
+    <row r="184">
+      <c r="H184" s="7" t="n"/>
+      <c r="I184" s="7" t="n"/>
+    </row>
+    <row r="185">
+      <c r="H185" s="7" t="n"/>
+      <c r="I185" s="7" t="n"/>
+    </row>
+    <row r="186">
+      <c r="H186" s="7" t="n"/>
+      <c r="I186" s="7" t="n"/>
+    </row>
+    <row r="187">
+      <c r="H187" s="7" t="n"/>
+      <c r="I187" s="7" t="n"/>
+    </row>
+    <row r="188">
+      <c r="H188" s="7" t="n"/>
+      <c r="I188" s="7" t="n"/>
+    </row>
+    <row r="189">
+      <c r="H189" s="7" t="n"/>
+      <c r="I189" s="7" t="n"/>
+    </row>
+    <row r="190">
+      <c r="H190" s="7" t="n"/>
+      <c r="I190" s="7" t="n"/>
+    </row>
+    <row r="191">
+      <c r="H191" s="7" t="n"/>
+      <c r="I191" s="7" t="n"/>
+    </row>
+    <row r="192">
+      <c r="H192" s="7" t="n"/>
+      <c r="I192" s="7" t="n"/>
+    </row>
+    <row r="193">
+      <c r="H193" s="7" t="n"/>
+      <c r="I193" s="7" t="n"/>
+    </row>
+    <row r="194">
+      <c r="H194" s="7" t="n"/>
+      <c r="I194" s="7" t="n"/>
+    </row>
+    <row r="195">
+      <c r="H195" s="7" t="n"/>
+      <c r="I195" s="7" t="n"/>
+    </row>
+    <row r="196">
+      <c r="H196" s="7" t="n"/>
+      <c r="I196" s="7" t="n"/>
+    </row>
+    <row r="197">
+      <c r="H197" s="7" t="n"/>
+      <c r="I197" s="7" t="n"/>
+    </row>
+    <row r="198">
+      <c r="H198" s="7" t="n"/>
+      <c r="I198" s="7" t="n"/>
+    </row>
+    <row r="199">
+      <c r="H199" s="7" t="n"/>
+      <c r="I199" s="7" t="n"/>
+    </row>
+    <row r="200">
+      <c r="H200" s="7" t="n"/>
+      <c r="I200" s="7" t="n"/>
+    </row>
+    <row r="201">
+      <c r="H201" s="7" t="n"/>
+      <c r="I201" s="7" t="n"/>
+    </row>
+    <row r="202">
+      <c r="H202" s="7" t="n"/>
+      <c r="I202" s="7" t="n"/>
+    </row>
+    <row r="203">
+      <c r="H203" s="7" t="n"/>
+      <c r="I203" s="7" t="n"/>
+    </row>
+    <row r="204">
+      <c r="H204" s="7" t="n"/>
+      <c r="I204" s="7" t="n"/>
+    </row>
+    <row r="205">
+      <c r="H205" s="7" t="n"/>
+      <c r="I205" s="7" t="n"/>
+    </row>
+    <row r="206">
+      <c r="H206" s="7" t="n"/>
+      <c r="I206" s="7" t="n"/>
+    </row>
+    <row r="207">
+      <c r="H207" s="7" t="n"/>
+      <c r="I207" s="7" t="n"/>
+    </row>
+    <row r="208">
+      <c r="H208" s="7" t="n"/>
+      <c r="I208" s="7" t="n"/>
+    </row>
+    <row r="209">
+      <c r="H209" s="7" t="n"/>
+      <c r="I209" s="7" t="n"/>
+    </row>
+    <row r="210">
+      <c r="H210" s="7" t="n"/>
+      <c r="I210" s="7" t="n"/>
+    </row>
+    <row r="211">
+      <c r="H211" s="7" t="n"/>
+      <c r="I211" s="7" t="n"/>
+    </row>
+    <row r="212">
+      <c r="H212" s="7" t="n"/>
+      <c r="I212" s="7" t="n"/>
+    </row>
+    <row r="213">
+      <c r="H213" s="7" t="n"/>
+      <c r="I213" s="7" t="n"/>
+    </row>
+    <row r="214">
+      <c r="H214" s="7" t="n"/>
+      <c r="I214" s="7" t="n"/>
+    </row>
+    <row r="215">
+      <c r="H215" s="7" t="n"/>
+      <c r="I215" s="7" t="n"/>
+    </row>
+    <row r="216">
+      <c r="H216" s="7" t="n"/>
+      <c r="I216" s="7" t="n"/>
+    </row>
+    <row r="217">
+      <c r="H217" s="7" t="n"/>
+      <c r="I217" s="7" t="n"/>
+    </row>
+    <row r="218">
+      <c r="H218" s="7" t="n"/>
+      <c r="I218" s="7" t="n"/>
+    </row>
+    <row r="219">
+      <c r="H219" s="7" t="n"/>
+      <c r="I219" s="7" t="n"/>
+    </row>
+    <row r="220">
+      <c r="H220" s="7" t="n"/>
+      <c r="I220" s="7" t="n"/>
+    </row>
+    <row r="221">
+      <c r="H221" s="7" t="n"/>
+      <c r="I221" s="7" t="n"/>
+    </row>
+    <row r="222">
+      <c r="H222" s="7" t="n"/>
+      <c r="I222" s="7" t="n"/>
+    </row>
+    <row r="223">
+      <c r="H223" s="7" t="n"/>
+      <c r="I223" s="7" t="n"/>
+    </row>
+    <row r="224">
+      <c r="H224" s="7" t="n"/>
+      <c r="I224" s="7" t="n"/>
+    </row>
+    <row r="225">
+      <c r="H225" s="7" t="n"/>
+      <c r="I225" s="7" t="n"/>
+    </row>
+    <row r="226">
+      <c r="H226" s="7" t="n"/>
+      <c r="I226" s="7" t="n"/>
+    </row>
+    <row r="227">
+      <c r="H227" s="7" t="n"/>
+      <c r="I227" s="7" t="n"/>
+    </row>
+    <row r="228">
+      <c r="H228" s="7" t="n"/>
+      <c r="I228" s="7" t="n"/>
+    </row>
+    <row r="229">
+      <c r="H229" s="7" t="n"/>
+      <c r="I229" s="7" t="n"/>
+    </row>
+    <row r="230">
+      <c r="H230" s="7" t="n"/>
+      <c r="I230" s="7" t="n"/>
+    </row>
+    <row r="231">
+      <c r="H231" s="7" t="n"/>
+      <c r="I231" s="7" t="n"/>
+    </row>
+    <row r="232">
+      <c r="H232" s="7" t="n"/>
+      <c r="I232" s="7" t="n"/>
+    </row>
+    <row r="233">
+      <c r="H233" s="7" t="n"/>
+      <c r="I233" s="7" t="n"/>
+    </row>
+    <row r="234">
+      <c r="H234" s="7" t="n"/>
+      <c r="I234" s="7" t="n"/>
+    </row>
+    <row r="235">
+      <c r="H235" s="7" t="n"/>
+      <c r="I235" s="7" t="n"/>
+    </row>
+    <row r="236">
+      <c r="H236" s="7" t="n"/>
+      <c r="I236" s="7" t="n"/>
+    </row>
+    <row r="237">
+      <c r="H237" s="7" t="n"/>
+      <c r="I237" s="7" t="n"/>
+    </row>
+    <row r="238">
+      <c r="H238" s="7" t="n"/>
+      <c r="I238" s="7" t="n"/>
+    </row>
+    <row r="239">
+      <c r="H239" s="7" t="n"/>
+      <c r="I239" s="7" t="n"/>
+    </row>
+    <row r="240">
+      <c r="H240" s="7" t="n"/>
+      <c r="I240" s="7" t="n"/>
+    </row>
+    <row r="241">
+      <c r="H241" s="7" t="n"/>
+      <c r="I241" s="7" t="n"/>
+    </row>
+    <row r="242">
+      <c r="H242" s="7" t="n"/>
+      <c r="I242" s="7" t="n"/>
+    </row>
+    <row r="243">
+      <c r="H243" s="7" t="n"/>
+      <c r="I243" s="7" t="n"/>
+    </row>
+    <row r="244">
+      <c r="H244" s="7" t="n"/>
+      <c r="I244" s="7" t="n"/>
+    </row>
+    <row r="245">
+      <c r="H245" s="7" t="n"/>
+      <c r="I245" s="7" t="n"/>
+    </row>
+    <row r="246">
+      <c r="H246" s="7" t="n"/>
+      <c r="I246" s="7" t="n"/>
+    </row>
+    <row r="247">
+      <c r="H247" s="7" t="n"/>
+      <c r="I247" s="7" t="n"/>
+    </row>
+    <row r="248">
+      <c r="H248" s="7" t="n"/>
+      <c r="I248" s="7" t="n"/>
+    </row>
+    <row r="249">
+      <c r="H249" s="7" t="n"/>
+      <c r="I249" s="7" t="n"/>
+    </row>
+    <row r="250">
+      <c r="H250" s="7" t="n"/>
+      <c r="I250" s="7" t="n"/>
+    </row>
+    <row r="251">
+      <c r="H251" s="7" t="n"/>
+      <c r="I251" s="7" t="n"/>
+    </row>
+    <row r="252">
+      <c r="H252" s="7" t="n"/>
+      <c r="I252" s="7" t="n"/>
+    </row>
+    <row r="253">
+      <c r="H253" s="7" t="n"/>
+      <c r="I253" s="7" t="n"/>
+    </row>
+    <row r="254">
+      <c r="H254" s="7" t="n"/>
+      <c r="I254" s="7" t="n"/>
+    </row>
+    <row r="255">
+      <c r="H255" s="7" t="n"/>
+      <c r="I255" s="7" t="n"/>
+    </row>
+    <row r="256">
+      <c r="H256" s="7" t="n"/>
+      <c r="I256" s="7" t="n"/>
+    </row>
+    <row r="257">
+      <c r="H257" s="7" t="n"/>
+      <c r="I257" s="7" t="n"/>
+    </row>
+    <row r="258">
+      <c r="H258" s="7" t="n"/>
+      <c r="I258" s="7" t="n"/>
+    </row>
+    <row r="259">
+      <c r="H259" s="7" t="n"/>
+      <c r="I259" s="7" t="n"/>
+    </row>
+    <row r="260">
+      <c r="H260" s="7" t="n"/>
+      <c r="I260" s="7" t="n"/>
+    </row>
+    <row r="261">
+      <c r="H261" s="7" t="n"/>
+      <c r="I261" s="7" t="n"/>
+    </row>
+    <row r="262">
+      <c r="H262" s="7" t="n"/>
+      <c r="I262" s="7" t="n"/>
+    </row>
+    <row r="263">
+      <c r="H263" s="7" t="n"/>
+      <c r="I263" s="7" t="n"/>
+    </row>
+    <row r="264">
+      <c r="H264" s="7" t="n"/>
+      <c r="I264" s="7" t="n"/>
+    </row>
+    <row r="265">
+      <c r="H265" s="7" t="n"/>
+      <c r="I265" s="7" t="n"/>
+    </row>
+    <row r="266">
+      <c r="H266" s="7" t="n"/>
+      <c r="I266" s="7" t="n"/>
+    </row>
+    <row r="267">
+      <c r="H267" s="7" t="n"/>
+      <c r="I267" s="7" t="n"/>
+    </row>
+    <row r="268">
+      <c r="H268" s="7" t="n"/>
+      <c r="I268" s="7" t="n"/>
+    </row>
+    <row r="269">
+      <c r="H269" s="7" t="n"/>
+      <c r="I269" s="7" t="n"/>
+    </row>
+    <row r="270">
+      <c r="H270" s="7" t="n"/>
+      <c r="I270" s="7" t="n"/>
+    </row>
+    <row r="271">
+      <c r="H271" s="7" t="n"/>
+      <c r="I271" s="7" t="n"/>
+    </row>
+    <row r="272">
+      <c r="H272" s="7" t="n"/>
+      <c r="I272" s="7" t="n"/>
+    </row>
+    <row r="273">
+      <c r="H273" s="7" t="n"/>
+      <c r="I273" s="7" t="n"/>
+    </row>
+    <row r="274">
+      <c r="H274" s="7" t="n"/>
+      <c r="I274" s="7" t="n"/>
+    </row>
+    <row r="275">
+      <c r="H275" s="7" t="n"/>
+      <c r="I275" s="7" t="n"/>
+    </row>
+    <row r="276">
+      <c r="H276" s="7" t="n"/>
+      <c r="I276" s="7" t="n"/>
+    </row>
+    <row r="277">
+      <c r="H277" s="7" t="n"/>
+      <c r="I277" s="7" t="n"/>
+    </row>
+    <row r="278">
+      <c r="H278" s="7" t="n"/>
+      <c r="I278" s="7" t="n"/>
+    </row>
+    <row r="279">
+      <c r="H279" s="7" t="n"/>
+      <c r="I279" s="7" t="n"/>
+    </row>
+    <row r="280">
+      <c r="H280" s="7" t="n"/>
+      <c r="I280" s="7" t="n"/>
+    </row>
+    <row r="281">
+      <c r="H281" s="7" t="n"/>
+      <c r="I281" s="7" t="n"/>
+    </row>
+    <row r="282">
+      <c r="H282" s="7" t="n"/>
+      <c r="I282" s="7" t="n"/>
+    </row>
+    <row r="283">
+      <c r="H283" s="7" t="n"/>
+      <c r="I283" s="7" t="n"/>
+    </row>
+    <row r="284">
+      <c r="H284" s="7" t="n"/>
+      <c r="I284" s="7" t="n"/>
+    </row>
+    <row r="285">
+      <c r="H285" s="7" t="n"/>
+      <c r="I285" s="7" t="n"/>
+    </row>
+    <row r="286">
+      <c r="H286" s="7" t="n"/>
+      <c r="I286" s="7" t="n"/>
+    </row>
+    <row r="287">
+      <c r="H287" s="7" t="n"/>
+      <c r="I287" s="7" t="n"/>
+    </row>
+    <row r="288">
+      <c r="H288" s="7" t="n"/>
+      <c r="I288" s="7" t="n"/>
+    </row>
+    <row r="289">
+      <c r="H289" s="7" t="n"/>
+      <c r="I289" s="7" t="n"/>
+    </row>
+    <row r="290">
+      <c r="H290" s="7" t="n"/>
+      <c r="I290" s="7" t="n"/>
+    </row>
+    <row r="291">
+      <c r="H291" s="7" t="n"/>
+      <c r="I291" s="7" t="n"/>
+    </row>
+    <row r="292">
+      <c r="H292" s="7" t="n"/>
+      <c r="I292" s="7" t="n"/>
+    </row>
+    <row r="293">
+      <c r="H293" s="7" t="n"/>
+      <c r="I293" s="7" t="n"/>
+    </row>
+    <row r="294">
+      <c r="H294" s="7" t="n"/>
+      <c r="I294" s="7" t="n"/>
+    </row>
+    <row r="295">
+      <c r="H295" s="7" t="n"/>
+      <c r="I295" s="7" t="n"/>
+    </row>
+    <row r="296">
+      <c r="H296" s="7" t="n"/>
+      <c r="I296" s="7" t="n"/>
+    </row>
+    <row r="297">
+      <c r="H297" s="7" t="n"/>
+      <c r="I297" s="7" t="n"/>
+    </row>
+    <row r="298">
+      <c r="H298" s="7" t="n"/>
+      <c r="I298" s="7" t="n"/>
+    </row>
+    <row r="299">
+      <c r="H299" s="7" t="n"/>
+      <c r="I299" s="7" t="n"/>
+    </row>
+    <row r="300">
+      <c r="H300" s="7" t="n"/>
+      <c r="I300" s="7" t="n"/>
+    </row>
+    <row r="301">
+      <c r="H301" s="7" t="n"/>
+      <c r="I301" s="7" t="n"/>
+    </row>
+    <row r="302">
+      <c r="H302" s="7" t="n"/>
+      <c r="I302" s="7" t="n"/>
+    </row>
+    <row r="303">
+      <c r="H303" s="7" t="n"/>
+      <c r="I303" s="7" t="n"/>
+    </row>
+    <row r="304">
+      <c r="H304" s="7" t="n"/>
+      <c r="I304" s="7" t="n"/>
+    </row>
+    <row r="305">
+      <c r="H305" s="7" t="n"/>
+      <c r="I305" s="7" t="n"/>
+    </row>
+    <row r="306">
+      <c r="H306" s="7" t="n"/>
+      <c r="I306" s="7" t="n"/>
+    </row>
+    <row r="307">
+      <c r="H307" s="7" t="n"/>
+      <c r="I307" s="7" t="n"/>
+    </row>
+    <row r="308">
+      <c r="H308" s="7" t="n"/>
+      <c r="I308" s="7" t="n"/>
+    </row>
+    <row r="309">
+      <c r="H309" s="7" t="n"/>
+      <c r="I309" s="7" t="n"/>
+    </row>
+    <row r="310">
+      <c r="H310" s="7" t="n"/>
+      <c r="I310" s="7" t="n"/>
+    </row>
+    <row r="311">
+      <c r="H311" s="7" t="n"/>
+      <c r="I311" s="7" t="n"/>
+    </row>
+    <row r="312">
+      <c r="H312" s="7" t="n"/>
+      <c r="I312" s="7" t="n"/>
+    </row>
+    <row r="313">
+      <c r="H313" s="7" t="n"/>
+      <c r="I313" s="7" t="n"/>
+    </row>
+    <row r="314">
+      <c r="H314" s="7" t="n"/>
+      <c r="I314" s="7" t="n"/>
+    </row>
+    <row r="315">
+      <c r="H315" s="7" t="n"/>
+      <c r="I315" s="7" t="n"/>
+    </row>
+    <row r="316">
+      <c r="H316" s="7" t="n"/>
+      <c r="I316" s="7" t="n"/>
+    </row>
+    <row r="317">
+      <c r="H317" s="7" t="n"/>
+      <c r="I317" s="7" t="n"/>
+    </row>
+    <row r="318">
+      <c r="H318" s="7" t="n"/>
+      <c r="I318" s="7" t="n"/>
+    </row>
+    <row r="319">
+      <c r="H319" s="7" t="n"/>
+      <c r="I319" s="7" t="n"/>
+    </row>
+    <row r="320">
+      <c r="H320" s="7" t="n"/>
+      <c r="I320" s="7" t="n"/>
+    </row>
+    <row r="321">
+      <c r="H321" s="7" t="n"/>
+      <c r="I321" s="7" t="n"/>
+    </row>
+    <row r="322">
+      <c r="H322" s="7" t="n"/>
+      <c r="I322" s="7" t="n"/>
+    </row>
+    <row r="323">
+      <c r="H323" s="7" t="n"/>
+      <c r="I323" s="7" t="n"/>
+    </row>
+    <row r="324">
+      <c r="H324" s="7" t="n"/>
+      <c r="I324" s="7" t="n"/>
+    </row>
+    <row r="325">
+      <c r="H325" s="7" t="n"/>
+      <c r="I325" s="7" t="n"/>
+    </row>
+    <row r="326">
+      <c r="H326" s="7" t="n"/>
+      <c r="I326" s="7" t="n"/>
+    </row>
+    <row r="327">
+      <c r="H327" s="7" t="n"/>
+      <c r="I327" s="7" t="n"/>
+    </row>
+    <row r="328">
+      <c r="H328" s="7" t="n"/>
+      <c r="I328" s="7" t="n"/>
+    </row>
+    <row r="329">
+      <c r="H329" s="7" t="n"/>
+      <c r="I329" s="7" t="n"/>
+    </row>
+    <row r="330">
+      <c r="H330" s="7" t="n"/>
+      <c r="I330" s="7" t="n"/>
+    </row>
+    <row r="331">
+      <c r="H331" s="7" t="n"/>
+      <c r="I331" s="7" t="n"/>
+    </row>
+    <row r="332">
+      <c r="H332" s="7" t="n"/>
+      <c r="I332" s="7" t="n"/>
+    </row>
+    <row r="333">
+      <c r="H333" s="7" t="n"/>
+      <c r="I333" s="7" t="n"/>
+    </row>
+    <row r="334">
+      <c r="H334" s="7" t="n"/>
+      <c r="I334" s="7" t="n"/>
+    </row>
+    <row r="335">
+      <c r="H335" s="7" t="n"/>
+      <c r="I335" s="7" t="n"/>
+    </row>
+    <row r="336">
+      <c r="H336" s="7" t="n"/>
+      <c r="I336" s="7" t="n"/>
+    </row>
+    <row r="337">
+      <c r="H337" s="7" t="n"/>
+      <c r="I337" s="7" t="n"/>
+    </row>
+    <row r="338">
+      <c r="H338" s="7" t="n"/>
+      <c r="I338" s="7" t="n"/>
+    </row>
+    <row r="339">
+      <c r="H339" s="7" t="n"/>
+      <c r="I339" s="7" t="n"/>
+    </row>
+    <row r="340">
+      <c r="H340" s="7" t="n"/>
+      <c r="I340" s="7" t="n"/>
+    </row>
+    <row r="341">
+      <c r="H341" s="7" t="n"/>
+      <c r="I341" s="7" t="n"/>
+    </row>
+    <row r="342">
+      <c r="H342" s="7" t="n"/>
+      <c r="I342" s="7" t="n"/>
+    </row>
+    <row r="343">
+      <c r="H343" s="7" t="n"/>
+      <c r="I343" s="7" t="n"/>
+    </row>
+    <row r="344">
+      <c r="H344" s="7" t="n"/>
+      <c r="I344" s="7" t="n"/>
+    </row>
+    <row r="345">
+      <c r="H345" s="7" t="n"/>
+      <c r="I345" s="7" t="n"/>
+    </row>
+    <row r="346">
+      <c r="H346" s="7" t="n"/>
+      <c r="I346" s="7" t="n"/>
+    </row>
+    <row r="347">
+      <c r="H347" s="7" t="n"/>
+      <c r="I347" s="7" t="n"/>
+    </row>
+    <row r="348">
+      <c r="H348" s="7" t="n"/>
+      <c r="I348" s="7" t="n"/>
+    </row>
+    <row r="349">
+      <c r="H349" s="7" t="n"/>
+      <c r="I349" s="7" t="n"/>
+    </row>
+    <row r="350">
+      <c r="H350" s="7" t="n"/>
+      <c r="I350" s="7" t="n"/>
+    </row>
+    <row r="351">
+      <c r="H351" s="7" t="n"/>
+      <c r="I351" s="7" t="n"/>
+    </row>
+    <row r="352">
+      <c r="H352" s="7" t="n"/>
+      <c r="I352" s="7" t="n"/>
+    </row>
+    <row r="353">
+      <c r="H353" s="7" t="n"/>
+      <c r="I353" s="7" t="n"/>
+    </row>
+    <row r="354">
+      <c r="H354" s="7" t="n"/>
+      <c r="I354" s="7" t="n"/>
+    </row>
+    <row r="355">
+      <c r="H355" s="7" t="n"/>
+      <c r="I355" s="7" t="n"/>
+    </row>
+    <row r="356">
+      <c r="H356" s="7" t="n"/>
+      <c r="I356" s="7" t="n"/>
+    </row>
+    <row r="357">
+      <c r="H357" s="7" t="n"/>
+      <c r="I357" s="7" t="n"/>
+    </row>
+    <row r="358">
+      <c r="H358" s="7" t="n"/>
+      <c r="I358" s="7" t="n"/>
+    </row>
+    <row r="359">
+      <c r="H359" s="7" t="n"/>
+      <c r="I359" s="7" t="n"/>
+    </row>
+    <row r="360">
+      <c r="H360" s="7" t="n"/>
+      <c r="I360" s="7" t="n"/>
+    </row>
+    <row r="361">
+      <c r="H361" s="7" t="n"/>
+      <c r="I361" s="7" t="n"/>
+    </row>
+    <row r="362">
+      <c r="H362" s="7" t="n"/>
+      <c r="I362" s="7" t="n"/>
+    </row>
+    <row r="363">
+      <c r="H363" s="7" t="n"/>
+      <c r="I363" s="7" t="n"/>
+    </row>
+    <row r="364">
+      <c r="H364" s="7" t="n"/>
+      <c r="I364" s="7" t="n"/>
+    </row>
+    <row r="365">
+      <c r="H365" s="7" t="n"/>
+      <c r="I365" s="7" t="n"/>
+    </row>
+    <row r="366">
+      <c r="H366" s="7" t="n"/>
+      <c r="I366" s="7" t="n"/>
+    </row>
+    <row r="367">
+      <c r="H367" s="7" t="n"/>
+      <c r="I367" s="7" t="n"/>
+    </row>
+    <row r="368">
+      <c r="H368" s="7" t="n"/>
+      <c r="I368" s="7" t="n"/>
+    </row>
+    <row r="369">
+      <c r="H369" s="7" t="n"/>
+      <c r="I369" s="7" t="n"/>
+    </row>
+    <row r="370">
+      <c r="H370" s="7" t="n"/>
+      <c r="I370" s="7" t="n"/>
+    </row>
+    <row r="371">
+      <c r="H371" s="7" t="n"/>
+      <c r="I371" s="7" t="n"/>
+    </row>
+    <row r="372">
+      <c r="H372" s="7" t="n"/>
+      <c r="I372" s="7" t="n"/>
+    </row>
+    <row r="373">
+      <c r="H373" s="7" t="n"/>
+      <c r="I373" s="7" t="n"/>
+    </row>
+    <row r="374">
+      <c r="H374" s="7" t="n"/>
+      <c r="I374" s="7" t="n"/>
+    </row>
+    <row r="375">
+      <c r="H375" s="7" t="n"/>
+      <c r="I375" s="7" t="n"/>
+    </row>
+    <row r="376">
+      <c r="H376" s="7" t="n"/>
+      <c r="I376" s="7" t="n"/>
+    </row>
+    <row r="377">
+      <c r="H377" s="7" t="n"/>
+      <c r="I377" s="7" t="n"/>
+    </row>
+    <row r="378">
+      <c r="H378" s="7" t="n"/>
+      <c r="I378" s="7" t="n"/>
+    </row>
+    <row r="379">
+      <c r="H379" s="7" t="n"/>
+      <c r="I379" s="7" t="n"/>
+    </row>
+    <row r="380">
+      <c r="H380" s="7" t="n"/>
+      <c r="I380" s="7" t="n"/>
+    </row>
+    <row r="381">
+      <c r="H381" s="7" t="n"/>
+      <c r="I381" s="7" t="n"/>
+    </row>
+    <row r="382">
+      <c r="H382" s="7" t="n"/>
+      <c r="I382" s="7" t="n"/>
+    </row>
+    <row r="383">
+      <c r="H383" s="7" t="n"/>
+      <c r="I383" s="7" t="n"/>
+    </row>
+    <row r="384">
+      <c r="H384" s="7" t="n"/>
+      <c r="I384" s="7" t="n"/>
+    </row>
+    <row r="385">
+      <c r="H385" s="7" t="n"/>
+      <c r="I385" s="7" t="n"/>
+    </row>
+    <row r="386">
+      <c r="H386" s="7" t="n"/>
+      <c r="I386" s="7" t="n"/>
+    </row>
+    <row r="387">
+      <c r="H387" s="7" t="n"/>
+      <c r="I387" s="7" t="n"/>
+    </row>
+    <row r="388">
+      <c r="H388" s="7" t="n"/>
+      <c r="I388" s="7" t="n"/>
+    </row>
+    <row r="389">
+      <c r="H389" s="7" t="n"/>
+      <c r="I389" s="7" t="n"/>
+    </row>
+    <row r="390">
+      <c r="H390" s="7" t="n"/>
+      <c r="I390" s="7" t="n"/>
+    </row>
+    <row r="391">
+      <c r="H391" s="7" t="n"/>
+      <c r="I391" s="7" t="n"/>
+    </row>
+    <row r="392">
+      <c r="H392" s="7" t="n"/>
+      <c r="I392" s="7" t="n"/>
+    </row>
+    <row r="393">
+      <c r="H393" s="7" t="n"/>
+      <c r="I393" s="7" t="n"/>
+    </row>
+    <row r="394">
+      <c r="H394" s="7" t="n"/>
+      <c r="I394" s="7" t="n"/>
+    </row>
+    <row r="395">
+      <c r="H395" s="7" t="n"/>
+      <c r="I395" s="7" t="n"/>
+    </row>
+    <row r="396">
+      <c r="H396" s="7" t="n"/>
+      <c r="I396" s="7" t="n"/>
+    </row>
+    <row r="397">
+      <c r="H397" s="7" t="n"/>
+      <c r="I397" s="7" t="n"/>
+    </row>
+    <row r="398">
+      <c r="H398" s="7" t="n"/>
+      <c r="I398" s="7" t="n"/>
+    </row>
+    <row r="399">
+      <c r="H399" s="7" t="n"/>
+      <c r="I399" s="7" t="n"/>
+    </row>
+    <row r="400">
+      <c r="H400" s="7" t="n"/>
+      <c r="I400" s="7" t="n"/>
+    </row>
+    <row r="401">
+      <c r="H401" s="7" t="n"/>
+      <c r="I401" s="7" t="n"/>
+    </row>
+    <row r="402">
+      <c r="H402" s="7" t="n"/>
+      <c r="I402" s="7" t="n"/>
+    </row>
+    <row r="403">
+      <c r="H403" s="7" t="n"/>
+      <c r="I403" s="7" t="n"/>
+    </row>
+    <row r="404">
+      <c r="H404" s="7" t="n"/>
+      <c r="I404" s="7" t="n"/>
+    </row>
+    <row r="405">
+      <c r="H405" s="7" t="n"/>
+      <c r="I405" s="7" t="n"/>
+    </row>
+    <row r="406">
+      <c r="H406" s="7" t="n"/>
+      <c r="I406" s="7" t="n"/>
+    </row>
+    <row r="407">
+      <c r="H407" s="7" t="n"/>
+      <c r="I407" s="7" t="n"/>
+    </row>
+    <row r="408">
+      <c r="H408" s="7" t="n"/>
+      <c r="I408" s="7" t="n"/>
+    </row>
+    <row r="409">
+      <c r="H409" s="7" t="n"/>
+      <c r="I409" s="7" t="n"/>
+    </row>
+    <row r="410">
+      <c r="H410" s="7" t="n"/>
+      <c r="I410" s="7" t="n"/>
+    </row>
+    <row r="411">
+      <c r="H411" s="7" t="n"/>
+      <c r="I411" s="7" t="n"/>
+    </row>
+    <row r="412">
+      <c r="H412" s="7" t="n"/>
+      <c r="I412" s="7" t="n"/>
+    </row>
+    <row r="413">
+      <c r="H413" s="7" t="n"/>
+      <c r="I413" s="7" t="n"/>
+    </row>
+    <row r="414">
+      <c r="H414" s="7" t="n"/>
+      <c r="I414" s="7" t="n"/>
+    </row>
+    <row r="415">
+      <c r="H415" s="7" t="n"/>
+      <c r="I415" s="7" t="n"/>
+    </row>
+    <row r="416">
+      <c r="H416" s="7" t="n"/>
+      <c r="I416" s="7" t="n"/>
+    </row>
+    <row r="417">
+      <c r="H417" s="7" t="n"/>
+      <c r="I417" s="7" t="n"/>
+    </row>
+    <row r="418">
+      <c r="H418" s="7" t="n"/>
+      <c r="I418" s="7" t="n"/>
+    </row>
+    <row r="419">
+      <c r="H419" s="7" t="n"/>
+      <c r="I419" s="7" t="n"/>
+    </row>
+    <row r="420">
+      <c r="H420" s="7" t="n"/>
+      <c r="I420" s="7" t="n"/>
+    </row>
+    <row r="421">
+      <c r="H421" s="7" t="n"/>
+      <c r="I421" s="7" t="n"/>
+    </row>
+    <row r="422">
+      <c r="H422" s="7" t="n"/>
+      <c r="I422" s="7" t="n"/>
+    </row>
+    <row r="423">
+      <c r="H423" s="7" t="n"/>
+      <c r="I423" s="7" t="n"/>
+    </row>
+    <row r="424">
+      <c r="H424" s="7" t="n"/>
+      <c r="I424" s="7" t="n"/>
+    </row>
+    <row r="425">
+      <c r="H425" s="7" t="n"/>
+      <c r="I425" s="7" t="n"/>
+    </row>
+    <row r="426">
+      <c r="H426" s="7" t="n"/>
+      <c r="I426" s="7" t="n"/>
+    </row>
+    <row r="427">
+      <c r="H427" s="7" t="n"/>
+      <c r="I427" s="7" t="n"/>
+    </row>
+    <row r="428">
+      <c r="H428" s="7" t="n"/>
+      <c r="I428" s="7" t="n"/>
+    </row>
+    <row r="429">
+      <c r="H429" s="7" t="n"/>
+      <c r="I429" s="7" t="n"/>
+    </row>
+    <row r="430">
+      <c r="H430" s="7" t="n"/>
+      <c r="I430" s="7" t="n"/>
+    </row>
+    <row r="431">
+      <c r="H431" s="7" t="n"/>
+      <c r="I431" s="7" t="n"/>
+    </row>
+    <row r="432">
+      <c r="H432" s="7" t="n"/>
+      <c r="I432" s="7" t="n"/>
+    </row>
+    <row r="433">
+      <c r="H433" s="7" t="n"/>
+      <c r="I433" s="7" t="n"/>
+    </row>
+    <row r="434">
+      <c r="H434" s="7" t="n"/>
+      <c r="I434" s="7" t="n"/>
+    </row>
+    <row r="435">
+      <c r="H435" s="7" t="n"/>
+      <c r="I435" s="7" t="n"/>
+    </row>
+    <row r="436">
+      <c r="H436" s="7" t="n"/>
+      <c r="I436" s="7" t="n"/>
+    </row>
+    <row r="437">
+      <c r="H437" s="7" t="n"/>
+      <c r="I437" s="7" t="n"/>
+    </row>
+    <row r="438">
+      <c r="H438" s="7" t="n"/>
+      <c r="I438" s="7" t="n"/>
+    </row>
+    <row r="439">
+      <c r="H439" s="7" t="n"/>
+      <c r="I439" s="7" t="n"/>
+    </row>
+    <row r="440">
+      <c r="H440" s="7" t="n"/>
+      <c r="I440" s="7" t="n"/>
+    </row>
+    <row r="441">
+      <c r="H441" s="7" t="n"/>
+      <c r="I441" s="7" t="n"/>
+    </row>
+    <row r="442">
+      <c r="H442" s="7" t="n"/>
+      <c r="I442" s="7" t="n"/>
+    </row>
+    <row r="443">
+      <c r="H443" s="7" t="n"/>
+      <c r="I443" s="7" t="n"/>
+    </row>
+    <row r="444">
+      <c r="H444" s="7" t="n"/>
+      <c r="I444" s="7" t="n"/>
+    </row>
+    <row r="445">
+      <c r="H445" s="7" t="n"/>
+      <c r="I445" s="7" t="n"/>
+    </row>
+    <row r="446">
+      <c r="H446" s="7" t="n"/>
+      <c r="I446" s="7" t="n"/>
+    </row>
+    <row r="447">
+      <c r="H447" s="7" t="n"/>
+      <c r="I447" s="7" t="n"/>
+    </row>
+    <row r="448">
+      <c r="H448" s="7" t="n"/>
+      <c r="I448" s="7" t="n"/>
+    </row>
+    <row r="449">
+      <c r="H449" s="7" t="n"/>
+      <c r="I449" s="7" t="n"/>
+    </row>
+    <row r="450">
+      <c r="H450" s="7" t="n"/>
+      <c r="I450" s="7" t="n"/>
+    </row>
+    <row r="451">
+      <c r="H451" s="7" t="n"/>
+      <c r="I451" s="7" t="n"/>
+    </row>
+    <row r="452">
+      <c r="H452" s="7" t="n"/>
+      <c r="I452" s="7" t="n"/>
+    </row>
+    <row r="453">
+      <c r="H453" s="7" t="n"/>
+      <c r="I453" s="7" t="n"/>
+    </row>
+    <row r="454">
+      <c r="H454" s="7" t="n"/>
+      <c r="I454" s="7" t="n"/>
+    </row>
+    <row r="455">
+      <c r="H455" s="7" t="n"/>
+      <c r="I455" s="7" t="n"/>
+    </row>
+    <row r="456">
+      <c r="H456" s="7" t="n"/>
+      <c r="I456" s="7" t="n"/>
+    </row>
+    <row r="457">
+      <c r="H457" s="7" t="n"/>
+      <c r="I457" s="7" t="n"/>
+    </row>
+    <row r="458">
+      <c r="H458" s="7" t="n"/>
+      <c r="I458" s="7" t="n"/>
+    </row>
+    <row r="459">
+      <c r="H459" s="7" t="n"/>
+      <c r="I459" s="7" t="n"/>
+    </row>
+    <row r="460">
+      <c r="H460" s="7" t="n"/>
+      <c r="I460" s="7" t="n"/>
+    </row>
+    <row r="461">
+      <c r="H461" s="7" t="n"/>
+      <c r="I461" s="7" t="n"/>
+    </row>
+    <row r="462">
+      <c r="H462" s="7" t="n"/>
+      <c r="I462" s="7" t="n"/>
+    </row>
+    <row r="463">
+      <c r="H463" s="7" t="n"/>
+      <c r="I463" s="7" t="n"/>
+    </row>
+    <row r="464">
+      <c r="H464" s="7" t="n"/>
+      <c r="I464" s="7" t="n"/>
+    </row>
+    <row r="465">
+      <c r="H465" s="7" t="n"/>
+      <c r="I465" s="7" t="n"/>
+    </row>
+    <row r="466">
+      <c r="H466" s="7" t="n"/>
+      <c r="I466" s="7" t="n"/>
+    </row>
+    <row r="467">
+      <c r="H467" s="7" t="n"/>
+      <c r="I467" s="7" t="n"/>
+    </row>
+    <row r="468">
+      <c r="H468" s="7" t="n"/>
+      <c r="I468" s="7" t="n"/>
+    </row>
+    <row r="469">
+      <c r="H469" s="7" t="n"/>
+      <c r="I469" s="7" t="n"/>
+    </row>
+    <row r="470">
+      <c r="H470" s="7" t="n"/>
+      <c r="I470" s="7" t="n"/>
+    </row>
+    <row r="471">
+      <c r="H471" s="7" t="n"/>
+      <c r="I471" s="7" t="n"/>
+    </row>
+    <row r="472">
+      <c r="H472" s="7" t="n"/>
+      <c r="I472" s="7" t="n"/>
+    </row>
+    <row r="473">
+      <c r="H473" s="7" t="n"/>
+      <c r="I473" s="7" t="n"/>
+    </row>
+    <row r="474">
+      <c r="H474" s="7" t="n"/>
+      <c r="I474" s="7" t="n"/>
+    </row>
+    <row r="475">
+      <c r="H475" s="7" t="n"/>
+      <c r="I475" s="7" t="n"/>
+    </row>
+    <row r="476">
+      <c r="H476" s="7" t="n"/>
+      <c r="I476" s="7" t="n"/>
+    </row>
+    <row r="477">
+      <c r="H477" s="7" t="n"/>
+      <c r="I477" s="7" t="n"/>
+    </row>
+    <row r="478">
+      <c r="H478" s="7" t="n"/>
+      <c r="I478" s="7" t="n"/>
+    </row>
+    <row r="479">
+      <c r="H479" s="7" t="n"/>
+      <c r="I479" s="7" t="n"/>
+    </row>
+    <row r="480">
+      <c r="H480" s="7" t="n"/>
+      <c r="I480" s="7" t="n"/>
+    </row>
+    <row r="481">
+      <c r="H481" s="7" t="n"/>
+      <c r="I481" s="7" t="n"/>
+    </row>
+    <row r="482">
+      <c r="H482" s="7" t="n"/>
+      <c r="I482" s="7" t="n"/>
+    </row>
+    <row r="483">
+      <c r="H483" s="7" t="n"/>
+      <c r="I483" s="7" t="n"/>
+    </row>
+    <row r="484">
+      <c r="H484" s="7" t="n"/>
+      <c r="I484" s="7" t="n"/>
+    </row>
+    <row r="485">
+      <c r="H485" s="7" t="n"/>
+      <c r="I485" s="7" t="n"/>
+    </row>
+    <row r="486">
+      <c r="H486" s="7" t="n"/>
+      <c r="I486" s="7" t="n"/>
+    </row>
+    <row r="487">
+      <c r="H487" s="7" t="n"/>
+      <c r="I487" s="7" t="n"/>
+    </row>
+    <row r="488">
+      <c r="H488" s="7" t="n"/>
+      <c r="I488" s="7" t="n"/>
+    </row>
+    <row r="489">
+      <c r="H489" s="7" t="n"/>
+      <c r="I489" s="7" t="n"/>
+    </row>
+    <row r="490">
+      <c r="H490" s="7" t="n"/>
+      <c r="I490" s="7" t="n"/>
+    </row>
+    <row r="491">
+      <c r="H491" s="7" t="n"/>
+      <c r="I491" s="7" t="n"/>
+    </row>
+    <row r="492">
+      <c r="H492" s="7" t="n"/>
+      <c r="I492" s="7" t="n"/>
+    </row>
+    <row r="493">
+      <c r="H493" s="7" t="n"/>
+      <c r="I493" s="7" t="n"/>
+    </row>
+    <row r="494">
+      <c r="H494" s="7" t="n"/>
+      <c r="I494" s="7" t="n"/>
+    </row>
+    <row r="495">
+      <c r="H495" s="7" t="n"/>
+      <c r="I495" s="7" t="n"/>
+    </row>
+    <row r="496">
+      <c r="H496" s="7" t="n"/>
+      <c r="I496" s="7" t="n"/>
+    </row>
+    <row r="497">
+      <c r="H497" s="7" t="n"/>
+      <c r="I497" s="7" t="n"/>
+    </row>
+    <row r="498">
+      <c r="H498" s="7" t="n"/>
+      <c r="I498" s="7" t="n"/>
+    </row>
+    <row r="499">
+      <c r="H499" s="7" t="n"/>
+      <c r="I499" s="7" t="n"/>
+    </row>
+    <row r="500">
+      <c r="H500" s="7" t="n"/>
+      <c r="I500" s="7" t="n"/>
+    </row>
+    <row r="501">
+      <c r="H501" s="7" t="n"/>
+      <c r="I501" s="7" t="n"/>
+    </row>
+    <row r="502">
+      <c r="H502" s="7" t="n"/>
+      <c r="I502" s="7" t="n"/>
+    </row>
+    <row r="503">
+      <c r="H503" s="7" t="n"/>
+      <c r="I503" s="7" t="n"/>
+    </row>
+    <row r="504">
+      <c r="H504" s="7" t="n"/>
+      <c r="I504" s="7" t="n"/>
+    </row>
+    <row r="505">
+      <c r="H505" s="7" t="n"/>
+      <c r="I505" s="7" t="n"/>
+    </row>
+    <row r="506">
+      <c r="H506" s="7" t="n"/>
+      <c r="I506" s="7" t="n"/>
+    </row>
+    <row r="507">
+      <c r="H507" s="7" t="n"/>
+      <c r="I507" s="7" t="n"/>
+    </row>
+    <row r="508">
+      <c r="H508" s="7" t="n"/>
+      <c r="I508" s="7" t="n"/>
+    </row>
+    <row r="509">
+      <c r="H509" s="7" t="n"/>
+      <c r="I509" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="α" error="α is a fraction, e.g. 0.05." type="decimal" operator="between">
+      <formula1>0.0000001</formula1>
+      <formula2>0.9999999</formula2>
+    </dataValidation>
+    <dataValidation sqref="B12 B13 B14 B32 B33 B34 B35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Must be positive" error="Must be greater than 0." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3792,1327 +6569,1327 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="28" t="n">
+      <c r="B14" s="31" t="n">
         <v>2.121</v>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="31" t="n">
         <v>3.76</v>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="31" t="n">
         <v>3.76</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="31" t="n">
         <v>1.88</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="32" t="n">
         <v>0.5642</v>
       </c>
-      <c r="G14" s="29" t="n">
+      <c r="G14" s="32" t="n">
         <v>1.7725</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="31" t="n">
         <v>1.843</v>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="28" t="n">
+      <c r="K14" s="31" t="n">
         <v>3.267</v>
       </c>
-      <c r="L14" s="28" t="n">
+      <c r="L14" s="31" t="n">
         <v>1.128</v>
       </c>
-      <c r="M14" s="29" t="n">
+      <c r="M14" s="32" t="n">
         <v>0.8865</v>
       </c>
-      <c r="N14" s="27" t="n">
+      <c r="N14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="28" t="n">
+      <c r="O14" s="31" t="n">
         <v>3.686</v>
       </c>
-      <c r="P14" s="27" t="n">
+      <c r="P14" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="28" t="n">
+      <c r="Q14" s="31" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="31" t="n">
         <v>1.732</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="31" t="n">
         <v>3.07</v>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="31" t="n">
         <v>2.394</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="31" t="n">
         <v>1.023</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="32" t="n">
         <v>0.7236</v>
       </c>
-      <c r="G15" s="29" t="n">
+      <c r="G15" s="32" t="n">
         <v>1.382</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="31" t="n">
         <v>1.858</v>
       </c>
-      <c r="J15" s="27" t="n">
+      <c r="J15" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="28" t="n">
+      <c r="K15" s="31" t="n">
         <v>2.568</v>
       </c>
-      <c r="L15" s="28" t="n">
+      <c r="L15" s="31" t="n">
         <v>1.693</v>
       </c>
-      <c r="M15" s="29" t="n">
+      <c r="M15" s="32" t="n">
         <v>0.5907</v>
       </c>
-      <c r="N15" s="27" t="n">
+      <c r="N15" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="28" t="n">
+      <c r="O15" s="31" t="n">
         <v>4.358</v>
       </c>
-      <c r="P15" s="27" t="n">
+      <c r="P15" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="30" t="n">
+      <c r="Q15" s="33" t="n">
         <v>2.575</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="28" t="n">
+      <c r="B16" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="31" t="n">
         <v>2.914</v>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="31" t="n">
         <v>1.88</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="31" t="n">
         <v>0.729</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="32" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="G16" s="29" t="n">
+      <c r="G16" s="32" t="n">
         <v>1.2533</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="31" t="n">
         <v>1.808</v>
       </c>
-      <c r="J16" s="27" t="n">
+      <c r="J16" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="28" t="n">
+      <c r="K16" s="31" t="n">
         <v>2.266</v>
       </c>
-      <c r="L16" s="28" t="n">
+      <c r="L16" s="31" t="n">
         <v>2.059</v>
       </c>
-      <c r="M16" s="29" t="n">
+      <c r="M16" s="32" t="n">
         <v>0.4857</v>
       </c>
-      <c r="N16" s="27" t="n">
+      <c r="N16" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="28" t="n">
+      <c r="O16" s="31" t="n">
         <v>4.698</v>
       </c>
-      <c r="P16" s="27" t="n">
+      <c r="P16" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="28" t="n">
+      <c r="Q16" s="31" t="n">
         <v>2.282</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="31" t="n">
         <v>1.342</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="31" t="n">
         <v>2.884</v>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="31" t="n">
         <v>1.596</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="31" t="n">
         <v>0.577</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="32" t="n">
         <v>0.8407</v>
       </c>
-      <c r="G17" s="29" t="n">
+      <c r="G17" s="32" t="n">
         <v>1.1894</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="31" t="n">
         <v>1.756</v>
       </c>
-      <c r="J17" s="27" t="n">
+      <c r="J17" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="28" t="n">
+      <c r="K17" s="31" t="n">
         <v>2.089</v>
       </c>
-      <c r="L17" s="28" t="n">
+      <c r="L17" s="31" t="n">
         <v>2.326</v>
       </c>
-      <c r="M17" s="29" t="n">
+      <c r="M17" s="32" t="n">
         <v>0.4299</v>
       </c>
-      <c r="N17" s="27" t="n">
+      <c r="N17" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="28" t="n">
+      <c r="O17" s="31" t="n">
         <v>4.918</v>
       </c>
-      <c r="P17" s="27" t="n">
+      <c r="P17" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="30" t="n">
+      <c r="Q17" s="33" t="n">
         <v>2.115</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="31" t="n">
         <v>1.225</v>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="31" t="n">
         <v>2.899</v>
       </c>
-      <c r="D18" s="28" t="n">
+      <c r="D18" s="31" t="n">
         <v>1.41</v>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E18" s="31" t="n">
         <v>0.483</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="32" t="n">
         <v>0.8686</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G18" s="32" t="n">
         <v>1.1512</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="31" t="n">
         <v>0.026</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="31" t="n">
         <v>1.711</v>
       </c>
-      <c r="J18" s="28" t="n">
+      <c r="J18" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" s="28" t="n">
+      <c r="K18" s="31" t="n">
         <v>1.97</v>
       </c>
-      <c r="L18" s="28" t="n">
+      <c r="L18" s="31" t="n">
         <v>2.534</v>
       </c>
-      <c r="M18" s="29" t="n">
+      <c r="M18" s="32" t="n">
         <v>0.3946</v>
       </c>
-      <c r="N18" s="27" t="n">
+      <c r="N18" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="28" t="n">
+      <c r="O18" s="31" t="n">
         <v>5.078</v>
       </c>
-      <c r="P18" s="27" t="n">
+      <c r="P18" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="28" t="n">
+      <c r="Q18" s="31" t="n">
         <v>2.004</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="31" t="n">
         <v>1.134</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="31" t="n">
         <v>2.935</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="31" t="n">
         <v>1.277</v>
       </c>
-      <c r="E19" s="28" t="n">
+      <c r="E19" s="31" t="n">
         <v>0.419</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="32" t="n">
         <v>0.8882</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="32" t="n">
         <v>1.1259</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="31" t="n">
         <v>0.105</v>
       </c>
-      <c r="I19" s="28" t="n">
+      <c r="I19" s="31" t="n">
         <v>1.672</v>
       </c>
-      <c r="J19" s="28" t="n">
+      <c r="J19" s="31" t="n">
         <v>0.118</v>
       </c>
-      <c r="K19" s="28" t="n">
+      <c r="K19" s="31" t="n">
         <v>1.882</v>
       </c>
-      <c r="L19" s="28" t="n">
+      <c r="L19" s="31" t="n">
         <v>2.704</v>
       </c>
-      <c r="M19" s="29" t="n">
+      <c r="M19" s="32" t="n">
         <v>0.3698</v>
       </c>
-      <c r="N19" s="30" t="n">
+      <c r="N19" s="33" t="n">
         <v>0.205</v>
       </c>
-      <c r="O19" s="30" t="n">
+      <c r="O19" s="33" t="n">
         <v>5.203</v>
       </c>
-      <c r="P19" s="28" t="n">
+      <c r="P19" s="31" t="n">
         <v>0.076</v>
       </c>
-      <c r="Q19" s="28" t="n">
+      <c r="Q19" s="31" t="n">
         <v>1.924</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="28" t="n">
+      <c r="B20" s="31" t="n">
         <v>1.061</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="31" t="n">
         <v>2.98</v>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="31" t="n">
         <v>1.175</v>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="31" t="n">
         <v>0.373</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="32" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="32" t="n">
         <v>1.1078</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="31" t="n">
         <v>0.167</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="I20" s="31" t="n">
         <v>1.638</v>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="31" t="n">
         <v>0.185</v>
       </c>
-      <c r="K20" s="28" t="n">
+      <c r="K20" s="31" t="n">
         <v>1.815</v>
       </c>
-      <c r="L20" s="28" t="n">
+      <c r="L20" s="31" t="n">
         <v>2.847</v>
       </c>
-      <c r="M20" s="29" t="n">
+      <c r="M20" s="32" t="n">
         <v>0.3512</v>
       </c>
-      <c r="N20" s="30" t="n">
+      <c r="N20" s="33" t="n">
         <v>0.387</v>
       </c>
-      <c r="O20" s="30" t="n">
+      <c r="O20" s="33" t="n">
         <v>5.307</v>
       </c>
-      <c r="P20" s="28" t="n">
+      <c r="P20" s="31" t="n">
         <v>0.136</v>
       </c>
-      <c r="Q20" s="28" t="n">
+      <c r="Q20" s="31" t="n">
         <v>1.864</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="28" t="n">
+      <c r="C21" s="31" t="n">
         <v>3.03</v>
       </c>
-      <c r="D21" s="28" t="n">
+      <c r="D21" s="31" t="n">
         <v>1.094</v>
       </c>
-      <c r="E21" s="28" t="n">
+      <c r="E21" s="31" t="n">
         <v>0.337</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="32" t="n">
         <v>0.9139</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="32" t="n">
         <v>1.0942</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="31" t="n">
         <v>0.219</v>
       </c>
-      <c r="I21" s="28" t="n">
+      <c r="I21" s="31" t="n">
         <v>1.609</v>
       </c>
-      <c r="J21" s="28" t="n">
+      <c r="J21" s="31" t="n">
         <v>0.239</v>
       </c>
-      <c r="K21" s="28" t="n">
+      <c r="K21" s="31" t="n">
         <v>1.761</v>
       </c>
-      <c r="L21" s="28" t="n">
+      <c r="L21" s="31" t="n">
         <v>2.97</v>
       </c>
-      <c r="M21" s="29" t="n">
+      <c r="M21" s="32" t="n">
         <v>0.3367</v>
       </c>
-      <c r="N21" s="30" t="n">
+      <c r="N21" s="33" t="n">
         <v>0.546</v>
       </c>
-      <c r="O21" s="30" t="n">
+      <c r="O21" s="33" t="n">
         <v>5.394</v>
       </c>
-      <c r="P21" s="28" t="n">
+      <c r="P21" s="31" t="n">
         <v>0.184</v>
       </c>
-      <c r="Q21" s="28" t="n">
+      <c r="Q21" s="31" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="28" t="n">
+      <c r="B22" s="31" t="n">
         <v>0.949</v>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="31" t="n">
         <v>3.085</v>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="31" t="n">
         <v>1.028</v>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="E22" s="31" t="n">
         <v>0.308</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="32" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="32" t="n">
         <v>1.0837</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="31" t="n">
         <v>0.262</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="I22" s="31" t="n">
         <v>1.584</v>
       </c>
-      <c r="J22" s="28" t="n">
+      <c r="J22" s="31" t="n">
         <v>0.284</v>
       </c>
-      <c r="K22" s="28" t="n">
+      <c r="K22" s="31" t="n">
         <v>1.716</v>
       </c>
-      <c r="L22" s="28" t="n">
+      <c r="L22" s="31" t="n">
         <v>3.078</v>
       </c>
-      <c r="M22" s="29" t="n">
+      <c r="M22" s="32" t="n">
         <v>0.3249</v>
       </c>
-      <c r="N22" s="28" t="n">
+      <c r="N22" s="31" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="O22" s="28" t="n">
+      <c r="O22" s="31" t="n">
         <v>5.469</v>
       </c>
-      <c r="P22" s="28" t="n">
+      <c r="P22" s="31" t="n">
         <v>0.223</v>
       </c>
-      <c r="Q22" s="28" t="n">
+      <c r="Q22" s="31" t="n">
         <v>1.777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="n">
+      <c r="A23" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="31" t="n">
         <v>0.905</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="31" t="n">
         <v>3.136</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="31" t="n">
         <v>0.973</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="E23" s="31" t="n">
         <v>0.285</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="32" t="n">
         <v>0.93</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G23" s="32" t="n">
         <v>1.0753</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="31" t="n">
         <v>0.299</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="31" t="n">
         <v>1.561</v>
       </c>
-      <c r="J23" s="28" t="n">
+      <c r="J23" s="31" t="n">
         <v>0.321</v>
       </c>
-      <c r="K23" s="28" t="n">
+      <c r="K23" s="31" t="n">
         <v>1.679</v>
       </c>
-      <c r="L23" s="28" t="n">
+      <c r="L23" s="31" t="n">
         <v>3.173</v>
       </c>
-      <c r="M23" s="29" t="n">
+      <c r="M23" s="32" t="n">
         <v>0.3152</v>
       </c>
-      <c r="N23" s="30" t="n">
+      <c r="N23" s="33" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="O23" s="30" t="n">
+      <c r="O23" s="33" t="n">
         <v>5.534</v>
       </c>
-      <c r="P23" s="28" t="n">
+      <c r="P23" s="31" t="n">
         <v>0.256</v>
       </c>
-      <c r="Q23" s="28" t="n">
+      <c r="Q23" s="31" t="n">
         <v>1.744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="28" t="n">
+      <c r="B24" s="31" t="n">
         <v>0.866</v>
       </c>
-      <c r="C24" s="28" t="n">
+      <c r="C24" s="31" t="n">
         <v>3.189</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D24" s="31" t="n">
         <v>0.925</v>
       </c>
-      <c r="E24" s="28" t="n">
+      <c r="E24" s="31" t="n">
         <v>0.266</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="32" t="n">
         <v>0.9359</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="32" t="n">
         <v>1.0684</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="31" t="n">
         <v>0.331</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="I24" s="31" t="n">
         <v>1.541</v>
       </c>
-      <c r="J24" s="28" t="n">
+      <c r="J24" s="31" t="n">
         <v>0.354</v>
       </c>
-      <c r="K24" s="28" t="n">
+      <c r="K24" s="31" t="n">
         <v>1.646</v>
       </c>
-      <c r="L24" s="28" t="n">
+      <c r="L24" s="31" t="n">
         <v>3.258</v>
       </c>
-      <c r="M24" s="29" t="n">
+      <c r="M24" s="32" t="n">
         <v>0.3069</v>
       </c>
-      <c r="N24" s="30" t="n">
+      <c r="N24" s="33" t="n">
         <v>0.924</v>
       </c>
-      <c r="O24" s="30" t="n">
+      <c r="O24" s="33" t="n">
         <v>5.592</v>
       </c>
-      <c r="P24" s="30" t="n">
+      <c r="P24" s="33" t="n">
         <v>0.284</v>
       </c>
-      <c r="Q24" s="30" t="n">
+      <c r="Q24" s="33" t="n">
         <v>1.716</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="n">
+      <c r="A25" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="28" t="n">
+      <c r="B25" s="31" t="n">
         <v>0.832</v>
       </c>
-      <c r="C25" s="28" t="n">
+      <c r="C25" s="31" t="n">
         <v>3.242</v>
       </c>
-      <c r="D25" s="28" t="n">
+      <c r="D25" s="31" t="n">
         <v>0.884</v>
       </c>
-      <c r="E25" s="28" t="n">
+      <c r="E25" s="31" t="n">
         <v>0.249</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="32" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="G25" s="29" t="n">
+      <c r="G25" s="32" t="n">
         <v>1.0627</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="31" t="n">
         <v>0.359</v>
       </c>
-      <c r="I25" s="28" t="n">
+      <c r="I25" s="31" t="n">
         <v>1.523</v>
       </c>
-      <c r="J25" s="28" t="n">
+      <c r="J25" s="31" t="n">
         <v>0.382</v>
       </c>
-      <c r="K25" s="28" t="n">
+      <c r="K25" s="31" t="n">
         <v>1.618</v>
       </c>
-      <c r="L25" s="28" t="n">
+      <c r="L25" s="31" t="n">
         <v>3.336</v>
       </c>
-      <c r="M25" s="29" t="n">
+      <c r="M25" s="32" t="n">
         <v>0.2998</v>
       </c>
-      <c r="N25" s="30" t="n">
+      <c r="N25" s="33" t="n">
         <v>1.026</v>
       </c>
-      <c r="O25" s="30" t="n">
+      <c r="O25" s="33" t="n">
         <v>5.646</v>
       </c>
-      <c r="P25" s="30" t="n">
+      <c r="P25" s="33" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q25" s="30" t="n">
+      <c r="Q25" s="33" t="n">
         <v>1.692</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="28" t="n">
+      <c r="B26" s="31" t="n">
         <v>0.802</v>
       </c>
-      <c r="C26" s="28" t="n">
+      <c r="C26" s="31" t="n">
         <v>3.295</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="31" t="n">
         <v>0.848</v>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="E26" s="31" t="n">
         <v>0.235</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="32" t="n">
         <v>0.9453</v>
       </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="32" t="n">
         <v>1.0579</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="31" t="n">
         <v>0.384</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="I26" s="31" t="n">
         <v>1.507</v>
       </c>
-      <c r="J26" s="28" t="n">
+      <c r="J26" s="31" t="n">
         <v>0.406</v>
       </c>
-      <c r="K26" s="28" t="n">
+      <c r="K26" s="31" t="n">
         <v>1.594</v>
       </c>
-      <c r="L26" s="28" t="n">
+      <c r="L26" s="31" t="n">
         <v>3.407</v>
       </c>
-      <c r="M26" s="29" t="n">
+      <c r="M26" s="32" t="n">
         <v>0.2935</v>
       </c>
-      <c r="N26" s="30" t="n">
+      <c r="N26" s="33" t="n">
         <v>1.121</v>
       </c>
-      <c r="O26" s="30" t="n">
+      <c r="O26" s="33" t="n">
         <v>5.693</v>
       </c>
-      <c r="P26" s="30" t="n">
+      <c r="P26" s="33" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q26" s="30" t="n">
+      <c r="Q26" s="33" t="n">
         <v>1.671</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="n">
+      <c r="A27" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="28" t="n">
+      <c r="B27" s="31" t="n">
         <v>0.775</v>
       </c>
-      <c r="C27" s="28" t="n">
+      <c r="C27" s="31" t="n">
         <v>3.347</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D27" s="31" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="E27" s="28" t="n">
+      <c r="E27" s="31" t="n">
         <v>0.223</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="32" t="n">
         <v>0.949</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="32" t="n">
         <v>1.0537</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="31" t="n">
         <v>0.406</v>
       </c>
-      <c r="I27" s="28" t="n">
+      <c r="I27" s="31" t="n">
         <v>1.492</v>
       </c>
-      <c r="J27" s="28" t="n">
+      <c r="J27" s="31" t="n">
         <v>0.428</v>
       </c>
-      <c r="K27" s="28" t="n">
+      <c r="K27" s="31" t="n">
         <v>1.572</v>
       </c>
-      <c r="L27" s="28" t="n">
+      <c r="L27" s="31" t="n">
         <v>3.472</v>
       </c>
-      <c r="M27" s="29" t="n">
+      <c r="M27" s="32" t="n">
         <v>0.288</v>
       </c>
-      <c r="N27" s="30" t="n">
+      <c r="N27" s="33" t="n">
         <v>1.207</v>
       </c>
-      <c r="O27" s="30" t="n">
+      <c r="O27" s="33" t="n">
         <v>5.737</v>
       </c>
-      <c r="P27" s="30" t="n">
+      <c r="P27" s="33" t="n">
         <v>0.348</v>
       </c>
-      <c r="Q27" s="30" t="n">
+      <c r="Q27" s="33" t="n">
         <v>1.652</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="28" t="n">
+      <c r="B28" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="28" t="n">
+      <c r="C28" s="31" t="n">
         <v>3.398</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="31" t="n">
         <v>0.788</v>
       </c>
-      <c r="E28" s="28" t="n">
+      <c r="E28" s="31" t="n">
         <v>0.212</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="32" t="n">
         <v>0.9523</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="32" t="n">
         <v>1.0501</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="31" t="n">
         <v>0.427</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="I28" s="31" t="n">
         <v>1.478</v>
       </c>
-      <c r="J28" s="28" t="n">
+      <c r="J28" s="31" t="n">
         <v>0.448</v>
       </c>
-      <c r="K28" s="28" t="n">
+      <c r="K28" s="31" t="n">
         <v>1.552</v>
       </c>
-      <c r="L28" s="28" t="n">
+      <c r="L28" s="31" t="n">
         <v>3.532</v>
       </c>
-      <c r="M28" s="29" t="n">
+      <c r="M28" s="32" t="n">
         <v>0.2831</v>
       </c>
-      <c r="N28" s="30" t="n">
+      <c r="N28" s="33" t="n">
         <v>1.285</v>
       </c>
-      <c r="O28" s="30" t="n">
+      <c r="O28" s="33" t="n">
         <v>5.779</v>
       </c>
-      <c r="P28" s="30" t="n">
+      <c r="P28" s="33" t="n">
         <v>0.364</v>
       </c>
-      <c r="Q28" s="30" t="n">
+      <c r="Q28" s="33" t="n">
         <v>1.636</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="n">
+      <c r="A29" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="28" t="n">
+      <c r="B29" s="31" t="n">
         <v>0.728</v>
       </c>
-      <c r="C29" s="28" t="n">
+      <c r="C29" s="31" t="n">
         <v>3.448</v>
       </c>
-      <c r="D29" s="28" t="n">
+      <c r="D29" s="31" t="n">
         <v>0.762</v>
       </c>
-      <c r="E29" s="28" t="n">
+      <c r="E29" s="31" t="n">
         <v>0.203</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="32" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="32" t="n">
         <v>1.047</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="31" t="n">
         <v>0.445</v>
       </c>
-      <c r="I29" s="28" t="n">
+      <c r="I29" s="31" t="n">
         <v>1.465</v>
       </c>
-      <c r="J29" s="28" t="n">
+      <c r="J29" s="31" t="n">
         <v>0.466</v>
       </c>
-      <c r="K29" s="28" t="n">
+      <c r="K29" s="31" t="n">
         <v>1.534</v>
       </c>
-      <c r="L29" s="28" t="n">
+      <c r="L29" s="31" t="n">
         <v>3.588</v>
       </c>
-      <c r="M29" s="29" t="n">
+      <c r="M29" s="32" t="n">
         <v>0.2787</v>
       </c>
-      <c r="N29" s="30" t="n">
+      <c r="N29" s="33" t="n">
         <v>1.359</v>
       </c>
-      <c r="O29" s="30" t="n">
+      <c r="O29" s="33" t="n">
         <v>5.817</v>
       </c>
-      <c r="P29" s="30" t="n">
+      <c r="P29" s="33" t="n">
         <v>0.379</v>
       </c>
-      <c r="Q29" s="30" t="n">
+      <c r="Q29" s="33" t="n">
         <v>1.621</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
+      <c r="A30" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="28" t="n">
+      <c r="B30" s="31" t="n">
         <v>0.707</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="31" t="n">
         <v>3.497</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="31" t="n">
         <v>0.738</v>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="E30" s="31" t="n">
         <v>0.194</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="32" t="n">
         <v>0.9576</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G30" s="32" t="n">
         <v>1.0442</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="31" t="n">
         <v>0.461</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="I30" s="31" t="n">
         <v>1.454</v>
       </c>
-      <c r="J30" s="28" t="n">
+      <c r="J30" s="31" t="n">
         <v>0.482</v>
       </c>
-      <c r="K30" s="28" t="n">
+      <c r="K30" s="31" t="n">
         <v>1.518</v>
       </c>
-      <c r="L30" s="28" t="n">
+      <c r="L30" s="31" t="n">
         <v>3.64</v>
       </c>
-      <c r="M30" s="29" t="n">
+      <c r="M30" s="32" t="n">
         <v>0.2747</v>
       </c>
-      <c r="N30" s="30" t="n">
+      <c r="N30" s="33" t="n">
         <v>1.426</v>
       </c>
-      <c r="O30" s="30" t="n">
+      <c r="O30" s="33" t="n">
         <v>5.854</v>
       </c>
-      <c r="P30" s="30" t="n">
+      <c r="P30" s="33" t="n">
         <v>0.392</v>
       </c>
-      <c r="Q30" s="28" t="n">
+      <c r="Q30" s="31" t="n">
         <v>1.608</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="n">
+      <c r="A31" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="28" t="n">
+      <c r="B31" s="31" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C31" s="28" t="n">
+      <c r="C31" s="31" t="n">
         <v>3.545</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="31" t="n">
         <v>0.717</v>
       </c>
-      <c r="E31" s="28" t="n">
+      <c r="E31" s="31" t="n">
         <v>0.187</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="32" t="n">
         <v>0.9599</v>
       </c>
-      <c r="G31" s="29" t="n">
+      <c r="G31" s="32" t="n">
         <v>1.0418</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="31" t="n">
         <v>0.477</v>
       </c>
-      <c r="I31" s="28" t="n">
+      <c r="I31" s="31" t="n">
         <v>1.443</v>
       </c>
-      <c r="J31" s="28" t="n">
+      <c r="J31" s="31" t="n">
         <v>0.497</v>
       </c>
-      <c r="K31" s="28" t="n">
+      <c r="K31" s="31" t="n">
         <v>1.503</v>
       </c>
-      <c r="L31" s="28" t="n">
+      <c r="L31" s="31" t="n">
         <v>3.689</v>
       </c>
-      <c r="M31" s="29" t="n">
+      <c r="M31" s="32" t="n">
         <v>0.2711</v>
       </c>
-      <c r="N31" s="30" t="n">
+      <c r="N31" s="33" t="n">
         <v>1.49</v>
       </c>
-      <c r="O31" s="30" t="n">
+      <c r="O31" s="33" t="n">
         <v>5.888</v>
       </c>
-      <c r="P31" s="30" t="n">
+      <c r="P31" s="33" t="n">
         <v>0.404</v>
       </c>
-      <c r="Q31" s="30" t="n">
+      <c r="Q31" s="33" t="n">
         <v>1.596</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n">
+      <c r="A32" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B32" s="31" t="n">
         <v>0.671</v>
       </c>
-      <c r="C32" s="28" t="n">
+      <c r="C32" s="31" t="n">
         <v>3.592</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="31" t="n">
         <v>0.697</v>
       </c>
-      <c r="E32" s="28" t="n">
+      <c r="E32" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="32" t="n">
         <v>0.9619</v>
       </c>
-      <c r="G32" s="29" t="n">
+      <c r="G32" s="32" t="n">
         <v>1.0396</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" s="31" t="n">
         <v>0.491</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="I32" s="31" t="n">
         <v>1.433</v>
       </c>
-      <c r="J32" s="28" t="n">
+      <c r="J32" s="31" t="n">
         <v>0.51</v>
       </c>
-      <c r="K32" s="28" t="n">
+      <c r="K32" s="31" t="n">
         <v>1.49</v>
       </c>
-      <c r="L32" s="28" t="n">
+      <c r="L32" s="31" t="n">
         <v>3.735</v>
       </c>
-      <c r="M32" s="29" t="n">
+      <c r="M32" s="32" t="n">
         <v>0.2677</v>
       </c>
-      <c r="N32" s="30" t="n">
+      <c r="N32" s="33" t="n">
         <v>1.548</v>
       </c>
-      <c r="O32" s="30" t="n">
+      <c r="O32" s="33" t="n">
         <v>5.922</v>
       </c>
-      <c r="P32" s="30" t="n">
+      <c r="P32" s="33" t="n">
         <v>0.414</v>
       </c>
-      <c r="Q32" s="30" t="n">
+      <c r="Q32" s="33" t="n">
         <v>1.586</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="n">
+      <c r="A33" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="31" t="n">
         <v>0.655</v>
       </c>
-      <c r="C33" s="28" t="n">
+      <c r="C33" s="31" t="n">
         <v>3.639</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="31" t="n">
         <v>0.679</v>
       </c>
-      <c r="E33" s="28" t="n">
+      <c r="E33" s="31" t="n">
         <v>0.173</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="32" t="n">
         <v>0.9638</v>
       </c>
-      <c r="G33" s="29" t="n">
+      <c r="G33" s="32" t="n">
         <v>1.0376</v>
       </c>
-      <c r="H33" s="28" t="n">
+      <c r="H33" s="31" t="n">
         <v>0.504</v>
       </c>
-      <c r="I33" s="28" t="n">
+      <c r="I33" s="31" t="n">
         <v>1.424</v>
       </c>
-      <c r="J33" s="28" t="n">
+      <c r="J33" s="31" t="n">
         <v>0.523</v>
       </c>
-      <c r="K33" s="28" t="n">
+      <c r="K33" s="31" t="n">
         <v>1.477</v>
       </c>
-      <c r="L33" s="28" t="n">
+      <c r="L33" s="31" t="n">
         <v>3.778</v>
       </c>
-      <c r="M33" s="29" t="n">
+      <c r="M33" s="32" t="n">
         <v>0.2647</v>
       </c>
-      <c r="N33" s="30" t="n">
+      <c r="N33" s="33" t="n">
         <v>1.606</v>
       </c>
-      <c r="O33" s="30" t="n">
+      <c r="O33" s="33" t="n">
         <v>5.95</v>
       </c>
-      <c r="P33" s="28" t="n">
+      <c r="P33" s="31" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q33" s="28" t="n">
+      <c r="Q33" s="31" t="n">
         <v>1.575</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n">
+      <c r="A34" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="28" t="n">
+      <c r="B34" s="31" t="n">
         <v>0.64</v>
       </c>
-      <c r="C34" s="28" t="n">
+      <c r="C34" s="31" t="n">
         <v>3.684</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D34" s="31" t="n">
         <v>0.662</v>
       </c>
-      <c r="E34" s="28" t="n">
+      <c r="E34" s="31" t="n">
         <v>0.167</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="32" t="n">
         <v>0.9655</v>
       </c>
-      <c r="G34" s="29" t="n">
+      <c r="G34" s="32" t="n">
         <v>1.0358</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H34" s="31" t="n">
         <v>0.516</v>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="I34" s="31" t="n">
         <v>1.415</v>
       </c>
-      <c r="J34" s="28" t="n">
+      <c r="J34" s="31" t="n">
         <v>0.534</v>
       </c>
-      <c r="K34" s="28" t="n">
+      <c r="K34" s="31" t="n">
         <v>1.466</v>
       </c>
-      <c r="L34" s="28" t="n">
+      <c r="L34" s="31" t="n">
         <v>3.819</v>
       </c>
-      <c r="M34" s="29" t="n">
+      <c r="M34" s="32" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N34" s="28" t="n">
+      <c r="N34" s="31" t="n">
         <v>1.659</v>
       </c>
-      <c r="O34" s="28" t="n">
+      <c r="O34" s="31" t="n">
         <v>5.979</v>
       </c>
-      <c r="P34" s="28" t="n">
+      <c r="P34" s="31" t="n">
         <v>0.434</v>
       </c>
-      <c r="Q34" s="28" t="n">
+      <c r="Q34" s="31" t="n">
         <v>1.566</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="n">
+      <c r="A35" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="28" t="n">
+      <c r="B35" s="31" t="n">
         <v>0.626</v>
       </c>
-      <c r="C35" s="28" t="n">
+      <c r="C35" s="31" t="n">
         <v>3.729</v>
       </c>
-      <c r="D35" s="28" t="n">
+      <c r="D35" s="31" t="n">
         <v>0.647</v>
       </c>
-      <c r="E35" s="28" t="n">
+      <c r="E35" s="31" t="n">
         <v>0.162</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="32" t="n">
         <v>0.967</v>
       </c>
-      <c r="G35" s="29" t="n">
+      <c r="G35" s="32" t="n">
         <v>1.0342</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="31" t="n">
         <v>0.527</v>
       </c>
-      <c r="I35" s="28" t="n">
+      <c r="I35" s="31" t="n">
         <v>1.407</v>
       </c>
-      <c r="J35" s="28" t="n">
+      <c r="J35" s="31" t="n">
         <v>0.545</v>
       </c>
-      <c r="K35" s="28" t="n">
+      <c r="K35" s="31" t="n">
         <v>1.455</v>
       </c>
-      <c r="L35" s="28" t="n">
+      <c r="L35" s="31" t="n">
         <v>3.858</v>
       </c>
-      <c r="M35" s="29" t="n">
+      <c r="M35" s="32" t="n">
         <v>0.2592</v>
       </c>
-      <c r="N35" s="28" t="n">
+      <c r="N35" s="31" t="n">
         <v>1.71</v>
       </c>
-      <c r="O35" s="28" t="n">
+      <c r="O35" s="31" t="n">
         <v>6.006</v>
       </c>
-      <c r="P35" s="28" t="n">
+      <c r="P35" s="31" t="n">
         <v>0.443</v>
       </c>
-      <c r="Q35" s="28" t="n">
+      <c r="Q35" s="31" t="n">
         <v>1.557</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n">
+      <c r="A36" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="28" t="n">
+      <c r="B36" s="31" t="n">
         <v>0.612</v>
       </c>
-      <c r="C36" s="28" t="n">
+      <c r="C36" s="31" t="n">
         <v>3.773</v>
       </c>
-      <c r="D36" s="28" t="n">
+      <c r="D36" s="31" t="n">
         <v>0.632</v>
       </c>
-      <c r="E36" s="28" t="n">
+      <c r="E36" s="31" t="n">
         <v>0.157</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="32" t="n">
         <v>0.9684</v>
       </c>
-      <c r="G36" s="29" t="n">
+      <c r="G36" s="32" t="n">
         <v>1.0327</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="31" t="n">
         <v>0.538</v>
       </c>
-      <c r="I36" s="28" t="n">
+      <c r="I36" s="31" t="n">
         <v>1.399</v>
       </c>
-      <c r="J36" s="28" t="n">
+      <c r="J36" s="31" t="n">
         <v>0.555</v>
       </c>
-      <c r="K36" s="28" t="n">
+      <c r="K36" s="31" t="n">
         <v>1.445</v>
       </c>
-      <c r="L36" s="28" t="n">
+      <c r="L36" s="31" t="n">
         <v>3.895</v>
       </c>
-      <c r="M36" s="29" t="n">
+      <c r="M36" s="32" t="n">
         <v>0.2567</v>
       </c>
-      <c r="N36" s="28" t="n">
+      <c r="N36" s="31" t="n">
         <v>1.759</v>
       </c>
-      <c r="O36" s="28" t="n">
+      <c r="O36" s="31" t="n">
         <v>6.031</v>
       </c>
-      <c r="P36" s="30" t="n">
+      <c r="P36" s="33" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q36" s="28" t="n">
+      <c r="Q36" s="31" t="n">
         <v>1.548</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="n">
+      <c r="A37" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="28" t="n">
+      <c r="B37" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="C37" s="28" t="n">
+      <c r="C37" s="31" t="n">
         <v>3.816</v>
       </c>
-      <c r="D37" s="28" t="n">
+      <c r="D37" s="31" t="n">
         <v>0.619</v>
       </c>
-      <c r="E37" s="28" t="n">
+      <c r="E37" s="31" t="n">
         <v>0.153</v>
       </c>
-      <c r="F37" s="31" t="n">
+      <c r="F37" s="34" t="n">
         <v>0.9696</v>
       </c>
-      <c r="G37" s="29" t="n">
+      <c r="G37" s="32" t="n">
         <v>1.0313</v>
       </c>
-      <c r="H37" s="28" t="n">
+      <c r="H37" s="31" t="n">
         <v>0.548</v>
       </c>
-      <c r="I37" s="28" t="n">
+      <c r="I37" s="31" t="n">
         <v>1.392</v>
       </c>
-      <c r="J37" s="28" t="n">
+      <c r="J37" s="31" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="K37" s="28" t="n">
+      <c r="K37" s="31" t="n">
         <v>1.435</v>
       </c>
-      <c r="L37" s="28" t="n">
+      <c r="L37" s="31" t="n">
         <v>3.931</v>
       </c>
-      <c r="M37" s="29" t="n">
+      <c r="M37" s="32" t="n">
         <v>0.2544</v>
       </c>
-      <c r="N37" s="30" t="n">
+      <c r="N37" s="33" t="n">
         <v>1.804</v>
       </c>
-      <c r="O37" s="30" t="n">
+      <c r="O37" s="33" t="n">
         <v>6.058</v>
       </c>
-      <c r="P37" s="28" t="n">
+      <c r="P37" s="31" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q37" s="28" t="n">
+      <c r="Q37" s="31" t="n">
         <v>1.541</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>&gt;25</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr"/>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="C38" s="35" t="inlineStr"/>
+      <c r="D38" s="35" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="E38" s="32" t="inlineStr"/>
-      <c r="F38" s="29" t="n">
+      <c r="E38" s="35" t="inlineStr"/>
+      <c r="F38" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="29" t="n">
+      <c r="G38" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="32" t="inlineStr">
+      <c r="H38" s="35" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="I38" s="32" t="inlineStr">
+      <c r="I38" s="35" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="J38" s="32" t="inlineStr">
+      <c r="J38" s="35" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="K38" s="32" t="inlineStr">
+      <c r="K38" s="35" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L38" s="32" t="inlineStr"/>
-      <c r="M38" s="32" t="inlineStr"/>
-      <c r="N38" s="32" t="inlineStr"/>
-      <c r="O38" s="32" t="inlineStr"/>
-      <c r="P38" s="32" t="inlineStr"/>
-      <c r="Q38" s="32" t="inlineStr"/>
+      <c r="L38" s="35" t="inlineStr"/>
+      <c r="M38" s="35" t="inlineStr"/>
+      <c r="N38" s="35" t="inlineStr"/>
+      <c r="O38" s="35" t="inlineStr"/>
+      <c r="P38" s="35" t="inlineStr"/>
+      <c r="Q38" s="35" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
@@ -5163,580 +7940,580 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="n">
+      <c r="A44" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="28" t="n">
+      <c r="B44" s="31" t="n">
         <v>1.128</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="32" t="n">
         <v>0.5642</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="32" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="32" t="n">
         <v>0.8525</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="n">
+      <c r="A45" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="28" t="n">
+      <c r="B45" s="31" t="n">
         <v>1.693</v>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="32" t="n">
         <v>0.7236</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="32" t="n">
         <v>0.8862</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="32" t="n">
         <v>0.8884</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="n">
+      <c r="A46" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="28" t="n">
+      <c r="B46" s="31" t="n">
         <v>2.059</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="32" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="32" t="n">
         <v>0.9213</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="32" t="n">
         <v>0.8798</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="n">
+      <c r="A47" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="28" t="n">
+      <c r="B47" s="31" t="n">
         <v>2.326</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="32" t="n">
         <v>0.8407</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="32" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="32" t="n">
         <v>0.8641</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="n">
+      <c r="A48" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="28" t="n">
+      <c r="B48" s="31" t="n">
         <v>2.534</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="32" t="n">
         <v>0.8686</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="32" t="n">
         <v>0.9515</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="32" t="n">
         <v>0.848</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="n">
+      <c r="A49" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="28" t="n">
+      <c r="B49" s="31" t="n">
         <v>2.704</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="32" t="n">
         <v>0.8882</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="32" t="n">
         <v>0.9594</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="32" t="n">
         <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="n">
+      <c r="A50" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="28" t="n">
+      <c r="B50" s="31" t="n">
         <v>2.847</v>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="32" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="32" t="n">
         <v>0.965</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="32" t="n">
         <v>0.8198</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="n">
+      <c r="A51" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="28" t="n">
+      <c r="B51" s="31" t="n">
         <v>2.97</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="32" t="n">
         <v>0.9139</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="32" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="32" t="n">
         <v>0.8078</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="n">
+      <c r="A52" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="28" t="n">
+      <c r="B52" s="31" t="n">
         <v>3.078</v>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="32" t="n">
         <v>0.9227</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="32" t="n">
         <v>0.9727</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="32" t="n">
         <v>0.7971</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="n">
+      <c r="A53" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="28" t="n">
+      <c r="B53" s="31" t="n">
         <v>3.173</v>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="32" t="n">
         <v>0.93</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="32" t="n">
         <v>0.9754</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="32" t="n">
         <v>0.7873</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="n">
+      <c r="A54" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="28" t="n">
+      <c r="B54" s="31" t="n">
         <v>3.258</v>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="32" t="n">
         <v>0.9359</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="32" t="n">
         <v>0.9776</v>
       </c>
-      <c r="E54" s="31" t="n">
+      <c r="E54" s="34" t="n">
         <v>0.7785</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="n">
+      <c r="A55" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="28" t="n">
+      <c r="B55" s="31" t="n">
         <v>3.336</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="32" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="32" t="n">
         <v>0.9794</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="32" t="n">
         <v>0.7704</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="27" t="n">
+      <c r="A56" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="28" t="n">
+      <c r="B56" s="31" t="n">
         <v>3.407</v>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="32" t="n">
         <v>0.9453</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="32" t="n">
         <v>0.981</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="32" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27" t="n">
+      <c r="A57" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="28" t="n">
+      <c r="B57" s="31" t="n">
         <v>3.472</v>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="32" t="n">
         <v>0.949</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="32" t="n">
         <v>0.9823</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="32" t="n">
         <v>0.7562</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="27" t="n">
+      <c r="A58" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B58" s="28" t="n">
+      <c r="B58" s="31" t="n">
         <v>3.532</v>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="32" t="n">
         <v>0.9523</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="32" t="n">
         <v>0.9835</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="32" t="n">
         <v>0.7499</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27" t="n">
+      <c r="A59" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B59" s="28" t="n">
+      <c r="B59" s="31" t="n">
         <v>3.588</v>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="32" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="32" t="n">
         <v>0.9845</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="32" t="n">
         <v>0.7441</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="27" t="n">
+      <c r="A60" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B60" s="28" t="n">
+      <c r="B60" s="31" t="n">
         <v>3.64</v>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="32" t="n">
         <v>0.9576</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="32" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="32" t="n">
         <v>0.7386</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="27" t="n">
+      <c r="A61" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B61" s="28" t="n">
+      <c r="B61" s="31" t="n">
         <v>3.689</v>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="32" t="n">
         <v>0.9599</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="32" t="n">
         <v>0.9862</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="32" t="n">
         <v>0.7335</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="27" t="n">
+      <c r="A62" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B62" s="28" t="n">
+      <c r="B62" s="31" t="n">
         <v>3.735</v>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="32" t="n">
         <v>0.9619</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="32" t="n">
         <v>0.9869</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="32" t="n">
         <v>0.7287</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="n">
+      <c r="A63" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="28" t="n">
+      <c r="B63" s="31" t="n">
         <v>3.778</v>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="32" t="n">
         <v>0.9638</v>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="32" t="n">
         <v>0.9876</v>
       </c>
-      <c r="E63" s="31" t="n">
+      <c r="E63" s="34" t="n">
         <v>0.7272</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="27" t="n">
+      <c r="A64" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B64" s="28" t="n">
+      <c r="B64" s="31" t="n">
         <v>3.819</v>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="32" t="n">
         <v>0.9655</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="32" t="n">
         <v>0.9882</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="32" t="n">
         <v>0.7199</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="n">
+      <c r="A65" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="28" t="n">
+      <c r="B65" s="31" t="n">
         <v>3.858</v>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="32" t="n">
         <v>0.967</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="32" t="n">
         <v>0.9887</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="32" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="27" t="n">
+      <c r="A66" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="28" t="n">
+      <c r="B66" s="31" t="n">
         <v>3.895</v>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="32" t="n">
         <v>0.9684</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="32" t="n">
         <v>0.9892</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="32" t="n">
         <v>0.7121</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="27" t="n">
+      <c r="A67" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B67" s="28" t="n">
+      <c r="B67" s="31" t="n">
         <v>3.931</v>
       </c>
-      <c r="C67" s="31" t="n">
+      <c r="C67" s="34" t="n">
         <v>0.9695</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="32" t="n">
         <v>0.9896</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="32" t="n">
         <v>0.7084</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="27" t="n">
+      <c r="A68" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="B68" s="28" t="n">
+      <c r="B68" s="31" t="n">
         <v>4.086</v>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="32" t="n">
         <v>0.9748</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="32" t="n">
         <v>0.9915</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="32" t="n">
         <v>0.6927</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="27" t="n">
+      <c r="A69" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="B69" s="28" t="n">
+      <c r="B69" s="31" t="n">
         <v>4.213</v>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="32" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D69" s="29" t="n">
+      <c r="D69" s="32" t="n">
         <v>0.9927</v>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="32" t="n">
         <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27" t="n">
+      <c r="A70" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="B70" s="28" t="n">
+      <c r="B70" s="31" t="n">
         <v>4.322</v>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="32" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D70" s="32" t="n">
         <v>0.9936</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="32" t="n">
         <v>0.6692</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27" t="n">
+      <c r="A71" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="B71" s="28" t="n">
+      <c r="B71" s="31" t="n">
         <v>4.415</v>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="32" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="32" t="n">
         <v>0.9943</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="32" t="n">
         <v>0.6601</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="27" t="n">
+      <c r="A72" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="B72" s="28" t="n">
+      <c r="B72" s="31" t="n">
         <v>4.498</v>
       </c>
-      <c r="C72" s="29" t="n">
+      <c r="C72" s="32" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D72" s="29" t="n">
+      <c r="D72" s="32" t="n">
         <v>0.9949</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="32" t="n">
         <v>0.6521</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="27" t="n">
+      <c r="A73" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="B73" s="28" t="n">
+      <c r="B73" s="31" t="n">
         <v>4.639</v>
       </c>
-      <c r="C73" s="29" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D73" s="29" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.9957</v>
       </c>
-      <c r="E73" s="29" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.6389</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="27" t="n">
+      <c r="A74" s="30" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="28" t="n">
+      <c r="B74" s="31" t="n">
         <v>4.755</v>
       </c>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.9892</v>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.9963</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.6283</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="27" t="n">
+      <c r="A75" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="B75" s="28" t="n">
+      <c r="B75" s="31" t="n">
         <v>4.854</v>
       </c>
-      <c r="C75" s="29" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.9906</v>
       </c>
-      <c r="D75" s="29" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.9968</v>
       </c>
-      <c r="E75" s="29" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.6194</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="27" t="n">
+      <c r="A76" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="B76" s="28" t="n">
+      <c r="B76" s="31" t="n">
         <v>4.939</v>
       </c>
-      <c r="C76" s="29" t="n">
+      <c r="C76" s="32" t="n">
         <v>0.9916</v>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="32" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="32" t="n">
         <v>0.6118</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27" t="n">
+      <c r="A77" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="B77" s="28" t="n">
+      <c r="B77" s="31" t="n">
         <v>5.015</v>
       </c>
-      <c r="C77" s="29" t="n">
+      <c r="C77" s="32" t="n">
         <v>0.9925</v>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="32" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="E77" s="29" t="n">
+      <c r="E77" s="32" t="n">
         <v>0.6052</v>
       </c>
     </row>
@@ -5814,786 +8591,786 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="27" t="n">
+      <c r="A83" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="28" t="n">
+      <c r="B83" s="31" t="n">
         <v>2.121</v>
       </c>
-      <c r="C83" s="28" t="n">
+      <c r="C83" s="31" t="n">
         <v>1.88</v>
       </c>
-      <c r="D83" s="28" t="n">
+      <c r="D83" s="31" t="n">
         <v>2.659</v>
       </c>
-      <c r="E83" s="29" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="F83" s="29" t="n">
+      <c r="F83" s="32" t="n">
         <v>1.2533</v>
       </c>
-      <c r="G83" s="27" t="n">
+      <c r="G83" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="28" t="n">
+      <c r="H83" s="31" t="n">
         <v>3.267</v>
       </c>
-      <c r="I83" s="27" t="n">
+      <c r="I83" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="28" t="n">
+      <c r="J83" s="31" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27" t="n">
+      <c r="A84" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="B84" s="28" t="n">
+      <c r="B84" s="31" t="n">
         <v>2.606</v>
       </c>
-      <c r="C84" s="32" t="inlineStr"/>
-      <c r="D84" s="32" t="inlineStr"/>
-      <c r="E84" s="32" t="inlineStr"/>
-      <c r="F84" s="32" t="inlineStr"/>
-      <c r="G84" s="32" t="inlineStr"/>
-      <c r="H84" s="32" t="inlineStr"/>
-      <c r="I84" s="32" t="inlineStr"/>
-      <c r="J84" s="32" t="inlineStr"/>
+      <c r="C84" s="35" t="inlineStr"/>
+      <c r="D84" s="35" t="inlineStr"/>
+      <c r="E84" s="35" t="inlineStr"/>
+      <c r="F84" s="35" t="inlineStr"/>
+      <c r="G84" s="35" t="inlineStr"/>
+      <c r="H84" s="35" t="inlineStr"/>
+      <c r="I84" s="35" t="inlineStr"/>
+      <c r="J84" s="35" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="27" t="n">
+      <c r="A85" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="28" t="n">
+      <c r="B85" s="31" t="n">
         <v>1.732</v>
       </c>
-      <c r="C85" s="28" t="n">
+      <c r="C85" s="31" t="n">
         <v>1.023</v>
       </c>
-      <c r="D85" s="28" t="n">
+      <c r="D85" s="31" t="n">
         <v>1.954</v>
       </c>
-      <c r="E85" s="29" t="n">
+      <c r="E85" s="32" t="n">
         <v>0.8862</v>
       </c>
-      <c r="F85" s="29" t="n">
+      <c r="F85" s="32" t="n">
         <v>1.1284</v>
       </c>
-      <c r="G85" s="27" t="n">
+      <c r="G85" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="28" t="n">
+      <c r="H85" s="31" t="n">
         <v>2.568</v>
       </c>
-      <c r="I85" s="27" t="n">
+      <c r="I85" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="28" t="n">
+      <c r="J85" s="31" t="n">
         <v>2.276</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="27" t="n">
+      <c r="A86" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="28" t="n">
+      <c r="B86" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="C86" s="28" t="n">
+      <c r="C86" s="31" t="n">
         <v>0.729</v>
       </c>
-      <c r="D86" s="28" t="n">
+      <c r="D86" s="31" t="n">
         <v>1.628</v>
       </c>
-      <c r="E86" s="29" t="n">
+      <c r="E86" s="32" t="n">
         <v>0.9213</v>
       </c>
-      <c r="F86" s="29" t="n">
+      <c r="F86" s="32" t="n">
         <v>1.0854</v>
       </c>
-      <c r="G86" s="27" t="n">
+      <c r="G86" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="28" t="n">
+      <c r="H86" s="31" t="n">
         <v>2.266</v>
       </c>
-      <c r="I86" s="27" t="n">
+      <c r="I86" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="28" t="n">
+      <c r="J86" s="31" t="n">
         <v>2.088</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="27" t="n">
+      <c r="A87" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="28" t="n">
+      <c r="B87" s="31" t="n">
         <v>1.342</v>
       </c>
-      <c r="C87" s="28" t="n">
+      <c r="C87" s="31" t="n">
         <v>0.577</v>
       </c>
-      <c r="D87" s="28" t="n">
+      <c r="D87" s="31" t="n">
         <v>1.427</v>
       </c>
-      <c r="E87" s="29" t="n">
+      <c r="E87" s="32" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F87" s="29" t="n">
+      <c r="F87" s="32" t="n">
         <v>1.0638</v>
       </c>
-      <c r="G87" s="27" t="n">
+      <c r="G87" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="28" t="n">
+      <c r="H87" s="31" t="n">
         <v>2.089</v>
       </c>
-      <c r="I87" s="27" t="n">
+      <c r="I87" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="28" t="n">
+      <c r="J87" s="31" t="n">
         <v>1.964</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27" t="n">
+      <c r="A88" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B88" s="28" t="n">
+      <c r="B88" s="31" t="n">
         <v>1.225</v>
       </c>
-      <c r="C88" s="28" t="n">
+      <c r="C88" s="31" t="n">
         <v>0.483</v>
       </c>
-      <c r="D88" s="28" t="n">
+      <c r="D88" s="31" t="n">
         <v>1.287</v>
       </c>
-      <c r="E88" s="29" t="n">
+      <c r="E88" s="32" t="n">
         <v>0.9515</v>
       </c>
-      <c r="F88" s="29" t="n">
+      <c r="F88" s="32" t="n">
         <v>1.051</v>
       </c>
-      <c r="G88" s="28" t="n">
+      <c r="G88" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="H88" s="28" t="n">
+      <c r="H88" s="31" t="n">
         <v>1.97</v>
       </c>
-      <c r="I88" s="28" t="n">
+      <c r="I88" s="31" t="n">
         <v>0.029</v>
       </c>
-      <c r="J88" s="28" t="n">
+      <c r="J88" s="31" t="n">
         <v>1.874</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="27" t="n">
+      <c r="A89" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B89" s="28" t="n">
+      <c r="B89" s="31" t="n">
         <v>1.134</v>
       </c>
-      <c r="C89" s="28" t="n">
+      <c r="C89" s="31" t="n">
         <v>0.419</v>
       </c>
-      <c r="D89" s="28" t="n">
+      <c r="D89" s="31" t="n">
         <v>1.182</v>
       </c>
-      <c r="E89" s="29" t="n">
+      <c r="E89" s="32" t="n">
         <v>0.9594</v>
       </c>
-      <c r="F89" s="29" t="n">
+      <c r="F89" s="32" t="n">
         <v>1.0423</v>
       </c>
-      <c r="G89" s="28" t="n">
+      <c r="G89" s="31" t="n">
         <v>0.118</v>
       </c>
-      <c r="H89" s="28" t="n">
+      <c r="H89" s="31" t="n">
         <v>1.882</v>
       </c>
-      <c r="I89" s="28" t="n">
+      <c r="I89" s="31" t="n">
         <v>0.113</v>
       </c>
-      <c r="J89" s="28" t="n">
+      <c r="J89" s="31" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="27" t="n">
+      <c r="A90" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="28" t="n">
+      <c r="B90" s="31" t="n">
         <v>1.061</v>
       </c>
-      <c r="C90" s="28" t="n">
+      <c r="C90" s="31" t="n">
         <v>0.373</v>
       </c>
-      <c r="D90" s="28" t="n">
+      <c r="D90" s="31" t="n">
         <v>1.099</v>
       </c>
-      <c r="E90" s="29" t="n">
+      <c r="E90" s="32" t="n">
         <v>0.965</v>
       </c>
-      <c r="F90" s="29" t="n">
+      <c r="F90" s="32" t="n">
         <v>1.0363</v>
       </c>
-      <c r="G90" s="28" t="n">
+      <c r="G90" s="31" t="n">
         <v>0.185</v>
       </c>
-      <c r="H90" s="28" t="n">
+      <c r="H90" s="31" t="n">
         <v>1.815</v>
       </c>
-      <c r="I90" s="28" t="n">
+      <c r="I90" s="31" t="n">
         <v>0.179</v>
       </c>
-      <c r="J90" s="28" t="n">
+      <c r="J90" s="31" t="n">
         <v>1.751</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="27" t="n">
+      <c r="A91" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="28" t="n">
+      <c r="B91" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="28" t="n">
+      <c r="C91" s="31" t="n">
         <v>0.337</v>
       </c>
-      <c r="D91" s="28" t="n">
+      <c r="D91" s="31" t="n">
         <v>1.032</v>
       </c>
-      <c r="E91" s="29" t="n">
+      <c r="E91" s="32" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="F91" s="29" t="n">
+      <c r="F91" s="32" t="n">
         <v>1.0317</v>
       </c>
-      <c r="G91" s="28" t="n">
+      <c r="G91" s="31" t="n">
         <v>0.239</v>
       </c>
-      <c r="H91" s="28" t="n">
+      <c r="H91" s="31" t="n">
         <v>1.761</v>
       </c>
-      <c r="I91" s="28" t="n">
+      <c r="I91" s="31" t="n">
         <v>0.232</v>
       </c>
-      <c r="J91" s="28" t="n">
+      <c r="J91" s="31" t="n">
         <v>1.707</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="27" t="n">
+      <c r="A92" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B92" s="28" t="n">
+      <c r="B92" s="31" t="n">
         <v>0.949</v>
       </c>
-      <c r="C92" s="28" t="n">
+      <c r="C92" s="31" t="n">
         <v>0.308</v>
       </c>
-      <c r="D92" s="28" t="n">
+      <c r="D92" s="31" t="n">
         <v>0.975</v>
       </c>
-      <c r="E92" s="29" t="n">
+      <c r="E92" s="32" t="n">
         <v>0.9727</v>
       </c>
-      <c r="F92" s="29" t="n">
+      <c r="F92" s="32" t="n">
         <v>1.0281</v>
       </c>
-      <c r="G92" s="28" t="n">
+      <c r="G92" s="31" t="n">
         <v>0.284</v>
       </c>
-      <c r="H92" s="28" t="n">
+      <c r="H92" s="31" t="n">
         <v>1.716</v>
       </c>
-      <c r="I92" s="28" t="n">
+      <c r="I92" s="31" t="n">
         <v>0.276</v>
       </c>
-      <c r="J92" s="28" t="n">
+      <c r="J92" s="31" t="n">
         <v>1.669</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27" t="n">
+      <c r="A93" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B93" s="28" t="n">
+      <c r="B93" s="31" t="n">
         <v>0.905</v>
       </c>
-      <c r="C93" s="28" t="n">
+      <c r="C93" s="31" t="n">
         <v>0.285</v>
       </c>
-      <c r="D93" s="28" t="n">
+      <c r="D93" s="31" t="n">
         <v>0.927</v>
       </c>
-      <c r="E93" s="29" t="n">
+      <c r="E93" s="32" t="n">
         <v>0.9754</v>
       </c>
-      <c r="F93" s="29" t="n">
+      <c r="F93" s="32" t="n">
         <v>1.0252</v>
       </c>
-      <c r="G93" s="28" t="n">
+      <c r="G93" s="31" t="n">
         <v>0.321</v>
       </c>
-      <c r="H93" s="28" t="n">
+      <c r="H93" s="31" t="n">
         <v>1.679</v>
       </c>
-      <c r="I93" s="28" t="n">
+      <c r="I93" s="31" t="n">
         <v>0.313</v>
       </c>
-      <c r="J93" s="28" t="n">
+      <c r="J93" s="31" t="n">
         <v>1.637</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27" t="n">
+      <c r="A94" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B94" s="28" t="n">
+      <c r="B94" s="31" t="n">
         <v>0.866</v>
       </c>
-      <c r="C94" s="28" t="n">
+      <c r="C94" s="31" t="n">
         <v>0.266</v>
       </c>
-      <c r="D94" s="28" t="n">
+      <c r="D94" s="31" t="n">
         <v>0.886</v>
       </c>
-      <c r="E94" s="29" t="n">
+      <c r="E94" s="32" t="n">
         <v>0.9776</v>
       </c>
-      <c r="F94" s="29" t="n">
+      <c r="F94" s="32" t="n">
         <v>1.0229</v>
       </c>
-      <c r="G94" s="28" t="n">
+      <c r="G94" s="31" t="n">
         <v>0.354</v>
       </c>
-      <c r="H94" s="28" t="n">
+      <c r="H94" s="31" t="n">
         <v>1.646</v>
       </c>
-      <c r="I94" s="28" t="n">
+      <c r="I94" s="31" t="n">
         <v>0.346</v>
       </c>
-      <c r="J94" s="28" t="n">
+      <c r="J94" s="31" t="n">
         <v>1.61</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27" t="n">
+      <c r="A95" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B95" s="28" t="n">
+      <c r="B95" s="31" t="n">
         <v>0.832</v>
       </c>
-      <c r="C95" s="28" t="n">
+      <c r="C95" s="31" t="n">
         <v>0.249</v>
       </c>
-      <c r="D95" s="28" t="n">
+      <c r="D95" s="31" t="n">
         <v>0.85</v>
       </c>
-      <c r="E95" s="29" t="n">
+      <c r="E95" s="32" t="n">
         <v>0.9794</v>
       </c>
-      <c r="F95" s="29" t="n">
+      <c r="F95" s="32" t="n">
         <v>1.021</v>
       </c>
-      <c r="G95" s="28" t="n">
+      <c r="G95" s="31" t="n">
         <v>0.382</v>
       </c>
-      <c r="H95" s="28" t="n">
+      <c r="H95" s="31" t="n">
         <v>1.618</v>
       </c>
-      <c r="I95" s="28" t="n">
+      <c r="I95" s="31" t="n">
         <v>0.374</v>
       </c>
-      <c r="J95" s="28" t="n">
+      <c r="J95" s="31" t="n">
         <v>1.585</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27" t="n">
+      <c r="A96" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B96" s="28" t="n">
+      <c r="B96" s="31" t="n">
         <v>0.802</v>
       </c>
-      <c r="C96" s="28" t="n">
+      <c r="C96" s="31" t="n">
         <v>0.235</v>
       </c>
-      <c r="D96" s="28" t="n">
+      <c r="D96" s="31" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E96" s="29" t="n">
+      <c r="E96" s="32" t="n">
         <v>0.981</v>
       </c>
-      <c r="F96" s="29" t="n">
+      <c r="F96" s="32" t="n">
         <v>1.0194</v>
       </c>
-      <c r="G96" s="28" t="n">
+      <c r="G96" s="31" t="n">
         <v>0.406</v>
       </c>
-      <c r="H96" s="28" t="n">
+      <c r="H96" s="31" t="n">
         <v>1.594</v>
       </c>
-      <c r="I96" s="28" t="n">
+      <c r="I96" s="31" t="n">
         <v>0.399</v>
       </c>
-      <c r="J96" s="28" t="n">
+      <c r="J96" s="31" t="n">
         <v>1.563</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="27" t="n">
+      <c r="A97" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B97" s="28" t="n">
+      <c r="B97" s="31" t="n">
         <v>0.775</v>
       </c>
-      <c r="C97" s="28" t="n">
+      <c r="C97" s="31" t="n">
         <v>0.223</v>
       </c>
-      <c r="D97" s="28" t="n">
+      <c r="D97" s="31" t="n">
         <v>0.789</v>
       </c>
-      <c r="E97" s="29" t="n">
+      <c r="E97" s="32" t="n">
         <v>0.9823</v>
       </c>
-      <c r="F97" s="29" t="n">
+      <c r="F97" s="32" t="n">
         <v>1.018</v>
       </c>
-      <c r="G97" s="28" t="n">
+      <c r="G97" s="31" t="n">
         <v>0.428</v>
       </c>
-      <c r="H97" s="28" t="n">
+      <c r="H97" s="31" t="n">
         <v>1.572</v>
       </c>
-      <c r="I97" s="28" t="n">
+      <c r="I97" s="31" t="n">
         <v>0.421</v>
       </c>
-      <c r="J97" s="28" t="n">
+      <c r="J97" s="31" t="n">
         <v>1.544</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="27" t="n">
+      <c r="A98" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B98" s="28" t="n">
+      <c r="B98" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="C98" s="28" t="n">
+      <c r="C98" s="31" t="n">
         <v>0.212</v>
       </c>
-      <c r="D98" s="28" t="n">
+      <c r="D98" s="31" t="n">
         <v>0.763</v>
       </c>
-      <c r="E98" s="29" t="n">
+      <c r="E98" s="32" t="n">
         <v>0.9835</v>
       </c>
-      <c r="F98" s="29" t="n">
+      <c r="F98" s="32" t="n">
         <v>1.0168</v>
       </c>
-      <c r="G98" s="28" t="n">
+      <c r="G98" s="31" t="n">
         <v>0.448</v>
       </c>
-      <c r="H98" s="28" t="n">
+      <c r="H98" s="31" t="n">
         <v>1.552</v>
       </c>
-      <c r="I98" s="28" t="n">
+      <c r="I98" s="31" t="n">
         <v>0.44</v>
       </c>
-      <c r="J98" s="28" t="n">
+      <c r="J98" s="31" t="n">
         <v>1.526</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="27" t="n">
+      <c r="A99" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="28" t="n">
+      <c r="B99" s="31" t="n">
         <v>0.728</v>
       </c>
-      <c r="C99" s="28" t="n">
+      <c r="C99" s="31" t="n">
         <v>0.203</v>
       </c>
-      <c r="D99" s="28" t="n">
+      <c r="D99" s="31" t="n">
         <v>0.739</v>
       </c>
-      <c r="E99" s="29" t="n">
+      <c r="E99" s="32" t="n">
         <v>0.9845</v>
       </c>
-      <c r="F99" s="29" t="n">
+      <c r="F99" s="32" t="n">
         <v>1.0157</v>
       </c>
-      <c r="G99" s="28" t="n">
+      <c r="G99" s="31" t="n">
         <v>0.466</v>
       </c>
-      <c r="H99" s="28" t="n">
+      <c r="H99" s="31" t="n">
         <v>1.534</v>
       </c>
-      <c r="I99" s="28" t="n">
+      <c r="I99" s="31" t="n">
         <v>0.458</v>
       </c>
-      <c r="J99" s="28" t="n">
+      <c r="J99" s="31" t="n">
         <v>1.511</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="27" t="n">
+      <c r="A100" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B100" s="28" t="n">
+      <c r="B100" s="31" t="n">
         <v>0.707</v>
       </c>
-      <c r="C100" s="28" t="n">
+      <c r="C100" s="31" t="n">
         <v>0.194</v>
       </c>
-      <c r="D100" s="28" t="n">
+      <c r="D100" s="31" t="n">
         <v>0.718</v>
       </c>
-      <c r="E100" s="29" t="n">
+      <c r="E100" s="32" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="F100" s="29" t="n">
+      <c r="F100" s="32" t="n">
         <v>1.0148</v>
       </c>
-      <c r="G100" s="28" t="n">
+      <c r="G100" s="31" t="n">
         <v>0.482</v>
       </c>
-      <c r="H100" s="28" t="n">
+      <c r="H100" s="31" t="n">
         <v>1.518</v>
       </c>
-      <c r="I100" s="28" t="n">
+      <c r="I100" s="31" t="n">
         <v>0.475</v>
       </c>
-      <c r="J100" s="28" t="n">
+      <c r="J100" s="31" t="n">
         <v>1.496</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="27" t="n">
+      <c r="A101" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B101" s="28" t="n">
+      <c r="B101" s="31" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C101" s="28" t="n">
+      <c r="C101" s="31" t="n">
         <v>0.187</v>
       </c>
-      <c r="D101" s="28" t="n">
+      <c r="D101" s="31" t="n">
         <v>0.698</v>
       </c>
-      <c r="E101" s="29" t="n">
+      <c r="E101" s="32" t="n">
         <v>0.9862</v>
       </c>
-      <c r="F101" s="29" t="n">
+      <c r="F101" s="32" t="n">
         <v>1.014</v>
       </c>
-      <c r="G101" s="28" t="n">
+      <c r="G101" s="31" t="n">
         <v>0.497</v>
       </c>
-      <c r="H101" s="28" t="n">
+      <c r="H101" s="31" t="n">
         <v>1.503</v>
       </c>
-      <c r="I101" s="28" t="n">
+      <c r="I101" s="31" t="n">
         <v>0.49</v>
       </c>
-      <c r="J101" s="28" t="n">
+      <c r="J101" s="31" t="n">
         <v>1.483</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27" t="n">
+      <c r="A102" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B102" s="28" t="n">
+      <c r="B102" s="31" t="n">
         <v>0.671</v>
       </c>
-      <c r="C102" s="28" t="n">
+      <c r="C102" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="D102" s="28" t="n">
+      <c r="D102" s="31" t="n">
         <v>0.68</v>
       </c>
-      <c r="E102" s="29" t="n">
+      <c r="E102" s="32" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F102" s="29" t="n">
+      <c r="F102" s="32" t="n">
         <v>1.0133</v>
       </c>
-      <c r="G102" s="28" t="n">
+      <c r="G102" s="31" t="n">
         <v>0.51</v>
       </c>
-      <c r="H102" s="28" t="n">
+      <c r="H102" s="31" t="n">
         <v>1.49</v>
       </c>
-      <c r="I102" s="28" t="n">
+      <c r="I102" s="31" t="n">
         <v>0.504</v>
       </c>
-      <c r="J102" s="28" t="n">
+      <c r="J102" s="31" t="n">
         <v>1.47</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="27" t="n">
+      <c r="A103" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B103" s="28" t="n">
+      <c r="B103" s="31" t="n">
         <v>0.655</v>
       </c>
-      <c r="C103" s="28" t="n">
+      <c r="C103" s="31" t="n">
         <v>0.173</v>
       </c>
-      <c r="D103" s="28" t="n">
+      <c r="D103" s="31" t="n">
         <v>0.663</v>
       </c>
-      <c r="E103" s="29" t="n">
+      <c r="E103" s="32" t="n">
         <v>0.9876</v>
       </c>
-      <c r="F103" s="29" t="n">
+      <c r="F103" s="32" t="n">
         <v>1.0126</v>
       </c>
-      <c r="G103" s="28" t="n">
+      <c r="G103" s="31" t="n">
         <v>0.523</v>
       </c>
-      <c r="H103" s="28" t="n">
+      <c r="H103" s="31" t="n">
         <v>1.477</v>
       </c>
-      <c r="I103" s="28" t="n">
+      <c r="I103" s="31" t="n">
         <v>0.516</v>
       </c>
-      <c r="J103" s="28" t="n">
+      <c r="J103" s="31" t="n">
         <v>1.459</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="27" t="n">
+      <c r="A104" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B104" s="28" t="n">
+      <c r="B104" s="31" t="n">
         <v>0.64</v>
       </c>
-      <c r="C104" s="28" t="n">
+      <c r="C104" s="31" t="n">
         <v>0.167</v>
       </c>
-      <c r="D104" s="28" t="n">
+      <c r="D104" s="31" t="n">
         <v>0.647</v>
       </c>
-      <c r="E104" s="29" t="n">
+      <c r="E104" s="32" t="n">
         <v>0.9882</v>
       </c>
-      <c r="F104" s="29" t="n">
+      <c r="F104" s="32" t="n">
         <v>1.0119</v>
       </c>
-      <c r="G104" s="28" t="n">
+      <c r="G104" s="31" t="n">
         <v>0.534</v>
       </c>
-      <c r="H104" s="28" t="n">
+      <c r="H104" s="31" t="n">
         <v>1.466</v>
       </c>
-      <c r="I104" s="28" t="n">
+      <c r="I104" s="31" t="n">
         <v>0.528</v>
       </c>
-      <c r="J104" s="28" t="n">
+      <c r="J104" s="31" t="n">
         <v>1.448</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="27" t="n">
+      <c r="A105" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B105" s="28" t="n">
+      <c r="B105" s="31" t="n">
         <v>0.626</v>
       </c>
-      <c r="C105" s="28" t="n">
+      <c r="C105" s="31" t="n">
         <v>0.162</v>
       </c>
-      <c r="D105" s="28" t="n">
+      <c r="D105" s="31" t="n">
         <v>0.633</v>
       </c>
-      <c r="E105" s="29" t="n">
+      <c r="E105" s="32" t="n">
         <v>0.9887</v>
       </c>
-      <c r="F105" s="29" t="n">
+      <c r="F105" s="32" t="n">
         <v>1.0114</v>
       </c>
-      <c r="G105" s="28" t="n">
+      <c r="G105" s="31" t="n">
         <v>0.545</v>
       </c>
-      <c r="H105" s="28" t="n">
+      <c r="H105" s="31" t="n">
         <v>1.455</v>
       </c>
-      <c r="I105" s="28" t="n">
+      <c r="I105" s="31" t="n">
         <v>0.539</v>
       </c>
-      <c r="J105" s="28" t="n">
+      <c r="J105" s="31" t="n">
         <v>1.438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="27" t="n">
+      <c r="A106" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B106" s="28" t="n">
+      <c r="B106" s="31" t="n">
         <v>0.612</v>
       </c>
-      <c r="C106" s="28" t="n">
+      <c r="C106" s="31" t="n">
         <v>0.157</v>
       </c>
-      <c r="D106" s="28" t="n">
+      <c r="D106" s="31" t="n">
         <v>0.619</v>
       </c>
-      <c r="E106" s="29" t="n">
+      <c r="E106" s="32" t="n">
         <v>0.9892</v>
       </c>
-      <c r="F106" s="29" t="n">
+      <c r="F106" s="32" t="n">
         <v>1.0109</v>
       </c>
-      <c r="G106" s="28" t="n">
+      <c r="G106" s="31" t="n">
         <v>0.555</v>
       </c>
-      <c r="H106" s="28" t="n">
+      <c r="H106" s="31" t="n">
         <v>1.445</v>
       </c>
-      <c r="I106" s="28" t="n">
+      <c r="I106" s="31" t="n">
         <v>0.549</v>
       </c>
-      <c r="J106" s="28" t="n">
+      <c r="J106" s="31" t="n">
         <v>1.429</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="27" t="n">
+      <c r="A107" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B107" s="28" t="n">
+      <c r="B107" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="C107" s="28" t="n">
+      <c r="C107" s="31" t="n">
         <v>0.153</v>
       </c>
-      <c r="D107" s="28" t="n">
+      <c r="D107" s="31" t="n">
         <v>0.606</v>
       </c>
-      <c r="E107" s="29" t="n">
+      <c r="E107" s="32" t="n">
         <v>0.9896</v>
       </c>
-      <c r="F107" s="29" t="n">
+      <c r="F107" s="32" t="n">
         <v>1.0105</v>
       </c>
-      <c r="G107" s="28" t="n">
+      <c r="G107" s="31" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H107" s="28" t="n">
+      <c r="H107" s="31" t="n">
         <v>1.435</v>
       </c>
-      <c r="I107" s="28" t="n">
+      <c r="I107" s="31" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J107" s="28" t="n">
+      <c r="J107" s="31" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -6666,698 +9443,698 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="27" t="n">
+      <c r="A113" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="28" t="n">
+      <c r="B113" s="31" t="n">
         <v>1.128</v>
       </c>
-      <c r="C113" s="29" t="n">
+      <c r="C113" s="32" t="n">
         <v>0.8865</v>
       </c>
-      <c r="D113" s="28" t="n">
+      <c r="D113" s="31" t="n">
         <v>0.853</v>
       </c>
-      <c r="E113" s="27" t="n">
+      <c r="E113" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="28" t="n">
+      <c r="F113" s="31" t="n">
         <v>3.686</v>
       </c>
-      <c r="G113" s="27" t="n">
+      <c r="G113" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="28" t="n">
+      <c r="H113" s="31" t="n">
         <v>3.267</v>
       </c>
-      <c r="I113" s="30" t="n">
+      <c r="I113" s="33" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="27" t="n">
+      <c r="A114" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="28" t="n">
+      <c r="B114" s="31" t="n">
         <v>1.693</v>
       </c>
-      <c r="C114" s="29" t="n">
+      <c r="C114" s="32" t="n">
         <v>0.5907</v>
       </c>
-      <c r="D114" s="28" t="n">
+      <c r="D114" s="31" t="n">
         <v>0.888</v>
       </c>
-      <c r="E114" s="27" t="n">
+      <c r="E114" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="28" t="n">
+      <c r="F114" s="31" t="n">
         <v>4.358</v>
       </c>
-      <c r="G114" s="27" t="n">
+      <c r="G114" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="30" t="n">
+      <c r="H114" s="33" t="n">
         <v>2.574</v>
       </c>
-      <c r="I114" s="28" t="n">
+      <c r="I114" s="31" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="27" t="n">
+      <c r="A115" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B115" s="28" t="n">
+      <c r="B115" s="31" t="n">
         <v>2.059</v>
       </c>
-      <c r="C115" s="29" t="n">
+      <c r="C115" s="32" t="n">
         <v>0.4857</v>
       </c>
-      <c r="D115" s="28" t="n">
+      <c r="D115" s="31" t="n">
         <v>0.88</v>
       </c>
-      <c r="E115" s="27" t="n">
+      <c r="E115" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="28" t="n">
+      <c r="F115" s="31" t="n">
         <v>4.698</v>
       </c>
-      <c r="G115" s="27" t="n">
+      <c r="G115" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="28" t="n">
+      <c r="H115" s="31" t="n">
         <v>2.282</v>
       </c>
-      <c r="I115" s="28" t="n">
+      <c r="I115" s="31" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="27" t="n">
+      <c r="A116" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="28" t="n">
+      <c r="B116" s="31" t="n">
         <v>2.326</v>
       </c>
-      <c r="C116" s="29" t="n">
+      <c r="C116" s="32" t="n">
         <v>0.4299</v>
       </c>
-      <c r="D116" s="28" t="n">
+      <c r="D116" s="31" t="n">
         <v>0.864</v>
       </c>
-      <c r="E116" s="27" t="n">
+      <c r="E116" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="28" t="n">
+      <c r="F116" s="31" t="n">
         <v>4.918</v>
       </c>
-      <c r="G116" s="27" t="n">
+      <c r="G116" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="30" t="n">
+      <c r="H116" s="33" t="n">
         <v>2.114</v>
       </c>
-      <c r="I116" s="28" t="n">
+      <c r="I116" s="31" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="27" t="n">
+      <c r="A117" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B117" s="28" t="n">
+      <c r="B117" s="31" t="n">
         <v>2.534</v>
       </c>
-      <c r="C117" s="29" t="n">
+      <c r="C117" s="32" t="n">
         <v>0.3946</v>
       </c>
-      <c r="D117" s="28" t="n">
+      <c r="D117" s="31" t="n">
         <v>0.848</v>
       </c>
-      <c r="E117" s="27" t="n">
+      <c r="E117" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="28" t="n">
+      <c r="F117" s="31" t="n">
         <v>5.078</v>
       </c>
-      <c r="G117" s="27" t="n">
+      <c r="G117" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="28" t="n">
+      <c r="H117" s="31" t="n">
         <v>2.004</v>
       </c>
-      <c r="I117" s="28" t="n">
+      <c r="I117" s="31" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="27" t="n">
+      <c r="A118" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="28" t="n">
+      <c r="B118" s="31" t="n">
         <v>2.704</v>
       </c>
-      <c r="C118" s="29" t="n">
+      <c r="C118" s="32" t="n">
         <v>0.3698</v>
       </c>
-      <c r="D118" s="28" t="n">
+      <c r="D118" s="31" t="n">
         <v>0.833</v>
       </c>
-      <c r="E118" s="30" t="n">
+      <c r="E118" s="33" t="n">
         <v>0.204</v>
       </c>
-      <c r="F118" s="30" t="n">
+      <c r="F118" s="33" t="n">
         <v>5.204</v>
       </c>
-      <c r="G118" s="28" t="n">
+      <c r="G118" s="31" t="n">
         <v>0.076</v>
       </c>
-      <c r="H118" s="28" t="n">
+      <c r="H118" s="31" t="n">
         <v>1.924</v>
       </c>
-      <c r="I118" s="28" t="n">
+      <c r="I118" s="31" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="27" t="n">
+      <c r="A119" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B119" s="28" t="n">
+      <c r="B119" s="31" t="n">
         <v>2.847</v>
       </c>
-      <c r="C119" s="29" t="n">
+      <c r="C119" s="32" t="n">
         <v>0.3512</v>
       </c>
-      <c r="D119" s="28" t="n">
+      <c r="D119" s="31" t="n">
         <v>0.82</v>
       </c>
-      <c r="E119" s="30" t="n">
+      <c r="E119" s="33" t="n">
         <v>0.388</v>
       </c>
-      <c r="F119" s="30" t="n">
+      <c r="F119" s="33" t="n">
         <v>5.306</v>
       </c>
-      <c r="G119" s="28" t="n">
+      <c r="G119" s="31" t="n">
         <v>0.136</v>
       </c>
-      <c r="H119" s="28" t="n">
+      <c r="H119" s="31" t="n">
         <v>1.864</v>
       </c>
-      <c r="I119" s="28" t="n">
+      <c r="I119" s="31" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="27" t="n">
+      <c r="A120" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="28" t="n">
+      <c r="B120" s="31" t="n">
         <v>2.97</v>
       </c>
-      <c r="C120" s="29" t="n">
+      <c r="C120" s="32" t="n">
         <v>0.3367</v>
       </c>
-      <c r="D120" s="28" t="n">
+      <c r="D120" s="31" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E120" s="30" t="n">
+      <c r="E120" s="33" t="n">
         <v>0.547</v>
       </c>
-      <c r="F120" s="30" t="n">
+      <c r="F120" s="33" t="n">
         <v>5.393</v>
       </c>
-      <c r="G120" s="28" t="n">
+      <c r="G120" s="31" t="n">
         <v>0.184</v>
       </c>
-      <c r="H120" s="28" t="n">
+      <c r="H120" s="31" t="n">
         <v>1.816</v>
       </c>
-      <c r="I120" s="28" t="n">
+      <c r="I120" s="31" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="27" t="n">
+      <c r="A121" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B121" s="28" t="n">
+      <c r="B121" s="31" t="n">
         <v>3.078</v>
       </c>
-      <c r="C121" s="29" t="n">
+      <c r="C121" s="32" t="n">
         <v>0.3249</v>
       </c>
-      <c r="D121" s="28" t="n">
+      <c r="D121" s="31" t="n">
         <v>0.797</v>
       </c>
-      <c r="E121" s="28" t="n">
+      <c r="E121" s="31" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F121" s="28" t="n">
+      <c r="F121" s="31" t="n">
         <v>5.469</v>
       </c>
-      <c r="G121" s="28" t="n">
+      <c r="G121" s="31" t="n">
         <v>0.223</v>
       </c>
-      <c r="H121" s="28" t="n">
+      <c r="H121" s="31" t="n">
         <v>1.777</v>
       </c>
-      <c r="I121" s="28" t="n">
+      <c r="I121" s="31" t="n">
         <v>0.975</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="27" t="n">
+      <c r="A122" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B122" s="28" t="n">
+      <c r="B122" s="31" t="n">
         <v>3.173</v>
       </c>
-      <c r="C122" s="29" t="n">
+      <c r="C122" s="32" t="n">
         <v>0.3152</v>
       </c>
-      <c r="D122" s="28" t="n">
+      <c r="D122" s="31" t="n">
         <v>0.787</v>
       </c>
-      <c r="E122" s="30" t="n">
+      <c r="E122" s="33" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F122" s="30" t="n">
+      <c r="F122" s="33" t="n">
         <v>5.535</v>
       </c>
-      <c r="G122" s="28" t="n">
+      <c r="G122" s="31" t="n">
         <v>0.256</v>
       </c>
-      <c r="H122" s="28" t="n">
+      <c r="H122" s="31" t="n">
         <v>1.744</v>
       </c>
-      <c r="I122" s="28" t="n">
+      <c r="I122" s="31" t="n">
         <v>0.945</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="27" t="n">
+      <c r="A123" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="28" t="n">
+      <c r="B123" s="31" t="n">
         <v>3.258</v>
       </c>
-      <c r="C123" s="29" t="n">
+      <c r="C123" s="32" t="n">
         <v>0.3069</v>
       </c>
-      <c r="D123" s="30" t="n">
+      <c r="D123" s="33" t="n">
         <v>0.778</v>
       </c>
-      <c r="E123" s="30" t="n">
+      <c r="E123" s="33" t="n">
         <v>0.922</v>
       </c>
-      <c r="F123" s="30" t="n">
+      <c r="F123" s="33" t="n">
         <v>5.594</v>
       </c>
-      <c r="G123" s="30" t="n">
+      <c r="G123" s="33" t="n">
         <v>0.283</v>
       </c>
-      <c r="H123" s="30" t="n">
+      <c r="H123" s="33" t="n">
         <v>1.717</v>
       </c>
-      <c r="I123" s="28" t="n">
+      <c r="I123" s="31" t="n">
         <v>0.921</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="27" t="n">
+      <c r="A124" s="30" t="n">
         <v>13</v>
       </c>
-      <c r="B124" s="28" t="n">
+      <c r="B124" s="31" t="n">
         <v>3.336</v>
       </c>
-      <c r="C124" s="29" t="n">
+      <c r="C124" s="32" t="n">
         <v>0.2998</v>
       </c>
-      <c r="D124" s="28" t="n">
+      <c r="D124" s="31" t="n">
         <v>0.77</v>
       </c>
-      <c r="E124" s="30" t="n">
+      <c r="E124" s="33" t="n">
         <v>1.025</v>
       </c>
-      <c r="F124" s="30" t="n">
+      <c r="F124" s="33" t="n">
         <v>5.647</v>
       </c>
-      <c r="G124" s="30" t="n">
+      <c r="G124" s="33" t="n">
         <v>0.307</v>
       </c>
-      <c r="H124" s="30" t="n">
+      <c r="H124" s="33" t="n">
         <v>1.693</v>
       </c>
-      <c r="I124" s="28" t="n">
+      <c r="I124" s="31" t="n">
         <v>0.899</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="27" t="n">
+      <c r="A125" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B125" s="28" t="n">
+      <c r="B125" s="31" t="n">
         <v>3.407</v>
       </c>
-      <c r="C125" s="29" t="n">
+      <c r="C125" s="32" t="n">
         <v>0.2935</v>
       </c>
-      <c r="D125" s="28" t="n">
+      <c r="D125" s="31" t="n">
         <v>0.763</v>
       </c>
-      <c r="E125" s="30" t="n">
+      <c r="E125" s="33" t="n">
         <v>1.118</v>
       </c>
-      <c r="F125" s="30" t="n">
+      <c r="F125" s="33" t="n">
         <v>5.696</v>
       </c>
-      <c r="G125" s="30" t="n">
+      <c r="G125" s="33" t="n">
         <v>0.328</v>
       </c>
-      <c r="H125" s="30" t="n">
+      <c r="H125" s="33" t="n">
         <v>1.672</v>
       </c>
-      <c r="I125" s="28" t="n">
+      <c r="I125" s="31" t="n">
         <v>0.881</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="27" t="n">
+      <c r="A126" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B126" s="28" t="n">
+      <c r="B126" s="31" t="n">
         <v>3.472</v>
       </c>
-      <c r="C126" s="29" t="n">
+      <c r="C126" s="32" t="n">
         <v>0.288</v>
       </c>
-      <c r="D126" s="28" t="n">
+      <c r="D126" s="31" t="n">
         <v>0.756</v>
       </c>
-      <c r="E126" s="30" t="n">
+      <c r="E126" s="33" t="n">
         <v>1.203</v>
       </c>
-      <c r="F126" s="30" t="n">
+      <c r="F126" s="33" t="n">
         <v>5.741</v>
       </c>
-      <c r="G126" s="30" t="n">
+      <c r="G126" s="33" t="n">
         <v>0.347</v>
       </c>
-      <c r="H126" s="30" t="n">
+      <c r="H126" s="33" t="n">
         <v>1.653</v>
       </c>
-      <c r="I126" s="28" t="n">
+      <c r="I126" s="31" t="n">
         <v>0.864</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="27" t="n">
+      <c r="A127" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B127" s="28" t="n">
+      <c r="B127" s="31" t="n">
         <v>3.532</v>
       </c>
-      <c r="C127" s="29" t="n">
+      <c r="C127" s="32" t="n">
         <v>0.2831</v>
       </c>
-      <c r="D127" s="28" t="n">
+      <c r="D127" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="E127" s="30" t="n">
+      <c r="E127" s="33" t="n">
         <v>1.282</v>
       </c>
-      <c r="F127" s="30" t="n">
+      <c r="F127" s="33" t="n">
         <v>5.782</v>
       </c>
-      <c r="G127" s="30" t="n">
+      <c r="G127" s="33" t="n">
         <v>0.363</v>
       </c>
-      <c r="H127" s="30" t="n">
+      <c r="H127" s="33" t="n">
         <v>1.637</v>
       </c>
-      <c r="I127" s="28" t="n">
+      <c r="I127" s="31" t="n">
         <v>0.849</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="27" t="n">
+      <c r="A128" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="B128" s="28" t="n">
+      <c r="B128" s="31" t="n">
         <v>3.588</v>
       </c>
-      <c r="C128" s="29" t="n">
+      <c r="C128" s="32" t="n">
         <v>0.2787</v>
       </c>
-      <c r="D128" s="28" t="n">
+      <c r="D128" s="31" t="n">
         <v>0.744</v>
       </c>
-      <c r="E128" s="30" t="n">
+      <c r="E128" s="33" t="n">
         <v>1.356</v>
       </c>
-      <c r="F128" s="30" t="n">
+      <c r="F128" s="33" t="n">
         <v>5.82</v>
       </c>
-      <c r="G128" s="30" t="n">
+      <c r="G128" s="33" t="n">
         <v>0.378</v>
       </c>
-      <c r="H128" s="30" t="n">
+      <c r="H128" s="33" t="n">
         <v>1.622</v>
       </c>
-      <c r="I128" s="28" t="n">
+      <c r="I128" s="31" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="27" t="n">
+      <c r="A129" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B129" s="28" t="n">
+      <c r="B129" s="31" t="n">
         <v>3.64</v>
       </c>
-      <c r="C129" s="29" t="n">
+      <c r="C129" s="32" t="n">
         <v>0.2747</v>
       </c>
-      <c r="D129" s="28" t="n">
+      <c r="D129" s="31" t="n">
         <v>0.739</v>
       </c>
-      <c r="E129" s="30" t="n">
+      <c r="E129" s="33" t="n">
         <v>1.424</v>
       </c>
-      <c r="F129" s="30" t="n">
+      <c r="F129" s="33" t="n">
         <v>5.856</v>
       </c>
-      <c r="G129" s="30" t="n">
+      <c r="G129" s="33" t="n">
         <v>0.391</v>
       </c>
-      <c r="H129" s="28" t="n">
+      <c r="H129" s="31" t="n">
         <v>1.608</v>
       </c>
-      <c r="I129" s="28" t="n">
+      <c r="I129" s="31" t="n">
         <v>0.824</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="27" t="n">
+      <c r="A130" s="30" t="n">
         <v>19</v>
       </c>
-      <c r="B130" s="28" t="n">
+      <c r="B130" s="31" t="n">
         <v>3.689</v>
       </c>
-      <c r="C130" s="29" t="n">
+      <c r="C130" s="32" t="n">
         <v>0.2711</v>
       </c>
-      <c r="D130" s="28" t="n">
+      <c r="D130" s="31" t="n">
         <v>0.734</v>
       </c>
-      <c r="E130" s="30" t="n">
+      <c r="E130" s="33" t="n">
         <v>1.487</v>
       </c>
-      <c r="F130" s="30" t="n">
+      <c r="F130" s="33" t="n">
         <v>5.891</v>
       </c>
-      <c r="G130" s="30" t="n">
+      <c r="G130" s="33" t="n">
         <v>0.403</v>
       </c>
-      <c r="H130" s="30" t="n">
+      <c r="H130" s="33" t="n">
         <v>1.597</v>
       </c>
-      <c r="I130" s="28" t="n">
+      <c r="I130" s="31" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="27" t="n">
+      <c r="A131" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="28" t="n">
+      <c r="B131" s="31" t="n">
         <v>3.735</v>
       </c>
-      <c r="C131" s="29" t="n">
+      <c r="C131" s="32" t="n">
         <v>0.2677</v>
       </c>
-      <c r="D131" s="28" t="n">
+      <c r="D131" s="31" t="n">
         <v>0.729</v>
       </c>
-      <c r="E131" s="30" t="n">
+      <c r="E131" s="33" t="n">
         <v>1.549</v>
       </c>
-      <c r="F131" s="30" t="n">
+      <c r="F131" s="33" t="n">
         <v>5.921</v>
       </c>
-      <c r="G131" s="30" t="n">
+      <c r="G131" s="33" t="n">
         <v>0.415</v>
       </c>
-      <c r="H131" s="30" t="n">
+      <c r="H131" s="33" t="n">
         <v>1.585</v>
       </c>
-      <c r="I131" s="28" t="n">
+      <c r="I131" s="31" t="n">
         <v>0.803</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="27" t="n">
+      <c r="A132" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="B132" s="28" t="n">
+      <c r="B132" s="31" t="n">
         <v>3.778</v>
       </c>
-      <c r="C132" s="29" t="n">
+      <c r="C132" s="32" t="n">
         <v>0.2647</v>
       </c>
-      <c r="D132" s="30" t="n">
+      <c r="D132" s="33" t="n">
         <v>0.724</v>
       </c>
-      <c r="E132" s="30" t="n">
+      <c r="E132" s="33" t="n">
         <v>1.605</v>
       </c>
-      <c r="F132" s="30" t="n">
+      <c r="F132" s="33" t="n">
         <v>5.951</v>
       </c>
-      <c r="G132" s="28" t="n">
+      <c r="G132" s="31" t="n">
         <v>0.425</v>
       </c>
-      <c r="H132" s="28" t="n">
+      <c r="H132" s="31" t="n">
         <v>1.575</v>
       </c>
-      <c r="I132" s="28" t="n">
+      <c r="I132" s="31" t="n">
         <v>0.794</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="27" t="n">
+      <c r="A133" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B133" s="28" t="n">
+      <c r="B133" s="31" t="n">
         <v>3.819</v>
       </c>
-      <c r="C133" s="29" t="n">
+      <c r="C133" s="32" t="n">
         <v>0.2618</v>
       </c>
-      <c r="D133" s="28" t="n">
+      <c r="D133" s="31" t="n">
         <v>0.72</v>
       </c>
-      <c r="E133" s="28" t="n">
+      <c r="E133" s="31" t="n">
         <v>1.659</v>
       </c>
-      <c r="F133" s="28" t="n">
+      <c r="F133" s="31" t="n">
         <v>5.979</v>
       </c>
-      <c r="G133" s="28" t="n">
+      <c r="G133" s="31" t="n">
         <v>0.434</v>
       </c>
-      <c r="H133" s="28" t="n">
+      <c r="H133" s="31" t="n">
         <v>1.566</v>
       </c>
-      <c r="I133" s="28" t="n">
+      <c r="I133" s="31" t="n">
         <v>0.786</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="27" t="n">
+      <c r="A134" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="B134" s="28" t="n">
+      <c r="B134" s="31" t="n">
         <v>3.858</v>
       </c>
-      <c r="C134" s="29" t="n">
+      <c r="C134" s="32" t="n">
         <v>0.2592</v>
       </c>
-      <c r="D134" s="28" t="n">
+      <c r="D134" s="31" t="n">
         <v>0.716</v>
       </c>
-      <c r="E134" s="28" t="n">
+      <c r="E134" s="31" t="n">
         <v>1.71</v>
       </c>
-      <c r="F134" s="28" t="n">
+      <c r="F134" s="31" t="n">
         <v>6.006</v>
       </c>
-      <c r="G134" s="28" t="n">
+      <c r="G134" s="31" t="n">
         <v>0.443</v>
       </c>
-      <c r="H134" s="28" t="n">
+      <c r="H134" s="31" t="n">
         <v>1.557</v>
       </c>
-      <c r="I134" s="28" t="n">
+      <c r="I134" s="31" t="n">
         <v>0.778</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="27" t="n">
+      <c r="A135" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B135" s="28" t="n">
+      <c r="B135" s="31" t="n">
         <v>3.895</v>
       </c>
-      <c r="C135" s="29" t="n">
+      <c r="C135" s="32" t="n">
         <v>0.2567</v>
       </c>
-      <c r="D135" s="28" t="n">
+      <c r="D135" s="31" t="n">
         <v>0.712</v>
       </c>
-      <c r="E135" s="28" t="n">
+      <c r="E135" s="31" t="n">
         <v>1.759</v>
       </c>
-      <c r="F135" s="28" t="n">
+      <c r="F135" s="31" t="n">
         <v>6.031</v>
       </c>
-      <c r="G135" s="30" t="n">
+      <c r="G135" s="33" t="n">
         <v>0.451</v>
       </c>
-      <c r="H135" s="28" t="n">
+      <c r="H135" s="31" t="n">
         <v>1.548</v>
       </c>
-      <c r="I135" s="28" t="n">
+      <c r="I135" s="31" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="27" t="n">
+      <c r="A136" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="B136" s="28" t="n">
+      <c r="B136" s="31" t="n">
         <v>3.931</v>
       </c>
-      <c r="C136" s="29" t="n">
+      <c r="C136" s="32" t="n">
         <v>0.2544</v>
       </c>
-      <c r="D136" s="28" t="n">
+      <c r="D136" s="31" t="n">
         <v>0.708</v>
       </c>
-      <c r="E136" s="30" t="n">
+      <c r="E136" s="33" t="n">
         <v>1.806</v>
       </c>
-      <c r="F136" s="30" t="n">
+      <c r="F136" s="33" t="n">
         <v>6.056</v>
       </c>
-      <c r="G136" s="28" t="n">
+      <c r="G136" s="31" t="n">
         <v>0.459</v>
       </c>
-      <c r="H136" s="28" t="n">
+      <c r="H136" s="31" t="n">
         <v>1.541</v>
       </c>
-      <c r="I136" s="28" t="n">
+      <c r="I136" s="31" t="n">
         <v>0.763</v>
       </c>
     </row>
@@ -7425,236 +10202,236 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="27" t="n">
+      <c r="A142" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B142" s="28" t="n">
+      <c r="B142" s="31" t="n">
         <v>1.88</v>
       </c>
-      <c r="C142" s="28" t="n">
+      <c r="C142" s="31" t="n">
         <v>2.659</v>
       </c>
-      <c r="D142" s="27" t="n">
+      <c r="D142" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="28" t="n">
+      <c r="E142" s="31" t="n">
         <v>3.267</v>
       </c>
-      <c r="F142" s="27" t="n">
+      <c r="F142" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="28" t="n">
+      <c r="G142" s="31" t="n">
         <v>3.267</v>
       </c>
-      <c r="H142" s="30" t="n">
+      <c r="H142" s="33" t="n">
         <v>2.659</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="27" t="n">
+      <c r="A143" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="28" t="n">
+      <c r="B143" s="31" t="n">
         <v>1.023</v>
       </c>
-      <c r="C143" s="28" t="n">
+      <c r="C143" s="31" t="n">
         <v>1.954</v>
       </c>
-      <c r="D143" s="27" t="n">
+      <c r="D143" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="28" t="n">
+      <c r="E143" s="31" t="n">
         <v>2.568</v>
       </c>
-      <c r="F143" s="27" t="n">
+      <c r="F143" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="30" t="n">
+      <c r="G143" s="33" t="n">
         <v>2.574</v>
       </c>
-      <c r="H143" s="28" t="n">
+      <c r="H143" s="31" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="27" t="n">
+      <c r="A144" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B144" s="28" t="n">
+      <c r="B144" s="31" t="n">
         <v>0.729</v>
       </c>
-      <c r="C144" s="28" t="n">
+      <c r="C144" s="31" t="n">
         <v>1.628</v>
       </c>
-      <c r="D144" s="27" t="n">
+      <c r="D144" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="28" t="n">
+      <c r="E144" s="31" t="n">
         <v>2.266</v>
       </c>
-      <c r="F144" s="27" t="n">
+      <c r="F144" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="28" t="n">
+      <c r="G144" s="31" t="n">
         <v>2.282</v>
       </c>
-      <c r="H144" s="28" t="n">
+      <c r="H144" s="31" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="27" t="n">
+      <c r="A145" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B145" s="28" t="n">
+      <c r="B145" s="31" t="n">
         <v>0.577</v>
       </c>
-      <c r="C145" s="28" t="n">
+      <c r="C145" s="31" t="n">
         <v>1.427</v>
       </c>
-      <c r="D145" s="27" t="n">
+      <c r="D145" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="E145" s="28" t="n">
+      <c r="E145" s="31" t="n">
         <v>2.089</v>
       </c>
-      <c r="F145" s="27" t="n">
+      <c r="F145" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="30" t="n">
+      <c r="G145" s="33" t="n">
         <v>2.114</v>
       </c>
-      <c r="H145" s="28" t="n">
+      <c r="H145" s="31" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="27" t="n">
+      <c r="A146" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B146" s="28" t="n">
+      <c r="B146" s="31" t="n">
         <v>0.483</v>
       </c>
-      <c r="C146" s="28" t="n">
+      <c r="C146" s="31" t="n">
         <v>1.287</v>
       </c>
-      <c r="D146" s="28" t="n">
+      <c r="D146" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="E146" s="28" t="n">
+      <c r="E146" s="31" t="n">
         <v>1.97</v>
       </c>
-      <c r="F146" s="27" t="n">
+      <c r="F146" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="28" t="n">
+      <c r="G146" s="31" t="n">
         <v>2.004</v>
       </c>
-      <c r="H146" s="28" t="n">
+      <c r="H146" s="31" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="27" t="n">
+      <c r="A147" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B147" s="28" t="n">
+      <c r="B147" s="31" t="n">
         <v>0.419</v>
       </c>
-      <c r="C147" s="28" t="n">
+      <c r="C147" s="31" t="n">
         <v>1.182</v>
       </c>
-      <c r="D147" s="28" t="n">
+      <c r="D147" s="31" t="n">
         <v>0.118</v>
       </c>
-      <c r="E147" s="28" t="n">
+      <c r="E147" s="31" t="n">
         <v>1.882</v>
       </c>
-      <c r="F147" s="28" t="n">
+      <c r="F147" s="31" t="n">
         <v>0.076</v>
       </c>
-      <c r="G147" s="28" t="n">
+      <c r="G147" s="31" t="n">
         <v>1.924</v>
       </c>
-      <c r="H147" s="28" t="n">
+      <c r="H147" s="31" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="27" t="n">
+      <c r="A148" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B148" s="28" t="n">
+      <c r="B148" s="31" t="n">
         <v>0.373</v>
       </c>
-      <c r="C148" s="28" t="n">
+      <c r="C148" s="31" t="n">
         <v>1.099</v>
       </c>
-      <c r="D148" s="28" t="n">
+      <c r="D148" s="31" t="n">
         <v>0.185</v>
       </c>
-      <c r="E148" s="28" t="n">
+      <c r="E148" s="31" t="n">
         <v>1.815</v>
       </c>
-      <c r="F148" s="28" t="n">
+      <c r="F148" s="31" t="n">
         <v>0.136</v>
       </c>
-      <c r="G148" s="28" t="n">
+      <c r="G148" s="31" t="n">
         <v>1.864</v>
       </c>
-      <c r="H148" s="28" t="n">
+      <c r="H148" s="31" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="27" t="n">
+      <c r="A149" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B149" s="28" t="n">
+      <c r="B149" s="31" t="n">
         <v>0.337</v>
       </c>
-      <c r="C149" s="28" t="n">
+      <c r="C149" s="31" t="n">
         <v>1.032</v>
       </c>
-      <c r="D149" s="28" t="n">
+      <c r="D149" s="31" t="n">
         <v>0.239</v>
       </c>
-      <c r="E149" s="28" t="n">
+      <c r="E149" s="31" t="n">
         <v>1.761</v>
       </c>
-      <c r="F149" s="28" t="n">
+      <c r="F149" s="31" t="n">
         <v>0.184</v>
       </c>
-      <c r="G149" s="28" t="n">
+      <c r="G149" s="31" t="n">
         <v>1.816</v>
       </c>
-      <c r="H149" s="28" t="n">
+      <c r="H149" s="31" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="27" t="n">
+      <c r="A150" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B150" s="28" t="n">
+      <c r="B150" s="31" t="n">
         <v>0.308</v>
       </c>
-      <c r="C150" s="28" t="n">
+      <c r="C150" s="31" t="n">
         <v>0.975</v>
       </c>
-      <c r="D150" s="28" t="n">
+      <c r="D150" s="31" t="n">
         <v>0.284</v>
       </c>
-      <c r="E150" s="28" t="n">
+      <c r="E150" s="31" t="n">
         <v>1.716</v>
       </c>
-      <c r="F150" s="28" t="n">
+      <c r="F150" s="31" t="n">
         <v>0.223</v>
       </c>
-      <c r="G150" s="28" t="n">
+      <c r="G150" s="31" t="n">
         <v>1.777</v>
       </c>
-      <c r="H150" s="28" t="n">
+      <c r="H150" s="31" t="n">
         <v>0.975</v>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normal" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sigma &amp; DPMO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance CI &amp; tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -187,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,6 +225,11 @@
     <xf numFmtId="174" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="175" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6362,6 +6368,1111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Confusion matrix: accuracy, recall, precision, F1 (training vs test, up to three models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 2/20260529_naert.pdf p. 19-32 (train/test, under-/overfitting, bias-variance, confusion matrix and its metrics)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Recall, precision and F1 shown with each class as the positive class (the course leaves that choice to the domain); no automatic bias/variance label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>UNVERIFIED: no course worked example prints these metrics; checked against an independent computation and by the stats-auditor (build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. Class names (optional, for your own reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Class 1</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>e.g. Goed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Class 2</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>e.g. Slecht</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2. Model A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>counts (rows = actual)</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Training: predicted class 1</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>predicted class 2</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Test: predicted class 1</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>predicted class 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>actual class 1</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>actual class 2</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Test − training</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Accuracy = (correct) / (all)</t>
+        </is>
+      </c>
+      <c r="B17" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,(B14+C15)/(B14+C14+B15+C15),""),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,(E14+F15)/(E14+F14+E15+F15),""),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="32">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C17)),C17-B17,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>p. 31 (misleading with unequal classes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Error rate = 1 − accuracy</t>
+        </is>
+      </c>
+      <c r="B18" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,(C14+B15)/(B14+C14+B15+C15),""),"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,(F14+E15)/(E14+F14+E15+F15),""),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="32">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(C18)),C18-B18,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Recall, class 1 positive = TP / (TP + FN)</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,B14/(B14+C14),""),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,E14/(E14+F14),""),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="32">
+        <f>IF(AND(ISNUMBER(B19),ISNUMBER(C19)),C19-B19,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Precision, class 1 positive = TP / (TP + FP)</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,B14/(B14+B15),""),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,E14/(E14+E15),""),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>IF(AND(ISNUMBER(B20),ISNUMBER(C20)),C20-B20,"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>F1, class 1 positive = 2·P·R / (P + R)</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,2*(B14/(B14+B15))*(B14/(B14+C14))/((B14/(B14+B15))+(B14/(B14+C14))),""),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,2*(E14/(E14+E15))*(E14/(E14+F14))/((E14/(E14+E15))+(E14/(E14+F14))),""),"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="32">
+        <f>IF(AND(ISNUMBER(B21),ISNUMBER(C21)),C21-B21,"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Recall, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B22" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,C15/(C15+B15),""),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,F15/(F15+E15),""),"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="32">
+        <f>IF(AND(ISNUMBER(B22),ISNUMBER(C22)),C22-B22,"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Precision, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,C15/(C15+C14),""),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,F15/(F15+F14),""),"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="32">
+        <f>IF(AND(ISNUMBER(B23),ISNUMBER(C23)),C23-B23,"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>F1, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B24" s="32">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,2*(C15/(C15+C14))*(C15/(C15+B15))/((C15/(C15+C14))+(C15/(C15+B15))),""),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="32">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,2*(F15/(F15+F14))*(F15/(F15+E15))/((F15/(F15+F14))+(F15/(F15+E15))),""),"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="32">
+        <f>IF(AND(ISNUMBER(B24),ISNUMBER(C24)),C24-B24,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Number of items</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>IFERROR(IF(COUNT(B14,C14,B15,C15)=4,(B14+C14+B15+C15),""),"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="24">
+        <f>IFERROR(IF(COUNT(E14,F14,E15,F15)=4,(E14+F14+E15+F15),""),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>3. Model B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>counts (rows = actual)</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Training: predicted class 1</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>predicted class 2</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Test: predicted class 1</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>predicted class 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>actual class 1</t>
+        </is>
+      </c>
+      <c r="B29" s="31" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>actual class 2</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Test − training</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Accuracy = (correct) / (all)</t>
+        </is>
+      </c>
+      <c r="B32" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,(B29+C30)/(B29+C29+B30+C30),""),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,(E29+F30)/(E29+F29+E30+F30),""),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="32">
+        <f>IF(AND(ISNUMBER(B32),ISNUMBER(C32)),C32-B32,"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>p. 31 (misleading with unequal classes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Error rate = 1 − accuracy</t>
+        </is>
+      </c>
+      <c r="B33" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,(C29+B30)/(B29+C29+B30+C30),""),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,(F29+E30)/(E29+F29+E30+F30),""),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="32">
+        <f>IF(AND(ISNUMBER(B33),ISNUMBER(C33)),C33-B33,"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Recall, class 1 positive = TP / (TP + FN)</t>
+        </is>
+      </c>
+      <c r="B34" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,B29/(B29+C29),""),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,E29/(E29+F29),""),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="32">
+        <f>IF(AND(ISNUMBER(B34),ISNUMBER(C34)),C34-B34,"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Precision, class 1 positive = TP / (TP + FP)</t>
+        </is>
+      </c>
+      <c r="B35" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,B29/(B29+B30),""),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,E29/(E29+E30),""),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="32">
+        <f>IF(AND(ISNUMBER(B35),ISNUMBER(C35)),C35-B35,"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>F1, class 1 positive = 2·P·R / (P + R)</t>
+        </is>
+      </c>
+      <c r="B36" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,2*(B29/(B29+B30))*(B29/(B29+C29))/((B29/(B29+B30))+(B29/(B29+C29))),""),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,2*(E29/(E29+E30))*(E29/(E29+F29))/((E29/(E29+E30))+(E29/(E29+F29))),""),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="32">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(C36)),C36-B36,"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Recall, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B37" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,C30/(C30+B30),""),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,F30/(F30+E30),""),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="32">
+        <f>IF(AND(ISNUMBER(B37),ISNUMBER(C37)),C37-B37,"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Precision, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B38" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,C30/(C30+C29),""),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,F30/(F30+F29),""),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="32">
+        <f>IF(AND(ISNUMBER(B38),ISNUMBER(C38)),C38-B38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>F1, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B39" s="32">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,2*(C30/(C30+C29))*(C30/(C30+B30))/((C30/(C30+C29))+(C30/(C30+B30))),""),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="32">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,2*(F30/(F30+F29))*(F30/(F30+E30))/((F30/(F30+F29))+(F30/(F30+E30))),""),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="32">
+        <f>IF(AND(ISNUMBER(B39),ISNUMBER(C39)),C39-B39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Number of items</t>
+        </is>
+      </c>
+      <c r="B40" s="24">
+        <f>IFERROR(IF(COUNT(B29,C29,B30,C30)=4,(B29+C29+B30+C30),""),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="24">
+        <f>IFERROR(IF(COUNT(E29,F29,E30,F30)=4,(E29+F29+E30+F30),""),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="8" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>4. Model C</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>counts (rows = actual)</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Training: predicted class 1</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>predicted class 2</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr"/>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Test: predicted class 1</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>predicted class 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>actual class 1</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n"/>
+      <c r="C44" s="31" t="n"/>
+      <c r="E44" s="31" t="n"/>
+      <c r="F44" s="31" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>actual class 2</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n"/>
+      <c r="C45" s="31" t="n"/>
+      <c r="E45" s="31" t="n"/>
+      <c r="F45" s="31" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Test − training</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Accuracy = (correct) / (all)</t>
+        </is>
+      </c>
+      <c r="B47" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,(B44+C45)/(B44+C44+B45+C45),""),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,(E44+F45)/(E44+F44+E45+F45),""),"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="32">
+        <f>IF(AND(ISNUMBER(B47),ISNUMBER(C47)),C47-B47,"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>p. 31 (misleading with unequal classes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Error rate = 1 − accuracy</t>
+        </is>
+      </c>
+      <c r="B48" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,(C44+B45)/(B44+C44+B45+C45),""),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,(F44+E45)/(E44+F44+E45+F45),""),"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="32">
+        <f>IF(AND(ISNUMBER(B48),ISNUMBER(C48)),C48-B48,"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Recall, class 1 positive = TP / (TP + FN)</t>
+        </is>
+      </c>
+      <c r="B49" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,B44/(B44+C44),""),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,E44/(E44+F44),""),"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="32">
+        <f>IF(AND(ISNUMBER(B49),ISNUMBER(C49)),C49-B49,"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Precision, class 1 positive = TP / (TP + FP)</t>
+        </is>
+      </c>
+      <c r="B50" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,B44/(B44+B45),""),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,E44/(E44+E45),""),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="32">
+        <f>IF(AND(ISNUMBER(B50),ISNUMBER(C50)),C50-B50,"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>F1, class 1 positive = 2·P·R / (P + R)</t>
+        </is>
+      </c>
+      <c r="B51" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,2*(B44/(B44+B45))*(B44/(B44+C44))/((B44/(B44+B45))+(B44/(B44+C44))),""),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,2*(E44/(E44+E45))*(E44/(E44+F44))/((E44/(E44+E45))+(E44/(E44+F44))),""),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="32">
+        <f>IF(AND(ISNUMBER(B51),ISNUMBER(C51)),C51-B51,"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Recall, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B52" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,C45/(C45+B45),""),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,F45/(F45+E45),""),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="32">
+        <f>IF(AND(ISNUMBER(B52),ISNUMBER(C52)),C52-B52,"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Precision, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B53" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,C45/(C45+C44),""),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,F45/(F45+F44),""),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="32">
+        <f>IF(AND(ISNUMBER(B53),ISNUMBER(C53)),C53-B53,"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>F1, class 2 positive</t>
+        </is>
+      </c>
+      <c r="B54" s="32">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,2*(C45/(C45+C44))*(C45/(C45+B45))/((C45/(C45+C44))+(C45/(C45+B45))),""),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="32">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,2*(F45/(F45+F44))*(F45/(F45+E45))/((F45/(F45+F44))+(F45/(F45+E45))),""),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="32">
+        <f>IF(AND(ISNUMBER(B54),ISNUMBER(C54)),C54-B54,"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>p. 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Number of items</t>
+        </is>
+      </c>
+      <c r="B55" s="24">
+        <f>IFERROR(IF(COUNT(B44,C44,B45,C45)=4,(B44+C44+B45+C45),""),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="24">
+        <f>IFERROR(IF(COUNT(E44,F44,E45,F45)=4,(E44+F44+E45+F45),""),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>5. Comparison and how the course reads it</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Training accuracy</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Test accuracy</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Test − training</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>Model A</t>
+        </is>
+      </c>
+      <c r="B59" s="32">
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="C59" s="32">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="D59" s="32">
+        <f>D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>Model B</t>
+        </is>
+      </c>
+      <c r="B60" s="32">
+        <f>B32</f>
+        <v/>
+      </c>
+      <c r="C60" s="32">
+        <f>C32</f>
+        <v/>
+      </c>
+      <c r="D60" s="32">
+        <f>D32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
+        <is>
+          <t>Model C</t>
+        </is>
+      </c>
+      <c r="B61" s="32">
+        <f>B47</f>
+        <v/>
+      </c>
+      <c r="C61" s="32">
+        <f>C47</f>
+        <v/>
+      </c>
+      <c r="D61" s="32">
+        <f>D47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Underfitted model (high bias, low variance): high training loss and high test loss, i.e. both accuracies low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Overfitted model (low bias, high variance): low training loss, high test loss, i.e. training accuracy high and test accuracy clearly lower.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Good fit (low bias, low variance): low training and test loss. Optimum at the minimum of bias² + variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Source: 20260529_naert.pdf p. 22-28 (underfitting, overfitting, bias-variance trade-off); decision trees p. 43-46.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B14 B15 B29 B30 B44 B45 C14 C15 C29 C30 C44 C45 E14 E15 E29 E30 E44 E45 F14 F15 F29 F30 F44 F45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Count" error="A count is a whole number, 0 or more." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6569,1327 +7680,1327 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="34" t="n">
         <v>2.121</v>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="34" t="n">
         <v>3.76</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="34" t="n">
         <v>3.76</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="34" t="n">
         <v>1.88</v>
       </c>
-      <c r="F14" s="32" t="n">
+      <c r="F14" s="35" t="n">
         <v>0.5642</v>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="35" t="n">
         <v>1.7725</v>
       </c>
-      <c r="H14" s="30" t="n">
+      <c r="H14" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="31" t="n">
+      <c r="I14" s="34" t="n">
         <v>1.843</v>
       </c>
-      <c r="J14" s="30" t="n">
+      <c r="J14" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="31" t="n">
+      <c r="K14" s="34" t="n">
         <v>3.267</v>
       </c>
-      <c r="L14" s="31" t="n">
+      <c r="L14" s="34" t="n">
         <v>1.128</v>
       </c>
-      <c r="M14" s="32" t="n">
+      <c r="M14" s="35" t="n">
         <v>0.8865</v>
       </c>
-      <c r="N14" s="30" t="n">
+      <c r="N14" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="31" t="n">
+      <c r="O14" s="34" t="n">
         <v>3.686</v>
       </c>
-      <c r="P14" s="30" t="n">
+      <c r="P14" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="31" t="n">
+      <c r="Q14" s="34" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="34" t="n">
         <v>1.732</v>
       </c>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="34" t="n">
         <v>3.07</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="34" t="n">
         <v>2.394</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="34" t="n">
         <v>1.023</v>
       </c>
-      <c r="F15" s="32" t="n">
+      <c r="F15" s="35" t="n">
         <v>0.7236</v>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="35" t="n">
         <v>1.382</v>
       </c>
-      <c r="H15" s="30" t="n">
+      <c r="H15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="31" t="n">
+      <c r="I15" s="34" t="n">
         <v>1.858</v>
       </c>
-      <c r="J15" s="30" t="n">
+      <c r="J15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="31" t="n">
+      <c r="K15" s="34" t="n">
         <v>2.568</v>
       </c>
-      <c r="L15" s="31" t="n">
+      <c r="L15" s="34" t="n">
         <v>1.693</v>
       </c>
-      <c r="M15" s="32" t="n">
+      <c r="M15" s="35" t="n">
         <v>0.5907</v>
       </c>
-      <c r="N15" s="30" t="n">
+      <c r="N15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="31" t="n">
+      <c r="O15" s="34" t="n">
         <v>4.358</v>
       </c>
-      <c r="P15" s="30" t="n">
+      <c r="P15" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="33" t="n">
+      <c r="Q15" s="36" t="n">
         <v>2.575</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="31" t="n">
+      <c r="B16" s="34" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="34" t="n">
         <v>2.914</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="34" t="n">
         <v>1.88</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="34" t="n">
         <v>0.729</v>
       </c>
-      <c r="F16" s="32" t="n">
+      <c r="F16" s="35" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="35" t="n">
         <v>1.2533</v>
       </c>
-      <c r="H16" s="30" t="n">
+      <c r="H16" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="31" t="n">
+      <c r="I16" s="34" t="n">
         <v>1.808</v>
       </c>
-      <c r="J16" s="30" t="n">
+      <c r="J16" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="31" t="n">
+      <c r="K16" s="34" t="n">
         <v>2.266</v>
       </c>
-      <c r="L16" s="31" t="n">
+      <c r="L16" s="34" t="n">
         <v>2.059</v>
       </c>
-      <c r="M16" s="32" t="n">
+      <c r="M16" s="35" t="n">
         <v>0.4857</v>
       </c>
-      <c r="N16" s="30" t="n">
+      <c r="N16" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="31" t="n">
+      <c r="O16" s="34" t="n">
         <v>4.698</v>
       </c>
-      <c r="P16" s="30" t="n">
+      <c r="P16" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="31" t="n">
+      <c r="Q16" s="34" t="n">
         <v>2.282</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="31" t="n">
+      <c r="B17" s="34" t="n">
         <v>1.342</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="34" t="n">
         <v>2.884</v>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="34" t="n">
         <v>1.596</v>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="34" t="n">
         <v>0.577</v>
       </c>
-      <c r="F17" s="32" t="n">
+      <c r="F17" s="35" t="n">
         <v>0.8407</v>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="35" t="n">
         <v>1.1894</v>
       </c>
-      <c r="H17" s="30" t="n">
+      <c r="H17" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="31" t="n">
+      <c r="I17" s="34" t="n">
         <v>1.756</v>
       </c>
-      <c r="J17" s="30" t="n">
+      <c r="J17" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="31" t="n">
+      <c r="K17" s="34" t="n">
         <v>2.089</v>
       </c>
-      <c r="L17" s="31" t="n">
+      <c r="L17" s="34" t="n">
         <v>2.326</v>
       </c>
-      <c r="M17" s="32" t="n">
+      <c r="M17" s="35" t="n">
         <v>0.4299</v>
       </c>
-      <c r="N17" s="30" t="n">
+      <c r="N17" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="31" t="n">
+      <c r="O17" s="34" t="n">
         <v>4.918</v>
       </c>
-      <c r="P17" s="30" t="n">
+      <c r="P17" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="33" t="n">
+      <c r="Q17" s="36" t="n">
         <v>2.115</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="31" t="n">
+      <c r="B18" s="34" t="n">
         <v>1.225</v>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="34" t="n">
         <v>2.899</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="34" t="n">
         <v>1.41</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="34" t="n">
         <v>0.483</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="35" t="n">
         <v>0.8686</v>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="35" t="n">
         <v>1.1512</v>
       </c>
-      <c r="H18" s="31" t="n">
+      <c r="H18" s="34" t="n">
         <v>0.026</v>
       </c>
-      <c r="I18" s="31" t="n">
+      <c r="I18" s="34" t="n">
         <v>1.711</v>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" s="31" t="n">
+      <c r="K18" s="34" t="n">
         <v>1.97</v>
       </c>
-      <c r="L18" s="31" t="n">
+      <c r="L18" s="34" t="n">
         <v>2.534</v>
       </c>
-      <c r="M18" s="32" t="n">
+      <c r="M18" s="35" t="n">
         <v>0.3946</v>
       </c>
-      <c r="N18" s="30" t="n">
+      <c r="N18" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="31" t="n">
+      <c r="O18" s="34" t="n">
         <v>5.078</v>
       </c>
-      <c r="P18" s="30" t="n">
+      <c r="P18" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="31" t="n">
+      <c r="Q18" s="34" t="n">
         <v>2.004</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="31" t="n">
+      <c r="B19" s="34" t="n">
         <v>1.134</v>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="34" t="n">
         <v>2.935</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="34" t="n">
         <v>1.277</v>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="34" t="n">
         <v>0.419</v>
       </c>
-      <c r="F19" s="32" t="n">
+      <c r="F19" s="35" t="n">
         <v>0.8882</v>
       </c>
-      <c r="G19" s="32" t="n">
+      <c r="G19" s="35" t="n">
         <v>1.1259</v>
       </c>
-      <c r="H19" s="31" t="n">
+      <c r="H19" s="34" t="n">
         <v>0.105</v>
       </c>
-      <c r="I19" s="31" t="n">
+      <c r="I19" s="34" t="n">
         <v>1.672</v>
       </c>
-      <c r="J19" s="31" t="n">
+      <c r="J19" s="34" t="n">
         <v>0.118</v>
       </c>
-      <c r="K19" s="31" t="n">
+      <c r="K19" s="34" t="n">
         <v>1.882</v>
       </c>
-      <c r="L19" s="31" t="n">
+      <c r="L19" s="34" t="n">
         <v>2.704</v>
       </c>
-      <c r="M19" s="32" t="n">
+      <c r="M19" s="35" t="n">
         <v>0.3698</v>
       </c>
-      <c r="N19" s="33" t="n">
+      <c r="N19" s="36" t="n">
         <v>0.205</v>
       </c>
-      <c r="O19" s="33" t="n">
+      <c r="O19" s="36" t="n">
         <v>5.203</v>
       </c>
-      <c r="P19" s="31" t="n">
+      <c r="P19" s="34" t="n">
         <v>0.076</v>
       </c>
-      <c r="Q19" s="31" t="n">
+      <c r="Q19" s="34" t="n">
         <v>1.924</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="34" t="n">
         <v>1.061</v>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C20" s="34" t="n">
         <v>2.98</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="34" t="n">
         <v>1.175</v>
       </c>
-      <c r="E20" s="31" t="n">
+      <c r="E20" s="34" t="n">
         <v>0.373</v>
       </c>
-      <c r="F20" s="32" t="n">
+      <c r="F20" s="35" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="G20" s="32" t="n">
+      <c r="G20" s="35" t="n">
         <v>1.1078</v>
       </c>
-      <c r="H20" s="31" t="n">
+      <c r="H20" s="34" t="n">
         <v>0.167</v>
       </c>
-      <c r="I20" s="31" t="n">
+      <c r="I20" s="34" t="n">
         <v>1.638</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="34" t="n">
         <v>0.185</v>
       </c>
-      <c r="K20" s="31" t="n">
+      <c r="K20" s="34" t="n">
         <v>1.815</v>
       </c>
-      <c r="L20" s="31" t="n">
+      <c r="L20" s="34" t="n">
         <v>2.847</v>
       </c>
-      <c r="M20" s="32" t="n">
+      <c r="M20" s="35" t="n">
         <v>0.3512</v>
       </c>
-      <c r="N20" s="33" t="n">
+      <c r="N20" s="36" t="n">
         <v>0.387</v>
       </c>
-      <c r="O20" s="33" t="n">
+      <c r="O20" s="36" t="n">
         <v>5.307</v>
       </c>
-      <c r="P20" s="31" t="n">
+      <c r="P20" s="34" t="n">
         <v>0.136</v>
       </c>
-      <c r="Q20" s="31" t="n">
+      <c r="Q20" s="34" t="n">
         <v>1.864</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="34" t="n">
         <v>3.03</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="34" t="n">
         <v>1.094</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="34" t="n">
         <v>0.337</v>
       </c>
-      <c r="F21" s="32" t="n">
+      <c r="F21" s="35" t="n">
         <v>0.9139</v>
       </c>
-      <c r="G21" s="32" t="n">
+      <c r="G21" s="35" t="n">
         <v>1.0942</v>
       </c>
-      <c r="H21" s="31" t="n">
+      <c r="H21" s="34" t="n">
         <v>0.219</v>
       </c>
-      <c r="I21" s="31" t="n">
+      <c r="I21" s="34" t="n">
         <v>1.609</v>
       </c>
-      <c r="J21" s="31" t="n">
+      <c r="J21" s="34" t="n">
         <v>0.239</v>
       </c>
-      <c r="K21" s="31" t="n">
+      <c r="K21" s="34" t="n">
         <v>1.761</v>
       </c>
-      <c r="L21" s="31" t="n">
+      <c r="L21" s="34" t="n">
         <v>2.97</v>
       </c>
-      <c r="M21" s="32" t="n">
+      <c r="M21" s="35" t="n">
         <v>0.3367</v>
       </c>
-      <c r="N21" s="33" t="n">
+      <c r="N21" s="36" t="n">
         <v>0.546</v>
       </c>
-      <c r="O21" s="33" t="n">
+      <c r="O21" s="36" t="n">
         <v>5.394</v>
       </c>
-      <c r="P21" s="31" t="n">
+      <c r="P21" s="34" t="n">
         <v>0.184</v>
       </c>
-      <c r="Q21" s="31" t="n">
+      <c r="Q21" s="34" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="34" t="n">
         <v>0.949</v>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C22" s="34" t="n">
         <v>3.085</v>
       </c>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="34" t="n">
         <v>1.028</v>
       </c>
-      <c r="E22" s="31" t="n">
+      <c r="E22" s="34" t="n">
         <v>0.308</v>
       </c>
-      <c r="F22" s="32" t="n">
+      <c r="F22" s="35" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G22" s="32" t="n">
+      <c r="G22" s="35" t="n">
         <v>1.0837</v>
       </c>
-      <c r="H22" s="31" t="n">
+      <c r="H22" s="34" t="n">
         <v>0.262</v>
       </c>
-      <c r="I22" s="31" t="n">
+      <c r="I22" s="34" t="n">
         <v>1.584</v>
       </c>
-      <c r="J22" s="31" t="n">
+      <c r="J22" s="34" t="n">
         <v>0.284</v>
       </c>
-      <c r="K22" s="31" t="n">
+      <c r="K22" s="34" t="n">
         <v>1.716</v>
       </c>
-      <c r="L22" s="31" t="n">
+      <c r="L22" s="34" t="n">
         <v>3.078</v>
       </c>
-      <c r="M22" s="32" t="n">
+      <c r="M22" s="35" t="n">
         <v>0.3249</v>
       </c>
-      <c r="N22" s="31" t="n">
+      <c r="N22" s="34" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="O22" s="31" t="n">
+      <c r="O22" s="34" t="n">
         <v>5.469</v>
       </c>
-      <c r="P22" s="31" t="n">
+      <c r="P22" s="34" t="n">
         <v>0.223</v>
       </c>
-      <c r="Q22" s="31" t="n">
+      <c r="Q22" s="34" t="n">
         <v>1.777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="34" t="n">
         <v>0.905</v>
       </c>
-      <c r="C23" s="31" t="n">
+      <c r="C23" s="34" t="n">
         <v>3.136</v>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="34" t="n">
         <v>0.973</v>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="34" t="n">
         <v>0.285</v>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="35" t="n">
         <v>0.93</v>
       </c>
-      <c r="G23" s="32" t="n">
+      <c r="G23" s="35" t="n">
         <v>1.0753</v>
       </c>
-      <c r="H23" s="31" t="n">
+      <c r="H23" s="34" t="n">
         <v>0.299</v>
       </c>
-      <c r="I23" s="31" t="n">
+      <c r="I23" s="34" t="n">
         <v>1.561</v>
       </c>
-      <c r="J23" s="31" t="n">
+      <c r="J23" s="34" t="n">
         <v>0.321</v>
       </c>
-      <c r="K23" s="31" t="n">
+      <c r="K23" s="34" t="n">
         <v>1.679</v>
       </c>
-      <c r="L23" s="31" t="n">
+      <c r="L23" s="34" t="n">
         <v>3.173</v>
       </c>
-      <c r="M23" s="32" t="n">
+      <c r="M23" s="35" t="n">
         <v>0.3152</v>
       </c>
-      <c r="N23" s="33" t="n">
+      <c r="N23" s="36" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="O23" s="33" t="n">
+      <c r="O23" s="36" t="n">
         <v>5.534</v>
       </c>
-      <c r="P23" s="31" t="n">
+      <c r="P23" s="34" t="n">
         <v>0.256</v>
       </c>
-      <c r="Q23" s="31" t="n">
+      <c r="Q23" s="34" t="n">
         <v>1.744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="34" t="n">
         <v>0.866</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="34" t="n">
         <v>3.189</v>
       </c>
-      <c r="D24" s="31" t="n">
+      <c r="D24" s="34" t="n">
         <v>0.925</v>
       </c>
-      <c r="E24" s="31" t="n">
+      <c r="E24" s="34" t="n">
         <v>0.266</v>
       </c>
-      <c r="F24" s="32" t="n">
+      <c r="F24" s="35" t="n">
         <v>0.9359</v>
       </c>
-      <c r="G24" s="32" t="n">
+      <c r="G24" s="35" t="n">
         <v>1.0684</v>
       </c>
-      <c r="H24" s="31" t="n">
+      <c r="H24" s="34" t="n">
         <v>0.331</v>
       </c>
-      <c r="I24" s="31" t="n">
+      <c r="I24" s="34" t="n">
         <v>1.541</v>
       </c>
-      <c r="J24" s="31" t="n">
+      <c r="J24" s="34" t="n">
         <v>0.354</v>
       </c>
-      <c r="K24" s="31" t="n">
+      <c r="K24" s="34" t="n">
         <v>1.646</v>
       </c>
-      <c r="L24" s="31" t="n">
+      <c r="L24" s="34" t="n">
         <v>3.258</v>
       </c>
-      <c r="M24" s="32" t="n">
+      <c r="M24" s="35" t="n">
         <v>0.3069</v>
       </c>
-      <c r="N24" s="33" t="n">
+      <c r="N24" s="36" t="n">
         <v>0.924</v>
       </c>
-      <c r="O24" s="33" t="n">
+      <c r="O24" s="36" t="n">
         <v>5.592</v>
       </c>
-      <c r="P24" s="33" t="n">
+      <c r="P24" s="36" t="n">
         <v>0.284</v>
       </c>
-      <c r="Q24" s="33" t="n">
+      <c r="Q24" s="36" t="n">
         <v>1.716</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="34" t="n">
         <v>0.832</v>
       </c>
-      <c r="C25" s="31" t="n">
+      <c r="C25" s="34" t="n">
         <v>3.242</v>
       </c>
-      <c r="D25" s="31" t="n">
+      <c r="D25" s="34" t="n">
         <v>0.884</v>
       </c>
-      <c r="E25" s="31" t="n">
+      <c r="E25" s="34" t="n">
         <v>0.249</v>
       </c>
-      <c r="F25" s="32" t="n">
+      <c r="F25" s="35" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="G25" s="32" t="n">
+      <c r="G25" s="35" t="n">
         <v>1.0627</v>
       </c>
-      <c r="H25" s="31" t="n">
+      <c r="H25" s="34" t="n">
         <v>0.359</v>
       </c>
-      <c r="I25" s="31" t="n">
+      <c r="I25" s="34" t="n">
         <v>1.523</v>
       </c>
-      <c r="J25" s="31" t="n">
+      <c r="J25" s="34" t="n">
         <v>0.382</v>
       </c>
-      <c r="K25" s="31" t="n">
+      <c r="K25" s="34" t="n">
         <v>1.618</v>
       </c>
-      <c r="L25" s="31" t="n">
+      <c r="L25" s="34" t="n">
         <v>3.336</v>
       </c>
-      <c r="M25" s="32" t="n">
+      <c r="M25" s="35" t="n">
         <v>0.2998</v>
       </c>
-      <c r="N25" s="33" t="n">
+      <c r="N25" s="36" t="n">
         <v>1.026</v>
       </c>
-      <c r="O25" s="33" t="n">
+      <c r="O25" s="36" t="n">
         <v>5.646</v>
       </c>
-      <c r="P25" s="33" t="n">
+      <c r="P25" s="36" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q25" s="33" t="n">
+      <c r="Q25" s="36" t="n">
         <v>1.692</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="34" t="n">
         <v>0.802</v>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="34" t="n">
         <v>3.295</v>
       </c>
-      <c r="D26" s="31" t="n">
+      <c r="D26" s="34" t="n">
         <v>0.848</v>
       </c>
-      <c r="E26" s="31" t="n">
+      <c r="E26" s="34" t="n">
         <v>0.235</v>
       </c>
-      <c r="F26" s="32" t="n">
+      <c r="F26" s="35" t="n">
         <v>0.9453</v>
       </c>
-      <c r="G26" s="32" t="n">
+      <c r="G26" s="35" t="n">
         <v>1.0579</v>
       </c>
-      <c r="H26" s="31" t="n">
+      <c r="H26" s="34" t="n">
         <v>0.384</v>
       </c>
-      <c r="I26" s="31" t="n">
+      <c r="I26" s="34" t="n">
         <v>1.507</v>
       </c>
-      <c r="J26" s="31" t="n">
+      <c r="J26" s="34" t="n">
         <v>0.406</v>
       </c>
-      <c r="K26" s="31" t="n">
+      <c r="K26" s="34" t="n">
         <v>1.594</v>
       </c>
-      <c r="L26" s="31" t="n">
+      <c r="L26" s="34" t="n">
         <v>3.407</v>
       </c>
-      <c r="M26" s="32" t="n">
+      <c r="M26" s="35" t="n">
         <v>0.2935</v>
       </c>
-      <c r="N26" s="33" t="n">
+      <c r="N26" s="36" t="n">
         <v>1.121</v>
       </c>
-      <c r="O26" s="33" t="n">
+      <c r="O26" s="36" t="n">
         <v>5.693</v>
       </c>
-      <c r="P26" s="33" t="n">
+      <c r="P26" s="36" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q26" s="33" t="n">
+      <c r="Q26" s="36" t="n">
         <v>1.671</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="31" t="n">
+      <c r="B27" s="34" t="n">
         <v>0.775</v>
       </c>
-      <c r="C27" s="31" t="n">
+      <c r="C27" s="34" t="n">
         <v>3.347</v>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="D27" s="34" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="E27" s="31" t="n">
+      <c r="E27" s="34" t="n">
         <v>0.223</v>
       </c>
-      <c r="F27" s="32" t="n">
+      <c r="F27" s="35" t="n">
         <v>0.949</v>
       </c>
-      <c r="G27" s="32" t="n">
+      <c r="G27" s="35" t="n">
         <v>1.0537</v>
       </c>
-      <c r="H27" s="31" t="n">
+      <c r="H27" s="34" t="n">
         <v>0.406</v>
       </c>
-      <c r="I27" s="31" t="n">
+      <c r="I27" s="34" t="n">
         <v>1.492</v>
       </c>
-      <c r="J27" s="31" t="n">
+      <c r="J27" s="34" t="n">
         <v>0.428</v>
       </c>
-      <c r="K27" s="31" t="n">
+      <c r="K27" s="34" t="n">
         <v>1.572</v>
       </c>
-      <c r="L27" s="31" t="n">
+      <c r="L27" s="34" t="n">
         <v>3.472</v>
       </c>
-      <c r="M27" s="32" t="n">
+      <c r="M27" s="35" t="n">
         <v>0.288</v>
       </c>
-      <c r="N27" s="33" t="n">
+      <c r="N27" s="36" t="n">
         <v>1.207</v>
       </c>
-      <c r="O27" s="33" t="n">
+      <c r="O27" s="36" t="n">
         <v>5.737</v>
       </c>
-      <c r="P27" s="33" t="n">
+      <c r="P27" s="36" t="n">
         <v>0.348</v>
       </c>
-      <c r="Q27" s="33" t="n">
+      <c r="Q27" s="36" t="n">
         <v>1.652</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="31" t="n">
+      <c r="B28" s="34" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="31" t="n">
+      <c r="C28" s="34" t="n">
         <v>3.398</v>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="34" t="n">
         <v>0.788</v>
       </c>
-      <c r="E28" s="31" t="n">
+      <c r="E28" s="34" t="n">
         <v>0.212</v>
       </c>
-      <c r="F28" s="32" t="n">
+      <c r="F28" s="35" t="n">
         <v>0.9523</v>
       </c>
-      <c r="G28" s="32" t="n">
+      <c r="G28" s="35" t="n">
         <v>1.0501</v>
       </c>
-      <c r="H28" s="31" t="n">
+      <c r="H28" s="34" t="n">
         <v>0.427</v>
       </c>
-      <c r="I28" s="31" t="n">
+      <c r="I28" s="34" t="n">
         <v>1.478</v>
       </c>
-      <c r="J28" s="31" t="n">
+      <c r="J28" s="34" t="n">
         <v>0.448</v>
       </c>
-      <c r="K28" s="31" t="n">
+      <c r="K28" s="34" t="n">
         <v>1.552</v>
       </c>
-      <c r="L28" s="31" t="n">
+      <c r="L28" s="34" t="n">
         <v>3.532</v>
       </c>
-      <c r="M28" s="32" t="n">
+      <c r="M28" s="35" t="n">
         <v>0.2831</v>
       </c>
-      <c r="N28" s="33" t="n">
+      <c r="N28" s="36" t="n">
         <v>1.285</v>
       </c>
-      <c r="O28" s="33" t="n">
+      <c r="O28" s="36" t="n">
         <v>5.779</v>
       </c>
-      <c r="P28" s="33" t="n">
+      <c r="P28" s="36" t="n">
         <v>0.364</v>
       </c>
-      <c r="Q28" s="33" t="n">
+      <c r="Q28" s="36" t="n">
         <v>1.636</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="31" t="n">
+      <c r="B29" s="34" t="n">
         <v>0.728</v>
       </c>
-      <c r="C29" s="31" t="n">
+      <c r="C29" s="34" t="n">
         <v>3.448</v>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="34" t="n">
         <v>0.762</v>
       </c>
-      <c r="E29" s="31" t="n">
+      <c r="E29" s="34" t="n">
         <v>0.203</v>
       </c>
-      <c r="F29" s="32" t="n">
+      <c r="F29" s="35" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="G29" s="32" t="n">
+      <c r="G29" s="35" t="n">
         <v>1.047</v>
       </c>
-      <c r="H29" s="31" t="n">
+      <c r="H29" s="34" t="n">
         <v>0.445</v>
       </c>
-      <c r="I29" s="31" t="n">
+      <c r="I29" s="34" t="n">
         <v>1.465</v>
       </c>
-      <c r="J29" s="31" t="n">
+      <c r="J29" s="34" t="n">
         <v>0.466</v>
       </c>
-      <c r="K29" s="31" t="n">
+      <c r="K29" s="34" t="n">
         <v>1.534</v>
       </c>
-      <c r="L29" s="31" t="n">
+      <c r="L29" s="34" t="n">
         <v>3.588</v>
       </c>
-      <c r="M29" s="32" t="n">
+      <c r="M29" s="35" t="n">
         <v>0.2787</v>
       </c>
-      <c r="N29" s="33" t="n">
+      <c r="N29" s="36" t="n">
         <v>1.359</v>
       </c>
-      <c r="O29" s="33" t="n">
+      <c r="O29" s="36" t="n">
         <v>5.817</v>
       </c>
-      <c r="P29" s="33" t="n">
+      <c r="P29" s="36" t="n">
         <v>0.379</v>
       </c>
-      <c r="Q29" s="33" t="n">
+      <c r="Q29" s="36" t="n">
         <v>1.621</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="31" t="n">
+      <c r="B30" s="34" t="n">
         <v>0.707</v>
       </c>
-      <c r="C30" s="31" t="n">
+      <c r="C30" s="34" t="n">
         <v>3.497</v>
       </c>
-      <c r="D30" s="31" t="n">
+      <c r="D30" s="34" t="n">
         <v>0.738</v>
       </c>
-      <c r="E30" s="31" t="n">
+      <c r="E30" s="34" t="n">
         <v>0.194</v>
       </c>
-      <c r="F30" s="32" t="n">
+      <c r="F30" s="35" t="n">
         <v>0.9576</v>
       </c>
-      <c r="G30" s="32" t="n">
+      <c r="G30" s="35" t="n">
         <v>1.0442</v>
       </c>
-      <c r="H30" s="31" t="n">
+      <c r="H30" s="34" t="n">
         <v>0.461</v>
       </c>
-      <c r="I30" s="31" t="n">
+      <c r="I30" s="34" t="n">
         <v>1.454</v>
       </c>
-      <c r="J30" s="31" t="n">
+      <c r="J30" s="34" t="n">
         <v>0.482</v>
       </c>
-      <c r="K30" s="31" t="n">
+      <c r="K30" s="34" t="n">
         <v>1.518</v>
       </c>
-      <c r="L30" s="31" t="n">
+      <c r="L30" s="34" t="n">
         <v>3.64</v>
       </c>
-      <c r="M30" s="32" t="n">
+      <c r="M30" s="35" t="n">
         <v>0.2747</v>
       </c>
-      <c r="N30" s="33" t="n">
+      <c r="N30" s="36" t="n">
         <v>1.426</v>
       </c>
-      <c r="O30" s="33" t="n">
+      <c r="O30" s="36" t="n">
         <v>5.854</v>
       </c>
-      <c r="P30" s="33" t="n">
+      <c r="P30" s="36" t="n">
         <v>0.392</v>
       </c>
-      <c r="Q30" s="31" t="n">
+      <c r="Q30" s="34" t="n">
         <v>1.608</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="31" t="n">
+      <c r="B31" s="34" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C31" s="31" t="n">
+      <c r="C31" s="34" t="n">
         <v>3.545</v>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="34" t="n">
         <v>0.717</v>
       </c>
-      <c r="E31" s="31" t="n">
+      <c r="E31" s="34" t="n">
         <v>0.187</v>
       </c>
-      <c r="F31" s="32" t="n">
+      <c r="F31" s="35" t="n">
         <v>0.9599</v>
       </c>
-      <c r="G31" s="32" t="n">
+      <c r="G31" s="35" t="n">
         <v>1.0418</v>
       </c>
-      <c r="H31" s="31" t="n">
+      <c r="H31" s="34" t="n">
         <v>0.477</v>
       </c>
-      <c r="I31" s="31" t="n">
+      <c r="I31" s="34" t="n">
         <v>1.443</v>
       </c>
-      <c r="J31" s="31" t="n">
+      <c r="J31" s="34" t="n">
         <v>0.497</v>
       </c>
-      <c r="K31" s="31" t="n">
+      <c r="K31" s="34" t="n">
         <v>1.503</v>
       </c>
-      <c r="L31" s="31" t="n">
+      <c r="L31" s="34" t="n">
         <v>3.689</v>
       </c>
-      <c r="M31" s="32" t="n">
+      <c r="M31" s="35" t="n">
         <v>0.2711</v>
       </c>
-      <c r="N31" s="33" t="n">
+      <c r="N31" s="36" t="n">
         <v>1.49</v>
       </c>
-      <c r="O31" s="33" t="n">
+      <c r="O31" s="36" t="n">
         <v>5.888</v>
       </c>
-      <c r="P31" s="33" t="n">
+      <c r="P31" s="36" t="n">
         <v>0.404</v>
       </c>
-      <c r="Q31" s="33" t="n">
+      <c r="Q31" s="36" t="n">
         <v>1.596</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="34" t="n">
         <v>0.671</v>
       </c>
-      <c r="C32" s="31" t="n">
+      <c r="C32" s="34" t="n">
         <v>3.592</v>
       </c>
-      <c r="D32" s="31" t="n">
+      <c r="D32" s="34" t="n">
         <v>0.697</v>
       </c>
-      <c r="E32" s="31" t="n">
+      <c r="E32" s="34" t="n">
         <v>0.18</v>
       </c>
-      <c r="F32" s="32" t="n">
+      <c r="F32" s="35" t="n">
         <v>0.9619</v>
       </c>
-      <c r="G32" s="32" t="n">
+      <c r="G32" s="35" t="n">
         <v>1.0396</v>
       </c>
-      <c r="H32" s="31" t="n">
+      <c r="H32" s="34" t="n">
         <v>0.491</v>
       </c>
-      <c r="I32" s="31" t="n">
+      <c r="I32" s="34" t="n">
         <v>1.433</v>
       </c>
-      <c r="J32" s="31" t="n">
+      <c r="J32" s="34" t="n">
         <v>0.51</v>
       </c>
-      <c r="K32" s="31" t="n">
+      <c r="K32" s="34" t="n">
         <v>1.49</v>
       </c>
-      <c r="L32" s="31" t="n">
+      <c r="L32" s="34" t="n">
         <v>3.735</v>
       </c>
-      <c r="M32" s="32" t="n">
+      <c r="M32" s="35" t="n">
         <v>0.2677</v>
       </c>
-      <c r="N32" s="33" t="n">
+      <c r="N32" s="36" t="n">
         <v>1.548</v>
       </c>
-      <c r="O32" s="33" t="n">
+      <c r="O32" s="36" t="n">
         <v>5.922</v>
       </c>
-      <c r="P32" s="33" t="n">
+      <c r="P32" s="36" t="n">
         <v>0.414</v>
       </c>
-      <c r="Q32" s="33" t="n">
+      <c r="Q32" s="36" t="n">
         <v>1.586</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="34" t="n">
         <v>0.655</v>
       </c>
-      <c r="C33" s="31" t="n">
+      <c r="C33" s="34" t="n">
         <v>3.639</v>
       </c>
-      <c r="D33" s="31" t="n">
+      <c r="D33" s="34" t="n">
         <v>0.679</v>
       </c>
-      <c r="E33" s="31" t="n">
+      <c r="E33" s="34" t="n">
         <v>0.173</v>
       </c>
-      <c r="F33" s="32" t="n">
+      <c r="F33" s="35" t="n">
         <v>0.9638</v>
       </c>
-      <c r="G33" s="32" t="n">
+      <c r="G33" s="35" t="n">
         <v>1.0376</v>
       </c>
-      <c r="H33" s="31" t="n">
+      <c r="H33" s="34" t="n">
         <v>0.504</v>
       </c>
-      <c r="I33" s="31" t="n">
+      <c r="I33" s="34" t="n">
         <v>1.424</v>
       </c>
-      <c r="J33" s="31" t="n">
+      <c r="J33" s="34" t="n">
         <v>0.523</v>
       </c>
-      <c r="K33" s="31" t="n">
+      <c r="K33" s="34" t="n">
         <v>1.477</v>
       </c>
-      <c r="L33" s="31" t="n">
+      <c r="L33" s="34" t="n">
         <v>3.778</v>
       </c>
-      <c r="M33" s="32" t="n">
+      <c r="M33" s="35" t="n">
         <v>0.2647</v>
       </c>
-      <c r="N33" s="33" t="n">
+      <c r="N33" s="36" t="n">
         <v>1.606</v>
       </c>
-      <c r="O33" s="33" t="n">
+      <c r="O33" s="36" t="n">
         <v>5.95</v>
       </c>
-      <c r="P33" s="31" t="n">
+      <c r="P33" s="34" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q33" s="31" t="n">
+      <c r="Q33" s="34" t="n">
         <v>1.575</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="34" t="n">
         <v>0.64</v>
       </c>
-      <c r="C34" s="31" t="n">
+      <c r="C34" s="34" t="n">
         <v>3.684</v>
       </c>
-      <c r="D34" s="31" t="n">
+      <c r="D34" s="34" t="n">
         <v>0.662</v>
       </c>
-      <c r="E34" s="31" t="n">
+      <c r="E34" s="34" t="n">
         <v>0.167</v>
       </c>
-      <c r="F34" s="32" t="n">
+      <c r="F34" s="35" t="n">
         <v>0.9655</v>
       </c>
-      <c r="G34" s="32" t="n">
+      <c r="G34" s="35" t="n">
         <v>1.0358</v>
       </c>
-      <c r="H34" s="31" t="n">
+      <c r="H34" s="34" t="n">
         <v>0.516</v>
       </c>
-      <c r="I34" s="31" t="n">
+      <c r="I34" s="34" t="n">
         <v>1.415</v>
       </c>
-      <c r="J34" s="31" t="n">
+      <c r="J34" s="34" t="n">
         <v>0.534</v>
       </c>
-      <c r="K34" s="31" t="n">
+      <c r="K34" s="34" t="n">
         <v>1.466</v>
       </c>
-      <c r="L34" s="31" t="n">
+      <c r="L34" s="34" t="n">
         <v>3.819</v>
       </c>
-      <c r="M34" s="32" t="n">
+      <c r="M34" s="35" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N34" s="31" t="n">
+      <c r="N34" s="34" t="n">
         <v>1.659</v>
       </c>
-      <c r="O34" s="31" t="n">
+      <c r="O34" s="34" t="n">
         <v>5.979</v>
       </c>
-      <c r="P34" s="31" t="n">
+      <c r="P34" s="34" t="n">
         <v>0.434</v>
       </c>
-      <c r="Q34" s="31" t="n">
+      <c r="Q34" s="34" t="n">
         <v>1.566</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="34" t="n">
         <v>0.626</v>
       </c>
-      <c r="C35" s="31" t="n">
+      <c r="C35" s="34" t="n">
         <v>3.729</v>
       </c>
-      <c r="D35" s="31" t="n">
+      <c r="D35" s="34" t="n">
         <v>0.647</v>
       </c>
-      <c r="E35" s="31" t="n">
+      <c r="E35" s="34" t="n">
         <v>0.162</v>
       </c>
-      <c r="F35" s="32" t="n">
+      <c r="F35" s="35" t="n">
         <v>0.967</v>
       </c>
-      <c r="G35" s="32" t="n">
+      <c r="G35" s="35" t="n">
         <v>1.0342</v>
       </c>
-      <c r="H35" s="31" t="n">
+      <c r="H35" s="34" t="n">
         <v>0.527</v>
       </c>
-      <c r="I35" s="31" t="n">
+      <c r="I35" s="34" t="n">
         <v>1.407</v>
       </c>
-      <c r="J35" s="31" t="n">
+      <c r="J35" s="34" t="n">
         <v>0.545</v>
       </c>
-      <c r="K35" s="31" t="n">
+      <c r="K35" s="34" t="n">
         <v>1.455</v>
       </c>
-      <c r="L35" s="31" t="n">
+      <c r="L35" s="34" t="n">
         <v>3.858</v>
       </c>
-      <c r="M35" s="32" t="n">
+      <c r="M35" s="35" t="n">
         <v>0.2592</v>
       </c>
-      <c r="N35" s="31" t="n">
+      <c r="N35" s="34" t="n">
         <v>1.71</v>
       </c>
-      <c r="O35" s="31" t="n">
+      <c r="O35" s="34" t="n">
         <v>6.006</v>
       </c>
-      <c r="P35" s="31" t="n">
+      <c r="P35" s="34" t="n">
         <v>0.443</v>
       </c>
-      <c r="Q35" s="31" t="n">
+      <c r="Q35" s="34" t="n">
         <v>1.557</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="31" t="n">
+      <c r="B36" s="34" t="n">
         <v>0.612</v>
       </c>
-      <c r="C36" s="31" t="n">
+      <c r="C36" s="34" t="n">
         <v>3.773</v>
       </c>
-      <c r="D36" s="31" t="n">
+      <c r="D36" s="34" t="n">
         <v>0.632</v>
       </c>
-      <c r="E36" s="31" t="n">
+      <c r="E36" s="34" t="n">
         <v>0.157</v>
       </c>
-      <c r="F36" s="32" t="n">
+      <c r="F36" s="35" t="n">
         <v>0.9684</v>
       </c>
-      <c r="G36" s="32" t="n">
+      <c r="G36" s="35" t="n">
         <v>1.0327</v>
       </c>
-      <c r="H36" s="31" t="n">
+      <c r="H36" s="34" t="n">
         <v>0.538</v>
       </c>
-      <c r="I36" s="31" t="n">
+      <c r="I36" s="34" t="n">
         <v>1.399</v>
       </c>
-      <c r="J36" s="31" t="n">
+      <c r="J36" s="34" t="n">
         <v>0.555</v>
       </c>
-      <c r="K36" s="31" t="n">
+      <c r="K36" s="34" t="n">
         <v>1.445</v>
       </c>
-      <c r="L36" s="31" t="n">
+      <c r="L36" s="34" t="n">
         <v>3.895</v>
       </c>
-      <c r="M36" s="32" t="n">
+      <c r="M36" s="35" t="n">
         <v>0.2567</v>
       </c>
-      <c r="N36" s="31" t="n">
+      <c r="N36" s="34" t="n">
         <v>1.759</v>
       </c>
-      <c r="O36" s="31" t="n">
+      <c r="O36" s="34" t="n">
         <v>6.031</v>
       </c>
-      <c r="P36" s="33" t="n">
+      <c r="P36" s="36" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q36" s="31" t="n">
+      <c r="Q36" s="34" t="n">
         <v>1.548</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="31" t="n">
+      <c r="B37" s="34" t="n">
         <v>0.6</v>
       </c>
-      <c r="C37" s="31" t="n">
+      <c r="C37" s="34" t="n">
         <v>3.816</v>
       </c>
-      <c r="D37" s="31" t="n">
+      <c r="D37" s="34" t="n">
         <v>0.619</v>
       </c>
-      <c r="E37" s="31" t="n">
+      <c r="E37" s="34" t="n">
         <v>0.153</v>
       </c>
-      <c r="F37" s="34" t="n">
+      <c r="F37" s="37" t="n">
         <v>0.9696</v>
       </c>
-      <c r="G37" s="32" t="n">
+      <c r="G37" s="35" t="n">
         <v>1.0313</v>
       </c>
-      <c r="H37" s="31" t="n">
+      <c r="H37" s="34" t="n">
         <v>0.548</v>
       </c>
-      <c r="I37" s="31" t="n">
+      <c r="I37" s="34" t="n">
         <v>1.392</v>
       </c>
-      <c r="J37" s="31" t="n">
+      <c r="J37" s="34" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="K37" s="31" t="n">
+      <c r="K37" s="34" t="n">
         <v>1.435</v>
       </c>
-      <c r="L37" s="31" t="n">
+      <c r="L37" s="34" t="n">
         <v>3.931</v>
       </c>
-      <c r="M37" s="32" t="n">
+      <c r="M37" s="35" t="n">
         <v>0.2544</v>
       </c>
-      <c r="N37" s="33" t="n">
+      <c r="N37" s="36" t="n">
         <v>1.804</v>
       </c>
-      <c r="O37" s="33" t="n">
+      <c r="O37" s="36" t="n">
         <v>6.058</v>
       </c>
-      <c r="P37" s="31" t="n">
+      <c r="P37" s="34" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q37" s="31" t="n">
+      <c r="Q37" s="34" t="n">
         <v>1.541</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>&gt;25</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="38" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr"/>
-      <c r="D38" s="35" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr"/>
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr"/>
-      <c r="F38" s="32" t="n">
+      <c r="E38" s="38" t="inlineStr"/>
+      <c r="F38" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="32" t="n">
+      <c r="G38" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="35" t="inlineStr">
+      <c r="H38" s="38" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="I38" s="35" t="inlineStr">
+      <c r="I38" s="38" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="J38" s="35" t="inlineStr">
+      <c r="J38" s="38" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="K38" s="35" t="inlineStr">
+      <c r="K38" s="38" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L38" s="35" t="inlineStr"/>
-      <c r="M38" s="35" t="inlineStr"/>
-      <c r="N38" s="35" t="inlineStr"/>
-      <c r="O38" s="35" t="inlineStr"/>
-      <c r="P38" s="35" t="inlineStr"/>
-      <c r="Q38" s="35" t="inlineStr"/>
+      <c r="L38" s="38" t="inlineStr"/>
+      <c r="M38" s="38" t="inlineStr"/>
+      <c r="N38" s="38" t="inlineStr"/>
+      <c r="O38" s="38" t="inlineStr"/>
+      <c r="P38" s="38" t="inlineStr"/>
+      <c r="Q38" s="38" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
@@ -7940,580 +9051,580 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="34" t="n">
         <v>1.128</v>
       </c>
-      <c r="C44" s="32" t="n">
+      <c r="C44" s="35" t="n">
         <v>0.5642</v>
       </c>
-      <c r="D44" s="32" t="n">
+      <c r="D44" s="35" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="E44" s="32" t="n">
+      <c r="E44" s="35" t="n">
         <v>0.8525</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="34" t="n">
         <v>1.693</v>
       </c>
-      <c r="C45" s="32" t="n">
+      <c r="C45" s="35" t="n">
         <v>0.7236</v>
       </c>
-      <c r="D45" s="32" t="n">
+      <c r="D45" s="35" t="n">
         <v>0.8862</v>
       </c>
-      <c r="E45" s="32" t="n">
+      <c r="E45" s="35" t="n">
         <v>0.8884</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="34" t="n">
         <v>2.059</v>
       </c>
-      <c r="C46" s="32" t="n">
+      <c r="C46" s="35" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="D46" s="32" t="n">
+      <c r="D46" s="35" t="n">
         <v>0.9213</v>
       </c>
-      <c r="E46" s="32" t="n">
+      <c r="E46" s="35" t="n">
         <v>0.8798</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="31" t="n">
+      <c r="B47" s="34" t="n">
         <v>2.326</v>
       </c>
-      <c r="C47" s="32" t="n">
+      <c r="C47" s="35" t="n">
         <v>0.8407</v>
       </c>
-      <c r="D47" s="32" t="n">
+      <c r="D47" s="35" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E47" s="32" t="n">
+      <c r="E47" s="35" t="n">
         <v>0.8641</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="34" t="n">
         <v>2.534</v>
       </c>
-      <c r="C48" s="32" t="n">
+      <c r="C48" s="35" t="n">
         <v>0.8686</v>
       </c>
-      <c r="D48" s="32" t="n">
+      <c r="D48" s="35" t="n">
         <v>0.9515</v>
       </c>
-      <c r="E48" s="32" t="n">
+      <c r="E48" s="35" t="n">
         <v>0.848</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="31" t="n">
+      <c r="B49" s="34" t="n">
         <v>2.704</v>
       </c>
-      <c r="C49" s="32" t="n">
+      <c r="C49" s="35" t="n">
         <v>0.8882</v>
       </c>
-      <c r="D49" s="32" t="n">
+      <c r="D49" s="35" t="n">
         <v>0.9594</v>
       </c>
-      <c r="E49" s="32" t="n">
+      <c r="E49" s="35" t="n">
         <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="31" t="n">
+      <c r="B50" s="34" t="n">
         <v>2.847</v>
       </c>
-      <c r="C50" s="32" t="n">
+      <c r="C50" s="35" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="D50" s="32" t="n">
+      <c r="D50" s="35" t="n">
         <v>0.965</v>
       </c>
-      <c r="E50" s="32" t="n">
+      <c r="E50" s="35" t="n">
         <v>0.8198</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="n">
+      <c r="A51" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="31" t="n">
+      <c r="B51" s="34" t="n">
         <v>2.97</v>
       </c>
-      <c r="C51" s="32" t="n">
+      <c r="C51" s="35" t="n">
         <v>0.9139</v>
       </c>
-      <c r="D51" s="32" t="n">
+      <c r="D51" s="35" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="E51" s="32" t="n">
+      <c r="E51" s="35" t="n">
         <v>0.8078</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="n">
+      <c r="A52" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="31" t="n">
+      <c r="B52" s="34" t="n">
         <v>3.078</v>
       </c>
-      <c r="C52" s="32" t="n">
+      <c r="C52" s="35" t="n">
         <v>0.9227</v>
       </c>
-      <c r="D52" s="32" t="n">
+      <c r="D52" s="35" t="n">
         <v>0.9727</v>
       </c>
-      <c r="E52" s="32" t="n">
+      <c r="E52" s="35" t="n">
         <v>0.7971</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="n">
+      <c r="A53" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="31" t="n">
+      <c r="B53" s="34" t="n">
         <v>3.173</v>
       </c>
-      <c r="C53" s="32" t="n">
+      <c r="C53" s="35" t="n">
         <v>0.93</v>
       </c>
-      <c r="D53" s="32" t="n">
+      <c r="D53" s="35" t="n">
         <v>0.9754</v>
       </c>
-      <c r="E53" s="32" t="n">
+      <c r="E53" s="35" t="n">
         <v>0.7873</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="n">
+      <c r="A54" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="31" t="n">
+      <c r="B54" s="34" t="n">
         <v>3.258</v>
       </c>
-      <c r="C54" s="32" t="n">
+      <c r="C54" s="35" t="n">
         <v>0.9359</v>
       </c>
-      <c r="D54" s="32" t="n">
+      <c r="D54" s="35" t="n">
         <v>0.9776</v>
       </c>
-      <c r="E54" s="34" t="n">
+      <c r="E54" s="37" t="n">
         <v>0.7785</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="31" t="n">
+      <c r="B55" s="34" t="n">
         <v>3.336</v>
       </c>
-      <c r="C55" s="32" t="n">
+      <c r="C55" s="35" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="D55" s="32" t="n">
+      <c r="D55" s="35" t="n">
         <v>0.9794</v>
       </c>
-      <c r="E55" s="32" t="n">
+      <c r="E55" s="35" t="n">
         <v>0.7704</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="n">
+      <c r="A56" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="31" t="n">
+      <c r="B56" s="34" t="n">
         <v>3.407</v>
       </c>
-      <c r="C56" s="32" t="n">
+      <c r="C56" s="35" t="n">
         <v>0.9453</v>
       </c>
-      <c r="D56" s="32" t="n">
+      <c r="D56" s="35" t="n">
         <v>0.981</v>
       </c>
-      <c r="E56" s="32" t="n">
+      <c r="E56" s="35" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="n">
+      <c r="A57" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="31" t="n">
+      <c r="B57" s="34" t="n">
         <v>3.472</v>
       </c>
-      <c r="C57" s="32" t="n">
+      <c r="C57" s="35" t="n">
         <v>0.949</v>
       </c>
-      <c r="D57" s="32" t="n">
+      <c r="D57" s="35" t="n">
         <v>0.9823</v>
       </c>
-      <c r="E57" s="32" t="n">
+      <c r="E57" s="35" t="n">
         <v>0.7562</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="n">
+      <c r="A58" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B58" s="31" t="n">
+      <c r="B58" s="34" t="n">
         <v>3.532</v>
       </c>
-      <c r="C58" s="32" t="n">
+      <c r="C58" s="35" t="n">
         <v>0.9523</v>
       </c>
-      <c r="D58" s="32" t="n">
+      <c r="D58" s="35" t="n">
         <v>0.9835</v>
       </c>
-      <c r="E58" s="32" t="n">
+      <c r="E58" s="35" t="n">
         <v>0.7499</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="n">
+      <c r="A59" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B59" s="31" t="n">
+      <c r="B59" s="34" t="n">
         <v>3.588</v>
       </c>
-      <c r="C59" s="32" t="n">
+      <c r="C59" s="35" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="D59" s="32" t="n">
+      <c r="D59" s="35" t="n">
         <v>0.9845</v>
       </c>
-      <c r="E59" s="32" t="n">
+      <c r="E59" s="35" t="n">
         <v>0.7441</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="n">
+      <c r="A60" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B60" s="31" t="n">
+      <c r="B60" s="34" t="n">
         <v>3.64</v>
       </c>
-      <c r="C60" s="32" t="n">
+      <c r="C60" s="35" t="n">
         <v>0.9576</v>
       </c>
-      <c r="D60" s="32" t="n">
+      <c r="D60" s="35" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="E60" s="32" t="n">
+      <c r="E60" s="35" t="n">
         <v>0.7386</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="n">
+      <c r="A61" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B61" s="31" t="n">
+      <c r="B61" s="34" t="n">
         <v>3.689</v>
       </c>
-      <c r="C61" s="32" t="n">
+      <c r="C61" s="35" t="n">
         <v>0.9599</v>
       </c>
-      <c r="D61" s="32" t="n">
+      <c r="D61" s="35" t="n">
         <v>0.9862</v>
       </c>
-      <c r="E61" s="32" t="n">
+      <c r="E61" s="35" t="n">
         <v>0.7335</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="n">
+      <c r="A62" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B62" s="31" t="n">
+      <c r="B62" s="34" t="n">
         <v>3.735</v>
       </c>
-      <c r="C62" s="32" t="n">
+      <c r="C62" s="35" t="n">
         <v>0.9619</v>
       </c>
-      <c r="D62" s="32" t="n">
+      <c r="D62" s="35" t="n">
         <v>0.9869</v>
       </c>
-      <c r="E62" s="32" t="n">
+      <c r="E62" s="35" t="n">
         <v>0.7287</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="n">
+      <c r="A63" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="31" t="n">
+      <c r="B63" s="34" t="n">
         <v>3.778</v>
       </c>
-      <c r="C63" s="32" t="n">
+      <c r="C63" s="35" t="n">
         <v>0.9638</v>
       </c>
-      <c r="D63" s="32" t="n">
+      <c r="D63" s="35" t="n">
         <v>0.9876</v>
       </c>
-      <c r="E63" s="34" t="n">
+      <c r="E63" s="37" t="n">
         <v>0.7272</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="n">
+      <c r="A64" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B64" s="31" t="n">
+      <c r="B64" s="34" t="n">
         <v>3.819</v>
       </c>
-      <c r="C64" s="32" t="n">
+      <c r="C64" s="35" t="n">
         <v>0.9655</v>
       </c>
-      <c r="D64" s="32" t="n">
+      <c r="D64" s="35" t="n">
         <v>0.9882</v>
       </c>
-      <c r="E64" s="32" t="n">
+      <c r="E64" s="35" t="n">
         <v>0.7199</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="n">
+      <c r="A65" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="31" t="n">
+      <c r="B65" s="34" t="n">
         <v>3.858</v>
       </c>
-      <c r="C65" s="32" t="n">
+      <c r="C65" s="35" t="n">
         <v>0.967</v>
       </c>
-      <c r="D65" s="32" t="n">
+      <c r="D65" s="35" t="n">
         <v>0.9887</v>
       </c>
-      <c r="E65" s="32" t="n">
+      <c r="E65" s="35" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="n">
+      <c r="A66" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="31" t="n">
+      <c r="B66" s="34" t="n">
         <v>3.895</v>
       </c>
-      <c r="C66" s="32" t="n">
+      <c r="C66" s="35" t="n">
         <v>0.9684</v>
       </c>
-      <c r="D66" s="32" t="n">
+      <c r="D66" s="35" t="n">
         <v>0.9892</v>
       </c>
-      <c r="E66" s="32" t="n">
+      <c r="E66" s="35" t="n">
         <v>0.7121</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="n">
+      <c r="A67" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B67" s="31" t="n">
+      <c r="B67" s="34" t="n">
         <v>3.931</v>
       </c>
-      <c r="C67" s="34" t="n">
+      <c r="C67" s="37" t="n">
         <v>0.9695</v>
       </c>
-      <c r="D67" s="32" t="n">
+      <c r="D67" s="35" t="n">
         <v>0.9896</v>
       </c>
-      <c r="E67" s="32" t="n">
+      <c r="E67" s="35" t="n">
         <v>0.7084</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="n">
+      <c r="A68" s="33" t="n">
         <v>30</v>
       </c>
-      <c r="B68" s="31" t="n">
+      <c r="B68" s="34" t="n">
         <v>4.086</v>
       </c>
-      <c r="C68" s="32" t="n">
+      <c r="C68" s="35" t="n">
         <v>0.9748</v>
       </c>
-      <c r="D68" s="32" t="n">
+      <c r="D68" s="35" t="n">
         <v>0.9915</v>
       </c>
-      <c r="E68" s="32" t="n">
+      <c r="E68" s="35" t="n">
         <v>0.6927</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="n">
+      <c r="A69" s="33" t="n">
         <v>35</v>
       </c>
-      <c r="B69" s="31" t="n">
+      <c r="B69" s="34" t="n">
         <v>4.213</v>
       </c>
-      <c r="C69" s="32" t="n">
+      <c r="C69" s="35" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D69" s="32" t="n">
+      <c r="D69" s="35" t="n">
         <v>0.9927</v>
       </c>
-      <c r="E69" s="32" t="n">
+      <c r="E69" s="35" t="n">
         <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="n">
+      <c r="A70" s="33" t="n">
         <v>40</v>
       </c>
-      <c r="B70" s="31" t="n">
+      <c r="B70" s="34" t="n">
         <v>4.322</v>
       </c>
-      <c r="C70" s="32" t="n">
+      <c r="C70" s="35" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D70" s="32" t="n">
+      <c r="D70" s="35" t="n">
         <v>0.9936</v>
       </c>
-      <c r="E70" s="32" t="n">
+      <c r="E70" s="35" t="n">
         <v>0.6692</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="n">
+      <c r="A71" s="33" t="n">
         <v>45</v>
       </c>
-      <c r="B71" s="31" t="n">
+      <c r="B71" s="34" t="n">
         <v>4.415</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C71" s="35" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D71" s="35" t="n">
         <v>0.9943</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E71" s="35" t="n">
         <v>0.6601</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="n">
+      <c r="A72" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B72" s="31" t="n">
+      <c r="B72" s="34" t="n">
         <v>4.498</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C72" s="35" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D72" s="35" t="n">
         <v>0.9949</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E72" s="35" t="n">
         <v>0.6521</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="n">
+      <c r="A73" s="33" t="n">
         <v>60</v>
       </c>
-      <c r="B73" s="31" t="n">
+      <c r="B73" s="34" t="n">
         <v>4.639</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C73" s="35" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D73" s="35" t="n">
         <v>0.9957</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E73" s="35" t="n">
         <v>0.6389</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="n">
+      <c r="A74" s="33" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B74" s="34" t="n">
         <v>4.755</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C74" s="35" t="n">
         <v>0.9892</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D74" s="35" t="n">
         <v>0.9963</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E74" s="35" t="n">
         <v>0.6283</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="n">
+      <c r="A75" s="33" t="n">
         <v>80</v>
       </c>
-      <c r="B75" s="31" t="n">
+      <c r="B75" s="34" t="n">
         <v>4.854</v>
       </c>
-      <c r="C75" s="32" t="n">
+      <c r="C75" s="35" t="n">
         <v>0.9906</v>
       </c>
-      <c r="D75" s="32" t="n">
+      <c r="D75" s="35" t="n">
         <v>0.9968</v>
       </c>
-      <c r="E75" s="32" t="n">
+      <c r="E75" s="35" t="n">
         <v>0.6194</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="n">
+      <c r="A76" s="33" t="n">
         <v>90</v>
       </c>
-      <c r="B76" s="31" t="n">
+      <c r="B76" s="34" t="n">
         <v>4.939</v>
       </c>
-      <c r="C76" s="32" t="n">
+      <c r="C76" s="35" t="n">
         <v>0.9916</v>
       </c>
-      <c r="D76" s="32" t="n">
+      <c r="D76" s="35" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E76" s="32" t="n">
+      <c r="E76" s="35" t="n">
         <v>0.6118</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="n">
+      <c r="A77" s="33" t="n">
         <v>100</v>
       </c>
-      <c r="B77" s="31" t="n">
+      <c r="B77" s="34" t="n">
         <v>5.015</v>
       </c>
-      <c r="C77" s="32" t="n">
+      <c r="C77" s="35" t="n">
         <v>0.9925</v>
       </c>
-      <c r="D77" s="32" t="n">
+      <c r="D77" s="35" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="E77" s="32" t="n">
+      <c r="E77" s="35" t="n">
         <v>0.6052</v>
       </c>
     </row>
@@ -8591,786 +9702,786 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="n">
+      <c r="A83" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="31" t="n">
+      <c r="B83" s="34" t="n">
         <v>2.121</v>
       </c>
-      <c r="C83" s="31" t="n">
+      <c r="C83" s="34" t="n">
         <v>1.88</v>
       </c>
-      <c r="D83" s="31" t="n">
+      <c r="D83" s="34" t="n">
         <v>2.659</v>
       </c>
-      <c r="E83" s="32" t="n">
+      <c r="E83" s="35" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="F83" s="32" t="n">
+      <c r="F83" s="35" t="n">
         <v>1.2533</v>
       </c>
-      <c r="G83" s="30" t="n">
+      <c r="G83" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="31" t="n">
+      <c r="H83" s="34" t="n">
         <v>3.267</v>
       </c>
-      <c r="I83" s="30" t="n">
+      <c r="I83" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="31" t="n">
+      <c r="J83" s="34" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30" t="n">
+      <c r="A84" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="B84" s="31" t="n">
+      <c r="B84" s="34" t="n">
         <v>2.606</v>
       </c>
-      <c r="C84" s="35" t="inlineStr"/>
-      <c r="D84" s="35" t="inlineStr"/>
-      <c r="E84" s="35" t="inlineStr"/>
-      <c r="F84" s="35" t="inlineStr"/>
-      <c r="G84" s="35" t="inlineStr"/>
-      <c r="H84" s="35" t="inlineStr"/>
-      <c r="I84" s="35" t="inlineStr"/>
-      <c r="J84" s="35" t="inlineStr"/>
+      <c r="C84" s="38" t="inlineStr"/>
+      <c r="D84" s="38" t="inlineStr"/>
+      <c r="E84" s="38" t="inlineStr"/>
+      <c r="F84" s="38" t="inlineStr"/>
+      <c r="G84" s="38" t="inlineStr"/>
+      <c r="H84" s="38" t="inlineStr"/>
+      <c r="I84" s="38" t="inlineStr"/>
+      <c r="J84" s="38" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="30" t="n">
+      <c r="A85" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="31" t="n">
+      <c r="B85" s="34" t="n">
         <v>1.732</v>
       </c>
-      <c r="C85" s="31" t="n">
+      <c r="C85" s="34" t="n">
         <v>1.023</v>
       </c>
-      <c r="D85" s="31" t="n">
+      <c r="D85" s="34" t="n">
         <v>1.954</v>
       </c>
-      <c r="E85" s="32" t="n">
+      <c r="E85" s="35" t="n">
         <v>0.8862</v>
       </c>
-      <c r="F85" s="32" t="n">
+      <c r="F85" s="35" t="n">
         <v>1.1284</v>
       </c>
-      <c r="G85" s="30" t="n">
+      <c r="G85" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="31" t="n">
+      <c r="H85" s="34" t="n">
         <v>2.568</v>
       </c>
-      <c r="I85" s="30" t="n">
+      <c r="I85" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="31" t="n">
+      <c r="J85" s="34" t="n">
         <v>2.276</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30" t="n">
+      <c r="A86" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="31" t="n">
+      <c r="B86" s="34" t="n">
         <v>1.5</v>
       </c>
-      <c r="C86" s="31" t="n">
+      <c r="C86" s="34" t="n">
         <v>0.729</v>
       </c>
-      <c r="D86" s="31" t="n">
+      <c r="D86" s="34" t="n">
         <v>1.628</v>
       </c>
-      <c r="E86" s="32" t="n">
+      <c r="E86" s="35" t="n">
         <v>0.9213</v>
       </c>
-      <c r="F86" s="32" t="n">
+      <c r="F86" s="35" t="n">
         <v>1.0854</v>
       </c>
-      <c r="G86" s="30" t="n">
+      <c r="G86" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="31" t="n">
+      <c r="H86" s="34" t="n">
         <v>2.266</v>
       </c>
-      <c r="I86" s="30" t="n">
+      <c r="I86" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="31" t="n">
+      <c r="J86" s="34" t="n">
         <v>2.088</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="n">
+      <c r="A87" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="31" t="n">
+      <c r="B87" s="34" t="n">
         <v>1.342</v>
       </c>
-      <c r="C87" s="31" t="n">
+      <c r="C87" s="34" t="n">
         <v>0.577</v>
       </c>
-      <c r="D87" s="31" t="n">
+      <c r="D87" s="34" t="n">
         <v>1.427</v>
       </c>
-      <c r="E87" s="32" t="n">
+      <c r="E87" s="35" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F87" s="32" t="n">
+      <c r="F87" s="35" t="n">
         <v>1.0638</v>
       </c>
-      <c r="G87" s="30" t="n">
+      <c r="G87" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="31" t="n">
+      <c r="H87" s="34" t="n">
         <v>2.089</v>
       </c>
-      <c r="I87" s="30" t="n">
+      <c r="I87" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="31" t="n">
+      <c r="J87" s="34" t="n">
         <v>1.964</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30" t="n">
+      <c r="A88" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B88" s="31" t="n">
+      <c r="B88" s="34" t="n">
         <v>1.225</v>
       </c>
-      <c r="C88" s="31" t="n">
+      <c r="C88" s="34" t="n">
         <v>0.483</v>
       </c>
-      <c r="D88" s="31" t="n">
+      <c r="D88" s="34" t="n">
         <v>1.287</v>
       </c>
-      <c r="E88" s="32" t="n">
+      <c r="E88" s="35" t="n">
         <v>0.9515</v>
       </c>
-      <c r="F88" s="32" t="n">
+      <c r="F88" s="35" t="n">
         <v>1.051</v>
       </c>
-      <c r="G88" s="31" t="n">
+      <c r="G88" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="H88" s="31" t="n">
+      <c r="H88" s="34" t="n">
         <v>1.97</v>
       </c>
-      <c r="I88" s="31" t="n">
+      <c r="I88" s="34" t="n">
         <v>0.029</v>
       </c>
-      <c r="J88" s="31" t="n">
+      <c r="J88" s="34" t="n">
         <v>1.874</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30" t="n">
+      <c r="A89" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B89" s="31" t="n">
+      <c r="B89" s="34" t="n">
         <v>1.134</v>
       </c>
-      <c r="C89" s="31" t="n">
+      <c r="C89" s="34" t="n">
         <v>0.419</v>
       </c>
-      <c r="D89" s="31" t="n">
+      <c r="D89" s="34" t="n">
         <v>1.182</v>
       </c>
-      <c r="E89" s="32" t="n">
+      <c r="E89" s="35" t="n">
         <v>0.9594</v>
       </c>
-      <c r="F89" s="32" t="n">
+      <c r="F89" s="35" t="n">
         <v>1.0423</v>
       </c>
-      <c r="G89" s="31" t="n">
+      <c r="G89" s="34" t="n">
         <v>0.118</v>
       </c>
-      <c r="H89" s="31" t="n">
+      <c r="H89" s="34" t="n">
         <v>1.882</v>
       </c>
-      <c r="I89" s="31" t="n">
+      <c r="I89" s="34" t="n">
         <v>0.113</v>
       </c>
-      <c r="J89" s="31" t="n">
+      <c r="J89" s="34" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30" t="n">
+      <c r="A90" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="31" t="n">
+      <c r="B90" s="34" t="n">
         <v>1.061</v>
       </c>
-      <c r="C90" s="31" t="n">
+      <c r="C90" s="34" t="n">
         <v>0.373</v>
       </c>
-      <c r="D90" s="31" t="n">
+      <c r="D90" s="34" t="n">
         <v>1.099</v>
       </c>
-      <c r="E90" s="32" t="n">
+      <c r="E90" s="35" t="n">
         <v>0.965</v>
       </c>
-      <c r="F90" s="32" t="n">
+      <c r="F90" s="35" t="n">
         <v>1.0363</v>
       </c>
-      <c r="G90" s="31" t="n">
+      <c r="G90" s="34" t="n">
         <v>0.185</v>
       </c>
-      <c r="H90" s="31" t="n">
+      <c r="H90" s="34" t="n">
         <v>1.815</v>
       </c>
-      <c r="I90" s="31" t="n">
+      <c r="I90" s="34" t="n">
         <v>0.179</v>
       </c>
-      <c r="J90" s="31" t="n">
+      <c r="J90" s="34" t="n">
         <v>1.751</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30" t="n">
+      <c r="A91" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="31" t="n">
+      <c r="B91" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="31" t="n">
+      <c r="C91" s="34" t="n">
         <v>0.337</v>
       </c>
-      <c r="D91" s="31" t="n">
+      <c r="D91" s="34" t="n">
         <v>1.032</v>
       </c>
-      <c r="E91" s="32" t="n">
+      <c r="E91" s="35" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="F91" s="32" t="n">
+      <c r="F91" s="35" t="n">
         <v>1.0317</v>
       </c>
-      <c r="G91" s="31" t="n">
+      <c r="G91" s="34" t="n">
         <v>0.239</v>
       </c>
-      <c r="H91" s="31" t="n">
+      <c r="H91" s="34" t="n">
         <v>1.761</v>
       </c>
-      <c r="I91" s="31" t="n">
+      <c r="I91" s="34" t="n">
         <v>0.232</v>
       </c>
-      <c r="J91" s="31" t="n">
+      <c r="J91" s="34" t="n">
         <v>1.707</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30" t="n">
+      <c r="A92" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B92" s="31" t="n">
+      <c r="B92" s="34" t="n">
         <v>0.949</v>
       </c>
-      <c r="C92" s="31" t="n">
+      <c r="C92" s="34" t="n">
         <v>0.308</v>
       </c>
-      <c r="D92" s="31" t="n">
+      <c r="D92" s="34" t="n">
         <v>0.975</v>
       </c>
-      <c r="E92" s="32" t="n">
+      <c r="E92" s="35" t="n">
         <v>0.9727</v>
       </c>
-      <c r="F92" s="32" t="n">
+      <c r="F92" s="35" t="n">
         <v>1.0281</v>
       </c>
-      <c r="G92" s="31" t="n">
+      <c r="G92" s="34" t="n">
         <v>0.284</v>
       </c>
-      <c r="H92" s="31" t="n">
+      <c r="H92" s="34" t="n">
         <v>1.716</v>
       </c>
-      <c r="I92" s="31" t="n">
+      <c r="I92" s="34" t="n">
         <v>0.276</v>
       </c>
-      <c r="J92" s="31" t="n">
+      <c r="J92" s="34" t="n">
         <v>1.669</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30" t="n">
+      <c r="A93" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B93" s="31" t="n">
+      <c r="B93" s="34" t="n">
         <v>0.905</v>
       </c>
-      <c r="C93" s="31" t="n">
+      <c r="C93" s="34" t="n">
         <v>0.285</v>
       </c>
-      <c r="D93" s="31" t="n">
+      <c r="D93" s="34" t="n">
         <v>0.927</v>
       </c>
-      <c r="E93" s="32" t="n">
+      <c r="E93" s="35" t="n">
         <v>0.9754</v>
       </c>
-      <c r="F93" s="32" t="n">
+      <c r="F93" s="35" t="n">
         <v>1.0252</v>
       </c>
-      <c r="G93" s="31" t="n">
+      <c r="G93" s="34" t="n">
         <v>0.321</v>
       </c>
-      <c r="H93" s="31" t="n">
+      <c r="H93" s="34" t="n">
         <v>1.679</v>
       </c>
-      <c r="I93" s="31" t="n">
+      <c r="I93" s="34" t="n">
         <v>0.313</v>
       </c>
-      <c r="J93" s="31" t="n">
+      <c r="J93" s="34" t="n">
         <v>1.637</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30" t="n">
+      <c r="A94" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B94" s="31" t="n">
+      <c r="B94" s="34" t="n">
         <v>0.866</v>
       </c>
-      <c r="C94" s="31" t="n">
+      <c r="C94" s="34" t="n">
         <v>0.266</v>
       </c>
-      <c r="D94" s="31" t="n">
+      <c r="D94" s="34" t="n">
         <v>0.886</v>
       </c>
-      <c r="E94" s="32" t="n">
+      <c r="E94" s="35" t="n">
         <v>0.9776</v>
       </c>
-      <c r="F94" s="32" t="n">
+      <c r="F94" s="35" t="n">
         <v>1.0229</v>
       </c>
-      <c r="G94" s="31" t="n">
+      <c r="G94" s="34" t="n">
         <v>0.354</v>
       </c>
-      <c r="H94" s="31" t="n">
+      <c r="H94" s="34" t="n">
         <v>1.646</v>
       </c>
-      <c r="I94" s="31" t="n">
+      <c r="I94" s="34" t="n">
         <v>0.346</v>
       </c>
-      <c r="J94" s="31" t="n">
+      <c r="J94" s="34" t="n">
         <v>1.61</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30" t="n">
+      <c r="A95" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B95" s="31" t="n">
+      <c r="B95" s="34" t="n">
         <v>0.832</v>
       </c>
-      <c r="C95" s="31" t="n">
+      <c r="C95" s="34" t="n">
         <v>0.249</v>
       </c>
-      <c r="D95" s="31" t="n">
+      <c r="D95" s="34" t="n">
         <v>0.85</v>
       </c>
-      <c r="E95" s="32" t="n">
+      <c r="E95" s="35" t="n">
         <v>0.9794</v>
       </c>
-      <c r="F95" s="32" t="n">
+      <c r="F95" s="35" t="n">
         <v>1.021</v>
       </c>
-      <c r="G95" s="31" t="n">
+      <c r="G95" s="34" t="n">
         <v>0.382</v>
       </c>
-      <c r="H95" s="31" t="n">
+      <c r="H95" s="34" t="n">
         <v>1.618</v>
       </c>
-      <c r="I95" s="31" t="n">
+      <c r="I95" s="34" t="n">
         <v>0.374</v>
       </c>
-      <c r="J95" s="31" t="n">
+      <c r="J95" s="34" t="n">
         <v>1.585</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30" t="n">
+      <c r="A96" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B96" s="31" t="n">
+      <c r="B96" s="34" t="n">
         <v>0.802</v>
       </c>
-      <c r="C96" s="31" t="n">
+      <c r="C96" s="34" t="n">
         <v>0.235</v>
       </c>
-      <c r="D96" s="31" t="n">
+      <c r="D96" s="34" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E96" s="32" t="n">
+      <c r="E96" s="35" t="n">
         <v>0.981</v>
       </c>
-      <c r="F96" s="32" t="n">
+      <c r="F96" s="35" t="n">
         <v>1.0194</v>
       </c>
-      <c r="G96" s="31" t="n">
+      <c r="G96" s="34" t="n">
         <v>0.406</v>
       </c>
-      <c r="H96" s="31" t="n">
+      <c r="H96" s="34" t="n">
         <v>1.594</v>
       </c>
-      <c r="I96" s="31" t="n">
+      <c r="I96" s="34" t="n">
         <v>0.399</v>
       </c>
-      <c r="J96" s="31" t="n">
+      <c r="J96" s="34" t="n">
         <v>1.563</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="30" t="n">
+      <c r="A97" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B97" s="31" t="n">
+      <c r="B97" s="34" t="n">
         <v>0.775</v>
       </c>
-      <c r="C97" s="31" t="n">
+      <c r="C97" s="34" t="n">
         <v>0.223</v>
       </c>
-      <c r="D97" s="31" t="n">
+      <c r="D97" s="34" t="n">
         <v>0.789</v>
       </c>
-      <c r="E97" s="32" t="n">
+      <c r="E97" s="35" t="n">
         <v>0.9823</v>
       </c>
-      <c r="F97" s="32" t="n">
+      <c r="F97" s="35" t="n">
         <v>1.018</v>
       </c>
-      <c r="G97" s="31" t="n">
+      <c r="G97" s="34" t="n">
         <v>0.428</v>
       </c>
-      <c r="H97" s="31" t="n">
+      <c r="H97" s="34" t="n">
         <v>1.572</v>
       </c>
-      <c r="I97" s="31" t="n">
+      <c r="I97" s="34" t="n">
         <v>0.421</v>
       </c>
-      <c r="J97" s="31" t="n">
+      <c r="J97" s="34" t="n">
         <v>1.544</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30" t="n">
+      <c r="A98" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B98" s="31" t="n">
+      <c r="B98" s="34" t="n">
         <v>0.75</v>
       </c>
-      <c r="C98" s="31" t="n">
+      <c r="C98" s="34" t="n">
         <v>0.212</v>
       </c>
-      <c r="D98" s="31" t="n">
+      <c r="D98" s="34" t="n">
         <v>0.763</v>
       </c>
-      <c r="E98" s="32" t="n">
+      <c r="E98" s="35" t="n">
         <v>0.9835</v>
       </c>
-      <c r="F98" s="32" t="n">
+      <c r="F98" s="35" t="n">
         <v>1.0168</v>
       </c>
-      <c r="G98" s="31" t="n">
+      <c r="G98" s="34" t="n">
         <v>0.448</v>
       </c>
-      <c r="H98" s="31" t="n">
+      <c r="H98" s="34" t="n">
         <v>1.552</v>
       </c>
-      <c r="I98" s="31" t="n">
+      <c r="I98" s="34" t="n">
         <v>0.44</v>
       </c>
-      <c r="J98" s="31" t="n">
+      <c r="J98" s="34" t="n">
         <v>1.526</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30" t="n">
+      <c r="A99" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="31" t="n">
+      <c r="B99" s="34" t="n">
         <v>0.728</v>
       </c>
-      <c r="C99" s="31" t="n">
+      <c r="C99" s="34" t="n">
         <v>0.203</v>
       </c>
-      <c r="D99" s="31" t="n">
+      <c r="D99" s="34" t="n">
         <v>0.739</v>
       </c>
-      <c r="E99" s="32" t="n">
+      <c r="E99" s="35" t="n">
         <v>0.9845</v>
       </c>
-      <c r="F99" s="32" t="n">
+      <c r="F99" s="35" t="n">
         <v>1.0157</v>
       </c>
-      <c r="G99" s="31" t="n">
+      <c r="G99" s="34" t="n">
         <v>0.466</v>
       </c>
-      <c r="H99" s="31" t="n">
+      <c r="H99" s="34" t="n">
         <v>1.534</v>
       </c>
-      <c r="I99" s="31" t="n">
+      <c r="I99" s="34" t="n">
         <v>0.458</v>
       </c>
-      <c r="J99" s="31" t="n">
+      <c r="J99" s="34" t="n">
         <v>1.511</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30" t="n">
+      <c r="A100" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B100" s="31" t="n">
+      <c r="B100" s="34" t="n">
         <v>0.707</v>
       </c>
-      <c r="C100" s="31" t="n">
+      <c r="C100" s="34" t="n">
         <v>0.194</v>
       </c>
-      <c r="D100" s="31" t="n">
+      <c r="D100" s="34" t="n">
         <v>0.718</v>
       </c>
-      <c r="E100" s="32" t="n">
+      <c r="E100" s="35" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="F100" s="32" t="n">
+      <c r="F100" s="35" t="n">
         <v>1.0148</v>
       </c>
-      <c r="G100" s="31" t="n">
+      <c r="G100" s="34" t="n">
         <v>0.482</v>
       </c>
-      <c r="H100" s="31" t="n">
+      <c r="H100" s="34" t="n">
         <v>1.518</v>
       </c>
-      <c r="I100" s="31" t="n">
+      <c r="I100" s="34" t="n">
         <v>0.475</v>
       </c>
-      <c r="J100" s="31" t="n">
+      <c r="J100" s="34" t="n">
         <v>1.496</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30" t="n">
+      <c r="A101" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B101" s="31" t="n">
+      <c r="B101" s="34" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C101" s="31" t="n">
+      <c r="C101" s="34" t="n">
         <v>0.187</v>
       </c>
-      <c r="D101" s="31" t="n">
+      <c r="D101" s="34" t="n">
         <v>0.698</v>
       </c>
-      <c r="E101" s="32" t="n">
+      <c r="E101" s="35" t="n">
         <v>0.9862</v>
       </c>
-      <c r="F101" s="32" t="n">
+      <c r="F101" s="35" t="n">
         <v>1.014</v>
       </c>
-      <c r="G101" s="31" t="n">
+      <c r="G101" s="34" t="n">
         <v>0.497</v>
       </c>
-      <c r="H101" s="31" t="n">
+      <c r="H101" s="34" t="n">
         <v>1.503</v>
       </c>
-      <c r="I101" s="31" t="n">
+      <c r="I101" s="34" t="n">
         <v>0.49</v>
       </c>
-      <c r="J101" s="31" t="n">
+      <c r="J101" s="34" t="n">
         <v>1.483</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30" t="n">
+      <c r="A102" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B102" s="31" t="n">
+      <c r="B102" s="34" t="n">
         <v>0.671</v>
       </c>
-      <c r="C102" s="31" t="n">
+      <c r="C102" s="34" t="n">
         <v>0.18</v>
       </c>
-      <c r="D102" s="31" t="n">
+      <c r="D102" s="34" t="n">
         <v>0.68</v>
       </c>
-      <c r="E102" s="32" t="n">
+      <c r="E102" s="35" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F102" s="32" t="n">
+      <c r="F102" s="35" t="n">
         <v>1.0133</v>
       </c>
-      <c r="G102" s="31" t="n">
+      <c r="G102" s="34" t="n">
         <v>0.51</v>
       </c>
-      <c r="H102" s="31" t="n">
+      <c r="H102" s="34" t="n">
         <v>1.49</v>
       </c>
-      <c r="I102" s="31" t="n">
+      <c r="I102" s="34" t="n">
         <v>0.504</v>
       </c>
-      <c r="J102" s="31" t="n">
+      <c r="J102" s="34" t="n">
         <v>1.47</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30" t="n">
+      <c r="A103" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B103" s="31" t="n">
+      <c r="B103" s="34" t="n">
         <v>0.655</v>
       </c>
-      <c r="C103" s="31" t="n">
+      <c r="C103" s="34" t="n">
         <v>0.173</v>
       </c>
-      <c r="D103" s="31" t="n">
+      <c r="D103" s="34" t="n">
         <v>0.663</v>
       </c>
-      <c r="E103" s="32" t="n">
+      <c r="E103" s="35" t="n">
         <v>0.9876</v>
       </c>
-      <c r="F103" s="32" t="n">
+      <c r="F103" s="35" t="n">
         <v>1.0126</v>
       </c>
-      <c r="G103" s="31" t="n">
+      <c r="G103" s="34" t="n">
         <v>0.523</v>
       </c>
-      <c r="H103" s="31" t="n">
+      <c r="H103" s="34" t="n">
         <v>1.477</v>
       </c>
-      <c r="I103" s="31" t="n">
+      <c r="I103" s="34" t="n">
         <v>0.516</v>
       </c>
-      <c r="J103" s="31" t="n">
+      <c r="J103" s="34" t="n">
         <v>1.459</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30" t="n">
+      <c r="A104" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B104" s="31" t="n">
+      <c r="B104" s="34" t="n">
         <v>0.64</v>
       </c>
-      <c r="C104" s="31" t="n">
+      <c r="C104" s="34" t="n">
         <v>0.167</v>
       </c>
-      <c r="D104" s="31" t="n">
+      <c r="D104" s="34" t="n">
         <v>0.647</v>
       </c>
-      <c r="E104" s="32" t="n">
+      <c r="E104" s="35" t="n">
         <v>0.9882</v>
       </c>
-      <c r="F104" s="32" t="n">
+      <c r="F104" s="35" t="n">
         <v>1.0119</v>
       </c>
-      <c r="G104" s="31" t="n">
+      <c r="G104" s="34" t="n">
         <v>0.534</v>
       </c>
-      <c r="H104" s="31" t="n">
+      <c r="H104" s="34" t="n">
         <v>1.466</v>
       </c>
-      <c r="I104" s="31" t="n">
+      <c r="I104" s="34" t="n">
         <v>0.528</v>
       </c>
-      <c r="J104" s="31" t="n">
+      <c r="J104" s="34" t="n">
         <v>1.448</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30" t="n">
+      <c r="A105" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B105" s="31" t="n">
+      <c r="B105" s="34" t="n">
         <v>0.626</v>
       </c>
-      <c r="C105" s="31" t="n">
+      <c r="C105" s="34" t="n">
         <v>0.162</v>
       </c>
-      <c r="D105" s="31" t="n">
+      <c r="D105" s="34" t="n">
         <v>0.633</v>
       </c>
-      <c r="E105" s="32" t="n">
+      <c r="E105" s="35" t="n">
         <v>0.9887</v>
       </c>
-      <c r="F105" s="32" t="n">
+      <c r="F105" s="35" t="n">
         <v>1.0114</v>
       </c>
-      <c r="G105" s="31" t="n">
+      <c r="G105" s="34" t="n">
         <v>0.545</v>
       </c>
-      <c r="H105" s="31" t="n">
+      <c r="H105" s="34" t="n">
         <v>1.455</v>
       </c>
-      <c r="I105" s="31" t="n">
+      <c r="I105" s="34" t="n">
         <v>0.539</v>
       </c>
-      <c r="J105" s="31" t="n">
+      <c r="J105" s="34" t="n">
         <v>1.438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30" t="n">
+      <c r="A106" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B106" s="31" t="n">
+      <c r="B106" s="34" t="n">
         <v>0.612</v>
       </c>
-      <c r="C106" s="31" t="n">
+      <c r="C106" s="34" t="n">
         <v>0.157</v>
       </c>
-      <c r="D106" s="31" t="n">
+      <c r="D106" s="34" t="n">
         <v>0.619</v>
       </c>
-      <c r="E106" s="32" t="n">
+      <c r="E106" s="35" t="n">
         <v>0.9892</v>
       </c>
-      <c r="F106" s="32" t="n">
+      <c r="F106" s="35" t="n">
         <v>1.0109</v>
       </c>
-      <c r="G106" s="31" t="n">
+      <c r="G106" s="34" t="n">
         <v>0.555</v>
       </c>
-      <c r="H106" s="31" t="n">
+      <c r="H106" s="34" t="n">
         <v>1.445</v>
       </c>
-      <c r="I106" s="31" t="n">
+      <c r="I106" s="34" t="n">
         <v>0.549</v>
       </c>
-      <c r="J106" s="31" t="n">
+      <c r="J106" s="34" t="n">
         <v>1.429</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="30" t="n">
+      <c r="A107" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B107" s="31" t="n">
+      <c r="B107" s="34" t="n">
         <v>0.6</v>
       </c>
-      <c r="C107" s="31" t="n">
+      <c r="C107" s="34" t="n">
         <v>0.153</v>
       </c>
-      <c r="D107" s="31" t="n">
+      <c r="D107" s="34" t="n">
         <v>0.606</v>
       </c>
-      <c r="E107" s="32" t="n">
+      <c r="E107" s="35" t="n">
         <v>0.9896</v>
       </c>
-      <c r="F107" s="32" t="n">
+      <c r="F107" s="35" t="n">
         <v>1.0105</v>
       </c>
-      <c r="G107" s="31" t="n">
+      <c r="G107" s="34" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H107" s="31" t="n">
+      <c r="H107" s="34" t="n">
         <v>1.435</v>
       </c>
-      <c r="I107" s="31" t="n">
+      <c r="I107" s="34" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J107" s="31" t="n">
+      <c r="J107" s="34" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -9443,698 +10554,698 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="30" t="n">
+      <c r="A113" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="31" t="n">
+      <c r="B113" s="34" t="n">
         <v>1.128</v>
       </c>
-      <c r="C113" s="32" t="n">
+      <c r="C113" s="35" t="n">
         <v>0.8865</v>
       </c>
-      <c r="D113" s="31" t="n">
+      <c r="D113" s="34" t="n">
         <v>0.853</v>
       </c>
-      <c r="E113" s="30" t="n">
+      <c r="E113" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="31" t="n">
+      <c r="F113" s="34" t="n">
         <v>3.686</v>
       </c>
-      <c r="G113" s="30" t="n">
+      <c r="G113" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="31" t="n">
+      <c r="H113" s="34" t="n">
         <v>3.267</v>
       </c>
-      <c r="I113" s="33" t="n">
+      <c r="I113" s="36" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="30" t="n">
+      <c r="A114" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="31" t="n">
+      <c r="B114" s="34" t="n">
         <v>1.693</v>
       </c>
-      <c r="C114" s="32" t="n">
+      <c r="C114" s="35" t="n">
         <v>0.5907</v>
       </c>
-      <c r="D114" s="31" t="n">
+      <c r="D114" s="34" t="n">
         <v>0.888</v>
       </c>
-      <c r="E114" s="30" t="n">
+      <c r="E114" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="31" t="n">
+      <c r="F114" s="34" t="n">
         <v>4.358</v>
       </c>
-      <c r="G114" s="30" t="n">
+      <c r="G114" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="33" t="n">
+      <c r="H114" s="36" t="n">
         <v>2.574</v>
       </c>
-      <c r="I114" s="31" t="n">
+      <c r="I114" s="34" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="30" t="n">
+      <c r="A115" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B115" s="31" t="n">
+      <c r="B115" s="34" t="n">
         <v>2.059</v>
       </c>
-      <c r="C115" s="32" t="n">
+      <c r="C115" s="35" t="n">
         <v>0.4857</v>
       </c>
-      <c r="D115" s="31" t="n">
+      <c r="D115" s="34" t="n">
         <v>0.88</v>
       </c>
-      <c r="E115" s="30" t="n">
+      <c r="E115" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="31" t="n">
+      <c r="F115" s="34" t="n">
         <v>4.698</v>
       </c>
-      <c r="G115" s="30" t="n">
+      <c r="G115" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="31" t="n">
+      <c r="H115" s="34" t="n">
         <v>2.282</v>
       </c>
-      <c r="I115" s="31" t="n">
+      <c r="I115" s="34" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="30" t="n">
+      <c r="A116" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="31" t="n">
+      <c r="B116" s="34" t="n">
         <v>2.326</v>
       </c>
-      <c r="C116" s="32" t="n">
+      <c r="C116" s="35" t="n">
         <v>0.4299</v>
       </c>
-      <c r="D116" s="31" t="n">
+      <c r="D116" s="34" t="n">
         <v>0.864</v>
       </c>
-      <c r="E116" s="30" t="n">
+      <c r="E116" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="31" t="n">
+      <c r="F116" s="34" t="n">
         <v>4.918</v>
       </c>
-      <c r="G116" s="30" t="n">
+      <c r="G116" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="33" t="n">
+      <c r="H116" s="36" t="n">
         <v>2.114</v>
       </c>
-      <c r="I116" s="31" t="n">
+      <c r="I116" s="34" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="30" t="n">
+      <c r="A117" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B117" s="31" t="n">
+      <c r="B117" s="34" t="n">
         <v>2.534</v>
       </c>
-      <c r="C117" s="32" t="n">
+      <c r="C117" s="35" t="n">
         <v>0.3946</v>
       </c>
-      <c r="D117" s="31" t="n">
+      <c r="D117" s="34" t="n">
         <v>0.848</v>
       </c>
-      <c r="E117" s="30" t="n">
+      <c r="E117" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="31" t="n">
+      <c r="F117" s="34" t="n">
         <v>5.078</v>
       </c>
-      <c r="G117" s="30" t="n">
+      <c r="G117" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="31" t="n">
+      <c r="H117" s="34" t="n">
         <v>2.004</v>
       </c>
-      <c r="I117" s="31" t="n">
+      <c r="I117" s="34" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="30" t="n">
+      <c r="A118" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="31" t="n">
+      <c r="B118" s="34" t="n">
         <v>2.704</v>
       </c>
-      <c r="C118" s="32" t="n">
+      <c r="C118" s="35" t="n">
         <v>0.3698</v>
       </c>
-      <c r="D118" s="31" t="n">
+      <c r="D118" s="34" t="n">
         <v>0.833</v>
       </c>
-      <c r="E118" s="33" t="n">
+      <c r="E118" s="36" t="n">
         <v>0.204</v>
       </c>
-      <c r="F118" s="33" t="n">
+      <c r="F118" s="36" t="n">
         <v>5.204</v>
       </c>
-      <c r="G118" s="31" t="n">
+      <c r="G118" s="34" t="n">
         <v>0.076</v>
       </c>
-      <c r="H118" s="31" t="n">
+      <c r="H118" s="34" t="n">
         <v>1.924</v>
       </c>
-      <c r="I118" s="31" t="n">
+      <c r="I118" s="34" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="30" t="n">
+      <c r="A119" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B119" s="31" t="n">
+      <c r="B119" s="34" t="n">
         <v>2.847</v>
       </c>
-      <c r="C119" s="32" t="n">
+      <c r="C119" s="35" t="n">
         <v>0.3512</v>
       </c>
-      <c r="D119" s="31" t="n">
+      <c r="D119" s="34" t="n">
         <v>0.82</v>
       </c>
-      <c r="E119" s="33" t="n">
+      <c r="E119" s="36" t="n">
         <v>0.388</v>
       </c>
-      <c r="F119" s="33" t="n">
+      <c r="F119" s="36" t="n">
         <v>5.306</v>
       </c>
-      <c r="G119" s="31" t="n">
+      <c r="G119" s="34" t="n">
         <v>0.136</v>
       </c>
-      <c r="H119" s="31" t="n">
+      <c r="H119" s="34" t="n">
         <v>1.864</v>
       </c>
-      <c r="I119" s="31" t="n">
+      <c r="I119" s="34" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="30" t="n">
+      <c r="A120" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="31" t="n">
+      <c r="B120" s="34" t="n">
         <v>2.97</v>
       </c>
-      <c r="C120" s="32" t="n">
+      <c r="C120" s="35" t="n">
         <v>0.3367</v>
       </c>
-      <c r="D120" s="31" t="n">
+      <c r="D120" s="34" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E120" s="33" t="n">
+      <c r="E120" s="36" t="n">
         <v>0.547</v>
       </c>
-      <c r="F120" s="33" t="n">
+      <c r="F120" s="36" t="n">
         <v>5.393</v>
       </c>
-      <c r="G120" s="31" t="n">
+      <c r="G120" s="34" t="n">
         <v>0.184</v>
       </c>
-      <c r="H120" s="31" t="n">
+      <c r="H120" s="34" t="n">
         <v>1.816</v>
       </c>
-      <c r="I120" s="31" t="n">
+      <c r="I120" s="34" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="30" t="n">
+      <c r="A121" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B121" s="31" t="n">
+      <c r="B121" s="34" t="n">
         <v>3.078</v>
       </c>
-      <c r="C121" s="32" t="n">
+      <c r="C121" s="35" t="n">
         <v>0.3249</v>
       </c>
-      <c r="D121" s="31" t="n">
+      <c r="D121" s="34" t="n">
         <v>0.797</v>
       </c>
-      <c r="E121" s="31" t="n">
+      <c r="E121" s="34" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F121" s="31" t="n">
+      <c r="F121" s="34" t="n">
         <v>5.469</v>
       </c>
-      <c r="G121" s="31" t="n">
+      <c r="G121" s="34" t="n">
         <v>0.223</v>
       </c>
-      <c r="H121" s="31" t="n">
+      <c r="H121" s="34" t="n">
         <v>1.777</v>
       </c>
-      <c r="I121" s="31" t="n">
+      <c r="I121" s="34" t="n">
         <v>0.975</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="30" t="n">
+      <c r="A122" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B122" s="31" t="n">
+      <c r="B122" s="34" t="n">
         <v>3.173</v>
       </c>
-      <c r="C122" s="32" t="n">
+      <c r="C122" s="35" t="n">
         <v>0.3152</v>
       </c>
-      <c r="D122" s="31" t="n">
+      <c r="D122" s="34" t="n">
         <v>0.787</v>
       </c>
-      <c r="E122" s="33" t="n">
+      <c r="E122" s="36" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F122" s="33" t="n">
+      <c r="F122" s="36" t="n">
         <v>5.535</v>
       </c>
-      <c r="G122" s="31" t="n">
+      <c r="G122" s="34" t="n">
         <v>0.256</v>
       </c>
-      <c r="H122" s="31" t="n">
+      <c r="H122" s="34" t="n">
         <v>1.744</v>
       </c>
-      <c r="I122" s="31" t="n">
+      <c r="I122" s="34" t="n">
         <v>0.945</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="30" t="n">
+      <c r="A123" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="31" t="n">
+      <c r="B123" s="34" t="n">
         <v>3.258</v>
       </c>
-      <c r="C123" s="32" t="n">
+      <c r="C123" s="35" t="n">
         <v>0.3069</v>
       </c>
-      <c r="D123" s="33" t="n">
+      <c r="D123" s="36" t="n">
         <v>0.778</v>
       </c>
-      <c r="E123" s="33" t="n">
+      <c r="E123" s="36" t="n">
         <v>0.922</v>
       </c>
-      <c r="F123" s="33" t="n">
+      <c r="F123" s="36" t="n">
         <v>5.594</v>
       </c>
-      <c r="G123" s="33" t="n">
+      <c r="G123" s="36" t="n">
         <v>0.283</v>
       </c>
-      <c r="H123" s="33" t="n">
+      <c r="H123" s="36" t="n">
         <v>1.717</v>
       </c>
-      <c r="I123" s="31" t="n">
+      <c r="I123" s="34" t="n">
         <v>0.921</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="30" t="n">
+      <c r="A124" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B124" s="31" t="n">
+      <c r="B124" s="34" t="n">
         <v>3.336</v>
       </c>
-      <c r="C124" s="32" t="n">
+      <c r="C124" s="35" t="n">
         <v>0.2998</v>
       </c>
-      <c r="D124" s="31" t="n">
+      <c r="D124" s="34" t="n">
         <v>0.77</v>
       </c>
-      <c r="E124" s="33" t="n">
+      <c r="E124" s="36" t="n">
         <v>1.025</v>
       </c>
-      <c r="F124" s="33" t="n">
+      <c r="F124" s="36" t="n">
         <v>5.647</v>
       </c>
-      <c r="G124" s="33" t="n">
+      <c r="G124" s="36" t="n">
         <v>0.307</v>
       </c>
-      <c r="H124" s="33" t="n">
+      <c r="H124" s="36" t="n">
         <v>1.693</v>
       </c>
-      <c r="I124" s="31" t="n">
+      <c r="I124" s="34" t="n">
         <v>0.899</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="30" t="n">
+      <c r="A125" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B125" s="31" t="n">
+      <c r="B125" s="34" t="n">
         <v>3.407</v>
       </c>
-      <c r="C125" s="32" t="n">
+      <c r="C125" s="35" t="n">
         <v>0.2935</v>
       </c>
-      <c r="D125" s="31" t="n">
+      <c r="D125" s="34" t="n">
         <v>0.763</v>
       </c>
-      <c r="E125" s="33" t="n">
+      <c r="E125" s="36" t="n">
         <v>1.118</v>
       </c>
-      <c r="F125" s="33" t="n">
+      <c r="F125" s="36" t="n">
         <v>5.696</v>
       </c>
-      <c r="G125" s="33" t="n">
+      <c r="G125" s="36" t="n">
         <v>0.328</v>
       </c>
-      <c r="H125" s="33" t="n">
+      <c r="H125" s="36" t="n">
         <v>1.672</v>
       </c>
-      <c r="I125" s="31" t="n">
+      <c r="I125" s="34" t="n">
         <v>0.881</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="30" t="n">
+      <c r="A126" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B126" s="31" t="n">
+      <c r="B126" s="34" t="n">
         <v>3.472</v>
       </c>
-      <c r="C126" s="32" t="n">
+      <c r="C126" s="35" t="n">
         <v>0.288</v>
       </c>
-      <c r="D126" s="31" t="n">
+      <c r="D126" s="34" t="n">
         <v>0.756</v>
       </c>
-      <c r="E126" s="33" t="n">
+      <c r="E126" s="36" t="n">
         <v>1.203</v>
       </c>
-      <c r="F126" s="33" t="n">
+      <c r="F126" s="36" t="n">
         <v>5.741</v>
       </c>
-      <c r="G126" s="33" t="n">
+      <c r="G126" s="36" t="n">
         <v>0.347</v>
       </c>
-      <c r="H126" s="33" t="n">
+      <c r="H126" s="36" t="n">
         <v>1.653</v>
       </c>
-      <c r="I126" s="31" t="n">
+      <c r="I126" s="34" t="n">
         <v>0.864</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="30" t="n">
+      <c r="A127" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B127" s="31" t="n">
+      <c r="B127" s="34" t="n">
         <v>3.532</v>
       </c>
-      <c r="C127" s="32" t="n">
+      <c r="C127" s="35" t="n">
         <v>0.2831</v>
       </c>
-      <c r="D127" s="31" t="n">
+      <c r="D127" s="34" t="n">
         <v>0.75</v>
       </c>
-      <c r="E127" s="33" t="n">
+      <c r="E127" s="36" t="n">
         <v>1.282</v>
       </c>
-      <c r="F127" s="33" t="n">
+      <c r="F127" s="36" t="n">
         <v>5.782</v>
       </c>
-      <c r="G127" s="33" t="n">
+      <c r="G127" s="36" t="n">
         <v>0.363</v>
       </c>
-      <c r="H127" s="33" t="n">
+      <c r="H127" s="36" t="n">
         <v>1.637</v>
       </c>
-      <c r="I127" s="31" t="n">
+      <c r="I127" s="34" t="n">
         <v>0.849</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="30" t="n">
+      <c r="A128" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B128" s="31" t="n">
+      <c r="B128" s="34" t="n">
         <v>3.588</v>
       </c>
-      <c r="C128" s="32" t="n">
+      <c r="C128" s="35" t="n">
         <v>0.2787</v>
       </c>
-      <c r="D128" s="31" t="n">
+      <c r="D128" s="34" t="n">
         <v>0.744</v>
       </c>
-      <c r="E128" s="33" t="n">
+      <c r="E128" s="36" t="n">
         <v>1.356</v>
       </c>
-      <c r="F128" s="33" t="n">
+      <c r="F128" s="36" t="n">
         <v>5.82</v>
       </c>
-      <c r="G128" s="33" t="n">
+      <c r="G128" s="36" t="n">
         <v>0.378</v>
       </c>
-      <c r="H128" s="33" t="n">
+      <c r="H128" s="36" t="n">
         <v>1.622</v>
       </c>
-      <c r="I128" s="31" t="n">
+      <c r="I128" s="34" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="30" t="n">
+      <c r="A129" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B129" s="31" t="n">
+      <c r="B129" s="34" t="n">
         <v>3.64</v>
       </c>
-      <c r="C129" s="32" t="n">
+      <c r="C129" s="35" t="n">
         <v>0.2747</v>
       </c>
-      <c r="D129" s="31" t="n">
+      <c r="D129" s="34" t="n">
         <v>0.739</v>
       </c>
-      <c r="E129" s="33" t="n">
+      <c r="E129" s="36" t="n">
         <v>1.424</v>
       </c>
-      <c r="F129" s="33" t="n">
+      <c r="F129" s="36" t="n">
         <v>5.856</v>
       </c>
-      <c r="G129" s="33" t="n">
+      <c r="G129" s="36" t="n">
         <v>0.391</v>
       </c>
-      <c r="H129" s="31" t="n">
+      <c r="H129" s="34" t="n">
         <v>1.608</v>
       </c>
-      <c r="I129" s="31" t="n">
+      <c r="I129" s="34" t="n">
         <v>0.824</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="30" t="n">
+      <c r="A130" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B130" s="31" t="n">
+      <c r="B130" s="34" t="n">
         <v>3.689</v>
       </c>
-      <c r="C130" s="32" t="n">
+      <c r="C130" s="35" t="n">
         <v>0.2711</v>
       </c>
-      <c r="D130" s="31" t="n">
+      <c r="D130" s="34" t="n">
         <v>0.734</v>
       </c>
-      <c r="E130" s="33" t="n">
+      <c r="E130" s="36" t="n">
         <v>1.487</v>
       </c>
-      <c r="F130" s="33" t="n">
+      <c r="F130" s="36" t="n">
         <v>5.891</v>
       </c>
-      <c r="G130" s="33" t="n">
+      <c r="G130" s="36" t="n">
         <v>0.403</v>
       </c>
-      <c r="H130" s="33" t="n">
+      <c r="H130" s="36" t="n">
         <v>1.597</v>
       </c>
-      <c r="I130" s="31" t="n">
+      <c r="I130" s="34" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="30" t="n">
+      <c r="A131" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="31" t="n">
+      <c r="B131" s="34" t="n">
         <v>3.735</v>
       </c>
-      <c r="C131" s="32" t="n">
+      <c r="C131" s="35" t="n">
         <v>0.2677</v>
       </c>
-      <c r="D131" s="31" t="n">
+      <c r="D131" s="34" t="n">
         <v>0.729</v>
       </c>
-      <c r="E131" s="33" t="n">
+      <c r="E131" s="36" t="n">
         <v>1.549</v>
       </c>
-      <c r="F131" s="33" t="n">
+      <c r="F131" s="36" t="n">
         <v>5.921</v>
       </c>
-      <c r="G131" s="33" t="n">
+      <c r="G131" s="36" t="n">
         <v>0.415</v>
       </c>
-      <c r="H131" s="33" t="n">
+      <c r="H131" s="36" t="n">
         <v>1.585</v>
       </c>
-      <c r="I131" s="31" t="n">
+      <c r="I131" s="34" t="n">
         <v>0.803</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="30" t="n">
+      <c r="A132" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B132" s="31" t="n">
+      <c r="B132" s="34" t="n">
         <v>3.778</v>
       </c>
-      <c r="C132" s="32" t="n">
+      <c r="C132" s="35" t="n">
         <v>0.2647</v>
       </c>
-      <c r="D132" s="33" t="n">
+      <c r="D132" s="36" t="n">
         <v>0.724</v>
       </c>
-      <c r="E132" s="33" t="n">
+      <c r="E132" s="36" t="n">
         <v>1.605</v>
       </c>
-      <c r="F132" s="33" t="n">
+      <c r="F132" s="36" t="n">
         <v>5.951</v>
       </c>
-      <c r="G132" s="31" t="n">
+      <c r="G132" s="34" t="n">
         <v>0.425</v>
       </c>
-      <c r="H132" s="31" t="n">
+      <c r="H132" s="34" t="n">
         <v>1.575</v>
       </c>
-      <c r="I132" s="31" t="n">
+      <c r="I132" s="34" t="n">
         <v>0.794</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="30" t="n">
+      <c r="A133" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B133" s="31" t="n">
+      <c r="B133" s="34" t="n">
         <v>3.819</v>
       </c>
-      <c r="C133" s="32" t="n">
+      <c r="C133" s="35" t="n">
         <v>0.2618</v>
       </c>
-      <c r="D133" s="31" t="n">
+      <c r="D133" s="34" t="n">
         <v>0.72</v>
       </c>
-      <c r="E133" s="31" t="n">
+      <c r="E133" s="34" t="n">
         <v>1.659</v>
       </c>
-      <c r="F133" s="31" t="n">
+      <c r="F133" s="34" t="n">
         <v>5.979</v>
       </c>
-      <c r="G133" s="31" t="n">
+      <c r="G133" s="34" t="n">
         <v>0.434</v>
       </c>
-      <c r="H133" s="31" t="n">
+      <c r="H133" s="34" t="n">
         <v>1.566</v>
       </c>
-      <c r="I133" s="31" t="n">
+      <c r="I133" s="34" t="n">
         <v>0.786</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="30" t="n">
+      <c r="A134" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B134" s="31" t="n">
+      <c r="B134" s="34" t="n">
         <v>3.858</v>
       </c>
-      <c r="C134" s="32" t="n">
+      <c r="C134" s="35" t="n">
         <v>0.2592</v>
       </c>
-      <c r="D134" s="31" t="n">
+      <c r="D134" s="34" t="n">
         <v>0.716</v>
       </c>
-      <c r="E134" s="31" t="n">
+      <c r="E134" s="34" t="n">
         <v>1.71</v>
       </c>
-      <c r="F134" s="31" t="n">
+      <c r="F134" s="34" t="n">
         <v>6.006</v>
       </c>
-      <c r="G134" s="31" t="n">
+      <c r="G134" s="34" t="n">
         <v>0.443</v>
       </c>
-      <c r="H134" s="31" t="n">
+      <c r="H134" s="34" t="n">
         <v>1.557</v>
       </c>
-      <c r="I134" s="31" t="n">
+      <c r="I134" s="34" t="n">
         <v>0.778</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="30" t="n">
+      <c r="A135" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B135" s="31" t="n">
+      <c r="B135" s="34" t="n">
         <v>3.895</v>
       </c>
-      <c r="C135" s="32" t="n">
+      <c r="C135" s="35" t="n">
         <v>0.2567</v>
       </c>
-      <c r="D135" s="31" t="n">
+      <c r="D135" s="34" t="n">
         <v>0.712</v>
       </c>
-      <c r="E135" s="31" t="n">
+      <c r="E135" s="34" t="n">
         <v>1.759</v>
       </c>
-      <c r="F135" s="31" t="n">
+      <c r="F135" s="34" t="n">
         <v>6.031</v>
       </c>
-      <c r="G135" s="33" t="n">
+      <c r="G135" s="36" t="n">
         <v>0.451</v>
       </c>
-      <c r="H135" s="31" t="n">
+      <c r="H135" s="34" t="n">
         <v>1.548</v>
       </c>
-      <c r="I135" s="31" t="n">
+      <c r="I135" s="34" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="30" t="n">
+      <c r="A136" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B136" s="31" t="n">
+      <c r="B136" s="34" t="n">
         <v>3.931</v>
       </c>
-      <c r="C136" s="32" t="n">
+      <c r="C136" s="35" t="n">
         <v>0.2544</v>
       </c>
-      <c r="D136" s="31" t="n">
+      <c r="D136" s="34" t="n">
         <v>0.708</v>
       </c>
-      <c r="E136" s="33" t="n">
+      <c r="E136" s="36" t="n">
         <v>1.806</v>
       </c>
-      <c r="F136" s="33" t="n">
+      <c r="F136" s="36" t="n">
         <v>6.056</v>
       </c>
-      <c r="G136" s="31" t="n">
+      <c r="G136" s="34" t="n">
         <v>0.459</v>
       </c>
-      <c r="H136" s="31" t="n">
+      <c r="H136" s="34" t="n">
         <v>1.541</v>
       </c>
-      <c r="I136" s="31" t="n">
+      <c r="I136" s="34" t="n">
         <v>0.763</v>
       </c>
     </row>
@@ -10202,236 +11313,236 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="30" t="n">
+      <c r="A142" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B142" s="31" t="n">
+      <c r="B142" s="34" t="n">
         <v>1.88</v>
       </c>
-      <c r="C142" s="31" t="n">
+      <c r="C142" s="34" t="n">
         <v>2.659</v>
       </c>
-      <c r="D142" s="30" t="n">
+      <c r="D142" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="31" t="n">
+      <c r="E142" s="34" t="n">
         <v>3.267</v>
       </c>
-      <c r="F142" s="30" t="n">
+      <c r="F142" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="31" t="n">
+      <c r="G142" s="34" t="n">
         <v>3.267</v>
       </c>
-      <c r="H142" s="33" t="n">
+      <c r="H142" s="36" t="n">
         <v>2.659</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="30" t="n">
+      <c r="A143" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="31" t="n">
+      <c r="B143" s="34" t="n">
         <v>1.023</v>
       </c>
-      <c r="C143" s="31" t="n">
+      <c r="C143" s="34" t="n">
         <v>1.954</v>
       </c>
-      <c r="D143" s="30" t="n">
+      <c r="D143" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="31" t="n">
+      <c r="E143" s="34" t="n">
         <v>2.568</v>
       </c>
-      <c r="F143" s="30" t="n">
+      <c r="F143" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="33" t="n">
+      <c r="G143" s="36" t="n">
         <v>2.574</v>
       </c>
-      <c r="H143" s="31" t="n">
+      <c r="H143" s="34" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="30" t="n">
+      <c r="A144" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B144" s="31" t="n">
+      <c r="B144" s="34" t="n">
         <v>0.729</v>
       </c>
-      <c r="C144" s="31" t="n">
+      <c r="C144" s="34" t="n">
         <v>1.628</v>
       </c>
-      <c r="D144" s="30" t="n">
+      <c r="D144" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="31" t="n">
+      <c r="E144" s="34" t="n">
         <v>2.266</v>
       </c>
-      <c r="F144" s="30" t="n">
+      <c r="F144" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="31" t="n">
+      <c r="G144" s="34" t="n">
         <v>2.282</v>
       </c>
-      <c r="H144" s="31" t="n">
+      <c r="H144" s="34" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="30" t="n">
+      <c r="A145" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B145" s="31" t="n">
+      <c r="B145" s="34" t="n">
         <v>0.577</v>
       </c>
-      <c r="C145" s="31" t="n">
+      <c r="C145" s="34" t="n">
         <v>1.427</v>
       </c>
-      <c r="D145" s="30" t="n">
+      <c r="D145" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E145" s="31" t="n">
+      <c r="E145" s="34" t="n">
         <v>2.089</v>
       </c>
-      <c r="F145" s="30" t="n">
+      <c r="F145" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="33" t="n">
+      <c r="G145" s="36" t="n">
         <v>2.114</v>
       </c>
-      <c r="H145" s="31" t="n">
+      <c r="H145" s="34" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="30" t="n">
+      <c r="A146" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B146" s="31" t="n">
+      <c r="B146" s="34" t="n">
         <v>0.483</v>
       </c>
-      <c r="C146" s="31" t="n">
+      <c r="C146" s="34" t="n">
         <v>1.287</v>
       </c>
-      <c r="D146" s="31" t="n">
+      <c r="D146" s="34" t="n">
         <v>0.03</v>
       </c>
-      <c r="E146" s="31" t="n">
+      <c r="E146" s="34" t="n">
         <v>1.97</v>
       </c>
-      <c r="F146" s="30" t="n">
+      <c r="F146" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="31" t="n">
+      <c r="G146" s="34" t="n">
         <v>2.004</v>
       </c>
-      <c r="H146" s="31" t="n">
+      <c r="H146" s="34" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="30" t="n">
+      <c r="A147" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B147" s="31" t="n">
+      <c r="B147" s="34" t="n">
         <v>0.419</v>
       </c>
-      <c r="C147" s="31" t="n">
+      <c r="C147" s="34" t="n">
         <v>1.182</v>
       </c>
-      <c r="D147" s="31" t="n">
+      <c r="D147" s="34" t="n">
         <v>0.118</v>
       </c>
-      <c r="E147" s="31" t="n">
+      <c r="E147" s="34" t="n">
         <v>1.882</v>
       </c>
-      <c r="F147" s="31" t="n">
+      <c r="F147" s="34" t="n">
         <v>0.076</v>
       </c>
-      <c r="G147" s="31" t="n">
+      <c r="G147" s="34" t="n">
         <v>1.924</v>
       </c>
-      <c r="H147" s="31" t="n">
+      <c r="H147" s="34" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="30" t="n">
+      <c r="A148" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B148" s="31" t="n">
+      <c r="B148" s="34" t="n">
         <v>0.373</v>
       </c>
-      <c r="C148" s="31" t="n">
+      <c r="C148" s="34" t="n">
         <v>1.099</v>
       </c>
-      <c r="D148" s="31" t="n">
+      <c r="D148" s="34" t="n">
         <v>0.185</v>
       </c>
-      <c r="E148" s="31" t="n">
+      <c r="E148" s="34" t="n">
         <v>1.815</v>
       </c>
-      <c r="F148" s="31" t="n">
+      <c r="F148" s="34" t="n">
         <v>0.136</v>
       </c>
-      <c r="G148" s="31" t="n">
+      <c r="G148" s="34" t="n">
         <v>1.864</v>
       </c>
-      <c r="H148" s="31" t="n">
+      <c r="H148" s="34" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="30" t="n">
+      <c r="A149" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B149" s="31" t="n">
+      <c r="B149" s="34" t="n">
         <v>0.337</v>
       </c>
-      <c r="C149" s="31" t="n">
+      <c r="C149" s="34" t="n">
         <v>1.032</v>
       </c>
-      <c r="D149" s="31" t="n">
+      <c r="D149" s="34" t="n">
         <v>0.239</v>
       </c>
-      <c r="E149" s="31" t="n">
+      <c r="E149" s="34" t="n">
         <v>1.761</v>
       </c>
-      <c r="F149" s="31" t="n">
+      <c r="F149" s="34" t="n">
         <v>0.184</v>
       </c>
-      <c r="G149" s="31" t="n">
+      <c r="G149" s="34" t="n">
         <v>1.816</v>
       </c>
-      <c r="H149" s="31" t="n">
+      <c r="H149" s="34" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="30" t="n">
+      <c r="A150" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B150" s="31" t="n">
+      <c r="B150" s="34" t="n">
         <v>0.308</v>
       </c>
-      <c r="C150" s="31" t="n">
+      <c r="C150" s="34" t="n">
         <v>0.975</v>
       </c>
-      <c r="D150" s="31" t="n">
+      <c r="D150" s="34" t="n">
         <v>0.284</v>
       </c>
-      <c r="E150" s="31" t="n">
+      <c r="E150" s="34" t="n">
         <v>1.716</v>
       </c>
-      <c r="F150" s="31" t="n">
+      <c r="F150" s="34" t="n">
         <v>0.223</v>
       </c>
-      <c r="G150" s="31" t="n">
+      <c r="G150" s="34" t="n">
         <v>1.777</v>
       </c>
-      <c r="H150" s="31" t="n">
+      <c r="H150" s="34" t="n">
         <v>0.975</v>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sigma &amp; DPMO" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance CI &amp; tests" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion matrix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -71,7 +72,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
@@ -84,8 +85,9 @@
     <numFmt numFmtId="173" formatCode="0.0000000000%"/>
     <numFmt numFmtId="174" formatCode="0.000000"/>
     <numFmt numFmtId="175" formatCode="0.0000000000"/>
+    <numFmt numFmtId="176" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +132,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
@@ -188,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,6 +238,8 @@
     </xf>
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7473,6 +7483,635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Distributions: E[X], Var[X] and probabilities (Bernoulli, binomial, hypergeometric, Poisson, exponential, uniform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 2/20260529_ottoy_Acceptance Sampling.pdf p. 12, 16, 20; Acceptance Sampling.xlsm; Testing of Hypotheses.xlsx; Les 1/20260522_naert_big data.pdf p. 5-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Excel's distribution functions as used in the course workbooks; k counts are whole numbers; P(X ≥ k) = 1 − P(X ≤ k − 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: binomial and hypergeometric blocks tested against course worked examples S04-WE02, S03-WE19, S03-WE21; Bernoulli, Poisson, exponential and uniform blocks have no course example (audited)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. Bernoulli: one item, X = 1 (e.g. non-conform) with probability p</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>p = P(X = 1) (fraction)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 2 in 40 -&gt; 0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>E[X] = p</t>
+        </is>
+      </c>
+      <c r="B10" s="28">
+        <f>IF(AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=1),B9,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Var[X] = p (1 − p)</t>
+        </is>
+      </c>
+      <c r="B11" s="28">
+        <f>IF(AND(ISNUMBER(B9),B9&gt;=0,B9&lt;=1),B9*(1-B9),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2. Binomial: number of successes (e.g. defectives) in n independent trials</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>n = number of trials (items)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>p = probability per trial (fraction)</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>k (for the probabilities)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>E[X] = n p</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(AND(ISNUMBER(B14),ISNUMBER(B15),B15&gt;=0,B15&lt;=1),B14*B15,"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Acceptance Sampling.pdf p. 12 (E[i] = Nπ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Var[X] = n p (1 − p)</t>
+        </is>
+      </c>
+      <c r="B18" s="28">
+        <f>IF(AND(ISNUMBER(B14),ISNUMBER(B15),B15&gt;=0,B15&lt;=1),B14*B15*(1-B15),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>σ = √Var[X]</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
+        <f>IF(ISNUMBER(B18),SQRT(B18),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>P(X = k)</t>
+        </is>
+      </c>
+      <c r="B20" s="34">
+        <f>IF(AND(AND(ISNUMBER(B14),ISNUMBER(B15),B15&gt;=0,B15&lt;=1),ISNUMBER(B16)),_xlfn.BINOM.DIST(B16,B14,B15,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>P[i] = C(n,i) p^i (1 − p)^(n − i) (p. 12); Excel BINOM.DIST(k; n; p; ONWAAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≤ k)</t>
+        </is>
+      </c>
+      <c r="B21" s="34">
+        <f>IF(AND(AND(ISNUMBER(B14),ISNUMBER(B15),B15&gt;=0,B15&lt;=1),ISNUMBER(B16)),_xlfn.BINOM.DIST(B16,B14,B15,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>OC-curve P[d ≤ c] (Confidence Intervals.xlsx, Testing of Hypotheses.xlsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≥ k)</t>
+        </is>
+      </c>
+      <c r="B22" s="34">
+        <f>IF(AND(AND(ISNUMBER(B14),ISNUMBER(B15),B15&gt;=0,B15&lt;=1),ISNUMBER(B16)),IF(B16&lt;=0,1,1-_xlfn.BINOM.DIST(B16-1,B14,B15,TRUE)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>3. Hypergeometric: defectives in a sample of n drawn without replacement from a lot</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>N = lot size</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>D = defectives in the lot</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>D = π · N</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>n = sample size</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>k (for the probabilities)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>E[X] = n D / N</t>
+        </is>
+      </c>
+      <c r="B29" s="28">
+        <f>IF(AND(ISNUMBER(B25),ISNUMBER(B26),ISNUMBER(B27),B25&gt;1,B26&lt;=B25,B27&lt;=B25),B27*B26/B25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Var[X] = n (D/N)(1 − D/N)(N − n)/(N − 1)</t>
+        </is>
+      </c>
+      <c r="B30" s="28">
+        <f>IF(AND(ISNUMBER(B25),ISNUMBER(B26),ISNUMBER(B27),B25&gt;1,B26&lt;=B25,B27&lt;=B25),B27*(B26/B25)*(1-B26/B25)*(B25-B27)/(B25-1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>P(X = k)</t>
+        </is>
+      </c>
+      <c r="B31" s="34">
+        <f>IF(AND(AND(ISNUMBER(B25),ISNUMBER(B26),ISNUMBER(B27),B25&gt;1,B26&lt;=B25,B27&lt;=B25),ISNUMBER(B28)),_xlfn.HYPGEOM.DIST(B28,B27,B26,B25,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Acceptance Sampling.pdf p. 16: P[d = i] = C(D,i) C(N−D,n−i) / C(N,n)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≤ k)</t>
+        </is>
+      </c>
+      <c r="B32" s="34">
+        <f>IF(AND(AND(ISNUMBER(B25),ISNUMBER(B26),ISNUMBER(B27),B25&gt;1,B26&lt;=B25,B27&lt;=B25),ISNUMBER(B28)),_xlfn.HYPGEOM.DIST(B28,B27,B26,B25,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Testing of Hypotheses.xlsx 'OC-curve (hypergeometric)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≥ k)</t>
+        </is>
+      </c>
+      <c r="B33" s="34">
+        <f>IF(AND(AND(ISNUMBER(B25),ISNUMBER(B26),ISNUMBER(B27),B25&gt;1,B26&lt;=B25,B27&lt;=B25),ISNUMBER(B28)),IF(B28&lt;=0,1,1-_xlfn.HYPGEOM.DIST(B28-1,B27,B26,B25,TRUE)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>4. Poisson: number of events in a fixed interval (e.g. orders per week)</t>
+        </is>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>λ = mean number of events per interval</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Naert Les 1 p. 9: λ = 2.959 customers / minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>k (for the probabilities)</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>E[X] = λ</t>
+        </is>
+      </c>
+      <c r="B38" s="28">
+        <f>IF(AND(ISNUMBER(B36),B36&gt;0),B36,"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Naert Les 1 p. 7-9 (Poisson for counts)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Var[X] = λ</t>
+        </is>
+      </c>
+      <c r="B39" s="28">
+        <f>IF(AND(ISNUMBER(B36),B36&gt;0),B36,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>P(X = k)</t>
+        </is>
+      </c>
+      <c r="B40" s="34">
+        <f>IF(AND(AND(ISNUMBER(B36),B36&gt;0),ISNUMBER(B37)),_xlfn.POISSON.DIST(B37,B36,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Excel POISSON.DIST(k; λ; ONWAAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≤ k)</t>
+        </is>
+      </c>
+      <c r="B41" s="34">
+        <f>IF(AND(AND(ISNUMBER(B36),B36&gt;0),ISNUMBER(B37)),_xlfn.POISSON.DIST(B37,B36,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≥ k)</t>
+        </is>
+      </c>
+      <c r="B42" s="34">
+        <f>IF(AND(AND(ISNUMBER(B36),B36&gt;0),ISNUMBER(B37)),IF(B37&lt;=0,1,1-_xlfn.POISSON.DIST(B37-1,B36,TRUE)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>5. Exponential: waiting time between events (rate λ per unit time)</t>
+        </is>
+      </c>
+      <c r="D44" s="33" t="inlineStr">
+        <is>
+          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>rate λ = events per unit time</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>e.g. 175.3 orders per week</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>t (for the probabilities)</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>E[T] = 1 / λ</t>
+        </is>
+      </c>
+      <c r="B47" s="28">
+        <f>IF(AND(ISNUMBER(B45),B45&gt;0),1/B45,"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Naert Les 1 p. 7 (exponential for waiting times)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Var[T] = 1 / λ²</t>
+        </is>
+      </c>
+      <c r="B48" s="29">
+        <f>IF(AND(ISNUMBER(B45),B45&gt;0),1/B45^2,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>P(T ≤ t) = 1 − e^(−λt)</t>
+        </is>
+      </c>
+      <c r="B49" s="34">
+        <f>IF(AND(AND(ISNUMBER(B45),B45&gt;0),ISNUMBER(B46)),_xlfn.EXPON.DIST(B46,B45,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Excel EXPON.DIST(t; λ; WAAR) (Acceptance Sampling.xlsm 'distributions')</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>P(T &gt; t) = e^(−λt)</t>
+        </is>
+      </c>
+      <c r="B50" s="34">
+        <f>IF(AND(AND(ISNUMBER(B45),B45&gt;0),ISNUMBER(B46)),EXP(-B45*B46),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>6. Uniform on [a, b]</t>
+        </is>
+      </c>
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>a (lower end)</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>b (upper end)</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>x (for the probability)</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>E[X] = (a + b) / 2</t>
+        </is>
+      </c>
+      <c r="B56" s="28">
+        <f>IF(AND(ISNUMBER(B53),ISNUMBER(B54),B54&gt;B53),(B53+B54)/2,"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Acceptance Sampling.xlsm 'distributions'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Var[X] = (b − a)² / 12</t>
+        </is>
+      </c>
+      <c r="B57" s="28">
+        <f>IF(AND(ISNUMBER(B53),ISNUMBER(B54),B54&gt;B53),(B54-B53)^2/12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>P(X ≤ x)</t>
+        </is>
+      </c>
+      <c r="B58" s="34">
+        <f>IF(AND(AND(ISNUMBER(B53),ISNUMBER(B54),B54&gt;B53),ISNUMBER(B55)),MIN(1,MAX(0,(B55-B53)/(B54-B53))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>7. Normal: E[X] = μ, Var[X] = σ²; probabilities and σ from a tail fraction on the Normal sheet</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B14 B16 B25 B26 B27 B28 B37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Type a whole number, 0 or more." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9 B15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Probability" error="Type a fraction between 0 and 1." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7680,1327 +8319,1327 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="n">
+      <c r="A14" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="36" t="n">
         <v>2.121</v>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C14" s="36" t="n">
         <v>3.76</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D14" s="36" t="n">
         <v>3.76</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="36" t="n">
         <v>1.88</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="37" t="n">
         <v>0.5642</v>
       </c>
-      <c r="G14" s="35" t="n">
+      <c r="G14" s="37" t="n">
         <v>1.7725</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="H14" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="34" t="n">
+      <c r="I14" s="36" t="n">
         <v>1.843</v>
       </c>
-      <c r="J14" s="33" t="n">
+      <c r="J14" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="34" t="n">
+      <c r="K14" s="36" t="n">
         <v>3.267</v>
       </c>
-      <c r="L14" s="34" t="n">
+      <c r="L14" s="36" t="n">
         <v>1.128</v>
       </c>
-      <c r="M14" s="35" t="n">
+      <c r="M14" s="37" t="n">
         <v>0.8865</v>
       </c>
-      <c r="N14" s="33" t="n">
+      <c r="N14" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="34" t="n">
+      <c r="O14" s="36" t="n">
         <v>3.686</v>
       </c>
-      <c r="P14" s="33" t="n">
+      <c r="P14" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="34" t="n">
+      <c r="Q14" s="36" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="n">
+      <c r="A15" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="34" t="n">
+      <c r="B15" s="36" t="n">
         <v>1.732</v>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C15" s="36" t="n">
         <v>3.07</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <v>2.394</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="36" t="n">
         <v>1.023</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="37" t="n">
         <v>0.7236</v>
       </c>
-      <c r="G15" s="35" t="n">
+      <c r="G15" s="37" t="n">
         <v>1.382</v>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="34" t="n">
+      <c r="I15" s="36" t="n">
         <v>1.858</v>
       </c>
-      <c r="J15" s="33" t="n">
+      <c r="J15" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="34" t="n">
+      <c r="K15" s="36" t="n">
         <v>2.568</v>
       </c>
-      <c r="L15" s="34" t="n">
+      <c r="L15" s="36" t="n">
         <v>1.693</v>
       </c>
-      <c r="M15" s="35" t="n">
+      <c r="M15" s="37" t="n">
         <v>0.5907</v>
       </c>
-      <c r="N15" s="33" t="n">
+      <c r="N15" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="34" t="n">
+      <c r="O15" s="36" t="n">
         <v>4.358</v>
       </c>
-      <c r="P15" s="33" t="n">
+      <c r="P15" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="36" t="n">
+      <c r="Q15" s="38" t="n">
         <v>2.575</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="n">
+      <c r="A16" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="34" t="n">
+      <c r="B16" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="34" t="n">
+      <c r="C16" s="36" t="n">
         <v>2.914</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="36" t="n">
         <v>1.88</v>
       </c>
-      <c r="E16" s="34" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.729</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="37" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="G16" s="35" t="n">
+      <c r="G16" s="37" t="n">
         <v>1.2533</v>
       </c>
-      <c r="H16" s="33" t="n">
+      <c r="H16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I16" s="36" t="n">
         <v>1.808</v>
       </c>
-      <c r="J16" s="33" t="n">
+      <c r="J16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="34" t="n">
+      <c r="K16" s="36" t="n">
         <v>2.266</v>
       </c>
-      <c r="L16" s="34" t="n">
+      <c r="L16" s="36" t="n">
         <v>2.059</v>
       </c>
-      <c r="M16" s="35" t="n">
+      <c r="M16" s="37" t="n">
         <v>0.4857</v>
       </c>
-      <c r="N16" s="33" t="n">
+      <c r="N16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="34" t="n">
+      <c r="O16" s="36" t="n">
         <v>4.698</v>
       </c>
-      <c r="P16" s="33" t="n">
+      <c r="P16" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="34" t="n">
+      <c r="Q16" s="36" t="n">
         <v>2.282</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n">
+      <c r="A17" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="34" t="n">
+      <c r="B17" s="36" t="n">
         <v>1.342</v>
       </c>
-      <c r="C17" s="34" t="n">
+      <c r="C17" s="36" t="n">
         <v>2.884</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="36" t="n">
         <v>1.596</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.577</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="37" t="n">
         <v>0.8407</v>
       </c>
-      <c r="G17" s="35" t="n">
+      <c r="G17" s="37" t="n">
         <v>1.1894</v>
       </c>
-      <c r="H17" s="33" t="n">
+      <c r="H17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="34" t="n">
+      <c r="I17" s="36" t="n">
         <v>1.756</v>
       </c>
-      <c r="J17" s="33" t="n">
+      <c r="J17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="34" t="n">
+      <c r="K17" s="36" t="n">
         <v>2.089</v>
       </c>
-      <c r="L17" s="34" t="n">
+      <c r="L17" s="36" t="n">
         <v>2.326</v>
       </c>
-      <c r="M17" s="35" t="n">
+      <c r="M17" s="37" t="n">
         <v>0.4299</v>
       </c>
-      <c r="N17" s="33" t="n">
+      <c r="N17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="34" t="n">
+      <c r="O17" s="36" t="n">
         <v>4.918</v>
       </c>
-      <c r="P17" s="33" t="n">
+      <c r="P17" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="36" t="n">
+      <c r="Q17" s="38" t="n">
         <v>2.115</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="n">
+      <c r="A18" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="34" t="n">
+      <c r="B18" s="36" t="n">
         <v>1.225</v>
       </c>
-      <c r="C18" s="34" t="n">
+      <c r="C18" s="36" t="n">
         <v>2.899</v>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D18" s="36" t="n">
         <v>1.41</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E18" s="36" t="n">
         <v>0.483</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="37" t="n">
         <v>0.8686</v>
       </c>
-      <c r="G18" s="35" t="n">
+      <c r="G18" s="37" t="n">
         <v>1.1512</v>
       </c>
-      <c r="H18" s="34" t="n">
+      <c r="H18" s="36" t="n">
         <v>0.026</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="36" t="n">
         <v>1.711</v>
       </c>
-      <c r="J18" s="34" t="n">
+      <c r="J18" s="36" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" s="34" t="n">
+      <c r="K18" s="36" t="n">
         <v>1.97</v>
       </c>
-      <c r="L18" s="34" t="n">
+      <c r="L18" s="36" t="n">
         <v>2.534</v>
       </c>
-      <c r="M18" s="35" t="n">
+      <c r="M18" s="37" t="n">
         <v>0.3946</v>
       </c>
-      <c r="N18" s="33" t="n">
+      <c r="N18" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="34" t="n">
+      <c r="O18" s="36" t="n">
         <v>5.078</v>
       </c>
-      <c r="P18" s="33" t="n">
+      <c r="P18" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="34" t="n">
+      <c r="Q18" s="36" t="n">
         <v>2.004</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="n">
+      <c r="A19" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="34" t="n">
+      <c r="B19" s="36" t="n">
         <v>1.134</v>
       </c>
-      <c r="C19" s="34" t="n">
+      <c r="C19" s="36" t="n">
         <v>2.935</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="36" t="n">
         <v>1.277</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="36" t="n">
         <v>0.419</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="37" t="n">
         <v>0.8882</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="37" t="n">
         <v>1.1259</v>
       </c>
-      <c r="H19" s="34" t="n">
+      <c r="H19" s="36" t="n">
         <v>0.105</v>
       </c>
-      <c r="I19" s="34" t="n">
+      <c r="I19" s="36" t="n">
         <v>1.672</v>
       </c>
-      <c r="J19" s="34" t="n">
+      <c r="J19" s="36" t="n">
         <v>0.118</v>
       </c>
-      <c r="K19" s="34" t="n">
+      <c r="K19" s="36" t="n">
         <v>1.882</v>
       </c>
-      <c r="L19" s="34" t="n">
+      <c r="L19" s="36" t="n">
         <v>2.704</v>
       </c>
-      <c r="M19" s="35" t="n">
+      <c r="M19" s="37" t="n">
         <v>0.3698</v>
       </c>
-      <c r="N19" s="36" t="n">
+      <c r="N19" s="38" t="n">
         <v>0.205</v>
       </c>
-      <c r="O19" s="36" t="n">
+      <c r="O19" s="38" t="n">
         <v>5.203</v>
       </c>
-      <c r="P19" s="34" t="n">
+      <c r="P19" s="36" t="n">
         <v>0.076</v>
       </c>
-      <c r="Q19" s="34" t="n">
+      <c r="Q19" s="36" t="n">
         <v>1.924</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="n">
+      <c r="A20" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="34" t="n">
+      <c r="B20" s="36" t="n">
         <v>1.061</v>
       </c>
-      <c r="C20" s="34" t="n">
+      <c r="C20" s="36" t="n">
         <v>2.98</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="36" t="n">
         <v>1.175</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="36" t="n">
         <v>0.373</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="37" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="G20" s="35" t="n">
+      <c r="G20" s="37" t="n">
         <v>1.1078</v>
       </c>
-      <c r="H20" s="34" t="n">
+      <c r="H20" s="36" t="n">
         <v>0.167</v>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I20" s="36" t="n">
         <v>1.638</v>
       </c>
-      <c r="J20" s="34" t="n">
+      <c r="J20" s="36" t="n">
         <v>0.185</v>
       </c>
-      <c r="K20" s="34" t="n">
+      <c r="K20" s="36" t="n">
         <v>1.815</v>
       </c>
-      <c r="L20" s="34" t="n">
+      <c r="L20" s="36" t="n">
         <v>2.847</v>
       </c>
-      <c r="M20" s="35" t="n">
+      <c r="M20" s="37" t="n">
         <v>0.3512</v>
       </c>
-      <c r="N20" s="36" t="n">
+      <c r="N20" s="38" t="n">
         <v>0.387</v>
       </c>
-      <c r="O20" s="36" t="n">
+      <c r="O20" s="38" t="n">
         <v>5.307</v>
       </c>
-      <c r="P20" s="34" t="n">
+      <c r="P20" s="36" t="n">
         <v>0.136</v>
       </c>
-      <c r="Q20" s="34" t="n">
+      <c r="Q20" s="36" t="n">
         <v>1.864</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="n">
+      <c r="A21" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="34" t="n">
+      <c r="B21" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="36" t="n">
         <v>3.03</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="36" t="n">
         <v>1.094</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="36" t="n">
         <v>0.337</v>
       </c>
-      <c r="F21" s="35" t="n">
+      <c r="F21" s="37" t="n">
         <v>0.9139</v>
       </c>
-      <c r="G21" s="35" t="n">
+      <c r="G21" s="37" t="n">
         <v>1.0942</v>
       </c>
-      <c r="H21" s="34" t="n">
+      <c r="H21" s="36" t="n">
         <v>0.219</v>
       </c>
-      <c r="I21" s="34" t="n">
+      <c r="I21" s="36" t="n">
         <v>1.609</v>
       </c>
-      <c r="J21" s="34" t="n">
+      <c r="J21" s="36" t="n">
         <v>0.239</v>
       </c>
-      <c r="K21" s="34" t="n">
+      <c r="K21" s="36" t="n">
         <v>1.761</v>
       </c>
-      <c r="L21" s="34" t="n">
+      <c r="L21" s="36" t="n">
         <v>2.97</v>
       </c>
-      <c r="M21" s="35" t="n">
+      <c r="M21" s="37" t="n">
         <v>0.3367</v>
       </c>
-      <c r="N21" s="36" t="n">
+      <c r="N21" s="38" t="n">
         <v>0.546</v>
       </c>
-      <c r="O21" s="36" t="n">
+      <c r="O21" s="38" t="n">
         <v>5.394</v>
       </c>
-      <c r="P21" s="34" t="n">
+      <c r="P21" s="36" t="n">
         <v>0.184</v>
       </c>
-      <c r="Q21" s="34" t="n">
+      <c r="Q21" s="36" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="n">
+      <c r="A22" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="34" t="n">
+      <c r="B22" s="36" t="n">
         <v>0.949</v>
       </c>
-      <c r="C22" s="34" t="n">
+      <c r="C22" s="36" t="n">
         <v>3.085</v>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D22" s="36" t="n">
         <v>1.028</v>
       </c>
-      <c r="E22" s="34" t="n">
+      <c r="E22" s="36" t="n">
         <v>0.308</v>
       </c>
-      <c r="F22" s="35" t="n">
+      <c r="F22" s="37" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G22" s="35" t="n">
+      <c r="G22" s="37" t="n">
         <v>1.0837</v>
       </c>
-      <c r="H22" s="34" t="n">
+      <c r="H22" s="36" t="n">
         <v>0.262</v>
       </c>
-      <c r="I22" s="34" t="n">
+      <c r="I22" s="36" t="n">
         <v>1.584</v>
       </c>
-      <c r="J22" s="34" t="n">
+      <c r="J22" s="36" t="n">
         <v>0.284</v>
       </c>
-      <c r="K22" s="34" t="n">
+      <c r="K22" s="36" t="n">
         <v>1.716</v>
       </c>
-      <c r="L22" s="34" t="n">
+      <c r="L22" s="36" t="n">
         <v>3.078</v>
       </c>
-      <c r="M22" s="35" t="n">
+      <c r="M22" s="37" t="n">
         <v>0.3249</v>
       </c>
-      <c r="N22" s="34" t="n">
+      <c r="N22" s="36" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="O22" s="34" t="n">
+      <c r="O22" s="36" t="n">
         <v>5.469</v>
       </c>
-      <c r="P22" s="34" t="n">
+      <c r="P22" s="36" t="n">
         <v>0.223</v>
       </c>
-      <c r="Q22" s="34" t="n">
+      <c r="Q22" s="36" t="n">
         <v>1.777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="n">
+      <c r="A23" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="34" t="n">
+      <c r="B23" s="36" t="n">
         <v>0.905</v>
       </c>
-      <c r="C23" s="34" t="n">
+      <c r="C23" s="36" t="n">
         <v>3.136</v>
       </c>
-      <c r="D23" s="34" t="n">
+      <c r="D23" s="36" t="n">
         <v>0.973</v>
       </c>
-      <c r="E23" s="34" t="n">
+      <c r="E23" s="36" t="n">
         <v>0.285</v>
       </c>
-      <c r="F23" s="35" t="n">
+      <c r="F23" s="37" t="n">
         <v>0.93</v>
       </c>
-      <c r="G23" s="35" t="n">
+      <c r="G23" s="37" t="n">
         <v>1.0753</v>
       </c>
-      <c r="H23" s="34" t="n">
+      <c r="H23" s="36" t="n">
         <v>0.299</v>
       </c>
-      <c r="I23" s="34" t="n">
+      <c r="I23" s="36" t="n">
         <v>1.561</v>
       </c>
-      <c r="J23" s="34" t="n">
+      <c r="J23" s="36" t="n">
         <v>0.321</v>
       </c>
-      <c r="K23" s="34" t="n">
+      <c r="K23" s="36" t="n">
         <v>1.679</v>
       </c>
-      <c r="L23" s="34" t="n">
+      <c r="L23" s="36" t="n">
         <v>3.173</v>
       </c>
-      <c r="M23" s="35" t="n">
+      <c r="M23" s="37" t="n">
         <v>0.3152</v>
       </c>
-      <c r="N23" s="36" t="n">
+      <c r="N23" s="38" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="O23" s="36" t="n">
+      <c r="O23" s="38" t="n">
         <v>5.534</v>
       </c>
-      <c r="P23" s="34" t="n">
+      <c r="P23" s="36" t="n">
         <v>0.256</v>
       </c>
-      <c r="Q23" s="34" t="n">
+      <c r="Q23" s="36" t="n">
         <v>1.744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="n">
+      <c r="A24" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="34" t="n">
+      <c r="B24" s="36" t="n">
         <v>0.866</v>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="36" t="n">
         <v>3.189</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="36" t="n">
         <v>0.925</v>
       </c>
-      <c r="E24" s="34" t="n">
+      <c r="E24" s="36" t="n">
         <v>0.266</v>
       </c>
-      <c r="F24" s="35" t="n">
+      <c r="F24" s="37" t="n">
         <v>0.9359</v>
       </c>
-      <c r="G24" s="35" t="n">
+      <c r="G24" s="37" t="n">
         <v>1.0684</v>
       </c>
-      <c r="H24" s="34" t="n">
+      <c r="H24" s="36" t="n">
         <v>0.331</v>
       </c>
-      <c r="I24" s="34" t="n">
+      <c r="I24" s="36" t="n">
         <v>1.541</v>
       </c>
-      <c r="J24" s="34" t="n">
+      <c r="J24" s="36" t="n">
         <v>0.354</v>
       </c>
-      <c r="K24" s="34" t="n">
+      <c r="K24" s="36" t="n">
         <v>1.646</v>
       </c>
-      <c r="L24" s="34" t="n">
+      <c r="L24" s="36" t="n">
         <v>3.258</v>
       </c>
-      <c r="M24" s="35" t="n">
+      <c r="M24" s="37" t="n">
         <v>0.3069</v>
       </c>
-      <c r="N24" s="36" t="n">
+      <c r="N24" s="38" t="n">
         <v>0.924</v>
       </c>
-      <c r="O24" s="36" t="n">
+      <c r="O24" s="38" t="n">
         <v>5.592</v>
       </c>
-      <c r="P24" s="36" t="n">
+      <c r="P24" s="38" t="n">
         <v>0.284</v>
       </c>
-      <c r="Q24" s="36" t="n">
+      <c r="Q24" s="38" t="n">
         <v>1.716</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="n">
+      <c r="A25" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="34" t="n">
+      <c r="B25" s="36" t="n">
         <v>0.832</v>
       </c>
-      <c r="C25" s="34" t="n">
+      <c r="C25" s="36" t="n">
         <v>3.242</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="36" t="n">
         <v>0.884</v>
       </c>
-      <c r="E25" s="34" t="n">
+      <c r="E25" s="36" t="n">
         <v>0.249</v>
       </c>
-      <c r="F25" s="35" t="n">
+      <c r="F25" s="37" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="G25" s="35" t="n">
+      <c r="G25" s="37" t="n">
         <v>1.0627</v>
       </c>
-      <c r="H25" s="34" t="n">
+      <c r="H25" s="36" t="n">
         <v>0.359</v>
       </c>
-      <c r="I25" s="34" t="n">
+      <c r="I25" s="36" t="n">
         <v>1.523</v>
       </c>
-      <c r="J25" s="34" t="n">
+      <c r="J25" s="36" t="n">
         <v>0.382</v>
       </c>
-      <c r="K25" s="34" t="n">
+      <c r="K25" s="36" t="n">
         <v>1.618</v>
       </c>
-      <c r="L25" s="34" t="n">
+      <c r="L25" s="36" t="n">
         <v>3.336</v>
       </c>
-      <c r="M25" s="35" t="n">
+      <c r="M25" s="37" t="n">
         <v>0.2998</v>
       </c>
-      <c r="N25" s="36" t="n">
+      <c r="N25" s="38" t="n">
         <v>1.026</v>
       </c>
-      <c r="O25" s="36" t="n">
+      <c r="O25" s="38" t="n">
         <v>5.646</v>
       </c>
-      <c r="P25" s="36" t="n">
+      <c r="P25" s="38" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q25" s="36" t="n">
+      <c r="Q25" s="38" t="n">
         <v>1.692</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="n">
+      <c r="A26" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="34" t="n">
+      <c r="B26" s="36" t="n">
         <v>0.802</v>
       </c>
-      <c r="C26" s="34" t="n">
+      <c r="C26" s="36" t="n">
         <v>3.295</v>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="36" t="n">
         <v>0.848</v>
       </c>
-      <c r="E26" s="34" t="n">
+      <c r="E26" s="36" t="n">
         <v>0.235</v>
       </c>
-      <c r="F26" s="35" t="n">
+      <c r="F26" s="37" t="n">
         <v>0.9453</v>
       </c>
-      <c r="G26" s="35" t="n">
+      <c r="G26" s="37" t="n">
         <v>1.0579</v>
       </c>
-      <c r="H26" s="34" t="n">
+      <c r="H26" s="36" t="n">
         <v>0.384</v>
       </c>
-      <c r="I26" s="34" t="n">
+      <c r="I26" s="36" t="n">
         <v>1.507</v>
       </c>
-      <c r="J26" s="34" t="n">
+      <c r="J26" s="36" t="n">
         <v>0.406</v>
       </c>
-      <c r="K26" s="34" t="n">
+      <c r="K26" s="36" t="n">
         <v>1.594</v>
       </c>
-      <c r="L26" s="34" t="n">
+      <c r="L26" s="36" t="n">
         <v>3.407</v>
       </c>
-      <c r="M26" s="35" t="n">
+      <c r="M26" s="37" t="n">
         <v>0.2935</v>
       </c>
-      <c r="N26" s="36" t="n">
+      <c r="N26" s="38" t="n">
         <v>1.121</v>
       </c>
-      <c r="O26" s="36" t="n">
+      <c r="O26" s="38" t="n">
         <v>5.693</v>
       </c>
-      <c r="P26" s="36" t="n">
+      <c r="P26" s="38" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q26" s="36" t="n">
+      <c r="Q26" s="38" t="n">
         <v>1.671</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="n">
+      <c r="A27" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="34" t="n">
+      <c r="B27" s="36" t="n">
         <v>0.775</v>
       </c>
-      <c r="C27" s="34" t="n">
+      <c r="C27" s="36" t="n">
         <v>3.347</v>
       </c>
-      <c r="D27" s="34" t="n">
+      <c r="D27" s="36" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="E27" s="34" t="n">
+      <c r="E27" s="36" t="n">
         <v>0.223</v>
       </c>
-      <c r="F27" s="35" t="n">
+      <c r="F27" s="37" t="n">
         <v>0.949</v>
       </c>
-      <c r="G27" s="35" t="n">
+      <c r="G27" s="37" t="n">
         <v>1.0537</v>
       </c>
-      <c r="H27" s="34" t="n">
+      <c r="H27" s="36" t="n">
         <v>0.406</v>
       </c>
-      <c r="I27" s="34" t="n">
+      <c r="I27" s="36" t="n">
         <v>1.492</v>
       </c>
-      <c r="J27" s="34" t="n">
+      <c r="J27" s="36" t="n">
         <v>0.428</v>
       </c>
-      <c r="K27" s="34" t="n">
+      <c r="K27" s="36" t="n">
         <v>1.572</v>
       </c>
-      <c r="L27" s="34" t="n">
+      <c r="L27" s="36" t="n">
         <v>3.472</v>
       </c>
-      <c r="M27" s="35" t="n">
+      <c r="M27" s="37" t="n">
         <v>0.288</v>
       </c>
-      <c r="N27" s="36" t="n">
+      <c r="N27" s="38" t="n">
         <v>1.207</v>
       </c>
-      <c r="O27" s="36" t="n">
+      <c r="O27" s="38" t="n">
         <v>5.737</v>
       </c>
-      <c r="P27" s="36" t="n">
+      <c r="P27" s="38" t="n">
         <v>0.348</v>
       </c>
-      <c r="Q27" s="36" t="n">
+      <c r="Q27" s="38" t="n">
         <v>1.652</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="n">
+      <c r="A28" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="34" t="n">
+      <c r="B28" s="36" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="34" t="n">
+      <c r="C28" s="36" t="n">
         <v>3.398</v>
       </c>
-      <c r="D28" s="34" t="n">
+      <c r="D28" s="36" t="n">
         <v>0.788</v>
       </c>
-      <c r="E28" s="34" t="n">
+      <c r="E28" s="36" t="n">
         <v>0.212</v>
       </c>
-      <c r="F28" s="35" t="n">
+      <c r="F28" s="37" t="n">
         <v>0.9523</v>
       </c>
-      <c r="G28" s="35" t="n">
+      <c r="G28" s="37" t="n">
         <v>1.0501</v>
       </c>
-      <c r="H28" s="34" t="n">
+      <c r="H28" s="36" t="n">
         <v>0.427</v>
       </c>
-      <c r="I28" s="34" t="n">
+      <c r="I28" s="36" t="n">
         <v>1.478</v>
       </c>
-      <c r="J28" s="34" t="n">
+      <c r="J28" s="36" t="n">
         <v>0.448</v>
       </c>
-      <c r="K28" s="34" t="n">
+      <c r="K28" s="36" t="n">
         <v>1.552</v>
       </c>
-      <c r="L28" s="34" t="n">
+      <c r="L28" s="36" t="n">
         <v>3.532</v>
       </c>
-      <c r="M28" s="35" t="n">
+      <c r="M28" s="37" t="n">
         <v>0.2831</v>
       </c>
-      <c r="N28" s="36" t="n">
+      <c r="N28" s="38" t="n">
         <v>1.285</v>
       </c>
-      <c r="O28" s="36" t="n">
+      <c r="O28" s="38" t="n">
         <v>5.779</v>
       </c>
-      <c r="P28" s="36" t="n">
+      <c r="P28" s="38" t="n">
         <v>0.364</v>
       </c>
-      <c r="Q28" s="36" t="n">
+      <c r="Q28" s="38" t="n">
         <v>1.636</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="n">
+      <c r="A29" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="34" t="n">
+      <c r="B29" s="36" t="n">
         <v>0.728</v>
       </c>
-      <c r="C29" s="34" t="n">
+      <c r="C29" s="36" t="n">
         <v>3.448</v>
       </c>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="36" t="n">
         <v>0.762</v>
       </c>
-      <c r="E29" s="34" t="n">
+      <c r="E29" s="36" t="n">
         <v>0.203</v>
       </c>
-      <c r="F29" s="35" t="n">
+      <c r="F29" s="37" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="G29" s="35" t="n">
+      <c r="G29" s="37" t="n">
         <v>1.047</v>
       </c>
-      <c r="H29" s="34" t="n">
+      <c r="H29" s="36" t="n">
         <v>0.445</v>
       </c>
-      <c r="I29" s="34" t="n">
+      <c r="I29" s="36" t="n">
         <v>1.465</v>
       </c>
-      <c r="J29" s="34" t="n">
+      <c r="J29" s="36" t="n">
         <v>0.466</v>
       </c>
-      <c r="K29" s="34" t="n">
+      <c r="K29" s="36" t="n">
         <v>1.534</v>
       </c>
-      <c r="L29" s="34" t="n">
+      <c r="L29" s="36" t="n">
         <v>3.588</v>
       </c>
-      <c r="M29" s="35" t="n">
+      <c r="M29" s="37" t="n">
         <v>0.2787</v>
       </c>
-      <c r="N29" s="36" t="n">
+      <c r="N29" s="38" t="n">
         <v>1.359</v>
       </c>
-      <c r="O29" s="36" t="n">
+      <c r="O29" s="38" t="n">
         <v>5.817</v>
       </c>
-      <c r="P29" s="36" t="n">
+      <c r="P29" s="38" t="n">
         <v>0.379</v>
       </c>
-      <c r="Q29" s="36" t="n">
+      <c r="Q29" s="38" t="n">
         <v>1.621</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="n">
+      <c r="A30" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="34" t="n">
+      <c r="B30" s="36" t="n">
         <v>0.707</v>
       </c>
-      <c r="C30" s="34" t="n">
+      <c r="C30" s="36" t="n">
         <v>3.497</v>
       </c>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="36" t="n">
         <v>0.738</v>
       </c>
-      <c r="E30" s="34" t="n">
+      <c r="E30" s="36" t="n">
         <v>0.194</v>
       </c>
-      <c r="F30" s="35" t="n">
+      <c r="F30" s="37" t="n">
         <v>0.9576</v>
       </c>
-      <c r="G30" s="35" t="n">
+      <c r="G30" s="37" t="n">
         <v>1.0442</v>
       </c>
-      <c r="H30" s="34" t="n">
+      <c r="H30" s="36" t="n">
         <v>0.461</v>
       </c>
-      <c r="I30" s="34" t="n">
+      <c r="I30" s="36" t="n">
         <v>1.454</v>
       </c>
-      <c r="J30" s="34" t="n">
+      <c r="J30" s="36" t="n">
         <v>0.482</v>
       </c>
-      <c r="K30" s="34" t="n">
+      <c r="K30" s="36" t="n">
         <v>1.518</v>
       </c>
-      <c r="L30" s="34" t="n">
+      <c r="L30" s="36" t="n">
         <v>3.64</v>
       </c>
-      <c r="M30" s="35" t="n">
+      <c r="M30" s="37" t="n">
         <v>0.2747</v>
       </c>
-      <c r="N30" s="36" t="n">
+      <c r="N30" s="38" t="n">
         <v>1.426</v>
       </c>
-      <c r="O30" s="36" t="n">
+      <c r="O30" s="38" t="n">
         <v>5.854</v>
       </c>
-      <c r="P30" s="36" t="n">
+      <c r="P30" s="38" t="n">
         <v>0.392</v>
       </c>
-      <c r="Q30" s="34" t="n">
+      <c r="Q30" s="36" t="n">
         <v>1.608</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="n">
+      <c r="A31" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="34" t="n">
+      <c r="B31" s="36" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C31" s="34" t="n">
+      <c r="C31" s="36" t="n">
         <v>3.545</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="36" t="n">
         <v>0.717</v>
       </c>
-      <c r="E31" s="34" t="n">
+      <c r="E31" s="36" t="n">
         <v>0.187</v>
       </c>
-      <c r="F31" s="35" t="n">
+      <c r="F31" s="37" t="n">
         <v>0.9599</v>
       </c>
-      <c r="G31" s="35" t="n">
+      <c r="G31" s="37" t="n">
         <v>1.0418</v>
       </c>
-      <c r="H31" s="34" t="n">
+      <c r="H31" s="36" t="n">
         <v>0.477</v>
       </c>
-      <c r="I31" s="34" t="n">
+      <c r="I31" s="36" t="n">
         <v>1.443</v>
       </c>
-      <c r="J31" s="34" t="n">
+      <c r="J31" s="36" t="n">
         <v>0.497</v>
       </c>
-      <c r="K31" s="34" t="n">
+      <c r="K31" s="36" t="n">
         <v>1.503</v>
       </c>
-      <c r="L31" s="34" t="n">
+      <c r="L31" s="36" t="n">
         <v>3.689</v>
       </c>
-      <c r="M31" s="35" t="n">
+      <c r="M31" s="37" t="n">
         <v>0.2711</v>
       </c>
-      <c r="N31" s="36" t="n">
+      <c r="N31" s="38" t="n">
         <v>1.49</v>
       </c>
-      <c r="O31" s="36" t="n">
+      <c r="O31" s="38" t="n">
         <v>5.888</v>
       </c>
-      <c r="P31" s="36" t="n">
+      <c r="P31" s="38" t="n">
         <v>0.404</v>
       </c>
-      <c r="Q31" s="36" t="n">
+      <c r="Q31" s="38" t="n">
         <v>1.596</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="n">
+      <c r="A32" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="34" t="n">
+      <c r="B32" s="36" t="n">
         <v>0.671</v>
       </c>
-      <c r="C32" s="34" t="n">
+      <c r="C32" s="36" t="n">
         <v>3.592</v>
       </c>
-      <c r="D32" s="34" t="n">
+      <c r="D32" s="36" t="n">
         <v>0.697</v>
       </c>
-      <c r="E32" s="34" t="n">
+      <c r="E32" s="36" t="n">
         <v>0.18</v>
       </c>
-      <c r="F32" s="35" t="n">
+      <c r="F32" s="37" t="n">
         <v>0.9619</v>
       </c>
-      <c r="G32" s="35" t="n">
+      <c r="G32" s="37" t="n">
         <v>1.0396</v>
       </c>
-      <c r="H32" s="34" t="n">
+      <c r="H32" s="36" t="n">
         <v>0.491</v>
       </c>
-      <c r="I32" s="34" t="n">
+      <c r="I32" s="36" t="n">
         <v>1.433</v>
       </c>
-      <c r="J32" s="34" t="n">
+      <c r="J32" s="36" t="n">
         <v>0.51</v>
       </c>
-      <c r="K32" s="34" t="n">
+      <c r="K32" s="36" t="n">
         <v>1.49</v>
       </c>
-      <c r="L32" s="34" t="n">
+      <c r="L32" s="36" t="n">
         <v>3.735</v>
       </c>
-      <c r="M32" s="35" t="n">
+      <c r="M32" s="37" t="n">
         <v>0.2677</v>
       </c>
-      <c r="N32" s="36" t="n">
+      <c r="N32" s="38" t="n">
         <v>1.548</v>
       </c>
-      <c r="O32" s="36" t="n">
+      <c r="O32" s="38" t="n">
         <v>5.922</v>
       </c>
-      <c r="P32" s="36" t="n">
+      <c r="P32" s="38" t="n">
         <v>0.414</v>
       </c>
-      <c r="Q32" s="36" t="n">
+      <c r="Q32" s="38" t="n">
         <v>1.586</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="n">
+      <c r="A33" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="34" t="n">
+      <c r="B33" s="36" t="n">
         <v>0.655</v>
       </c>
-      <c r="C33" s="34" t="n">
+      <c r="C33" s="36" t="n">
         <v>3.639</v>
       </c>
-      <c r="D33" s="34" t="n">
+      <c r="D33" s="36" t="n">
         <v>0.679</v>
       </c>
-      <c r="E33" s="34" t="n">
+      <c r="E33" s="36" t="n">
         <v>0.173</v>
       </c>
-      <c r="F33" s="35" t="n">
+      <c r="F33" s="37" t="n">
         <v>0.9638</v>
       </c>
-      <c r="G33" s="35" t="n">
+      <c r="G33" s="37" t="n">
         <v>1.0376</v>
       </c>
-      <c r="H33" s="34" t="n">
+      <c r="H33" s="36" t="n">
         <v>0.504</v>
       </c>
-      <c r="I33" s="34" t="n">
+      <c r="I33" s="36" t="n">
         <v>1.424</v>
       </c>
-      <c r="J33" s="34" t="n">
+      <c r="J33" s="36" t="n">
         <v>0.523</v>
       </c>
-      <c r="K33" s="34" t="n">
+      <c r="K33" s="36" t="n">
         <v>1.477</v>
       </c>
-      <c r="L33" s="34" t="n">
+      <c r="L33" s="36" t="n">
         <v>3.778</v>
       </c>
-      <c r="M33" s="35" t="n">
+      <c r="M33" s="37" t="n">
         <v>0.2647</v>
       </c>
-      <c r="N33" s="36" t="n">
+      <c r="N33" s="38" t="n">
         <v>1.606</v>
       </c>
-      <c r="O33" s="36" t="n">
+      <c r="O33" s="38" t="n">
         <v>5.95</v>
       </c>
-      <c r="P33" s="34" t="n">
+      <c r="P33" s="36" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q33" s="34" t="n">
+      <c r="Q33" s="36" t="n">
         <v>1.575</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="33" t="n">
+      <c r="A34" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="34" t="n">
+      <c r="B34" s="36" t="n">
         <v>0.64</v>
       </c>
-      <c r="C34" s="34" t="n">
+      <c r="C34" s="36" t="n">
         <v>3.684</v>
       </c>
-      <c r="D34" s="34" t="n">
+      <c r="D34" s="36" t="n">
         <v>0.662</v>
       </c>
-      <c r="E34" s="34" t="n">
+      <c r="E34" s="36" t="n">
         <v>0.167</v>
       </c>
-      <c r="F34" s="35" t="n">
+      <c r="F34" s="37" t="n">
         <v>0.9655</v>
       </c>
-      <c r="G34" s="35" t="n">
+      <c r="G34" s="37" t="n">
         <v>1.0358</v>
       </c>
-      <c r="H34" s="34" t="n">
+      <c r="H34" s="36" t="n">
         <v>0.516</v>
       </c>
-      <c r="I34" s="34" t="n">
+      <c r="I34" s="36" t="n">
         <v>1.415</v>
       </c>
-      <c r="J34" s="34" t="n">
+      <c r="J34" s="36" t="n">
         <v>0.534</v>
       </c>
-      <c r="K34" s="34" t="n">
+      <c r="K34" s="36" t="n">
         <v>1.466</v>
       </c>
-      <c r="L34" s="34" t="n">
+      <c r="L34" s="36" t="n">
         <v>3.819</v>
       </c>
-      <c r="M34" s="35" t="n">
+      <c r="M34" s="37" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N34" s="34" t="n">
+      <c r="N34" s="36" t="n">
         <v>1.659</v>
       </c>
-      <c r="O34" s="34" t="n">
+      <c r="O34" s="36" t="n">
         <v>5.979</v>
       </c>
-      <c r="P34" s="34" t="n">
+      <c r="P34" s="36" t="n">
         <v>0.434</v>
       </c>
-      <c r="Q34" s="34" t="n">
+      <c r="Q34" s="36" t="n">
         <v>1.566</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="n">
+      <c r="A35" s="35" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="34" t="n">
+      <c r="B35" s="36" t="n">
         <v>0.626</v>
       </c>
-      <c r="C35" s="34" t="n">
+      <c r="C35" s="36" t="n">
         <v>3.729</v>
       </c>
-      <c r="D35" s="34" t="n">
+      <c r="D35" s="36" t="n">
         <v>0.647</v>
       </c>
-      <c r="E35" s="34" t="n">
+      <c r="E35" s="36" t="n">
         <v>0.162</v>
       </c>
-      <c r="F35" s="35" t="n">
+      <c r="F35" s="37" t="n">
         <v>0.967</v>
       </c>
-      <c r="G35" s="35" t="n">
+      <c r="G35" s="37" t="n">
         <v>1.0342</v>
       </c>
-      <c r="H35" s="34" t="n">
+      <c r="H35" s="36" t="n">
         <v>0.527</v>
       </c>
-      <c r="I35" s="34" t="n">
+      <c r="I35" s="36" t="n">
         <v>1.407</v>
       </c>
-      <c r="J35" s="34" t="n">
+      <c r="J35" s="36" t="n">
         <v>0.545</v>
       </c>
-      <c r="K35" s="34" t="n">
+      <c r="K35" s="36" t="n">
         <v>1.455</v>
       </c>
-      <c r="L35" s="34" t="n">
+      <c r="L35" s="36" t="n">
         <v>3.858</v>
       </c>
-      <c r="M35" s="35" t="n">
+      <c r="M35" s="37" t="n">
         <v>0.2592</v>
       </c>
-      <c r="N35" s="34" t="n">
+      <c r="N35" s="36" t="n">
         <v>1.71</v>
       </c>
-      <c r="O35" s="34" t="n">
+      <c r="O35" s="36" t="n">
         <v>6.006</v>
       </c>
-      <c r="P35" s="34" t="n">
+      <c r="P35" s="36" t="n">
         <v>0.443</v>
       </c>
-      <c r="Q35" s="34" t="n">
+      <c r="Q35" s="36" t="n">
         <v>1.557</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="n">
+      <c r="A36" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="34" t="n">
+      <c r="B36" s="36" t="n">
         <v>0.612</v>
       </c>
-      <c r="C36" s="34" t="n">
+      <c r="C36" s="36" t="n">
         <v>3.773</v>
       </c>
-      <c r="D36" s="34" t="n">
+      <c r="D36" s="36" t="n">
         <v>0.632</v>
       </c>
-      <c r="E36" s="34" t="n">
+      <c r="E36" s="36" t="n">
         <v>0.157</v>
       </c>
-      <c r="F36" s="35" t="n">
+      <c r="F36" s="37" t="n">
         <v>0.9684</v>
       </c>
-      <c r="G36" s="35" t="n">
+      <c r="G36" s="37" t="n">
         <v>1.0327</v>
       </c>
-      <c r="H36" s="34" t="n">
+      <c r="H36" s="36" t="n">
         <v>0.538</v>
       </c>
-      <c r="I36" s="34" t="n">
+      <c r="I36" s="36" t="n">
         <v>1.399</v>
       </c>
-      <c r="J36" s="34" t="n">
+      <c r="J36" s="36" t="n">
         <v>0.555</v>
       </c>
-      <c r="K36" s="34" t="n">
+      <c r="K36" s="36" t="n">
         <v>1.445</v>
       </c>
-      <c r="L36" s="34" t="n">
+      <c r="L36" s="36" t="n">
         <v>3.895</v>
       </c>
-      <c r="M36" s="35" t="n">
+      <c r="M36" s="37" t="n">
         <v>0.2567</v>
       </c>
-      <c r="N36" s="34" t="n">
+      <c r="N36" s="36" t="n">
         <v>1.759</v>
       </c>
-      <c r="O36" s="34" t="n">
+      <c r="O36" s="36" t="n">
         <v>6.031</v>
       </c>
-      <c r="P36" s="36" t="n">
+      <c r="P36" s="38" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q36" s="34" t="n">
+      <c r="Q36" s="36" t="n">
         <v>1.548</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="n">
+      <c r="A37" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="34" t="n">
+      <c r="B37" s="36" t="n">
         <v>0.6</v>
       </c>
-      <c r="C37" s="34" t="n">
+      <c r="C37" s="36" t="n">
         <v>3.816</v>
       </c>
-      <c r="D37" s="34" t="n">
+      <c r="D37" s="36" t="n">
         <v>0.619</v>
       </c>
-      <c r="E37" s="34" t="n">
+      <c r="E37" s="36" t="n">
         <v>0.153</v>
       </c>
-      <c r="F37" s="37" t="n">
+      <c r="F37" s="39" t="n">
         <v>0.9696</v>
       </c>
-      <c r="G37" s="35" t="n">
+      <c r="G37" s="37" t="n">
         <v>1.0313</v>
       </c>
-      <c r="H37" s="34" t="n">
+      <c r="H37" s="36" t="n">
         <v>0.548</v>
       </c>
-      <c r="I37" s="34" t="n">
+      <c r="I37" s="36" t="n">
         <v>1.392</v>
       </c>
-      <c r="J37" s="34" t="n">
+      <c r="J37" s="36" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="K37" s="34" t="n">
+      <c r="K37" s="36" t="n">
         <v>1.435</v>
       </c>
-      <c r="L37" s="34" t="n">
+      <c r="L37" s="36" t="n">
         <v>3.931</v>
       </c>
-      <c r="M37" s="35" t="n">
+      <c r="M37" s="37" t="n">
         <v>0.2544</v>
       </c>
-      <c r="N37" s="36" t="n">
+      <c r="N37" s="38" t="n">
         <v>1.804</v>
       </c>
-      <c r="O37" s="36" t="n">
+      <c r="O37" s="38" t="n">
         <v>6.058</v>
       </c>
-      <c r="P37" s="34" t="n">
+      <c r="P37" s="36" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q37" s="34" t="n">
+      <c r="Q37" s="36" t="n">
         <v>1.541</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>&gt;25</t>
         </is>
       </c>
-      <c r="B38" s="38" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="C38" s="38" t="inlineStr"/>
-      <c r="D38" s="38" t="inlineStr">
+      <c r="C38" s="40" t="inlineStr"/>
+      <c r="D38" s="40" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="E38" s="38" t="inlineStr"/>
-      <c r="F38" s="35" t="n">
+      <c r="E38" s="40" t="inlineStr"/>
+      <c r="F38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="35" t="n">
+      <c r="G38" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="38" t="inlineStr">
+      <c r="H38" s="40" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="I38" s="38" t="inlineStr">
+      <c r="I38" s="40" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="J38" s="38" t="inlineStr">
+      <c r="J38" s="40" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="K38" s="38" t="inlineStr">
+      <c r="K38" s="40" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L38" s="38" t="inlineStr"/>
-      <c r="M38" s="38" t="inlineStr"/>
-      <c r="N38" s="38" t="inlineStr"/>
-      <c r="O38" s="38" t="inlineStr"/>
-      <c r="P38" s="38" t="inlineStr"/>
-      <c r="Q38" s="38" t="inlineStr"/>
+      <c r="L38" s="40" t="inlineStr"/>
+      <c r="M38" s="40" t="inlineStr"/>
+      <c r="N38" s="40" t="inlineStr"/>
+      <c r="O38" s="40" t="inlineStr"/>
+      <c r="P38" s="40" t="inlineStr"/>
+      <c r="Q38" s="40" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
@@ -9051,580 +9690,580 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="n">
+      <c r="A44" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="34" t="n">
+      <c r="B44" s="36" t="n">
         <v>1.128</v>
       </c>
-      <c r="C44" s="35" t="n">
+      <c r="C44" s="37" t="n">
         <v>0.5642</v>
       </c>
-      <c r="D44" s="35" t="n">
+      <c r="D44" s="37" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="E44" s="35" t="n">
+      <c r="E44" s="37" t="n">
         <v>0.8525</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="n">
+      <c r="A45" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="34" t="n">
+      <c r="B45" s="36" t="n">
         <v>1.693</v>
       </c>
-      <c r="C45" s="35" t="n">
+      <c r="C45" s="37" t="n">
         <v>0.7236</v>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="37" t="n">
         <v>0.8862</v>
       </c>
-      <c r="E45" s="35" t="n">
+      <c r="E45" s="37" t="n">
         <v>0.8884</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="n">
+      <c r="A46" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="34" t="n">
+      <c r="B46" s="36" t="n">
         <v>2.059</v>
       </c>
-      <c r="C46" s="35" t="n">
+      <c r="C46" s="37" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="D46" s="35" t="n">
+      <c r="D46" s="37" t="n">
         <v>0.9213</v>
       </c>
-      <c r="E46" s="35" t="n">
+      <c r="E46" s="37" t="n">
         <v>0.8798</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="n">
+      <c r="A47" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="34" t="n">
+      <c r="B47" s="36" t="n">
         <v>2.326</v>
       </c>
-      <c r="C47" s="35" t="n">
+      <c r="C47" s="37" t="n">
         <v>0.8407</v>
       </c>
-      <c r="D47" s="35" t="n">
+      <c r="D47" s="37" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E47" s="35" t="n">
+      <c r="E47" s="37" t="n">
         <v>0.8641</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="33" t="n">
+      <c r="A48" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="34" t="n">
+      <c r="B48" s="36" t="n">
         <v>2.534</v>
       </c>
-      <c r="C48" s="35" t="n">
+      <c r="C48" s="37" t="n">
         <v>0.8686</v>
       </c>
-      <c r="D48" s="35" t="n">
+      <c r="D48" s="37" t="n">
         <v>0.9515</v>
       </c>
-      <c r="E48" s="35" t="n">
+      <c r="E48" s="37" t="n">
         <v>0.848</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="n">
+      <c r="A49" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="34" t="n">
+      <c r="B49" s="36" t="n">
         <v>2.704</v>
       </c>
-      <c r="C49" s="35" t="n">
+      <c r="C49" s="37" t="n">
         <v>0.8882</v>
       </c>
-      <c r="D49" s="35" t="n">
+      <c r="D49" s="37" t="n">
         <v>0.9594</v>
       </c>
-      <c r="E49" s="35" t="n">
+      <c r="E49" s="37" t="n">
         <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="n">
+      <c r="A50" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="34" t="n">
+      <c r="B50" s="36" t="n">
         <v>2.847</v>
       </c>
-      <c r="C50" s="35" t="n">
+      <c r="C50" s="37" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="D50" s="35" t="n">
+      <c r="D50" s="37" t="n">
         <v>0.965</v>
       </c>
-      <c r="E50" s="35" t="n">
+      <c r="E50" s="37" t="n">
         <v>0.8198</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="n">
+      <c r="A51" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="34" t="n">
+      <c r="B51" s="36" t="n">
         <v>2.97</v>
       </c>
-      <c r="C51" s="35" t="n">
+      <c r="C51" s="37" t="n">
         <v>0.9139</v>
       </c>
-      <c r="D51" s="35" t="n">
+      <c r="D51" s="37" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="E51" s="35" t="n">
+      <c r="E51" s="37" t="n">
         <v>0.8078</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="33" t="n">
+      <c r="A52" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="34" t="n">
+      <c r="B52" s="36" t="n">
         <v>3.078</v>
       </c>
-      <c r="C52" s="35" t="n">
+      <c r="C52" s="37" t="n">
         <v>0.9227</v>
       </c>
-      <c r="D52" s="35" t="n">
+      <c r="D52" s="37" t="n">
         <v>0.9727</v>
       </c>
-      <c r="E52" s="35" t="n">
+      <c r="E52" s="37" t="n">
         <v>0.7971</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="n">
+      <c r="A53" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="34" t="n">
+      <c r="B53" s="36" t="n">
         <v>3.173</v>
       </c>
-      <c r="C53" s="35" t="n">
+      <c r="C53" s="37" t="n">
         <v>0.93</v>
       </c>
-      <c r="D53" s="35" t="n">
+      <c r="D53" s="37" t="n">
         <v>0.9754</v>
       </c>
-      <c r="E53" s="35" t="n">
+      <c r="E53" s="37" t="n">
         <v>0.7873</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="33" t="n">
+      <c r="A54" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="34" t="n">
+      <c r="B54" s="36" t="n">
         <v>3.258</v>
       </c>
-      <c r="C54" s="35" t="n">
+      <c r="C54" s="37" t="n">
         <v>0.9359</v>
       </c>
-      <c r="D54" s="35" t="n">
+      <c r="D54" s="37" t="n">
         <v>0.9776</v>
       </c>
-      <c r="E54" s="37" t="n">
+      <c r="E54" s="39" t="n">
         <v>0.7785</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="n">
+      <c r="A55" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="34" t="n">
+      <c r="B55" s="36" t="n">
         <v>3.336</v>
       </c>
-      <c r="C55" s="35" t="n">
+      <c r="C55" s="37" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="D55" s="35" t="n">
+      <c r="D55" s="37" t="n">
         <v>0.9794</v>
       </c>
-      <c r="E55" s="35" t="n">
+      <c r="E55" s="37" t="n">
         <v>0.7704</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="33" t="n">
+      <c r="A56" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="34" t="n">
+      <c r="B56" s="36" t="n">
         <v>3.407</v>
       </c>
-      <c r="C56" s="35" t="n">
+      <c r="C56" s="37" t="n">
         <v>0.9453</v>
       </c>
-      <c r="D56" s="35" t="n">
+      <c r="D56" s="37" t="n">
         <v>0.981</v>
       </c>
-      <c r="E56" s="35" t="n">
+      <c r="E56" s="37" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="n">
+      <c r="A57" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="34" t="n">
+      <c r="B57" s="36" t="n">
         <v>3.472</v>
       </c>
-      <c r="C57" s="35" t="n">
+      <c r="C57" s="37" t="n">
         <v>0.949</v>
       </c>
-      <c r="D57" s="35" t="n">
+      <c r="D57" s="37" t="n">
         <v>0.9823</v>
       </c>
-      <c r="E57" s="35" t="n">
+      <c r="E57" s="37" t="n">
         <v>0.7562</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="33" t="n">
+      <c r="A58" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B58" s="34" t="n">
+      <c r="B58" s="36" t="n">
         <v>3.532</v>
       </c>
-      <c r="C58" s="35" t="n">
+      <c r="C58" s="37" t="n">
         <v>0.9523</v>
       </c>
-      <c r="D58" s="35" t="n">
+      <c r="D58" s="37" t="n">
         <v>0.9835</v>
       </c>
-      <c r="E58" s="35" t="n">
+      <c r="E58" s="37" t="n">
         <v>0.7499</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="33" t="n">
+      <c r="A59" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="B59" s="34" t="n">
+      <c r="B59" s="36" t="n">
         <v>3.588</v>
       </c>
-      <c r="C59" s="35" t="n">
+      <c r="C59" s="37" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="D59" s="35" t="n">
+      <c r="D59" s="37" t="n">
         <v>0.9845</v>
       </c>
-      <c r="E59" s="35" t="n">
+      <c r="E59" s="37" t="n">
         <v>0.7441</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="33" t="n">
+      <c r="A60" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B60" s="34" t="n">
+      <c r="B60" s="36" t="n">
         <v>3.64</v>
       </c>
-      <c r="C60" s="35" t="n">
+      <c r="C60" s="37" t="n">
         <v>0.9576</v>
       </c>
-      <c r="D60" s="35" t="n">
+      <c r="D60" s="37" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="E60" s="35" t="n">
+      <c r="E60" s="37" t="n">
         <v>0.7386</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="33" t="n">
+      <c r="A61" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="B61" s="34" t="n">
+      <c r="B61" s="36" t="n">
         <v>3.689</v>
       </c>
-      <c r="C61" s="35" t="n">
+      <c r="C61" s="37" t="n">
         <v>0.9599</v>
       </c>
-      <c r="D61" s="35" t="n">
+      <c r="D61" s="37" t="n">
         <v>0.9862</v>
       </c>
-      <c r="E61" s="35" t="n">
+      <c r="E61" s="37" t="n">
         <v>0.7335</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="33" t="n">
+      <c r="A62" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="B62" s="34" t="n">
+      <c r="B62" s="36" t="n">
         <v>3.735</v>
       </c>
-      <c r="C62" s="35" t="n">
+      <c r="C62" s="37" t="n">
         <v>0.9619</v>
       </c>
-      <c r="D62" s="35" t="n">
+      <c r="D62" s="37" t="n">
         <v>0.9869</v>
       </c>
-      <c r="E62" s="35" t="n">
+      <c r="E62" s="37" t="n">
         <v>0.7287</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="33" t="n">
+      <c r="A63" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="34" t="n">
+      <c r="B63" s="36" t="n">
         <v>3.778</v>
       </c>
-      <c r="C63" s="35" t="n">
+      <c r="C63" s="37" t="n">
         <v>0.9638</v>
       </c>
-      <c r="D63" s="35" t="n">
+      <c r="D63" s="37" t="n">
         <v>0.9876</v>
       </c>
-      <c r="E63" s="37" t="n">
+      <c r="E63" s="39" t="n">
         <v>0.7272</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="33" t="n">
+      <c r="A64" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="B64" s="34" t="n">
+      <c r="B64" s="36" t="n">
         <v>3.819</v>
       </c>
-      <c r="C64" s="35" t="n">
+      <c r="C64" s="37" t="n">
         <v>0.9655</v>
       </c>
-      <c r="D64" s="35" t="n">
+      <c r="D64" s="37" t="n">
         <v>0.9882</v>
       </c>
-      <c r="E64" s="35" t="n">
+      <c r="E64" s="37" t="n">
         <v>0.7199</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="33" t="n">
+      <c r="A65" s="35" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="34" t="n">
+      <c r="B65" s="36" t="n">
         <v>3.858</v>
       </c>
-      <c r="C65" s="35" t="n">
+      <c r="C65" s="37" t="n">
         <v>0.967</v>
       </c>
-      <c r="D65" s="35" t="n">
+      <c r="D65" s="37" t="n">
         <v>0.9887</v>
       </c>
-      <c r="E65" s="35" t="n">
+      <c r="E65" s="37" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="33" t="n">
+      <c r="A66" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="34" t="n">
+      <c r="B66" s="36" t="n">
         <v>3.895</v>
       </c>
-      <c r="C66" s="35" t="n">
+      <c r="C66" s="37" t="n">
         <v>0.9684</v>
       </c>
-      <c r="D66" s="35" t="n">
+      <c r="D66" s="37" t="n">
         <v>0.9892</v>
       </c>
-      <c r="E66" s="35" t="n">
+      <c r="E66" s="37" t="n">
         <v>0.7121</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="33" t="n">
+      <c r="A67" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="B67" s="34" t="n">
+      <c r="B67" s="36" t="n">
         <v>3.931</v>
       </c>
-      <c r="C67" s="37" t="n">
+      <c r="C67" s="39" t="n">
         <v>0.9695</v>
       </c>
-      <c r="D67" s="35" t="n">
+      <c r="D67" s="37" t="n">
         <v>0.9896</v>
       </c>
-      <c r="E67" s="35" t="n">
+      <c r="E67" s="37" t="n">
         <v>0.7084</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="33" t="n">
+      <c r="A68" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B68" s="34" t="n">
+      <c r="B68" s="36" t="n">
         <v>4.086</v>
       </c>
-      <c r="C68" s="35" t="n">
+      <c r="C68" s="37" t="n">
         <v>0.9748</v>
       </c>
-      <c r="D68" s="35" t="n">
+      <c r="D68" s="37" t="n">
         <v>0.9915</v>
       </c>
-      <c r="E68" s="35" t="n">
+      <c r="E68" s="37" t="n">
         <v>0.6927</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="33" t="n">
+      <c r="A69" s="35" t="n">
         <v>35</v>
       </c>
-      <c r="B69" s="34" t="n">
+      <c r="B69" s="36" t="n">
         <v>4.213</v>
       </c>
-      <c r="C69" s="35" t="n">
+      <c r="C69" s="37" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D69" s="35" t="n">
+      <c r="D69" s="37" t="n">
         <v>0.9927</v>
       </c>
-      <c r="E69" s="35" t="n">
+      <c r="E69" s="37" t="n">
         <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="33" t="n">
+      <c r="A70" s="35" t="n">
         <v>40</v>
       </c>
-      <c r="B70" s="34" t="n">
+      <c r="B70" s="36" t="n">
         <v>4.322</v>
       </c>
-      <c r="C70" s="35" t="n">
+      <c r="C70" s="37" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D70" s="35" t="n">
+      <c r="D70" s="37" t="n">
         <v>0.9936</v>
       </c>
-      <c r="E70" s="35" t="n">
+      <c r="E70" s="37" t="n">
         <v>0.6692</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="33" t="n">
+      <c r="A71" s="35" t="n">
         <v>45</v>
       </c>
-      <c r="B71" s="34" t="n">
+      <c r="B71" s="36" t="n">
         <v>4.415</v>
       </c>
-      <c r="C71" s="35" t="n">
+      <c r="C71" s="37" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D71" s="35" t="n">
+      <c r="D71" s="37" t="n">
         <v>0.9943</v>
       </c>
-      <c r="E71" s="35" t="n">
+      <c r="E71" s="37" t="n">
         <v>0.6601</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="33" t="n">
+      <c r="A72" s="35" t="n">
         <v>50</v>
       </c>
-      <c r="B72" s="34" t="n">
+      <c r="B72" s="36" t="n">
         <v>4.498</v>
       </c>
-      <c r="C72" s="35" t="n">
+      <c r="C72" s="37" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D72" s="35" t="n">
+      <c r="D72" s="37" t="n">
         <v>0.9949</v>
       </c>
-      <c r="E72" s="35" t="n">
+      <c r="E72" s="37" t="n">
         <v>0.6521</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="33" t="n">
+      <c r="A73" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="B73" s="34" t="n">
+      <c r="B73" s="36" t="n">
         <v>4.639</v>
       </c>
-      <c r="C73" s="35" t="n">
+      <c r="C73" s="37" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D73" s="35" t="n">
+      <c r="D73" s="37" t="n">
         <v>0.9957</v>
       </c>
-      <c r="E73" s="35" t="n">
+      <c r="E73" s="37" t="n">
         <v>0.6389</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="33" t="n">
+      <c r="A74" s="35" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="34" t="n">
+      <c r="B74" s="36" t="n">
         <v>4.755</v>
       </c>
-      <c r="C74" s="35" t="n">
+      <c r="C74" s="37" t="n">
         <v>0.9892</v>
       </c>
-      <c r="D74" s="35" t="n">
+      <c r="D74" s="37" t="n">
         <v>0.9963</v>
       </c>
-      <c r="E74" s="35" t="n">
+      <c r="E74" s="37" t="n">
         <v>0.6283</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="33" t="n">
+      <c r="A75" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="B75" s="34" t="n">
+      <c r="B75" s="36" t="n">
         <v>4.854</v>
       </c>
-      <c r="C75" s="35" t="n">
+      <c r="C75" s="37" t="n">
         <v>0.9906</v>
       </c>
-      <c r="D75" s="35" t="n">
+      <c r="D75" s="37" t="n">
         <v>0.9968</v>
       </c>
-      <c r="E75" s="35" t="n">
+      <c r="E75" s="37" t="n">
         <v>0.6194</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="33" t="n">
+      <c r="A76" s="35" t="n">
         <v>90</v>
       </c>
-      <c r="B76" s="34" t="n">
+      <c r="B76" s="36" t="n">
         <v>4.939</v>
       </c>
-      <c r="C76" s="35" t="n">
+      <c r="C76" s="37" t="n">
         <v>0.9916</v>
       </c>
-      <c r="D76" s="35" t="n">
+      <c r="D76" s="37" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E76" s="35" t="n">
+      <c r="E76" s="37" t="n">
         <v>0.6118</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="33" t="n">
+      <c r="A77" s="35" t="n">
         <v>100</v>
       </c>
-      <c r="B77" s="34" t="n">
+      <c r="B77" s="36" t="n">
         <v>5.015</v>
       </c>
-      <c r="C77" s="35" t="n">
+      <c r="C77" s="37" t="n">
         <v>0.9925</v>
       </c>
-      <c r="D77" s="35" t="n">
+      <c r="D77" s="37" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="E77" s="35" t="n">
+      <c r="E77" s="37" t="n">
         <v>0.6052</v>
       </c>
     </row>
@@ -9702,786 +10341,786 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="33" t="n">
+      <c r="A83" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="34" t="n">
+      <c r="B83" s="36" t="n">
         <v>2.121</v>
       </c>
-      <c r="C83" s="34" t="n">
+      <c r="C83" s="36" t="n">
         <v>1.88</v>
       </c>
-      <c r="D83" s="34" t="n">
+      <c r="D83" s="36" t="n">
         <v>2.659</v>
       </c>
-      <c r="E83" s="35" t="n">
+      <c r="E83" s="37" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="F83" s="35" t="n">
+      <c r="F83" s="37" t="n">
         <v>1.2533</v>
       </c>
-      <c r="G83" s="33" t="n">
+      <c r="G83" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="34" t="n">
+      <c r="H83" s="36" t="n">
         <v>3.267</v>
       </c>
-      <c r="I83" s="33" t="n">
+      <c r="I83" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="34" t="n">
+      <c r="J83" s="36" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="33" t="n">
+      <c r="A84" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="B84" s="34" t="n">
+      <c r="B84" s="36" t="n">
         <v>2.606</v>
       </c>
-      <c r="C84" s="38" t="inlineStr"/>
-      <c r="D84" s="38" t="inlineStr"/>
-      <c r="E84" s="38" t="inlineStr"/>
-      <c r="F84" s="38" t="inlineStr"/>
-      <c r="G84" s="38" t="inlineStr"/>
-      <c r="H84" s="38" t="inlineStr"/>
-      <c r="I84" s="38" t="inlineStr"/>
-      <c r="J84" s="38" t="inlineStr"/>
+      <c r="C84" s="40" t="inlineStr"/>
+      <c r="D84" s="40" t="inlineStr"/>
+      <c r="E84" s="40" t="inlineStr"/>
+      <c r="F84" s="40" t="inlineStr"/>
+      <c r="G84" s="40" t="inlineStr"/>
+      <c r="H84" s="40" t="inlineStr"/>
+      <c r="I84" s="40" t="inlineStr"/>
+      <c r="J84" s="40" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="33" t="n">
+      <c r="A85" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="34" t="n">
+      <c r="B85" s="36" t="n">
         <v>1.732</v>
       </c>
-      <c r="C85" s="34" t="n">
+      <c r="C85" s="36" t="n">
         <v>1.023</v>
       </c>
-      <c r="D85" s="34" t="n">
+      <c r="D85" s="36" t="n">
         <v>1.954</v>
       </c>
-      <c r="E85" s="35" t="n">
+      <c r="E85" s="37" t="n">
         <v>0.8862</v>
       </c>
-      <c r="F85" s="35" t="n">
+      <c r="F85" s="37" t="n">
         <v>1.1284</v>
       </c>
-      <c r="G85" s="33" t="n">
+      <c r="G85" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="34" t="n">
+      <c r="H85" s="36" t="n">
         <v>2.568</v>
       </c>
-      <c r="I85" s="33" t="n">
+      <c r="I85" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="34" t="n">
+      <c r="J85" s="36" t="n">
         <v>2.276</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="33" t="n">
+      <c r="A86" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="34" t="n">
+      <c r="B86" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="C86" s="34" t="n">
+      <c r="C86" s="36" t="n">
         <v>0.729</v>
       </c>
-      <c r="D86" s="34" t="n">
+      <c r="D86" s="36" t="n">
         <v>1.628</v>
       </c>
-      <c r="E86" s="35" t="n">
+      <c r="E86" s="37" t="n">
         <v>0.9213</v>
       </c>
-      <c r="F86" s="35" t="n">
+      <c r="F86" s="37" t="n">
         <v>1.0854</v>
       </c>
-      <c r="G86" s="33" t="n">
+      <c r="G86" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="34" t="n">
+      <c r="H86" s="36" t="n">
         <v>2.266</v>
       </c>
-      <c r="I86" s="33" t="n">
+      <c r="I86" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="34" t="n">
+      <c r="J86" s="36" t="n">
         <v>2.088</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="33" t="n">
+      <c r="A87" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="34" t="n">
+      <c r="B87" s="36" t="n">
         <v>1.342</v>
       </c>
-      <c r="C87" s="34" t="n">
+      <c r="C87" s="36" t="n">
         <v>0.577</v>
       </c>
-      <c r="D87" s="34" t="n">
+      <c r="D87" s="36" t="n">
         <v>1.427</v>
       </c>
-      <c r="E87" s="35" t="n">
+      <c r="E87" s="37" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F87" s="35" t="n">
+      <c r="F87" s="37" t="n">
         <v>1.0638</v>
       </c>
-      <c r="G87" s="33" t="n">
+      <c r="G87" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="34" t="n">
+      <c r="H87" s="36" t="n">
         <v>2.089</v>
       </c>
-      <c r="I87" s="33" t="n">
+      <c r="I87" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="34" t="n">
+      <c r="J87" s="36" t="n">
         <v>1.964</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="33" t="n">
+      <c r="A88" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B88" s="34" t="n">
+      <c r="B88" s="36" t="n">
         <v>1.225</v>
       </c>
-      <c r="C88" s="34" t="n">
+      <c r="C88" s="36" t="n">
         <v>0.483</v>
       </c>
-      <c r="D88" s="34" t="n">
+      <c r="D88" s="36" t="n">
         <v>1.287</v>
       </c>
-      <c r="E88" s="35" t="n">
+      <c r="E88" s="37" t="n">
         <v>0.9515</v>
       </c>
-      <c r="F88" s="35" t="n">
+      <c r="F88" s="37" t="n">
         <v>1.051</v>
       </c>
-      <c r="G88" s="34" t="n">
+      <c r="G88" s="36" t="n">
         <v>0.03</v>
       </c>
-      <c r="H88" s="34" t="n">
+      <c r="H88" s="36" t="n">
         <v>1.97</v>
       </c>
-      <c r="I88" s="34" t="n">
+      <c r="I88" s="36" t="n">
         <v>0.029</v>
       </c>
-      <c r="J88" s="34" t="n">
+      <c r="J88" s="36" t="n">
         <v>1.874</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="33" t="n">
+      <c r="A89" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B89" s="34" t="n">
+      <c r="B89" s="36" t="n">
         <v>1.134</v>
       </c>
-      <c r="C89" s="34" t="n">
+      <c r="C89" s="36" t="n">
         <v>0.419</v>
       </c>
-      <c r="D89" s="34" t="n">
+      <c r="D89" s="36" t="n">
         <v>1.182</v>
       </c>
-      <c r="E89" s="35" t="n">
+      <c r="E89" s="37" t="n">
         <v>0.9594</v>
       </c>
-      <c r="F89" s="35" t="n">
+      <c r="F89" s="37" t="n">
         <v>1.0423</v>
       </c>
-      <c r="G89" s="34" t="n">
+      <c r="G89" s="36" t="n">
         <v>0.118</v>
       </c>
-      <c r="H89" s="34" t="n">
+      <c r="H89" s="36" t="n">
         <v>1.882</v>
       </c>
-      <c r="I89" s="34" t="n">
+      <c r="I89" s="36" t="n">
         <v>0.113</v>
       </c>
-      <c r="J89" s="34" t="n">
+      <c r="J89" s="36" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="33" t="n">
+      <c r="A90" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="34" t="n">
+      <c r="B90" s="36" t="n">
         <v>1.061</v>
       </c>
-      <c r="C90" s="34" t="n">
+      <c r="C90" s="36" t="n">
         <v>0.373</v>
       </c>
-      <c r="D90" s="34" t="n">
+      <c r="D90" s="36" t="n">
         <v>1.099</v>
       </c>
-      <c r="E90" s="35" t="n">
+      <c r="E90" s="37" t="n">
         <v>0.965</v>
       </c>
-      <c r="F90" s="35" t="n">
+      <c r="F90" s="37" t="n">
         <v>1.0363</v>
       </c>
-      <c r="G90" s="34" t="n">
+      <c r="G90" s="36" t="n">
         <v>0.185</v>
       </c>
-      <c r="H90" s="34" t="n">
+      <c r="H90" s="36" t="n">
         <v>1.815</v>
       </c>
-      <c r="I90" s="34" t="n">
+      <c r="I90" s="36" t="n">
         <v>0.179</v>
       </c>
-      <c r="J90" s="34" t="n">
+      <c r="J90" s="36" t="n">
         <v>1.751</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="33" t="n">
+      <c r="A91" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="34" t="n">
+      <c r="B91" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="34" t="n">
+      <c r="C91" s="36" t="n">
         <v>0.337</v>
       </c>
-      <c r="D91" s="34" t="n">
+      <c r="D91" s="36" t="n">
         <v>1.032</v>
       </c>
-      <c r="E91" s="35" t="n">
+      <c r="E91" s="37" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="F91" s="35" t="n">
+      <c r="F91" s="37" t="n">
         <v>1.0317</v>
       </c>
-      <c r="G91" s="34" t="n">
+      <c r="G91" s="36" t="n">
         <v>0.239</v>
       </c>
-      <c r="H91" s="34" t="n">
+      <c r="H91" s="36" t="n">
         <v>1.761</v>
       </c>
-      <c r="I91" s="34" t="n">
+      <c r="I91" s="36" t="n">
         <v>0.232</v>
       </c>
-      <c r="J91" s="34" t="n">
+      <c r="J91" s="36" t="n">
         <v>1.707</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="33" t="n">
+      <c r="A92" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B92" s="34" t="n">
+      <c r="B92" s="36" t="n">
         <v>0.949</v>
       </c>
-      <c r="C92" s="34" t="n">
+      <c r="C92" s="36" t="n">
         <v>0.308</v>
       </c>
-      <c r="D92" s="34" t="n">
+      <c r="D92" s="36" t="n">
         <v>0.975</v>
       </c>
-      <c r="E92" s="35" t="n">
+      <c r="E92" s="37" t="n">
         <v>0.9727</v>
       </c>
-      <c r="F92" s="35" t="n">
+      <c r="F92" s="37" t="n">
         <v>1.0281</v>
       </c>
-      <c r="G92" s="34" t="n">
+      <c r="G92" s="36" t="n">
         <v>0.284</v>
       </c>
-      <c r="H92" s="34" t="n">
+      <c r="H92" s="36" t="n">
         <v>1.716</v>
       </c>
-      <c r="I92" s="34" t="n">
+      <c r="I92" s="36" t="n">
         <v>0.276</v>
       </c>
-      <c r="J92" s="34" t="n">
+      <c r="J92" s="36" t="n">
         <v>1.669</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="33" t="n">
+      <c r="A93" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B93" s="34" t="n">
+      <c r="B93" s="36" t="n">
         <v>0.905</v>
       </c>
-      <c r="C93" s="34" t="n">
+      <c r="C93" s="36" t="n">
         <v>0.285</v>
       </c>
-      <c r="D93" s="34" t="n">
+      <c r="D93" s="36" t="n">
         <v>0.927</v>
       </c>
-      <c r="E93" s="35" t="n">
+      <c r="E93" s="37" t="n">
         <v>0.9754</v>
       </c>
-      <c r="F93" s="35" t="n">
+      <c r="F93" s="37" t="n">
         <v>1.0252</v>
       </c>
-      <c r="G93" s="34" t="n">
+      <c r="G93" s="36" t="n">
         <v>0.321</v>
       </c>
-      <c r="H93" s="34" t="n">
+      <c r="H93" s="36" t="n">
         <v>1.679</v>
       </c>
-      <c r="I93" s="34" t="n">
+      <c r="I93" s="36" t="n">
         <v>0.313</v>
       </c>
-      <c r="J93" s="34" t="n">
+      <c r="J93" s="36" t="n">
         <v>1.637</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="33" t="n">
+      <c r="A94" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B94" s="34" t="n">
+      <c r="B94" s="36" t="n">
         <v>0.866</v>
       </c>
-      <c r="C94" s="34" t="n">
+      <c r="C94" s="36" t="n">
         <v>0.266</v>
       </c>
-      <c r="D94" s="34" t="n">
+      <c r="D94" s="36" t="n">
         <v>0.886</v>
       </c>
-      <c r="E94" s="35" t="n">
+      <c r="E94" s="37" t="n">
         <v>0.9776</v>
       </c>
-      <c r="F94" s="35" t="n">
+      <c r="F94" s="37" t="n">
         <v>1.0229</v>
       </c>
-      <c r="G94" s="34" t="n">
+      <c r="G94" s="36" t="n">
         <v>0.354</v>
       </c>
-      <c r="H94" s="34" t="n">
+      <c r="H94" s="36" t="n">
         <v>1.646</v>
       </c>
-      <c r="I94" s="34" t="n">
+      <c r="I94" s="36" t="n">
         <v>0.346</v>
       </c>
-      <c r="J94" s="34" t="n">
+      <c r="J94" s="36" t="n">
         <v>1.61</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="33" t="n">
+      <c r="A95" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B95" s="34" t="n">
+      <c r="B95" s="36" t="n">
         <v>0.832</v>
       </c>
-      <c r="C95" s="34" t="n">
+      <c r="C95" s="36" t="n">
         <v>0.249</v>
       </c>
-      <c r="D95" s="34" t="n">
+      <c r="D95" s="36" t="n">
         <v>0.85</v>
       </c>
-      <c r="E95" s="35" t="n">
+      <c r="E95" s="37" t="n">
         <v>0.9794</v>
       </c>
-      <c r="F95" s="35" t="n">
+      <c r="F95" s="37" t="n">
         <v>1.021</v>
       </c>
-      <c r="G95" s="34" t="n">
+      <c r="G95" s="36" t="n">
         <v>0.382</v>
       </c>
-      <c r="H95" s="34" t="n">
+      <c r="H95" s="36" t="n">
         <v>1.618</v>
       </c>
-      <c r="I95" s="34" t="n">
+      <c r="I95" s="36" t="n">
         <v>0.374</v>
       </c>
-      <c r="J95" s="34" t="n">
+      <c r="J95" s="36" t="n">
         <v>1.585</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="33" t="n">
+      <c r="A96" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B96" s="34" t="n">
+      <c r="B96" s="36" t="n">
         <v>0.802</v>
       </c>
-      <c r="C96" s="34" t="n">
+      <c r="C96" s="36" t="n">
         <v>0.235</v>
       </c>
-      <c r="D96" s="34" t="n">
+      <c r="D96" s="36" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E96" s="35" t="n">
+      <c r="E96" s="37" t="n">
         <v>0.981</v>
       </c>
-      <c r="F96" s="35" t="n">
+      <c r="F96" s="37" t="n">
         <v>1.0194</v>
       </c>
-      <c r="G96" s="34" t="n">
+      <c r="G96" s="36" t="n">
         <v>0.406</v>
       </c>
-      <c r="H96" s="34" t="n">
+      <c r="H96" s="36" t="n">
         <v>1.594</v>
       </c>
-      <c r="I96" s="34" t="n">
+      <c r="I96" s="36" t="n">
         <v>0.399</v>
       </c>
-      <c r="J96" s="34" t="n">
+      <c r="J96" s="36" t="n">
         <v>1.563</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="33" t="n">
+      <c r="A97" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="B97" s="34" t="n">
+      <c r="B97" s="36" t="n">
         <v>0.775</v>
       </c>
-      <c r="C97" s="34" t="n">
+      <c r="C97" s="36" t="n">
         <v>0.223</v>
       </c>
-      <c r="D97" s="34" t="n">
+      <c r="D97" s="36" t="n">
         <v>0.789</v>
       </c>
-      <c r="E97" s="35" t="n">
+      <c r="E97" s="37" t="n">
         <v>0.9823</v>
       </c>
-      <c r="F97" s="35" t="n">
+      <c r="F97" s="37" t="n">
         <v>1.018</v>
       </c>
-      <c r="G97" s="34" t="n">
+      <c r="G97" s="36" t="n">
         <v>0.428</v>
       </c>
-      <c r="H97" s="34" t="n">
+      <c r="H97" s="36" t="n">
         <v>1.572</v>
       </c>
-      <c r="I97" s="34" t="n">
+      <c r="I97" s="36" t="n">
         <v>0.421</v>
       </c>
-      <c r="J97" s="34" t="n">
+      <c r="J97" s="36" t="n">
         <v>1.544</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="33" t="n">
+      <c r="A98" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B98" s="34" t="n">
+      <c r="B98" s="36" t="n">
         <v>0.75</v>
       </c>
-      <c r="C98" s="34" t="n">
+      <c r="C98" s="36" t="n">
         <v>0.212</v>
       </c>
-      <c r="D98" s="34" t="n">
+      <c r="D98" s="36" t="n">
         <v>0.763</v>
       </c>
-      <c r="E98" s="35" t="n">
+      <c r="E98" s="37" t="n">
         <v>0.9835</v>
       </c>
-      <c r="F98" s="35" t="n">
+      <c r="F98" s="37" t="n">
         <v>1.0168</v>
       </c>
-      <c r="G98" s="34" t="n">
+      <c r="G98" s="36" t="n">
         <v>0.448</v>
       </c>
-      <c r="H98" s="34" t="n">
+      <c r="H98" s="36" t="n">
         <v>1.552</v>
       </c>
-      <c r="I98" s="34" t="n">
+      <c r="I98" s="36" t="n">
         <v>0.44</v>
       </c>
-      <c r="J98" s="34" t="n">
+      <c r="J98" s="36" t="n">
         <v>1.526</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="33" t="n">
+      <c r="A99" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="34" t="n">
+      <c r="B99" s="36" t="n">
         <v>0.728</v>
       </c>
-      <c r="C99" s="34" t="n">
+      <c r="C99" s="36" t="n">
         <v>0.203</v>
       </c>
-      <c r="D99" s="34" t="n">
+      <c r="D99" s="36" t="n">
         <v>0.739</v>
       </c>
-      <c r="E99" s="35" t="n">
+      <c r="E99" s="37" t="n">
         <v>0.9845</v>
       </c>
-      <c r="F99" s="35" t="n">
+      <c r="F99" s="37" t="n">
         <v>1.0157</v>
       </c>
-      <c r="G99" s="34" t="n">
+      <c r="G99" s="36" t="n">
         <v>0.466</v>
       </c>
-      <c r="H99" s="34" t="n">
+      <c r="H99" s="36" t="n">
         <v>1.534</v>
       </c>
-      <c r="I99" s="34" t="n">
+      <c r="I99" s="36" t="n">
         <v>0.458</v>
       </c>
-      <c r="J99" s="34" t="n">
+      <c r="J99" s="36" t="n">
         <v>1.511</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="33" t="n">
+      <c r="A100" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B100" s="34" t="n">
+      <c r="B100" s="36" t="n">
         <v>0.707</v>
       </c>
-      <c r="C100" s="34" t="n">
+      <c r="C100" s="36" t="n">
         <v>0.194</v>
       </c>
-      <c r="D100" s="34" t="n">
+      <c r="D100" s="36" t="n">
         <v>0.718</v>
       </c>
-      <c r="E100" s="35" t="n">
+      <c r="E100" s="37" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="F100" s="35" t="n">
+      <c r="F100" s="37" t="n">
         <v>1.0148</v>
       </c>
-      <c r="G100" s="34" t="n">
+      <c r="G100" s="36" t="n">
         <v>0.482</v>
       </c>
-      <c r="H100" s="34" t="n">
+      <c r="H100" s="36" t="n">
         <v>1.518</v>
       </c>
-      <c r="I100" s="34" t="n">
+      <c r="I100" s="36" t="n">
         <v>0.475</v>
       </c>
-      <c r="J100" s="34" t="n">
+      <c r="J100" s="36" t="n">
         <v>1.496</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="33" t="n">
+      <c r="A101" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="B101" s="34" t="n">
+      <c r="B101" s="36" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C101" s="34" t="n">
+      <c r="C101" s="36" t="n">
         <v>0.187</v>
       </c>
-      <c r="D101" s="34" t="n">
+      <c r="D101" s="36" t="n">
         <v>0.698</v>
       </c>
-      <c r="E101" s="35" t="n">
+      <c r="E101" s="37" t="n">
         <v>0.9862</v>
       </c>
-      <c r="F101" s="35" t="n">
+      <c r="F101" s="37" t="n">
         <v>1.014</v>
       </c>
-      <c r="G101" s="34" t="n">
+      <c r="G101" s="36" t="n">
         <v>0.497</v>
       </c>
-      <c r="H101" s="34" t="n">
+      <c r="H101" s="36" t="n">
         <v>1.503</v>
       </c>
-      <c r="I101" s="34" t="n">
+      <c r="I101" s="36" t="n">
         <v>0.49</v>
       </c>
-      <c r="J101" s="34" t="n">
+      <c r="J101" s="36" t="n">
         <v>1.483</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="33" t="n">
+      <c r="A102" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="B102" s="34" t="n">
+      <c r="B102" s="36" t="n">
         <v>0.671</v>
       </c>
-      <c r="C102" s="34" t="n">
+      <c r="C102" s="36" t="n">
         <v>0.18</v>
       </c>
-      <c r="D102" s="34" t="n">
+      <c r="D102" s="36" t="n">
         <v>0.68</v>
       </c>
-      <c r="E102" s="35" t="n">
+      <c r="E102" s="37" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F102" s="35" t="n">
+      <c r="F102" s="37" t="n">
         <v>1.0133</v>
       </c>
-      <c r="G102" s="34" t="n">
+      <c r="G102" s="36" t="n">
         <v>0.51</v>
       </c>
-      <c r="H102" s="34" t="n">
+      <c r="H102" s="36" t="n">
         <v>1.49</v>
       </c>
-      <c r="I102" s="34" t="n">
+      <c r="I102" s="36" t="n">
         <v>0.504</v>
       </c>
-      <c r="J102" s="34" t="n">
+      <c r="J102" s="36" t="n">
         <v>1.47</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="33" t="n">
+      <c r="A103" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="B103" s="34" t="n">
+      <c r="B103" s="36" t="n">
         <v>0.655</v>
       </c>
-      <c r="C103" s="34" t="n">
+      <c r="C103" s="36" t="n">
         <v>0.173</v>
       </c>
-      <c r="D103" s="34" t="n">
+      <c r="D103" s="36" t="n">
         <v>0.663</v>
       </c>
-      <c r="E103" s="35" t="n">
+      <c r="E103" s="37" t="n">
         <v>0.9876</v>
       </c>
-      <c r="F103" s="35" t="n">
+      <c r="F103" s="37" t="n">
         <v>1.0126</v>
       </c>
-      <c r="G103" s="34" t="n">
+      <c r="G103" s="36" t="n">
         <v>0.523</v>
       </c>
-      <c r="H103" s="34" t="n">
+      <c r="H103" s="36" t="n">
         <v>1.477</v>
       </c>
-      <c r="I103" s="34" t="n">
+      <c r="I103" s="36" t="n">
         <v>0.516</v>
       </c>
-      <c r="J103" s="34" t="n">
+      <c r="J103" s="36" t="n">
         <v>1.459</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="33" t="n">
+      <c r="A104" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="B104" s="34" t="n">
+      <c r="B104" s="36" t="n">
         <v>0.64</v>
       </c>
-      <c r="C104" s="34" t="n">
+      <c r="C104" s="36" t="n">
         <v>0.167</v>
       </c>
-      <c r="D104" s="34" t="n">
+      <c r="D104" s="36" t="n">
         <v>0.647</v>
       </c>
-      <c r="E104" s="35" t="n">
+      <c r="E104" s="37" t="n">
         <v>0.9882</v>
       </c>
-      <c r="F104" s="35" t="n">
+      <c r="F104" s="37" t="n">
         <v>1.0119</v>
       </c>
-      <c r="G104" s="34" t="n">
+      <c r="G104" s="36" t="n">
         <v>0.534</v>
       </c>
-      <c r="H104" s="34" t="n">
+      <c r="H104" s="36" t="n">
         <v>1.466</v>
       </c>
-      <c r="I104" s="34" t="n">
+      <c r="I104" s="36" t="n">
         <v>0.528</v>
       </c>
-      <c r="J104" s="34" t="n">
+      <c r="J104" s="36" t="n">
         <v>1.448</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="33" t="n">
+      <c r="A105" s="35" t="n">
         <v>23</v>
       </c>
-      <c r="B105" s="34" t="n">
+      <c r="B105" s="36" t="n">
         <v>0.626</v>
       </c>
-      <c r="C105" s="34" t="n">
+      <c r="C105" s="36" t="n">
         <v>0.162</v>
       </c>
-      <c r="D105" s="34" t="n">
+      <c r="D105" s="36" t="n">
         <v>0.633</v>
       </c>
-      <c r="E105" s="35" t="n">
+      <c r="E105" s="37" t="n">
         <v>0.9887</v>
       </c>
-      <c r="F105" s="35" t="n">
+      <c r="F105" s="37" t="n">
         <v>1.0114</v>
       </c>
-      <c r="G105" s="34" t="n">
+      <c r="G105" s="36" t="n">
         <v>0.545</v>
       </c>
-      <c r="H105" s="34" t="n">
+      <c r="H105" s="36" t="n">
         <v>1.455</v>
       </c>
-      <c r="I105" s="34" t="n">
+      <c r="I105" s="36" t="n">
         <v>0.539</v>
       </c>
-      <c r="J105" s="34" t="n">
+      <c r="J105" s="36" t="n">
         <v>1.438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="33" t="n">
+      <c r="A106" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="B106" s="34" t="n">
+      <c r="B106" s="36" t="n">
         <v>0.612</v>
       </c>
-      <c r="C106" s="34" t="n">
+      <c r="C106" s="36" t="n">
         <v>0.157</v>
       </c>
-      <c r="D106" s="34" t="n">
+      <c r="D106" s="36" t="n">
         <v>0.619</v>
       </c>
-      <c r="E106" s="35" t="n">
+      <c r="E106" s="37" t="n">
         <v>0.9892</v>
       </c>
-      <c r="F106" s="35" t="n">
+      <c r="F106" s="37" t="n">
         <v>1.0109</v>
       </c>
-      <c r="G106" s="34" t="n">
+      <c r="G106" s="36" t="n">
         <v>0.555</v>
       </c>
-      <c r="H106" s="34" t="n">
+      <c r="H106" s="36" t="n">
         <v>1.445</v>
       </c>
-      <c r="I106" s="34" t="n">
+      <c r="I106" s="36" t="n">
         <v>0.549</v>
       </c>
-      <c r="J106" s="34" t="n">
+      <c r="J106" s="36" t="n">
         <v>1.429</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="33" t="n">
+      <c r="A107" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="B107" s="34" t="n">
+      <c r="B107" s="36" t="n">
         <v>0.6</v>
       </c>
-      <c r="C107" s="34" t="n">
+      <c r="C107" s="36" t="n">
         <v>0.153</v>
       </c>
-      <c r="D107" s="34" t="n">
+      <c r="D107" s="36" t="n">
         <v>0.606</v>
       </c>
-      <c r="E107" s="35" t="n">
+      <c r="E107" s="37" t="n">
         <v>0.9896</v>
       </c>
-      <c r="F107" s="35" t="n">
+      <c r="F107" s="37" t="n">
         <v>1.0105</v>
       </c>
-      <c r="G107" s="34" t="n">
+      <c r="G107" s="36" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H107" s="34" t="n">
+      <c r="H107" s="36" t="n">
         <v>1.435</v>
       </c>
-      <c r="I107" s="34" t="n">
+      <c r="I107" s="36" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J107" s="34" t="n">
+      <c r="J107" s="36" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -10554,698 +11193,698 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="33" t="n">
+      <c r="A113" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="34" t="n">
+      <c r="B113" s="36" t="n">
         <v>1.128</v>
       </c>
-      <c r="C113" s="35" t="n">
+      <c r="C113" s="37" t="n">
         <v>0.8865</v>
       </c>
-      <c r="D113" s="34" t="n">
+      <c r="D113" s="36" t="n">
         <v>0.853</v>
       </c>
-      <c r="E113" s="33" t="n">
+      <c r="E113" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="34" t="n">
+      <c r="F113" s="36" t="n">
         <v>3.686</v>
       </c>
-      <c r="G113" s="33" t="n">
+      <c r="G113" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="34" t="n">
+      <c r="H113" s="36" t="n">
         <v>3.267</v>
       </c>
-      <c r="I113" s="36" t="n">
+      <c r="I113" s="38" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="33" t="n">
+      <c r="A114" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="34" t="n">
+      <c r="B114" s="36" t="n">
         <v>1.693</v>
       </c>
-      <c r="C114" s="35" t="n">
+      <c r="C114" s="37" t="n">
         <v>0.5907</v>
       </c>
-      <c r="D114" s="34" t="n">
+      <c r="D114" s="36" t="n">
         <v>0.888</v>
       </c>
-      <c r="E114" s="33" t="n">
+      <c r="E114" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="34" t="n">
+      <c r="F114" s="36" t="n">
         <v>4.358</v>
       </c>
-      <c r="G114" s="33" t="n">
+      <c r="G114" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="36" t="n">
+      <c r="H114" s="38" t="n">
         <v>2.574</v>
       </c>
-      <c r="I114" s="34" t="n">
+      <c r="I114" s="36" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="33" t="n">
+      <c r="A115" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B115" s="34" t="n">
+      <c r="B115" s="36" t="n">
         <v>2.059</v>
       </c>
-      <c r="C115" s="35" t="n">
+      <c r="C115" s="37" t="n">
         <v>0.4857</v>
       </c>
-      <c r="D115" s="34" t="n">
+      <c r="D115" s="36" t="n">
         <v>0.88</v>
       </c>
-      <c r="E115" s="33" t="n">
+      <c r="E115" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="34" t="n">
+      <c r="F115" s="36" t="n">
         <v>4.698</v>
       </c>
-      <c r="G115" s="33" t="n">
+      <c r="G115" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="34" t="n">
+      <c r="H115" s="36" t="n">
         <v>2.282</v>
       </c>
-      <c r="I115" s="34" t="n">
+      <c r="I115" s="36" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="33" t="n">
+      <c r="A116" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="34" t="n">
+      <c r="B116" s="36" t="n">
         <v>2.326</v>
       </c>
-      <c r="C116" s="35" t="n">
+      <c r="C116" s="37" t="n">
         <v>0.4299</v>
       </c>
-      <c r="D116" s="34" t="n">
+      <c r="D116" s="36" t="n">
         <v>0.864</v>
       </c>
-      <c r="E116" s="33" t="n">
+      <c r="E116" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="34" t="n">
+      <c r="F116" s="36" t="n">
         <v>4.918</v>
       </c>
-      <c r="G116" s="33" t="n">
+      <c r="G116" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="36" t="n">
+      <c r="H116" s="38" t="n">
         <v>2.114</v>
       </c>
-      <c r="I116" s="34" t="n">
+      <c r="I116" s="36" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="33" t="n">
+      <c r="A117" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B117" s="34" t="n">
+      <c r="B117" s="36" t="n">
         <v>2.534</v>
       </c>
-      <c r="C117" s="35" t="n">
+      <c r="C117" s="37" t="n">
         <v>0.3946</v>
       </c>
-      <c r="D117" s="34" t="n">
+      <c r="D117" s="36" t="n">
         <v>0.848</v>
       </c>
-      <c r="E117" s="33" t="n">
+      <c r="E117" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="34" t="n">
+      <c r="F117" s="36" t="n">
         <v>5.078</v>
       </c>
-      <c r="G117" s="33" t="n">
+      <c r="G117" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="34" t="n">
+      <c r="H117" s="36" t="n">
         <v>2.004</v>
       </c>
-      <c r="I117" s="34" t="n">
+      <c r="I117" s="36" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="33" t="n">
+      <c r="A118" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="34" t="n">
+      <c r="B118" s="36" t="n">
         <v>2.704</v>
       </c>
-      <c r="C118" s="35" t="n">
+      <c r="C118" s="37" t="n">
         <v>0.3698</v>
       </c>
-      <c r="D118" s="34" t="n">
+      <c r="D118" s="36" t="n">
         <v>0.833</v>
       </c>
-      <c r="E118" s="36" t="n">
+      <c r="E118" s="38" t="n">
         <v>0.204</v>
       </c>
-      <c r="F118" s="36" t="n">
+      <c r="F118" s="38" t="n">
         <v>5.204</v>
       </c>
-      <c r="G118" s="34" t="n">
+      <c r="G118" s="36" t="n">
         <v>0.076</v>
       </c>
-      <c r="H118" s="34" t="n">
+      <c r="H118" s="36" t="n">
         <v>1.924</v>
       </c>
-      <c r="I118" s="34" t="n">
+      <c r="I118" s="36" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="33" t="n">
+      <c r="A119" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B119" s="34" t="n">
+      <c r="B119" s="36" t="n">
         <v>2.847</v>
       </c>
-      <c r="C119" s="35" t="n">
+      <c r="C119" s="37" t="n">
         <v>0.3512</v>
       </c>
-      <c r="D119" s="34" t="n">
+      <c r="D119" s="36" t="n">
         <v>0.82</v>
       </c>
-      <c r="E119" s="36" t="n">
+      <c r="E119" s="38" t="n">
         <v>0.388</v>
       </c>
-      <c r="F119" s="36" t="n">
+      <c r="F119" s="38" t="n">
         <v>5.306</v>
       </c>
-      <c r="G119" s="34" t="n">
+      <c r="G119" s="36" t="n">
         <v>0.136</v>
       </c>
-      <c r="H119" s="34" t="n">
+      <c r="H119" s="36" t="n">
         <v>1.864</v>
       </c>
-      <c r="I119" s="34" t="n">
+      <c r="I119" s="36" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="33" t="n">
+      <c r="A120" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="34" t="n">
+      <c r="B120" s="36" t="n">
         <v>2.97</v>
       </c>
-      <c r="C120" s="35" t="n">
+      <c r="C120" s="37" t="n">
         <v>0.3367</v>
       </c>
-      <c r="D120" s="34" t="n">
+      <c r="D120" s="36" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E120" s="36" t="n">
+      <c r="E120" s="38" t="n">
         <v>0.547</v>
       </c>
-      <c r="F120" s="36" t="n">
+      <c r="F120" s="38" t="n">
         <v>5.393</v>
       </c>
-      <c r="G120" s="34" t="n">
+      <c r="G120" s="36" t="n">
         <v>0.184</v>
       </c>
-      <c r="H120" s="34" t="n">
+      <c r="H120" s="36" t="n">
         <v>1.816</v>
       </c>
-      <c r="I120" s="34" t="n">
+      <c r="I120" s="36" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="33" t="n">
+      <c r="A121" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B121" s="34" t="n">
+      <c r="B121" s="36" t="n">
         <v>3.078</v>
       </c>
-      <c r="C121" s="35" t="n">
+      <c r="C121" s="37" t="n">
         <v>0.3249</v>
       </c>
-      <c r="D121" s="34" t="n">
+      <c r="D121" s="36" t="n">
         <v>0.797</v>
       </c>
-      <c r="E121" s="34" t="n">
+      <c r="E121" s="36" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F121" s="34" t="n">
+      <c r="F121" s="36" t="n">
         <v>5.469</v>
       </c>
-      <c r="G121" s="34" t="n">
+      <c r="G121" s="36" t="n">
         <v>0.223</v>
       </c>
-      <c r="H121" s="34" t="n">
+      <c r="H121" s="36" t="n">
         <v>1.777</v>
       </c>
-      <c r="I121" s="34" t="n">
+      <c r="I121" s="36" t="n">
         <v>0.975</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="33" t="n">
+      <c r="A122" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B122" s="34" t="n">
+      <c r="B122" s="36" t="n">
         <v>3.173</v>
       </c>
-      <c r="C122" s="35" t="n">
+      <c r="C122" s="37" t="n">
         <v>0.3152</v>
       </c>
-      <c r="D122" s="34" t="n">
+      <c r="D122" s="36" t="n">
         <v>0.787</v>
       </c>
-      <c r="E122" s="36" t="n">
+      <c r="E122" s="38" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F122" s="36" t="n">
+      <c r="F122" s="38" t="n">
         <v>5.535</v>
       </c>
-      <c r="G122" s="34" t="n">
+      <c r="G122" s="36" t="n">
         <v>0.256</v>
       </c>
-      <c r="H122" s="34" t="n">
+      <c r="H122" s="36" t="n">
         <v>1.744</v>
       </c>
-      <c r="I122" s="34" t="n">
+      <c r="I122" s="36" t="n">
         <v>0.945</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="33" t="n">
+      <c r="A123" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="34" t="n">
+      <c r="B123" s="36" t="n">
         <v>3.258</v>
       </c>
-      <c r="C123" s="35" t="n">
+      <c r="C123" s="37" t="n">
         <v>0.3069</v>
       </c>
-      <c r="D123" s="36" t="n">
+      <c r="D123" s="38" t="n">
         <v>0.778</v>
       </c>
-      <c r="E123" s="36" t="n">
+      <c r="E123" s="38" t="n">
         <v>0.922</v>
       </c>
-      <c r="F123" s="36" t="n">
+      <c r="F123" s="38" t="n">
         <v>5.594</v>
       </c>
-      <c r="G123" s="36" t="n">
+      <c r="G123" s="38" t="n">
         <v>0.283</v>
       </c>
-      <c r="H123" s="36" t="n">
+      <c r="H123" s="38" t="n">
         <v>1.717</v>
       </c>
-      <c r="I123" s="34" t="n">
+      <c r="I123" s="36" t="n">
         <v>0.921</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="33" t="n">
+      <c r="A124" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B124" s="34" t="n">
+      <c r="B124" s="36" t="n">
         <v>3.336</v>
       </c>
-      <c r="C124" s="35" t="n">
+      <c r="C124" s="37" t="n">
         <v>0.2998</v>
       </c>
-      <c r="D124" s="34" t="n">
+      <c r="D124" s="36" t="n">
         <v>0.77</v>
       </c>
-      <c r="E124" s="36" t="n">
+      <c r="E124" s="38" t="n">
         <v>1.025</v>
       </c>
-      <c r="F124" s="36" t="n">
+      <c r="F124" s="38" t="n">
         <v>5.647</v>
       </c>
-      <c r="G124" s="36" t="n">
+      <c r="G124" s="38" t="n">
         <v>0.307</v>
       </c>
-      <c r="H124" s="36" t="n">
+      <c r="H124" s="38" t="n">
         <v>1.693</v>
       </c>
-      <c r="I124" s="34" t="n">
+      <c r="I124" s="36" t="n">
         <v>0.899</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="33" t="n">
+      <c r="A125" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B125" s="34" t="n">
+      <c r="B125" s="36" t="n">
         <v>3.407</v>
       </c>
-      <c r="C125" s="35" t="n">
+      <c r="C125" s="37" t="n">
         <v>0.2935</v>
       </c>
-      <c r="D125" s="34" t="n">
+      <c r="D125" s="36" t="n">
         <v>0.763</v>
       </c>
-      <c r="E125" s="36" t="n">
+      <c r="E125" s="38" t="n">
         <v>1.118</v>
       </c>
-      <c r="F125" s="36" t="n">
+      <c r="F125" s="38" t="n">
         <v>5.696</v>
       </c>
-      <c r="G125" s="36" t="n">
+      <c r="G125" s="38" t="n">
         <v>0.328</v>
       </c>
-      <c r="H125" s="36" t="n">
+      <c r="H125" s="38" t="n">
         <v>1.672</v>
       </c>
-      <c r="I125" s="34" t="n">
+      <c r="I125" s="36" t="n">
         <v>0.881</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="33" t="n">
+      <c r="A126" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="B126" s="34" t="n">
+      <c r="B126" s="36" t="n">
         <v>3.472</v>
       </c>
-      <c r="C126" s="35" t="n">
+      <c r="C126" s="37" t="n">
         <v>0.288</v>
       </c>
-      <c r="D126" s="34" t="n">
+      <c r="D126" s="36" t="n">
         <v>0.756</v>
       </c>
-      <c r="E126" s="36" t="n">
+      <c r="E126" s="38" t="n">
         <v>1.203</v>
       </c>
-      <c r="F126" s="36" t="n">
+      <c r="F126" s="38" t="n">
         <v>5.741</v>
       </c>
-      <c r="G126" s="36" t="n">
+      <c r="G126" s="38" t="n">
         <v>0.347</v>
       </c>
-      <c r="H126" s="36" t="n">
+      <c r="H126" s="38" t="n">
         <v>1.653</v>
       </c>
-      <c r="I126" s="34" t="n">
+      <c r="I126" s="36" t="n">
         <v>0.864</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="33" t="n">
+      <c r="A127" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B127" s="34" t="n">
+      <c r="B127" s="36" t="n">
         <v>3.532</v>
       </c>
-      <c r="C127" s="35" t="n">
+      <c r="C127" s="37" t="n">
         <v>0.2831</v>
       </c>
-      <c r="D127" s="34" t="n">
+      <c r="D127" s="36" t="n">
         <v>0.75</v>
       </c>
-      <c r="E127" s="36" t="n">
+      <c r="E127" s="38" t="n">
         <v>1.282</v>
       </c>
-      <c r="F127" s="36" t="n">
+      <c r="F127" s="38" t="n">
         <v>5.782</v>
       </c>
-      <c r="G127" s="36" t="n">
+      <c r="G127" s="38" t="n">
         <v>0.363</v>
       </c>
-      <c r="H127" s="36" t="n">
+      <c r="H127" s="38" t="n">
         <v>1.637</v>
       </c>
-      <c r="I127" s="34" t="n">
+      <c r="I127" s="36" t="n">
         <v>0.849</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="33" t="n">
+      <c r="A128" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="B128" s="34" t="n">
+      <c r="B128" s="36" t="n">
         <v>3.588</v>
       </c>
-      <c r="C128" s="35" t="n">
+      <c r="C128" s="37" t="n">
         <v>0.2787</v>
       </c>
-      <c r="D128" s="34" t="n">
+      <c r="D128" s="36" t="n">
         <v>0.744</v>
       </c>
-      <c r="E128" s="36" t="n">
+      <c r="E128" s="38" t="n">
         <v>1.356</v>
       </c>
-      <c r="F128" s="36" t="n">
+      <c r="F128" s="38" t="n">
         <v>5.82</v>
       </c>
-      <c r="G128" s="36" t="n">
+      <c r="G128" s="38" t="n">
         <v>0.378</v>
       </c>
-      <c r="H128" s="36" t="n">
+      <c r="H128" s="38" t="n">
         <v>1.622</v>
       </c>
-      <c r="I128" s="34" t="n">
+      <c r="I128" s="36" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="33" t="n">
+      <c r="A129" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B129" s="34" t="n">
+      <c r="B129" s="36" t="n">
         <v>3.64</v>
       </c>
-      <c r="C129" s="35" t="n">
+      <c r="C129" s="37" t="n">
         <v>0.2747</v>
       </c>
-      <c r="D129" s="34" t="n">
+      <c r="D129" s="36" t="n">
         <v>0.739</v>
       </c>
-      <c r="E129" s="36" t="n">
+      <c r="E129" s="38" t="n">
         <v>1.424</v>
       </c>
-      <c r="F129" s="36" t="n">
+      <c r="F129" s="38" t="n">
         <v>5.856</v>
       </c>
-      <c r="G129" s="36" t="n">
+      <c r="G129" s="38" t="n">
         <v>0.391</v>
       </c>
-      <c r="H129" s="34" t="n">
+      <c r="H129" s="36" t="n">
         <v>1.608</v>
       </c>
-      <c r="I129" s="34" t="n">
+      <c r="I129" s="36" t="n">
         <v>0.824</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="33" t="n">
+      <c r="A130" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="B130" s="34" t="n">
+      <c r="B130" s="36" t="n">
         <v>3.689</v>
       </c>
-      <c r="C130" s="35" t="n">
+      <c r="C130" s="37" t="n">
         <v>0.2711</v>
       </c>
-      <c r="D130" s="34" t="n">
+      <c r="D130" s="36" t="n">
         <v>0.734</v>
       </c>
-      <c r="E130" s="36" t="n">
+      <c r="E130" s="38" t="n">
         <v>1.487</v>
       </c>
-      <c r="F130" s="36" t="n">
+      <c r="F130" s="38" t="n">
         <v>5.891</v>
       </c>
-      <c r="G130" s="36" t="n">
+      <c r="G130" s="38" t="n">
         <v>0.403</v>
       </c>
-      <c r="H130" s="36" t="n">
+      <c r="H130" s="38" t="n">
         <v>1.597</v>
       </c>
-      <c r="I130" s="34" t="n">
+      <c r="I130" s="36" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="33" t="n">
+      <c r="A131" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="34" t="n">
+      <c r="B131" s="36" t="n">
         <v>3.735</v>
       </c>
-      <c r="C131" s="35" t="n">
+      <c r="C131" s="37" t="n">
         <v>0.2677</v>
       </c>
-      <c r="D131" s="34" t="n">
+      <c r="D131" s="36" t="n">
         <v>0.729</v>
       </c>
-      <c r="E131" s="36" t="n">
+      <c r="E131" s="38" t="n">
         <v>1.549</v>
       </c>
-      <c r="F131" s="36" t="n">
+      <c r="F131" s="38" t="n">
         <v>5.921</v>
       </c>
-      <c r="G131" s="36" t="n">
+      <c r="G131" s="38" t="n">
         <v>0.415</v>
       </c>
-      <c r="H131" s="36" t="n">
+      <c r="H131" s="38" t="n">
         <v>1.585</v>
       </c>
-      <c r="I131" s="34" t="n">
+      <c r="I131" s="36" t="n">
         <v>0.803</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="33" t="n">
+      <c r="A132" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="B132" s="34" t="n">
+      <c r="B132" s="36" t="n">
         <v>3.778</v>
       </c>
-      <c r="C132" s="35" t="n">
+      <c r="C132" s="37" t="n">
         <v>0.2647</v>
       </c>
-      <c r="D132" s="36" t="n">
+      <c r="D132" s="38" t="n">
         <v>0.724</v>
       </c>
-      <c r="E132" s="36" t="n">
+      <c r="E132" s="38" t="n">
         <v>1.605</v>
       </c>
-      <c r="F132" s="36" t="n">
+      <c r="F132" s="38" t="n">
         <v>5.951</v>
       </c>
-      <c r="G132" s="34" t="n">
+      <c r="G132" s="36" t="n">
         <v>0.425</v>
       </c>
-      <c r="H132" s="34" t="n">
+      <c r="H132" s="36" t="n">
         <v>1.575</v>
       </c>
-      <c r="I132" s="34" t="n">
+      <c r="I132" s="36" t="n">
         <v>0.794</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="33" t="n">
+      <c r="A133" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="B133" s="34" t="n">
+      <c r="B133" s="36" t="n">
         <v>3.819</v>
       </c>
-      <c r="C133" s="35" t="n">
+      <c r="C133" s="37" t="n">
         <v>0.2618</v>
       </c>
-      <c r="D133" s="34" t="n">
+      <c r="D133" s="36" t="n">
         <v>0.72</v>
       </c>
-      <c r="E133" s="34" t="n">
+      <c r="E133" s="36" t="n">
         <v>1.659</v>
       </c>
-      <c r="F133" s="34" t="n">
+      <c r="F133" s="36" t="n">
         <v>5.979</v>
       </c>
-      <c r="G133" s="34" t="n">
+      <c r="G133" s="36" t="n">
         <v>0.434</v>
       </c>
-      <c r="H133" s="34" t="n">
+      <c r="H133" s="36" t="n">
         <v>1.566</v>
       </c>
-      <c r="I133" s="34" t="n">
+      <c r="I133" s="36" t="n">
         <v>0.786</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="33" t="n">
+      <c r="A134" s="35" t="n">
         <v>23</v>
       </c>
-      <c r="B134" s="34" t="n">
+      <c r="B134" s="36" t="n">
         <v>3.858</v>
       </c>
-      <c r="C134" s="35" t="n">
+      <c r="C134" s="37" t="n">
         <v>0.2592</v>
       </c>
-      <c r="D134" s="34" t="n">
+      <c r="D134" s="36" t="n">
         <v>0.716</v>
       </c>
-      <c r="E134" s="34" t="n">
+      <c r="E134" s="36" t="n">
         <v>1.71</v>
       </c>
-      <c r="F134" s="34" t="n">
+      <c r="F134" s="36" t="n">
         <v>6.006</v>
       </c>
-      <c r="G134" s="34" t="n">
+      <c r="G134" s="36" t="n">
         <v>0.443</v>
       </c>
-      <c r="H134" s="34" t="n">
+      <c r="H134" s="36" t="n">
         <v>1.557</v>
       </c>
-      <c r="I134" s="34" t="n">
+      <c r="I134" s="36" t="n">
         <v>0.778</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="33" t="n">
+      <c r="A135" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="B135" s="34" t="n">
+      <c r="B135" s="36" t="n">
         <v>3.895</v>
       </c>
-      <c r="C135" s="35" t="n">
+      <c r="C135" s="37" t="n">
         <v>0.2567</v>
       </c>
-      <c r="D135" s="34" t="n">
+      <c r="D135" s="36" t="n">
         <v>0.712</v>
       </c>
-      <c r="E135" s="34" t="n">
+      <c r="E135" s="36" t="n">
         <v>1.759</v>
       </c>
-      <c r="F135" s="34" t="n">
+      <c r="F135" s="36" t="n">
         <v>6.031</v>
       </c>
-      <c r="G135" s="36" t="n">
+      <c r="G135" s="38" t="n">
         <v>0.451</v>
       </c>
-      <c r="H135" s="34" t="n">
+      <c r="H135" s="36" t="n">
         <v>1.548</v>
       </c>
-      <c r="I135" s="34" t="n">
+      <c r="I135" s="36" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="33" t="n">
+      <c r="A136" s="35" t="n">
         <v>25</v>
       </c>
-      <c r="B136" s="34" t="n">
+      <c r="B136" s="36" t="n">
         <v>3.931</v>
       </c>
-      <c r="C136" s="35" t="n">
+      <c r="C136" s="37" t="n">
         <v>0.2544</v>
       </c>
-      <c r="D136" s="34" t="n">
+      <c r="D136" s="36" t="n">
         <v>0.708</v>
       </c>
-      <c r="E136" s="36" t="n">
+      <c r="E136" s="38" t="n">
         <v>1.806</v>
       </c>
-      <c r="F136" s="36" t="n">
+      <c r="F136" s="38" t="n">
         <v>6.056</v>
       </c>
-      <c r="G136" s="34" t="n">
+      <c r="G136" s="36" t="n">
         <v>0.459</v>
       </c>
-      <c r="H136" s="34" t="n">
+      <c r="H136" s="36" t="n">
         <v>1.541</v>
       </c>
-      <c r="I136" s="34" t="n">
+      <c r="I136" s="36" t="n">
         <v>0.763</v>
       </c>
     </row>
@@ -11313,236 +11952,236 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="33" t="n">
+      <c r="A142" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B142" s="34" t="n">
+      <c r="B142" s="36" t="n">
         <v>1.88</v>
       </c>
-      <c r="C142" s="34" t="n">
+      <c r="C142" s="36" t="n">
         <v>2.659</v>
       </c>
-      <c r="D142" s="33" t="n">
+      <c r="D142" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="34" t="n">
+      <c r="E142" s="36" t="n">
         <v>3.267</v>
       </c>
-      <c r="F142" s="33" t="n">
+      <c r="F142" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="34" t="n">
+      <c r="G142" s="36" t="n">
         <v>3.267</v>
       </c>
-      <c r="H142" s="36" t="n">
+      <c r="H142" s="38" t="n">
         <v>2.659</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="33" t="n">
+      <c r="A143" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="34" t="n">
+      <c r="B143" s="36" t="n">
         <v>1.023</v>
       </c>
-      <c r="C143" s="34" t="n">
+      <c r="C143" s="36" t="n">
         <v>1.954</v>
       </c>
-      <c r="D143" s="33" t="n">
+      <c r="D143" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="34" t="n">
+      <c r="E143" s="36" t="n">
         <v>2.568</v>
       </c>
-      <c r="F143" s="33" t="n">
+      <c r="F143" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="36" t="n">
+      <c r="G143" s="38" t="n">
         <v>2.574</v>
       </c>
-      <c r="H143" s="34" t="n">
+      <c r="H143" s="36" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="33" t="n">
+      <c r="A144" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B144" s="34" t="n">
+      <c r="B144" s="36" t="n">
         <v>0.729</v>
       </c>
-      <c r="C144" s="34" t="n">
+      <c r="C144" s="36" t="n">
         <v>1.628</v>
       </c>
-      <c r="D144" s="33" t="n">
+      <c r="D144" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="34" t="n">
+      <c r="E144" s="36" t="n">
         <v>2.266</v>
       </c>
-      <c r="F144" s="33" t="n">
+      <c r="F144" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="34" t="n">
+      <c r="G144" s="36" t="n">
         <v>2.282</v>
       </c>
-      <c r="H144" s="34" t="n">
+      <c r="H144" s="36" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="33" t="n">
+      <c r="A145" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B145" s="34" t="n">
+      <c r="B145" s="36" t="n">
         <v>0.577</v>
       </c>
-      <c r="C145" s="34" t="n">
+      <c r="C145" s="36" t="n">
         <v>1.427</v>
       </c>
-      <c r="D145" s="33" t="n">
+      <c r="D145" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E145" s="34" t="n">
+      <c r="E145" s="36" t="n">
         <v>2.089</v>
       </c>
-      <c r="F145" s="33" t="n">
+      <c r="F145" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="36" t="n">
+      <c r="G145" s="38" t="n">
         <v>2.114</v>
       </c>
-      <c r="H145" s="34" t="n">
+      <c r="H145" s="36" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="33" t="n">
+      <c r="A146" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B146" s="34" t="n">
+      <c r="B146" s="36" t="n">
         <v>0.483</v>
       </c>
-      <c r="C146" s="34" t="n">
+      <c r="C146" s="36" t="n">
         <v>1.287</v>
       </c>
-      <c r="D146" s="34" t="n">
+      <c r="D146" s="36" t="n">
         <v>0.03</v>
       </c>
-      <c r="E146" s="34" t="n">
+      <c r="E146" s="36" t="n">
         <v>1.97</v>
       </c>
-      <c r="F146" s="33" t="n">
+      <c r="F146" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="34" t="n">
+      <c r="G146" s="36" t="n">
         <v>2.004</v>
       </c>
-      <c r="H146" s="34" t="n">
+      <c r="H146" s="36" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="33" t="n">
+      <c r="A147" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B147" s="34" t="n">
+      <c r="B147" s="36" t="n">
         <v>0.419</v>
       </c>
-      <c r="C147" s="34" t="n">
+      <c r="C147" s="36" t="n">
         <v>1.182</v>
       </c>
-      <c r="D147" s="34" t="n">
+      <c r="D147" s="36" t="n">
         <v>0.118</v>
       </c>
-      <c r="E147" s="34" t="n">
+      <c r="E147" s="36" t="n">
         <v>1.882</v>
       </c>
-      <c r="F147" s="34" t="n">
+      <c r="F147" s="36" t="n">
         <v>0.076</v>
       </c>
-      <c r="G147" s="34" t="n">
+      <c r="G147" s="36" t="n">
         <v>1.924</v>
       </c>
-      <c r="H147" s="34" t="n">
+      <c r="H147" s="36" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="33" t="n">
+      <c r="A148" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B148" s="34" t="n">
+      <c r="B148" s="36" t="n">
         <v>0.373</v>
       </c>
-      <c r="C148" s="34" t="n">
+      <c r="C148" s="36" t="n">
         <v>1.099</v>
       </c>
-      <c r="D148" s="34" t="n">
+      <c r="D148" s="36" t="n">
         <v>0.185</v>
       </c>
-      <c r="E148" s="34" t="n">
+      <c r="E148" s="36" t="n">
         <v>1.815</v>
       </c>
-      <c r="F148" s="34" t="n">
+      <c r="F148" s="36" t="n">
         <v>0.136</v>
       </c>
-      <c r="G148" s="34" t="n">
+      <c r="G148" s="36" t="n">
         <v>1.864</v>
       </c>
-      <c r="H148" s="34" t="n">
+      <c r="H148" s="36" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="33" t="n">
+      <c r="A149" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B149" s="34" t="n">
+      <c r="B149" s="36" t="n">
         <v>0.337</v>
       </c>
-      <c r="C149" s="34" t="n">
+      <c r="C149" s="36" t="n">
         <v>1.032</v>
       </c>
-      <c r="D149" s="34" t="n">
+      <c r="D149" s="36" t="n">
         <v>0.239</v>
       </c>
-      <c r="E149" s="34" t="n">
+      <c r="E149" s="36" t="n">
         <v>1.761</v>
       </c>
-      <c r="F149" s="34" t="n">
+      <c r="F149" s="36" t="n">
         <v>0.184</v>
       </c>
-      <c r="G149" s="34" t="n">
+      <c r="G149" s="36" t="n">
         <v>1.816</v>
       </c>
-      <c r="H149" s="34" t="n">
+      <c r="H149" s="36" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="33" t="n">
+      <c r="A150" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B150" s="34" t="n">
+      <c r="B150" s="36" t="n">
         <v>0.308</v>
       </c>
-      <c r="C150" s="34" t="n">
+      <c r="C150" s="36" t="n">
         <v>0.975</v>
       </c>
-      <c r="D150" s="34" t="n">
+      <c r="D150" s="36" t="n">
         <v>0.284</v>
       </c>
-      <c r="E150" s="34" t="n">
+      <c r="E150" s="36" t="n">
         <v>1.716</v>
       </c>
-      <c r="F150" s="34" t="n">
+      <c r="F150" s="36" t="n">
         <v>0.223</v>
       </c>
-      <c r="G150" s="34" t="n">
+      <c r="G150" s="36" t="n">
         <v>1.777</v>
       </c>
-      <c r="H150" s="34" t="n">
+      <c r="H150" s="36" t="n">
         <v>0.975</v>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance CI &amp; tests" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion matrix" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean &amp; proportion" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -8112,6 +8113,5762 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N509"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Means and proportions: CI and tests (z, t, unpaired and paired t, proportion exact and approximate, Z-test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 2/20260529_ottoy_Confidence Intervals.pdf p. 4, 9-15; Confidence Intervals - Further Reading (Dutch).pdf p. 5-20; Testing of Hypotheses.pdf p. 12; Testing of Hypotheses - Further Reading (Dutch).pdf p. 10-14; Test Recipes - Further Reading (Dutch).pdf p. 4-10; Six Sigma For Dummies.pdf p. 189-198</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Decisions 5, 6, 8: α input prefilled 0.05; two-sided, lower-only and upper-only side by side; pooled variance with n1 + n2 − 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: tested against course worked examples S03-WE01, S03-WE02, S03-WE04, S03-WE10, S03-WE13, S03-WE14, S03-WE15, S08-WE12, S08-WE13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. Settings</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Optional: paste raw values below. n, mean and s are then computed from them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Significance α (confidence = 1 − α)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>course has no default; most course examples use 5 %; use the value the question gives</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>Sample 1</t>
+        </is>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
+        <is>
+          <t>Sample 2</t>
+        </is>
+      </c>
+      <c r="N9" s="26" t="inlineStr">
+        <is>
+          <t>L − M (paired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="13">
+        <f>IF(AND(ISNUMBER(L10),ISNUMBER(M10)),L10-M10,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2. One mean μ</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="7" t="n"/>
+      <c r="N11" s="13">
+        <f>IF(AND(ISNUMBER(L11),ISNUMBER(M11)),L11-M11,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>or paste the data in column L</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n"/>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="13">
+        <f>IF(AND(ISNUMBER(L12),ISNUMBER(M12)),L12-M12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>sample mean x̄</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n"/>
+      <c r="L13" s="7" t="n"/>
+      <c r="M13" s="7" t="n"/>
+      <c r="N13" s="13">
+        <f>IF(AND(ISNUMBER(L13),ISNUMBER(M13)),L13-M13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>s = sample standard deviation (STDEV.S)</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>for the t rows</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="13">
+        <f>IF(AND(ISNUMBER(L14),ISNUMBER(M14)),L14-M14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>σ = known population standard deviation</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>for the z rows (only if the question gives σ)</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="13">
+        <f>IF(AND(ISNUMBER(L15),ISNUMBER(M15)),L15-M15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>μ0 for the test</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="13">
+        <f>IF(AND(ISNUMBER(L16),ISNUMBER(M16)),L16-M16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>n used</t>
+        </is>
+      </c>
+      <c r="B17" s="24">
+        <f>IF(COUNT(L10:L509)&gt;1,COUNT(L10:L509),IF(ISNUMBER(B12),B12,""))</f>
+        <v/>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>from column L if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="13">
+        <f>IF(AND(ISNUMBER(L17),ISNUMBER(M17)),L17-M17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>x̄ used</t>
+        </is>
+      </c>
+      <c r="B18" s="28">
+        <f>IF(COUNT(L10:L509)&gt;1,AVERAGE(L10:L509),IF(ISNUMBER(B13),B13,""))</f>
+        <v/>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>from column L if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="13">
+        <f>IF(AND(ISNUMBER(L18),ISNUMBER(M18)),L18-M18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>s used</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
+        <f>IF(COUNT(L10:L509)&gt;1,_xlfn.STDEV.S(L10:L509),IF(ISNUMBER(B14),B14,""))</f>
+        <v/>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>from column L if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n"/>
+      <c r="M19" s="7" t="n"/>
+      <c r="N19" s="13">
+        <f>IF(AND(ISNUMBER(L19),ISNUMBER(M19)),L19-M19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>standard error with σ: σ / √n</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
+        <f>IF(AND(ISNUMBER(B15),ISNUMBER(B17)),B15/SQRT(B17),"")</f>
+        <v/>
+      </c>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="13">
+        <f>IF(AND(ISNUMBER(L20),ISNUMBER(M20)),L20-M20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>standard error with s: s / √n</t>
+        </is>
+      </c>
+      <c r="B21" s="28">
+        <f>IF(AND(ISNUMBER(B19),ISNUMBER(B17)),B19/SQRT(B17),"")</f>
+        <v/>
+      </c>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="13">
+        <f>IF(AND(ISNUMBER(L21),ISNUMBER(M21)),L21-M21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>degrees of freedom n − 1</t>
+        </is>
+      </c>
+      <c r="B22" s="24">
+        <f>IF(ISNUMBER(B17),B17-1,"")</f>
+        <v/>
+      </c>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
+      <c r="N22" s="13">
+        <f>IF(AND(ISNUMBER(L22),ISNUMBER(M22)),L22-M22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="13">
+        <f>IF(AND(ISNUMBER(L23),ISNUMBER(M23)),L23-M23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Confidence interval for μ (1 − α)</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>σ known (z): from</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>σ unknown (t): from</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="n"/>
+      <c r="M24" s="7" t="n"/>
+      <c r="N24" s="13">
+        <f>IF(AND(ISNUMBER(L24),ISNUMBER(M24)),L24-M24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),B18-_xlfn.NORM.S.INV(1-B9/2)*B20,"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),B18+_xlfn.NORM.S.INV(1-B9/2)*B20,"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),B18-_xlfn.T.INV(1-B9/2,B22)*B21,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),B18+_xlfn.T.INV(1-B9/2,B22)*B21,"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>CI Further Reading p. 5-8; Confidence Intervals.pdf p. 9-10</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="13">
+        <f>IF(AND(ISNUMBER(L25),ISNUMBER(M25)),L25-M25,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>lower bound only (μ at least …)</t>
+        </is>
+      </c>
+      <c r="B26" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),B18-_xlfn.NORM.S.INV(1-B9)*B20,"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),B18-_xlfn.T.INV(1-B9,B22)*B21,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="L26" s="7" t="n"/>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="13">
+        <f>IF(AND(ISNUMBER(L26),ISNUMBER(M26)),L26-M26,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>upper bound only (μ at most …)</t>
+        </is>
+      </c>
+      <c r="B27" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),"−∞","")</f>
+        <v/>
+      </c>
+      <c r="C27" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),B18+_xlfn.NORM.S.INV(1-B9)*B20,"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),"−∞","")</f>
+        <v/>
+      </c>
+      <c r="E27" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),B18+_xlfn.T.INV(1-B9,B22)*B21,"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Confidence Intervals.pdf p. 15 (one-sided 98 %-CI ]−∞, 9.98[)</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="13">
+        <f>IF(AND(ISNUMBER(L27),ISNUMBER(M27)),L27-M27,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="13">
+        <f>IF(AND(ISNUMBER(L28),ISNUMBER(M28)),L28-M28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>z-test (σ known): test of H0: μ = μ0</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>z = (x̄ − μ0) / (σ/√n)</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>critical value</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical value</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>critical x̄</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical x̄</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="13">
+        <f>IF(AND(ISNUMBER(L29),ISNUMBER(M29)),L29-M29,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ ≠ μ0</t>
+        </is>
+      </c>
+      <c r="B30" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),(B18-B16)/B20,"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),-_xlfn.NORM.S.INV(1-B9/2),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.NORM.S.INV(1-B9/2),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="11">
+        <f>IF(ISNUMBER(C30),$B$16+C30*B20,"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="11">
+        <f>IF(ISNUMBER(D30),$B$16+D30*B20,"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="14">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),2*_xlfn.NORM.S.DIST(-ABS(B30),TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="13">
+        <f>IF(ISNUMBER(G30),IF(G30&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="13">
+        <f>IF(AND(ISNUMBER(L30),ISNUMBER(M30)),L30-M30,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ &gt; μ0</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),(B18-B16)/B20,"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.NORM.S.INV(1-B9),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>IF(ISNUMBER(C31),$B$16+C31*B20,"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="11">
+        <f>IF(ISNUMBER(D31),$B$16+D31*B20,"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="14">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.NORM.S.DIST(-B31,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="13">
+        <f>IF(ISNUMBER(G31),IF(G31&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="13">
+        <f>IF(AND(ISNUMBER(L31),ISNUMBER(M31)),L31-M31,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ &lt; μ0</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),(B18-B16)/B20,"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),-_xlfn.NORM.S.INV(1-B9),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>IF(ISNUMBER(C32),$B$16+C32*B20,"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
+        <f>IF(ISNUMBER(D32),$B$16+D32*B20,"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="14">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B20),ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.NORM.S.DIST(B32,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="13">
+        <f>IF(ISNUMBER(G32),IF(G32&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="13">
+        <f>IF(AND(ISNUMBER(L32),ISNUMBER(M32)),L32-M32,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="13">
+        <f>IF(AND(ISNUMBER(L33),ISNUMBER(M33)),L33-M33,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>t-test (σ unknown): test of H0: μ = μ0</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>t = (x̄ − μ0) / (s/√n)</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>critical value</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical value</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>critical x̄</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical x̄</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="13">
+        <f>IF(AND(ISNUMBER(L34),ISNUMBER(M34)),L34-M34,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ ≠ μ0</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),(B18-B16)/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),-_xlfn.T.INV(1-B9/2,B22),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.T.INV(1-B9/2,B22),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="11">
+        <f>IF(ISNUMBER(C35),$B$16+C35*B21,"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="11">
+        <f>IF(ISNUMBER(D35),$B$16+D35*B21,"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="14">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.T.DIST.2T(ABS(B35),B22),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="13">
+        <f>IF(ISNUMBER(G35),IF(G35&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="13">
+        <f>IF(AND(ISNUMBER(L35),ISNUMBER(M35)),L35-M35,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ &gt; μ0</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),(B18-B16)/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.T.INV(1-B9,B22),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>IF(ISNUMBER(C36),$B$16+C36*B21,"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
+        <f>IF(ISNUMBER(D36),$B$16+D36*B21,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="14">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.T.DIST.RT(B36,B22),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="13">
+        <f>IF(ISNUMBER(G36),IF(G36&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="13">
+        <f>IF(AND(ISNUMBER(L36),ISNUMBER(M36)),L36-M36,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ &lt; μ0</t>
+        </is>
+      </c>
+      <c r="B37" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),(B18-B16)/B21,"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="11">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),-_xlfn.T.INV(1-B9,B22),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="E37" s="11">
+        <f>IF(ISNUMBER(C37),$B$16+C37*B21,"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="11">
+        <f>IF(ISNUMBER(D37),$B$16+D37*B21,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="14">
+        <f>IF(AND(AND(ISNUMBER(B18),ISNUMBER(B21),B22&gt;0,ISNUMBER(B9)),ISNUMBER(B16)),_xlfn.T.DIST(B37,B22,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="13">
+        <f>IF(ISNUMBER(G37),IF(G37&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="13">
+        <f>IF(AND(ISNUMBER(L37),ISNUMBER(M37)),L37-M37,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Sources: z-test Testing of Hypotheses - Further Reading (Dutch) p. 10-14; t-test Test Recipes p. 4, Testing of Hypotheses.pdf p. 12.</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="13">
+        <f>IF(AND(ISNUMBER(L38),ISNUMBER(M38)),L38-M38,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="13">
+        <f>IF(AND(ISNUMBER(L39),ISNUMBER(M39)),L39-M39,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="13">
+        <f>IF(AND(ISNUMBER(L40),ISNUMBER(M40)),L40-M40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>3. Two means, unpaired samples (σ1 = σ2 assumed: pooled s_p)</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="13">
+        <f>IF(AND(ISNUMBER(L41),ISNUMBER(M41)),L41-M41,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>n1</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>or paste sample 1 in column L</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="13">
+        <f>IF(AND(ISNUMBER(L42),ISNUMBER(M42)),L42-M42,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>x̄1</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="13">
+        <f>IF(AND(ISNUMBER(L43),ISNUMBER(M43)),L43-M43,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="13">
+        <f>IF(AND(ISNUMBER(L44),ISNUMBER(M44)),L44-M44,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>n2</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>or paste sample 2 in column M</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="13">
+        <f>IF(AND(ISNUMBER(L45),ISNUMBER(M45)),L45-M45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>x̄2</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="13">
+        <f>IF(AND(ISNUMBER(L46),ISNUMBER(M46)),L46-M46,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="13">
+        <f>IF(AND(ISNUMBER(L47),ISNUMBER(M47)),L47-M47,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>d0 = μ1 − μ2 under H0</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="n"/>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>leave empty for 0</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="13">
+        <f>IF(AND(ISNUMBER(L48),ISNUMBER(M48)),L48-M48,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>n1 used</t>
+        </is>
+      </c>
+      <c r="B49" s="24">
+        <f>IF(COUNT(L10:L509)&gt;1,COUNT(L10:L509),IF(ISNUMBER(B42),B42,""))</f>
+        <v/>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>from column L if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="13">
+        <f>IF(AND(ISNUMBER(L49),ISNUMBER(M49)),L49-M49,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>x̄1 used</t>
+        </is>
+      </c>
+      <c r="B50" s="28">
+        <f>IF(COUNT(L10:L509)&gt;1,AVERAGE(L10:L509),IF(ISNUMBER(B43),B43,""))</f>
+        <v/>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>from column L if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="13">
+        <f>IF(AND(ISNUMBER(L50),ISNUMBER(M50)),L50-M50,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>s1 used</t>
+        </is>
+      </c>
+      <c r="B51" s="28">
+        <f>IF(COUNT(L10:L509)&gt;1,_xlfn.STDEV.S(L10:L509),IF(ISNUMBER(B44),B44,""))</f>
+        <v/>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>from column L if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="13">
+        <f>IF(AND(ISNUMBER(L51),ISNUMBER(M51)),L51-M51,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>n2 used</t>
+        </is>
+      </c>
+      <c r="B52" s="24">
+        <f>IF(COUNT(M10:M509)&gt;1,COUNT(M10:M509),IF(ISNUMBER(B45),B45,""))</f>
+        <v/>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>from column M if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
+      <c r="N52" s="13">
+        <f>IF(AND(ISNUMBER(L52),ISNUMBER(M52)),L52-M52,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>x̄2 used</t>
+        </is>
+      </c>
+      <c r="B53" s="28">
+        <f>IF(COUNT(M10:M509)&gt;1,AVERAGE(M10:M509),IF(ISNUMBER(B46),B46,""))</f>
+        <v/>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>from column M if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
+      <c r="N53" s="13">
+        <f>IF(AND(ISNUMBER(L53),ISNUMBER(M53)),L53-M53,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>s2 used</t>
+        </is>
+      </c>
+      <c r="B54" s="28">
+        <f>IF(COUNT(M10:M509)&gt;1,_xlfn.STDEV.S(M10:M509),IF(ISNUMBER(B47),B47,""))</f>
+        <v/>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>from column M if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
+      <c r="N54" s="13">
+        <f>IF(AND(ISNUMBER(L54),ISNUMBER(M54)),L54-M54,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>s_p = √[((n1 − 1)s1² + (n2 − 1)s2²) / (n1 + n2 − 2)]</t>
+        </is>
+      </c>
+      <c r="B55" s="28">
+        <f>IF(AND(ISNUMBER(B49),ISNUMBER(B50),ISNUMBER(B51),ISNUMBER(B52),ISNUMBER(B53),ISNUMBER(B54),N(B49)+N(B52)&gt;2),SQRT(((B49-1)*B51^2+(B52-1)*B54^2)/(B49+B52-2)),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Test Recipes p. 5 (decision 8; CI Further Reading p. 15 prints n1 + n2 − 1)</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="13">
+        <f>IF(AND(ISNUMBER(L55),ISNUMBER(M55)),L55-M55,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>degrees of freedom n1 + n2 − 2</t>
+        </is>
+      </c>
+      <c r="B56" s="24">
+        <f>IF(AND(ISNUMBER(B49),ISNUMBER(B50),ISNUMBER(B51),ISNUMBER(B52),ISNUMBER(B53),ISNUMBER(B54),N(B49)+N(B52)&gt;2),B49+B52-2,"")</f>
+        <v/>
+      </c>
+      <c r="L56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
+      <c r="N56" s="13">
+        <f>IF(AND(ISNUMBER(L56),ISNUMBER(M56)),L56-M56,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>standard error s_p √(1/n1 + 1/n2)</t>
+        </is>
+      </c>
+      <c r="B57" s="28">
+        <f>IF(ISNUMBER(B55),B55*SQRT(1/B49+1/B52),"")</f>
+        <v/>
+      </c>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
+      <c r="N57" s="13">
+        <f>IF(AND(ISNUMBER(L57),ISNUMBER(M57)),L57-M57,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>x̄1 − x̄2</t>
+        </is>
+      </c>
+      <c r="B58" s="28">
+        <f>IF(AND(ISNUMBER(B49),ISNUMBER(B50),ISNUMBER(B51),ISNUMBER(B52),ISNUMBER(B53),ISNUMBER(B54),N(B49)+N(B52)&gt;2),B50-B53,"")</f>
+        <v/>
+      </c>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
+      <c r="N58" s="13">
+        <f>IF(AND(ISNUMBER(L58),ISNUMBER(M58)),L58-M58,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="13">
+        <f>IF(AND(ISNUMBER(L59),ISNUMBER(M59)),L59-M59,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>CI for μ1 − μ2 (1 − α)</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>± (half-width)</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>t used</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="13">
+        <f>IF(AND(ISNUMBER(L60),ISNUMBER(M60)),L60-M60,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B61" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),B58-_xlfn.T.INV(1-B9/2,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),B58+_xlfn.T.INV(1-B9/2,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9/2,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9/2,B56),"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>CI Further Reading p. 15-17 (S03-WE13: −5,6 ± 6,19)</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="13">
+        <f>IF(AND(ISNUMBER(L61),ISNUMBER(M61)),L61-M61,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>lower bound only (μ1 − μ2 at least …)</t>
+        </is>
+      </c>
+      <c r="B62" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),B58-_xlfn.T.INV(1-B9,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D62" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="E62" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B56),"")</f>
+        <v/>
+      </c>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="13">
+        <f>IF(AND(ISNUMBER(L62),ISNUMBER(M62)),L62-M62,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>upper bound only (μ1 − μ2 at most …)</t>
+        </is>
+      </c>
+      <c r="B63" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),"−∞","")</f>
+        <v/>
+      </c>
+      <c r="C63" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),B58+_xlfn.T.INV(1-B9,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="28">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B56)*B57,"")</f>
+        <v/>
+      </c>
+      <c r="E63" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B56),"")</f>
+        <v/>
+      </c>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
+      <c r="N63" s="13">
+        <f>IF(AND(ISNUMBER(L63),ISNUMBER(M63)),L63-M63,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
+      <c r="N64" s="13">
+        <f>IF(AND(ISNUMBER(L64),ISNUMBER(M64)),L64-M64,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>t-test of H0: μ1 − μ2 = d0</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>t = (difference − d0) / SE</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>critical t</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical t</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr"/>
+      <c r="F65" s="10" t="inlineStr"/>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="n"/>
+      <c r="M65" s="7" t="n"/>
+      <c r="N65" s="13">
+        <f>IF(AND(ISNUMBER(L65),ISNUMBER(M65)),L65-M65,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ1 − μ2 ≠ d0</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),(B58-IF(ISNUMBER(B48),B48,0))/B57,"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),-_xlfn.T.INV(1-B9/2,B56),"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9/2,B56),"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="14">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.DIST.2T(ABS(B66),B56),"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="13">
+        <f>IF(ISNUMBER(G66),IF(G66&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
+      <c r="N66" s="13">
+        <f>IF(AND(ISNUMBER(L66),ISNUMBER(M66)),L66-M66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ1 − μ2 &gt; d0</t>
+        </is>
+      </c>
+      <c r="B67" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),(B58-IF(ISNUMBER(B48),B48,0))/B57,"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B56),"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G67" s="14">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.DIST.RT(B67,B56),"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="13">
+        <f>IF(ISNUMBER(G67),IF(G67&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L67" s="7" t="n"/>
+      <c r="M67" s="7" t="n"/>
+      <c r="N67" s="13">
+        <f>IF(AND(ISNUMBER(L67),ISNUMBER(M67)),L67-M67,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ1 − μ2 &lt; d0</t>
+        </is>
+      </c>
+      <c r="B68" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),(B58-IF(ISNUMBER(B48),B48,0))/B57,"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),-_xlfn.T.INV(1-B9,B56),"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G68" s="14">
+        <f>IF(AND(ISNUMBER(B58),ISNUMBER(B57),ISNUMBER(B56),B56&gt;0,ISNUMBER(B9)),_xlfn.T.DIST(B68,B56,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="13">
+        <f>IF(ISNUMBER(G68),IF(G68&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L68" s="7" t="n"/>
+      <c r="M68" s="7" t="n"/>
+      <c r="N68" s="13">
+        <f>IF(AND(ISNUMBER(L68),ISNUMBER(M68)),L68-M68,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
+      <c r="N69" s="13">
+        <f>IF(AND(ISNUMBER(L69),ISNUMBER(M69)),L69-M69,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="L70" s="7" t="n"/>
+      <c r="M70" s="7" t="n"/>
+      <c r="N70" s="13">
+        <f>IF(AND(ISNUMBER(L70),ISNUMBER(M70)),L70-M70,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="L71" s="7" t="n"/>
+      <c r="M71" s="7" t="n"/>
+      <c r="N71" s="13">
+        <f>IF(AND(ISNUMBER(L71),ISNUMBER(M71)),L71-M71,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>4. Two means, paired samples (differences v = sample 1 − sample 2)</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
+      <c r="N72" s="13">
+        <f>IF(AND(ISNUMBER(L72),ISNUMBER(M72)),L72-M72,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>n = number of pairs</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>or paste the pairs in columns L and M (same rows)</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
+      <c r="N73" s="13">
+        <f>IF(AND(ISNUMBER(L73),ISNUMBER(M73)),L73-M73,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>v̄ = mean difference</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="n"/>
+      <c r="L74" s="7" t="n"/>
+      <c r="M74" s="7" t="n"/>
+      <c r="N74" s="13">
+        <f>IF(AND(ISNUMBER(L74),ISNUMBER(M74)),L74-M74,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>s_v = standard deviation of the differences</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="n"/>
+      <c r="L75" s="7" t="n"/>
+      <c r="M75" s="7" t="n"/>
+      <c r="N75" s="13">
+        <f>IF(AND(ISNUMBER(L75),ISNUMBER(M75)),L75-M75,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>d0 under H0</t>
+        </is>
+      </c>
+      <c r="B76" s="27" t="n"/>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>leave empty for 0</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="n"/>
+      <c r="N76" s="13">
+        <f>IF(AND(ISNUMBER(L76),ISNUMBER(M76)),L76-M76,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>n used</t>
+        </is>
+      </c>
+      <c r="B77" s="24">
+        <f>IF(COUNT(N10:N509)&gt;1,COUNT(N10:N509),IF(ISNUMBER(B73),B73,""))</f>
+        <v/>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>from column N if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="n"/>
+      <c r="M77" s="7" t="n"/>
+      <c r="N77" s="13">
+        <f>IF(AND(ISNUMBER(L77),ISNUMBER(M77)),L77-M77,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>v̄ used</t>
+        </is>
+      </c>
+      <c r="B78" s="28">
+        <f>IF(COUNT(N10:N509)&gt;1,AVERAGE(N10:N509),IF(ISNUMBER(B74),B74,""))</f>
+        <v/>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>from column N if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="n"/>
+      <c r="M78" s="7" t="n"/>
+      <c r="N78" s="13">
+        <f>IF(AND(ISNUMBER(L78),ISNUMBER(M78)),L78-M78,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>s_v used</t>
+        </is>
+      </c>
+      <c r="B79" s="28">
+        <f>IF(COUNT(N10:N509)&gt;1,_xlfn.STDEV.S(N10:N509),IF(ISNUMBER(B75),B75,""))</f>
+        <v/>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>from column N if it holds 2+ values, else the typed value</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="13">
+        <f>IF(AND(ISNUMBER(L79),ISNUMBER(M79)),L79-M79,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>standard error s_v / √n</t>
+        </is>
+      </c>
+      <c r="B80" s="28">
+        <f>IF(AND(ISNUMBER(B77),ISNUMBER(B79),B77&gt;1),B79/SQRT(B77),"")</f>
+        <v/>
+      </c>
+      <c r="L80" s="7" t="n"/>
+      <c r="M80" s="7" t="n"/>
+      <c r="N80" s="13">
+        <f>IF(AND(ISNUMBER(L80),ISNUMBER(M80)),L80-M80,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>degrees of freedom n − 1</t>
+        </is>
+      </c>
+      <c r="B81" s="24">
+        <f>IF(AND(ISNUMBER(B77),ISNUMBER(B79),B77&gt;1),B77-1,"")</f>
+        <v/>
+      </c>
+      <c r="L81" s="7" t="n"/>
+      <c r="M81" s="7" t="n"/>
+      <c r="N81" s="13">
+        <f>IF(AND(ISNUMBER(L81),ISNUMBER(M81)),L81-M81,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="L82" s="7" t="n"/>
+      <c r="M82" s="7" t="n"/>
+      <c r="N82" s="13">
+        <f>IF(AND(ISNUMBER(L82),ISNUMBER(M82)),L82-M82,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>CI for μ1 − μ2 (1 − α)</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>± (half-width)</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>t used</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="n"/>
+      <c r="M83" s="7" t="n"/>
+      <c r="N83" s="13">
+        <f>IF(AND(ISNUMBER(L83),ISNUMBER(M83)),L83-M83,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B84" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),B78-_xlfn.T.INV(1-B9/2,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),B78+_xlfn.T.INV(1-B9/2,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9/2,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9/2,B81),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>CI Further Reading p. 16, 18 (S03-WE14: −3,3 ± 1,72); Test Recipes p. 7-8</t>
+        </is>
+      </c>
+      <c r="L84" s="7" t="n"/>
+      <c r="M84" s="7" t="n"/>
+      <c r="N84" s="13">
+        <f>IF(AND(ISNUMBER(L84),ISNUMBER(M84)),L84-M84,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>lower bound only (μ1 − μ2 at least …)</t>
+        </is>
+      </c>
+      <c r="B85" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),B78-_xlfn.T.INV(1-B9,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D85" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B81),"")</f>
+        <v/>
+      </c>
+      <c r="L85" s="7" t="n"/>
+      <c r="M85" s="7" t="n"/>
+      <c r="N85" s="13">
+        <f>IF(AND(ISNUMBER(L85),ISNUMBER(M85)),L85-M85,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>upper bound only (μ1 − μ2 at most …)</t>
+        </is>
+      </c>
+      <c r="B86" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),"−∞","")</f>
+        <v/>
+      </c>
+      <c r="C86" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),B78+_xlfn.T.INV(1-B9,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="28">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B81)*B80,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B81),"")</f>
+        <v/>
+      </c>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
+      <c r="N86" s="13">
+        <f>IF(AND(ISNUMBER(L86),ISNUMBER(M86)),L86-M86,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="L87" s="7" t="n"/>
+      <c r="M87" s="7" t="n"/>
+      <c r="N87" s="13">
+        <f>IF(AND(ISNUMBER(L87),ISNUMBER(M87)),L87-M87,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>t-test of H0: μ1 − μ2 = d0</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>t = (difference − d0) / SE</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>critical t</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical t</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr"/>
+      <c r="F88" s="10" t="inlineStr"/>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
+      <c r="N88" s="13">
+        <f>IF(AND(ISNUMBER(L88),ISNUMBER(M88)),L88-M88,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ1 − μ2 ≠ d0</t>
+        </is>
+      </c>
+      <c r="B89" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),(B78-IF(ISNUMBER(B76),B76,0))/B80,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),-_xlfn.T.INV(1-B9/2,B81),"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9/2,B81),"")</f>
+        <v/>
+      </c>
+      <c r="G89" s="14">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.DIST.2T(ABS(B89),B81),"")</f>
+        <v/>
+      </c>
+      <c r="H89" s="13">
+        <f>IF(ISNUMBER(G89),IF(G89&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L89" s="7" t="n"/>
+      <c r="M89" s="7" t="n"/>
+      <c r="N89" s="13">
+        <f>IF(AND(ISNUMBER(L89),ISNUMBER(M89)),L89-M89,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ1 − μ2 &gt; d0</t>
+        </is>
+      </c>
+      <c r="B90" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),(B78-IF(ISNUMBER(B76),B76,0))/B80,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.INV(1-B9,B81),"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G90" s="14">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.DIST.RT(B90,B81),"")</f>
+        <v/>
+      </c>
+      <c r="H90" s="13">
+        <f>IF(ISNUMBER(G90),IF(G90&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L90" s="7" t="n"/>
+      <c r="M90" s="7" t="n"/>
+      <c r="N90" s="13">
+        <f>IF(AND(ISNUMBER(L90),ISNUMBER(M90)),L90-M90,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>HA: μ1 − μ2 &lt; d0</t>
+        </is>
+      </c>
+      <c r="B91" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),(B78-IF(ISNUMBER(B76),B76,0))/B80,"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),-_xlfn.T.INV(1-B9,B81),"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G91" s="14">
+        <f>IF(AND(ISNUMBER(B78),ISNUMBER(B80),ISNUMBER(B81),B81&gt;0,ISNUMBER(B9)),_xlfn.T.DIST(B91,B81,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H91" s="13">
+        <f>IF(ISNUMBER(G91),IF(G91&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L91" s="7" t="n"/>
+      <c r="M91" s="7" t="n"/>
+      <c r="N91" s="13">
+        <f>IF(AND(ISNUMBER(L91),ISNUMBER(M91)),L91-M91,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="L92" s="7" t="n"/>
+      <c r="M92" s="7" t="n"/>
+      <c r="N92" s="13">
+        <f>IF(AND(ISNUMBER(L92),ISNUMBER(M92)),L92-M92,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="L93" s="7" t="n"/>
+      <c r="M93" s="7" t="n"/>
+      <c r="N93" s="13">
+        <f>IF(AND(ISNUMBER(L93),ISNUMBER(M93)),L93-M93,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>5. One proportion π (e.g. fraction defective)</t>
+        </is>
+      </c>
+      <c r="L94" s="7" t="n"/>
+      <c r="M94" s="7" t="n"/>
+      <c r="N94" s="13">
+        <f>IF(AND(ISNUMBER(L94),ISNUMBER(M94)),L94-M94,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>n = sample size</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="n"/>
+      <c r="L95" s="7" t="n"/>
+      <c r="M95" s="7" t="n"/>
+      <c r="N95" s="13">
+        <f>IF(AND(ISNUMBER(L95),ISNUMBER(M95)),L95-M95,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>x = number of successes (e.g. defectives)</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="n"/>
+      <c r="L96" s="7" t="n"/>
+      <c r="M96" s="7" t="n"/>
+      <c r="N96" s="13">
+        <f>IF(AND(ISNUMBER(L96),ISNUMBER(M96)),L96-M96,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>π0 for the test (fraction)</t>
+        </is>
+      </c>
+      <c r="B97" s="20" t="n"/>
+      <c r="L97" s="7" t="n"/>
+      <c r="M97" s="7" t="n"/>
+      <c r="N97" s="13">
+        <f>IF(AND(ISNUMBER(L97),ISNUMBER(M97)),L97-M97,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>p = x / n</t>
+        </is>
+      </c>
+      <c r="B98" s="14">
+        <f>IF(AND(ISNUMBER(B95),ISNUMBER(B96),B95&gt;0,B96&gt;=0,B96&lt;=B95),B96/B95,"")</f>
+        <v/>
+      </c>
+      <c r="L98" s="7" t="n"/>
+      <c r="M98" s="7" t="n"/>
+      <c r="N98" s="13">
+        <f>IF(AND(ISNUMBER(L98),ISNUMBER(M98)),L98-M98,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>standard error √(p(1 − p)/n)</t>
+        </is>
+      </c>
+      <c r="B99" s="28">
+        <f>IF(ISNUMBER(B98),SQRT(B98*(1-B98)/B95),"")</f>
+        <v/>
+      </c>
+      <c r="L99" s="7" t="n"/>
+      <c r="M99" s="7" t="n"/>
+      <c r="N99" s="13">
+        <f>IF(AND(ISNUMBER(L99),ISNUMBER(M99)),L99-M99,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Condition for the Z-test: n · π0 &gt; 5</t>
+        </is>
+      </c>
+      <c r="B100" s="13">
+        <f>IF(AND(ISNUMBER(B95),ISNUMBER(B97)),IF(B95*B97&gt;5,"met","NOT met: use the exact (binomial) interval"),"")</f>
+        <v/>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Test Recipes p. 9-10</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="n"/>
+      <c r="M100" s="7" t="n"/>
+      <c r="N100" s="13">
+        <f>IF(AND(ISNUMBER(L100),ISNUMBER(M100)),L100-M100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="L101" s="7" t="n"/>
+      <c r="M101" s="7" t="n"/>
+      <c r="N101" s="13">
+        <f>IF(AND(ISNUMBER(L101),ISNUMBER(M101)),L101-M101,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>CI for π (1 − α)</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>normal approx.: from</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>exact (binomial): from</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="L102" s="7" t="n"/>
+      <c r="M102" s="7" t="n"/>
+      <c r="N102" s="13">
+        <f>IF(AND(ISNUMBER(L102),ISNUMBER(M102)),L102-M102,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B103" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),B98-_xlfn.NORM.S.INV(1-B9/2)*B99,"")</f>
+        <v/>
+      </c>
+      <c r="C103" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),B98+_xlfn.NORM.S.INV(1-B9/2)*B99,"")</f>
+        <v/>
+      </c>
+      <c r="D103" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),IF(B96=0,0,_xlfn.BETA.INV(B9/2,B96,B95-B96+1)),"")</f>
+        <v/>
+      </c>
+      <c r="E103" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),IF(B96=B95,1,_xlfn.BETA.INV(1-B9/2,B96+1,B95-B96)),"")</f>
+        <v/>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>CI Further Reading p. 20 (normal approx.; exact = R binom.test); Confidence Intervals.pdf p. 4</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="n"/>
+      <c r="M103" s="7" t="n"/>
+      <c r="N103" s="13">
+        <f>IF(AND(ISNUMBER(L103),ISNUMBER(M103)),L103-M103,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>lower bound only (π at least …)</t>
+        </is>
+      </c>
+      <c r="B104" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),B98-_xlfn.NORM.S.INV(1-B9)*B99,"")</f>
+        <v/>
+      </c>
+      <c r="C104" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D104" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),IF(B96=0,0,_xlfn.BETA.INV(B9,B96,B95-B96+1)),"")</f>
+        <v/>
+      </c>
+      <c r="E104" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="L104" s="7" t="n"/>
+      <c r="M104" s="7" t="n"/>
+      <c r="N104" s="13">
+        <f>IF(AND(ISNUMBER(L104),ISNUMBER(M104)),L104-M104,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>upper bound only (π at most …)</t>
+        </is>
+      </c>
+      <c r="B105" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),"−∞","")</f>
+        <v/>
+      </c>
+      <c r="C105" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),B98+_xlfn.NORM.S.INV(1-B9)*B99,"")</f>
+        <v/>
+      </c>
+      <c r="D105" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),0,"")</f>
+        <v/>
+      </c>
+      <c r="E105" s="14">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B9)),IF(B96=B95,1,_xlfn.BETA.INV(1-B9,B96+1,B95-B96)),"")</f>
+        <v/>
+      </c>
+      <c r="L105" s="7" t="n"/>
+      <c r="M105" s="7" t="n"/>
+      <c r="N105" s="13">
+        <f>IF(AND(ISNUMBER(L105),ISNUMBER(M105)),L105-M105,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="L106" s="7" t="n"/>
+      <c r="M106" s="7" t="n"/>
+      <c r="N106" s="13">
+        <f>IF(AND(ISNUMBER(L106),ISNUMBER(M106)),L106-M106,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>Z-test of H0: π = π0</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>z = (p − π0) / √(π0(1 − π0)/n)</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>critical z</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>2nd critical z</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr"/>
+      <c r="F107" s="10" t="inlineStr"/>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>p-value</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>Decision at α</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="n"/>
+      <c r="M107" s="7" t="n"/>
+      <c r="N107" s="13">
+        <f>IF(AND(ISNUMBER(L107),ISNUMBER(M107)),L107-M107,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>HA: π ≠ π0</t>
+        </is>
+      </c>
+      <c r="B108" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),(B98-B97)/SQRT(B97*(1-B97)/B95),"")</f>
+        <v/>
+      </c>
+      <c r="C108" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),-_xlfn.NORM.S.INV(1-B9/2),"")</f>
+        <v/>
+      </c>
+      <c r="D108" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),_xlfn.NORM.S.INV(1-B9/2),"")</f>
+        <v/>
+      </c>
+      <c r="G108" s="14">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),2*_xlfn.NORM.S.DIST(-ABS(B108),TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H108" s="13">
+        <f>IF(ISNUMBER(G108),IF(G108&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L108" s="7" t="n"/>
+      <c r="M108" s="7" t="n"/>
+      <c r="N108" s="13">
+        <f>IF(AND(ISNUMBER(L108),ISNUMBER(M108)),L108-M108,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>HA: π &gt; π0</t>
+        </is>
+      </c>
+      <c r="B109" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),(B98-B97)/SQRT(B97*(1-B97)/B95),"")</f>
+        <v/>
+      </c>
+      <c r="C109" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),_xlfn.NORM.S.INV(1-B9),"")</f>
+        <v/>
+      </c>
+      <c r="D109" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G109" s="14">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),_xlfn.NORM.S.DIST(-B109,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H109" s="13">
+        <f>IF(ISNUMBER(G109),IF(G109&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L109" s="7" t="n"/>
+      <c r="M109" s="7" t="n"/>
+      <c r="N109" s="13">
+        <f>IF(AND(ISNUMBER(L109),ISNUMBER(M109)),L109-M109,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>HA: π &lt; π0</t>
+        </is>
+      </c>
+      <c r="B110" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),(B98-B97)/SQRT(B97*(1-B97)/B95),"")</f>
+        <v/>
+      </c>
+      <c r="C110" s="11">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),-_xlfn.NORM.S.INV(1-B9),"")</f>
+        <v/>
+      </c>
+      <c r="D110" s="11">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="G110" s="14">
+        <f>IF(AND(AND(ISNUMBER(B98),ISNUMBER(B9)),ISNUMBER(B97),B97&gt;0,B97&lt;1),_xlfn.NORM.S.DIST(B110,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="H110" s="13">
+        <f>IF(ISNUMBER(G110),IF(G110&lt;B9,"reject H0","do not reject H0"),"")</f>
+        <v/>
+      </c>
+      <c r="L110" s="7" t="n"/>
+      <c r="M110" s="7" t="n"/>
+      <c r="N110" s="13">
+        <f>IF(AND(ISNUMBER(L110),ISNUMBER(M110)),L110-M110,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="L111" s="7" t="n"/>
+      <c r="M111" s="7" t="n"/>
+      <c r="N111" s="13">
+        <f>IF(AND(ISNUMBER(L111),ISNUMBER(M111)),L111-M111,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>6. Two proportions: difference π1 − π2 (normal approximation)</t>
+        </is>
+      </c>
+      <c r="L112" s="7" t="n"/>
+      <c r="M112" s="7" t="n"/>
+      <c r="N112" s="13">
+        <f>IF(AND(ISNUMBER(L112),ISNUMBER(M112)),L112-M112,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>n1</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="n"/>
+      <c r="L113" s="7" t="n"/>
+      <c r="M113" s="7" t="n"/>
+      <c r="N113" s="13">
+        <f>IF(AND(ISNUMBER(L113),ISNUMBER(M113)),L113-M113,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>x1 = successes in sample 1</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="n"/>
+      <c r="L114" s="7" t="n"/>
+      <c r="M114" s="7" t="n"/>
+      <c r="N114" s="13">
+        <f>IF(AND(ISNUMBER(L114),ISNUMBER(M114)),L114-M114,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>n2</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="n"/>
+      <c r="L115" s="7" t="n"/>
+      <c r="M115" s="7" t="n"/>
+      <c r="N115" s="13">
+        <f>IF(AND(ISNUMBER(L115),ISNUMBER(M115)),L115-M115,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>x2 = successes in sample 2</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="n"/>
+      <c r="L116" s="7" t="n"/>
+      <c r="M116" s="7" t="n"/>
+      <c r="N116" s="13">
+        <f>IF(AND(ISNUMBER(L116),ISNUMBER(M116)),L116-M116,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>p1 = x1 / n1</t>
+        </is>
+      </c>
+      <c r="B117" s="14">
+        <f>IF(AND(ISNUMBER(B113),ISNUMBER(B114),ISNUMBER(B115),ISNUMBER(B116),B113&gt;0,B115&gt;0),B114/B113,"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="7" t="n"/>
+      <c r="M117" s="7" t="n"/>
+      <c r="N117" s="13">
+        <f>IF(AND(ISNUMBER(L117),ISNUMBER(M117)),L117-M117,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>p2 = x2 / n2</t>
+        </is>
+      </c>
+      <c r="B118" s="14">
+        <f>IF(AND(ISNUMBER(B113),ISNUMBER(B114),ISNUMBER(B115),ISNUMBER(B116),B113&gt;0,B115&gt;0),B116/B115,"")</f>
+        <v/>
+      </c>
+      <c r="L118" s="7" t="n"/>
+      <c r="M118" s="7" t="n"/>
+      <c r="N118" s="13">
+        <f>IF(AND(ISNUMBER(L118),ISNUMBER(M118)),L118-M118,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>p1 − p2</t>
+        </is>
+      </c>
+      <c r="B119" s="14">
+        <f>IF(AND(ISNUMBER(B113),ISNUMBER(B114),ISNUMBER(B115),ISNUMBER(B116),B113&gt;0,B115&gt;0),B117-B118,"")</f>
+        <v/>
+      </c>
+      <c r="L119" s="7" t="n"/>
+      <c r="M119" s="7" t="n"/>
+      <c r="N119" s="13">
+        <f>IF(AND(ISNUMBER(L119),ISNUMBER(M119)),L119-M119,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>standard error √(p1(1 − p1)/n1 + p2(1 − p2)/n2)</t>
+        </is>
+      </c>
+      <c r="B120" s="28">
+        <f>IF(AND(ISNUMBER(B113),ISNUMBER(B114),ISNUMBER(B115),ISNUMBER(B116),B113&gt;0,B115&gt;0),SQRT(B117*(1-B117)/B113+B118*(1-B118)/B115),"")</f>
+        <v/>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>CI Further Reading p. 20; Dummies p. 197</t>
+        </is>
+      </c>
+      <c r="L120" s="7" t="n"/>
+      <c r="M120" s="7" t="n"/>
+      <c r="N120" s="13">
+        <f>IF(AND(ISNUMBER(L120),ISNUMBER(M120)),L120-M120,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="L121" s="7" t="n"/>
+      <c r="M121" s="7" t="n"/>
+      <c r="N121" s="13">
+        <f>IF(AND(ISNUMBER(L121),ISNUMBER(M121)),L121-M121,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>CI for π1 − π2 (1 − α)</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="inlineStr">
+        <is>
+          <t>± (half-width)</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr"/>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="L122" s="7" t="n"/>
+      <c r="M122" s="7" t="n"/>
+      <c r="N122" s="13">
+        <f>IF(AND(ISNUMBER(L122),ISNUMBER(M122)),L122-M122,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>two-sided</t>
+        </is>
+      </c>
+      <c r="B123" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),B119-_xlfn.NORM.S.INV(1-B9/2)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="C123" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),B119+_xlfn.NORM.S.INV(1-B9/2)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="D123" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),_xlfn.NORM.S.INV(1-B9/2)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 197 (S08-WE13)</t>
+        </is>
+      </c>
+      <c r="L123" s="7" t="n"/>
+      <c r="M123" s="7" t="n"/>
+      <c r="N123" s="13">
+        <f>IF(AND(ISNUMBER(L123),ISNUMBER(M123)),L123-M123,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>lower bound only (π1 − π2 at least …)</t>
+        </is>
+      </c>
+      <c r="B124" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),B119-_xlfn.NORM.S.INV(1-B9)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="C124" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),"+∞","")</f>
+        <v/>
+      </c>
+      <c r="D124" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),_xlfn.NORM.S.INV(1-B9)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="L124" s="7" t="n"/>
+      <c r="M124" s="7" t="n"/>
+      <c r="N124" s="13">
+        <f>IF(AND(ISNUMBER(L124),ISNUMBER(M124)),L124-M124,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>upper bound only (π1 − π2 at most …)</t>
+        </is>
+      </c>
+      <c r="B125" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),"−∞","")</f>
+        <v/>
+      </c>
+      <c r="C125" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),B119+_xlfn.NORM.S.INV(1-B9)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="D125" s="14">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B120),ISNUMBER(B9)),_xlfn.NORM.S.INV(1-B9)*B120,"")</f>
+        <v/>
+      </c>
+      <c r="L125" s="7" t="n"/>
+      <c r="M125" s="7" t="n"/>
+      <c r="N125" s="13">
+        <f>IF(AND(ISNUMBER(L125),ISNUMBER(M125)),L125-M125,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="L126" s="7" t="n"/>
+      <c r="M126" s="7" t="n"/>
+      <c r="N126" s="13">
+        <f>IF(AND(ISNUMBER(L126),ISNUMBER(M126)),L126-M126,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="L127" s="7" t="n"/>
+      <c r="M127" s="7" t="n"/>
+      <c r="N127" s="13">
+        <f>IF(AND(ISNUMBER(L127),ISNUMBER(M127)),L127-M127,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="L128" s="7" t="n"/>
+      <c r="M128" s="7" t="n"/>
+      <c r="N128" s="13">
+        <f>IF(AND(ISNUMBER(L128),ISNUMBER(M128)),L128-M128,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="L129" s="7" t="n"/>
+      <c r="M129" s="7" t="n"/>
+      <c r="N129" s="13">
+        <f>IF(AND(ISNUMBER(L129),ISNUMBER(M129)),L129-M129,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="L130" s="7" t="n"/>
+      <c r="M130" s="7" t="n"/>
+      <c r="N130" s="13">
+        <f>IF(AND(ISNUMBER(L130),ISNUMBER(M130)),L130-M130,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="L131" s="7" t="n"/>
+      <c r="M131" s="7" t="n"/>
+      <c r="N131" s="13">
+        <f>IF(AND(ISNUMBER(L131),ISNUMBER(M131)),L131-M131,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="L132" s="7" t="n"/>
+      <c r="M132" s="7" t="n"/>
+      <c r="N132" s="13">
+        <f>IF(AND(ISNUMBER(L132),ISNUMBER(M132)),L132-M132,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="L133" s="7" t="n"/>
+      <c r="M133" s="7" t="n"/>
+      <c r="N133" s="13">
+        <f>IF(AND(ISNUMBER(L133),ISNUMBER(M133)),L133-M133,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="L134" s="7" t="n"/>
+      <c r="M134" s="7" t="n"/>
+      <c r="N134" s="13">
+        <f>IF(AND(ISNUMBER(L134),ISNUMBER(M134)),L134-M134,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="L135" s="7" t="n"/>
+      <c r="M135" s="7" t="n"/>
+      <c r="N135" s="13">
+        <f>IF(AND(ISNUMBER(L135),ISNUMBER(M135)),L135-M135,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="L136" s="7" t="n"/>
+      <c r="M136" s="7" t="n"/>
+      <c r="N136" s="13">
+        <f>IF(AND(ISNUMBER(L136),ISNUMBER(M136)),L136-M136,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="L137" s="7" t="n"/>
+      <c r="M137" s="7" t="n"/>
+      <c r="N137" s="13">
+        <f>IF(AND(ISNUMBER(L137),ISNUMBER(M137)),L137-M137,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="L138" s="7" t="n"/>
+      <c r="M138" s="7" t="n"/>
+      <c r="N138" s="13">
+        <f>IF(AND(ISNUMBER(L138),ISNUMBER(M138)),L138-M138,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="L139" s="7" t="n"/>
+      <c r="M139" s="7" t="n"/>
+      <c r="N139" s="13">
+        <f>IF(AND(ISNUMBER(L139),ISNUMBER(M139)),L139-M139,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="L140" s="7" t="n"/>
+      <c r="M140" s="7" t="n"/>
+      <c r="N140" s="13">
+        <f>IF(AND(ISNUMBER(L140),ISNUMBER(M140)),L140-M140,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="L141" s="7" t="n"/>
+      <c r="M141" s="7" t="n"/>
+      <c r="N141" s="13">
+        <f>IF(AND(ISNUMBER(L141),ISNUMBER(M141)),L141-M141,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="L142" s="7" t="n"/>
+      <c r="M142" s="7" t="n"/>
+      <c r="N142" s="13">
+        <f>IF(AND(ISNUMBER(L142),ISNUMBER(M142)),L142-M142,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="L143" s="7" t="n"/>
+      <c r="M143" s="7" t="n"/>
+      <c r="N143" s="13">
+        <f>IF(AND(ISNUMBER(L143),ISNUMBER(M143)),L143-M143,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="L144" s="7" t="n"/>
+      <c r="M144" s="7" t="n"/>
+      <c r="N144" s="13">
+        <f>IF(AND(ISNUMBER(L144),ISNUMBER(M144)),L144-M144,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="L145" s="7" t="n"/>
+      <c r="M145" s="7" t="n"/>
+      <c r="N145" s="13">
+        <f>IF(AND(ISNUMBER(L145),ISNUMBER(M145)),L145-M145,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="L146" s="7" t="n"/>
+      <c r="M146" s="7" t="n"/>
+      <c r="N146" s="13">
+        <f>IF(AND(ISNUMBER(L146),ISNUMBER(M146)),L146-M146,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="L147" s="7" t="n"/>
+      <c r="M147" s="7" t="n"/>
+      <c r="N147" s="13">
+        <f>IF(AND(ISNUMBER(L147),ISNUMBER(M147)),L147-M147,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="L148" s="7" t="n"/>
+      <c r="M148" s="7" t="n"/>
+      <c r="N148" s="13">
+        <f>IF(AND(ISNUMBER(L148),ISNUMBER(M148)),L148-M148,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="L149" s="7" t="n"/>
+      <c r="M149" s="7" t="n"/>
+      <c r="N149" s="13">
+        <f>IF(AND(ISNUMBER(L149),ISNUMBER(M149)),L149-M149,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="L150" s="7" t="n"/>
+      <c r="M150" s="7" t="n"/>
+      <c r="N150" s="13">
+        <f>IF(AND(ISNUMBER(L150),ISNUMBER(M150)),L150-M150,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="L151" s="7" t="n"/>
+      <c r="M151" s="7" t="n"/>
+      <c r="N151" s="13">
+        <f>IF(AND(ISNUMBER(L151),ISNUMBER(M151)),L151-M151,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="L152" s="7" t="n"/>
+      <c r="M152" s="7" t="n"/>
+      <c r="N152" s="13">
+        <f>IF(AND(ISNUMBER(L152),ISNUMBER(M152)),L152-M152,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="L153" s="7" t="n"/>
+      <c r="M153" s="7" t="n"/>
+      <c r="N153" s="13">
+        <f>IF(AND(ISNUMBER(L153),ISNUMBER(M153)),L153-M153,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="L154" s="7" t="n"/>
+      <c r="M154" s="7" t="n"/>
+      <c r="N154" s="13">
+        <f>IF(AND(ISNUMBER(L154),ISNUMBER(M154)),L154-M154,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="L155" s="7" t="n"/>
+      <c r="M155" s="7" t="n"/>
+      <c r="N155" s="13">
+        <f>IF(AND(ISNUMBER(L155),ISNUMBER(M155)),L155-M155,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="L156" s="7" t="n"/>
+      <c r="M156" s="7" t="n"/>
+      <c r="N156" s="13">
+        <f>IF(AND(ISNUMBER(L156),ISNUMBER(M156)),L156-M156,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="L157" s="7" t="n"/>
+      <c r="M157" s="7" t="n"/>
+      <c r="N157" s="13">
+        <f>IF(AND(ISNUMBER(L157),ISNUMBER(M157)),L157-M157,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="L158" s="7" t="n"/>
+      <c r="M158" s="7" t="n"/>
+      <c r="N158" s="13">
+        <f>IF(AND(ISNUMBER(L158),ISNUMBER(M158)),L158-M158,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="L159" s="7" t="n"/>
+      <c r="M159" s="7" t="n"/>
+      <c r="N159" s="13">
+        <f>IF(AND(ISNUMBER(L159),ISNUMBER(M159)),L159-M159,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="L160" s="7" t="n"/>
+      <c r="M160" s="7" t="n"/>
+      <c r="N160" s="13">
+        <f>IF(AND(ISNUMBER(L160),ISNUMBER(M160)),L160-M160,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="L161" s="7" t="n"/>
+      <c r="M161" s="7" t="n"/>
+      <c r="N161" s="13">
+        <f>IF(AND(ISNUMBER(L161),ISNUMBER(M161)),L161-M161,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="L162" s="7" t="n"/>
+      <c r="M162" s="7" t="n"/>
+      <c r="N162" s="13">
+        <f>IF(AND(ISNUMBER(L162),ISNUMBER(M162)),L162-M162,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="L163" s="7" t="n"/>
+      <c r="M163" s="7" t="n"/>
+      <c r="N163" s="13">
+        <f>IF(AND(ISNUMBER(L163),ISNUMBER(M163)),L163-M163,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="L164" s="7" t="n"/>
+      <c r="M164" s="7" t="n"/>
+      <c r="N164" s="13">
+        <f>IF(AND(ISNUMBER(L164),ISNUMBER(M164)),L164-M164,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="L165" s="7" t="n"/>
+      <c r="M165" s="7" t="n"/>
+      <c r="N165" s="13">
+        <f>IF(AND(ISNUMBER(L165),ISNUMBER(M165)),L165-M165,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="L166" s="7" t="n"/>
+      <c r="M166" s="7" t="n"/>
+      <c r="N166" s="13">
+        <f>IF(AND(ISNUMBER(L166),ISNUMBER(M166)),L166-M166,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="L167" s="7" t="n"/>
+      <c r="M167" s="7" t="n"/>
+      <c r="N167" s="13">
+        <f>IF(AND(ISNUMBER(L167),ISNUMBER(M167)),L167-M167,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="L168" s="7" t="n"/>
+      <c r="M168" s="7" t="n"/>
+      <c r="N168" s="13">
+        <f>IF(AND(ISNUMBER(L168),ISNUMBER(M168)),L168-M168,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="L169" s="7" t="n"/>
+      <c r="M169" s="7" t="n"/>
+      <c r="N169" s="13">
+        <f>IF(AND(ISNUMBER(L169),ISNUMBER(M169)),L169-M169,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="L170" s="7" t="n"/>
+      <c r="M170" s="7" t="n"/>
+      <c r="N170" s="13">
+        <f>IF(AND(ISNUMBER(L170),ISNUMBER(M170)),L170-M170,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="L171" s="7" t="n"/>
+      <c r="M171" s="7" t="n"/>
+      <c r="N171" s="13">
+        <f>IF(AND(ISNUMBER(L171),ISNUMBER(M171)),L171-M171,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="L172" s="7" t="n"/>
+      <c r="M172" s="7" t="n"/>
+      <c r="N172" s="13">
+        <f>IF(AND(ISNUMBER(L172),ISNUMBER(M172)),L172-M172,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="L173" s="7" t="n"/>
+      <c r="M173" s="7" t="n"/>
+      <c r="N173" s="13">
+        <f>IF(AND(ISNUMBER(L173),ISNUMBER(M173)),L173-M173,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="L174" s="7" t="n"/>
+      <c r="M174" s="7" t="n"/>
+      <c r="N174" s="13">
+        <f>IF(AND(ISNUMBER(L174),ISNUMBER(M174)),L174-M174,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="L175" s="7" t="n"/>
+      <c r="M175" s="7" t="n"/>
+      <c r="N175" s="13">
+        <f>IF(AND(ISNUMBER(L175),ISNUMBER(M175)),L175-M175,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="L176" s="7" t="n"/>
+      <c r="M176" s="7" t="n"/>
+      <c r="N176" s="13">
+        <f>IF(AND(ISNUMBER(L176),ISNUMBER(M176)),L176-M176,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="L177" s="7" t="n"/>
+      <c r="M177" s="7" t="n"/>
+      <c r="N177" s="13">
+        <f>IF(AND(ISNUMBER(L177),ISNUMBER(M177)),L177-M177,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="L178" s="7" t="n"/>
+      <c r="M178" s="7" t="n"/>
+      <c r="N178" s="13">
+        <f>IF(AND(ISNUMBER(L178),ISNUMBER(M178)),L178-M178,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="L179" s="7" t="n"/>
+      <c r="M179" s="7" t="n"/>
+      <c r="N179" s="13">
+        <f>IF(AND(ISNUMBER(L179),ISNUMBER(M179)),L179-M179,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="L180" s="7" t="n"/>
+      <c r="M180" s="7" t="n"/>
+      <c r="N180" s="13">
+        <f>IF(AND(ISNUMBER(L180),ISNUMBER(M180)),L180-M180,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="L181" s="7" t="n"/>
+      <c r="M181" s="7" t="n"/>
+      <c r="N181" s="13">
+        <f>IF(AND(ISNUMBER(L181),ISNUMBER(M181)),L181-M181,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="L182" s="7" t="n"/>
+      <c r="M182" s="7" t="n"/>
+      <c r="N182" s="13">
+        <f>IF(AND(ISNUMBER(L182),ISNUMBER(M182)),L182-M182,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="L183" s="7" t="n"/>
+      <c r="M183" s="7" t="n"/>
+      <c r="N183" s="13">
+        <f>IF(AND(ISNUMBER(L183),ISNUMBER(M183)),L183-M183,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="L184" s="7" t="n"/>
+      <c r="M184" s="7" t="n"/>
+      <c r="N184" s="13">
+        <f>IF(AND(ISNUMBER(L184),ISNUMBER(M184)),L184-M184,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="L185" s="7" t="n"/>
+      <c r="M185" s="7" t="n"/>
+      <c r="N185" s="13">
+        <f>IF(AND(ISNUMBER(L185),ISNUMBER(M185)),L185-M185,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="L186" s="7" t="n"/>
+      <c r="M186" s="7" t="n"/>
+      <c r="N186" s="13">
+        <f>IF(AND(ISNUMBER(L186),ISNUMBER(M186)),L186-M186,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="L187" s="7" t="n"/>
+      <c r="M187" s="7" t="n"/>
+      <c r="N187" s="13">
+        <f>IF(AND(ISNUMBER(L187),ISNUMBER(M187)),L187-M187,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="L188" s="7" t="n"/>
+      <c r="M188" s="7" t="n"/>
+      <c r="N188" s="13">
+        <f>IF(AND(ISNUMBER(L188),ISNUMBER(M188)),L188-M188,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="L189" s="7" t="n"/>
+      <c r="M189" s="7" t="n"/>
+      <c r="N189" s="13">
+        <f>IF(AND(ISNUMBER(L189),ISNUMBER(M189)),L189-M189,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="L190" s="7" t="n"/>
+      <c r="M190" s="7" t="n"/>
+      <c r="N190" s="13">
+        <f>IF(AND(ISNUMBER(L190),ISNUMBER(M190)),L190-M190,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="L191" s="7" t="n"/>
+      <c r="M191" s="7" t="n"/>
+      <c r="N191" s="13">
+        <f>IF(AND(ISNUMBER(L191),ISNUMBER(M191)),L191-M191,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="L192" s="7" t="n"/>
+      <c r="M192" s="7" t="n"/>
+      <c r="N192" s="13">
+        <f>IF(AND(ISNUMBER(L192),ISNUMBER(M192)),L192-M192,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="L193" s="7" t="n"/>
+      <c r="M193" s="7" t="n"/>
+      <c r="N193" s="13">
+        <f>IF(AND(ISNUMBER(L193),ISNUMBER(M193)),L193-M193,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="L194" s="7" t="n"/>
+      <c r="M194" s="7" t="n"/>
+      <c r="N194" s="13">
+        <f>IF(AND(ISNUMBER(L194),ISNUMBER(M194)),L194-M194,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="L195" s="7" t="n"/>
+      <c r="M195" s="7" t="n"/>
+      <c r="N195" s="13">
+        <f>IF(AND(ISNUMBER(L195),ISNUMBER(M195)),L195-M195,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="L196" s="7" t="n"/>
+      <c r="M196" s="7" t="n"/>
+      <c r="N196" s="13">
+        <f>IF(AND(ISNUMBER(L196),ISNUMBER(M196)),L196-M196,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="L197" s="7" t="n"/>
+      <c r="M197" s="7" t="n"/>
+      <c r="N197" s="13">
+        <f>IF(AND(ISNUMBER(L197),ISNUMBER(M197)),L197-M197,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="L198" s="7" t="n"/>
+      <c r="M198" s="7" t="n"/>
+      <c r="N198" s="13">
+        <f>IF(AND(ISNUMBER(L198),ISNUMBER(M198)),L198-M198,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="L199" s="7" t="n"/>
+      <c r="M199" s="7" t="n"/>
+      <c r="N199" s="13">
+        <f>IF(AND(ISNUMBER(L199),ISNUMBER(M199)),L199-M199,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="L200" s="7" t="n"/>
+      <c r="M200" s="7" t="n"/>
+      <c r="N200" s="13">
+        <f>IF(AND(ISNUMBER(L200),ISNUMBER(M200)),L200-M200,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="L201" s="7" t="n"/>
+      <c r="M201" s="7" t="n"/>
+      <c r="N201" s="13">
+        <f>IF(AND(ISNUMBER(L201),ISNUMBER(M201)),L201-M201,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="L202" s="7" t="n"/>
+      <c r="M202" s="7" t="n"/>
+      <c r="N202" s="13">
+        <f>IF(AND(ISNUMBER(L202),ISNUMBER(M202)),L202-M202,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="L203" s="7" t="n"/>
+      <c r="M203" s="7" t="n"/>
+      <c r="N203" s="13">
+        <f>IF(AND(ISNUMBER(L203),ISNUMBER(M203)),L203-M203,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="L204" s="7" t="n"/>
+      <c r="M204" s="7" t="n"/>
+      <c r="N204" s="13">
+        <f>IF(AND(ISNUMBER(L204),ISNUMBER(M204)),L204-M204,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="L205" s="7" t="n"/>
+      <c r="M205" s="7" t="n"/>
+      <c r="N205" s="13">
+        <f>IF(AND(ISNUMBER(L205),ISNUMBER(M205)),L205-M205,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="L206" s="7" t="n"/>
+      <c r="M206" s="7" t="n"/>
+      <c r="N206" s="13">
+        <f>IF(AND(ISNUMBER(L206),ISNUMBER(M206)),L206-M206,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="L207" s="7" t="n"/>
+      <c r="M207" s="7" t="n"/>
+      <c r="N207" s="13">
+        <f>IF(AND(ISNUMBER(L207),ISNUMBER(M207)),L207-M207,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="L208" s="7" t="n"/>
+      <c r="M208" s="7" t="n"/>
+      <c r="N208" s="13">
+        <f>IF(AND(ISNUMBER(L208),ISNUMBER(M208)),L208-M208,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="L209" s="7" t="n"/>
+      <c r="M209" s="7" t="n"/>
+      <c r="N209" s="13">
+        <f>IF(AND(ISNUMBER(L209),ISNUMBER(M209)),L209-M209,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="L210" s="7" t="n"/>
+      <c r="M210" s="7" t="n"/>
+      <c r="N210" s="13">
+        <f>IF(AND(ISNUMBER(L210),ISNUMBER(M210)),L210-M210,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="L211" s="7" t="n"/>
+      <c r="M211" s="7" t="n"/>
+      <c r="N211" s="13">
+        <f>IF(AND(ISNUMBER(L211),ISNUMBER(M211)),L211-M211,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="L212" s="7" t="n"/>
+      <c r="M212" s="7" t="n"/>
+      <c r="N212" s="13">
+        <f>IF(AND(ISNUMBER(L212),ISNUMBER(M212)),L212-M212,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="L213" s="7" t="n"/>
+      <c r="M213" s="7" t="n"/>
+      <c r="N213" s="13">
+        <f>IF(AND(ISNUMBER(L213),ISNUMBER(M213)),L213-M213,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="L214" s="7" t="n"/>
+      <c r="M214" s="7" t="n"/>
+      <c r="N214" s="13">
+        <f>IF(AND(ISNUMBER(L214),ISNUMBER(M214)),L214-M214,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="L215" s="7" t="n"/>
+      <c r="M215" s="7" t="n"/>
+      <c r="N215" s="13">
+        <f>IF(AND(ISNUMBER(L215),ISNUMBER(M215)),L215-M215,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="L216" s="7" t="n"/>
+      <c r="M216" s="7" t="n"/>
+      <c r="N216" s="13">
+        <f>IF(AND(ISNUMBER(L216),ISNUMBER(M216)),L216-M216,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="L217" s="7" t="n"/>
+      <c r="M217" s="7" t="n"/>
+      <c r="N217" s="13">
+        <f>IF(AND(ISNUMBER(L217),ISNUMBER(M217)),L217-M217,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="L218" s="7" t="n"/>
+      <c r="M218" s="7" t="n"/>
+      <c r="N218" s="13">
+        <f>IF(AND(ISNUMBER(L218),ISNUMBER(M218)),L218-M218,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="L219" s="7" t="n"/>
+      <c r="M219" s="7" t="n"/>
+      <c r="N219" s="13">
+        <f>IF(AND(ISNUMBER(L219),ISNUMBER(M219)),L219-M219,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="L220" s="7" t="n"/>
+      <c r="M220" s="7" t="n"/>
+      <c r="N220" s="13">
+        <f>IF(AND(ISNUMBER(L220),ISNUMBER(M220)),L220-M220,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="L221" s="7" t="n"/>
+      <c r="M221" s="7" t="n"/>
+      <c r="N221" s="13">
+        <f>IF(AND(ISNUMBER(L221),ISNUMBER(M221)),L221-M221,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="L222" s="7" t="n"/>
+      <c r="M222" s="7" t="n"/>
+      <c r="N222" s="13">
+        <f>IF(AND(ISNUMBER(L222),ISNUMBER(M222)),L222-M222,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="L223" s="7" t="n"/>
+      <c r="M223" s="7" t="n"/>
+      <c r="N223" s="13">
+        <f>IF(AND(ISNUMBER(L223),ISNUMBER(M223)),L223-M223,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="L224" s="7" t="n"/>
+      <c r="M224" s="7" t="n"/>
+      <c r="N224" s="13">
+        <f>IF(AND(ISNUMBER(L224),ISNUMBER(M224)),L224-M224,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="L225" s="7" t="n"/>
+      <c r="M225" s="7" t="n"/>
+      <c r="N225" s="13">
+        <f>IF(AND(ISNUMBER(L225),ISNUMBER(M225)),L225-M225,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="L226" s="7" t="n"/>
+      <c r="M226" s="7" t="n"/>
+      <c r="N226" s="13">
+        <f>IF(AND(ISNUMBER(L226),ISNUMBER(M226)),L226-M226,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="L227" s="7" t="n"/>
+      <c r="M227" s="7" t="n"/>
+      <c r="N227" s="13">
+        <f>IF(AND(ISNUMBER(L227),ISNUMBER(M227)),L227-M227,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="L228" s="7" t="n"/>
+      <c r="M228" s="7" t="n"/>
+      <c r="N228" s="13">
+        <f>IF(AND(ISNUMBER(L228),ISNUMBER(M228)),L228-M228,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="L229" s="7" t="n"/>
+      <c r="M229" s="7" t="n"/>
+      <c r="N229" s="13">
+        <f>IF(AND(ISNUMBER(L229),ISNUMBER(M229)),L229-M229,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="L230" s="7" t="n"/>
+      <c r="M230" s="7" t="n"/>
+      <c r="N230" s="13">
+        <f>IF(AND(ISNUMBER(L230),ISNUMBER(M230)),L230-M230,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="L231" s="7" t="n"/>
+      <c r="M231" s="7" t="n"/>
+      <c r="N231" s="13">
+        <f>IF(AND(ISNUMBER(L231),ISNUMBER(M231)),L231-M231,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="L232" s="7" t="n"/>
+      <c r="M232" s="7" t="n"/>
+      <c r="N232" s="13">
+        <f>IF(AND(ISNUMBER(L232),ISNUMBER(M232)),L232-M232,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="L233" s="7" t="n"/>
+      <c r="M233" s="7" t="n"/>
+      <c r="N233" s="13">
+        <f>IF(AND(ISNUMBER(L233),ISNUMBER(M233)),L233-M233,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="L234" s="7" t="n"/>
+      <c r="M234" s="7" t="n"/>
+      <c r="N234" s="13">
+        <f>IF(AND(ISNUMBER(L234),ISNUMBER(M234)),L234-M234,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="L235" s="7" t="n"/>
+      <c r="M235" s="7" t="n"/>
+      <c r="N235" s="13">
+        <f>IF(AND(ISNUMBER(L235),ISNUMBER(M235)),L235-M235,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="L236" s="7" t="n"/>
+      <c r="M236" s="7" t="n"/>
+      <c r="N236" s="13">
+        <f>IF(AND(ISNUMBER(L236),ISNUMBER(M236)),L236-M236,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="L237" s="7" t="n"/>
+      <c r="M237" s="7" t="n"/>
+      <c r="N237" s="13">
+        <f>IF(AND(ISNUMBER(L237),ISNUMBER(M237)),L237-M237,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="L238" s="7" t="n"/>
+      <c r="M238" s="7" t="n"/>
+      <c r="N238" s="13">
+        <f>IF(AND(ISNUMBER(L238),ISNUMBER(M238)),L238-M238,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="L239" s="7" t="n"/>
+      <c r="M239" s="7" t="n"/>
+      <c r="N239" s="13">
+        <f>IF(AND(ISNUMBER(L239),ISNUMBER(M239)),L239-M239,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="L240" s="7" t="n"/>
+      <c r="M240" s="7" t="n"/>
+      <c r="N240" s="13">
+        <f>IF(AND(ISNUMBER(L240),ISNUMBER(M240)),L240-M240,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="L241" s="7" t="n"/>
+      <c r="M241" s="7" t="n"/>
+      <c r="N241" s="13">
+        <f>IF(AND(ISNUMBER(L241),ISNUMBER(M241)),L241-M241,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="L242" s="7" t="n"/>
+      <c r="M242" s="7" t="n"/>
+      <c r="N242" s="13">
+        <f>IF(AND(ISNUMBER(L242),ISNUMBER(M242)),L242-M242,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="L243" s="7" t="n"/>
+      <c r="M243" s="7" t="n"/>
+      <c r="N243" s="13">
+        <f>IF(AND(ISNUMBER(L243),ISNUMBER(M243)),L243-M243,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="L244" s="7" t="n"/>
+      <c r="M244" s="7" t="n"/>
+      <c r="N244" s="13">
+        <f>IF(AND(ISNUMBER(L244),ISNUMBER(M244)),L244-M244,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="L245" s="7" t="n"/>
+      <c r="M245" s="7" t="n"/>
+      <c r="N245" s="13">
+        <f>IF(AND(ISNUMBER(L245),ISNUMBER(M245)),L245-M245,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="L246" s="7" t="n"/>
+      <c r="M246" s="7" t="n"/>
+      <c r="N246" s="13">
+        <f>IF(AND(ISNUMBER(L246),ISNUMBER(M246)),L246-M246,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="L247" s="7" t="n"/>
+      <c r="M247" s="7" t="n"/>
+      <c r="N247" s="13">
+        <f>IF(AND(ISNUMBER(L247),ISNUMBER(M247)),L247-M247,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="L248" s="7" t="n"/>
+      <c r="M248" s="7" t="n"/>
+      <c r="N248" s="13">
+        <f>IF(AND(ISNUMBER(L248),ISNUMBER(M248)),L248-M248,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="L249" s="7" t="n"/>
+      <c r="M249" s="7" t="n"/>
+      <c r="N249" s="13">
+        <f>IF(AND(ISNUMBER(L249),ISNUMBER(M249)),L249-M249,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="L250" s="7" t="n"/>
+      <c r="M250" s="7" t="n"/>
+      <c r="N250" s="13">
+        <f>IF(AND(ISNUMBER(L250),ISNUMBER(M250)),L250-M250,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="L251" s="7" t="n"/>
+      <c r="M251" s="7" t="n"/>
+      <c r="N251" s="13">
+        <f>IF(AND(ISNUMBER(L251),ISNUMBER(M251)),L251-M251,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="L252" s="7" t="n"/>
+      <c r="M252" s="7" t="n"/>
+      <c r="N252" s="13">
+        <f>IF(AND(ISNUMBER(L252),ISNUMBER(M252)),L252-M252,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="L253" s="7" t="n"/>
+      <c r="M253" s="7" t="n"/>
+      <c r="N253" s="13">
+        <f>IF(AND(ISNUMBER(L253),ISNUMBER(M253)),L253-M253,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="L254" s="7" t="n"/>
+      <c r="M254" s="7" t="n"/>
+      <c r="N254" s="13">
+        <f>IF(AND(ISNUMBER(L254),ISNUMBER(M254)),L254-M254,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="L255" s="7" t="n"/>
+      <c r="M255" s="7" t="n"/>
+      <c r="N255" s="13">
+        <f>IF(AND(ISNUMBER(L255),ISNUMBER(M255)),L255-M255,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="L256" s="7" t="n"/>
+      <c r="M256" s="7" t="n"/>
+      <c r="N256" s="13">
+        <f>IF(AND(ISNUMBER(L256),ISNUMBER(M256)),L256-M256,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="L257" s="7" t="n"/>
+      <c r="M257" s="7" t="n"/>
+      <c r="N257" s="13">
+        <f>IF(AND(ISNUMBER(L257),ISNUMBER(M257)),L257-M257,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="L258" s="7" t="n"/>
+      <c r="M258" s="7" t="n"/>
+      <c r="N258" s="13">
+        <f>IF(AND(ISNUMBER(L258),ISNUMBER(M258)),L258-M258,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="L259" s="7" t="n"/>
+      <c r="M259" s="7" t="n"/>
+      <c r="N259" s="13">
+        <f>IF(AND(ISNUMBER(L259),ISNUMBER(M259)),L259-M259,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="L260" s="7" t="n"/>
+      <c r="M260" s="7" t="n"/>
+      <c r="N260" s="13">
+        <f>IF(AND(ISNUMBER(L260),ISNUMBER(M260)),L260-M260,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="L261" s="7" t="n"/>
+      <c r="M261" s="7" t="n"/>
+      <c r="N261" s="13">
+        <f>IF(AND(ISNUMBER(L261),ISNUMBER(M261)),L261-M261,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="L262" s="7" t="n"/>
+      <c r="M262" s="7" t="n"/>
+      <c r="N262" s="13">
+        <f>IF(AND(ISNUMBER(L262),ISNUMBER(M262)),L262-M262,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="L263" s="7" t="n"/>
+      <c r="M263" s="7" t="n"/>
+      <c r="N263" s="13">
+        <f>IF(AND(ISNUMBER(L263),ISNUMBER(M263)),L263-M263,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="L264" s="7" t="n"/>
+      <c r="M264" s="7" t="n"/>
+      <c r="N264" s="13">
+        <f>IF(AND(ISNUMBER(L264),ISNUMBER(M264)),L264-M264,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="L265" s="7" t="n"/>
+      <c r="M265" s="7" t="n"/>
+      <c r="N265" s="13">
+        <f>IF(AND(ISNUMBER(L265),ISNUMBER(M265)),L265-M265,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="L266" s="7" t="n"/>
+      <c r="M266" s="7" t="n"/>
+      <c r="N266" s="13">
+        <f>IF(AND(ISNUMBER(L266),ISNUMBER(M266)),L266-M266,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="L267" s="7" t="n"/>
+      <c r="M267" s="7" t="n"/>
+      <c r="N267" s="13">
+        <f>IF(AND(ISNUMBER(L267),ISNUMBER(M267)),L267-M267,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="L268" s="7" t="n"/>
+      <c r="M268" s="7" t="n"/>
+      <c r="N268" s="13">
+        <f>IF(AND(ISNUMBER(L268),ISNUMBER(M268)),L268-M268,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="L269" s="7" t="n"/>
+      <c r="M269" s="7" t="n"/>
+      <c r="N269" s="13">
+        <f>IF(AND(ISNUMBER(L269),ISNUMBER(M269)),L269-M269,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="L270" s="7" t="n"/>
+      <c r="M270" s="7" t="n"/>
+      <c r="N270" s="13">
+        <f>IF(AND(ISNUMBER(L270),ISNUMBER(M270)),L270-M270,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="L271" s="7" t="n"/>
+      <c r="M271" s="7" t="n"/>
+      <c r="N271" s="13">
+        <f>IF(AND(ISNUMBER(L271),ISNUMBER(M271)),L271-M271,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="L272" s="7" t="n"/>
+      <c r="M272" s="7" t="n"/>
+      <c r="N272" s="13">
+        <f>IF(AND(ISNUMBER(L272),ISNUMBER(M272)),L272-M272,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="L273" s="7" t="n"/>
+      <c r="M273" s="7" t="n"/>
+      <c r="N273" s="13">
+        <f>IF(AND(ISNUMBER(L273),ISNUMBER(M273)),L273-M273,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="L274" s="7" t="n"/>
+      <c r="M274" s="7" t="n"/>
+      <c r="N274" s="13">
+        <f>IF(AND(ISNUMBER(L274),ISNUMBER(M274)),L274-M274,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="L275" s="7" t="n"/>
+      <c r="M275" s="7" t="n"/>
+      <c r="N275" s="13">
+        <f>IF(AND(ISNUMBER(L275),ISNUMBER(M275)),L275-M275,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="L276" s="7" t="n"/>
+      <c r="M276" s="7" t="n"/>
+      <c r="N276" s="13">
+        <f>IF(AND(ISNUMBER(L276),ISNUMBER(M276)),L276-M276,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="L277" s="7" t="n"/>
+      <c r="M277" s="7" t="n"/>
+      <c r="N277" s="13">
+        <f>IF(AND(ISNUMBER(L277),ISNUMBER(M277)),L277-M277,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="L278" s="7" t="n"/>
+      <c r="M278" s="7" t="n"/>
+      <c r="N278" s="13">
+        <f>IF(AND(ISNUMBER(L278),ISNUMBER(M278)),L278-M278,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="L279" s="7" t="n"/>
+      <c r="M279" s="7" t="n"/>
+      <c r="N279" s="13">
+        <f>IF(AND(ISNUMBER(L279),ISNUMBER(M279)),L279-M279,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="L280" s="7" t="n"/>
+      <c r="M280" s="7" t="n"/>
+      <c r="N280" s="13">
+        <f>IF(AND(ISNUMBER(L280),ISNUMBER(M280)),L280-M280,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="L281" s="7" t="n"/>
+      <c r="M281" s="7" t="n"/>
+      <c r="N281" s="13">
+        <f>IF(AND(ISNUMBER(L281),ISNUMBER(M281)),L281-M281,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="L282" s="7" t="n"/>
+      <c r="M282" s="7" t="n"/>
+      <c r="N282" s="13">
+        <f>IF(AND(ISNUMBER(L282),ISNUMBER(M282)),L282-M282,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="L283" s="7" t="n"/>
+      <c r="M283" s="7" t="n"/>
+      <c r="N283" s="13">
+        <f>IF(AND(ISNUMBER(L283),ISNUMBER(M283)),L283-M283,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="L284" s="7" t="n"/>
+      <c r="M284" s="7" t="n"/>
+      <c r="N284" s="13">
+        <f>IF(AND(ISNUMBER(L284),ISNUMBER(M284)),L284-M284,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="L285" s="7" t="n"/>
+      <c r="M285" s="7" t="n"/>
+      <c r="N285" s="13">
+        <f>IF(AND(ISNUMBER(L285),ISNUMBER(M285)),L285-M285,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="L286" s="7" t="n"/>
+      <c r="M286" s="7" t="n"/>
+      <c r="N286" s="13">
+        <f>IF(AND(ISNUMBER(L286),ISNUMBER(M286)),L286-M286,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="L287" s="7" t="n"/>
+      <c r="M287" s="7" t="n"/>
+      <c r="N287" s="13">
+        <f>IF(AND(ISNUMBER(L287),ISNUMBER(M287)),L287-M287,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="L288" s="7" t="n"/>
+      <c r="M288" s="7" t="n"/>
+      <c r="N288" s="13">
+        <f>IF(AND(ISNUMBER(L288),ISNUMBER(M288)),L288-M288,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="L289" s="7" t="n"/>
+      <c r="M289" s="7" t="n"/>
+      <c r="N289" s="13">
+        <f>IF(AND(ISNUMBER(L289),ISNUMBER(M289)),L289-M289,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="L290" s="7" t="n"/>
+      <c r="M290" s="7" t="n"/>
+      <c r="N290" s="13">
+        <f>IF(AND(ISNUMBER(L290),ISNUMBER(M290)),L290-M290,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="L291" s="7" t="n"/>
+      <c r="M291" s="7" t="n"/>
+      <c r="N291" s="13">
+        <f>IF(AND(ISNUMBER(L291),ISNUMBER(M291)),L291-M291,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="L292" s="7" t="n"/>
+      <c r="M292" s="7" t="n"/>
+      <c r="N292" s="13">
+        <f>IF(AND(ISNUMBER(L292),ISNUMBER(M292)),L292-M292,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="L293" s="7" t="n"/>
+      <c r="M293" s="7" t="n"/>
+      <c r="N293" s="13">
+        <f>IF(AND(ISNUMBER(L293),ISNUMBER(M293)),L293-M293,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="L294" s="7" t="n"/>
+      <c r="M294" s="7" t="n"/>
+      <c r="N294" s="13">
+        <f>IF(AND(ISNUMBER(L294),ISNUMBER(M294)),L294-M294,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="L295" s="7" t="n"/>
+      <c r="M295" s="7" t="n"/>
+      <c r="N295" s="13">
+        <f>IF(AND(ISNUMBER(L295),ISNUMBER(M295)),L295-M295,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="L296" s="7" t="n"/>
+      <c r="M296" s="7" t="n"/>
+      <c r="N296" s="13">
+        <f>IF(AND(ISNUMBER(L296),ISNUMBER(M296)),L296-M296,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="L297" s="7" t="n"/>
+      <c r="M297" s="7" t="n"/>
+      <c r="N297" s="13">
+        <f>IF(AND(ISNUMBER(L297),ISNUMBER(M297)),L297-M297,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="L298" s="7" t="n"/>
+      <c r="M298" s="7" t="n"/>
+      <c r="N298" s="13">
+        <f>IF(AND(ISNUMBER(L298),ISNUMBER(M298)),L298-M298,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="L299" s="7" t="n"/>
+      <c r="M299" s="7" t="n"/>
+      <c r="N299" s="13">
+        <f>IF(AND(ISNUMBER(L299),ISNUMBER(M299)),L299-M299,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="L300" s="7" t="n"/>
+      <c r="M300" s="7" t="n"/>
+      <c r="N300" s="13">
+        <f>IF(AND(ISNUMBER(L300),ISNUMBER(M300)),L300-M300,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="L301" s="7" t="n"/>
+      <c r="M301" s="7" t="n"/>
+      <c r="N301" s="13">
+        <f>IF(AND(ISNUMBER(L301),ISNUMBER(M301)),L301-M301,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="L302" s="7" t="n"/>
+      <c r="M302" s="7" t="n"/>
+      <c r="N302" s="13">
+        <f>IF(AND(ISNUMBER(L302),ISNUMBER(M302)),L302-M302,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="L303" s="7" t="n"/>
+      <c r="M303" s="7" t="n"/>
+      <c r="N303" s="13">
+        <f>IF(AND(ISNUMBER(L303),ISNUMBER(M303)),L303-M303,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="L304" s="7" t="n"/>
+      <c r="M304" s="7" t="n"/>
+      <c r="N304" s="13">
+        <f>IF(AND(ISNUMBER(L304),ISNUMBER(M304)),L304-M304,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="L305" s="7" t="n"/>
+      <c r="M305" s="7" t="n"/>
+      <c r="N305" s="13">
+        <f>IF(AND(ISNUMBER(L305),ISNUMBER(M305)),L305-M305,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="L306" s="7" t="n"/>
+      <c r="M306" s="7" t="n"/>
+      <c r="N306" s="13">
+        <f>IF(AND(ISNUMBER(L306),ISNUMBER(M306)),L306-M306,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="L307" s="7" t="n"/>
+      <c r="M307" s="7" t="n"/>
+      <c r="N307" s="13">
+        <f>IF(AND(ISNUMBER(L307),ISNUMBER(M307)),L307-M307,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="L308" s="7" t="n"/>
+      <c r="M308" s="7" t="n"/>
+      <c r="N308" s="13">
+        <f>IF(AND(ISNUMBER(L308),ISNUMBER(M308)),L308-M308,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="L309" s="7" t="n"/>
+      <c r="M309" s="7" t="n"/>
+      <c r="N309" s="13">
+        <f>IF(AND(ISNUMBER(L309),ISNUMBER(M309)),L309-M309,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310">
+      <c r="L310" s="7" t="n"/>
+      <c r="M310" s="7" t="n"/>
+      <c r="N310" s="13">
+        <f>IF(AND(ISNUMBER(L310),ISNUMBER(M310)),L310-M310,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="L311" s="7" t="n"/>
+      <c r="M311" s="7" t="n"/>
+      <c r="N311" s="13">
+        <f>IF(AND(ISNUMBER(L311),ISNUMBER(M311)),L311-M311,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="L312" s="7" t="n"/>
+      <c r="M312" s="7" t="n"/>
+      <c r="N312" s="13">
+        <f>IF(AND(ISNUMBER(L312),ISNUMBER(M312)),L312-M312,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="L313" s="7" t="n"/>
+      <c r="M313" s="7" t="n"/>
+      <c r="N313" s="13">
+        <f>IF(AND(ISNUMBER(L313),ISNUMBER(M313)),L313-M313,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="L314" s="7" t="n"/>
+      <c r="M314" s="7" t="n"/>
+      <c r="N314" s="13">
+        <f>IF(AND(ISNUMBER(L314),ISNUMBER(M314)),L314-M314,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="L315" s="7" t="n"/>
+      <c r="M315" s="7" t="n"/>
+      <c r="N315" s="13">
+        <f>IF(AND(ISNUMBER(L315),ISNUMBER(M315)),L315-M315,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316">
+      <c r="L316" s="7" t="n"/>
+      <c r="M316" s="7" t="n"/>
+      <c r="N316" s="13">
+        <f>IF(AND(ISNUMBER(L316),ISNUMBER(M316)),L316-M316,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="L317" s="7" t="n"/>
+      <c r="M317" s="7" t="n"/>
+      <c r="N317" s="13">
+        <f>IF(AND(ISNUMBER(L317),ISNUMBER(M317)),L317-M317,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="L318" s="7" t="n"/>
+      <c r="M318" s="7" t="n"/>
+      <c r="N318" s="13">
+        <f>IF(AND(ISNUMBER(L318),ISNUMBER(M318)),L318-M318,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="L319" s="7" t="n"/>
+      <c r="M319" s="7" t="n"/>
+      <c r="N319" s="13">
+        <f>IF(AND(ISNUMBER(L319),ISNUMBER(M319)),L319-M319,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="L320" s="7" t="n"/>
+      <c r="M320" s="7" t="n"/>
+      <c r="N320" s="13">
+        <f>IF(AND(ISNUMBER(L320),ISNUMBER(M320)),L320-M320,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="L321" s="7" t="n"/>
+      <c r="M321" s="7" t="n"/>
+      <c r="N321" s="13">
+        <f>IF(AND(ISNUMBER(L321),ISNUMBER(M321)),L321-M321,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="L322" s="7" t="n"/>
+      <c r="M322" s="7" t="n"/>
+      <c r="N322" s="13">
+        <f>IF(AND(ISNUMBER(L322),ISNUMBER(M322)),L322-M322,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="L323" s="7" t="n"/>
+      <c r="M323" s="7" t="n"/>
+      <c r="N323" s="13">
+        <f>IF(AND(ISNUMBER(L323),ISNUMBER(M323)),L323-M323,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="L324" s="7" t="n"/>
+      <c r="M324" s="7" t="n"/>
+      <c r="N324" s="13">
+        <f>IF(AND(ISNUMBER(L324),ISNUMBER(M324)),L324-M324,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="L325" s="7" t="n"/>
+      <c r="M325" s="7" t="n"/>
+      <c r="N325" s="13">
+        <f>IF(AND(ISNUMBER(L325),ISNUMBER(M325)),L325-M325,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="L326" s="7" t="n"/>
+      <c r="M326" s="7" t="n"/>
+      <c r="N326" s="13">
+        <f>IF(AND(ISNUMBER(L326),ISNUMBER(M326)),L326-M326,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="L327" s="7" t="n"/>
+      <c r="M327" s="7" t="n"/>
+      <c r="N327" s="13">
+        <f>IF(AND(ISNUMBER(L327),ISNUMBER(M327)),L327-M327,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="L328" s="7" t="n"/>
+      <c r="M328" s="7" t="n"/>
+      <c r="N328" s="13">
+        <f>IF(AND(ISNUMBER(L328),ISNUMBER(M328)),L328-M328,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="L329" s="7" t="n"/>
+      <c r="M329" s="7" t="n"/>
+      <c r="N329" s="13">
+        <f>IF(AND(ISNUMBER(L329),ISNUMBER(M329)),L329-M329,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330">
+      <c r="L330" s="7" t="n"/>
+      <c r="M330" s="7" t="n"/>
+      <c r="N330" s="13">
+        <f>IF(AND(ISNUMBER(L330),ISNUMBER(M330)),L330-M330,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="L331" s="7" t="n"/>
+      <c r="M331" s="7" t="n"/>
+      <c r="N331" s="13">
+        <f>IF(AND(ISNUMBER(L331),ISNUMBER(M331)),L331-M331,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="L332" s="7" t="n"/>
+      <c r="M332" s="7" t="n"/>
+      <c r="N332" s="13">
+        <f>IF(AND(ISNUMBER(L332),ISNUMBER(M332)),L332-M332,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="L333" s="7" t="n"/>
+      <c r="M333" s="7" t="n"/>
+      <c r="N333" s="13">
+        <f>IF(AND(ISNUMBER(L333),ISNUMBER(M333)),L333-M333,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="L334" s="7" t="n"/>
+      <c r="M334" s="7" t="n"/>
+      <c r="N334" s="13">
+        <f>IF(AND(ISNUMBER(L334),ISNUMBER(M334)),L334-M334,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="L335" s="7" t="n"/>
+      <c r="M335" s="7" t="n"/>
+      <c r="N335" s="13">
+        <f>IF(AND(ISNUMBER(L335),ISNUMBER(M335)),L335-M335,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="L336" s="7" t="n"/>
+      <c r="M336" s="7" t="n"/>
+      <c r="N336" s="13">
+        <f>IF(AND(ISNUMBER(L336),ISNUMBER(M336)),L336-M336,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="L337" s="7" t="n"/>
+      <c r="M337" s="7" t="n"/>
+      <c r="N337" s="13">
+        <f>IF(AND(ISNUMBER(L337),ISNUMBER(M337)),L337-M337,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="L338" s="7" t="n"/>
+      <c r="M338" s="7" t="n"/>
+      <c r="N338" s="13">
+        <f>IF(AND(ISNUMBER(L338),ISNUMBER(M338)),L338-M338,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339">
+      <c r="L339" s="7" t="n"/>
+      <c r="M339" s="7" t="n"/>
+      <c r="N339" s="13">
+        <f>IF(AND(ISNUMBER(L339),ISNUMBER(M339)),L339-M339,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="L340" s="7" t="n"/>
+      <c r="M340" s="7" t="n"/>
+      <c r="N340" s="13">
+        <f>IF(AND(ISNUMBER(L340),ISNUMBER(M340)),L340-M340,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="L341" s="7" t="n"/>
+      <c r="M341" s="7" t="n"/>
+      <c r="N341" s="13">
+        <f>IF(AND(ISNUMBER(L341),ISNUMBER(M341)),L341-M341,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="L342" s="7" t="n"/>
+      <c r="M342" s="7" t="n"/>
+      <c r="N342" s="13">
+        <f>IF(AND(ISNUMBER(L342),ISNUMBER(M342)),L342-M342,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343">
+      <c r="L343" s="7" t="n"/>
+      <c r="M343" s="7" t="n"/>
+      <c r="N343" s="13">
+        <f>IF(AND(ISNUMBER(L343),ISNUMBER(M343)),L343-M343,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344">
+      <c r="L344" s="7" t="n"/>
+      <c r="M344" s="7" t="n"/>
+      <c r="N344" s="13">
+        <f>IF(AND(ISNUMBER(L344),ISNUMBER(M344)),L344-M344,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="L345" s="7" t="n"/>
+      <c r="M345" s="7" t="n"/>
+      <c r="N345" s="13">
+        <f>IF(AND(ISNUMBER(L345),ISNUMBER(M345)),L345-M345,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="L346" s="7" t="n"/>
+      <c r="M346" s="7" t="n"/>
+      <c r="N346" s="13">
+        <f>IF(AND(ISNUMBER(L346),ISNUMBER(M346)),L346-M346,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347">
+      <c r="L347" s="7" t="n"/>
+      <c r="M347" s="7" t="n"/>
+      <c r="N347" s="13">
+        <f>IF(AND(ISNUMBER(L347),ISNUMBER(M347)),L347-M347,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="L348" s="7" t="n"/>
+      <c r="M348" s="7" t="n"/>
+      <c r="N348" s="13">
+        <f>IF(AND(ISNUMBER(L348),ISNUMBER(M348)),L348-M348,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349">
+      <c r="L349" s="7" t="n"/>
+      <c r="M349" s="7" t="n"/>
+      <c r="N349" s="13">
+        <f>IF(AND(ISNUMBER(L349),ISNUMBER(M349)),L349-M349,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="L350" s="7" t="n"/>
+      <c r="M350" s="7" t="n"/>
+      <c r="N350" s="13">
+        <f>IF(AND(ISNUMBER(L350),ISNUMBER(M350)),L350-M350,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="L351" s="7" t="n"/>
+      <c r="M351" s="7" t="n"/>
+      <c r="N351" s="13">
+        <f>IF(AND(ISNUMBER(L351),ISNUMBER(M351)),L351-M351,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="L352" s="7" t="n"/>
+      <c r="M352" s="7" t="n"/>
+      <c r="N352" s="13">
+        <f>IF(AND(ISNUMBER(L352),ISNUMBER(M352)),L352-M352,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="L353" s="7" t="n"/>
+      <c r="M353" s="7" t="n"/>
+      <c r="N353" s="13">
+        <f>IF(AND(ISNUMBER(L353),ISNUMBER(M353)),L353-M353,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="L354" s="7" t="n"/>
+      <c r="M354" s="7" t="n"/>
+      <c r="N354" s="13">
+        <f>IF(AND(ISNUMBER(L354),ISNUMBER(M354)),L354-M354,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="L355" s="7" t="n"/>
+      <c r="M355" s="7" t="n"/>
+      <c r="N355" s="13">
+        <f>IF(AND(ISNUMBER(L355),ISNUMBER(M355)),L355-M355,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="L356" s="7" t="n"/>
+      <c r="M356" s="7" t="n"/>
+      <c r="N356" s="13">
+        <f>IF(AND(ISNUMBER(L356),ISNUMBER(M356)),L356-M356,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="L357" s="7" t="n"/>
+      <c r="M357" s="7" t="n"/>
+      <c r="N357" s="13">
+        <f>IF(AND(ISNUMBER(L357),ISNUMBER(M357)),L357-M357,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="L358" s="7" t="n"/>
+      <c r="M358" s="7" t="n"/>
+      <c r="N358" s="13">
+        <f>IF(AND(ISNUMBER(L358),ISNUMBER(M358)),L358-M358,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="L359" s="7" t="n"/>
+      <c r="M359" s="7" t="n"/>
+      <c r="N359" s="13">
+        <f>IF(AND(ISNUMBER(L359),ISNUMBER(M359)),L359-M359,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="L360" s="7" t="n"/>
+      <c r="M360" s="7" t="n"/>
+      <c r="N360" s="13">
+        <f>IF(AND(ISNUMBER(L360),ISNUMBER(M360)),L360-M360,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="L361" s="7" t="n"/>
+      <c r="M361" s="7" t="n"/>
+      <c r="N361" s="13">
+        <f>IF(AND(ISNUMBER(L361),ISNUMBER(M361)),L361-M361,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362">
+      <c r="L362" s="7" t="n"/>
+      <c r="M362" s="7" t="n"/>
+      <c r="N362" s="13">
+        <f>IF(AND(ISNUMBER(L362),ISNUMBER(M362)),L362-M362,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="L363" s="7" t="n"/>
+      <c r="M363" s="7" t="n"/>
+      <c r="N363" s="13">
+        <f>IF(AND(ISNUMBER(L363),ISNUMBER(M363)),L363-M363,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364">
+      <c r="L364" s="7" t="n"/>
+      <c r="M364" s="7" t="n"/>
+      <c r="N364" s="13">
+        <f>IF(AND(ISNUMBER(L364),ISNUMBER(M364)),L364-M364,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="L365" s="7" t="n"/>
+      <c r="M365" s="7" t="n"/>
+      <c r="N365" s="13">
+        <f>IF(AND(ISNUMBER(L365),ISNUMBER(M365)),L365-M365,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="L366" s="7" t="n"/>
+      <c r="M366" s="7" t="n"/>
+      <c r="N366" s="13">
+        <f>IF(AND(ISNUMBER(L366),ISNUMBER(M366)),L366-M366,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="L367" s="7" t="n"/>
+      <c r="M367" s="7" t="n"/>
+      <c r="N367" s="13">
+        <f>IF(AND(ISNUMBER(L367),ISNUMBER(M367)),L367-M367,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="L368" s="7" t="n"/>
+      <c r="M368" s="7" t="n"/>
+      <c r="N368" s="13">
+        <f>IF(AND(ISNUMBER(L368),ISNUMBER(M368)),L368-M368,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="L369" s="7" t="n"/>
+      <c r="M369" s="7" t="n"/>
+      <c r="N369" s="13">
+        <f>IF(AND(ISNUMBER(L369),ISNUMBER(M369)),L369-M369,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="L370" s="7" t="n"/>
+      <c r="M370" s="7" t="n"/>
+      <c r="N370" s="13">
+        <f>IF(AND(ISNUMBER(L370),ISNUMBER(M370)),L370-M370,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="L371" s="7" t="n"/>
+      <c r="M371" s="7" t="n"/>
+      <c r="N371" s="13">
+        <f>IF(AND(ISNUMBER(L371),ISNUMBER(M371)),L371-M371,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="L372" s="7" t="n"/>
+      <c r="M372" s="7" t="n"/>
+      <c r="N372" s="13">
+        <f>IF(AND(ISNUMBER(L372),ISNUMBER(M372)),L372-M372,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="L373" s="7" t="n"/>
+      <c r="M373" s="7" t="n"/>
+      <c r="N373" s="13">
+        <f>IF(AND(ISNUMBER(L373),ISNUMBER(M373)),L373-M373,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="L374" s="7" t="n"/>
+      <c r="M374" s="7" t="n"/>
+      <c r="N374" s="13">
+        <f>IF(AND(ISNUMBER(L374),ISNUMBER(M374)),L374-M374,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="L375" s="7" t="n"/>
+      <c r="M375" s="7" t="n"/>
+      <c r="N375" s="13">
+        <f>IF(AND(ISNUMBER(L375),ISNUMBER(M375)),L375-M375,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="L376" s="7" t="n"/>
+      <c r="M376" s="7" t="n"/>
+      <c r="N376" s="13">
+        <f>IF(AND(ISNUMBER(L376),ISNUMBER(M376)),L376-M376,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="L377" s="7" t="n"/>
+      <c r="M377" s="7" t="n"/>
+      <c r="N377" s="13">
+        <f>IF(AND(ISNUMBER(L377),ISNUMBER(M377)),L377-M377,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="L378" s="7" t="n"/>
+      <c r="M378" s="7" t="n"/>
+      <c r="N378" s="13">
+        <f>IF(AND(ISNUMBER(L378),ISNUMBER(M378)),L378-M378,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="L379" s="7" t="n"/>
+      <c r="M379" s="7" t="n"/>
+      <c r="N379" s="13">
+        <f>IF(AND(ISNUMBER(L379),ISNUMBER(M379)),L379-M379,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="L380" s="7" t="n"/>
+      <c r="M380" s="7" t="n"/>
+      <c r="N380" s="13">
+        <f>IF(AND(ISNUMBER(L380),ISNUMBER(M380)),L380-M380,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="L381" s="7" t="n"/>
+      <c r="M381" s="7" t="n"/>
+      <c r="N381" s="13">
+        <f>IF(AND(ISNUMBER(L381),ISNUMBER(M381)),L381-M381,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="L382" s="7" t="n"/>
+      <c r="M382" s="7" t="n"/>
+      <c r="N382" s="13">
+        <f>IF(AND(ISNUMBER(L382),ISNUMBER(M382)),L382-M382,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="L383" s="7" t="n"/>
+      <c r="M383" s="7" t="n"/>
+      <c r="N383" s="13">
+        <f>IF(AND(ISNUMBER(L383),ISNUMBER(M383)),L383-M383,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="L384" s="7" t="n"/>
+      <c r="M384" s="7" t="n"/>
+      <c r="N384" s="13">
+        <f>IF(AND(ISNUMBER(L384),ISNUMBER(M384)),L384-M384,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="L385" s="7" t="n"/>
+      <c r="M385" s="7" t="n"/>
+      <c r="N385" s="13">
+        <f>IF(AND(ISNUMBER(L385),ISNUMBER(M385)),L385-M385,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="L386" s="7" t="n"/>
+      <c r="M386" s="7" t="n"/>
+      <c r="N386" s="13">
+        <f>IF(AND(ISNUMBER(L386),ISNUMBER(M386)),L386-M386,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="L387" s="7" t="n"/>
+      <c r="M387" s="7" t="n"/>
+      <c r="N387" s="13">
+        <f>IF(AND(ISNUMBER(L387),ISNUMBER(M387)),L387-M387,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="L388" s="7" t="n"/>
+      <c r="M388" s="7" t="n"/>
+      <c r="N388" s="13">
+        <f>IF(AND(ISNUMBER(L388),ISNUMBER(M388)),L388-M388,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="L389" s="7" t="n"/>
+      <c r="M389" s="7" t="n"/>
+      <c r="N389" s="13">
+        <f>IF(AND(ISNUMBER(L389),ISNUMBER(M389)),L389-M389,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="L390" s="7" t="n"/>
+      <c r="M390" s="7" t="n"/>
+      <c r="N390" s="13">
+        <f>IF(AND(ISNUMBER(L390),ISNUMBER(M390)),L390-M390,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="L391" s="7" t="n"/>
+      <c r="M391" s="7" t="n"/>
+      <c r="N391" s="13">
+        <f>IF(AND(ISNUMBER(L391),ISNUMBER(M391)),L391-M391,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="L392" s="7" t="n"/>
+      <c r="M392" s="7" t="n"/>
+      <c r="N392" s="13">
+        <f>IF(AND(ISNUMBER(L392),ISNUMBER(M392)),L392-M392,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="L393" s="7" t="n"/>
+      <c r="M393" s="7" t="n"/>
+      <c r="N393" s="13">
+        <f>IF(AND(ISNUMBER(L393),ISNUMBER(M393)),L393-M393,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="L394" s="7" t="n"/>
+      <c r="M394" s="7" t="n"/>
+      <c r="N394" s="13">
+        <f>IF(AND(ISNUMBER(L394),ISNUMBER(M394)),L394-M394,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="L395" s="7" t="n"/>
+      <c r="M395" s="7" t="n"/>
+      <c r="N395" s="13">
+        <f>IF(AND(ISNUMBER(L395),ISNUMBER(M395)),L395-M395,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="L396" s="7" t="n"/>
+      <c r="M396" s="7" t="n"/>
+      <c r="N396" s="13">
+        <f>IF(AND(ISNUMBER(L396),ISNUMBER(M396)),L396-M396,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="L397" s="7" t="n"/>
+      <c r="M397" s="7" t="n"/>
+      <c r="N397" s="13">
+        <f>IF(AND(ISNUMBER(L397),ISNUMBER(M397)),L397-M397,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="L398" s="7" t="n"/>
+      <c r="M398" s="7" t="n"/>
+      <c r="N398" s="13">
+        <f>IF(AND(ISNUMBER(L398),ISNUMBER(M398)),L398-M398,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="L399" s="7" t="n"/>
+      <c r="M399" s="7" t="n"/>
+      <c r="N399" s="13">
+        <f>IF(AND(ISNUMBER(L399),ISNUMBER(M399)),L399-M399,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="L400" s="7" t="n"/>
+      <c r="M400" s="7" t="n"/>
+      <c r="N400" s="13">
+        <f>IF(AND(ISNUMBER(L400),ISNUMBER(M400)),L400-M400,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="L401" s="7" t="n"/>
+      <c r="M401" s="7" t="n"/>
+      <c r="N401" s="13">
+        <f>IF(AND(ISNUMBER(L401),ISNUMBER(M401)),L401-M401,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="L402" s="7" t="n"/>
+      <c r="M402" s="7" t="n"/>
+      <c r="N402" s="13">
+        <f>IF(AND(ISNUMBER(L402),ISNUMBER(M402)),L402-M402,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="L403" s="7" t="n"/>
+      <c r="M403" s="7" t="n"/>
+      <c r="N403" s="13">
+        <f>IF(AND(ISNUMBER(L403),ISNUMBER(M403)),L403-M403,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="L404" s="7" t="n"/>
+      <c r="M404" s="7" t="n"/>
+      <c r="N404" s="13">
+        <f>IF(AND(ISNUMBER(L404),ISNUMBER(M404)),L404-M404,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="L405" s="7" t="n"/>
+      <c r="M405" s="7" t="n"/>
+      <c r="N405" s="13">
+        <f>IF(AND(ISNUMBER(L405),ISNUMBER(M405)),L405-M405,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="L406" s="7" t="n"/>
+      <c r="M406" s="7" t="n"/>
+      <c r="N406" s="13">
+        <f>IF(AND(ISNUMBER(L406),ISNUMBER(M406)),L406-M406,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="L407" s="7" t="n"/>
+      <c r="M407" s="7" t="n"/>
+      <c r="N407" s="13">
+        <f>IF(AND(ISNUMBER(L407),ISNUMBER(M407)),L407-M407,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="L408" s="7" t="n"/>
+      <c r="M408" s="7" t="n"/>
+      <c r="N408" s="13">
+        <f>IF(AND(ISNUMBER(L408),ISNUMBER(M408)),L408-M408,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="L409" s="7" t="n"/>
+      <c r="M409" s="7" t="n"/>
+      <c r="N409" s="13">
+        <f>IF(AND(ISNUMBER(L409),ISNUMBER(M409)),L409-M409,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="L410" s="7" t="n"/>
+      <c r="M410" s="7" t="n"/>
+      <c r="N410" s="13">
+        <f>IF(AND(ISNUMBER(L410),ISNUMBER(M410)),L410-M410,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="L411" s="7" t="n"/>
+      <c r="M411" s="7" t="n"/>
+      <c r="N411" s="13">
+        <f>IF(AND(ISNUMBER(L411),ISNUMBER(M411)),L411-M411,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="L412" s="7" t="n"/>
+      <c r="M412" s="7" t="n"/>
+      <c r="N412" s="13">
+        <f>IF(AND(ISNUMBER(L412),ISNUMBER(M412)),L412-M412,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="L413" s="7" t="n"/>
+      <c r="M413" s="7" t="n"/>
+      <c r="N413" s="13">
+        <f>IF(AND(ISNUMBER(L413),ISNUMBER(M413)),L413-M413,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="L414" s="7" t="n"/>
+      <c r="M414" s="7" t="n"/>
+      <c r="N414" s="13">
+        <f>IF(AND(ISNUMBER(L414),ISNUMBER(M414)),L414-M414,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="L415" s="7" t="n"/>
+      <c r="M415" s="7" t="n"/>
+      <c r="N415" s="13">
+        <f>IF(AND(ISNUMBER(L415),ISNUMBER(M415)),L415-M415,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="416">
+      <c r="L416" s="7" t="n"/>
+      <c r="M416" s="7" t="n"/>
+      <c r="N416" s="13">
+        <f>IF(AND(ISNUMBER(L416),ISNUMBER(M416)),L416-M416,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="L417" s="7" t="n"/>
+      <c r="M417" s="7" t="n"/>
+      <c r="N417" s="13">
+        <f>IF(AND(ISNUMBER(L417),ISNUMBER(M417)),L417-M417,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="L418" s="7" t="n"/>
+      <c r="M418" s="7" t="n"/>
+      <c r="N418" s="13">
+        <f>IF(AND(ISNUMBER(L418),ISNUMBER(M418)),L418-M418,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="L419" s="7" t="n"/>
+      <c r="M419" s="7" t="n"/>
+      <c r="N419" s="13">
+        <f>IF(AND(ISNUMBER(L419),ISNUMBER(M419)),L419-M419,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="L420" s="7" t="n"/>
+      <c r="M420" s="7" t="n"/>
+      <c r="N420" s="13">
+        <f>IF(AND(ISNUMBER(L420),ISNUMBER(M420)),L420-M420,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="L421" s="7" t="n"/>
+      <c r="M421" s="7" t="n"/>
+      <c r="N421" s="13">
+        <f>IF(AND(ISNUMBER(L421),ISNUMBER(M421)),L421-M421,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="L422" s="7" t="n"/>
+      <c r="M422" s="7" t="n"/>
+      <c r="N422" s="13">
+        <f>IF(AND(ISNUMBER(L422),ISNUMBER(M422)),L422-M422,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="L423" s="7" t="n"/>
+      <c r="M423" s="7" t="n"/>
+      <c r="N423" s="13">
+        <f>IF(AND(ISNUMBER(L423),ISNUMBER(M423)),L423-M423,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="L424" s="7" t="n"/>
+      <c r="M424" s="7" t="n"/>
+      <c r="N424" s="13">
+        <f>IF(AND(ISNUMBER(L424),ISNUMBER(M424)),L424-M424,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="425">
+      <c r="L425" s="7" t="n"/>
+      <c r="M425" s="7" t="n"/>
+      <c r="N425" s="13">
+        <f>IF(AND(ISNUMBER(L425),ISNUMBER(M425)),L425-M425,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="L426" s="7" t="n"/>
+      <c r="M426" s="7" t="n"/>
+      <c r="N426" s="13">
+        <f>IF(AND(ISNUMBER(L426),ISNUMBER(M426)),L426-M426,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="L427" s="7" t="n"/>
+      <c r="M427" s="7" t="n"/>
+      <c r="N427" s="13">
+        <f>IF(AND(ISNUMBER(L427),ISNUMBER(M427)),L427-M427,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="L428" s="7" t="n"/>
+      <c r="M428" s="7" t="n"/>
+      <c r="N428" s="13">
+        <f>IF(AND(ISNUMBER(L428),ISNUMBER(M428)),L428-M428,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="L429" s="7" t="n"/>
+      <c r="M429" s="7" t="n"/>
+      <c r="N429" s="13">
+        <f>IF(AND(ISNUMBER(L429),ISNUMBER(M429)),L429-M429,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="L430" s="7" t="n"/>
+      <c r="M430" s="7" t="n"/>
+      <c r="N430" s="13">
+        <f>IF(AND(ISNUMBER(L430),ISNUMBER(M430)),L430-M430,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="L431" s="7" t="n"/>
+      <c r="M431" s="7" t="n"/>
+      <c r="N431" s="13">
+        <f>IF(AND(ISNUMBER(L431),ISNUMBER(M431)),L431-M431,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="L432" s="7" t="n"/>
+      <c r="M432" s="7" t="n"/>
+      <c r="N432" s="13">
+        <f>IF(AND(ISNUMBER(L432),ISNUMBER(M432)),L432-M432,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="L433" s="7" t="n"/>
+      <c r="M433" s="7" t="n"/>
+      <c r="N433" s="13">
+        <f>IF(AND(ISNUMBER(L433),ISNUMBER(M433)),L433-M433,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="L434" s="7" t="n"/>
+      <c r="M434" s="7" t="n"/>
+      <c r="N434" s="13">
+        <f>IF(AND(ISNUMBER(L434),ISNUMBER(M434)),L434-M434,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="L435" s="7" t="n"/>
+      <c r="M435" s="7" t="n"/>
+      <c r="N435" s="13">
+        <f>IF(AND(ISNUMBER(L435),ISNUMBER(M435)),L435-M435,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="L436" s="7" t="n"/>
+      <c r="M436" s="7" t="n"/>
+      <c r="N436" s="13">
+        <f>IF(AND(ISNUMBER(L436),ISNUMBER(M436)),L436-M436,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="L437" s="7" t="n"/>
+      <c r="M437" s="7" t="n"/>
+      <c r="N437" s="13">
+        <f>IF(AND(ISNUMBER(L437),ISNUMBER(M437)),L437-M437,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="438">
+      <c r="L438" s="7" t="n"/>
+      <c r="M438" s="7" t="n"/>
+      <c r="N438" s="13">
+        <f>IF(AND(ISNUMBER(L438),ISNUMBER(M438)),L438-M438,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="L439" s="7" t="n"/>
+      <c r="M439" s="7" t="n"/>
+      <c r="N439" s="13">
+        <f>IF(AND(ISNUMBER(L439),ISNUMBER(M439)),L439-M439,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="L440" s="7" t="n"/>
+      <c r="M440" s="7" t="n"/>
+      <c r="N440" s="13">
+        <f>IF(AND(ISNUMBER(L440),ISNUMBER(M440)),L440-M440,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="L441" s="7" t="n"/>
+      <c r="M441" s="7" t="n"/>
+      <c r="N441" s="13">
+        <f>IF(AND(ISNUMBER(L441),ISNUMBER(M441)),L441-M441,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="L442" s="7" t="n"/>
+      <c r="M442" s="7" t="n"/>
+      <c r="N442" s="13">
+        <f>IF(AND(ISNUMBER(L442),ISNUMBER(M442)),L442-M442,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="443">
+      <c r="L443" s="7" t="n"/>
+      <c r="M443" s="7" t="n"/>
+      <c r="N443" s="13">
+        <f>IF(AND(ISNUMBER(L443),ISNUMBER(M443)),L443-M443,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="L444" s="7" t="n"/>
+      <c r="M444" s="7" t="n"/>
+      <c r="N444" s="13">
+        <f>IF(AND(ISNUMBER(L444),ISNUMBER(M444)),L444-M444,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="L445" s="7" t="n"/>
+      <c r="M445" s="7" t="n"/>
+      <c r="N445" s="13">
+        <f>IF(AND(ISNUMBER(L445),ISNUMBER(M445)),L445-M445,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="446">
+      <c r="L446" s="7" t="n"/>
+      <c r="M446" s="7" t="n"/>
+      <c r="N446" s="13">
+        <f>IF(AND(ISNUMBER(L446),ISNUMBER(M446)),L446-M446,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="447">
+      <c r="L447" s="7" t="n"/>
+      <c r="M447" s="7" t="n"/>
+      <c r="N447" s="13">
+        <f>IF(AND(ISNUMBER(L447),ISNUMBER(M447)),L447-M447,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="L448" s="7" t="n"/>
+      <c r="M448" s="7" t="n"/>
+      <c r="N448" s="13">
+        <f>IF(AND(ISNUMBER(L448),ISNUMBER(M448)),L448-M448,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="L449" s="7" t="n"/>
+      <c r="M449" s="7" t="n"/>
+      <c r="N449" s="13">
+        <f>IF(AND(ISNUMBER(L449),ISNUMBER(M449)),L449-M449,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="L450" s="7" t="n"/>
+      <c r="M450" s="7" t="n"/>
+      <c r="N450" s="13">
+        <f>IF(AND(ISNUMBER(L450),ISNUMBER(M450)),L450-M450,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="451">
+      <c r="L451" s="7" t="n"/>
+      <c r="M451" s="7" t="n"/>
+      <c r="N451" s="13">
+        <f>IF(AND(ISNUMBER(L451),ISNUMBER(M451)),L451-M451,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="L452" s="7" t="n"/>
+      <c r="M452" s="7" t="n"/>
+      <c r="N452" s="13">
+        <f>IF(AND(ISNUMBER(L452),ISNUMBER(M452)),L452-M452,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="L453" s="7" t="n"/>
+      <c r="M453" s="7" t="n"/>
+      <c r="N453" s="13">
+        <f>IF(AND(ISNUMBER(L453),ISNUMBER(M453)),L453-M453,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="L454" s="7" t="n"/>
+      <c r="M454" s="7" t="n"/>
+      <c r="N454" s="13">
+        <f>IF(AND(ISNUMBER(L454),ISNUMBER(M454)),L454-M454,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="L455" s="7" t="n"/>
+      <c r="M455" s="7" t="n"/>
+      <c r="N455" s="13">
+        <f>IF(AND(ISNUMBER(L455),ISNUMBER(M455)),L455-M455,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="L456" s="7" t="n"/>
+      <c r="M456" s="7" t="n"/>
+      <c r="N456" s="13">
+        <f>IF(AND(ISNUMBER(L456),ISNUMBER(M456)),L456-M456,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="L457" s="7" t="n"/>
+      <c r="M457" s="7" t="n"/>
+      <c r="N457" s="13">
+        <f>IF(AND(ISNUMBER(L457),ISNUMBER(M457)),L457-M457,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="L458" s="7" t="n"/>
+      <c r="M458" s="7" t="n"/>
+      <c r="N458" s="13">
+        <f>IF(AND(ISNUMBER(L458),ISNUMBER(M458)),L458-M458,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="459">
+      <c r="L459" s="7" t="n"/>
+      <c r="M459" s="7" t="n"/>
+      <c r="N459" s="13">
+        <f>IF(AND(ISNUMBER(L459),ISNUMBER(M459)),L459-M459,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="460">
+      <c r="L460" s="7" t="n"/>
+      <c r="M460" s="7" t="n"/>
+      <c r="N460" s="13">
+        <f>IF(AND(ISNUMBER(L460),ISNUMBER(M460)),L460-M460,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="461">
+      <c r="L461" s="7" t="n"/>
+      <c r="M461" s="7" t="n"/>
+      <c r="N461" s="13">
+        <f>IF(AND(ISNUMBER(L461),ISNUMBER(M461)),L461-M461,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="462">
+      <c r="L462" s="7" t="n"/>
+      <c r="M462" s="7" t="n"/>
+      <c r="N462" s="13">
+        <f>IF(AND(ISNUMBER(L462),ISNUMBER(M462)),L462-M462,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="463">
+      <c r="L463" s="7" t="n"/>
+      <c r="M463" s="7" t="n"/>
+      <c r="N463" s="13">
+        <f>IF(AND(ISNUMBER(L463),ISNUMBER(M463)),L463-M463,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="464">
+      <c r="L464" s="7" t="n"/>
+      <c r="M464" s="7" t="n"/>
+      <c r="N464" s="13">
+        <f>IF(AND(ISNUMBER(L464),ISNUMBER(M464)),L464-M464,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="465">
+      <c r="L465" s="7" t="n"/>
+      <c r="M465" s="7" t="n"/>
+      <c r="N465" s="13">
+        <f>IF(AND(ISNUMBER(L465),ISNUMBER(M465)),L465-M465,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="466">
+      <c r="L466" s="7" t="n"/>
+      <c r="M466" s="7" t="n"/>
+      <c r="N466" s="13">
+        <f>IF(AND(ISNUMBER(L466),ISNUMBER(M466)),L466-M466,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="L467" s="7" t="n"/>
+      <c r="M467" s="7" t="n"/>
+      <c r="N467" s="13">
+        <f>IF(AND(ISNUMBER(L467),ISNUMBER(M467)),L467-M467,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="468">
+      <c r="L468" s="7" t="n"/>
+      <c r="M468" s="7" t="n"/>
+      <c r="N468" s="13">
+        <f>IF(AND(ISNUMBER(L468),ISNUMBER(M468)),L468-M468,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="469">
+      <c r="L469" s="7" t="n"/>
+      <c r="M469" s="7" t="n"/>
+      <c r="N469" s="13">
+        <f>IF(AND(ISNUMBER(L469),ISNUMBER(M469)),L469-M469,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="L470" s="7" t="n"/>
+      <c r="M470" s="7" t="n"/>
+      <c r="N470" s="13">
+        <f>IF(AND(ISNUMBER(L470),ISNUMBER(M470)),L470-M470,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471">
+      <c r="L471" s="7" t="n"/>
+      <c r="M471" s="7" t="n"/>
+      <c r="N471" s="13">
+        <f>IF(AND(ISNUMBER(L471),ISNUMBER(M471)),L471-M471,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="472">
+      <c r="L472" s="7" t="n"/>
+      <c r="M472" s="7" t="n"/>
+      <c r="N472" s="13">
+        <f>IF(AND(ISNUMBER(L472),ISNUMBER(M472)),L472-M472,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="473">
+      <c r="L473" s="7" t="n"/>
+      <c r="M473" s="7" t="n"/>
+      <c r="N473" s="13">
+        <f>IF(AND(ISNUMBER(L473),ISNUMBER(M473)),L473-M473,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="474">
+      <c r="L474" s="7" t="n"/>
+      <c r="M474" s="7" t="n"/>
+      <c r="N474" s="13">
+        <f>IF(AND(ISNUMBER(L474),ISNUMBER(M474)),L474-M474,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="475">
+      <c r="L475" s="7" t="n"/>
+      <c r="M475" s="7" t="n"/>
+      <c r="N475" s="13">
+        <f>IF(AND(ISNUMBER(L475),ISNUMBER(M475)),L475-M475,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="476">
+      <c r="L476" s="7" t="n"/>
+      <c r="M476" s="7" t="n"/>
+      <c r="N476" s="13">
+        <f>IF(AND(ISNUMBER(L476),ISNUMBER(M476)),L476-M476,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="477">
+      <c r="L477" s="7" t="n"/>
+      <c r="M477" s="7" t="n"/>
+      <c r="N477" s="13">
+        <f>IF(AND(ISNUMBER(L477),ISNUMBER(M477)),L477-M477,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="478">
+      <c r="L478" s="7" t="n"/>
+      <c r="M478" s="7" t="n"/>
+      <c r="N478" s="13">
+        <f>IF(AND(ISNUMBER(L478),ISNUMBER(M478)),L478-M478,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="479">
+      <c r="L479" s="7" t="n"/>
+      <c r="M479" s="7" t="n"/>
+      <c r="N479" s="13">
+        <f>IF(AND(ISNUMBER(L479),ISNUMBER(M479)),L479-M479,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="L480" s="7" t="n"/>
+      <c r="M480" s="7" t="n"/>
+      <c r="N480" s="13">
+        <f>IF(AND(ISNUMBER(L480),ISNUMBER(M480)),L480-M480,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="481">
+      <c r="L481" s="7" t="n"/>
+      <c r="M481" s="7" t="n"/>
+      <c r="N481" s="13">
+        <f>IF(AND(ISNUMBER(L481),ISNUMBER(M481)),L481-M481,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="482">
+      <c r="L482" s="7" t="n"/>
+      <c r="M482" s="7" t="n"/>
+      <c r="N482" s="13">
+        <f>IF(AND(ISNUMBER(L482),ISNUMBER(M482)),L482-M482,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="L483" s="7" t="n"/>
+      <c r="M483" s="7" t="n"/>
+      <c r="N483" s="13">
+        <f>IF(AND(ISNUMBER(L483),ISNUMBER(M483)),L483-M483,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484">
+      <c r="L484" s="7" t="n"/>
+      <c r="M484" s="7" t="n"/>
+      <c r="N484" s="13">
+        <f>IF(AND(ISNUMBER(L484),ISNUMBER(M484)),L484-M484,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="485">
+      <c r="L485" s="7" t="n"/>
+      <c r="M485" s="7" t="n"/>
+      <c r="N485" s="13">
+        <f>IF(AND(ISNUMBER(L485),ISNUMBER(M485)),L485-M485,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="486">
+      <c r="L486" s="7" t="n"/>
+      <c r="M486" s="7" t="n"/>
+      <c r="N486" s="13">
+        <f>IF(AND(ISNUMBER(L486),ISNUMBER(M486)),L486-M486,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="487">
+      <c r="L487" s="7" t="n"/>
+      <c r="M487" s="7" t="n"/>
+      <c r="N487" s="13">
+        <f>IF(AND(ISNUMBER(L487),ISNUMBER(M487)),L487-M487,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="488">
+      <c r="L488" s="7" t="n"/>
+      <c r="M488" s="7" t="n"/>
+      <c r="N488" s="13">
+        <f>IF(AND(ISNUMBER(L488),ISNUMBER(M488)),L488-M488,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489">
+      <c r="L489" s="7" t="n"/>
+      <c r="M489" s="7" t="n"/>
+      <c r="N489" s="13">
+        <f>IF(AND(ISNUMBER(L489),ISNUMBER(M489)),L489-M489,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="490">
+      <c r="L490" s="7" t="n"/>
+      <c r="M490" s="7" t="n"/>
+      <c r="N490" s="13">
+        <f>IF(AND(ISNUMBER(L490),ISNUMBER(M490)),L490-M490,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="491">
+      <c r="L491" s="7" t="n"/>
+      <c r="M491" s="7" t="n"/>
+      <c r="N491" s="13">
+        <f>IF(AND(ISNUMBER(L491),ISNUMBER(M491)),L491-M491,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="492">
+      <c r="L492" s="7" t="n"/>
+      <c r="M492" s="7" t="n"/>
+      <c r="N492" s="13">
+        <f>IF(AND(ISNUMBER(L492),ISNUMBER(M492)),L492-M492,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="L493" s="7" t="n"/>
+      <c r="M493" s="7" t="n"/>
+      <c r="N493" s="13">
+        <f>IF(AND(ISNUMBER(L493),ISNUMBER(M493)),L493-M493,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="494">
+      <c r="L494" s="7" t="n"/>
+      <c r="M494" s="7" t="n"/>
+      <c r="N494" s="13">
+        <f>IF(AND(ISNUMBER(L494),ISNUMBER(M494)),L494-M494,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="495">
+      <c r="L495" s="7" t="n"/>
+      <c r="M495" s="7" t="n"/>
+      <c r="N495" s="13">
+        <f>IF(AND(ISNUMBER(L495),ISNUMBER(M495)),L495-M495,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="L496" s="7" t="n"/>
+      <c r="M496" s="7" t="n"/>
+      <c r="N496" s="13">
+        <f>IF(AND(ISNUMBER(L496),ISNUMBER(M496)),L496-M496,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497">
+      <c r="L497" s="7" t="n"/>
+      <c r="M497" s="7" t="n"/>
+      <c r="N497" s="13">
+        <f>IF(AND(ISNUMBER(L497),ISNUMBER(M497)),L497-M497,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="498">
+      <c r="L498" s="7" t="n"/>
+      <c r="M498" s="7" t="n"/>
+      <c r="N498" s="13">
+        <f>IF(AND(ISNUMBER(L498),ISNUMBER(M498)),L498-M498,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="499">
+      <c r="L499" s="7" t="n"/>
+      <c r="M499" s="7" t="n"/>
+      <c r="N499" s="13">
+        <f>IF(AND(ISNUMBER(L499),ISNUMBER(M499)),L499-M499,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="500">
+      <c r="L500" s="7" t="n"/>
+      <c r="M500" s="7" t="n"/>
+      <c r="N500" s="13">
+        <f>IF(AND(ISNUMBER(L500),ISNUMBER(M500)),L500-M500,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="501">
+      <c r="L501" s="7" t="n"/>
+      <c r="M501" s="7" t="n"/>
+      <c r="N501" s="13">
+        <f>IF(AND(ISNUMBER(L501),ISNUMBER(M501)),L501-M501,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="502">
+      <c r="L502" s="7" t="n"/>
+      <c r="M502" s="7" t="n"/>
+      <c r="N502" s="13">
+        <f>IF(AND(ISNUMBER(L502),ISNUMBER(M502)),L502-M502,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="503">
+      <c r="L503" s="7" t="n"/>
+      <c r="M503" s="7" t="n"/>
+      <c r="N503" s="13">
+        <f>IF(AND(ISNUMBER(L503),ISNUMBER(M503)),L503-M503,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="504">
+      <c r="L504" s="7" t="n"/>
+      <c r="M504" s="7" t="n"/>
+      <c r="N504" s="13">
+        <f>IF(AND(ISNUMBER(L504),ISNUMBER(M504)),L504-M504,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="505">
+      <c r="L505" s="7" t="n"/>
+      <c r="M505" s="7" t="n"/>
+      <c r="N505" s="13">
+        <f>IF(AND(ISNUMBER(L505),ISNUMBER(M505)),L505-M505,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="L506" s="7" t="n"/>
+      <c r="M506" s="7" t="n"/>
+      <c r="N506" s="13">
+        <f>IF(AND(ISNUMBER(L506),ISNUMBER(M506)),L506-M506,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="507">
+      <c r="L507" s="7" t="n"/>
+      <c r="M507" s="7" t="n"/>
+      <c r="N507" s="13">
+        <f>IF(AND(ISNUMBER(L507),ISNUMBER(M507)),L507-M507,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="508">
+      <c r="L508" s="7" t="n"/>
+      <c r="M508" s="7" t="n"/>
+      <c r="N508" s="13">
+        <f>IF(AND(ISNUMBER(L508),ISNUMBER(M508)),L508-M508,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="L509" s="7" t="n"/>
+      <c r="M509" s="7" t="n"/>
+      <c r="N509" s="13">
+        <f>IF(AND(ISNUMBER(L509),ISNUMBER(M509)),L509-M509,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B9 B97" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fraction" error="Type a fraction, e.g. 0.05." type="decimal" operator="between">
+      <formula1>0.0000001</formula1>
+      <formula2>0.9999999</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion matrix" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distributions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean &amp; proportion" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control charts" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -13869,6 +13870,7579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V316"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Control charts: X̄-R and X̄-s (subgroups), I-MR (individuals), p chart and u chart, with out-of-limit flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 55, 62-73; ___4.1 tabellen SPC.pdf p. 1-2; Six Sigma For Dummies.pdf p. 239-256; Les 5/20260619_ottoy_Rheostat Knob Data.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Decision 4: constants from Table 18 (A2, D3, D4, B3, B4, d2), Table A (c4), Six Sigma Demystified (A3, E2); 3σ limits; a negative lower limit is shown as 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: tested against course worked examples S06-WE03, S06-WE05, S06-WE06, S08-WE18, S08-WE21, S10-WE04a, S10-WE04b; a few printed values disagree (build/README.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. X̄-R and X̄-s charts from subgroups (fill the table from row 30: raw values, or x̄ and R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>n = subgroup size, when subgroups are typed as x̄ and R</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>raw values: n is counted per row</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Summary of the subgroups</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>k = number of subgroups</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>IF(COUNT(P30:P79)&gt;0,COUNT(P30:P79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>n used (largest subgroup size)</t>
+        </is>
+      </c>
+      <c r="B13" s="24">
+        <f>IF(COUNT(O30:O79)&gt;0,MAX(O30:O79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Equal subgroup sizes?</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>IF(COUNT(O30:O79)&gt;0,IF(MIN(O30:O79)=MAX(O30:O79),"yes","NO: limits use the largest n (deck p. 73: variable sample size)"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>X̿ = mean of the subgroup means</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
+        <f>IF(COUNT(P30:P79)&gt;0,AVERAGE(P30:P79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>R̄ = mean range</t>
+        </is>
+      </c>
+      <c r="B16" s="28">
+        <f>IF(COUNT(Q30:Q79)&gt;0,AVERAGE(Q30:Q79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>s̄ = mean standard deviation</t>
+        </is>
+      </c>
+      <c r="B17" s="28">
+        <f>IF(COUNT(R30:R79)&gt;0,AVERAGE(R30:R79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>σ̂ = R̄ / d2  (d2 in column C)</t>
+        </is>
+      </c>
+      <c r="B18" s="28">
+        <f>IF(AND(ISNUMBER(B16),ISNUMBER(C18)),B16/C18,"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="12">
+        <f>IF(ISNUMBER(B13),IFERROR(INDEX(T18_d2,MATCH(B13,T18_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 64 (speaker notes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>σ̂ = s̄ / c4  (c4 in column C)</t>
+        </is>
+      </c>
+      <c r="B19" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(C19)),B17/C19,"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="11">
+        <f>IF(ISNUMBER(B13),IFERROR(INDEX(TA_c4,MATCH(B13,TA_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>___4.1 tabellen SPC.pdf p. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>σ(x̄) = σ̂ / √n  (with R̄/d2)</t>
+        </is>
+      </c>
+      <c r="B20" s="28">
+        <f>IF(AND(ISNUMBER(B18),ISNUMBER(B13)),B18/SQRT(B13),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 64 notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>UCL</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Constants</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>X̄ chart with R̄: X̿ ± A2·R̄</t>
+        </is>
+      </c>
+      <c r="B23" s="28">
+        <f>IF(AND(AND(ISNUMBER(B15),ISNUMBER(F23)),ISNUMBER(B16)),B15-F23*B16,"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>IF(ISNUMBER(B15),B15,"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>IF(AND(AND(ISNUMBER(B15),ISNUMBER(F23)),ISNUMBER(B16)),B15+F23*B16,"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="F23" s="12">
+        <f>IF(ISNUMBER($B$13),IFERROR(INDEX(T18_A2,MATCH($B$13,T18_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 73; Dummies p. 249</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>R chart: D3·R̄ … D4·R̄</t>
+        </is>
+      </c>
+      <c r="B24" s="28">
+        <f>IF(AND(ISNUMBER(B16),ISNUMBER(F24),ISNUMBER(G24)),F24*B16,"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="28">
+        <f>IF(ISNUMBER(B16),B16,"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="28">
+        <f>IF(AND(ISNUMBER(B16),ISNUMBER(F24),ISNUMBER(G24)),G24*B16,"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>D3, D4</t>
+        </is>
+      </c>
+      <c r="F24" s="12">
+        <f>IF(ISNUMBER($B$13),IFERROR(INDEX(T18_D3,MATCH($B$13,T18_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="12">
+        <f>IF(ISNUMBER($B$13),IFERROR(INDEX(T18_D4,MATCH($B$13,T18_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>X̄ chart with s̄: X̿ ± A3·s̄</t>
+        </is>
+      </c>
+      <c r="B25" s="28">
+        <f>IF(AND(AND(ISNUMBER(B15),ISNUMBER(F25)),ISNUMBER(B17)),B15-F25*B17,"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>IF(ISNUMBER(B15),B15,"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>IF(AND(AND(ISNUMBER(B15),ISNUMBER(F25)),ISNUMBER(B17)),B15+F25*B17,"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="F25" s="12">
+        <f>IF(ISNUMBER($B$13),IFERROR(INDEX(SSD1_A3,MATCH($B$13,SSD1_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 73 (preferred for n &gt; 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>s chart: B3·s̄ … B4·s̄</t>
+        </is>
+      </c>
+      <c r="B26" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(F26),ISNUMBER(G26)),F26*B17,"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>IF(ISNUMBER(B17),B17,"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>IF(AND(ISNUMBER(B17),ISNUMBER(F26),ISNUMBER(G26)),G26*B17,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>B3, B4</t>
+        </is>
+      </c>
+      <c r="F26" s="12">
+        <f>IF(ISNUMBER($B$13),IFERROR(INDEX(T18_B3,MATCH($B$13,T18_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="12">
+        <f>IF(ISNUMBER($B$13),IFERROR(INDEX(T18_B4,MATCH($B$13,T18_n,0)),"n not in table"),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>deck p. 73</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Subgroup</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>x7</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>x8</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>x10</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>or: x̄ typed</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>R typed</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>s typed</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>x̄</t>
+        </is>
+      </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>x̄ vs X̄-R</t>
+        </is>
+      </c>
+      <c r="T29" s="10" t="inlineStr">
+        <is>
+          <t>R vs R</t>
+        </is>
+      </c>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
+          <t>x̄ vs X̄-s</t>
+        </is>
+      </c>
+      <c r="V29" s="10" t="inlineStr">
+        <is>
+          <t>s vs s</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="7" t="n"/>
+      <c r="K30" s="7" t="n"/>
+      <c r="L30" s="7" t="n"/>
+      <c r="M30" s="7" t="n"/>
+      <c r="N30" s="7" t="n"/>
+      <c r="O30" s="24">
+        <f>IF(COUNT(B30:K30)&gt;0,COUNT(B30:K30),IF(OR(ISNUMBER(L30),ISNUMBER(M30)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P30" s="28">
+        <f>IF(COUNT(B30:K30)&gt;0,AVERAGE(B30:K30),IF(ISNUMBER(L30),L30,""))</f>
+        <v/>
+      </c>
+      <c r="Q30" s="28">
+        <f>IF(COUNT(B30:K30)&gt;1,MAX(B30:K30)-MIN(B30:K30),IF(ISNUMBER(M30),M30,""))</f>
+        <v/>
+      </c>
+      <c r="R30" s="28">
+        <f>IF(COUNT(B30:K30)&gt;1,_xlfn.STDEV.S(B30:K30),IF(ISNUMBER(N30),N30,""))</f>
+        <v/>
+      </c>
+      <c r="S30" s="13">
+        <f>IF(AND(ISNUMBER(P30),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P30&gt;$D$23,"above UCL",IF(P30&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T30" s="13">
+        <f>IF(AND(ISNUMBER(Q30),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q30&gt;$D$24,"above UCL",IF(Q30&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U30" s="13">
+        <f>IF(AND(ISNUMBER(P30),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P30&gt;$D$25,"above UCL",IF(P30&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V30" s="13">
+        <f>IF(AND(ISNUMBER(R30),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R30&gt;$D$26,"above UCL",IF(R30&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
+      <c r="L31" s="7" t="n"/>
+      <c r="M31" s="7" t="n"/>
+      <c r="N31" s="7" t="n"/>
+      <c r="O31" s="24">
+        <f>IF(COUNT(B31:K31)&gt;0,COUNT(B31:K31),IF(OR(ISNUMBER(L31),ISNUMBER(M31)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P31" s="28">
+        <f>IF(COUNT(B31:K31)&gt;0,AVERAGE(B31:K31),IF(ISNUMBER(L31),L31,""))</f>
+        <v/>
+      </c>
+      <c r="Q31" s="28">
+        <f>IF(COUNT(B31:K31)&gt;1,MAX(B31:K31)-MIN(B31:K31),IF(ISNUMBER(M31),M31,""))</f>
+        <v/>
+      </c>
+      <c r="R31" s="28">
+        <f>IF(COUNT(B31:K31)&gt;1,_xlfn.STDEV.S(B31:K31),IF(ISNUMBER(N31),N31,""))</f>
+        <v/>
+      </c>
+      <c r="S31" s="13">
+        <f>IF(AND(ISNUMBER(P31),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P31&gt;$D$23,"above UCL",IF(P31&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T31" s="13">
+        <f>IF(AND(ISNUMBER(Q31),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q31&gt;$D$24,"above UCL",IF(Q31&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U31" s="13">
+        <f>IF(AND(ISNUMBER(P31),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P31&gt;$D$25,"above UCL",IF(P31&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V31" s="13">
+        <f>IF(AND(ISNUMBER(R31),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R31&gt;$D$26,"above UCL",IF(R31&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="7" t="n"/>
+      <c r="N32" s="7" t="n"/>
+      <c r="O32" s="24">
+        <f>IF(COUNT(B32:K32)&gt;0,COUNT(B32:K32),IF(OR(ISNUMBER(L32),ISNUMBER(M32)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P32" s="28">
+        <f>IF(COUNT(B32:K32)&gt;0,AVERAGE(B32:K32),IF(ISNUMBER(L32),L32,""))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="28">
+        <f>IF(COUNT(B32:K32)&gt;1,MAX(B32:K32)-MIN(B32:K32),IF(ISNUMBER(M32),M32,""))</f>
+        <v/>
+      </c>
+      <c r="R32" s="28">
+        <f>IF(COUNT(B32:K32)&gt;1,_xlfn.STDEV.S(B32:K32),IF(ISNUMBER(N32),N32,""))</f>
+        <v/>
+      </c>
+      <c r="S32" s="13">
+        <f>IF(AND(ISNUMBER(P32),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P32&gt;$D$23,"above UCL",IF(P32&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T32" s="13">
+        <f>IF(AND(ISNUMBER(Q32),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q32&gt;$D$24,"above UCL",IF(Q32&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U32" s="13">
+        <f>IF(AND(ISNUMBER(P32),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P32&gt;$D$25,"above UCL",IF(P32&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V32" s="13">
+        <f>IF(AND(ISNUMBER(R32),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R32&gt;$D$26,"above UCL",IF(R32&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
+      <c r="L33" s="7" t="n"/>
+      <c r="M33" s="7" t="n"/>
+      <c r="N33" s="7" t="n"/>
+      <c r="O33" s="24">
+        <f>IF(COUNT(B33:K33)&gt;0,COUNT(B33:K33),IF(OR(ISNUMBER(L33),ISNUMBER(M33)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P33" s="28">
+        <f>IF(COUNT(B33:K33)&gt;0,AVERAGE(B33:K33),IF(ISNUMBER(L33),L33,""))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="28">
+        <f>IF(COUNT(B33:K33)&gt;1,MAX(B33:K33)-MIN(B33:K33),IF(ISNUMBER(M33),M33,""))</f>
+        <v/>
+      </c>
+      <c r="R33" s="28">
+        <f>IF(COUNT(B33:K33)&gt;1,_xlfn.STDEV.S(B33:K33),IF(ISNUMBER(N33),N33,""))</f>
+        <v/>
+      </c>
+      <c r="S33" s="13">
+        <f>IF(AND(ISNUMBER(P33),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P33&gt;$D$23,"above UCL",IF(P33&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T33" s="13">
+        <f>IF(AND(ISNUMBER(Q33),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q33&gt;$D$24,"above UCL",IF(Q33&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U33" s="13">
+        <f>IF(AND(ISNUMBER(P33),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P33&gt;$D$25,"above UCL",IF(P33&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V33" s="13">
+        <f>IF(AND(ISNUMBER(R33),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R33&gt;$D$26,"above UCL",IF(R33&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="7" t="n"/>
+      <c r="L34" s="7" t="n"/>
+      <c r="M34" s="7" t="n"/>
+      <c r="N34" s="7" t="n"/>
+      <c r="O34" s="24">
+        <f>IF(COUNT(B34:K34)&gt;0,COUNT(B34:K34),IF(OR(ISNUMBER(L34),ISNUMBER(M34)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P34" s="28">
+        <f>IF(COUNT(B34:K34)&gt;0,AVERAGE(B34:K34),IF(ISNUMBER(L34),L34,""))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="28">
+        <f>IF(COUNT(B34:K34)&gt;1,MAX(B34:K34)-MIN(B34:K34),IF(ISNUMBER(M34),M34,""))</f>
+        <v/>
+      </c>
+      <c r="R34" s="28">
+        <f>IF(COUNT(B34:K34)&gt;1,_xlfn.STDEV.S(B34:K34),IF(ISNUMBER(N34),N34,""))</f>
+        <v/>
+      </c>
+      <c r="S34" s="13">
+        <f>IF(AND(ISNUMBER(P34),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P34&gt;$D$23,"above UCL",IF(P34&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="13">
+        <f>IF(AND(ISNUMBER(Q34),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q34&gt;$D$24,"above UCL",IF(Q34&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U34" s="13">
+        <f>IF(AND(ISNUMBER(P34),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P34&gt;$D$25,"above UCL",IF(P34&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V34" s="13">
+        <f>IF(AND(ISNUMBER(R34),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R34&gt;$D$26,"above UCL",IF(R34&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
+      <c r="K35" s="7" t="n"/>
+      <c r="L35" s="7" t="n"/>
+      <c r="M35" s="7" t="n"/>
+      <c r="N35" s="7" t="n"/>
+      <c r="O35" s="24">
+        <f>IF(COUNT(B35:K35)&gt;0,COUNT(B35:K35),IF(OR(ISNUMBER(L35),ISNUMBER(M35)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P35" s="28">
+        <f>IF(COUNT(B35:K35)&gt;0,AVERAGE(B35:K35),IF(ISNUMBER(L35),L35,""))</f>
+        <v/>
+      </c>
+      <c r="Q35" s="28">
+        <f>IF(COUNT(B35:K35)&gt;1,MAX(B35:K35)-MIN(B35:K35),IF(ISNUMBER(M35),M35,""))</f>
+        <v/>
+      </c>
+      <c r="R35" s="28">
+        <f>IF(COUNT(B35:K35)&gt;1,_xlfn.STDEV.S(B35:K35),IF(ISNUMBER(N35),N35,""))</f>
+        <v/>
+      </c>
+      <c r="S35" s="13">
+        <f>IF(AND(ISNUMBER(P35),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P35&gt;$D$23,"above UCL",IF(P35&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="13">
+        <f>IF(AND(ISNUMBER(Q35),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q35&gt;$D$24,"above UCL",IF(Q35&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U35" s="13">
+        <f>IF(AND(ISNUMBER(P35),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P35&gt;$D$25,"above UCL",IF(P35&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V35" s="13">
+        <f>IF(AND(ISNUMBER(R35),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R35&gt;$D$26,"above UCL",IF(R35&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="7" t="n"/>
+      <c r="N36" s="7" t="n"/>
+      <c r="O36" s="24">
+        <f>IF(COUNT(B36:K36)&gt;0,COUNT(B36:K36),IF(OR(ISNUMBER(L36),ISNUMBER(M36)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P36" s="28">
+        <f>IF(COUNT(B36:K36)&gt;0,AVERAGE(B36:K36),IF(ISNUMBER(L36),L36,""))</f>
+        <v/>
+      </c>
+      <c r="Q36" s="28">
+        <f>IF(COUNT(B36:K36)&gt;1,MAX(B36:K36)-MIN(B36:K36),IF(ISNUMBER(M36),M36,""))</f>
+        <v/>
+      </c>
+      <c r="R36" s="28">
+        <f>IF(COUNT(B36:K36)&gt;1,_xlfn.STDEV.S(B36:K36),IF(ISNUMBER(N36),N36,""))</f>
+        <v/>
+      </c>
+      <c r="S36" s="13">
+        <f>IF(AND(ISNUMBER(P36),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P36&gt;$D$23,"above UCL",IF(P36&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T36" s="13">
+        <f>IF(AND(ISNUMBER(Q36),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q36&gt;$D$24,"above UCL",IF(Q36&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U36" s="13">
+        <f>IF(AND(ISNUMBER(P36),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P36&gt;$D$25,"above UCL",IF(P36&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V36" s="13">
+        <f>IF(AND(ISNUMBER(R36),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R36&gt;$D$26,"above UCL",IF(R36&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="24">
+        <f>IF(COUNT(B37:K37)&gt;0,COUNT(B37:K37),IF(OR(ISNUMBER(L37),ISNUMBER(M37)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P37" s="28">
+        <f>IF(COUNT(B37:K37)&gt;0,AVERAGE(B37:K37),IF(ISNUMBER(L37),L37,""))</f>
+        <v/>
+      </c>
+      <c r="Q37" s="28">
+        <f>IF(COUNT(B37:K37)&gt;1,MAX(B37:K37)-MIN(B37:K37),IF(ISNUMBER(M37),M37,""))</f>
+        <v/>
+      </c>
+      <c r="R37" s="28">
+        <f>IF(COUNT(B37:K37)&gt;1,_xlfn.STDEV.S(B37:K37),IF(ISNUMBER(N37),N37,""))</f>
+        <v/>
+      </c>
+      <c r="S37" s="13">
+        <f>IF(AND(ISNUMBER(P37),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P37&gt;$D$23,"above UCL",IF(P37&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T37" s="13">
+        <f>IF(AND(ISNUMBER(Q37),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q37&gt;$D$24,"above UCL",IF(Q37&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U37" s="13">
+        <f>IF(AND(ISNUMBER(P37),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P37&gt;$D$25,"above UCL",IF(P37&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V37" s="13">
+        <f>IF(AND(ISNUMBER(R37),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R37&gt;$D$26,"above UCL",IF(R37&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="7" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="7" t="n"/>
+      <c r="M38" s="7" t="n"/>
+      <c r="N38" s="7" t="n"/>
+      <c r="O38" s="24">
+        <f>IF(COUNT(B38:K38)&gt;0,COUNT(B38:K38),IF(OR(ISNUMBER(L38),ISNUMBER(M38)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P38" s="28">
+        <f>IF(COUNT(B38:K38)&gt;0,AVERAGE(B38:K38),IF(ISNUMBER(L38),L38,""))</f>
+        <v/>
+      </c>
+      <c r="Q38" s="28">
+        <f>IF(COUNT(B38:K38)&gt;1,MAX(B38:K38)-MIN(B38:K38),IF(ISNUMBER(M38),M38,""))</f>
+        <v/>
+      </c>
+      <c r="R38" s="28">
+        <f>IF(COUNT(B38:K38)&gt;1,_xlfn.STDEV.S(B38:K38),IF(ISNUMBER(N38),N38,""))</f>
+        <v/>
+      </c>
+      <c r="S38" s="13">
+        <f>IF(AND(ISNUMBER(P38),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P38&gt;$D$23,"above UCL",IF(P38&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="13">
+        <f>IF(AND(ISNUMBER(Q38),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q38&gt;$D$24,"above UCL",IF(Q38&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="13">
+        <f>IF(AND(ISNUMBER(P38),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P38&gt;$D$25,"above UCL",IF(P38&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V38" s="13">
+        <f>IF(AND(ISNUMBER(R38),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R38&gt;$D$26,"above UCL",IF(R38&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>10</v>
+      </c>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="K39" s="7" t="n"/>
+      <c r="L39" s="7" t="n"/>
+      <c r="M39" s="7" t="n"/>
+      <c r="N39" s="7" t="n"/>
+      <c r="O39" s="24">
+        <f>IF(COUNT(B39:K39)&gt;0,COUNT(B39:K39),IF(OR(ISNUMBER(L39),ISNUMBER(M39)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P39" s="28">
+        <f>IF(COUNT(B39:K39)&gt;0,AVERAGE(B39:K39),IF(ISNUMBER(L39),L39,""))</f>
+        <v/>
+      </c>
+      <c r="Q39" s="28">
+        <f>IF(COUNT(B39:K39)&gt;1,MAX(B39:K39)-MIN(B39:K39),IF(ISNUMBER(M39),M39,""))</f>
+        <v/>
+      </c>
+      <c r="R39" s="28">
+        <f>IF(COUNT(B39:K39)&gt;1,_xlfn.STDEV.S(B39:K39),IF(ISNUMBER(N39),N39,""))</f>
+        <v/>
+      </c>
+      <c r="S39" s="13">
+        <f>IF(AND(ISNUMBER(P39),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P39&gt;$D$23,"above UCL",IF(P39&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="13">
+        <f>IF(AND(ISNUMBER(Q39),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q39&gt;$D$24,"above UCL",IF(Q39&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="13">
+        <f>IF(AND(ISNUMBER(P39),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P39&gt;$D$25,"above UCL",IF(P39&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V39" s="13">
+        <f>IF(AND(ISNUMBER(R39),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R39&gt;$D$26,"above UCL",IF(R39&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>11</v>
+      </c>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="K40" s="7" t="n"/>
+      <c r="L40" s="7" t="n"/>
+      <c r="M40" s="7" t="n"/>
+      <c r="N40" s="7" t="n"/>
+      <c r="O40" s="24">
+        <f>IF(COUNT(B40:K40)&gt;0,COUNT(B40:K40),IF(OR(ISNUMBER(L40),ISNUMBER(M40)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P40" s="28">
+        <f>IF(COUNT(B40:K40)&gt;0,AVERAGE(B40:K40),IF(ISNUMBER(L40),L40,""))</f>
+        <v/>
+      </c>
+      <c r="Q40" s="28">
+        <f>IF(COUNT(B40:K40)&gt;1,MAX(B40:K40)-MIN(B40:K40),IF(ISNUMBER(M40),M40,""))</f>
+        <v/>
+      </c>
+      <c r="R40" s="28">
+        <f>IF(COUNT(B40:K40)&gt;1,_xlfn.STDEV.S(B40:K40),IF(ISNUMBER(N40),N40,""))</f>
+        <v/>
+      </c>
+      <c r="S40" s="13">
+        <f>IF(AND(ISNUMBER(P40),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P40&gt;$D$23,"above UCL",IF(P40&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T40" s="13">
+        <f>IF(AND(ISNUMBER(Q40),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q40&gt;$D$24,"above UCL",IF(Q40&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U40" s="13">
+        <f>IF(AND(ISNUMBER(P40),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P40&gt;$D$25,"above UCL",IF(P40&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V40" s="13">
+        <f>IF(AND(ISNUMBER(R40),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R40&gt;$D$26,"above UCL",IF(R40&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+      <c r="L41" s="7" t="n"/>
+      <c r="M41" s="7" t="n"/>
+      <c r="N41" s="7" t="n"/>
+      <c r="O41" s="24">
+        <f>IF(COUNT(B41:K41)&gt;0,COUNT(B41:K41),IF(OR(ISNUMBER(L41),ISNUMBER(M41)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P41" s="28">
+        <f>IF(COUNT(B41:K41)&gt;0,AVERAGE(B41:K41),IF(ISNUMBER(L41),L41,""))</f>
+        <v/>
+      </c>
+      <c r="Q41" s="28">
+        <f>IF(COUNT(B41:K41)&gt;1,MAX(B41:K41)-MIN(B41:K41),IF(ISNUMBER(M41),M41,""))</f>
+        <v/>
+      </c>
+      <c r="R41" s="28">
+        <f>IF(COUNT(B41:K41)&gt;1,_xlfn.STDEV.S(B41:K41),IF(ISNUMBER(N41),N41,""))</f>
+        <v/>
+      </c>
+      <c r="S41" s="13">
+        <f>IF(AND(ISNUMBER(P41),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P41&gt;$D$23,"above UCL",IF(P41&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T41" s="13">
+        <f>IF(AND(ISNUMBER(Q41),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q41&gt;$D$24,"above UCL",IF(Q41&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U41" s="13">
+        <f>IF(AND(ISNUMBER(P41),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P41&gt;$D$25,"above UCL",IF(P41&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V41" s="13">
+        <f>IF(AND(ISNUMBER(R41),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R41&gt;$D$26,"above UCL",IF(R41&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
+      <c r="L42" s="7" t="n"/>
+      <c r="M42" s="7" t="n"/>
+      <c r="N42" s="7" t="n"/>
+      <c r="O42" s="24">
+        <f>IF(COUNT(B42:K42)&gt;0,COUNT(B42:K42),IF(OR(ISNUMBER(L42),ISNUMBER(M42)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P42" s="28">
+        <f>IF(COUNT(B42:K42)&gt;0,AVERAGE(B42:K42),IF(ISNUMBER(L42),L42,""))</f>
+        <v/>
+      </c>
+      <c r="Q42" s="28">
+        <f>IF(COUNT(B42:K42)&gt;1,MAX(B42:K42)-MIN(B42:K42),IF(ISNUMBER(M42),M42,""))</f>
+        <v/>
+      </c>
+      <c r="R42" s="28">
+        <f>IF(COUNT(B42:K42)&gt;1,_xlfn.STDEV.S(B42:K42),IF(ISNUMBER(N42),N42,""))</f>
+        <v/>
+      </c>
+      <c r="S42" s="13">
+        <f>IF(AND(ISNUMBER(P42),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P42&gt;$D$23,"above UCL",IF(P42&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T42" s="13">
+        <f>IF(AND(ISNUMBER(Q42),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q42&gt;$D$24,"above UCL",IF(Q42&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U42" s="13">
+        <f>IF(AND(ISNUMBER(P42),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P42&gt;$D$25,"above UCL",IF(P42&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V42" s="13">
+        <f>IF(AND(ISNUMBER(R42),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R42&gt;$D$26,"above UCL",IF(R42&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="24">
+        <f>IF(COUNT(B43:K43)&gt;0,COUNT(B43:K43),IF(OR(ISNUMBER(L43),ISNUMBER(M43)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P43" s="28">
+        <f>IF(COUNT(B43:K43)&gt;0,AVERAGE(B43:K43),IF(ISNUMBER(L43),L43,""))</f>
+        <v/>
+      </c>
+      <c r="Q43" s="28">
+        <f>IF(COUNT(B43:K43)&gt;1,MAX(B43:K43)-MIN(B43:K43),IF(ISNUMBER(M43),M43,""))</f>
+        <v/>
+      </c>
+      <c r="R43" s="28">
+        <f>IF(COUNT(B43:K43)&gt;1,_xlfn.STDEV.S(B43:K43),IF(ISNUMBER(N43),N43,""))</f>
+        <v/>
+      </c>
+      <c r="S43" s="13">
+        <f>IF(AND(ISNUMBER(P43),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P43&gt;$D$23,"above UCL",IF(P43&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T43" s="13">
+        <f>IF(AND(ISNUMBER(Q43),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q43&gt;$D$24,"above UCL",IF(Q43&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U43" s="13">
+        <f>IF(AND(ISNUMBER(P43),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P43&gt;$D$25,"above UCL",IF(P43&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V43" s="13">
+        <f>IF(AND(ISNUMBER(R43),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R43&gt;$D$26,"above UCL",IF(R43&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+      <c r="L44" s="7" t="n"/>
+      <c r="M44" s="7" t="n"/>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="24">
+        <f>IF(COUNT(B44:K44)&gt;0,COUNT(B44:K44),IF(OR(ISNUMBER(L44),ISNUMBER(M44)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P44" s="28">
+        <f>IF(COUNT(B44:K44)&gt;0,AVERAGE(B44:K44),IF(ISNUMBER(L44),L44,""))</f>
+        <v/>
+      </c>
+      <c r="Q44" s="28">
+        <f>IF(COUNT(B44:K44)&gt;1,MAX(B44:K44)-MIN(B44:K44),IF(ISNUMBER(M44),M44,""))</f>
+        <v/>
+      </c>
+      <c r="R44" s="28">
+        <f>IF(COUNT(B44:K44)&gt;1,_xlfn.STDEV.S(B44:K44),IF(ISNUMBER(N44),N44,""))</f>
+        <v/>
+      </c>
+      <c r="S44" s="13">
+        <f>IF(AND(ISNUMBER(P44),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P44&gt;$D$23,"above UCL",IF(P44&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T44" s="13">
+        <f>IF(AND(ISNUMBER(Q44),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q44&gt;$D$24,"above UCL",IF(Q44&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U44" s="13">
+        <f>IF(AND(ISNUMBER(P44),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P44&gt;$D$25,"above UCL",IF(P44&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V44" s="13">
+        <f>IF(AND(ISNUMBER(R44),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R44&gt;$D$26,"above UCL",IF(R44&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>16</v>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="7" t="n"/>
+      <c r="L45" s="7" t="n"/>
+      <c r="M45" s="7" t="n"/>
+      <c r="N45" s="7" t="n"/>
+      <c r="O45" s="24">
+        <f>IF(COUNT(B45:K45)&gt;0,COUNT(B45:K45),IF(OR(ISNUMBER(L45),ISNUMBER(M45)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P45" s="28">
+        <f>IF(COUNT(B45:K45)&gt;0,AVERAGE(B45:K45),IF(ISNUMBER(L45),L45,""))</f>
+        <v/>
+      </c>
+      <c r="Q45" s="28">
+        <f>IF(COUNT(B45:K45)&gt;1,MAX(B45:K45)-MIN(B45:K45),IF(ISNUMBER(M45),M45,""))</f>
+        <v/>
+      </c>
+      <c r="R45" s="28">
+        <f>IF(COUNT(B45:K45)&gt;1,_xlfn.STDEV.S(B45:K45),IF(ISNUMBER(N45),N45,""))</f>
+        <v/>
+      </c>
+      <c r="S45" s="13">
+        <f>IF(AND(ISNUMBER(P45),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P45&gt;$D$23,"above UCL",IF(P45&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T45" s="13">
+        <f>IF(AND(ISNUMBER(Q45),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q45&gt;$D$24,"above UCL",IF(Q45&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U45" s="13">
+        <f>IF(AND(ISNUMBER(P45),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P45&gt;$D$25,"above UCL",IF(P45&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V45" s="13">
+        <f>IF(AND(ISNUMBER(R45),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R45&gt;$D$26,"above UCL",IF(R45&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>17</v>
+      </c>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
+      <c r="L46" s="7" t="n"/>
+      <c r="M46" s="7" t="n"/>
+      <c r="N46" s="7" t="n"/>
+      <c r="O46" s="24">
+        <f>IF(COUNT(B46:K46)&gt;0,COUNT(B46:K46),IF(OR(ISNUMBER(L46),ISNUMBER(M46)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P46" s="28">
+        <f>IF(COUNT(B46:K46)&gt;0,AVERAGE(B46:K46),IF(ISNUMBER(L46),L46,""))</f>
+        <v/>
+      </c>
+      <c r="Q46" s="28">
+        <f>IF(COUNT(B46:K46)&gt;1,MAX(B46:K46)-MIN(B46:K46),IF(ISNUMBER(M46),M46,""))</f>
+        <v/>
+      </c>
+      <c r="R46" s="28">
+        <f>IF(COUNT(B46:K46)&gt;1,_xlfn.STDEV.S(B46:K46),IF(ISNUMBER(N46),N46,""))</f>
+        <v/>
+      </c>
+      <c r="S46" s="13">
+        <f>IF(AND(ISNUMBER(P46),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P46&gt;$D$23,"above UCL",IF(P46&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T46" s="13">
+        <f>IF(AND(ISNUMBER(Q46),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q46&gt;$D$24,"above UCL",IF(Q46&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U46" s="13">
+        <f>IF(AND(ISNUMBER(P46),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P46&gt;$D$25,"above UCL",IF(P46&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V46" s="13">
+        <f>IF(AND(ISNUMBER(R46),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R46&gt;$D$26,"above UCL",IF(R46&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>18</v>
+      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+      <c r="L47" s="7" t="n"/>
+      <c r="M47" s="7" t="n"/>
+      <c r="N47" s="7" t="n"/>
+      <c r="O47" s="24">
+        <f>IF(COUNT(B47:K47)&gt;0,COUNT(B47:K47),IF(OR(ISNUMBER(L47),ISNUMBER(M47)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P47" s="28">
+        <f>IF(COUNT(B47:K47)&gt;0,AVERAGE(B47:K47),IF(ISNUMBER(L47),L47,""))</f>
+        <v/>
+      </c>
+      <c r="Q47" s="28">
+        <f>IF(COUNT(B47:K47)&gt;1,MAX(B47:K47)-MIN(B47:K47),IF(ISNUMBER(M47),M47,""))</f>
+        <v/>
+      </c>
+      <c r="R47" s="28">
+        <f>IF(COUNT(B47:K47)&gt;1,_xlfn.STDEV.S(B47:K47),IF(ISNUMBER(N47),N47,""))</f>
+        <v/>
+      </c>
+      <c r="S47" s="13">
+        <f>IF(AND(ISNUMBER(P47),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P47&gt;$D$23,"above UCL",IF(P47&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T47" s="13">
+        <f>IF(AND(ISNUMBER(Q47),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q47&gt;$D$24,"above UCL",IF(Q47&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U47" s="13">
+        <f>IF(AND(ISNUMBER(P47),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P47&gt;$D$25,"above UCL",IF(P47&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V47" s="13">
+        <f>IF(AND(ISNUMBER(R47),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R47&gt;$D$26,"above UCL",IF(R47&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>19</v>
+      </c>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n"/>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+      <c r="L48" s="7" t="n"/>
+      <c r="M48" s="7" t="n"/>
+      <c r="N48" s="7" t="n"/>
+      <c r="O48" s="24">
+        <f>IF(COUNT(B48:K48)&gt;0,COUNT(B48:K48),IF(OR(ISNUMBER(L48),ISNUMBER(M48)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P48" s="28">
+        <f>IF(COUNT(B48:K48)&gt;0,AVERAGE(B48:K48),IF(ISNUMBER(L48),L48,""))</f>
+        <v/>
+      </c>
+      <c r="Q48" s="28">
+        <f>IF(COUNT(B48:K48)&gt;1,MAX(B48:K48)-MIN(B48:K48),IF(ISNUMBER(M48),M48,""))</f>
+        <v/>
+      </c>
+      <c r="R48" s="28">
+        <f>IF(COUNT(B48:K48)&gt;1,_xlfn.STDEV.S(B48:K48),IF(ISNUMBER(N48),N48,""))</f>
+        <v/>
+      </c>
+      <c r="S48" s="13">
+        <f>IF(AND(ISNUMBER(P48),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P48&gt;$D$23,"above UCL",IF(P48&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T48" s="13">
+        <f>IF(AND(ISNUMBER(Q48),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q48&gt;$D$24,"above UCL",IF(Q48&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U48" s="13">
+        <f>IF(AND(ISNUMBER(P48),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P48&gt;$D$25,"above UCL",IF(P48&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V48" s="13">
+        <f>IF(AND(ISNUMBER(R48),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R48&gt;$D$26,"above UCL",IF(R48&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>20</v>
+      </c>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
+      <c r="K49" s="7" t="n"/>
+      <c r="L49" s="7" t="n"/>
+      <c r="M49" s="7" t="n"/>
+      <c r="N49" s="7" t="n"/>
+      <c r="O49" s="24">
+        <f>IF(COUNT(B49:K49)&gt;0,COUNT(B49:K49),IF(OR(ISNUMBER(L49),ISNUMBER(M49)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P49" s="28">
+        <f>IF(COUNT(B49:K49)&gt;0,AVERAGE(B49:K49),IF(ISNUMBER(L49),L49,""))</f>
+        <v/>
+      </c>
+      <c r="Q49" s="28">
+        <f>IF(COUNT(B49:K49)&gt;1,MAX(B49:K49)-MIN(B49:K49),IF(ISNUMBER(M49),M49,""))</f>
+        <v/>
+      </c>
+      <c r="R49" s="28">
+        <f>IF(COUNT(B49:K49)&gt;1,_xlfn.STDEV.S(B49:K49),IF(ISNUMBER(N49),N49,""))</f>
+        <v/>
+      </c>
+      <c r="S49" s="13">
+        <f>IF(AND(ISNUMBER(P49),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P49&gt;$D$23,"above UCL",IF(P49&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T49" s="13">
+        <f>IF(AND(ISNUMBER(Q49),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q49&gt;$D$24,"above UCL",IF(Q49&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U49" s="13">
+        <f>IF(AND(ISNUMBER(P49),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P49&gt;$D$25,"above UCL",IF(P49&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V49" s="13">
+        <f>IF(AND(ISNUMBER(R49),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R49&gt;$D$26,"above UCL",IF(R49&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>21</v>
+      </c>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n"/>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="7" t="n"/>
+      <c r="L50" s="7" t="n"/>
+      <c r="M50" s="7" t="n"/>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="24">
+        <f>IF(COUNT(B50:K50)&gt;0,COUNT(B50:K50),IF(OR(ISNUMBER(L50),ISNUMBER(M50)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P50" s="28">
+        <f>IF(COUNT(B50:K50)&gt;0,AVERAGE(B50:K50),IF(ISNUMBER(L50),L50,""))</f>
+        <v/>
+      </c>
+      <c r="Q50" s="28">
+        <f>IF(COUNT(B50:K50)&gt;1,MAX(B50:K50)-MIN(B50:K50),IF(ISNUMBER(M50),M50,""))</f>
+        <v/>
+      </c>
+      <c r="R50" s="28">
+        <f>IF(COUNT(B50:K50)&gt;1,_xlfn.STDEV.S(B50:K50),IF(ISNUMBER(N50),N50,""))</f>
+        <v/>
+      </c>
+      <c r="S50" s="13">
+        <f>IF(AND(ISNUMBER(P50),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P50&gt;$D$23,"above UCL",IF(P50&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T50" s="13">
+        <f>IF(AND(ISNUMBER(Q50),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q50&gt;$D$24,"above UCL",IF(Q50&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U50" s="13">
+        <f>IF(AND(ISNUMBER(P50),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P50&gt;$D$25,"above UCL",IF(P50&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V50" s="13">
+        <f>IF(AND(ISNUMBER(R50),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R50&gt;$D$26,"above UCL",IF(R50&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>22</v>
+      </c>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+      <c r="I51" s="7" t="n"/>
+      <c r="J51" s="7" t="n"/>
+      <c r="K51" s="7" t="n"/>
+      <c r="L51" s="7" t="n"/>
+      <c r="M51" s="7" t="n"/>
+      <c r="N51" s="7" t="n"/>
+      <c r="O51" s="24">
+        <f>IF(COUNT(B51:K51)&gt;0,COUNT(B51:K51),IF(OR(ISNUMBER(L51),ISNUMBER(M51)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P51" s="28">
+        <f>IF(COUNT(B51:K51)&gt;0,AVERAGE(B51:K51),IF(ISNUMBER(L51),L51,""))</f>
+        <v/>
+      </c>
+      <c r="Q51" s="28">
+        <f>IF(COUNT(B51:K51)&gt;1,MAX(B51:K51)-MIN(B51:K51),IF(ISNUMBER(M51),M51,""))</f>
+        <v/>
+      </c>
+      <c r="R51" s="28">
+        <f>IF(COUNT(B51:K51)&gt;1,_xlfn.STDEV.S(B51:K51),IF(ISNUMBER(N51),N51,""))</f>
+        <v/>
+      </c>
+      <c r="S51" s="13">
+        <f>IF(AND(ISNUMBER(P51),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P51&gt;$D$23,"above UCL",IF(P51&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T51" s="13">
+        <f>IF(AND(ISNUMBER(Q51),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q51&gt;$D$24,"above UCL",IF(Q51&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U51" s="13">
+        <f>IF(AND(ISNUMBER(P51),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P51&gt;$D$25,"above UCL",IF(P51&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V51" s="13">
+        <f>IF(AND(ISNUMBER(R51),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R51&gt;$D$26,"above UCL",IF(R51&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>23</v>
+      </c>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+      <c r="L52" s="7" t="n"/>
+      <c r="M52" s="7" t="n"/>
+      <c r="N52" s="7" t="n"/>
+      <c r="O52" s="24">
+        <f>IF(COUNT(B52:K52)&gt;0,COUNT(B52:K52),IF(OR(ISNUMBER(L52),ISNUMBER(M52)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P52" s="28">
+        <f>IF(COUNT(B52:K52)&gt;0,AVERAGE(B52:K52),IF(ISNUMBER(L52),L52,""))</f>
+        <v/>
+      </c>
+      <c r="Q52" s="28">
+        <f>IF(COUNT(B52:K52)&gt;1,MAX(B52:K52)-MIN(B52:K52),IF(ISNUMBER(M52),M52,""))</f>
+        <v/>
+      </c>
+      <c r="R52" s="28">
+        <f>IF(COUNT(B52:K52)&gt;1,_xlfn.STDEV.S(B52:K52),IF(ISNUMBER(N52),N52,""))</f>
+        <v/>
+      </c>
+      <c r="S52" s="13">
+        <f>IF(AND(ISNUMBER(P52),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P52&gt;$D$23,"above UCL",IF(P52&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T52" s="13">
+        <f>IF(AND(ISNUMBER(Q52),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q52&gt;$D$24,"above UCL",IF(Q52&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U52" s="13">
+        <f>IF(AND(ISNUMBER(P52),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P52&gt;$D$25,"above UCL",IF(P52&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V52" s="13">
+        <f>IF(AND(ISNUMBER(R52),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R52&gt;$D$26,"above UCL",IF(R52&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>24</v>
+      </c>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
+      <c r="I53" s="7" t="n"/>
+      <c r="J53" s="7" t="n"/>
+      <c r="K53" s="7" t="n"/>
+      <c r="L53" s="7" t="n"/>
+      <c r="M53" s="7" t="n"/>
+      <c r="N53" s="7" t="n"/>
+      <c r="O53" s="24">
+        <f>IF(COUNT(B53:K53)&gt;0,COUNT(B53:K53),IF(OR(ISNUMBER(L53),ISNUMBER(M53)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P53" s="28">
+        <f>IF(COUNT(B53:K53)&gt;0,AVERAGE(B53:K53),IF(ISNUMBER(L53),L53,""))</f>
+        <v/>
+      </c>
+      <c r="Q53" s="28">
+        <f>IF(COUNT(B53:K53)&gt;1,MAX(B53:K53)-MIN(B53:K53),IF(ISNUMBER(M53),M53,""))</f>
+        <v/>
+      </c>
+      <c r="R53" s="28">
+        <f>IF(COUNT(B53:K53)&gt;1,_xlfn.STDEV.S(B53:K53),IF(ISNUMBER(N53),N53,""))</f>
+        <v/>
+      </c>
+      <c r="S53" s="13">
+        <f>IF(AND(ISNUMBER(P53),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P53&gt;$D$23,"above UCL",IF(P53&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T53" s="13">
+        <f>IF(AND(ISNUMBER(Q53),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q53&gt;$D$24,"above UCL",IF(Q53&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U53" s="13">
+        <f>IF(AND(ISNUMBER(P53),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P53&gt;$D$25,"above UCL",IF(P53&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V53" s="13">
+        <f>IF(AND(ISNUMBER(R53),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R53&gt;$D$26,"above UCL",IF(R53&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>25</v>
+      </c>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
+      <c r="K54" s="7" t="n"/>
+      <c r="L54" s="7" t="n"/>
+      <c r="M54" s="7" t="n"/>
+      <c r="N54" s="7" t="n"/>
+      <c r="O54" s="24">
+        <f>IF(COUNT(B54:K54)&gt;0,COUNT(B54:K54),IF(OR(ISNUMBER(L54),ISNUMBER(M54)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P54" s="28">
+        <f>IF(COUNT(B54:K54)&gt;0,AVERAGE(B54:K54),IF(ISNUMBER(L54),L54,""))</f>
+        <v/>
+      </c>
+      <c r="Q54" s="28">
+        <f>IF(COUNT(B54:K54)&gt;1,MAX(B54:K54)-MIN(B54:K54),IF(ISNUMBER(M54),M54,""))</f>
+        <v/>
+      </c>
+      <c r="R54" s="28">
+        <f>IF(COUNT(B54:K54)&gt;1,_xlfn.STDEV.S(B54:K54),IF(ISNUMBER(N54),N54,""))</f>
+        <v/>
+      </c>
+      <c r="S54" s="13">
+        <f>IF(AND(ISNUMBER(P54),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P54&gt;$D$23,"above UCL",IF(P54&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T54" s="13">
+        <f>IF(AND(ISNUMBER(Q54),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q54&gt;$D$24,"above UCL",IF(Q54&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U54" s="13">
+        <f>IF(AND(ISNUMBER(P54),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P54&gt;$D$25,"above UCL",IF(P54&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V54" s="13">
+        <f>IF(AND(ISNUMBER(R54),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R54&gt;$D$26,"above UCL",IF(R54&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>26</v>
+      </c>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="n"/>
+      <c r="I55" s="7" t="n"/>
+      <c r="J55" s="7" t="n"/>
+      <c r="K55" s="7" t="n"/>
+      <c r="L55" s="7" t="n"/>
+      <c r="M55" s="7" t="n"/>
+      <c r="N55" s="7" t="n"/>
+      <c r="O55" s="24">
+        <f>IF(COUNT(B55:K55)&gt;0,COUNT(B55:K55),IF(OR(ISNUMBER(L55),ISNUMBER(M55)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P55" s="28">
+        <f>IF(COUNT(B55:K55)&gt;0,AVERAGE(B55:K55),IF(ISNUMBER(L55),L55,""))</f>
+        <v/>
+      </c>
+      <c r="Q55" s="28">
+        <f>IF(COUNT(B55:K55)&gt;1,MAX(B55:K55)-MIN(B55:K55),IF(ISNUMBER(M55),M55,""))</f>
+        <v/>
+      </c>
+      <c r="R55" s="28">
+        <f>IF(COUNT(B55:K55)&gt;1,_xlfn.STDEV.S(B55:K55),IF(ISNUMBER(N55),N55,""))</f>
+        <v/>
+      </c>
+      <c r="S55" s="13">
+        <f>IF(AND(ISNUMBER(P55),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P55&gt;$D$23,"above UCL",IF(P55&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T55" s="13">
+        <f>IF(AND(ISNUMBER(Q55),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q55&gt;$D$24,"above UCL",IF(Q55&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U55" s="13">
+        <f>IF(AND(ISNUMBER(P55),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P55&gt;$D$25,"above UCL",IF(P55&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V55" s="13">
+        <f>IF(AND(ISNUMBER(R55),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R55&gt;$D$26,"above UCL",IF(R55&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>27</v>
+      </c>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
+      <c r="K56" s="7" t="n"/>
+      <c r="L56" s="7" t="n"/>
+      <c r="M56" s="7" t="n"/>
+      <c r="N56" s="7" t="n"/>
+      <c r="O56" s="24">
+        <f>IF(COUNT(B56:K56)&gt;0,COUNT(B56:K56),IF(OR(ISNUMBER(L56),ISNUMBER(M56)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P56" s="28">
+        <f>IF(COUNT(B56:K56)&gt;0,AVERAGE(B56:K56),IF(ISNUMBER(L56),L56,""))</f>
+        <v/>
+      </c>
+      <c r="Q56" s="28">
+        <f>IF(COUNT(B56:K56)&gt;1,MAX(B56:K56)-MIN(B56:K56),IF(ISNUMBER(M56),M56,""))</f>
+        <v/>
+      </c>
+      <c r="R56" s="28">
+        <f>IF(COUNT(B56:K56)&gt;1,_xlfn.STDEV.S(B56:K56),IF(ISNUMBER(N56),N56,""))</f>
+        <v/>
+      </c>
+      <c r="S56" s="13">
+        <f>IF(AND(ISNUMBER(P56),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P56&gt;$D$23,"above UCL",IF(P56&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T56" s="13">
+        <f>IF(AND(ISNUMBER(Q56),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q56&gt;$D$24,"above UCL",IF(Q56&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U56" s="13">
+        <f>IF(AND(ISNUMBER(P56),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P56&gt;$D$25,"above UCL",IF(P56&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V56" s="13">
+        <f>IF(AND(ISNUMBER(R56),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R56&gt;$D$26,"above UCL",IF(R56&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>28</v>
+      </c>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="n"/>
+      <c r="I57" s="7" t="n"/>
+      <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="n"/>
+      <c r="L57" s="7" t="n"/>
+      <c r="M57" s="7" t="n"/>
+      <c r="N57" s="7" t="n"/>
+      <c r="O57" s="24">
+        <f>IF(COUNT(B57:K57)&gt;0,COUNT(B57:K57),IF(OR(ISNUMBER(L57),ISNUMBER(M57)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P57" s="28">
+        <f>IF(COUNT(B57:K57)&gt;0,AVERAGE(B57:K57),IF(ISNUMBER(L57),L57,""))</f>
+        <v/>
+      </c>
+      <c r="Q57" s="28">
+        <f>IF(COUNT(B57:K57)&gt;1,MAX(B57:K57)-MIN(B57:K57),IF(ISNUMBER(M57),M57,""))</f>
+        <v/>
+      </c>
+      <c r="R57" s="28">
+        <f>IF(COUNT(B57:K57)&gt;1,_xlfn.STDEV.S(B57:K57),IF(ISNUMBER(N57),N57,""))</f>
+        <v/>
+      </c>
+      <c r="S57" s="13">
+        <f>IF(AND(ISNUMBER(P57),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P57&gt;$D$23,"above UCL",IF(P57&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T57" s="13">
+        <f>IF(AND(ISNUMBER(Q57),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q57&gt;$D$24,"above UCL",IF(Q57&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U57" s="13">
+        <f>IF(AND(ISNUMBER(P57),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P57&gt;$D$25,"above UCL",IF(P57&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V57" s="13">
+        <f>IF(AND(ISNUMBER(R57),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R57&gt;$D$26,"above UCL",IF(R57&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>29</v>
+      </c>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
+      <c r="K58" s="7" t="n"/>
+      <c r="L58" s="7" t="n"/>
+      <c r="M58" s="7" t="n"/>
+      <c r="N58" s="7" t="n"/>
+      <c r="O58" s="24">
+        <f>IF(COUNT(B58:K58)&gt;0,COUNT(B58:K58),IF(OR(ISNUMBER(L58),ISNUMBER(M58)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P58" s="28">
+        <f>IF(COUNT(B58:K58)&gt;0,AVERAGE(B58:K58),IF(ISNUMBER(L58),L58,""))</f>
+        <v/>
+      </c>
+      <c r="Q58" s="28">
+        <f>IF(COUNT(B58:K58)&gt;1,MAX(B58:K58)-MIN(B58:K58),IF(ISNUMBER(M58),M58,""))</f>
+        <v/>
+      </c>
+      <c r="R58" s="28">
+        <f>IF(COUNT(B58:K58)&gt;1,_xlfn.STDEV.S(B58:K58),IF(ISNUMBER(N58),N58,""))</f>
+        <v/>
+      </c>
+      <c r="S58" s="13">
+        <f>IF(AND(ISNUMBER(P58),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P58&gt;$D$23,"above UCL",IF(P58&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T58" s="13">
+        <f>IF(AND(ISNUMBER(Q58),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q58&gt;$D$24,"above UCL",IF(Q58&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U58" s="13">
+        <f>IF(AND(ISNUMBER(P58),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P58&gt;$D$25,"above UCL",IF(P58&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V58" s="13">
+        <f>IF(AND(ISNUMBER(R58),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R58&gt;$D$26,"above UCL",IF(R58&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>30</v>
+      </c>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+      <c r="I59" s="7" t="n"/>
+      <c r="J59" s="7" t="n"/>
+      <c r="K59" s="7" t="n"/>
+      <c r="L59" s="7" t="n"/>
+      <c r="M59" s="7" t="n"/>
+      <c r="N59" s="7" t="n"/>
+      <c r="O59" s="24">
+        <f>IF(COUNT(B59:K59)&gt;0,COUNT(B59:K59),IF(OR(ISNUMBER(L59),ISNUMBER(M59)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P59" s="28">
+        <f>IF(COUNT(B59:K59)&gt;0,AVERAGE(B59:K59),IF(ISNUMBER(L59),L59,""))</f>
+        <v/>
+      </c>
+      <c r="Q59" s="28">
+        <f>IF(COUNT(B59:K59)&gt;1,MAX(B59:K59)-MIN(B59:K59),IF(ISNUMBER(M59),M59,""))</f>
+        <v/>
+      </c>
+      <c r="R59" s="28">
+        <f>IF(COUNT(B59:K59)&gt;1,_xlfn.STDEV.S(B59:K59),IF(ISNUMBER(N59),N59,""))</f>
+        <v/>
+      </c>
+      <c r="S59" s="13">
+        <f>IF(AND(ISNUMBER(P59),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P59&gt;$D$23,"above UCL",IF(P59&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T59" s="13">
+        <f>IF(AND(ISNUMBER(Q59),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q59&gt;$D$24,"above UCL",IF(Q59&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U59" s="13">
+        <f>IF(AND(ISNUMBER(P59),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P59&gt;$D$25,"above UCL",IF(P59&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V59" s="13">
+        <f>IF(AND(ISNUMBER(R59),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R59&gt;$D$26,"above UCL",IF(R59&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>31</v>
+      </c>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+      <c r="L60" s="7" t="n"/>
+      <c r="M60" s="7" t="n"/>
+      <c r="N60" s="7" t="n"/>
+      <c r="O60" s="24">
+        <f>IF(COUNT(B60:K60)&gt;0,COUNT(B60:K60),IF(OR(ISNUMBER(L60),ISNUMBER(M60)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P60" s="28">
+        <f>IF(COUNT(B60:K60)&gt;0,AVERAGE(B60:K60),IF(ISNUMBER(L60),L60,""))</f>
+        <v/>
+      </c>
+      <c r="Q60" s="28">
+        <f>IF(COUNT(B60:K60)&gt;1,MAX(B60:K60)-MIN(B60:K60),IF(ISNUMBER(M60),M60,""))</f>
+        <v/>
+      </c>
+      <c r="R60" s="28">
+        <f>IF(COUNT(B60:K60)&gt;1,_xlfn.STDEV.S(B60:K60),IF(ISNUMBER(N60),N60,""))</f>
+        <v/>
+      </c>
+      <c r="S60" s="13">
+        <f>IF(AND(ISNUMBER(P60),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P60&gt;$D$23,"above UCL",IF(P60&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T60" s="13">
+        <f>IF(AND(ISNUMBER(Q60),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q60&gt;$D$24,"above UCL",IF(Q60&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U60" s="13">
+        <f>IF(AND(ISNUMBER(P60),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P60&gt;$D$25,"above UCL",IF(P60&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V60" s="13">
+        <f>IF(AND(ISNUMBER(R60),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R60&gt;$D$26,"above UCL",IF(R60&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>32</v>
+      </c>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="n"/>
+      <c r="I61" s="7" t="n"/>
+      <c r="J61" s="7" t="n"/>
+      <c r="K61" s="7" t="n"/>
+      <c r="L61" s="7" t="n"/>
+      <c r="M61" s="7" t="n"/>
+      <c r="N61" s="7" t="n"/>
+      <c r="O61" s="24">
+        <f>IF(COUNT(B61:K61)&gt;0,COUNT(B61:K61),IF(OR(ISNUMBER(L61),ISNUMBER(M61)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P61" s="28">
+        <f>IF(COUNT(B61:K61)&gt;0,AVERAGE(B61:K61),IF(ISNUMBER(L61),L61,""))</f>
+        <v/>
+      </c>
+      <c r="Q61" s="28">
+        <f>IF(COUNT(B61:K61)&gt;1,MAX(B61:K61)-MIN(B61:K61),IF(ISNUMBER(M61),M61,""))</f>
+        <v/>
+      </c>
+      <c r="R61" s="28">
+        <f>IF(COUNT(B61:K61)&gt;1,_xlfn.STDEV.S(B61:K61),IF(ISNUMBER(N61),N61,""))</f>
+        <v/>
+      </c>
+      <c r="S61" s="13">
+        <f>IF(AND(ISNUMBER(P61),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P61&gt;$D$23,"above UCL",IF(P61&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T61" s="13">
+        <f>IF(AND(ISNUMBER(Q61),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q61&gt;$D$24,"above UCL",IF(Q61&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U61" s="13">
+        <f>IF(AND(ISNUMBER(P61),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P61&gt;$D$25,"above UCL",IF(P61&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V61" s="13">
+        <f>IF(AND(ISNUMBER(R61),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R61&gt;$D$26,"above UCL",IF(R61&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>33</v>
+      </c>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="7" t="n"/>
+      <c r="L62" s="7" t="n"/>
+      <c r="M62" s="7" t="n"/>
+      <c r="N62" s="7" t="n"/>
+      <c r="O62" s="24">
+        <f>IF(COUNT(B62:K62)&gt;0,COUNT(B62:K62),IF(OR(ISNUMBER(L62),ISNUMBER(M62)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P62" s="28">
+        <f>IF(COUNT(B62:K62)&gt;0,AVERAGE(B62:K62),IF(ISNUMBER(L62),L62,""))</f>
+        <v/>
+      </c>
+      <c r="Q62" s="28">
+        <f>IF(COUNT(B62:K62)&gt;1,MAX(B62:K62)-MIN(B62:K62),IF(ISNUMBER(M62),M62,""))</f>
+        <v/>
+      </c>
+      <c r="R62" s="28">
+        <f>IF(COUNT(B62:K62)&gt;1,_xlfn.STDEV.S(B62:K62),IF(ISNUMBER(N62),N62,""))</f>
+        <v/>
+      </c>
+      <c r="S62" s="13">
+        <f>IF(AND(ISNUMBER(P62),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P62&gt;$D$23,"above UCL",IF(P62&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T62" s="13">
+        <f>IF(AND(ISNUMBER(Q62),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q62&gt;$D$24,"above UCL",IF(Q62&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U62" s="13">
+        <f>IF(AND(ISNUMBER(P62),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P62&gt;$D$25,"above UCL",IF(P62&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V62" s="13">
+        <f>IF(AND(ISNUMBER(R62),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R62&gt;$D$26,"above UCL",IF(R62&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>34</v>
+      </c>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
+      <c r="N63" s="7" t="n"/>
+      <c r="O63" s="24">
+        <f>IF(COUNT(B63:K63)&gt;0,COUNT(B63:K63),IF(OR(ISNUMBER(L63),ISNUMBER(M63)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P63" s="28">
+        <f>IF(COUNT(B63:K63)&gt;0,AVERAGE(B63:K63),IF(ISNUMBER(L63),L63,""))</f>
+        <v/>
+      </c>
+      <c r="Q63" s="28">
+        <f>IF(COUNT(B63:K63)&gt;1,MAX(B63:K63)-MIN(B63:K63),IF(ISNUMBER(M63),M63,""))</f>
+        <v/>
+      </c>
+      <c r="R63" s="28">
+        <f>IF(COUNT(B63:K63)&gt;1,_xlfn.STDEV.S(B63:K63),IF(ISNUMBER(N63),N63,""))</f>
+        <v/>
+      </c>
+      <c r="S63" s="13">
+        <f>IF(AND(ISNUMBER(P63),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P63&gt;$D$23,"above UCL",IF(P63&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T63" s="13">
+        <f>IF(AND(ISNUMBER(Q63),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q63&gt;$D$24,"above UCL",IF(Q63&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U63" s="13">
+        <f>IF(AND(ISNUMBER(P63),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P63&gt;$D$25,"above UCL",IF(P63&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V63" s="13">
+        <f>IF(AND(ISNUMBER(R63),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R63&gt;$D$26,"above UCL",IF(R63&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>35</v>
+      </c>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="7" t="n"/>
+      <c r="M64" s="7" t="n"/>
+      <c r="N64" s="7" t="n"/>
+      <c r="O64" s="24">
+        <f>IF(COUNT(B64:K64)&gt;0,COUNT(B64:K64),IF(OR(ISNUMBER(L64),ISNUMBER(M64)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P64" s="28">
+        <f>IF(COUNT(B64:K64)&gt;0,AVERAGE(B64:K64),IF(ISNUMBER(L64),L64,""))</f>
+        <v/>
+      </c>
+      <c r="Q64" s="28">
+        <f>IF(COUNT(B64:K64)&gt;1,MAX(B64:K64)-MIN(B64:K64),IF(ISNUMBER(M64),M64,""))</f>
+        <v/>
+      </c>
+      <c r="R64" s="28">
+        <f>IF(COUNT(B64:K64)&gt;1,_xlfn.STDEV.S(B64:K64),IF(ISNUMBER(N64),N64,""))</f>
+        <v/>
+      </c>
+      <c r="S64" s="13">
+        <f>IF(AND(ISNUMBER(P64),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P64&gt;$D$23,"above UCL",IF(P64&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T64" s="13">
+        <f>IF(AND(ISNUMBER(Q64),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q64&gt;$D$24,"above UCL",IF(Q64&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U64" s="13">
+        <f>IF(AND(ISNUMBER(P64),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P64&gt;$D$25,"above UCL",IF(P64&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V64" s="13">
+        <f>IF(AND(ISNUMBER(R64),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R64&gt;$D$26,"above UCL",IF(R64&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>36</v>
+      </c>
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+      <c r="J65" s="7" t="n"/>
+      <c r="K65" s="7" t="n"/>
+      <c r="L65" s="7" t="n"/>
+      <c r="M65" s="7" t="n"/>
+      <c r="N65" s="7" t="n"/>
+      <c r="O65" s="24">
+        <f>IF(COUNT(B65:K65)&gt;0,COUNT(B65:K65),IF(OR(ISNUMBER(L65),ISNUMBER(M65)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P65" s="28">
+        <f>IF(COUNT(B65:K65)&gt;0,AVERAGE(B65:K65),IF(ISNUMBER(L65),L65,""))</f>
+        <v/>
+      </c>
+      <c r="Q65" s="28">
+        <f>IF(COUNT(B65:K65)&gt;1,MAX(B65:K65)-MIN(B65:K65),IF(ISNUMBER(M65),M65,""))</f>
+        <v/>
+      </c>
+      <c r="R65" s="28">
+        <f>IF(COUNT(B65:K65)&gt;1,_xlfn.STDEV.S(B65:K65),IF(ISNUMBER(N65),N65,""))</f>
+        <v/>
+      </c>
+      <c r="S65" s="13">
+        <f>IF(AND(ISNUMBER(P65),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P65&gt;$D$23,"above UCL",IF(P65&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T65" s="13">
+        <f>IF(AND(ISNUMBER(Q65),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q65&gt;$D$24,"above UCL",IF(Q65&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U65" s="13">
+        <f>IF(AND(ISNUMBER(P65),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P65&gt;$D$25,"above UCL",IF(P65&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V65" s="13">
+        <f>IF(AND(ISNUMBER(R65),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R65&gt;$D$26,"above UCL",IF(R65&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>37</v>
+      </c>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
+      <c r="L66" s="7" t="n"/>
+      <c r="M66" s="7" t="n"/>
+      <c r="N66" s="7" t="n"/>
+      <c r="O66" s="24">
+        <f>IF(COUNT(B66:K66)&gt;0,COUNT(B66:K66),IF(OR(ISNUMBER(L66),ISNUMBER(M66)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P66" s="28">
+        <f>IF(COUNT(B66:K66)&gt;0,AVERAGE(B66:K66),IF(ISNUMBER(L66),L66,""))</f>
+        <v/>
+      </c>
+      <c r="Q66" s="28">
+        <f>IF(COUNT(B66:K66)&gt;1,MAX(B66:K66)-MIN(B66:K66),IF(ISNUMBER(M66),M66,""))</f>
+        <v/>
+      </c>
+      <c r="R66" s="28">
+        <f>IF(COUNT(B66:K66)&gt;1,_xlfn.STDEV.S(B66:K66),IF(ISNUMBER(N66),N66,""))</f>
+        <v/>
+      </c>
+      <c r="S66" s="13">
+        <f>IF(AND(ISNUMBER(P66),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P66&gt;$D$23,"above UCL",IF(P66&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T66" s="13">
+        <f>IF(AND(ISNUMBER(Q66),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q66&gt;$D$24,"above UCL",IF(Q66&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U66" s="13">
+        <f>IF(AND(ISNUMBER(P66),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P66&gt;$D$25,"above UCL",IF(P66&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V66" s="13">
+        <f>IF(AND(ISNUMBER(R66),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R66&gt;$D$26,"above UCL",IF(R66&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>38</v>
+      </c>
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="7" t="n"/>
+      <c r="I67" s="7" t="n"/>
+      <c r="J67" s="7" t="n"/>
+      <c r="K67" s="7" t="n"/>
+      <c r="L67" s="7" t="n"/>
+      <c r="M67" s="7" t="n"/>
+      <c r="N67" s="7" t="n"/>
+      <c r="O67" s="24">
+        <f>IF(COUNT(B67:K67)&gt;0,COUNT(B67:K67),IF(OR(ISNUMBER(L67),ISNUMBER(M67)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P67" s="28">
+        <f>IF(COUNT(B67:K67)&gt;0,AVERAGE(B67:K67),IF(ISNUMBER(L67),L67,""))</f>
+        <v/>
+      </c>
+      <c r="Q67" s="28">
+        <f>IF(COUNT(B67:K67)&gt;1,MAX(B67:K67)-MIN(B67:K67),IF(ISNUMBER(M67),M67,""))</f>
+        <v/>
+      </c>
+      <c r="R67" s="28">
+        <f>IF(COUNT(B67:K67)&gt;1,_xlfn.STDEV.S(B67:K67),IF(ISNUMBER(N67),N67,""))</f>
+        <v/>
+      </c>
+      <c r="S67" s="13">
+        <f>IF(AND(ISNUMBER(P67),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P67&gt;$D$23,"above UCL",IF(P67&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T67" s="13">
+        <f>IF(AND(ISNUMBER(Q67),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q67&gt;$D$24,"above UCL",IF(Q67&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U67" s="13">
+        <f>IF(AND(ISNUMBER(P67),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P67&gt;$D$25,"above UCL",IF(P67&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V67" s="13">
+        <f>IF(AND(ISNUMBER(R67),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R67&gt;$D$26,"above UCL",IF(R67&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>39</v>
+      </c>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
+      <c r="J68" s="7" t="n"/>
+      <c r="K68" s="7" t="n"/>
+      <c r="L68" s="7" t="n"/>
+      <c r="M68" s="7" t="n"/>
+      <c r="N68" s="7" t="n"/>
+      <c r="O68" s="24">
+        <f>IF(COUNT(B68:K68)&gt;0,COUNT(B68:K68),IF(OR(ISNUMBER(L68),ISNUMBER(M68)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P68" s="28">
+        <f>IF(COUNT(B68:K68)&gt;0,AVERAGE(B68:K68),IF(ISNUMBER(L68),L68,""))</f>
+        <v/>
+      </c>
+      <c r="Q68" s="28">
+        <f>IF(COUNT(B68:K68)&gt;1,MAX(B68:K68)-MIN(B68:K68),IF(ISNUMBER(M68),M68,""))</f>
+        <v/>
+      </c>
+      <c r="R68" s="28">
+        <f>IF(COUNT(B68:K68)&gt;1,_xlfn.STDEV.S(B68:K68),IF(ISNUMBER(N68),N68,""))</f>
+        <v/>
+      </c>
+      <c r="S68" s="13">
+        <f>IF(AND(ISNUMBER(P68),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P68&gt;$D$23,"above UCL",IF(P68&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T68" s="13">
+        <f>IF(AND(ISNUMBER(Q68),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q68&gt;$D$24,"above UCL",IF(Q68&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U68" s="13">
+        <f>IF(AND(ISNUMBER(P68),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P68&gt;$D$25,"above UCL",IF(P68&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V68" s="13">
+        <f>IF(AND(ISNUMBER(R68),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R68&gt;$D$26,"above UCL",IF(R68&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>40</v>
+      </c>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+      <c r="J69" s="7" t="n"/>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
+      <c r="N69" s="7" t="n"/>
+      <c r="O69" s="24">
+        <f>IF(COUNT(B69:K69)&gt;0,COUNT(B69:K69),IF(OR(ISNUMBER(L69),ISNUMBER(M69)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P69" s="28">
+        <f>IF(COUNT(B69:K69)&gt;0,AVERAGE(B69:K69),IF(ISNUMBER(L69),L69,""))</f>
+        <v/>
+      </c>
+      <c r="Q69" s="28">
+        <f>IF(COUNT(B69:K69)&gt;1,MAX(B69:K69)-MIN(B69:K69),IF(ISNUMBER(M69),M69,""))</f>
+        <v/>
+      </c>
+      <c r="R69" s="28">
+        <f>IF(COUNT(B69:K69)&gt;1,_xlfn.STDEV.S(B69:K69),IF(ISNUMBER(N69),N69,""))</f>
+        <v/>
+      </c>
+      <c r="S69" s="13">
+        <f>IF(AND(ISNUMBER(P69),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P69&gt;$D$23,"above UCL",IF(P69&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T69" s="13">
+        <f>IF(AND(ISNUMBER(Q69),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q69&gt;$D$24,"above UCL",IF(Q69&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U69" s="13">
+        <f>IF(AND(ISNUMBER(P69),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P69&gt;$D$25,"above UCL",IF(P69&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V69" s="13">
+        <f>IF(AND(ISNUMBER(R69),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R69&gt;$D$26,"above UCL",IF(R69&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>41</v>
+      </c>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7" t="n"/>
+      <c r="I70" s="7" t="n"/>
+      <c r="J70" s="7" t="n"/>
+      <c r="K70" s="7" t="n"/>
+      <c r="L70" s="7" t="n"/>
+      <c r="M70" s="7" t="n"/>
+      <c r="N70" s="7" t="n"/>
+      <c r="O70" s="24">
+        <f>IF(COUNT(B70:K70)&gt;0,COUNT(B70:K70),IF(OR(ISNUMBER(L70),ISNUMBER(M70)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P70" s="28">
+        <f>IF(COUNT(B70:K70)&gt;0,AVERAGE(B70:K70),IF(ISNUMBER(L70),L70,""))</f>
+        <v/>
+      </c>
+      <c r="Q70" s="28">
+        <f>IF(COUNT(B70:K70)&gt;1,MAX(B70:K70)-MIN(B70:K70),IF(ISNUMBER(M70),M70,""))</f>
+        <v/>
+      </c>
+      <c r="R70" s="28">
+        <f>IF(COUNT(B70:K70)&gt;1,_xlfn.STDEV.S(B70:K70),IF(ISNUMBER(N70),N70,""))</f>
+        <v/>
+      </c>
+      <c r="S70" s="13">
+        <f>IF(AND(ISNUMBER(P70),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P70&gt;$D$23,"above UCL",IF(P70&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T70" s="13">
+        <f>IF(AND(ISNUMBER(Q70),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q70&gt;$D$24,"above UCL",IF(Q70&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U70" s="13">
+        <f>IF(AND(ISNUMBER(P70),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P70&gt;$D$25,"above UCL",IF(P70&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V70" s="13">
+        <f>IF(AND(ISNUMBER(R70),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R70&gt;$D$26,"above UCL",IF(R70&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>42</v>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+      <c r="J71" s="7" t="n"/>
+      <c r="K71" s="7" t="n"/>
+      <c r="L71" s="7" t="n"/>
+      <c r="M71" s="7" t="n"/>
+      <c r="N71" s="7" t="n"/>
+      <c r="O71" s="24">
+        <f>IF(COUNT(B71:K71)&gt;0,COUNT(B71:K71),IF(OR(ISNUMBER(L71),ISNUMBER(M71)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P71" s="28">
+        <f>IF(COUNT(B71:K71)&gt;0,AVERAGE(B71:K71),IF(ISNUMBER(L71),L71,""))</f>
+        <v/>
+      </c>
+      <c r="Q71" s="28">
+        <f>IF(COUNT(B71:K71)&gt;1,MAX(B71:K71)-MIN(B71:K71),IF(ISNUMBER(M71),M71,""))</f>
+        <v/>
+      </c>
+      <c r="R71" s="28">
+        <f>IF(COUNT(B71:K71)&gt;1,_xlfn.STDEV.S(B71:K71),IF(ISNUMBER(N71),N71,""))</f>
+        <v/>
+      </c>
+      <c r="S71" s="13">
+        <f>IF(AND(ISNUMBER(P71),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P71&gt;$D$23,"above UCL",IF(P71&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T71" s="13">
+        <f>IF(AND(ISNUMBER(Q71),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q71&gt;$D$24,"above UCL",IF(Q71&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U71" s="13">
+        <f>IF(AND(ISNUMBER(P71),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P71&gt;$D$25,"above UCL",IF(P71&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V71" s="13">
+        <f>IF(AND(ISNUMBER(R71),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R71&gt;$D$26,"above UCL",IF(R71&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>43</v>
+      </c>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
+      <c r="I72" s="7" t="n"/>
+      <c r="J72" s="7" t="n"/>
+      <c r="K72" s="7" t="n"/>
+      <c r="L72" s="7" t="n"/>
+      <c r="M72" s="7" t="n"/>
+      <c r="N72" s="7" t="n"/>
+      <c r="O72" s="24">
+        <f>IF(COUNT(B72:K72)&gt;0,COUNT(B72:K72),IF(OR(ISNUMBER(L72),ISNUMBER(M72)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P72" s="28">
+        <f>IF(COUNT(B72:K72)&gt;0,AVERAGE(B72:K72),IF(ISNUMBER(L72),L72,""))</f>
+        <v/>
+      </c>
+      <c r="Q72" s="28">
+        <f>IF(COUNT(B72:K72)&gt;1,MAX(B72:K72)-MIN(B72:K72),IF(ISNUMBER(M72),M72,""))</f>
+        <v/>
+      </c>
+      <c r="R72" s="28">
+        <f>IF(COUNT(B72:K72)&gt;1,_xlfn.STDEV.S(B72:K72),IF(ISNUMBER(N72),N72,""))</f>
+        <v/>
+      </c>
+      <c r="S72" s="13">
+        <f>IF(AND(ISNUMBER(P72),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P72&gt;$D$23,"above UCL",IF(P72&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T72" s="13">
+        <f>IF(AND(ISNUMBER(Q72),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q72&gt;$D$24,"above UCL",IF(Q72&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U72" s="13">
+        <f>IF(AND(ISNUMBER(P72),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P72&gt;$D$25,"above UCL",IF(P72&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V72" s="13">
+        <f>IF(AND(ISNUMBER(R72),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R72&gt;$D$26,"above UCL",IF(R72&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>44</v>
+      </c>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
+      <c r="N73" s="7" t="n"/>
+      <c r="O73" s="24">
+        <f>IF(COUNT(B73:K73)&gt;0,COUNT(B73:K73),IF(OR(ISNUMBER(L73),ISNUMBER(M73)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P73" s="28">
+        <f>IF(COUNT(B73:K73)&gt;0,AVERAGE(B73:K73),IF(ISNUMBER(L73),L73,""))</f>
+        <v/>
+      </c>
+      <c r="Q73" s="28">
+        <f>IF(COUNT(B73:K73)&gt;1,MAX(B73:K73)-MIN(B73:K73),IF(ISNUMBER(M73),M73,""))</f>
+        <v/>
+      </c>
+      <c r="R73" s="28">
+        <f>IF(COUNT(B73:K73)&gt;1,_xlfn.STDEV.S(B73:K73),IF(ISNUMBER(N73),N73,""))</f>
+        <v/>
+      </c>
+      <c r="S73" s="13">
+        <f>IF(AND(ISNUMBER(P73),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P73&gt;$D$23,"above UCL",IF(P73&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T73" s="13">
+        <f>IF(AND(ISNUMBER(Q73),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q73&gt;$D$24,"above UCL",IF(Q73&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U73" s="13">
+        <f>IF(AND(ISNUMBER(P73),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P73&gt;$D$25,"above UCL",IF(P73&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V73" s="13">
+        <f>IF(AND(ISNUMBER(R73),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R73&gt;$D$26,"above UCL",IF(R73&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>45</v>
+      </c>
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="7" t="n"/>
+      <c r="D74" s="7" t="n"/>
+      <c r="E74" s="7" t="n"/>
+      <c r="F74" s="7" t="n"/>
+      <c r="G74" s="7" t="n"/>
+      <c r="H74" s="7" t="n"/>
+      <c r="I74" s="7" t="n"/>
+      <c r="J74" s="7" t="n"/>
+      <c r="K74" s="7" t="n"/>
+      <c r="L74" s="7" t="n"/>
+      <c r="M74" s="7" t="n"/>
+      <c r="N74" s="7" t="n"/>
+      <c r="O74" s="24">
+        <f>IF(COUNT(B74:K74)&gt;0,COUNT(B74:K74),IF(OR(ISNUMBER(L74),ISNUMBER(M74)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P74" s="28">
+        <f>IF(COUNT(B74:K74)&gt;0,AVERAGE(B74:K74),IF(ISNUMBER(L74),L74,""))</f>
+        <v/>
+      </c>
+      <c r="Q74" s="28">
+        <f>IF(COUNT(B74:K74)&gt;1,MAX(B74:K74)-MIN(B74:K74),IF(ISNUMBER(M74),M74,""))</f>
+        <v/>
+      </c>
+      <c r="R74" s="28">
+        <f>IF(COUNT(B74:K74)&gt;1,_xlfn.STDEV.S(B74:K74),IF(ISNUMBER(N74),N74,""))</f>
+        <v/>
+      </c>
+      <c r="S74" s="13">
+        <f>IF(AND(ISNUMBER(P74),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P74&gt;$D$23,"above UCL",IF(P74&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T74" s="13">
+        <f>IF(AND(ISNUMBER(Q74),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q74&gt;$D$24,"above UCL",IF(Q74&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U74" s="13">
+        <f>IF(AND(ISNUMBER(P74),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P74&gt;$D$25,"above UCL",IF(P74&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V74" s="13">
+        <f>IF(AND(ISNUMBER(R74),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R74&gt;$D$26,"above UCL",IF(R74&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>46</v>
+      </c>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
+      <c r="J75" s="7" t="n"/>
+      <c r="K75" s="7" t="n"/>
+      <c r="L75" s="7" t="n"/>
+      <c r="M75" s="7" t="n"/>
+      <c r="N75" s="7" t="n"/>
+      <c r="O75" s="24">
+        <f>IF(COUNT(B75:K75)&gt;0,COUNT(B75:K75),IF(OR(ISNUMBER(L75),ISNUMBER(M75)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P75" s="28">
+        <f>IF(COUNT(B75:K75)&gt;0,AVERAGE(B75:K75),IF(ISNUMBER(L75),L75,""))</f>
+        <v/>
+      </c>
+      <c r="Q75" s="28">
+        <f>IF(COUNT(B75:K75)&gt;1,MAX(B75:K75)-MIN(B75:K75),IF(ISNUMBER(M75),M75,""))</f>
+        <v/>
+      </c>
+      <c r="R75" s="28">
+        <f>IF(COUNT(B75:K75)&gt;1,_xlfn.STDEV.S(B75:K75),IF(ISNUMBER(N75),N75,""))</f>
+        <v/>
+      </c>
+      <c r="S75" s="13">
+        <f>IF(AND(ISNUMBER(P75),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P75&gt;$D$23,"above UCL",IF(P75&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T75" s="13">
+        <f>IF(AND(ISNUMBER(Q75),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q75&gt;$D$24,"above UCL",IF(Q75&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U75" s="13">
+        <f>IF(AND(ISNUMBER(P75),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P75&gt;$D$25,"above UCL",IF(P75&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V75" s="13">
+        <f>IF(AND(ISNUMBER(R75),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R75&gt;$D$26,"above UCL",IF(R75&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>47</v>
+      </c>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n"/>
+      <c r="I76" s="7" t="n"/>
+      <c r="J76" s="7" t="n"/>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="n"/>
+      <c r="N76" s="7" t="n"/>
+      <c r="O76" s="24">
+        <f>IF(COUNT(B76:K76)&gt;0,COUNT(B76:K76),IF(OR(ISNUMBER(L76),ISNUMBER(M76)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P76" s="28">
+        <f>IF(COUNT(B76:K76)&gt;0,AVERAGE(B76:K76),IF(ISNUMBER(L76),L76,""))</f>
+        <v/>
+      </c>
+      <c r="Q76" s="28">
+        <f>IF(COUNT(B76:K76)&gt;1,MAX(B76:K76)-MIN(B76:K76),IF(ISNUMBER(M76),M76,""))</f>
+        <v/>
+      </c>
+      <c r="R76" s="28">
+        <f>IF(COUNT(B76:K76)&gt;1,_xlfn.STDEV.S(B76:K76),IF(ISNUMBER(N76),N76,""))</f>
+        <v/>
+      </c>
+      <c r="S76" s="13">
+        <f>IF(AND(ISNUMBER(P76),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P76&gt;$D$23,"above UCL",IF(P76&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T76" s="13">
+        <f>IF(AND(ISNUMBER(Q76),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q76&gt;$D$24,"above UCL",IF(Q76&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U76" s="13">
+        <f>IF(AND(ISNUMBER(P76),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P76&gt;$D$25,"above UCL",IF(P76&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V76" s="13">
+        <f>IF(AND(ISNUMBER(R76),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R76&gt;$D$26,"above UCL",IF(R76&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>48</v>
+      </c>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="7" t="n"/>
+      <c r="K77" s="7" t="n"/>
+      <c r="L77" s="7" t="n"/>
+      <c r="M77" s="7" t="n"/>
+      <c r="N77" s="7" t="n"/>
+      <c r="O77" s="24">
+        <f>IF(COUNT(B77:K77)&gt;0,COUNT(B77:K77),IF(OR(ISNUMBER(L77),ISNUMBER(M77)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P77" s="28">
+        <f>IF(COUNT(B77:K77)&gt;0,AVERAGE(B77:K77),IF(ISNUMBER(L77),L77,""))</f>
+        <v/>
+      </c>
+      <c r="Q77" s="28">
+        <f>IF(COUNT(B77:K77)&gt;1,MAX(B77:K77)-MIN(B77:K77),IF(ISNUMBER(M77),M77,""))</f>
+        <v/>
+      </c>
+      <c r="R77" s="28">
+        <f>IF(COUNT(B77:K77)&gt;1,_xlfn.STDEV.S(B77:K77),IF(ISNUMBER(N77),N77,""))</f>
+        <v/>
+      </c>
+      <c r="S77" s="13">
+        <f>IF(AND(ISNUMBER(P77),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P77&gt;$D$23,"above UCL",IF(P77&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T77" s="13">
+        <f>IF(AND(ISNUMBER(Q77),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q77&gt;$D$24,"above UCL",IF(Q77&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U77" s="13">
+        <f>IF(AND(ISNUMBER(P77),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P77&gt;$D$25,"above UCL",IF(P77&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V77" s="13">
+        <f>IF(AND(ISNUMBER(R77),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R77&gt;$D$26,"above UCL",IF(R77&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>49</v>
+      </c>
+      <c r="B78" s="7" t="n"/>
+      <c r="C78" s="7" t="n"/>
+      <c r="D78" s="7" t="n"/>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
+      <c r="G78" s="7" t="n"/>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+      <c r="J78" s="7" t="n"/>
+      <c r="K78" s="7" t="n"/>
+      <c r="L78" s="7" t="n"/>
+      <c r="M78" s="7" t="n"/>
+      <c r="N78" s="7" t="n"/>
+      <c r="O78" s="24">
+        <f>IF(COUNT(B78:K78)&gt;0,COUNT(B78:K78),IF(OR(ISNUMBER(L78),ISNUMBER(M78)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P78" s="28">
+        <f>IF(COUNT(B78:K78)&gt;0,AVERAGE(B78:K78),IF(ISNUMBER(L78),L78,""))</f>
+        <v/>
+      </c>
+      <c r="Q78" s="28">
+        <f>IF(COUNT(B78:K78)&gt;1,MAX(B78:K78)-MIN(B78:K78),IF(ISNUMBER(M78),M78,""))</f>
+        <v/>
+      </c>
+      <c r="R78" s="28">
+        <f>IF(COUNT(B78:K78)&gt;1,_xlfn.STDEV.S(B78:K78),IF(ISNUMBER(N78),N78,""))</f>
+        <v/>
+      </c>
+      <c r="S78" s="13">
+        <f>IF(AND(ISNUMBER(P78),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P78&gt;$D$23,"above UCL",IF(P78&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T78" s="13">
+        <f>IF(AND(ISNUMBER(Q78),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q78&gt;$D$24,"above UCL",IF(Q78&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U78" s="13">
+        <f>IF(AND(ISNUMBER(P78),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P78&gt;$D$25,"above UCL",IF(P78&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V78" s="13">
+        <f>IF(AND(ISNUMBER(R78),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R78&gt;$D$26,"above UCL",IF(R78&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>50</v>
+      </c>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="7" t="n"/>
+      <c r="O79" s="24">
+        <f>IF(COUNT(B79:K79)&gt;0,COUNT(B79:K79),IF(OR(ISNUMBER(L79),ISNUMBER(M79)),$B$9,""))</f>
+        <v/>
+      </c>
+      <c r="P79" s="28">
+        <f>IF(COUNT(B79:K79)&gt;0,AVERAGE(B79:K79),IF(ISNUMBER(L79),L79,""))</f>
+        <v/>
+      </c>
+      <c r="Q79" s="28">
+        <f>IF(COUNT(B79:K79)&gt;1,MAX(B79:K79)-MIN(B79:K79),IF(ISNUMBER(M79),M79,""))</f>
+        <v/>
+      </c>
+      <c r="R79" s="28">
+        <f>IF(COUNT(B79:K79)&gt;1,_xlfn.STDEV.S(B79:K79),IF(ISNUMBER(N79),N79,""))</f>
+        <v/>
+      </c>
+      <c r="S79" s="13">
+        <f>IF(AND(ISNUMBER(P79),ISNUMBER($B$23),ISNUMBER($D$23)),IF(P79&gt;$D$23,"above UCL",IF(P79&lt;$B$23,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="T79" s="13">
+        <f>IF(AND(ISNUMBER(Q79),ISNUMBER($B$24),ISNUMBER($D$24)),IF(Q79&gt;$D$24,"above UCL",IF(Q79&lt;$B$24,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="U79" s="13">
+        <f>IF(AND(ISNUMBER(P79),ISNUMBER($B$25),ISNUMBER($D$25)),IF(P79&gt;$D$25,"above UCL",IF(P79&lt;$B$25,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="V79" s="13">
+        <f>IF(AND(ISNUMBER(R79),ISNUMBER($B$26),ISNUMBER($D$26)),IF(R79&gt;$D$26,"above UCL",IF(R79&lt;$B$26,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2. Individuals and moving range (I-MR): one value per time point (table from row 93)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>k = number of values</t>
+        </is>
+      </c>
+      <c r="B83" s="24">
+        <f>IF(COUNT(B93:B192)&gt;0,COUNT(B93:B192),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>X̄ = mean of the values</t>
+        </is>
+      </c>
+      <c r="B84" s="28">
+        <f>IF(COUNT(B93:B192)&gt;0,AVERAGE(B93:B192),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>MR̄ = mean moving range</t>
+        </is>
+      </c>
+      <c r="B85" s="28">
+        <f>IF(COUNT(C93:C192)&gt;0,AVERAGE(C93:C192),"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 249 (MR_i = |X_(i+1) − X_i|)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>σ̂ = MR̄ / d2(n = 2)  (d2 in column C)</t>
+        </is>
+      </c>
+      <c r="B86" s="28">
+        <f>IF(ISNUMBER(B85),B85/C86,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="12">
+        <f>INDEX(T18_d2,MATCH(2,T18_n,0))</f>
+        <v/>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 116 (σ_ST = R̄/1.128)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>LCL</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>UCL</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Constants</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>X chart: X̄ ± E2·MR̄</t>
+        </is>
+      </c>
+      <c r="B89" s="28">
+        <f>IF(AND(ISNUMBER(B84),ISNUMBER(B85)),B84-F89*B85,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="28">
+        <f>IF(ISNUMBER(B84),B84,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="28">
+        <f>IF(AND(ISNUMBER(B84),ISNUMBER(B85)),B84+F89*B85,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>E2 (n = 2)</t>
+        </is>
+      </c>
+      <c r="F89" s="12">
+        <f>INDEX(SSD2_E2,MATCH(2,SSD2_n,0))</f>
+        <v/>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 249</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>MR chart: D3·MR̄ … D4·MR̄</t>
+        </is>
+      </c>
+      <c r="B90" s="28">
+        <f>IF(ISNUMBER(B85),F90*B85,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="28">
+        <f>IF(ISNUMBER(B85),B85,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="28">
+        <f>IF(ISNUMBER(B85),G90*B85,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>D3, D4 (n = 2)</t>
+        </is>
+      </c>
+      <c r="F90" s="12">
+        <f>INDEX(T18_D3,MATCH(2,T18_n,0))</f>
+        <v/>
+      </c>
+      <c r="G90" s="12">
+        <f>INDEX(T18_D4,MATCH(2,T18_n,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>value x_i</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>MR_i = |x_i − x_(i−1)|</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>x vs X chart</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>MR vs MR chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="28">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D93" s="13">
+        <f>IF(AND(ISNUMBER(B93),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B93&gt;$D$89,"above UCL",IF(B93&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>IF(AND(ISNUMBER(C93),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C93&gt;$D$90,"above UCL",IF(C93&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2</v>
+      </c>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="28">
+        <f>IF(AND(ISNUMBER(B94),ISNUMBER(B93)),ABS(B94-B93),"")</f>
+        <v/>
+      </c>
+      <c r="D94" s="13">
+        <f>IF(AND(ISNUMBER(B94),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B94&gt;$D$89,"above UCL",IF(B94&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="13">
+        <f>IF(AND(ISNUMBER(C94),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C94&gt;$D$90,"above UCL",IF(C94&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="28">
+        <f>IF(AND(ISNUMBER(B95),ISNUMBER(B94)),ABS(B95-B94),"")</f>
+        <v/>
+      </c>
+      <c r="D95" s="13">
+        <f>IF(AND(ISNUMBER(B95),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B95&gt;$D$89,"above UCL",IF(B95&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="13">
+        <f>IF(AND(ISNUMBER(C95),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C95&gt;$D$90,"above UCL",IF(C95&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4</v>
+      </c>
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="28">
+        <f>IF(AND(ISNUMBER(B96),ISNUMBER(B95)),ABS(B96-B95),"")</f>
+        <v/>
+      </c>
+      <c r="D96" s="13">
+        <f>IF(AND(ISNUMBER(B96),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B96&gt;$D$89,"above UCL",IF(B96&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="13">
+        <f>IF(AND(ISNUMBER(C96),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C96&gt;$D$90,"above UCL",IF(C96&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="28">
+        <f>IF(AND(ISNUMBER(B97),ISNUMBER(B96)),ABS(B97-B96),"")</f>
+        <v/>
+      </c>
+      <c r="D97" s="13">
+        <f>IF(AND(ISNUMBER(B97),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B97&gt;$D$89,"above UCL",IF(B97&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E97" s="13">
+        <f>IF(AND(ISNUMBER(C97),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C97&gt;$D$90,"above UCL",IF(C97&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>6</v>
+      </c>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="28">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER(B97)),ABS(B98-B97),"")</f>
+        <v/>
+      </c>
+      <c r="D98" s="13">
+        <f>IF(AND(ISNUMBER(B98),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B98&gt;$D$89,"above UCL",IF(B98&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E98" s="13">
+        <f>IF(AND(ISNUMBER(C98),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C98&gt;$D$90,"above UCL",IF(C98&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>7</v>
+      </c>
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="28">
+        <f>IF(AND(ISNUMBER(B99),ISNUMBER(B98)),ABS(B99-B98),"")</f>
+        <v/>
+      </c>
+      <c r="D99" s="13">
+        <f>IF(AND(ISNUMBER(B99),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B99&gt;$D$89,"above UCL",IF(B99&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E99" s="13">
+        <f>IF(AND(ISNUMBER(C99),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C99&gt;$D$90,"above UCL",IF(C99&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>8</v>
+      </c>
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="28">
+        <f>IF(AND(ISNUMBER(B100),ISNUMBER(B99)),ABS(B100-B99),"")</f>
+        <v/>
+      </c>
+      <c r="D100" s="13">
+        <f>IF(AND(ISNUMBER(B100),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B100&gt;$D$89,"above UCL",IF(B100&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E100" s="13">
+        <f>IF(AND(ISNUMBER(C100),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C100&gt;$D$90,"above UCL",IF(C100&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>9</v>
+      </c>
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="28">
+        <f>IF(AND(ISNUMBER(B101),ISNUMBER(B100)),ABS(B101-B100),"")</f>
+        <v/>
+      </c>
+      <c r="D101" s="13">
+        <f>IF(AND(ISNUMBER(B101),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B101&gt;$D$89,"above UCL",IF(B101&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E101" s="13">
+        <f>IF(AND(ISNUMBER(C101),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C101&gt;$D$90,"above UCL",IF(C101&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>10</v>
+      </c>
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="28">
+        <f>IF(AND(ISNUMBER(B102),ISNUMBER(B101)),ABS(B102-B101),"")</f>
+        <v/>
+      </c>
+      <c r="D102" s="13">
+        <f>IF(AND(ISNUMBER(B102),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B102&gt;$D$89,"above UCL",IF(B102&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E102" s="13">
+        <f>IF(AND(ISNUMBER(C102),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C102&gt;$D$90,"above UCL",IF(C102&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>11</v>
+      </c>
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="28">
+        <f>IF(AND(ISNUMBER(B103),ISNUMBER(B102)),ABS(B103-B102),"")</f>
+        <v/>
+      </c>
+      <c r="D103" s="13">
+        <f>IF(AND(ISNUMBER(B103),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B103&gt;$D$89,"above UCL",IF(B103&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E103" s="13">
+        <f>IF(AND(ISNUMBER(C103),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C103&gt;$D$90,"above UCL",IF(C103&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>12</v>
+      </c>
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="28">
+        <f>IF(AND(ISNUMBER(B104),ISNUMBER(B103)),ABS(B104-B103),"")</f>
+        <v/>
+      </c>
+      <c r="D104" s="13">
+        <f>IF(AND(ISNUMBER(B104),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B104&gt;$D$89,"above UCL",IF(B104&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E104" s="13">
+        <f>IF(AND(ISNUMBER(C104),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C104&gt;$D$90,"above UCL",IF(C104&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>13</v>
+      </c>
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="28">
+        <f>IF(AND(ISNUMBER(B105),ISNUMBER(B104)),ABS(B105-B104),"")</f>
+        <v/>
+      </c>
+      <c r="D105" s="13">
+        <f>IF(AND(ISNUMBER(B105),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B105&gt;$D$89,"above UCL",IF(B105&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E105" s="13">
+        <f>IF(AND(ISNUMBER(C105),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C105&gt;$D$90,"above UCL",IF(C105&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>14</v>
+      </c>
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="28">
+        <f>IF(AND(ISNUMBER(B106),ISNUMBER(B105)),ABS(B106-B105),"")</f>
+        <v/>
+      </c>
+      <c r="D106" s="13">
+        <f>IF(AND(ISNUMBER(B106),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B106&gt;$D$89,"above UCL",IF(B106&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E106" s="13">
+        <f>IF(AND(ISNUMBER(C106),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C106&gt;$D$90,"above UCL",IF(C106&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>15</v>
+      </c>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="28">
+        <f>IF(AND(ISNUMBER(B107),ISNUMBER(B106)),ABS(B107-B106),"")</f>
+        <v/>
+      </c>
+      <c r="D107" s="13">
+        <f>IF(AND(ISNUMBER(B107),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B107&gt;$D$89,"above UCL",IF(B107&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E107" s="13">
+        <f>IF(AND(ISNUMBER(C107),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C107&gt;$D$90,"above UCL",IF(C107&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>16</v>
+      </c>
+      <c r="B108" s="7" t="n"/>
+      <c r="C108" s="28">
+        <f>IF(AND(ISNUMBER(B108),ISNUMBER(B107)),ABS(B108-B107),"")</f>
+        <v/>
+      </c>
+      <c r="D108" s="13">
+        <f>IF(AND(ISNUMBER(B108),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B108&gt;$D$89,"above UCL",IF(B108&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E108" s="13">
+        <f>IF(AND(ISNUMBER(C108),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C108&gt;$D$90,"above UCL",IF(C108&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>17</v>
+      </c>
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="28">
+        <f>IF(AND(ISNUMBER(B109),ISNUMBER(B108)),ABS(B109-B108),"")</f>
+        <v/>
+      </c>
+      <c r="D109" s="13">
+        <f>IF(AND(ISNUMBER(B109),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B109&gt;$D$89,"above UCL",IF(B109&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E109" s="13">
+        <f>IF(AND(ISNUMBER(C109),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C109&gt;$D$90,"above UCL",IF(C109&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>18</v>
+      </c>
+      <c r="B110" s="7" t="n"/>
+      <c r="C110" s="28">
+        <f>IF(AND(ISNUMBER(B110),ISNUMBER(B109)),ABS(B110-B109),"")</f>
+        <v/>
+      </c>
+      <c r="D110" s="13">
+        <f>IF(AND(ISNUMBER(B110),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B110&gt;$D$89,"above UCL",IF(B110&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E110" s="13">
+        <f>IF(AND(ISNUMBER(C110),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C110&gt;$D$90,"above UCL",IF(C110&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>19</v>
+      </c>
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="28">
+        <f>IF(AND(ISNUMBER(B111),ISNUMBER(B110)),ABS(B111-B110),"")</f>
+        <v/>
+      </c>
+      <c r="D111" s="13">
+        <f>IF(AND(ISNUMBER(B111),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B111&gt;$D$89,"above UCL",IF(B111&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E111" s="13">
+        <f>IF(AND(ISNUMBER(C111),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C111&gt;$D$90,"above UCL",IF(C111&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>20</v>
+      </c>
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="28">
+        <f>IF(AND(ISNUMBER(B112),ISNUMBER(B111)),ABS(B112-B111),"")</f>
+        <v/>
+      </c>
+      <c r="D112" s="13">
+        <f>IF(AND(ISNUMBER(B112),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B112&gt;$D$89,"above UCL",IF(B112&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E112" s="13">
+        <f>IF(AND(ISNUMBER(C112),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C112&gt;$D$90,"above UCL",IF(C112&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>21</v>
+      </c>
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="28">
+        <f>IF(AND(ISNUMBER(B113),ISNUMBER(B112)),ABS(B113-B112),"")</f>
+        <v/>
+      </c>
+      <c r="D113" s="13">
+        <f>IF(AND(ISNUMBER(B113),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B113&gt;$D$89,"above UCL",IF(B113&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E113" s="13">
+        <f>IF(AND(ISNUMBER(C113),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C113&gt;$D$90,"above UCL",IF(C113&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>22</v>
+      </c>
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="28">
+        <f>IF(AND(ISNUMBER(B114),ISNUMBER(B113)),ABS(B114-B113),"")</f>
+        <v/>
+      </c>
+      <c r="D114" s="13">
+        <f>IF(AND(ISNUMBER(B114),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B114&gt;$D$89,"above UCL",IF(B114&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E114" s="13">
+        <f>IF(AND(ISNUMBER(C114),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C114&gt;$D$90,"above UCL",IF(C114&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>23</v>
+      </c>
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="28">
+        <f>IF(AND(ISNUMBER(B115),ISNUMBER(B114)),ABS(B115-B114),"")</f>
+        <v/>
+      </c>
+      <c r="D115" s="13">
+        <f>IF(AND(ISNUMBER(B115),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B115&gt;$D$89,"above UCL",IF(B115&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E115" s="13">
+        <f>IF(AND(ISNUMBER(C115),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C115&gt;$D$90,"above UCL",IF(C115&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>24</v>
+      </c>
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="28">
+        <f>IF(AND(ISNUMBER(B116),ISNUMBER(B115)),ABS(B116-B115),"")</f>
+        <v/>
+      </c>
+      <c r="D116" s="13">
+        <f>IF(AND(ISNUMBER(B116),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B116&gt;$D$89,"above UCL",IF(B116&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E116" s="13">
+        <f>IF(AND(ISNUMBER(C116),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C116&gt;$D$90,"above UCL",IF(C116&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>25</v>
+      </c>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="28">
+        <f>IF(AND(ISNUMBER(B117),ISNUMBER(B116)),ABS(B117-B116),"")</f>
+        <v/>
+      </c>
+      <c r="D117" s="13">
+        <f>IF(AND(ISNUMBER(B117),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B117&gt;$D$89,"above UCL",IF(B117&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E117" s="13">
+        <f>IF(AND(ISNUMBER(C117),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C117&gt;$D$90,"above UCL",IF(C117&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>26</v>
+      </c>
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="28">
+        <f>IF(AND(ISNUMBER(B118),ISNUMBER(B117)),ABS(B118-B117),"")</f>
+        <v/>
+      </c>
+      <c r="D118" s="13">
+        <f>IF(AND(ISNUMBER(B118),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B118&gt;$D$89,"above UCL",IF(B118&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E118" s="13">
+        <f>IF(AND(ISNUMBER(C118),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C118&gt;$D$90,"above UCL",IF(C118&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>27</v>
+      </c>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="28">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER(B118)),ABS(B119-B118),"")</f>
+        <v/>
+      </c>
+      <c r="D119" s="13">
+        <f>IF(AND(ISNUMBER(B119),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B119&gt;$D$89,"above UCL",IF(B119&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E119" s="13">
+        <f>IF(AND(ISNUMBER(C119),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C119&gt;$D$90,"above UCL",IF(C119&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>28</v>
+      </c>
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="28">
+        <f>IF(AND(ISNUMBER(B120),ISNUMBER(B119)),ABS(B120-B119),"")</f>
+        <v/>
+      </c>
+      <c r="D120" s="13">
+        <f>IF(AND(ISNUMBER(B120),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B120&gt;$D$89,"above UCL",IF(B120&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E120" s="13">
+        <f>IF(AND(ISNUMBER(C120),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C120&gt;$D$90,"above UCL",IF(C120&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>29</v>
+      </c>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="28">
+        <f>IF(AND(ISNUMBER(B121),ISNUMBER(B120)),ABS(B121-B120),"")</f>
+        <v/>
+      </c>
+      <c r="D121" s="13">
+        <f>IF(AND(ISNUMBER(B121),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B121&gt;$D$89,"above UCL",IF(B121&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E121" s="13">
+        <f>IF(AND(ISNUMBER(C121),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C121&gt;$D$90,"above UCL",IF(C121&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>30</v>
+      </c>
+      <c r="B122" s="7" t="n"/>
+      <c r="C122" s="28">
+        <f>IF(AND(ISNUMBER(B122),ISNUMBER(B121)),ABS(B122-B121),"")</f>
+        <v/>
+      </c>
+      <c r="D122" s="13">
+        <f>IF(AND(ISNUMBER(B122),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B122&gt;$D$89,"above UCL",IF(B122&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E122" s="13">
+        <f>IF(AND(ISNUMBER(C122),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C122&gt;$D$90,"above UCL",IF(C122&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>31</v>
+      </c>
+      <c r="B123" s="7" t="n"/>
+      <c r="C123" s="28">
+        <f>IF(AND(ISNUMBER(B123),ISNUMBER(B122)),ABS(B123-B122),"")</f>
+        <v/>
+      </c>
+      <c r="D123" s="13">
+        <f>IF(AND(ISNUMBER(B123),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B123&gt;$D$89,"above UCL",IF(B123&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E123" s="13">
+        <f>IF(AND(ISNUMBER(C123),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C123&gt;$D$90,"above UCL",IF(C123&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>32</v>
+      </c>
+      <c r="B124" s="7" t="n"/>
+      <c r="C124" s="28">
+        <f>IF(AND(ISNUMBER(B124),ISNUMBER(B123)),ABS(B124-B123),"")</f>
+        <v/>
+      </c>
+      <c r="D124" s="13">
+        <f>IF(AND(ISNUMBER(B124),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B124&gt;$D$89,"above UCL",IF(B124&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E124" s="13">
+        <f>IF(AND(ISNUMBER(C124),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C124&gt;$D$90,"above UCL",IF(C124&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>33</v>
+      </c>
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="28">
+        <f>IF(AND(ISNUMBER(B125),ISNUMBER(B124)),ABS(B125-B124),"")</f>
+        <v/>
+      </c>
+      <c r="D125" s="13">
+        <f>IF(AND(ISNUMBER(B125),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B125&gt;$D$89,"above UCL",IF(B125&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E125" s="13">
+        <f>IF(AND(ISNUMBER(C125),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C125&gt;$D$90,"above UCL",IF(C125&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>34</v>
+      </c>
+      <c r="B126" s="7" t="n"/>
+      <c r="C126" s="28">
+        <f>IF(AND(ISNUMBER(B126),ISNUMBER(B125)),ABS(B126-B125),"")</f>
+        <v/>
+      </c>
+      <c r="D126" s="13">
+        <f>IF(AND(ISNUMBER(B126),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B126&gt;$D$89,"above UCL",IF(B126&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E126" s="13">
+        <f>IF(AND(ISNUMBER(C126),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C126&gt;$D$90,"above UCL",IF(C126&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>35</v>
+      </c>
+      <c r="B127" s="7" t="n"/>
+      <c r="C127" s="28">
+        <f>IF(AND(ISNUMBER(B127),ISNUMBER(B126)),ABS(B127-B126),"")</f>
+        <v/>
+      </c>
+      <c r="D127" s="13">
+        <f>IF(AND(ISNUMBER(B127),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B127&gt;$D$89,"above UCL",IF(B127&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E127" s="13">
+        <f>IF(AND(ISNUMBER(C127),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C127&gt;$D$90,"above UCL",IF(C127&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>36</v>
+      </c>
+      <c r="B128" s="7" t="n"/>
+      <c r="C128" s="28">
+        <f>IF(AND(ISNUMBER(B128),ISNUMBER(B127)),ABS(B128-B127),"")</f>
+        <v/>
+      </c>
+      <c r="D128" s="13">
+        <f>IF(AND(ISNUMBER(B128),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B128&gt;$D$89,"above UCL",IF(B128&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E128" s="13">
+        <f>IF(AND(ISNUMBER(C128),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C128&gt;$D$90,"above UCL",IF(C128&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>37</v>
+      </c>
+      <c r="B129" s="7" t="n"/>
+      <c r="C129" s="28">
+        <f>IF(AND(ISNUMBER(B129),ISNUMBER(B128)),ABS(B129-B128),"")</f>
+        <v/>
+      </c>
+      <c r="D129" s="13">
+        <f>IF(AND(ISNUMBER(B129),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B129&gt;$D$89,"above UCL",IF(B129&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E129" s="13">
+        <f>IF(AND(ISNUMBER(C129),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C129&gt;$D$90,"above UCL",IF(C129&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>38</v>
+      </c>
+      <c r="B130" s="7" t="n"/>
+      <c r="C130" s="28">
+        <f>IF(AND(ISNUMBER(B130),ISNUMBER(B129)),ABS(B130-B129),"")</f>
+        <v/>
+      </c>
+      <c r="D130" s="13">
+        <f>IF(AND(ISNUMBER(B130),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B130&gt;$D$89,"above UCL",IF(B130&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E130" s="13">
+        <f>IF(AND(ISNUMBER(C130),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C130&gt;$D$90,"above UCL",IF(C130&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>39</v>
+      </c>
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="28">
+        <f>IF(AND(ISNUMBER(B131),ISNUMBER(B130)),ABS(B131-B130),"")</f>
+        <v/>
+      </c>
+      <c r="D131" s="13">
+        <f>IF(AND(ISNUMBER(B131),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B131&gt;$D$89,"above UCL",IF(B131&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E131" s="13">
+        <f>IF(AND(ISNUMBER(C131),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C131&gt;$D$90,"above UCL",IF(C131&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>40</v>
+      </c>
+      <c r="B132" s="7" t="n"/>
+      <c r="C132" s="28">
+        <f>IF(AND(ISNUMBER(B132),ISNUMBER(B131)),ABS(B132-B131),"")</f>
+        <v/>
+      </c>
+      <c r="D132" s="13">
+        <f>IF(AND(ISNUMBER(B132),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B132&gt;$D$89,"above UCL",IF(B132&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E132" s="13">
+        <f>IF(AND(ISNUMBER(C132),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C132&gt;$D$90,"above UCL",IF(C132&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>41</v>
+      </c>
+      <c r="B133" s="7" t="n"/>
+      <c r="C133" s="28">
+        <f>IF(AND(ISNUMBER(B133),ISNUMBER(B132)),ABS(B133-B132),"")</f>
+        <v/>
+      </c>
+      <c r="D133" s="13">
+        <f>IF(AND(ISNUMBER(B133),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B133&gt;$D$89,"above UCL",IF(B133&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E133" s="13">
+        <f>IF(AND(ISNUMBER(C133),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C133&gt;$D$90,"above UCL",IF(C133&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>42</v>
+      </c>
+      <c r="B134" s="7" t="n"/>
+      <c r="C134" s="28">
+        <f>IF(AND(ISNUMBER(B134),ISNUMBER(B133)),ABS(B134-B133),"")</f>
+        <v/>
+      </c>
+      <c r="D134" s="13">
+        <f>IF(AND(ISNUMBER(B134),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B134&gt;$D$89,"above UCL",IF(B134&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E134" s="13">
+        <f>IF(AND(ISNUMBER(C134),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C134&gt;$D$90,"above UCL",IF(C134&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>43</v>
+      </c>
+      <c r="B135" s="7" t="n"/>
+      <c r="C135" s="28">
+        <f>IF(AND(ISNUMBER(B135),ISNUMBER(B134)),ABS(B135-B134),"")</f>
+        <v/>
+      </c>
+      <c r="D135" s="13">
+        <f>IF(AND(ISNUMBER(B135),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B135&gt;$D$89,"above UCL",IF(B135&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E135" s="13">
+        <f>IF(AND(ISNUMBER(C135),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C135&gt;$D$90,"above UCL",IF(C135&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>44</v>
+      </c>
+      <c r="B136" s="7" t="n"/>
+      <c r="C136" s="28">
+        <f>IF(AND(ISNUMBER(B136),ISNUMBER(B135)),ABS(B136-B135),"")</f>
+        <v/>
+      </c>
+      <c r="D136" s="13">
+        <f>IF(AND(ISNUMBER(B136),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B136&gt;$D$89,"above UCL",IF(B136&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E136" s="13">
+        <f>IF(AND(ISNUMBER(C136),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C136&gt;$D$90,"above UCL",IF(C136&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>45</v>
+      </c>
+      <c r="B137" s="7" t="n"/>
+      <c r="C137" s="28">
+        <f>IF(AND(ISNUMBER(B137),ISNUMBER(B136)),ABS(B137-B136),"")</f>
+        <v/>
+      </c>
+      <c r="D137" s="13">
+        <f>IF(AND(ISNUMBER(B137),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B137&gt;$D$89,"above UCL",IF(B137&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E137" s="13">
+        <f>IF(AND(ISNUMBER(C137),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C137&gt;$D$90,"above UCL",IF(C137&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>46</v>
+      </c>
+      <c r="B138" s="7" t="n"/>
+      <c r="C138" s="28">
+        <f>IF(AND(ISNUMBER(B138),ISNUMBER(B137)),ABS(B138-B137),"")</f>
+        <v/>
+      </c>
+      <c r="D138" s="13">
+        <f>IF(AND(ISNUMBER(B138),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B138&gt;$D$89,"above UCL",IF(B138&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E138" s="13">
+        <f>IF(AND(ISNUMBER(C138),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C138&gt;$D$90,"above UCL",IF(C138&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>47</v>
+      </c>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="28">
+        <f>IF(AND(ISNUMBER(B139),ISNUMBER(B138)),ABS(B139-B138),"")</f>
+        <v/>
+      </c>
+      <c r="D139" s="13">
+        <f>IF(AND(ISNUMBER(B139),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B139&gt;$D$89,"above UCL",IF(B139&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E139" s="13">
+        <f>IF(AND(ISNUMBER(C139),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C139&gt;$D$90,"above UCL",IF(C139&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>48</v>
+      </c>
+      <c r="B140" s="7" t="n"/>
+      <c r="C140" s="28">
+        <f>IF(AND(ISNUMBER(B140),ISNUMBER(B139)),ABS(B140-B139),"")</f>
+        <v/>
+      </c>
+      <c r="D140" s="13">
+        <f>IF(AND(ISNUMBER(B140),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B140&gt;$D$89,"above UCL",IF(B140&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E140" s="13">
+        <f>IF(AND(ISNUMBER(C140),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C140&gt;$D$90,"above UCL",IF(C140&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>49</v>
+      </c>
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="28">
+        <f>IF(AND(ISNUMBER(B141),ISNUMBER(B140)),ABS(B141-B140),"")</f>
+        <v/>
+      </c>
+      <c r="D141" s="13">
+        <f>IF(AND(ISNUMBER(B141),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B141&gt;$D$89,"above UCL",IF(B141&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E141" s="13">
+        <f>IF(AND(ISNUMBER(C141),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C141&gt;$D$90,"above UCL",IF(C141&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>50</v>
+      </c>
+      <c r="B142" s="7" t="n"/>
+      <c r="C142" s="28">
+        <f>IF(AND(ISNUMBER(B142),ISNUMBER(B141)),ABS(B142-B141),"")</f>
+        <v/>
+      </c>
+      <c r="D142" s="13">
+        <f>IF(AND(ISNUMBER(B142),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B142&gt;$D$89,"above UCL",IF(B142&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E142" s="13">
+        <f>IF(AND(ISNUMBER(C142),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C142&gt;$D$90,"above UCL",IF(C142&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>51</v>
+      </c>
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="28">
+        <f>IF(AND(ISNUMBER(B143),ISNUMBER(B142)),ABS(B143-B142),"")</f>
+        <v/>
+      </c>
+      <c r="D143" s="13">
+        <f>IF(AND(ISNUMBER(B143),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B143&gt;$D$89,"above UCL",IF(B143&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E143" s="13">
+        <f>IF(AND(ISNUMBER(C143),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C143&gt;$D$90,"above UCL",IF(C143&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>52</v>
+      </c>
+      <c r="B144" s="7" t="n"/>
+      <c r="C144" s="28">
+        <f>IF(AND(ISNUMBER(B144),ISNUMBER(B143)),ABS(B144-B143),"")</f>
+        <v/>
+      </c>
+      <c r="D144" s="13">
+        <f>IF(AND(ISNUMBER(B144),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B144&gt;$D$89,"above UCL",IF(B144&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E144" s="13">
+        <f>IF(AND(ISNUMBER(C144),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C144&gt;$D$90,"above UCL",IF(C144&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>53</v>
+      </c>
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="28">
+        <f>IF(AND(ISNUMBER(B145),ISNUMBER(B144)),ABS(B145-B144),"")</f>
+        <v/>
+      </c>
+      <c r="D145" s="13">
+        <f>IF(AND(ISNUMBER(B145),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B145&gt;$D$89,"above UCL",IF(B145&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E145" s="13">
+        <f>IF(AND(ISNUMBER(C145),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C145&gt;$D$90,"above UCL",IF(C145&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>54</v>
+      </c>
+      <c r="B146" s="7" t="n"/>
+      <c r="C146" s="28">
+        <f>IF(AND(ISNUMBER(B146),ISNUMBER(B145)),ABS(B146-B145),"")</f>
+        <v/>
+      </c>
+      <c r="D146" s="13">
+        <f>IF(AND(ISNUMBER(B146),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B146&gt;$D$89,"above UCL",IF(B146&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E146" s="13">
+        <f>IF(AND(ISNUMBER(C146),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C146&gt;$D$90,"above UCL",IF(C146&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>55</v>
+      </c>
+      <c r="B147" s="7" t="n"/>
+      <c r="C147" s="28">
+        <f>IF(AND(ISNUMBER(B147),ISNUMBER(B146)),ABS(B147-B146),"")</f>
+        <v/>
+      </c>
+      <c r="D147" s="13">
+        <f>IF(AND(ISNUMBER(B147),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B147&gt;$D$89,"above UCL",IF(B147&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E147" s="13">
+        <f>IF(AND(ISNUMBER(C147),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C147&gt;$D$90,"above UCL",IF(C147&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>56</v>
+      </c>
+      <c r="B148" s="7" t="n"/>
+      <c r="C148" s="28">
+        <f>IF(AND(ISNUMBER(B148),ISNUMBER(B147)),ABS(B148-B147),"")</f>
+        <v/>
+      </c>
+      <c r="D148" s="13">
+        <f>IF(AND(ISNUMBER(B148),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B148&gt;$D$89,"above UCL",IF(B148&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E148" s="13">
+        <f>IF(AND(ISNUMBER(C148),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C148&gt;$D$90,"above UCL",IF(C148&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>57</v>
+      </c>
+      <c r="B149" s="7" t="n"/>
+      <c r="C149" s="28">
+        <f>IF(AND(ISNUMBER(B149),ISNUMBER(B148)),ABS(B149-B148),"")</f>
+        <v/>
+      </c>
+      <c r="D149" s="13">
+        <f>IF(AND(ISNUMBER(B149),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B149&gt;$D$89,"above UCL",IF(B149&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E149" s="13">
+        <f>IF(AND(ISNUMBER(C149),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C149&gt;$D$90,"above UCL",IF(C149&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>58</v>
+      </c>
+      <c r="B150" s="7" t="n"/>
+      <c r="C150" s="28">
+        <f>IF(AND(ISNUMBER(B150),ISNUMBER(B149)),ABS(B150-B149),"")</f>
+        <v/>
+      </c>
+      <c r="D150" s="13">
+        <f>IF(AND(ISNUMBER(B150),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B150&gt;$D$89,"above UCL",IF(B150&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E150" s="13">
+        <f>IF(AND(ISNUMBER(C150),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C150&gt;$D$90,"above UCL",IF(C150&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>59</v>
+      </c>
+      <c r="B151" s="7" t="n"/>
+      <c r="C151" s="28">
+        <f>IF(AND(ISNUMBER(B151),ISNUMBER(B150)),ABS(B151-B150),"")</f>
+        <v/>
+      </c>
+      <c r="D151" s="13">
+        <f>IF(AND(ISNUMBER(B151),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B151&gt;$D$89,"above UCL",IF(B151&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E151" s="13">
+        <f>IF(AND(ISNUMBER(C151),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C151&gt;$D$90,"above UCL",IF(C151&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>60</v>
+      </c>
+      <c r="B152" s="7" t="n"/>
+      <c r="C152" s="28">
+        <f>IF(AND(ISNUMBER(B152),ISNUMBER(B151)),ABS(B152-B151),"")</f>
+        <v/>
+      </c>
+      <c r="D152" s="13">
+        <f>IF(AND(ISNUMBER(B152),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B152&gt;$D$89,"above UCL",IF(B152&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E152" s="13">
+        <f>IF(AND(ISNUMBER(C152),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C152&gt;$D$90,"above UCL",IF(C152&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>61</v>
+      </c>
+      <c r="B153" s="7" t="n"/>
+      <c r="C153" s="28">
+        <f>IF(AND(ISNUMBER(B153),ISNUMBER(B152)),ABS(B153-B152),"")</f>
+        <v/>
+      </c>
+      <c r="D153" s="13">
+        <f>IF(AND(ISNUMBER(B153),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B153&gt;$D$89,"above UCL",IF(B153&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E153" s="13">
+        <f>IF(AND(ISNUMBER(C153),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C153&gt;$D$90,"above UCL",IF(C153&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>62</v>
+      </c>
+      <c r="B154" s="7" t="n"/>
+      <c r="C154" s="28">
+        <f>IF(AND(ISNUMBER(B154),ISNUMBER(B153)),ABS(B154-B153),"")</f>
+        <v/>
+      </c>
+      <c r="D154" s="13">
+        <f>IF(AND(ISNUMBER(B154),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B154&gt;$D$89,"above UCL",IF(B154&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E154" s="13">
+        <f>IF(AND(ISNUMBER(C154),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C154&gt;$D$90,"above UCL",IF(C154&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>63</v>
+      </c>
+      <c r="B155" s="7" t="n"/>
+      <c r="C155" s="28">
+        <f>IF(AND(ISNUMBER(B155),ISNUMBER(B154)),ABS(B155-B154),"")</f>
+        <v/>
+      </c>
+      <c r="D155" s="13">
+        <f>IF(AND(ISNUMBER(B155),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B155&gt;$D$89,"above UCL",IF(B155&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E155" s="13">
+        <f>IF(AND(ISNUMBER(C155),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C155&gt;$D$90,"above UCL",IF(C155&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>64</v>
+      </c>
+      <c r="B156" s="7" t="n"/>
+      <c r="C156" s="28">
+        <f>IF(AND(ISNUMBER(B156),ISNUMBER(B155)),ABS(B156-B155),"")</f>
+        <v/>
+      </c>
+      <c r="D156" s="13">
+        <f>IF(AND(ISNUMBER(B156),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B156&gt;$D$89,"above UCL",IF(B156&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E156" s="13">
+        <f>IF(AND(ISNUMBER(C156),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C156&gt;$D$90,"above UCL",IF(C156&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>65</v>
+      </c>
+      <c r="B157" s="7" t="n"/>
+      <c r="C157" s="28">
+        <f>IF(AND(ISNUMBER(B157),ISNUMBER(B156)),ABS(B157-B156),"")</f>
+        <v/>
+      </c>
+      <c r="D157" s="13">
+        <f>IF(AND(ISNUMBER(B157),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B157&gt;$D$89,"above UCL",IF(B157&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E157" s="13">
+        <f>IF(AND(ISNUMBER(C157),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C157&gt;$D$90,"above UCL",IF(C157&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>66</v>
+      </c>
+      <c r="B158" s="7" t="n"/>
+      <c r="C158" s="28">
+        <f>IF(AND(ISNUMBER(B158),ISNUMBER(B157)),ABS(B158-B157),"")</f>
+        <v/>
+      </c>
+      <c r="D158" s="13">
+        <f>IF(AND(ISNUMBER(B158),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B158&gt;$D$89,"above UCL",IF(B158&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E158" s="13">
+        <f>IF(AND(ISNUMBER(C158),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C158&gt;$D$90,"above UCL",IF(C158&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>67</v>
+      </c>
+      <c r="B159" s="7" t="n"/>
+      <c r="C159" s="28">
+        <f>IF(AND(ISNUMBER(B159),ISNUMBER(B158)),ABS(B159-B158),"")</f>
+        <v/>
+      </c>
+      <c r="D159" s="13">
+        <f>IF(AND(ISNUMBER(B159),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B159&gt;$D$89,"above UCL",IF(B159&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E159" s="13">
+        <f>IF(AND(ISNUMBER(C159),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C159&gt;$D$90,"above UCL",IF(C159&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>68</v>
+      </c>
+      <c r="B160" s="7" t="n"/>
+      <c r="C160" s="28">
+        <f>IF(AND(ISNUMBER(B160),ISNUMBER(B159)),ABS(B160-B159),"")</f>
+        <v/>
+      </c>
+      <c r="D160" s="13">
+        <f>IF(AND(ISNUMBER(B160),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B160&gt;$D$89,"above UCL",IF(B160&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E160" s="13">
+        <f>IF(AND(ISNUMBER(C160),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C160&gt;$D$90,"above UCL",IF(C160&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>69</v>
+      </c>
+      <c r="B161" s="7" t="n"/>
+      <c r="C161" s="28">
+        <f>IF(AND(ISNUMBER(B161),ISNUMBER(B160)),ABS(B161-B160),"")</f>
+        <v/>
+      </c>
+      <c r="D161" s="13">
+        <f>IF(AND(ISNUMBER(B161),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B161&gt;$D$89,"above UCL",IF(B161&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E161" s="13">
+        <f>IF(AND(ISNUMBER(C161),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C161&gt;$D$90,"above UCL",IF(C161&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>70</v>
+      </c>
+      <c r="B162" s="7" t="n"/>
+      <c r="C162" s="28">
+        <f>IF(AND(ISNUMBER(B162),ISNUMBER(B161)),ABS(B162-B161),"")</f>
+        <v/>
+      </c>
+      <c r="D162" s="13">
+        <f>IF(AND(ISNUMBER(B162),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B162&gt;$D$89,"above UCL",IF(B162&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E162" s="13">
+        <f>IF(AND(ISNUMBER(C162),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C162&gt;$D$90,"above UCL",IF(C162&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>71</v>
+      </c>
+      <c r="B163" s="7" t="n"/>
+      <c r="C163" s="28">
+        <f>IF(AND(ISNUMBER(B163),ISNUMBER(B162)),ABS(B163-B162),"")</f>
+        <v/>
+      </c>
+      <c r="D163" s="13">
+        <f>IF(AND(ISNUMBER(B163),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B163&gt;$D$89,"above UCL",IF(B163&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E163" s="13">
+        <f>IF(AND(ISNUMBER(C163),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C163&gt;$D$90,"above UCL",IF(C163&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>72</v>
+      </c>
+      <c r="B164" s="7" t="n"/>
+      <c r="C164" s="28">
+        <f>IF(AND(ISNUMBER(B164),ISNUMBER(B163)),ABS(B164-B163),"")</f>
+        <v/>
+      </c>
+      <c r="D164" s="13">
+        <f>IF(AND(ISNUMBER(B164),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B164&gt;$D$89,"above UCL",IF(B164&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E164" s="13">
+        <f>IF(AND(ISNUMBER(C164),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C164&gt;$D$90,"above UCL",IF(C164&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>73</v>
+      </c>
+      <c r="B165" s="7" t="n"/>
+      <c r="C165" s="28">
+        <f>IF(AND(ISNUMBER(B165),ISNUMBER(B164)),ABS(B165-B164),"")</f>
+        <v/>
+      </c>
+      <c r="D165" s="13">
+        <f>IF(AND(ISNUMBER(B165),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B165&gt;$D$89,"above UCL",IF(B165&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E165" s="13">
+        <f>IF(AND(ISNUMBER(C165),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C165&gt;$D$90,"above UCL",IF(C165&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>74</v>
+      </c>
+      <c r="B166" s="7" t="n"/>
+      <c r="C166" s="28">
+        <f>IF(AND(ISNUMBER(B166),ISNUMBER(B165)),ABS(B166-B165),"")</f>
+        <v/>
+      </c>
+      <c r="D166" s="13">
+        <f>IF(AND(ISNUMBER(B166),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B166&gt;$D$89,"above UCL",IF(B166&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E166" s="13">
+        <f>IF(AND(ISNUMBER(C166),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C166&gt;$D$90,"above UCL",IF(C166&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>75</v>
+      </c>
+      <c r="B167" s="7" t="n"/>
+      <c r="C167" s="28">
+        <f>IF(AND(ISNUMBER(B167),ISNUMBER(B166)),ABS(B167-B166),"")</f>
+        <v/>
+      </c>
+      <c r="D167" s="13">
+        <f>IF(AND(ISNUMBER(B167),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B167&gt;$D$89,"above UCL",IF(B167&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E167" s="13">
+        <f>IF(AND(ISNUMBER(C167),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C167&gt;$D$90,"above UCL",IF(C167&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>76</v>
+      </c>
+      <c r="B168" s="7" t="n"/>
+      <c r="C168" s="28">
+        <f>IF(AND(ISNUMBER(B168),ISNUMBER(B167)),ABS(B168-B167),"")</f>
+        <v/>
+      </c>
+      <c r="D168" s="13">
+        <f>IF(AND(ISNUMBER(B168),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B168&gt;$D$89,"above UCL",IF(B168&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E168" s="13">
+        <f>IF(AND(ISNUMBER(C168),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C168&gt;$D$90,"above UCL",IF(C168&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>77</v>
+      </c>
+      <c r="B169" s="7" t="n"/>
+      <c r="C169" s="28">
+        <f>IF(AND(ISNUMBER(B169),ISNUMBER(B168)),ABS(B169-B168),"")</f>
+        <v/>
+      </c>
+      <c r="D169" s="13">
+        <f>IF(AND(ISNUMBER(B169),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B169&gt;$D$89,"above UCL",IF(B169&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E169" s="13">
+        <f>IF(AND(ISNUMBER(C169),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C169&gt;$D$90,"above UCL",IF(C169&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>78</v>
+      </c>
+      <c r="B170" s="7" t="n"/>
+      <c r="C170" s="28">
+        <f>IF(AND(ISNUMBER(B170),ISNUMBER(B169)),ABS(B170-B169),"")</f>
+        <v/>
+      </c>
+      <c r="D170" s="13">
+        <f>IF(AND(ISNUMBER(B170),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B170&gt;$D$89,"above UCL",IF(B170&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E170" s="13">
+        <f>IF(AND(ISNUMBER(C170),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C170&gt;$D$90,"above UCL",IF(C170&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>79</v>
+      </c>
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="28">
+        <f>IF(AND(ISNUMBER(B171),ISNUMBER(B170)),ABS(B171-B170),"")</f>
+        <v/>
+      </c>
+      <c r="D171" s="13">
+        <f>IF(AND(ISNUMBER(B171),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B171&gt;$D$89,"above UCL",IF(B171&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E171" s="13">
+        <f>IF(AND(ISNUMBER(C171),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C171&gt;$D$90,"above UCL",IF(C171&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>80</v>
+      </c>
+      <c r="B172" s="7" t="n"/>
+      <c r="C172" s="28">
+        <f>IF(AND(ISNUMBER(B172),ISNUMBER(B171)),ABS(B172-B171),"")</f>
+        <v/>
+      </c>
+      <c r="D172" s="13">
+        <f>IF(AND(ISNUMBER(B172),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B172&gt;$D$89,"above UCL",IF(B172&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E172" s="13">
+        <f>IF(AND(ISNUMBER(C172),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C172&gt;$D$90,"above UCL",IF(C172&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>81</v>
+      </c>
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="28">
+        <f>IF(AND(ISNUMBER(B173),ISNUMBER(B172)),ABS(B173-B172),"")</f>
+        <v/>
+      </c>
+      <c r="D173" s="13">
+        <f>IF(AND(ISNUMBER(B173),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B173&gt;$D$89,"above UCL",IF(B173&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E173" s="13">
+        <f>IF(AND(ISNUMBER(C173),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C173&gt;$D$90,"above UCL",IF(C173&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>82</v>
+      </c>
+      <c r="B174" s="7" t="n"/>
+      <c r="C174" s="28">
+        <f>IF(AND(ISNUMBER(B174),ISNUMBER(B173)),ABS(B174-B173),"")</f>
+        <v/>
+      </c>
+      <c r="D174" s="13">
+        <f>IF(AND(ISNUMBER(B174),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B174&gt;$D$89,"above UCL",IF(B174&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E174" s="13">
+        <f>IF(AND(ISNUMBER(C174),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C174&gt;$D$90,"above UCL",IF(C174&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>83</v>
+      </c>
+      <c r="B175" s="7" t="n"/>
+      <c r="C175" s="28">
+        <f>IF(AND(ISNUMBER(B175),ISNUMBER(B174)),ABS(B175-B174),"")</f>
+        <v/>
+      </c>
+      <c r="D175" s="13">
+        <f>IF(AND(ISNUMBER(B175),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B175&gt;$D$89,"above UCL",IF(B175&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E175" s="13">
+        <f>IF(AND(ISNUMBER(C175),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C175&gt;$D$90,"above UCL",IF(C175&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>84</v>
+      </c>
+      <c r="B176" s="7" t="n"/>
+      <c r="C176" s="28">
+        <f>IF(AND(ISNUMBER(B176),ISNUMBER(B175)),ABS(B176-B175),"")</f>
+        <v/>
+      </c>
+      <c r="D176" s="13">
+        <f>IF(AND(ISNUMBER(B176),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B176&gt;$D$89,"above UCL",IF(B176&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E176" s="13">
+        <f>IF(AND(ISNUMBER(C176),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C176&gt;$D$90,"above UCL",IF(C176&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>85</v>
+      </c>
+      <c r="B177" s="7" t="n"/>
+      <c r="C177" s="28">
+        <f>IF(AND(ISNUMBER(B177),ISNUMBER(B176)),ABS(B177-B176),"")</f>
+        <v/>
+      </c>
+      <c r="D177" s="13">
+        <f>IF(AND(ISNUMBER(B177),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B177&gt;$D$89,"above UCL",IF(B177&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E177" s="13">
+        <f>IF(AND(ISNUMBER(C177),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C177&gt;$D$90,"above UCL",IF(C177&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>86</v>
+      </c>
+      <c r="B178" s="7" t="n"/>
+      <c r="C178" s="28">
+        <f>IF(AND(ISNUMBER(B178),ISNUMBER(B177)),ABS(B178-B177),"")</f>
+        <v/>
+      </c>
+      <c r="D178" s="13">
+        <f>IF(AND(ISNUMBER(B178),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B178&gt;$D$89,"above UCL",IF(B178&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E178" s="13">
+        <f>IF(AND(ISNUMBER(C178),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C178&gt;$D$90,"above UCL",IF(C178&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>87</v>
+      </c>
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="28">
+        <f>IF(AND(ISNUMBER(B179),ISNUMBER(B178)),ABS(B179-B178),"")</f>
+        <v/>
+      </c>
+      <c r="D179" s="13">
+        <f>IF(AND(ISNUMBER(B179),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B179&gt;$D$89,"above UCL",IF(B179&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E179" s="13">
+        <f>IF(AND(ISNUMBER(C179),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C179&gt;$D$90,"above UCL",IF(C179&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>88</v>
+      </c>
+      <c r="B180" s="7" t="n"/>
+      <c r="C180" s="28">
+        <f>IF(AND(ISNUMBER(B180),ISNUMBER(B179)),ABS(B180-B179),"")</f>
+        <v/>
+      </c>
+      <c r="D180" s="13">
+        <f>IF(AND(ISNUMBER(B180),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B180&gt;$D$89,"above UCL",IF(B180&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E180" s="13">
+        <f>IF(AND(ISNUMBER(C180),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C180&gt;$D$90,"above UCL",IF(C180&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>89</v>
+      </c>
+      <c r="B181" s="7" t="n"/>
+      <c r="C181" s="28">
+        <f>IF(AND(ISNUMBER(B181),ISNUMBER(B180)),ABS(B181-B180),"")</f>
+        <v/>
+      </c>
+      <c r="D181" s="13">
+        <f>IF(AND(ISNUMBER(B181),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B181&gt;$D$89,"above UCL",IF(B181&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E181" s="13">
+        <f>IF(AND(ISNUMBER(C181),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C181&gt;$D$90,"above UCL",IF(C181&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>90</v>
+      </c>
+      <c r="B182" s="7" t="n"/>
+      <c r="C182" s="28">
+        <f>IF(AND(ISNUMBER(B182),ISNUMBER(B181)),ABS(B182-B181),"")</f>
+        <v/>
+      </c>
+      <c r="D182" s="13">
+        <f>IF(AND(ISNUMBER(B182),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B182&gt;$D$89,"above UCL",IF(B182&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E182" s="13">
+        <f>IF(AND(ISNUMBER(C182),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C182&gt;$D$90,"above UCL",IF(C182&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>91</v>
+      </c>
+      <c r="B183" s="7" t="n"/>
+      <c r="C183" s="28">
+        <f>IF(AND(ISNUMBER(B183),ISNUMBER(B182)),ABS(B183-B182),"")</f>
+        <v/>
+      </c>
+      <c r="D183" s="13">
+        <f>IF(AND(ISNUMBER(B183),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B183&gt;$D$89,"above UCL",IF(B183&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E183" s="13">
+        <f>IF(AND(ISNUMBER(C183),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C183&gt;$D$90,"above UCL",IF(C183&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>92</v>
+      </c>
+      <c r="B184" s="7" t="n"/>
+      <c r="C184" s="28">
+        <f>IF(AND(ISNUMBER(B184),ISNUMBER(B183)),ABS(B184-B183),"")</f>
+        <v/>
+      </c>
+      <c r="D184" s="13">
+        <f>IF(AND(ISNUMBER(B184),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B184&gt;$D$89,"above UCL",IF(B184&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E184" s="13">
+        <f>IF(AND(ISNUMBER(C184),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C184&gt;$D$90,"above UCL",IF(C184&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>93</v>
+      </c>
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="28">
+        <f>IF(AND(ISNUMBER(B185),ISNUMBER(B184)),ABS(B185-B184),"")</f>
+        <v/>
+      </c>
+      <c r="D185" s="13">
+        <f>IF(AND(ISNUMBER(B185),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B185&gt;$D$89,"above UCL",IF(B185&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E185" s="13">
+        <f>IF(AND(ISNUMBER(C185),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C185&gt;$D$90,"above UCL",IF(C185&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>94</v>
+      </c>
+      <c r="B186" s="7" t="n"/>
+      <c r="C186" s="28">
+        <f>IF(AND(ISNUMBER(B186),ISNUMBER(B185)),ABS(B186-B185),"")</f>
+        <v/>
+      </c>
+      <c r="D186" s="13">
+        <f>IF(AND(ISNUMBER(B186),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B186&gt;$D$89,"above UCL",IF(B186&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E186" s="13">
+        <f>IF(AND(ISNUMBER(C186),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C186&gt;$D$90,"above UCL",IF(C186&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>95</v>
+      </c>
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="28">
+        <f>IF(AND(ISNUMBER(B187),ISNUMBER(B186)),ABS(B187-B186),"")</f>
+        <v/>
+      </c>
+      <c r="D187" s="13">
+        <f>IF(AND(ISNUMBER(B187),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B187&gt;$D$89,"above UCL",IF(B187&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E187" s="13">
+        <f>IF(AND(ISNUMBER(C187),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C187&gt;$D$90,"above UCL",IF(C187&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>96</v>
+      </c>
+      <c r="B188" s="7" t="n"/>
+      <c r="C188" s="28">
+        <f>IF(AND(ISNUMBER(B188),ISNUMBER(B187)),ABS(B188-B187),"")</f>
+        <v/>
+      </c>
+      <c r="D188" s="13">
+        <f>IF(AND(ISNUMBER(B188),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B188&gt;$D$89,"above UCL",IF(B188&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E188" s="13">
+        <f>IF(AND(ISNUMBER(C188),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C188&gt;$D$90,"above UCL",IF(C188&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>97</v>
+      </c>
+      <c r="B189" s="7" t="n"/>
+      <c r="C189" s="28">
+        <f>IF(AND(ISNUMBER(B189),ISNUMBER(B188)),ABS(B189-B188),"")</f>
+        <v/>
+      </c>
+      <c r="D189" s="13">
+        <f>IF(AND(ISNUMBER(B189),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B189&gt;$D$89,"above UCL",IF(B189&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E189" s="13">
+        <f>IF(AND(ISNUMBER(C189),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C189&gt;$D$90,"above UCL",IF(C189&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>98</v>
+      </c>
+      <c r="B190" s="7" t="n"/>
+      <c r="C190" s="28">
+        <f>IF(AND(ISNUMBER(B190),ISNUMBER(B189)),ABS(B190-B189),"")</f>
+        <v/>
+      </c>
+      <c r="D190" s="13">
+        <f>IF(AND(ISNUMBER(B190),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B190&gt;$D$89,"above UCL",IF(B190&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E190" s="13">
+        <f>IF(AND(ISNUMBER(C190),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C190&gt;$D$90,"above UCL",IF(C190&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>99</v>
+      </c>
+      <c r="B191" s="7" t="n"/>
+      <c r="C191" s="28">
+        <f>IF(AND(ISNUMBER(B191),ISNUMBER(B190)),ABS(B191-B190),"")</f>
+        <v/>
+      </c>
+      <c r="D191" s="13">
+        <f>IF(AND(ISNUMBER(B191),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B191&gt;$D$89,"above UCL",IF(B191&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E191" s="13">
+        <f>IF(AND(ISNUMBER(C191),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C191&gt;$D$90,"above UCL",IF(C191&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>100</v>
+      </c>
+      <c r="B192" s="7" t="n"/>
+      <c r="C192" s="28">
+        <f>IF(AND(ISNUMBER(B192),ISNUMBER(B191)),ABS(B192-B191),"")</f>
+        <v/>
+      </c>
+      <c r="D192" s="13">
+        <f>IF(AND(ISNUMBER(B192),ISNUMBER($B$89),ISNUMBER($D$89)),IF(B192&gt;$D$89,"above UCL",IF(B192&lt;$B$89,"below LCL","")),"")</f>
+        <v/>
+      </c>
+      <c r="E192" s="13">
+        <f>IF(AND(ISNUMBER(C192),ISNUMBER($B$90),ISNUMBER($D$90)),IF(C192&gt;$D$90,"above UCL",IF(C192&lt;$B$90,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>3. p chart: fraction defective per subgroup (defectives: pass / fail data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>total inspected (units)</t>
+        </is>
+      </c>
+      <c r="B196" s="24">
+        <f>IF(COUNT(B201:B250)&gt;0,SUM(B201:B250),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>total defectives</t>
+        </is>
+      </c>
+      <c r="B197" s="24">
+        <f>IF(COUNT(B201:B250)&gt;0,SUM(C201:C250),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>p̄ = total defectives / total inspected</t>
+        </is>
+      </c>
+      <c r="B198" s="28">
+        <f>IF(AND(COUNT(B201:B250)&gt;0,B196&gt;0),B197/B196,"")</f>
+        <v/>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 254 (binomial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>Limits per subgroup: centre ± 3 · √(p̄(1 − p̄)/n_i); a negative lower limit is 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>subgroup size n_i</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
+        <is>
+          <t>defectives d_i</t>
+        </is>
+      </c>
+      <c r="D200" s="10" t="inlineStr">
+        <is>
+          <t>p_i</t>
+        </is>
+      </c>
+      <c r="E200" s="10" t="inlineStr">
+        <is>
+          <t>LCL_i</t>
+        </is>
+      </c>
+      <c r="F200" s="10" t="inlineStr">
+        <is>
+          <t>UCL_i</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>1</v>
+      </c>
+      <c r="B201" s="7" t="n"/>
+      <c r="C201" s="7" t="n"/>
+      <c r="D201" s="28">
+        <f>IF(AND(ISNUMBER(B201),ISNUMBER(C201),B201&gt;0,ISNUMBER($B$198)),C201/B201,"")</f>
+        <v/>
+      </c>
+      <c r="E201" s="28">
+        <f>IF(AND(ISNUMBER(B201),ISNUMBER(C201),B201&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B201)),"")</f>
+        <v/>
+      </c>
+      <c r="F201" s="28">
+        <f>IF(AND(ISNUMBER(B201),ISNUMBER(C201),B201&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B201),"")</f>
+        <v/>
+      </c>
+      <c r="G201" s="13">
+        <f>IF(AND(ISNUMBER(D201),ISNUMBER(E201),ISNUMBER(F201)),IF(D201&gt;F201,"above UCL",IF(D201&lt;E201,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2</v>
+      </c>
+      <c r="B202" s="7" t="n"/>
+      <c r="C202" s="7" t="n"/>
+      <c r="D202" s="28">
+        <f>IF(AND(ISNUMBER(B202),ISNUMBER(C202),B202&gt;0,ISNUMBER($B$198)),C202/B202,"")</f>
+        <v/>
+      </c>
+      <c r="E202" s="28">
+        <f>IF(AND(ISNUMBER(B202),ISNUMBER(C202),B202&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B202)),"")</f>
+        <v/>
+      </c>
+      <c r="F202" s="28">
+        <f>IF(AND(ISNUMBER(B202),ISNUMBER(C202),B202&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B202),"")</f>
+        <v/>
+      </c>
+      <c r="G202" s="13">
+        <f>IF(AND(ISNUMBER(D202),ISNUMBER(E202),ISNUMBER(F202)),IF(D202&gt;F202,"above UCL",IF(D202&lt;E202,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3</v>
+      </c>
+      <c r="B203" s="7" t="n"/>
+      <c r="C203" s="7" t="n"/>
+      <c r="D203" s="28">
+        <f>IF(AND(ISNUMBER(B203),ISNUMBER(C203),B203&gt;0,ISNUMBER($B$198)),C203/B203,"")</f>
+        <v/>
+      </c>
+      <c r="E203" s="28">
+        <f>IF(AND(ISNUMBER(B203),ISNUMBER(C203),B203&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B203)),"")</f>
+        <v/>
+      </c>
+      <c r="F203" s="28">
+        <f>IF(AND(ISNUMBER(B203),ISNUMBER(C203),B203&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B203),"")</f>
+        <v/>
+      </c>
+      <c r="G203" s="13">
+        <f>IF(AND(ISNUMBER(D203),ISNUMBER(E203),ISNUMBER(F203)),IF(D203&gt;F203,"above UCL",IF(D203&lt;E203,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4</v>
+      </c>
+      <c r="B204" s="7" t="n"/>
+      <c r="C204" s="7" t="n"/>
+      <c r="D204" s="28">
+        <f>IF(AND(ISNUMBER(B204),ISNUMBER(C204),B204&gt;0,ISNUMBER($B$198)),C204/B204,"")</f>
+        <v/>
+      </c>
+      <c r="E204" s="28">
+        <f>IF(AND(ISNUMBER(B204),ISNUMBER(C204),B204&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B204)),"")</f>
+        <v/>
+      </c>
+      <c r="F204" s="28">
+        <f>IF(AND(ISNUMBER(B204),ISNUMBER(C204),B204&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B204),"")</f>
+        <v/>
+      </c>
+      <c r="G204" s="13">
+        <f>IF(AND(ISNUMBER(D204),ISNUMBER(E204),ISNUMBER(F204)),IF(D204&gt;F204,"above UCL",IF(D204&lt;E204,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>5</v>
+      </c>
+      <c r="B205" s="7" t="n"/>
+      <c r="C205" s="7" t="n"/>
+      <c r="D205" s="28">
+        <f>IF(AND(ISNUMBER(B205),ISNUMBER(C205),B205&gt;0,ISNUMBER($B$198)),C205/B205,"")</f>
+        <v/>
+      </c>
+      <c r="E205" s="28">
+        <f>IF(AND(ISNUMBER(B205),ISNUMBER(C205),B205&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B205)),"")</f>
+        <v/>
+      </c>
+      <c r="F205" s="28">
+        <f>IF(AND(ISNUMBER(B205),ISNUMBER(C205),B205&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B205),"")</f>
+        <v/>
+      </c>
+      <c r="G205" s="13">
+        <f>IF(AND(ISNUMBER(D205),ISNUMBER(E205),ISNUMBER(F205)),IF(D205&gt;F205,"above UCL",IF(D205&lt;E205,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>6</v>
+      </c>
+      <c r="B206" s="7" t="n"/>
+      <c r="C206" s="7" t="n"/>
+      <c r="D206" s="28">
+        <f>IF(AND(ISNUMBER(B206),ISNUMBER(C206),B206&gt;0,ISNUMBER($B$198)),C206/B206,"")</f>
+        <v/>
+      </c>
+      <c r="E206" s="28">
+        <f>IF(AND(ISNUMBER(B206),ISNUMBER(C206),B206&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B206)),"")</f>
+        <v/>
+      </c>
+      <c r="F206" s="28">
+        <f>IF(AND(ISNUMBER(B206),ISNUMBER(C206),B206&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B206),"")</f>
+        <v/>
+      </c>
+      <c r="G206" s="13">
+        <f>IF(AND(ISNUMBER(D206),ISNUMBER(E206),ISNUMBER(F206)),IF(D206&gt;F206,"above UCL",IF(D206&lt;E206,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>7</v>
+      </c>
+      <c r="B207" s="7" t="n"/>
+      <c r="C207" s="7" t="n"/>
+      <c r="D207" s="28">
+        <f>IF(AND(ISNUMBER(B207),ISNUMBER(C207),B207&gt;0,ISNUMBER($B$198)),C207/B207,"")</f>
+        <v/>
+      </c>
+      <c r="E207" s="28">
+        <f>IF(AND(ISNUMBER(B207),ISNUMBER(C207),B207&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B207)),"")</f>
+        <v/>
+      </c>
+      <c r="F207" s="28">
+        <f>IF(AND(ISNUMBER(B207),ISNUMBER(C207),B207&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B207),"")</f>
+        <v/>
+      </c>
+      <c r="G207" s="13">
+        <f>IF(AND(ISNUMBER(D207),ISNUMBER(E207),ISNUMBER(F207)),IF(D207&gt;F207,"above UCL",IF(D207&lt;E207,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>8</v>
+      </c>
+      <c r="B208" s="7" t="n"/>
+      <c r="C208" s="7" t="n"/>
+      <c r="D208" s="28">
+        <f>IF(AND(ISNUMBER(B208),ISNUMBER(C208),B208&gt;0,ISNUMBER($B$198)),C208/B208,"")</f>
+        <v/>
+      </c>
+      <c r="E208" s="28">
+        <f>IF(AND(ISNUMBER(B208),ISNUMBER(C208),B208&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B208)),"")</f>
+        <v/>
+      </c>
+      <c r="F208" s="28">
+        <f>IF(AND(ISNUMBER(B208),ISNUMBER(C208),B208&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B208),"")</f>
+        <v/>
+      </c>
+      <c r="G208" s="13">
+        <f>IF(AND(ISNUMBER(D208),ISNUMBER(E208),ISNUMBER(F208)),IF(D208&gt;F208,"above UCL",IF(D208&lt;E208,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>9</v>
+      </c>
+      <c r="B209" s="7" t="n"/>
+      <c r="C209" s="7" t="n"/>
+      <c r="D209" s="28">
+        <f>IF(AND(ISNUMBER(B209),ISNUMBER(C209),B209&gt;0,ISNUMBER($B$198)),C209/B209,"")</f>
+        <v/>
+      </c>
+      <c r="E209" s="28">
+        <f>IF(AND(ISNUMBER(B209),ISNUMBER(C209),B209&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B209)),"")</f>
+        <v/>
+      </c>
+      <c r="F209" s="28">
+        <f>IF(AND(ISNUMBER(B209),ISNUMBER(C209),B209&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B209),"")</f>
+        <v/>
+      </c>
+      <c r="G209" s="13">
+        <f>IF(AND(ISNUMBER(D209),ISNUMBER(E209),ISNUMBER(F209)),IF(D209&gt;F209,"above UCL",IF(D209&lt;E209,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>10</v>
+      </c>
+      <c r="B210" s="7" t="n"/>
+      <c r="C210" s="7" t="n"/>
+      <c r="D210" s="28">
+        <f>IF(AND(ISNUMBER(B210),ISNUMBER(C210),B210&gt;0,ISNUMBER($B$198)),C210/B210,"")</f>
+        <v/>
+      </c>
+      <c r="E210" s="28">
+        <f>IF(AND(ISNUMBER(B210),ISNUMBER(C210),B210&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B210)),"")</f>
+        <v/>
+      </c>
+      <c r="F210" s="28">
+        <f>IF(AND(ISNUMBER(B210),ISNUMBER(C210),B210&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B210),"")</f>
+        <v/>
+      </c>
+      <c r="G210" s="13">
+        <f>IF(AND(ISNUMBER(D210),ISNUMBER(E210),ISNUMBER(F210)),IF(D210&gt;F210,"above UCL",IF(D210&lt;E210,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>11</v>
+      </c>
+      <c r="B211" s="7" t="n"/>
+      <c r="C211" s="7" t="n"/>
+      <c r="D211" s="28">
+        <f>IF(AND(ISNUMBER(B211),ISNUMBER(C211),B211&gt;0,ISNUMBER($B$198)),C211/B211,"")</f>
+        <v/>
+      </c>
+      <c r="E211" s="28">
+        <f>IF(AND(ISNUMBER(B211),ISNUMBER(C211),B211&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B211)),"")</f>
+        <v/>
+      </c>
+      <c r="F211" s="28">
+        <f>IF(AND(ISNUMBER(B211),ISNUMBER(C211),B211&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B211),"")</f>
+        <v/>
+      </c>
+      <c r="G211" s="13">
+        <f>IF(AND(ISNUMBER(D211),ISNUMBER(E211),ISNUMBER(F211)),IF(D211&gt;F211,"above UCL",IF(D211&lt;E211,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>12</v>
+      </c>
+      <c r="B212" s="7" t="n"/>
+      <c r="C212" s="7" t="n"/>
+      <c r="D212" s="28">
+        <f>IF(AND(ISNUMBER(B212),ISNUMBER(C212),B212&gt;0,ISNUMBER($B$198)),C212/B212,"")</f>
+        <v/>
+      </c>
+      <c r="E212" s="28">
+        <f>IF(AND(ISNUMBER(B212),ISNUMBER(C212),B212&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B212)),"")</f>
+        <v/>
+      </c>
+      <c r="F212" s="28">
+        <f>IF(AND(ISNUMBER(B212),ISNUMBER(C212),B212&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B212),"")</f>
+        <v/>
+      </c>
+      <c r="G212" s="13">
+        <f>IF(AND(ISNUMBER(D212),ISNUMBER(E212),ISNUMBER(F212)),IF(D212&gt;F212,"above UCL",IF(D212&lt;E212,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>13</v>
+      </c>
+      <c r="B213" s="7" t="n"/>
+      <c r="C213" s="7" t="n"/>
+      <c r="D213" s="28">
+        <f>IF(AND(ISNUMBER(B213),ISNUMBER(C213),B213&gt;0,ISNUMBER($B$198)),C213/B213,"")</f>
+        <v/>
+      </c>
+      <c r="E213" s="28">
+        <f>IF(AND(ISNUMBER(B213),ISNUMBER(C213),B213&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B213)),"")</f>
+        <v/>
+      </c>
+      <c r="F213" s="28">
+        <f>IF(AND(ISNUMBER(B213),ISNUMBER(C213),B213&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B213),"")</f>
+        <v/>
+      </c>
+      <c r="G213" s="13">
+        <f>IF(AND(ISNUMBER(D213),ISNUMBER(E213),ISNUMBER(F213)),IF(D213&gt;F213,"above UCL",IF(D213&lt;E213,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>14</v>
+      </c>
+      <c r="B214" s="7" t="n"/>
+      <c r="C214" s="7" t="n"/>
+      <c r="D214" s="28">
+        <f>IF(AND(ISNUMBER(B214),ISNUMBER(C214),B214&gt;0,ISNUMBER($B$198)),C214/B214,"")</f>
+        <v/>
+      </c>
+      <c r="E214" s="28">
+        <f>IF(AND(ISNUMBER(B214),ISNUMBER(C214),B214&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B214)),"")</f>
+        <v/>
+      </c>
+      <c r="F214" s="28">
+        <f>IF(AND(ISNUMBER(B214),ISNUMBER(C214),B214&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B214),"")</f>
+        <v/>
+      </c>
+      <c r="G214" s="13">
+        <f>IF(AND(ISNUMBER(D214),ISNUMBER(E214),ISNUMBER(F214)),IF(D214&gt;F214,"above UCL",IF(D214&lt;E214,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>15</v>
+      </c>
+      <c r="B215" s="7" t="n"/>
+      <c r="C215" s="7" t="n"/>
+      <c r="D215" s="28">
+        <f>IF(AND(ISNUMBER(B215),ISNUMBER(C215),B215&gt;0,ISNUMBER($B$198)),C215/B215,"")</f>
+        <v/>
+      </c>
+      <c r="E215" s="28">
+        <f>IF(AND(ISNUMBER(B215),ISNUMBER(C215),B215&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B215)),"")</f>
+        <v/>
+      </c>
+      <c r="F215" s="28">
+        <f>IF(AND(ISNUMBER(B215),ISNUMBER(C215),B215&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B215),"")</f>
+        <v/>
+      </c>
+      <c r="G215" s="13">
+        <f>IF(AND(ISNUMBER(D215),ISNUMBER(E215),ISNUMBER(F215)),IF(D215&gt;F215,"above UCL",IF(D215&lt;E215,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>16</v>
+      </c>
+      <c r="B216" s="7" t="n"/>
+      <c r="C216" s="7" t="n"/>
+      <c r="D216" s="28">
+        <f>IF(AND(ISNUMBER(B216),ISNUMBER(C216),B216&gt;0,ISNUMBER($B$198)),C216/B216,"")</f>
+        <v/>
+      </c>
+      <c r="E216" s="28">
+        <f>IF(AND(ISNUMBER(B216),ISNUMBER(C216),B216&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B216)),"")</f>
+        <v/>
+      </c>
+      <c r="F216" s="28">
+        <f>IF(AND(ISNUMBER(B216),ISNUMBER(C216),B216&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B216),"")</f>
+        <v/>
+      </c>
+      <c r="G216" s="13">
+        <f>IF(AND(ISNUMBER(D216),ISNUMBER(E216),ISNUMBER(F216)),IF(D216&gt;F216,"above UCL",IF(D216&lt;E216,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>17</v>
+      </c>
+      <c r="B217" s="7" t="n"/>
+      <c r="C217" s="7" t="n"/>
+      <c r="D217" s="28">
+        <f>IF(AND(ISNUMBER(B217),ISNUMBER(C217),B217&gt;0,ISNUMBER($B$198)),C217/B217,"")</f>
+        <v/>
+      </c>
+      <c r="E217" s="28">
+        <f>IF(AND(ISNUMBER(B217),ISNUMBER(C217),B217&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B217)),"")</f>
+        <v/>
+      </c>
+      <c r="F217" s="28">
+        <f>IF(AND(ISNUMBER(B217),ISNUMBER(C217),B217&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B217),"")</f>
+        <v/>
+      </c>
+      <c r="G217" s="13">
+        <f>IF(AND(ISNUMBER(D217),ISNUMBER(E217),ISNUMBER(F217)),IF(D217&gt;F217,"above UCL",IF(D217&lt;E217,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>18</v>
+      </c>
+      <c r="B218" s="7" t="n"/>
+      <c r="C218" s="7" t="n"/>
+      <c r="D218" s="28">
+        <f>IF(AND(ISNUMBER(B218),ISNUMBER(C218),B218&gt;0,ISNUMBER($B$198)),C218/B218,"")</f>
+        <v/>
+      </c>
+      <c r="E218" s="28">
+        <f>IF(AND(ISNUMBER(B218),ISNUMBER(C218),B218&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B218)),"")</f>
+        <v/>
+      </c>
+      <c r="F218" s="28">
+        <f>IF(AND(ISNUMBER(B218),ISNUMBER(C218),B218&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B218),"")</f>
+        <v/>
+      </c>
+      <c r="G218" s="13">
+        <f>IF(AND(ISNUMBER(D218),ISNUMBER(E218),ISNUMBER(F218)),IF(D218&gt;F218,"above UCL",IF(D218&lt;E218,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>19</v>
+      </c>
+      <c r="B219" s="7" t="n"/>
+      <c r="C219" s="7" t="n"/>
+      <c r="D219" s="28">
+        <f>IF(AND(ISNUMBER(B219),ISNUMBER(C219),B219&gt;0,ISNUMBER($B$198)),C219/B219,"")</f>
+        <v/>
+      </c>
+      <c r="E219" s="28">
+        <f>IF(AND(ISNUMBER(B219),ISNUMBER(C219),B219&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B219)),"")</f>
+        <v/>
+      </c>
+      <c r="F219" s="28">
+        <f>IF(AND(ISNUMBER(B219),ISNUMBER(C219),B219&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B219),"")</f>
+        <v/>
+      </c>
+      <c r="G219" s="13">
+        <f>IF(AND(ISNUMBER(D219),ISNUMBER(E219),ISNUMBER(F219)),IF(D219&gt;F219,"above UCL",IF(D219&lt;E219,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>20</v>
+      </c>
+      <c r="B220" s="7" t="n"/>
+      <c r="C220" s="7" t="n"/>
+      <c r="D220" s="28">
+        <f>IF(AND(ISNUMBER(B220),ISNUMBER(C220),B220&gt;0,ISNUMBER($B$198)),C220/B220,"")</f>
+        <v/>
+      </c>
+      <c r="E220" s="28">
+        <f>IF(AND(ISNUMBER(B220),ISNUMBER(C220),B220&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B220)),"")</f>
+        <v/>
+      </c>
+      <c r="F220" s="28">
+        <f>IF(AND(ISNUMBER(B220),ISNUMBER(C220),B220&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B220),"")</f>
+        <v/>
+      </c>
+      <c r="G220" s="13">
+        <f>IF(AND(ISNUMBER(D220),ISNUMBER(E220),ISNUMBER(F220)),IF(D220&gt;F220,"above UCL",IF(D220&lt;E220,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>21</v>
+      </c>
+      <c r="B221" s="7" t="n"/>
+      <c r="C221" s="7" t="n"/>
+      <c r="D221" s="28">
+        <f>IF(AND(ISNUMBER(B221),ISNUMBER(C221),B221&gt;0,ISNUMBER($B$198)),C221/B221,"")</f>
+        <v/>
+      </c>
+      <c r="E221" s="28">
+        <f>IF(AND(ISNUMBER(B221),ISNUMBER(C221),B221&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B221)),"")</f>
+        <v/>
+      </c>
+      <c r="F221" s="28">
+        <f>IF(AND(ISNUMBER(B221),ISNUMBER(C221),B221&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B221),"")</f>
+        <v/>
+      </c>
+      <c r="G221" s="13">
+        <f>IF(AND(ISNUMBER(D221),ISNUMBER(E221),ISNUMBER(F221)),IF(D221&gt;F221,"above UCL",IF(D221&lt;E221,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>22</v>
+      </c>
+      <c r="B222" s="7" t="n"/>
+      <c r="C222" s="7" t="n"/>
+      <c r="D222" s="28">
+        <f>IF(AND(ISNUMBER(B222),ISNUMBER(C222),B222&gt;0,ISNUMBER($B$198)),C222/B222,"")</f>
+        <v/>
+      </c>
+      <c r="E222" s="28">
+        <f>IF(AND(ISNUMBER(B222),ISNUMBER(C222),B222&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B222)),"")</f>
+        <v/>
+      </c>
+      <c r="F222" s="28">
+        <f>IF(AND(ISNUMBER(B222),ISNUMBER(C222),B222&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B222),"")</f>
+        <v/>
+      </c>
+      <c r="G222" s="13">
+        <f>IF(AND(ISNUMBER(D222),ISNUMBER(E222),ISNUMBER(F222)),IF(D222&gt;F222,"above UCL",IF(D222&lt;E222,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>23</v>
+      </c>
+      <c r="B223" s="7" t="n"/>
+      <c r="C223" s="7" t="n"/>
+      <c r="D223" s="28">
+        <f>IF(AND(ISNUMBER(B223),ISNUMBER(C223),B223&gt;0,ISNUMBER($B$198)),C223/B223,"")</f>
+        <v/>
+      </c>
+      <c r="E223" s="28">
+        <f>IF(AND(ISNUMBER(B223),ISNUMBER(C223),B223&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B223)),"")</f>
+        <v/>
+      </c>
+      <c r="F223" s="28">
+        <f>IF(AND(ISNUMBER(B223),ISNUMBER(C223),B223&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B223),"")</f>
+        <v/>
+      </c>
+      <c r="G223" s="13">
+        <f>IF(AND(ISNUMBER(D223),ISNUMBER(E223),ISNUMBER(F223)),IF(D223&gt;F223,"above UCL",IF(D223&lt;E223,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>24</v>
+      </c>
+      <c r="B224" s="7" t="n"/>
+      <c r="C224" s="7" t="n"/>
+      <c r="D224" s="28">
+        <f>IF(AND(ISNUMBER(B224),ISNUMBER(C224),B224&gt;0,ISNUMBER($B$198)),C224/B224,"")</f>
+        <v/>
+      </c>
+      <c r="E224" s="28">
+        <f>IF(AND(ISNUMBER(B224),ISNUMBER(C224),B224&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B224)),"")</f>
+        <v/>
+      </c>
+      <c r="F224" s="28">
+        <f>IF(AND(ISNUMBER(B224),ISNUMBER(C224),B224&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B224),"")</f>
+        <v/>
+      </c>
+      <c r="G224" s="13">
+        <f>IF(AND(ISNUMBER(D224),ISNUMBER(E224),ISNUMBER(F224)),IF(D224&gt;F224,"above UCL",IF(D224&lt;E224,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>25</v>
+      </c>
+      <c r="B225" s="7" t="n"/>
+      <c r="C225" s="7" t="n"/>
+      <c r="D225" s="28">
+        <f>IF(AND(ISNUMBER(B225),ISNUMBER(C225),B225&gt;0,ISNUMBER($B$198)),C225/B225,"")</f>
+        <v/>
+      </c>
+      <c r="E225" s="28">
+        <f>IF(AND(ISNUMBER(B225),ISNUMBER(C225),B225&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B225)),"")</f>
+        <v/>
+      </c>
+      <c r="F225" s="28">
+        <f>IF(AND(ISNUMBER(B225),ISNUMBER(C225),B225&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B225),"")</f>
+        <v/>
+      </c>
+      <c r="G225" s="13">
+        <f>IF(AND(ISNUMBER(D225),ISNUMBER(E225),ISNUMBER(F225)),IF(D225&gt;F225,"above UCL",IF(D225&lt;E225,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>26</v>
+      </c>
+      <c r="B226" s="7" t="n"/>
+      <c r="C226" s="7" t="n"/>
+      <c r="D226" s="28">
+        <f>IF(AND(ISNUMBER(B226),ISNUMBER(C226),B226&gt;0,ISNUMBER($B$198)),C226/B226,"")</f>
+        <v/>
+      </c>
+      <c r="E226" s="28">
+        <f>IF(AND(ISNUMBER(B226),ISNUMBER(C226),B226&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B226)),"")</f>
+        <v/>
+      </c>
+      <c r="F226" s="28">
+        <f>IF(AND(ISNUMBER(B226),ISNUMBER(C226),B226&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B226),"")</f>
+        <v/>
+      </c>
+      <c r="G226" s="13">
+        <f>IF(AND(ISNUMBER(D226),ISNUMBER(E226),ISNUMBER(F226)),IF(D226&gt;F226,"above UCL",IF(D226&lt;E226,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>27</v>
+      </c>
+      <c r="B227" s="7" t="n"/>
+      <c r="C227" s="7" t="n"/>
+      <c r="D227" s="28">
+        <f>IF(AND(ISNUMBER(B227),ISNUMBER(C227),B227&gt;0,ISNUMBER($B$198)),C227/B227,"")</f>
+        <v/>
+      </c>
+      <c r="E227" s="28">
+        <f>IF(AND(ISNUMBER(B227),ISNUMBER(C227),B227&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B227)),"")</f>
+        <v/>
+      </c>
+      <c r="F227" s="28">
+        <f>IF(AND(ISNUMBER(B227),ISNUMBER(C227),B227&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B227),"")</f>
+        <v/>
+      </c>
+      <c r="G227" s="13">
+        <f>IF(AND(ISNUMBER(D227),ISNUMBER(E227),ISNUMBER(F227)),IF(D227&gt;F227,"above UCL",IF(D227&lt;E227,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>28</v>
+      </c>
+      <c r="B228" s="7" t="n"/>
+      <c r="C228" s="7" t="n"/>
+      <c r="D228" s="28">
+        <f>IF(AND(ISNUMBER(B228),ISNUMBER(C228),B228&gt;0,ISNUMBER($B$198)),C228/B228,"")</f>
+        <v/>
+      </c>
+      <c r="E228" s="28">
+        <f>IF(AND(ISNUMBER(B228),ISNUMBER(C228),B228&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B228)),"")</f>
+        <v/>
+      </c>
+      <c r="F228" s="28">
+        <f>IF(AND(ISNUMBER(B228),ISNUMBER(C228),B228&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B228),"")</f>
+        <v/>
+      </c>
+      <c r="G228" s="13">
+        <f>IF(AND(ISNUMBER(D228),ISNUMBER(E228),ISNUMBER(F228)),IF(D228&gt;F228,"above UCL",IF(D228&lt;E228,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>29</v>
+      </c>
+      <c r="B229" s="7" t="n"/>
+      <c r="C229" s="7" t="n"/>
+      <c r="D229" s="28">
+        <f>IF(AND(ISNUMBER(B229),ISNUMBER(C229),B229&gt;0,ISNUMBER($B$198)),C229/B229,"")</f>
+        <v/>
+      </c>
+      <c r="E229" s="28">
+        <f>IF(AND(ISNUMBER(B229),ISNUMBER(C229),B229&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B229)),"")</f>
+        <v/>
+      </c>
+      <c r="F229" s="28">
+        <f>IF(AND(ISNUMBER(B229),ISNUMBER(C229),B229&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B229),"")</f>
+        <v/>
+      </c>
+      <c r="G229" s="13">
+        <f>IF(AND(ISNUMBER(D229),ISNUMBER(E229),ISNUMBER(F229)),IF(D229&gt;F229,"above UCL",IF(D229&lt;E229,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>30</v>
+      </c>
+      <c r="B230" s="7" t="n"/>
+      <c r="C230" s="7" t="n"/>
+      <c r="D230" s="28">
+        <f>IF(AND(ISNUMBER(B230),ISNUMBER(C230),B230&gt;0,ISNUMBER($B$198)),C230/B230,"")</f>
+        <v/>
+      </c>
+      <c r="E230" s="28">
+        <f>IF(AND(ISNUMBER(B230),ISNUMBER(C230),B230&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B230)),"")</f>
+        <v/>
+      </c>
+      <c r="F230" s="28">
+        <f>IF(AND(ISNUMBER(B230),ISNUMBER(C230),B230&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B230),"")</f>
+        <v/>
+      </c>
+      <c r="G230" s="13">
+        <f>IF(AND(ISNUMBER(D230),ISNUMBER(E230),ISNUMBER(F230)),IF(D230&gt;F230,"above UCL",IF(D230&lt;E230,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>31</v>
+      </c>
+      <c r="B231" s="7" t="n"/>
+      <c r="C231" s="7" t="n"/>
+      <c r="D231" s="28">
+        <f>IF(AND(ISNUMBER(B231),ISNUMBER(C231),B231&gt;0,ISNUMBER($B$198)),C231/B231,"")</f>
+        <v/>
+      </c>
+      <c r="E231" s="28">
+        <f>IF(AND(ISNUMBER(B231),ISNUMBER(C231),B231&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B231)),"")</f>
+        <v/>
+      </c>
+      <c r="F231" s="28">
+        <f>IF(AND(ISNUMBER(B231),ISNUMBER(C231),B231&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B231),"")</f>
+        <v/>
+      </c>
+      <c r="G231" s="13">
+        <f>IF(AND(ISNUMBER(D231),ISNUMBER(E231),ISNUMBER(F231)),IF(D231&gt;F231,"above UCL",IF(D231&lt;E231,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>32</v>
+      </c>
+      <c r="B232" s="7" t="n"/>
+      <c r="C232" s="7" t="n"/>
+      <c r="D232" s="28">
+        <f>IF(AND(ISNUMBER(B232),ISNUMBER(C232),B232&gt;0,ISNUMBER($B$198)),C232/B232,"")</f>
+        <v/>
+      </c>
+      <c r="E232" s="28">
+        <f>IF(AND(ISNUMBER(B232),ISNUMBER(C232),B232&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B232)),"")</f>
+        <v/>
+      </c>
+      <c r="F232" s="28">
+        <f>IF(AND(ISNUMBER(B232),ISNUMBER(C232),B232&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B232),"")</f>
+        <v/>
+      </c>
+      <c r="G232" s="13">
+        <f>IF(AND(ISNUMBER(D232),ISNUMBER(E232),ISNUMBER(F232)),IF(D232&gt;F232,"above UCL",IF(D232&lt;E232,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>33</v>
+      </c>
+      <c r="B233" s="7" t="n"/>
+      <c r="C233" s="7" t="n"/>
+      <c r="D233" s="28">
+        <f>IF(AND(ISNUMBER(B233),ISNUMBER(C233),B233&gt;0,ISNUMBER($B$198)),C233/B233,"")</f>
+        <v/>
+      </c>
+      <c r="E233" s="28">
+        <f>IF(AND(ISNUMBER(B233),ISNUMBER(C233),B233&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B233)),"")</f>
+        <v/>
+      </c>
+      <c r="F233" s="28">
+        <f>IF(AND(ISNUMBER(B233),ISNUMBER(C233),B233&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B233),"")</f>
+        <v/>
+      </c>
+      <c r="G233" s="13">
+        <f>IF(AND(ISNUMBER(D233),ISNUMBER(E233),ISNUMBER(F233)),IF(D233&gt;F233,"above UCL",IF(D233&lt;E233,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>34</v>
+      </c>
+      <c r="B234" s="7" t="n"/>
+      <c r="C234" s="7" t="n"/>
+      <c r="D234" s="28">
+        <f>IF(AND(ISNUMBER(B234),ISNUMBER(C234),B234&gt;0,ISNUMBER($B$198)),C234/B234,"")</f>
+        <v/>
+      </c>
+      <c r="E234" s="28">
+        <f>IF(AND(ISNUMBER(B234),ISNUMBER(C234),B234&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B234)),"")</f>
+        <v/>
+      </c>
+      <c r="F234" s="28">
+        <f>IF(AND(ISNUMBER(B234),ISNUMBER(C234),B234&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B234),"")</f>
+        <v/>
+      </c>
+      <c r="G234" s="13">
+        <f>IF(AND(ISNUMBER(D234),ISNUMBER(E234),ISNUMBER(F234)),IF(D234&gt;F234,"above UCL",IF(D234&lt;E234,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>35</v>
+      </c>
+      <c r="B235" s="7" t="n"/>
+      <c r="C235" s="7" t="n"/>
+      <c r="D235" s="28">
+        <f>IF(AND(ISNUMBER(B235),ISNUMBER(C235),B235&gt;0,ISNUMBER($B$198)),C235/B235,"")</f>
+        <v/>
+      </c>
+      <c r="E235" s="28">
+        <f>IF(AND(ISNUMBER(B235),ISNUMBER(C235),B235&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B235)),"")</f>
+        <v/>
+      </c>
+      <c r="F235" s="28">
+        <f>IF(AND(ISNUMBER(B235),ISNUMBER(C235),B235&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B235),"")</f>
+        <v/>
+      </c>
+      <c r="G235" s="13">
+        <f>IF(AND(ISNUMBER(D235),ISNUMBER(E235),ISNUMBER(F235)),IF(D235&gt;F235,"above UCL",IF(D235&lt;E235,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>36</v>
+      </c>
+      <c r="B236" s="7" t="n"/>
+      <c r="C236" s="7" t="n"/>
+      <c r="D236" s="28">
+        <f>IF(AND(ISNUMBER(B236),ISNUMBER(C236),B236&gt;0,ISNUMBER($B$198)),C236/B236,"")</f>
+        <v/>
+      </c>
+      <c r="E236" s="28">
+        <f>IF(AND(ISNUMBER(B236),ISNUMBER(C236),B236&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B236)),"")</f>
+        <v/>
+      </c>
+      <c r="F236" s="28">
+        <f>IF(AND(ISNUMBER(B236),ISNUMBER(C236),B236&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B236),"")</f>
+        <v/>
+      </c>
+      <c r="G236" s="13">
+        <f>IF(AND(ISNUMBER(D236),ISNUMBER(E236),ISNUMBER(F236)),IF(D236&gt;F236,"above UCL",IF(D236&lt;E236,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>37</v>
+      </c>
+      <c r="B237" s="7" t="n"/>
+      <c r="C237" s="7" t="n"/>
+      <c r="D237" s="28">
+        <f>IF(AND(ISNUMBER(B237),ISNUMBER(C237),B237&gt;0,ISNUMBER($B$198)),C237/B237,"")</f>
+        <v/>
+      </c>
+      <c r="E237" s="28">
+        <f>IF(AND(ISNUMBER(B237),ISNUMBER(C237),B237&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B237)),"")</f>
+        <v/>
+      </c>
+      <c r="F237" s="28">
+        <f>IF(AND(ISNUMBER(B237),ISNUMBER(C237),B237&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B237),"")</f>
+        <v/>
+      </c>
+      <c r="G237" s="13">
+        <f>IF(AND(ISNUMBER(D237),ISNUMBER(E237),ISNUMBER(F237)),IF(D237&gt;F237,"above UCL",IF(D237&lt;E237,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>38</v>
+      </c>
+      <c r="B238" s="7" t="n"/>
+      <c r="C238" s="7" t="n"/>
+      <c r="D238" s="28">
+        <f>IF(AND(ISNUMBER(B238),ISNUMBER(C238),B238&gt;0,ISNUMBER($B$198)),C238/B238,"")</f>
+        <v/>
+      </c>
+      <c r="E238" s="28">
+        <f>IF(AND(ISNUMBER(B238),ISNUMBER(C238),B238&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B238)),"")</f>
+        <v/>
+      </c>
+      <c r="F238" s="28">
+        <f>IF(AND(ISNUMBER(B238),ISNUMBER(C238),B238&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B238),"")</f>
+        <v/>
+      </c>
+      <c r="G238" s="13">
+        <f>IF(AND(ISNUMBER(D238),ISNUMBER(E238),ISNUMBER(F238)),IF(D238&gt;F238,"above UCL",IF(D238&lt;E238,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>39</v>
+      </c>
+      <c r="B239" s="7" t="n"/>
+      <c r="C239" s="7" t="n"/>
+      <c r="D239" s="28">
+        <f>IF(AND(ISNUMBER(B239),ISNUMBER(C239),B239&gt;0,ISNUMBER($B$198)),C239/B239,"")</f>
+        <v/>
+      </c>
+      <c r="E239" s="28">
+        <f>IF(AND(ISNUMBER(B239),ISNUMBER(C239),B239&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B239)),"")</f>
+        <v/>
+      </c>
+      <c r="F239" s="28">
+        <f>IF(AND(ISNUMBER(B239),ISNUMBER(C239),B239&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B239),"")</f>
+        <v/>
+      </c>
+      <c r="G239" s="13">
+        <f>IF(AND(ISNUMBER(D239),ISNUMBER(E239),ISNUMBER(F239)),IF(D239&gt;F239,"above UCL",IF(D239&lt;E239,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>40</v>
+      </c>
+      <c r="B240" s="7" t="n"/>
+      <c r="C240" s="7" t="n"/>
+      <c r="D240" s="28">
+        <f>IF(AND(ISNUMBER(B240),ISNUMBER(C240),B240&gt;0,ISNUMBER($B$198)),C240/B240,"")</f>
+        <v/>
+      </c>
+      <c r="E240" s="28">
+        <f>IF(AND(ISNUMBER(B240),ISNUMBER(C240),B240&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B240)),"")</f>
+        <v/>
+      </c>
+      <c r="F240" s="28">
+        <f>IF(AND(ISNUMBER(B240),ISNUMBER(C240),B240&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B240),"")</f>
+        <v/>
+      </c>
+      <c r="G240" s="13">
+        <f>IF(AND(ISNUMBER(D240),ISNUMBER(E240),ISNUMBER(F240)),IF(D240&gt;F240,"above UCL",IF(D240&lt;E240,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>41</v>
+      </c>
+      <c r="B241" s="7" t="n"/>
+      <c r="C241" s="7" t="n"/>
+      <c r="D241" s="28">
+        <f>IF(AND(ISNUMBER(B241),ISNUMBER(C241),B241&gt;0,ISNUMBER($B$198)),C241/B241,"")</f>
+        <v/>
+      </c>
+      <c r="E241" s="28">
+        <f>IF(AND(ISNUMBER(B241),ISNUMBER(C241),B241&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B241)),"")</f>
+        <v/>
+      </c>
+      <c r="F241" s="28">
+        <f>IF(AND(ISNUMBER(B241),ISNUMBER(C241),B241&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B241),"")</f>
+        <v/>
+      </c>
+      <c r="G241" s="13">
+        <f>IF(AND(ISNUMBER(D241),ISNUMBER(E241),ISNUMBER(F241)),IF(D241&gt;F241,"above UCL",IF(D241&lt;E241,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>42</v>
+      </c>
+      <c r="B242" s="7" t="n"/>
+      <c r="C242" s="7" t="n"/>
+      <c r="D242" s="28">
+        <f>IF(AND(ISNUMBER(B242),ISNUMBER(C242),B242&gt;0,ISNUMBER($B$198)),C242/B242,"")</f>
+        <v/>
+      </c>
+      <c r="E242" s="28">
+        <f>IF(AND(ISNUMBER(B242),ISNUMBER(C242),B242&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B242)),"")</f>
+        <v/>
+      </c>
+      <c r="F242" s="28">
+        <f>IF(AND(ISNUMBER(B242),ISNUMBER(C242),B242&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B242),"")</f>
+        <v/>
+      </c>
+      <c r="G242" s="13">
+        <f>IF(AND(ISNUMBER(D242),ISNUMBER(E242),ISNUMBER(F242)),IF(D242&gt;F242,"above UCL",IF(D242&lt;E242,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>43</v>
+      </c>
+      <c r="B243" s="7" t="n"/>
+      <c r="C243" s="7" t="n"/>
+      <c r="D243" s="28">
+        <f>IF(AND(ISNUMBER(B243),ISNUMBER(C243),B243&gt;0,ISNUMBER($B$198)),C243/B243,"")</f>
+        <v/>
+      </c>
+      <c r="E243" s="28">
+        <f>IF(AND(ISNUMBER(B243),ISNUMBER(C243),B243&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B243)),"")</f>
+        <v/>
+      </c>
+      <c r="F243" s="28">
+        <f>IF(AND(ISNUMBER(B243),ISNUMBER(C243),B243&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B243),"")</f>
+        <v/>
+      </c>
+      <c r="G243" s="13">
+        <f>IF(AND(ISNUMBER(D243),ISNUMBER(E243),ISNUMBER(F243)),IF(D243&gt;F243,"above UCL",IF(D243&lt;E243,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>44</v>
+      </c>
+      <c r="B244" s="7" t="n"/>
+      <c r="C244" s="7" t="n"/>
+      <c r="D244" s="28">
+        <f>IF(AND(ISNUMBER(B244),ISNUMBER(C244),B244&gt;0,ISNUMBER($B$198)),C244/B244,"")</f>
+        <v/>
+      </c>
+      <c r="E244" s="28">
+        <f>IF(AND(ISNUMBER(B244),ISNUMBER(C244),B244&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B244)),"")</f>
+        <v/>
+      </c>
+      <c r="F244" s="28">
+        <f>IF(AND(ISNUMBER(B244),ISNUMBER(C244),B244&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B244),"")</f>
+        <v/>
+      </c>
+      <c r="G244" s="13">
+        <f>IF(AND(ISNUMBER(D244),ISNUMBER(E244),ISNUMBER(F244)),IF(D244&gt;F244,"above UCL",IF(D244&lt;E244,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>45</v>
+      </c>
+      <c r="B245" s="7" t="n"/>
+      <c r="C245" s="7" t="n"/>
+      <c r="D245" s="28">
+        <f>IF(AND(ISNUMBER(B245),ISNUMBER(C245),B245&gt;0,ISNUMBER($B$198)),C245/B245,"")</f>
+        <v/>
+      </c>
+      <c r="E245" s="28">
+        <f>IF(AND(ISNUMBER(B245),ISNUMBER(C245),B245&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B245)),"")</f>
+        <v/>
+      </c>
+      <c r="F245" s="28">
+        <f>IF(AND(ISNUMBER(B245),ISNUMBER(C245),B245&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B245),"")</f>
+        <v/>
+      </c>
+      <c r="G245" s="13">
+        <f>IF(AND(ISNUMBER(D245),ISNUMBER(E245),ISNUMBER(F245)),IF(D245&gt;F245,"above UCL",IF(D245&lt;E245,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>46</v>
+      </c>
+      <c r="B246" s="7" t="n"/>
+      <c r="C246" s="7" t="n"/>
+      <c r="D246" s="28">
+        <f>IF(AND(ISNUMBER(B246),ISNUMBER(C246),B246&gt;0,ISNUMBER($B$198)),C246/B246,"")</f>
+        <v/>
+      </c>
+      <c r="E246" s="28">
+        <f>IF(AND(ISNUMBER(B246),ISNUMBER(C246),B246&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B246)),"")</f>
+        <v/>
+      </c>
+      <c r="F246" s="28">
+        <f>IF(AND(ISNUMBER(B246),ISNUMBER(C246),B246&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B246),"")</f>
+        <v/>
+      </c>
+      <c r="G246" s="13">
+        <f>IF(AND(ISNUMBER(D246),ISNUMBER(E246),ISNUMBER(F246)),IF(D246&gt;F246,"above UCL",IF(D246&lt;E246,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>47</v>
+      </c>
+      <c r="B247" s="7" t="n"/>
+      <c r="C247" s="7" t="n"/>
+      <c r="D247" s="28">
+        <f>IF(AND(ISNUMBER(B247),ISNUMBER(C247),B247&gt;0,ISNUMBER($B$198)),C247/B247,"")</f>
+        <v/>
+      </c>
+      <c r="E247" s="28">
+        <f>IF(AND(ISNUMBER(B247),ISNUMBER(C247),B247&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B247)),"")</f>
+        <v/>
+      </c>
+      <c r="F247" s="28">
+        <f>IF(AND(ISNUMBER(B247),ISNUMBER(C247),B247&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B247),"")</f>
+        <v/>
+      </c>
+      <c r="G247" s="13">
+        <f>IF(AND(ISNUMBER(D247),ISNUMBER(E247),ISNUMBER(F247)),IF(D247&gt;F247,"above UCL",IF(D247&lt;E247,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>48</v>
+      </c>
+      <c r="B248" s="7" t="n"/>
+      <c r="C248" s="7" t="n"/>
+      <c r="D248" s="28">
+        <f>IF(AND(ISNUMBER(B248),ISNUMBER(C248),B248&gt;0,ISNUMBER($B$198)),C248/B248,"")</f>
+        <v/>
+      </c>
+      <c r="E248" s="28">
+        <f>IF(AND(ISNUMBER(B248),ISNUMBER(C248),B248&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B248)),"")</f>
+        <v/>
+      </c>
+      <c r="F248" s="28">
+        <f>IF(AND(ISNUMBER(B248),ISNUMBER(C248),B248&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B248),"")</f>
+        <v/>
+      </c>
+      <c r="G248" s="13">
+        <f>IF(AND(ISNUMBER(D248),ISNUMBER(E248),ISNUMBER(F248)),IF(D248&gt;F248,"above UCL",IF(D248&lt;E248,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>49</v>
+      </c>
+      <c r="B249" s="7" t="n"/>
+      <c r="C249" s="7" t="n"/>
+      <c r="D249" s="28">
+        <f>IF(AND(ISNUMBER(B249),ISNUMBER(C249),B249&gt;0,ISNUMBER($B$198)),C249/B249,"")</f>
+        <v/>
+      </c>
+      <c r="E249" s="28">
+        <f>IF(AND(ISNUMBER(B249),ISNUMBER(C249),B249&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B249)),"")</f>
+        <v/>
+      </c>
+      <c r="F249" s="28">
+        <f>IF(AND(ISNUMBER(B249),ISNUMBER(C249),B249&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B249),"")</f>
+        <v/>
+      </c>
+      <c r="G249" s="13">
+        <f>IF(AND(ISNUMBER(D249),ISNUMBER(E249),ISNUMBER(F249)),IF(D249&gt;F249,"above UCL",IF(D249&lt;E249,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>50</v>
+      </c>
+      <c r="B250" s="7" t="n"/>
+      <c r="C250" s="7" t="n"/>
+      <c r="D250" s="28">
+        <f>IF(AND(ISNUMBER(B250),ISNUMBER(C250),B250&gt;0,ISNUMBER($B$198)),C250/B250,"")</f>
+        <v/>
+      </c>
+      <c r="E250" s="28">
+        <f>IF(AND(ISNUMBER(B250),ISNUMBER(C250),B250&gt;0,ISNUMBER($B$198)),MAX(0,$B$198-3*SQRT($B$198*(1-$B$198)/B250)),"")</f>
+        <v/>
+      </c>
+      <c r="F250" s="28">
+        <f>IF(AND(ISNUMBER(B250),ISNUMBER(C250),B250&gt;0,ISNUMBER($B$198)),$B$198+3*SQRT($B$198*(1-$B$198)/B250),"")</f>
+        <v/>
+      </c>
+      <c r="G250" s="13">
+        <f>IF(AND(ISNUMBER(D250),ISNUMBER(E250),ISNUMBER(F250)),IF(D250&gt;F250,"above UCL",IF(D250&lt;E250,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="inlineStr">
+        <is>
+          <t>4. u chart: defects per unit per subgroup (defects: count data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>total inspected (units)</t>
+        </is>
+      </c>
+      <c r="B254" s="24">
+        <f>IF(COUNT(B259:B308)&gt;0,SUM(B259:B308),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>total defects</t>
+        </is>
+      </c>
+      <c r="B255" s="24">
+        <f>IF(COUNT(B259:B308)&gt;0,SUM(C259:C308),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>ū = total defects / total units</t>
+        </is>
+      </c>
+      <c r="B256" s="28">
+        <f>IF(AND(COUNT(B259:B308)&gt;0,B254&gt;0),B255/B254,"")</f>
+        <v/>
+      </c>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>Dummies p. 254 (Poisson)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>Limits per subgroup: centre ± 3 · √(ū/n_i); a negative lower limit is 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="10" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B258" s="10" t="inlineStr">
+        <is>
+          <t>subgroup size n_i</t>
+        </is>
+      </c>
+      <c r="C258" s="10" t="inlineStr">
+        <is>
+          <t>defects c_i</t>
+        </is>
+      </c>
+      <c r="D258" s="10" t="inlineStr">
+        <is>
+          <t>u_i</t>
+        </is>
+      </c>
+      <c r="E258" s="10" t="inlineStr">
+        <is>
+          <t>LCL_i</t>
+        </is>
+      </c>
+      <c r="F258" s="10" t="inlineStr">
+        <is>
+          <t>UCL_i</t>
+        </is>
+      </c>
+      <c r="G258" s="10" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>1</v>
+      </c>
+      <c r="B259" s="7" t="n"/>
+      <c r="C259" s="7" t="n"/>
+      <c r="D259" s="28">
+        <f>IF(AND(ISNUMBER(B259),ISNUMBER(C259),B259&gt;0,ISNUMBER($B$256)),C259/B259,"")</f>
+        <v/>
+      </c>
+      <c r="E259" s="28">
+        <f>IF(AND(ISNUMBER(B259),ISNUMBER(C259),B259&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B259)),"")</f>
+        <v/>
+      </c>
+      <c r="F259" s="28">
+        <f>IF(AND(ISNUMBER(B259),ISNUMBER(C259),B259&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B259),"")</f>
+        <v/>
+      </c>
+      <c r="G259" s="13">
+        <f>IF(AND(ISNUMBER(D259),ISNUMBER(E259),ISNUMBER(F259)),IF(D259&gt;F259,"above UCL",IF(D259&lt;E259,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2</v>
+      </c>
+      <c r="B260" s="7" t="n"/>
+      <c r="C260" s="7" t="n"/>
+      <c r="D260" s="28">
+        <f>IF(AND(ISNUMBER(B260),ISNUMBER(C260),B260&gt;0,ISNUMBER($B$256)),C260/B260,"")</f>
+        <v/>
+      </c>
+      <c r="E260" s="28">
+        <f>IF(AND(ISNUMBER(B260),ISNUMBER(C260),B260&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B260)),"")</f>
+        <v/>
+      </c>
+      <c r="F260" s="28">
+        <f>IF(AND(ISNUMBER(B260),ISNUMBER(C260),B260&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B260),"")</f>
+        <v/>
+      </c>
+      <c r="G260" s="13">
+        <f>IF(AND(ISNUMBER(D260),ISNUMBER(E260),ISNUMBER(F260)),IF(D260&gt;F260,"above UCL",IF(D260&lt;E260,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>3</v>
+      </c>
+      <c r="B261" s="7" t="n"/>
+      <c r="C261" s="7" t="n"/>
+      <c r="D261" s="28">
+        <f>IF(AND(ISNUMBER(B261),ISNUMBER(C261),B261&gt;0,ISNUMBER($B$256)),C261/B261,"")</f>
+        <v/>
+      </c>
+      <c r="E261" s="28">
+        <f>IF(AND(ISNUMBER(B261),ISNUMBER(C261),B261&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B261)),"")</f>
+        <v/>
+      </c>
+      <c r="F261" s="28">
+        <f>IF(AND(ISNUMBER(B261),ISNUMBER(C261),B261&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B261),"")</f>
+        <v/>
+      </c>
+      <c r="G261" s="13">
+        <f>IF(AND(ISNUMBER(D261),ISNUMBER(E261),ISNUMBER(F261)),IF(D261&gt;F261,"above UCL",IF(D261&lt;E261,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>4</v>
+      </c>
+      <c r="B262" s="7" t="n"/>
+      <c r="C262" s="7" t="n"/>
+      <c r="D262" s="28">
+        <f>IF(AND(ISNUMBER(B262),ISNUMBER(C262),B262&gt;0,ISNUMBER($B$256)),C262/B262,"")</f>
+        <v/>
+      </c>
+      <c r="E262" s="28">
+        <f>IF(AND(ISNUMBER(B262),ISNUMBER(C262),B262&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B262)),"")</f>
+        <v/>
+      </c>
+      <c r="F262" s="28">
+        <f>IF(AND(ISNUMBER(B262),ISNUMBER(C262),B262&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B262),"")</f>
+        <v/>
+      </c>
+      <c r="G262" s="13">
+        <f>IF(AND(ISNUMBER(D262),ISNUMBER(E262),ISNUMBER(F262)),IF(D262&gt;F262,"above UCL",IF(D262&lt;E262,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>5</v>
+      </c>
+      <c r="B263" s="7" t="n"/>
+      <c r="C263" s="7" t="n"/>
+      <c r="D263" s="28">
+        <f>IF(AND(ISNUMBER(B263),ISNUMBER(C263),B263&gt;0,ISNUMBER($B$256)),C263/B263,"")</f>
+        <v/>
+      </c>
+      <c r="E263" s="28">
+        <f>IF(AND(ISNUMBER(B263),ISNUMBER(C263),B263&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B263)),"")</f>
+        <v/>
+      </c>
+      <c r="F263" s="28">
+        <f>IF(AND(ISNUMBER(B263),ISNUMBER(C263),B263&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B263),"")</f>
+        <v/>
+      </c>
+      <c r="G263" s="13">
+        <f>IF(AND(ISNUMBER(D263),ISNUMBER(E263),ISNUMBER(F263)),IF(D263&gt;F263,"above UCL",IF(D263&lt;E263,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>6</v>
+      </c>
+      <c r="B264" s="7" t="n"/>
+      <c r="C264" s="7" t="n"/>
+      <c r="D264" s="28">
+        <f>IF(AND(ISNUMBER(B264),ISNUMBER(C264),B264&gt;0,ISNUMBER($B$256)),C264/B264,"")</f>
+        <v/>
+      </c>
+      <c r="E264" s="28">
+        <f>IF(AND(ISNUMBER(B264),ISNUMBER(C264),B264&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B264)),"")</f>
+        <v/>
+      </c>
+      <c r="F264" s="28">
+        <f>IF(AND(ISNUMBER(B264),ISNUMBER(C264),B264&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B264),"")</f>
+        <v/>
+      </c>
+      <c r="G264" s="13">
+        <f>IF(AND(ISNUMBER(D264),ISNUMBER(E264),ISNUMBER(F264)),IF(D264&gt;F264,"above UCL",IF(D264&lt;E264,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>7</v>
+      </c>
+      <c r="B265" s="7" t="n"/>
+      <c r="C265" s="7" t="n"/>
+      <c r="D265" s="28">
+        <f>IF(AND(ISNUMBER(B265),ISNUMBER(C265),B265&gt;0,ISNUMBER($B$256)),C265/B265,"")</f>
+        <v/>
+      </c>
+      <c r="E265" s="28">
+        <f>IF(AND(ISNUMBER(B265),ISNUMBER(C265),B265&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B265)),"")</f>
+        <v/>
+      </c>
+      <c r="F265" s="28">
+        <f>IF(AND(ISNUMBER(B265),ISNUMBER(C265),B265&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B265),"")</f>
+        <v/>
+      </c>
+      <c r="G265" s="13">
+        <f>IF(AND(ISNUMBER(D265),ISNUMBER(E265),ISNUMBER(F265)),IF(D265&gt;F265,"above UCL",IF(D265&lt;E265,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>8</v>
+      </c>
+      <c r="B266" s="7" t="n"/>
+      <c r="C266" s="7" t="n"/>
+      <c r="D266" s="28">
+        <f>IF(AND(ISNUMBER(B266),ISNUMBER(C266),B266&gt;0,ISNUMBER($B$256)),C266/B266,"")</f>
+        <v/>
+      </c>
+      <c r="E266" s="28">
+        <f>IF(AND(ISNUMBER(B266),ISNUMBER(C266),B266&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B266)),"")</f>
+        <v/>
+      </c>
+      <c r="F266" s="28">
+        <f>IF(AND(ISNUMBER(B266),ISNUMBER(C266),B266&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B266),"")</f>
+        <v/>
+      </c>
+      <c r="G266" s="13">
+        <f>IF(AND(ISNUMBER(D266),ISNUMBER(E266),ISNUMBER(F266)),IF(D266&gt;F266,"above UCL",IF(D266&lt;E266,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>9</v>
+      </c>
+      <c r="B267" s="7" t="n"/>
+      <c r="C267" s="7" t="n"/>
+      <c r="D267" s="28">
+        <f>IF(AND(ISNUMBER(B267),ISNUMBER(C267),B267&gt;0,ISNUMBER($B$256)),C267/B267,"")</f>
+        <v/>
+      </c>
+      <c r="E267" s="28">
+        <f>IF(AND(ISNUMBER(B267),ISNUMBER(C267),B267&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B267)),"")</f>
+        <v/>
+      </c>
+      <c r="F267" s="28">
+        <f>IF(AND(ISNUMBER(B267),ISNUMBER(C267),B267&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B267),"")</f>
+        <v/>
+      </c>
+      <c r="G267" s="13">
+        <f>IF(AND(ISNUMBER(D267),ISNUMBER(E267),ISNUMBER(F267)),IF(D267&gt;F267,"above UCL",IF(D267&lt;E267,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>10</v>
+      </c>
+      <c r="B268" s="7" t="n"/>
+      <c r="C268" s="7" t="n"/>
+      <c r="D268" s="28">
+        <f>IF(AND(ISNUMBER(B268),ISNUMBER(C268),B268&gt;0,ISNUMBER($B$256)),C268/B268,"")</f>
+        <v/>
+      </c>
+      <c r="E268" s="28">
+        <f>IF(AND(ISNUMBER(B268),ISNUMBER(C268),B268&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B268)),"")</f>
+        <v/>
+      </c>
+      <c r="F268" s="28">
+        <f>IF(AND(ISNUMBER(B268),ISNUMBER(C268),B268&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B268),"")</f>
+        <v/>
+      </c>
+      <c r="G268" s="13">
+        <f>IF(AND(ISNUMBER(D268),ISNUMBER(E268),ISNUMBER(F268)),IF(D268&gt;F268,"above UCL",IF(D268&lt;E268,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>11</v>
+      </c>
+      <c r="B269" s="7" t="n"/>
+      <c r="C269" s="7" t="n"/>
+      <c r="D269" s="28">
+        <f>IF(AND(ISNUMBER(B269),ISNUMBER(C269),B269&gt;0,ISNUMBER($B$256)),C269/B269,"")</f>
+        <v/>
+      </c>
+      <c r="E269" s="28">
+        <f>IF(AND(ISNUMBER(B269),ISNUMBER(C269),B269&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B269)),"")</f>
+        <v/>
+      </c>
+      <c r="F269" s="28">
+        <f>IF(AND(ISNUMBER(B269),ISNUMBER(C269),B269&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B269),"")</f>
+        <v/>
+      </c>
+      <c r="G269" s="13">
+        <f>IF(AND(ISNUMBER(D269),ISNUMBER(E269),ISNUMBER(F269)),IF(D269&gt;F269,"above UCL",IF(D269&lt;E269,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>12</v>
+      </c>
+      <c r="B270" s="7" t="n"/>
+      <c r="C270" s="7" t="n"/>
+      <c r="D270" s="28">
+        <f>IF(AND(ISNUMBER(B270),ISNUMBER(C270),B270&gt;0,ISNUMBER($B$256)),C270/B270,"")</f>
+        <v/>
+      </c>
+      <c r="E270" s="28">
+        <f>IF(AND(ISNUMBER(B270),ISNUMBER(C270),B270&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B270)),"")</f>
+        <v/>
+      </c>
+      <c r="F270" s="28">
+        <f>IF(AND(ISNUMBER(B270),ISNUMBER(C270),B270&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B270),"")</f>
+        <v/>
+      </c>
+      <c r="G270" s="13">
+        <f>IF(AND(ISNUMBER(D270),ISNUMBER(E270),ISNUMBER(F270)),IF(D270&gt;F270,"above UCL",IF(D270&lt;E270,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>13</v>
+      </c>
+      <c r="B271" s="7" t="n"/>
+      <c r="C271" s="7" t="n"/>
+      <c r="D271" s="28">
+        <f>IF(AND(ISNUMBER(B271),ISNUMBER(C271),B271&gt;0,ISNUMBER($B$256)),C271/B271,"")</f>
+        <v/>
+      </c>
+      <c r="E271" s="28">
+        <f>IF(AND(ISNUMBER(B271),ISNUMBER(C271),B271&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B271)),"")</f>
+        <v/>
+      </c>
+      <c r="F271" s="28">
+        <f>IF(AND(ISNUMBER(B271),ISNUMBER(C271),B271&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B271),"")</f>
+        <v/>
+      </c>
+      <c r="G271" s="13">
+        <f>IF(AND(ISNUMBER(D271),ISNUMBER(E271),ISNUMBER(F271)),IF(D271&gt;F271,"above UCL",IF(D271&lt;E271,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>14</v>
+      </c>
+      <c r="B272" s="7" t="n"/>
+      <c r="C272" s="7" t="n"/>
+      <c r="D272" s="28">
+        <f>IF(AND(ISNUMBER(B272),ISNUMBER(C272),B272&gt;0,ISNUMBER($B$256)),C272/B272,"")</f>
+        <v/>
+      </c>
+      <c r="E272" s="28">
+        <f>IF(AND(ISNUMBER(B272),ISNUMBER(C272),B272&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B272)),"")</f>
+        <v/>
+      </c>
+      <c r="F272" s="28">
+        <f>IF(AND(ISNUMBER(B272),ISNUMBER(C272),B272&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B272),"")</f>
+        <v/>
+      </c>
+      <c r="G272" s="13">
+        <f>IF(AND(ISNUMBER(D272),ISNUMBER(E272),ISNUMBER(F272)),IF(D272&gt;F272,"above UCL",IF(D272&lt;E272,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>15</v>
+      </c>
+      <c r="B273" s="7" t="n"/>
+      <c r="C273" s="7" t="n"/>
+      <c r="D273" s="28">
+        <f>IF(AND(ISNUMBER(B273),ISNUMBER(C273),B273&gt;0,ISNUMBER($B$256)),C273/B273,"")</f>
+        <v/>
+      </c>
+      <c r="E273" s="28">
+        <f>IF(AND(ISNUMBER(B273),ISNUMBER(C273),B273&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B273)),"")</f>
+        <v/>
+      </c>
+      <c r="F273" s="28">
+        <f>IF(AND(ISNUMBER(B273),ISNUMBER(C273),B273&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B273),"")</f>
+        <v/>
+      </c>
+      <c r="G273" s="13">
+        <f>IF(AND(ISNUMBER(D273),ISNUMBER(E273),ISNUMBER(F273)),IF(D273&gt;F273,"above UCL",IF(D273&lt;E273,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>16</v>
+      </c>
+      <c r="B274" s="7" t="n"/>
+      <c r="C274" s="7" t="n"/>
+      <c r="D274" s="28">
+        <f>IF(AND(ISNUMBER(B274),ISNUMBER(C274),B274&gt;0,ISNUMBER($B$256)),C274/B274,"")</f>
+        <v/>
+      </c>
+      <c r="E274" s="28">
+        <f>IF(AND(ISNUMBER(B274),ISNUMBER(C274),B274&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B274)),"")</f>
+        <v/>
+      </c>
+      <c r="F274" s="28">
+        <f>IF(AND(ISNUMBER(B274),ISNUMBER(C274),B274&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B274),"")</f>
+        <v/>
+      </c>
+      <c r="G274" s="13">
+        <f>IF(AND(ISNUMBER(D274),ISNUMBER(E274),ISNUMBER(F274)),IF(D274&gt;F274,"above UCL",IF(D274&lt;E274,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>17</v>
+      </c>
+      <c r="B275" s="7" t="n"/>
+      <c r="C275" s="7" t="n"/>
+      <c r="D275" s="28">
+        <f>IF(AND(ISNUMBER(B275),ISNUMBER(C275),B275&gt;0,ISNUMBER($B$256)),C275/B275,"")</f>
+        <v/>
+      </c>
+      <c r="E275" s="28">
+        <f>IF(AND(ISNUMBER(B275),ISNUMBER(C275),B275&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B275)),"")</f>
+        <v/>
+      </c>
+      <c r="F275" s="28">
+        <f>IF(AND(ISNUMBER(B275),ISNUMBER(C275),B275&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B275),"")</f>
+        <v/>
+      </c>
+      <c r="G275" s="13">
+        <f>IF(AND(ISNUMBER(D275),ISNUMBER(E275),ISNUMBER(F275)),IF(D275&gt;F275,"above UCL",IF(D275&lt;E275,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>18</v>
+      </c>
+      <c r="B276" s="7" t="n"/>
+      <c r="C276" s="7" t="n"/>
+      <c r="D276" s="28">
+        <f>IF(AND(ISNUMBER(B276),ISNUMBER(C276),B276&gt;0,ISNUMBER($B$256)),C276/B276,"")</f>
+        <v/>
+      </c>
+      <c r="E276" s="28">
+        <f>IF(AND(ISNUMBER(B276),ISNUMBER(C276),B276&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B276)),"")</f>
+        <v/>
+      </c>
+      <c r="F276" s="28">
+        <f>IF(AND(ISNUMBER(B276),ISNUMBER(C276),B276&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B276),"")</f>
+        <v/>
+      </c>
+      <c r="G276" s="13">
+        <f>IF(AND(ISNUMBER(D276),ISNUMBER(E276),ISNUMBER(F276)),IF(D276&gt;F276,"above UCL",IF(D276&lt;E276,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>19</v>
+      </c>
+      <c r="B277" s="7" t="n"/>
+      <c r="C277" s="7" t="n"/>
+      <c r="D277" s="28">
+        <f>IF(AND(ISNUMBER(B277),ISNUMBER(C277),B277&gt;0,ISNUMBER($B$256)),C277/B277,"")</f>
+        <v/>
+      </c>
+      <c r="E277" s="28">
+        <f>IF(AND(ISNUMBER(B277),ISNUMBER(C277),B277&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B277)),"")</f>
+        <v/>
+      </c>
+      <c r="F277" s="28">
+        <f>IF(AND(ISNUMBER(B277),ISNUMBER(C277),B277&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B277),"")</f>
+        <v/>
+      </c>
+      <c r="G277" s="13">
+        <f>IF(AND(ISNUMBER(D277),ISNUMBER(E277),ISNUMBER(F277)),IF(D277&gt;F277,"above UCL",IF(D277&lt;E277,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>20</v>
+      </c>
+      <c r="B278" s="7" t="n"/>
+      <c r="C278" s="7" t="n"/>
+      <c r="D278" s="28">
+        <f>IF(AND(ISNUMBER(B278),ISNUMBER(C278),B278&gt;0,ISNUMBER($B$256)),C278/B278,"")</f>
+        <v/>
+      </c>
+      <c r="E278" s="28">
+        <f>IF(AND(ISNUMBER(B278),ISNUMBER(C278),B278&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B278)),"")</f>
+        <v/>
+      </c>
+      <c r="F278" s="28">
+        <f>IF(AND(ISNUMBER(B278),ISNUMBER(C278),B278&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B278),"")</f>
+        <v/>
+      </c>
+      <c r="G278" s="13">
+        <f>IF(AND(ISNUMBER(D278),ISNUMBER(E278),ISNUMBER(F278)),IF(D278&gt;F278,"above UCL",IF(D278&lt;E278,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>21</v>
+      </c>
+      <c r="B279" s="7" t="n"/>
+      <c r="C279" s="7" t="n"/>
+      <c r="D279" s="28">
+        <f>IF(AND(ISNUMBER(B279),ISNUMBER(C279),B279&gt;0,ISNUMBER($B$256)),C279/B279,"")</f>
+        <v/>
+      </c>
+      <c r="E279" s="28">
+        <f>IF(AND(ISNUMBER(B279),ISNUMBER(C279),B279&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B279)),"")</f>
+        <v/>
+      </c>
+      <c r="F279" s="28">
+        <f>IF(AND(ISNUMBER(B279),ISNUMBER(C279),B279&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B279),"")</f>
+        <v/>
+      </c>
+      <c r="G279" s="13">
+        <f>IF(AND(ISNUMBER(D279),ISNUMBER(E279),ISNUMBER(F279)),IF(D279&gt;F279,"above UCL",IF(D279&lt;E279,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>22</v>
+      </c>
+      <c r="B280" s="7" t="n"/>
+      <c r="C280" s="7" t="n"/>
+      <c r="D280" s="28">
+        <f>IF(AND(ISNUMBER(B280),ISNUMBER(C280),B280&gt;0,ISNUMBER($B$256)),C280/B280,"")</f>
+        <v/>
+      </c>
+      <c r="E280" s="28">
+        <f>IF(AND(ISNUMBER(B280),ISNUMBER(C280),B280&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B280)),"")</f>
+        <v/>
+      </c>
+      <c r="F280" s="28">
+        <f>IF(AND(ISNUMBER(B280),ISNUMBER(C280),B280&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B280),"")</f>
+        <v/>
+      </c>
+      <c r="G280" s="13">
+        <f>IF(AND(ISNUMBER(D280),ISNUMBER(E280),ISNUMBER(F280)),IF(D280&gt;F280,"above UCL",IF(D280&lt;E280,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>23</v>
+      </c>
+      <c r="B281" s="7" t="n"/>
+      <c r="C281" s="7" t="n"/>
+      <c r="D281" s="28">
+        <f>IF(AND(ISNUMBER(B281),ISNUMBER(C281),B281&gt;0,ISNUMBER($B$256)),C281/B281,"")</f>
+        <v/>
+      </c>
+      <c r="E281" s="28">
+        <f>IF(AND(ISNUMBER(B281),ISNUMBER(C281),B281&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B281)),"")</f>
+        <v/>
+      </c>
+      <c r="F281" s="28">
+        <f>IF(AND(ISNUMBER(B281),ISNUMBER(C281),B281&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B281),"")</f>
+        <v/>
+      </c>
+      <c r="G281" s="13">
+        <f>IF(AND(ISNUMBER(D281),ISNUMBER(E281),ISNUMBER(F281)),IF(D281&gt;F281,"above UCL",IF(D281&lt;E281,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>24</v>
+      </c>
+      <c r="B282" s="7" t="n"/>
+      <c r="C282" s="7" t="n"/>
+      <c r="D282" s="28">
+        <f>IF(AND(ISNUMBER(B282),ISNUMBER(C282),B282&gt;0,ISNUMBER($B$256)),C282/B282,"")</f>
+        <v/>
+      </c>
+      <c r="E282" s="28">
+        <f>IF(AND(ISNUMBER(B282),ISNUMBER(C282),B282&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B282)),"")</f>
+        <v/>
+      </c>
+      <c r="F282" s="28">
+        <f>IF(AND(ISNUMBER(B282),ISNUMBER(C282),B282&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B282),"")</f>
+        <v/>
+      </c>
+      <c r="G282" s="13">
+        <f>IF(AND(ISNUMBER(D282),ISNUMBER(E282),ISNUMBER(F282)),IF(D282&gt;F282,"above UCL",IF(D282&lt;E282,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>25</v>
+      </c>
+      <c r="B283" s="7" t="n"/>
+      <c r="C283" s="7" t="n"/>
+      <c r="D283" s="28">
+        <f>IF(AND(ISNUMBER(B283),ISNUMBER(C283),B283&gt;0,ISNUMBER($B$256)),C283/B283,"")</f>
+        <v/>
+      </c>
+      <c r="E283" s="28">
+        <f>IF(AND(ISNUMBER(B283),ISNUMBER(C283),B283&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B283)),"")</f>
+        <v/>
+      </c>
+      <c r="F283" s="28">
+        <f>IF(AND(ISNUMBER(B283),ISNUMBER(C283),B283&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B283),"")</f>
+        <v/>
+      </c>
+      <c r="G283" s="13">
+        <f>IF(AND(ISNUMBER(D283),ISNUMBER(E283),ISNUMBER(F283)),IF(D283&gt;F283,"above UCL",IF(D283&lt;E283,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>26</v>
+      </c>
+      <c r="B284" s="7" t="n"/>
+      <c r="C284" s="7" t="n"/>
+      <c r="D284" s="28">
+        <f>IF(AND(ISNUMBER(B284),ISNUMBER(C284),B284&gt;0,ISNUMBER($B$256)),C284/B284,"")</f>
+        <v/>
+      </c>
+      <c r="E284" s="28">
+        <f>IF(AND(ISNUMBER(B284),ISNUMBER(C284),B284&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B284)),"")</f>
+        <v/>
+      </c>
+      <c r="F284" s="28">
+        <f>IF(AND(ISNUMBER(B284),ISNUMBER(C284),B284&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B284),"")</f>
+        <v/>
+      </c>
+      <c r="G284" s="13">
+        <f>IF(AND(ISNUMBER(D284),ISNUMBER(E284),ISNUMBER(F284)),IF(D284&gt;F284,"above UCL",IF(D284&lt;E284,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>27</v>
+      </c>
+      <c r="B285" s="7" t="n"/>
+      <c r="C285" s="7" t="n"/>
+      <c r="D285" s="28">
+        <f>IF(AND(ISNUMBER(B285),ISNUMBER(C285),B285&gt;0,ISNUMBER($B$256)),C285/B285,"")</f>
+        <v/>
+      </c>
+      <c r="E285" s="28">
+        <f>IF(AND(ISNUMBER(B285),ISNUMBER(C285),B285&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B285)),"")</f>
+        <v/>
+      </c>
+      <c r="F285" s="28">
+        <f>IF(AND(ISNUMBER(B285),ISNUMBER(C285),B285&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B285),"")</f>
+        <v/>
+      </c>
+      <c r="G285" s="13">
+        <f>IF(AND(ISNUMBER(D285),ISNUMBER(E285),ISNUMBER(F285)),IF(D285&gt;F285,"above UCL",IF(D285&lt;E285,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>28</v>
+      </c>
+      <c r="B286" s="7" t="n"/>
+      <c r="C286" s="7" t="n"/>
+      <c r="D286" s="28">
+        <f>IF(AND(ISNUMBER(B286),ISNUMBER(C286),B286&gt;0,ISNUMBER($B$256)),C286/B286,"")</f>
+        <v/>
+      </c>
+      <c r="E286" s="28">
+        <f>IF(AND(ISNUMBER(B286),ISNUMBER(C286),B286&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B286)),"")</f>
+        <v/>
+      </c>
+      <c r="F286" s="28">
+        <f>IF(AND(ISNUMBER(B286),ISNUMBER(C286),B286&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B286),"")</f>
+        <v/>
+      </c>
+      <c r="G286" s="13">
+        <f>IF(AND(ISNUMBER(D286),ISNUMBER(E286),ISNUMBER(F286)),IF(D286&gt;F286,"above UCL",IF(D286&lt;E286,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>29</v>
+      </c>
+      <c r="B287" s="7" t="n"/>
+      <c r="C287" s="7" t="n"/>
+      <c r="D287" s="28">
+        <f>IF(AND(ISNUMBER(B287),ISNUMBER(C287),B287&gt;0,ISNUMBER($B$256)),C287/B287,"")</f>
+        <v/>
+      </c>
+      <c r="E287" s="28">
+        <f>IF(AND(ISNUMBER(B287),ISNUMBER(C287),B287&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B287)),"")</f>
+        <v/>
+      </c>
+      <c r="F287" s="28">
+        <f>IF(AND(ISNUMBER(B287),ISNUMBER(C287),B287&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B287),"")</f>
+        <v/>
+      </c>
+      <c r="G287" s="13">
+        <f>IF(AND(ISNUMBER(D287),ISNUMBER(E287),ISNUMBER(F287)),IF(D287&gt;F287,"above UCL",IF(D287&lt;E287,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>30</v>
+      </c>
+      <c r="B288" s="7" t="n"/>
+      <c r="C288" s="7" t="n"/>
+      <c r="D288" s="28">
+        <f>IF(AND(ISNUMBER(B288),ISNUMBER(C288),B288&gt;0,ISNUMBER($B$256)),C288/B288,"")</f>
+        <v/>
+      </c>
+      <c r="E288" s="28">
+        <f>IF(AND(ISNUMBER(B288),ISNUMBER(C288),B288&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B288)),"")</f>
+        <v/>
+      </c>
+      <c r="F288" s="28">
+        <f>IF(AND(ISNUMBER(B288),ISNUMBER(C288),B288&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B288),"")</f>
+        <v/>
+      </c>
+      <c r="G288" s="13">
+        <f>IF(AND(ISNUMBER(D288),ISNUMBER(E288),ISNUMBER(F288)),IF(D288&gt;F288,"above UCL",IF(D288&lt;E288,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>31</v>
+      </c>
+      <c r="B289" s="7" t="n"/>
+      <c r="C289" s="7" t="n"/>
+      <c r="D289" s="28">
+        <f>IF(AND(ISNUMBER(B289),ISNUMBER(C289),B289&gt;0,ISNUMBER($B$256)),C289/B289,"")</f>
+        <v/>
+      </c>
+      <c r="E289" s="28">
+        <f>IF(AND(ISNUMBER(B289),ISNUMBER(C289),B289&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B289)),"")</f>
+        <v/>
+      </c>
+      <c r="F289" s="28">
+        <f>IF(AND(ISNUMBER(B289),ISNUMBER(C289),B289&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B289),"")</f>
+        <v/>
+      </c>
+      <c r="G289" s="13">
+        <f>IF(AND(ISNUMBER(D289),ISNUMBER(E289),ISNUMBER(F289)),IF(D289&gt;F289,"above UCL",IF(D289&lt;E289,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>32</v>
+      </c>
+      <c r="B290" s="7" t="n"/>
+      <c r="C290" s="7" t="n"/>
+      <c r="D290" s="28">
+        <f>IF(AND(ISNUMBER(B290),ISNUMBER(C290),B290&gt;0,ISNUMBER($B$256)),C290/B290,"")</f>
+        <v/>
+      </c>
+      <c r="E290" s="28">
+        <f>IF(AND(ISNUMBER(B290),ISNUMBER(C290),B290&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B290)),"")</f>
+        <v/>
+      </c>
+      <c r="F290" s="28">
+        <f>IF(AND(ISNUMBER(B290),ISNUMBER(C290),B290&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B290),"")</f>
+        <v/>
+      </c>
+      <c r="G290" s="13">
+        <f>IF(AND(ISNUMBER(D290),ISNUMBER(E290),ISNUMBER(F290)),IF(D290&gt;F290,"above UCL",IF(D290&lt;E290,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>33</v>
+      </c>
+      <c r="B291" s="7" t="n"/>
+      <c r="C291" s="7" t="n"/>
+      <c r="D291" s="28">
+        <f>IF(AND(ISNUMBER(B291),ISNUMBER(C291),B291&gt;0,ISNUMBER($B$256)),C291/B291,"")</f>
+        <v/>
+      </c>
+      <c r="E291" s="28">
+        <f>IF(AND(ISNUMBER(B291),ISNUMBER(C291),B291&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B291)),"")</f>
+        <v/>
+      </c>
+      <c r="F291" s="28">
+        <f>IF(AND(ISNUMBER(B291),ISNUMBER(C291),B291&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B291),"")</f>
+        <v/>
+      </c>
+      <c r="G291" s="13">
+        <f>IF(AND(ISNUMBER(D291),ISNUMBER(E291),ISNUMBER(F291)),IF(D291&gt;F291,"above UCL",IF(D291&lt;E291,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>34</v>
+      </c>
+      <c r="B292" s="7" t="n"/>
+      <c r="C292" s="7" t="n"/>
+      <c r="D292" s="28">
+        <f>IF(AND(ISNUMBER(B292),ISNUMBER(C292),B292&gt;0,ISNUMBER($B$256)),C292/B292,"")</f>
+        <v/>
+      </c>
+      <c r="E292" s="28">
+        <f>IF(AND(ISNUMBER(B292),ISNUMBER(C292),B292&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B292)),"")</f>
+        <v/>
+      </c>
+      <c r="F292" s="28">
+        <f>IF(AND(ISNUMBER(B292),ISNUMBER(C292),B292&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B292),"")</f>
+        <v/>
+      </c>
+      <c r="G292" s="13">
+        <f>IF(AND(ISNUMBER(D292),ISNUMBER(E292),ISNUMBER(F292)),IF(D292&gt;F292,"above UCL",IF(D292&lt;E292,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>35</v>
+      </c>
+      <c r="B293" s="7" t="n"/>
+      <c r="C293" s="7" t="n"/>
+      <c r="D293" s="28">
+        <f>IF(AND(ISNUMBER(B293),ISNUMBER(C293),B293&gt;0,ISNUMBER($B$256)),C293/B293,"")</f>
+        <v/>
+      </c>
+      <c r="E293" s="28">
+        <f>IF(AND(ISNUMBER(B293),ISNUMBER(C293),B293&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B293)),"")</f>
+        <v/>
+      </c>
+      <c r="F293" s="28">
+        <f>IF(AND(ISNUMBER(B293),ISNUMBER(C293),B293&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B293),"")</f>
+        <v/>
+      </c>
+      <c r="G293" s="13">
+        <f>IF(AND(ISNUMBER(D293),ISNUMBER(E293),ISNUMBER(F293)),IF(D293&gt;F293,"above UCL",IF(D293&lt;E293,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>36</v>
+      </c>
+      <c r="B294" s="7" t="n"/>
+      <c r="C294" s="7" t="n"/>
+      <c r="D294" s="28">
+        <f>IF(AND(ISNUMBER(B294),ISNUMBER(C294),B294&gt;0,ISNUMBER($B$256)),C294/B294,"")</f>
+        <v/>
+      </c>
+      <c r="E294" s="28">
+        <f>IF(AND(ISNUMBER(B294),ISNUMBER(C294),B294&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B294)),"")</f>
+        <v/>
+      </c>
+      <c r="F294" s="28">
+        <f>IF(AND(ISNUMBER(B294),ISNUMBER(C294),B294&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B294),"")</f>
+        <v/>
+      </c>
+      <c r="G294" s="13">
+        <f>IF(AND(ISNUMBER(D294),ISNUMBER(E294),ISNUMBER(F294)),IF(D294&gt;F294,"above UCL",IF(D294&lt;E294,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>37</v>
+      </c>
+      <c r="B295" s="7" t="n"/>
+      <c r="C295" s="7" t="n"/>
+      <c r="D295" s="28">
+        <f>IF(AND(ISNUMBER(B295),ISNUMBER(C295),B295&gt;0,ISNUMBER($B$256)),C295/B295,"")</f>
+        <v/>
+      </c>
+      <c r="E295" s="28">
+        <f>IF(AND(ISNUMBER(B295),ISNUMBER(C295),B295&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B295)),"")</f>
+        <v/>
+      </c>
+      <c r="F295" s="28">
+        <f>IF(AND(ISNUMBER(B295),ISNUMBER(C295),B295&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B295),"")</f>
+        <v/>
+      </c>
+      <c r="G295" s="13">
+        <f>IF(AND(ISNUMBER(D295),ISNUMBER(E295),ISNUMBER(F295)),IF(D295&gt;F295,"above UCL",IF(D295&lt;E295,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>38</v>
+      </c>
+      <c r="B296" s="7" t="n"/>
+      <c r="C296" s="7" t="n"/>
+      <c r="D296" s="28">
+        <f>IF(AND(ISNUMBER(B296),ISNUMBER(C296),B296&gt;0,ISNUMBER($B$256)),C296/B296,"")</f>
+        <v/>
+      </c>
+      <c r="E296" s="28">
+        <f>IF(AND(ISNUMBER(B296),ISNUMBER(C296),B296&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B296)),"")</f>
+        <v/>
+      </c>
+      <c r="F296" s="28">
+        <f>IF(AND(ISNUMBER(B296),ISNUMBER(C296),B296&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B296),"")</f>
+        <v/>
+      </c>
+      <c r="G296" s="13">
+        <f>IF(AND(ISNUMBER(D296),ISNUMBER(E296),ISNUMBER(F296)),IF(D296&gt;F296,"above UCL",IF(D296&lt;E296,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>39</v>
+      </c>
+      <c r="B297" s="7" t="n"/>
+      <c r="C297" s="7" t="n"/>
+      <c r="D297" s="28">
+        <f>IF(AND(ISNUMBER(B297),ISNUMBER(C297),B297&gt;0,ISNUMBER($B$256)),C297/B297,"")</f>
+        <v/>
+      </c>
+      <c r="E297" s="28">
+        <f>IF(AND(ISNUMBER(B297),ISNUMBER(C297),B297&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B297)),"")</f>
+        <v/>
+      </c>
+      <c r="F297" s="28">
+        <f>IF(AND(ISNUMBER(B297),ISNUMBER(C297),B297&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B297),"")</f>
+        <v/>
+      </c>
+      <c r="G297" s="13">
+        <f>IF(AND(ISNUMBER(D297),ISNUMBER(E297),ISNUMBER(F297)),IF(D297&gt;F297,"above UCL",IF(D297&lt;E297,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>40</v>
+      </c>
+      <c r="B298" s="7" t="n"/>
+      <c r="C298" s="7" t="n"/>
+      <c r="D298" s="28">
+        <f>IF(AND(ISNUMBER(B298),ISNUMBER(C298),B298&gt;0,ISNUMBER($B$256)),C298/B298,"")</f>
+        <v/>
+      </c>
+      <c r="E298" s="28">
+        <f>IF(AND(ISNUMBER(B298),ISNUMBER(C298),B298&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B298)),"")</f>
+        <v/>
+      </c>
+      <c r="F298" s="28">
+        <f>IF(AND(ISNUMBER(B298),ISNUMBER(C298),B298&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B298),"")</f>
+        <v/>
+      </c>
+      <c r="G298" s="13">
+        <f>IF(AND(ISNUMBER(D298),ISNUMBER(E298),ISNUMBER(F298)),IF(D298&gt;F298,"above UCL",IF(D298&lt;E298,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>41</v>
+      </c>
+      <c r="B299" s="7" t="n"/>
+      <c r="C299" s="7" t="n"/>
+      <c r="D299" s="28">
+        <f>IF(AND(ISNUMBER(B299),ISNUMBER(C299),B299&gt;0,ISNUMBER($B$256)),C299/B299,"")</f>
+        <v/>
+      </c>
+      <c r="E299" s="28">
+        <f>IF(AND(ISNUMBER(B299),ISNUMBER(C299),B299&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B299)),"")</f>
+        <v/>
+      </c>
+      <c r="F299" s="28">
+        <f>IF(AND(ISNUMBER(B299),ISNUMBER(C299),B299&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B299),"")</f>
+        <v/>
+      </c>
+      <c r="G299" s="13">
+        <f>IF(AND(ISNUMBER(D299),ISNUMBER(E299),ISNUMBER(F299)),IF(D299&gt;F299,"above UCL",IF(D299&lt;E299,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>42</v>
+      </c>
+      <c r="B300" s="7" t="n"/>
+      <c r="C300" s="7" t="n"/>
+      <c r="D300" s="28">
+        <f>IF(AND(ISNUMBER(B300),ISNUMBER(C300),B300&gt;0,ISNUMBER($B$256)),C300/B300,"")</f>
+        <v/>
+      </c>
+      <c r="E300" s="28">
+        <f>IF(AND(ISNUMBER(B300),ISNUMBER(C300),B300&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B300)),"")</f>
+        <v/>
+      </c>
+      <c r="F300" s="28">
+        <f>IF(AND(ISNUMBER(B300),ISNUMBER(C300),B300&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B300),"")</f>
+        <v/>
+      </c>
+      <c r="G300" s="13">
+        <f>IF(AND(ISNUMBER(D300),ISNUMBER(E300),ISNUMBER(F300)),IF(D300&gt;F300,"above UCL",IF(D300&lt;E300,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>43</v>
+      </c>
+      <c r="B301" s="7" t="n"/>
+      <c r="C301" s="7" t="n"/>
+      <c r="D301" s="28">
+        <f>IF(AND(ISNUMBER(B301),ISNUMBER(C301),B301&gt;0,ISNUMBER($B$256)),C301/B301,"")</f>
+        <v/>
+      </c>
+      <c r="E301" s="28">
+        <f>IF(AND(ISNUMBER(B301),ISNUMBER(C301),B301&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B301)),"")</f>
+        <v/>
+      </c>
+      <c r="F301" s="28">
+        <f>IF(AND(ISNUMBER(B301),ISNUMBER(C301),B301&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B301),"")</f>
+        <v/>
+      </c>
+      <c r="G301" s="13">
+        <f>IF(AND(ISNUMBER(D301),ISNUMBER(E301),ISNUMBER(F301)),IF(D301&gt;F301,"above UCL",IF(D301&lt;E301,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>44</v>
+      </c>
+      <c r="B302" s="7" t="n"/>
+      <c r="C302" s="7" t="n"/>
+      <c r="D302" s="28">
+        <f>IF(AND(ISNUMBER(B302),ISNUMBER(C302),B302&gt;0,ISNUMBER($B$256)),C302/B302,"")</f>
+        <v/>
+      </c>
+      <c r="E302" s="28">
+        <f>IF(AND(ISNUMBER(B302),ISNUMBER(C302),B302&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B302)),"")</f>
+        <v/>
+      </c>
+      <c r="F302" s="28">
+        <f>IF(AND(ISNUMBER(B302),ISNUMBER(C302),B302&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B302),"")</f>
+        <v/>
+      </c>
+      <c r="G302" s="13">
+        <f>IF(AND(ISNUMBER(D302),ISNUMBER(E302),ISNUMBER(F302)),IF(D302&gt;F302,"above UCL",IF(D302&lt;E302,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>45</v>
+      </c>
+      <c r="B303" s="7" t="n"/>
+      <c r="C303" s="7" t="n"/>
+      <c r="D303" s="28">
+        <f>IF(AND(ISNUMBER(B303),ISNUMBER(C303),B303&gt;0,ISNUMBER($B$256)),C303/B303,"")</f>
+        <v/>
+      </c>
+      <c r="E303" s="28">
+        <f>IF(AND(ISNUMBER(B303),ISNUMBER(C303),B303&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B303)),"")</f>
+        <v/>
+      </c>
+      <c r="F303" s="28">
+        <f>IF(AND(ISNUMBER(B303),ISNUMBER(C303),B303&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B303),"")</f>
+        <v/>
+      </c>
+      <c r="G303" s="13">
+        <f>IF(AND(ISNUMBER(D303),ISNUMBER(E303),ISNUMBER(F303)),IF(D303&gt;F303,"above UCL",IF(D303&lt;E303,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>46</v>
+      </c>
+      <c r="B304" s="7" t="n"/>
+      <c r="C304" s="7" t="n"/>
+      <c r="D304" s="28">
+        <f>IF(AND(ISNUMBER(B304),ISNUMBER(C304),B304&gt;0,ISNUMBER($B$256)),C304/B304,"")</f>
+        <v/>
+      </c>
+      <c r="E304" s="28">
+        <f>IF(AND(ISNUMBER(B304),ISNUMBER(C304),B304&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B304)),"")</f>
+        <v/>
+      </c>
+      <c r="F304" s="28">
+        <f>IF(AND(ISNUMBER(B304),ISNUMBER(C304),B304&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B304),"")</f>
+        <v/>
+      </c>
+      <c r="G304" s="13">
+        <f>IF(AND(ISNUMBER(D304),ISNUMBER(E304),ISNUMBER(F304)),IF(D304&gt;F304,"above UCL",IF(D304&lt;E304,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>47</v>
+      </c>
+      <c r="B305" s="7" t="n"/>
+      <c r="C305" s="7" t="n"/>
+      <c r="D305" s="28">
+        <f>IF(AND(ISNUMBER(B305),ISNUMBER(C305),B305&gt;0,ISNUMBER($B$256)),C305/B305,"")</f>
+        <v/>
+      </c>
+      <c r="E305" s="28">
+        <f>IF(AND(ISNUMBER(B305),ISNUMBER(C305),B305&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B305)),"")</f>
+        <v/>
+      </c>
+      <c r="F305" s="28">
+        <f>IF(AND(ISNUMBER(B305),ISNUMBER(C305),B305&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B305),"")</f>
+        <v/>
+      </c>
+      <c r="G305" s="13">
+        <f>IF(AND(ISNUMBER(D305),ISNUMBER(E305),ISNUMBER(F305)),IF(D305&gt;F305,"above UCL",IF(D305&lt;E305,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>48</v>
+      </c>
+      <c r="B306" s="7" t="n"/>
+      <c r="C306" s="7" t="n"/>
+      <c r="D306" s="28">
+        <f>IF(AND(ISNUMBER(B306),ISNUMBER(C306),B306&gt;0,ISNUMBER($B$256)),C306/B306,"")</f>
+        <v/>
+      </c>
+      <c r="E306" s="28">
+        <f>IF(AND(ISNUMBER(B306),ISNUMBER(C306),B306&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B306)),"")</f>
+        <v/>
+      </c>
+      <c r="F306" s="28">
+        <f>IF(AND(ISNUMBER(B306),ISNUMBER(C306),B306&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B306),"")</f>
+        <v/>
+      </c>
+      <c r="G306" s="13">
+        <f>IF(AND(ISNUMBER(D306),ISNUMBER(E306),ISNUMBER(F306)),IF(D306&gt;F306,"above UCL",IF(D306&lt;E306,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>49</v>
+      </c>
+      <c r="B307" s="7" t="n"/>
+      <c r="C307" s="7" t="n"/>
+      <c r="D307" s="28">
+        <f>IF(AND(ISNUMBER(B307),ISNUMBER(C307),B307&gt;0,ISNUMBER($B$256)),C307/B307,"")</f>
+        <v/>
+      </c>
+      <c r="E307" s="28">
+        <f>IF(AND(ISNUMBER(B307),ISNUMBER(C307),B307&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B307)),"")</f>
+        <v/>
+      </c>
+      <c r="F307" s="28">
+        <f>IF(AND(ISNUMBER(B307),ISNUMBER(C307),B307&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B307),"")</f>
+        <v/>
+      </c>
+      <c r="G307" s="13">
+        <f>IF(AND(ISNUMBER(D307),ISNUMBER(E307),ISNUMBER(F307)),IF(D307&gt;F307,"above UCL",IF(D307&lt;E307,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>50</v>
+      </c>
+      <c r="B308" s="7" t="n"/>
+      <c r="C308" s="7" t="n"/>
+      <c r="D308" s="28">
+        <f>IF(AND(ISNUMBER(B308),ISNUMBER(C308),B308&gt;0,ISNUMBER($B$256)),C308/B308,"")</f>
+        <v/>
+      </c>
+      <c r="E308" s="28">
+        <f>IF(AND(ISNUMBER(B308),ISNUMBER(C308),B308&gt;0,ISNUMBER($B$256)),MAX(0,$B$256-3*SQRT($B$256/B308)),"")</f>
+        <v/>
+      </c>
+      <c r="F308" s="28">
+        <f>IF(AND(ISNUMBER(B308),ISNUMBER(C308),B308&gt;0,ISNUMBER($B$256)),$B$256+3*SQRT($B$256/B308),"")</f>
+        <v/>
+      </c>
+      <c r="G308" s="13">
+        <f>IF(AND(ISNUMBER(D308),ISNUMBER(E308),ISNUMBER(F308)),IF(D308&gt;F308,"above UCL",IF(D308&lt;E308,"below LCL","")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="inlineStr">
+        <is>
+          <t>5. Reading the chart: Western Electric rules (deck p. 67-68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="inlineStr">
+        <is>
+          <t>1. One or more points outside the control limits (flagged in the tables above).</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="6" t="inlineStr">
+        <is>
+          <t>2. Two of three consecutive points outside the two-sigma warning limits but still inside the control limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="inlineStr">
+        <is>
+          <t>3. Four of five consecutive points beyond the one-sigma limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>4. A run of eight consecutive points on one side of the centre line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="8" t="inlineStr">
+        <is>
+          <t>More sensitizing rules, zones A/B/C and tampering vs. under-reacting: deck p. 64-69; Dummies p. 245-247.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Subgroup size" error="n is a whole number, 2 to 25." type="whole" operator="between">
+      <formula1>2</formula1>
+      <formula2>25</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -16,7 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mean &amp; proportion" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control charts" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gage R&amp;R" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance sampling" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="T18_n">Tables!$A$14:$A$38</definedName>
@@ -206,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -253,6 +254,7 @@
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2168,6 +2170,1629 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Acceptance sampling: OC curve of a plan (n, c), producer's / consumer's risk, AOQ, AOQL, ATI, variables plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>source/course/Les 2/20260529_ottoy_Acceptance Sampling - Further Reading.pdf p. 2-10; Acceptance Sampling.pdf p. 23-27; Testing of Hypotheses.pdf p. 5-11; Testing of Hypotheses.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Convention used</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Decision 12: α and β inputs prefilled 5 % and 10 % (p. 4; its worked examples use β = 5 %); hypergeometric OC with M = [Np] when N is given, binomial always shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>VERIFIED: tested against course worked examples S03-WE06, S03-WE07, S03-WE20, S03-WE21, S04-WE12, S04-WE16, S04-WE18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>1. The plan (n, c) and the quality levels (fractions: 0.02 = 2 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>n = sample size</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>c = acceptance number (accept if defectives ≤ c)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>N = lot size (optional: exact hypergeometric OC, AOQ, ATI)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>AQL (acceptable quality level)</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>should normally pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>LQL = LTPD (limiting quality level)</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>should normally be rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>α = producer's risk target</t>
+        </is>
+      </c>
+      <c r="B14" s="35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>p. 4: normally 5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>β = consumer's risk target</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>p. 4: normally 10 %; its examples use 5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Producer's risk: rejecting a good lot (type I). Consumer's risk: accepting a bad lot (type II). Further Reading p. 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2. Risks of the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr"/>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>binomial</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>hypergeometric (needs N)</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Course source</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>OC(AQL) = P(accept a lot at AQL)</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$12)),_xlfn.BINOM.DIST($B$10,$B$9,$B$12,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$12),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT($B$12*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Further Reading p. 4; Testing of Hypotheses.pdf p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Producer's risk α = 1 − OC(AQL)</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$12)),1-_xlfn.BINOM.DIST($B$10,$B$9,$B$12,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$12),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),1-_xlfn.HYPGEOM.DIST($B$10,$B$9,INT($B$12*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Consumer's risk β = OC(LQL) = P(accept a lot at LQL)</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$13)),_xlfn.BINOM.DIST($B$10,$B$9,$B$13,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$13),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT($B$13*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Meets both targets (α ≤ target and β ≤ target)?</t>
+        </is>
+      </c>
+      <c r="B24" s="13">
+        <f>IF(AND(ISNUMBER(B21),ISNUMBER(B22)),IF(AND(B21&lt;=$B$14,B22&lt;=$B$15),"yes","no"),"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="13">
+        <f>IF(AND(ISNUMBER(C21),ISNUMBER(C22)),IF(AND(C21&lt;=$B$14,C22&lt;=$B$15),"yes","no"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>3. One lot quality p: acceptance, outgoing quality, inspection effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>p = fraction defective of the lot</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>OC(p), binomial</t>
+        </is>
+      </c>
+      <c r="B28" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$27)),_xlfn.BINOM.DIST($B$10,$B$9,$B$27,TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>OC(p), hypergeometric</t>
+        </is>
+      </c>
+      <c r="B29" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$27)),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT($B$27*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>AOQ(p) = p·OC(p)·(1 − (n/N)·Rs*)</t>
+        </is>
+      </c>
+      <c r="B30" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$27)),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),IF(B29=0,0,$B$27*B29*(1-($B$9/$B$11)*IF(OR($B$10=0,INT($B$27*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT($B$27*$B$11)-1,$B$11-1,TRUE)/B29))),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>p. 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>AOQ(p) ≈ p·OC(p) (n &lt;&lt; N; hypergeometric OC if N is given)</t>
+        </is>
+      </c>
+      <c r="B31" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$27)),$B$27*IF(ISNUMBER(B29),B29,B28),"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>p. 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>ATI(p) = n·OC(p) + N·(1 − OC(p))</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER($B$27)),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),$B$9*B29+$B$11*(1-B29),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>p. 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>4. Variables plan (normal measurements): accept if (x̄ − limit) / s ≥ k   (p. 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Uses AQL = p0, LQL = pt, α and β from section 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>k = (z_pt z_α + z_p0 z_β) / (z_(1−α) + z_(1−β))</t>
+        </is>
+      </c>
+      <c r="B38" s="11">
+        <f>IF(AND(ISNUMBER($B$12),ISNUMBER($B$13),ISNUMBER($B$14),ISNUMBER($B$15),$B$13&gt;$B$12),(_xlfn.NORM.S.INV($B$13)*_xlfn.NORM.S.INV($B$14)+_xlfn.NORM.S.INV($B$12)*_xlfn.NORM.S.INV($B$15))/(_xlfn.NORM.S.INV(1-$B$14)+_xlfn.NORM.S.INV(1-$B$15)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Further Reading p. 9 (z_q = q-quantile of N(0,1))</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>n = (z_(1−α) + z_(1−β))² (1 + k²/2) / (z_pt − z_p0)²</t>
+        </is>
+      </c>
+      <c r="B39" s="38">
+        <f>IF(ISNUMBER(B38),(_xlfn.NORM.S.INV(1-$B$14)+_xlfn.NORM.S.INV(1-$B$15))^2*(1+B38^2/2)/(_xlfn.NORM.S.INV($B$13)-_xlfn.NORM.S.INV($B$12))^2,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>n rounded up</t>
+        </is>
+      </c>
+      <c r="B40" s="24">
+        <f>IF(ISNUMBER(B39),ROUNDUP(B39,0),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>p. 9 example: 63.2 -&gt; 64</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>OC(AQL) of this plan</t>
+        </is>
+      </c>
+      <c r="B41" s="14">
+        <f>IF(ISNUMBER(B40),1-_xlfn.NORM.S.DIST((_xlfn.NORM.S.INV($B$12)+B38)*SQRT(B40)/SQRT(1+B38^2/2),TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>p. 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>OC(LQL) of this plan</t>
+        </is>
+      </c>
+      <c r="B42" s="14">
+        <f>IF(ISNUMBER(B40),1-_xlfn.NORM.S.DIST((_xlfn.NORM.S.INV($B$13)+B38)*SQRT(B40)/SQRT(1+B38^2/2),TRUE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>5. OC curve, AOQ and ATI over a range of p (AOQL = the largest AOQ in the table)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>AOQL with the exact formula (column E) and the p where it occurs</t>
+        </is>
+      </c>
+      <c r="B45" s="14">
+        <f>IF(COUNT(E50:E90)&gt;0,MAX(E50:E90),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="14">
+        <f>IF(ISNUMBER(B45),INDEX(A50:A90,MATCH(B45,E50:E90,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>exact only to the table step</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>AOQL with the approximation p·OC(p) (column D) and its p</t>
+        </is>
+      </c>
+      <c r="B46" s="14">
+        <f>IF(COUNT(D50:D90)&gt;0,MAX(D50:D90),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="14">
+        <f>IF(ISNUMBER(B46),INDEX(A50:A90,MATCH(B46,D50:D90,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>p. 10 example (250, 5), N = 1000: 'AOQL ≈ 1.3 % at p ≈ 1.8 %' is this approximation</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Table step of p</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Testing of Hypotheses.xlsx uses 0.005 (p from 0 to 0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>OC binomial</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>OC hypergeometric</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>AOQ ≈ p·OC(p)</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>AOQ (exact, p. 10)</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>ATI</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14">
+        <f>IF(ISNUMBER($B$48),0*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B50" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A50),A50&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A50,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A50),A50&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A50*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="14">
+        <f>IF(ISNUMBER(C50),A50*C50,IF(ISNUMBER(B50),A50*B50,""))</f>
+        <v/>
+      </c>
+      <c r="E50" s="14">
+        <f>IF(ISNUMBER(C50),IF(C50=0,0,A50*C50*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A50*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A50*$B$11)-1,$B$11-1,TRUE)/C50))),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="16">
+        <f>IF(ISNUMBER(C50),$B$9*C50+$B$11*(1-C50),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14">
+        <f>IF(ISNUMBER($B$48),1*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B51" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A51),A51&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A51,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A51),A51&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A51*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="14">
+        <f>IF(ISNUMBER(C51),A51*C51,IF(ISNUMBER(B51),A51*B51,""))</f>
+        <v/>
+      </c>
+      <c r="E51" s="14">
+        <f>IF(ISNUMBER(C51),IF(C51=0,0,A51*C51*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A51*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A51*$B$11)-1,$B$11-1,TRUE)/C51))),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="16">
+        <f>IF(ISNUMBER(C51),$B$9*C51+$B$11*(1-C51),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14">
+        <f>IF(ISNUMBER($B$48),2*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B52" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A52),A52&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A52,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A52),A52&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A52*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="14">
+        <f>IF(ISNUMBER(C52),A52*C52,IF(ISNUMBER(B52),A52*B52,""))</f>
+        <v/>
+      </c>
+      <c r="E52" s="14">
+        <f>IF(ISNUMBER(C52),IF(C52=0,0,A52*C52*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A52*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A52*$B$11)-1,$B$11-1,TRUE)/C52))),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="16">
+        <f>IF(ISNUMBER(C52),$B$9*C52+$B$11*(1-C52),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14">
+        <f>IF(ISNUMBER($B$48),3*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B53" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A53),A53&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A53,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A53),A53&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A53*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="14">
+        <f>IF(ISNUMBER(C53),A53*C53,IF(ISNUMBER(B53),A53*B53,""))</f>
+        <v/>
+      </c>
+      <c r="E53" s="14">
+        <f>IF(ISNUMBER(C53),IF(C53=0,0,A53*C53*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A53*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A53*$B$11)-1,$B$11-1,TRUE)/C53))),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="16">
+        <f>IF(ISNUMBER(C53),$B$9*C53+$B$11*(1-C53),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14">
+        <f>IF(ISNUMBER($B$48),4*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B54" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A54),A54&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A54,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A54),A54&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A54*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="14">
+        <f>IF(ISNUMBER(C54),A54*C54,IF(ISNUMBER(B54),A54*B54,""))</f>
+        <v/>
+      </c>
+      <c r="E54" s="14">
+        <f>IF(ISNUMBER(C54),IF(C54=0,0,A54*C54*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A54*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A54*$B$11)-1,$B$11-1,TRUE)/C54))),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="16">
+        <f>IF(ISNUMBER(C54),$B$9*C54+$B$11*(1-C54),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14">
+        <f>IF(ISNUMBER($B$48),5*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B55" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A55),A55&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A55,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A55),A55&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A55*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="14">
+        <f>IF(ISNUMBER(C55),A55*C55,IF(ISNUMBER(B55),A55*B55,""))</f>
+        <v/>
+      </c>
+      <c r="E55" s="14">
+        <f>IF(ISNUMBER(C55),IF(C55=0,0,A55*C55*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A55*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A55*$B$11)-1,$B$11-1,TRUE)/C55))),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="16">
+        <f>IF(ISNUMBER(C55),$B$9*C55+$B$11*(1-C55),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14">
+        <f>IF(ISNUMBER($B$48),6*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B56" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A56),A56&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A56,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A56),A56&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A56*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="14">
+        <f>IF(ISNUMBER(C56),A56*C56,IF(ISNUMBER(B56),A56*B56,""))</f>
+        <v/>
+      </c>
+      <c r="E56" s="14">
+        <f>IF(ISNUMBER(C56),IF(C56=0,0,A56*C56*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A56*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A56*$B$11)-1,$B$11-1,TRUE)/C56))),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="16">
+        <f>IF(ISNUMBER(C56),$B$9*C56+$B$11*(1-C56),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14">
+        <f>IF(ISNUMBER($B$48),7*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B57" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A57),A57&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A57,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A57),A57&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A57*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="14">
+        <f>IF(ISNUMBER(C57),A57*C57,IF(ISNUMBER(B57),A57*B57,""))</f>
+        <v/>
+      </c>
+      <c r="E57" s="14">
+        <f>IF(ISNUMBER(C57),IF(C57=0,0,A57*C57*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A57*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A57*$B$11)-1,$B$11-1,TRUE)/C57))),"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="16">
+        <f>IF(ISNUMBER(C57),$B$9*C57+$B$11*(1-C57),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14">
+        <f>IF(ISNUMBER($B$48),8*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B58" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A58),A58&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A58,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A58),A58&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A58*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="14">
+        <f>IF(ISNUMBER(C58),A58*C58,IF(ISNUMBER(B58),A58*B58,""))</f>
+        <v/>
+      </c>
+      <c r="E58" s="14">
+        <f>IF(ISNUMBER(C58),IF(C58=0,0,A58*C58*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A58*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A58*$B$11)-1,$B$11-1,TRUE)/C58))),"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="16">
+        <f>IF(ISNUMBER(C58),$B$9*C58+$B$11*(1-C58),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14">
+        <f>IF(ISNUMBER($B$48),9*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B59" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A59),A59&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A59,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A59),A59&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A59*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="14">
+        <f>IF(ISNUMBER(C59),A59*C59,IF(ISNUMBER(B59),A59*B59,""))</f>
+        <v/>
+      </c>
+      <c r="E59" s="14">
+        <f>IF(ISNUMBER(C59),IF(C59=0,0,A59*C59*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A59*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A59*$B$11)-1,$B$11-1,TRUE)/C59))),"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="16">
+        <f>IF(ISNUMBER(C59),$B$9*C59+$B$11*(1-C59),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14">
+        <f>IF(ISNUMBER($B$48),10*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B60" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A60),A60&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A60,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A60),A60&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A60*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="14">
+        <f>IF(ISNUMBER(C60),A60*C60,IF(ISNUMBER(B60),A60*B60,""))</f>
+        <v/>
+      </c>
+      <c r="E60" s="14">
+        <f>IF(ISNUMBER(C60),IF(C60=0,0,A60*C60*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A60*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A60*$B$11)-1,$B$11-1,TRUE)/C60))),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="16">
+        <f>IF(ISNUMBER(C60),$B$9*C60+$B$11*(1-C60),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14">
+        <f>IF(ISNUMBER($B$48),11*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B61" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A61),A61&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A61,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A61),A61&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A61*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="14">
+        <f>IF(ISNUMBER(C61),A61*C61,IF(ISNUMBER(B61),A61*B61,""))</f>
+        <v/>
+      </c>
+      <c r="E61" s="14">
+        <f>IF(ISNUMBER(C61),IF(C61=0,0,A61*C61*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A61*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A61*$B$11)-1,$B$11-1,TRUE)/C61))),"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="16">
+        <f>IF(ISNUMBER(C61),$B$9*C61+$B$11*(1-C61),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14">
+        <f>IF(ISNUMBER($B$48),12*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B62" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A62),A62&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A62,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A62),A62&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A62*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="14">
+        <f>IF(ISNUMBER(C62),A62*C62,IF(ISNUMBER(B62),A62*B62,""))</f>
+        <v/>
+      </c>
+      <c r="E62" s="14">
+        <f>IF(ISNUMBER(C62),IF(C62=0,0,A62*C62*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A62*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A62*$B$11)-1,$B$11-1,TRUE)/C62))),"")</f>
+        <v/>
+      </c>
+      <c r="F62" s="16">
+        <f>IF(ISNUMBER(C62),$B$9*C62+$B$11*(1-C62),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14">
+        <f>IF(ISNUMBER($B$48),13*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B63" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A63),A63&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A63,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C63" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A63),A63&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A63*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="14">
+        <f>IF(ISNUMBER(C63),A63*C63,IF(ISNUMBER(B63),A63*B63,""))</f>
+        <v/>
+      </c>
+      <c r="E63" s="14">
+        <f>IF(ISNUMBER(C63),IF(C63=0,0,A63*C63*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A63*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A63*$B$11)-1,$B$11-1,TRUE)/C63))),"")</f>
+        <v/>
+      </c>
+      <c r="F63" s="16">
+        <f>IF(ISNUMBER(C63),$B$9*C63+$B$11*(1-C63),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14">
+        <f>IF(ISNUMBER($B$48),14*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B64" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A64),A64&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A64,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C64" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A64),A64&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A64*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="14">
+        <f>IF(ISNUMBER(C64),A64*C64,IF(ISNUMBER(B64),A64*B64,""))</f>
+        <v/>
+      </c>
+      <c r="E64" s="14">
+        <f>IF(ISNUMBER(C64),IF(C64=0,0,A64*C64*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A64*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A64*$B$11)-1,$B$11-1,TRUE)/C64))),"")</f>
+        <v/>
+      </c>
+      <c r="F64" s="16">
+        <f>IF(ISNUMBER(C64),$B$9*C64+$B$11*(1-C64),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14">
+        <f>IF(ISNUMBER($B$48),15*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B65" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A65),A65&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A65,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A65),A65&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A65*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="14">
+        <f>IF(ISNUMBER(C65),A65*C65,IF(ISNUMBER(B65),A65*B65,""))</f>
+        <v/>
+      </c>
+      <c r="E65" s="14">
+        <f>IF(ISNUMBER(C65),IF(C65=0,0,A65*C65*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A65*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A65*$B$11)-1,$B$11-1,TRUE)/C65))),"")</f>
+        <v/>
+      </c>
+      <c r="F65" s="16">
+        <f>IF(ISNUMBER(C65),$B$9*C65+$B$11*(1-C65),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14">
+        <f>IF(ISNUMBER($B$48),16*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B66" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A66),A66&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A66,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A66),A66&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A66*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="14">
+        <f>IF(ISNUMBER(C66),A66*C66,IF(ISNUMBER(B66),A66*B66,""))</f>
+        <v/>
+      </c>
+      <c r="E66" s="14">
+        <f>IF(ISNUMBER(C66),IF(C66=0,0,A66*C66*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A66*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A66*$B$11)-1,$B$11-1,TRUE)/C66))),"")</f>
+        <v/>
+      </c>
+      <c r="F66" s="16">
+        <f>IF(ISNUMBER(C66),$B$9*C66+$B$11*(1-C66),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14">
+        <f>IF(ISNUMBER($B$48),17*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B67" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A67),A67&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A67,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A67),A67&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A67*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="14">
+        <f>IF(ISNUMBER(C67),A67*C67,IF(ISNUMBER(B67),A67*B67,""))</f>
+        <v/>
+      </c>
+      <c r="E67" s="14">
+        <f>IF(ISNUMBER(C67),IF(C67=0,0,A67*C67*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A67*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A67*$B$11)-1,$B$11-1,TRUE)/C67))),"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="16">
+        <f>IF(ISNUMBER(C67),$B$9*C67+$B$11*(1-C67),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14">
+        <f>IF(ISNUMBER($B$48),18*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B68" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A68),A68&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A68,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A68),A68&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A68*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="14">
+        <f>IF(ISNUMBER(C68),A68*C68,IF(ISNUMBER(B68),A68*B68,""))</f>
+        <v/>
+      </c>
+      <c r="E68" s="14">
+        <f>IF(ISNUMBER(C68),IF(C68=0,0,A68*C68*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A68*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A68*$B$11)-1,$B$11-1,TRUE)/C68))),"")</f>
+        <v/>
+      </c>
+      <c r="F68" s="16">
+        <f>IF(ISNUMBER(C68),$B$9*C68+$B$11*(1-C68),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14">
+        <f>IF(ISNUMBER($B$48),19*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B69" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A69),A69&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A69,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A69),A69&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A69*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D69" s="14">
+        <f>IF(ISNUMBER(C69),A69*C69,IF(ISNUMBER(B69),A69*B69,""))</f>
+        <v/>
+      </c>
+      <c r="E69" s="14">
+        <f>IF(ISNUMBER(C69),IF(C69=0,0,A69*C69*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A69*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A69*$B$11)-1,$B$11-1,TRUE)/C69))),"")</f>
+        <v/>
+      </c>
+      <c r="F69" s="16">
+        <f>IF(ISNUMBER(C69),$B$9*C69+$B$11*(1-C69),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14">
+        <f>IF(ISNUMBER($B$48),20*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B70" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A70),A70&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A70,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C70" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A70),A70&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A70*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D70" s="14">
+        <f>IF(ISNUMBER(C70),A70*C70,IF(ISNUMBER(B70),A70*B70,""))</f>
+        <v/>
+      </c>
+      <c r="E70" s="14">
+        <f>IF(ISNUMBER(C70),IF(C70=0,0,A70*C70*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A70*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A70*$B$11)-1,$B$11-1,TRUE)/C70))),"")</f>
+        <v/>
+      </c>
+      <c r="F70" s="16">
+        <f>IF(ISNUMBER(C70),$B$9*C70+$B$11*(1-C70),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14">
+        <f>IF(ISNUMBER($B$48),21*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B71" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A71),A71&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A71,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A71),A71&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A71*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="14">
+        <f>IF(ISNUMBER(C71),A71*C71,IF(ISNUMBER(B71),A71*B71,""))</f>
+        <v/>
+      </c>
+      <c r="E71" s="14">
+        <f>IF(ISNUMBER(C71),IF(C71=0,0,A71*C71*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A71*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A71*$B$11)-1,$B$11-1,TRUE)/C71))),"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="16">
+        <f>IF(ISNUMBER(C71),$B$9*C71+$B$11*(1-C71),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14">
+        <f>IF(ISNUMBER($B$48),22*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B72" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A72),A72&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A72,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A72),A72&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A72*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D72" s="14">
+        <f>IF(ISNUMBER(C72),A72*C72,IF(ISNUMBER(B72),A72*B72,""))</f>
+        <v/>
+      </c>
+      <c r="E72" s="14">
+        <f>IF(ISNUMBER(C72),IF(C72=0,0,A72*C72*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A72*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A72*$B$11)-1,$B$11-1,TRUE)/C72))),"")</f>
+        <v/>
+      </c>
+      <c r="F72" s="16">
+        <f>IF(ISNUMBER(C72),$B$9*C72+$B$11*(1-C72),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14">
+        <f>IF(ISNUMBER($B$48),23*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B73" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A73),A73&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A73,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C73" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A73),A73&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A73*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D73" s="14">
+        <f>IF(ISNUMBER(C73),A73*C73,IF(ISNUMBER(B73),A73*B73,""))</f>
+        <v/>
+      </c>
+      <c r="E73" s="14">
+        <f>IF(ISNUMBER(C73),IF(C73=0,0,A73*C73*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A73*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A73*$B$11)-1,$B$11-1,TRUE)/C73))),"")</f>
+        <v/>
+      </c>
+      <c r="F73" s="16">
+        <f>IF(ISNUMBER(C73),$B$9*C73+$B$11*(1-C73),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14">
+        <f>IF(ISNUMBER($B$48),24*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B74" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A74),A74&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A74,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C74" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A74),A74&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A74*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D74" s="14">
+        <f>IF(ISNUMBER(C74),A74*C74,IF(ISNUMBER(B74),A74*B74,""))</f>
+        <v/>
+      </c>
+      <c r="E74" s="14">
+        <f>IF(ISNUMBER(C74),IF(C74=0,0,A74*C74*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A74*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A74*$B$11)-1,$B$11-1,TRUE)/C74))),"")</f>
+        <v/>
+      </c>
+      <c r="F74" s="16">
+        <f>IF(ISNUMBER(C74),$B$9*C74+$B$11*(1-C74),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14">
+        <f>IF(ISNUMBER($B$48),25*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B75" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A75),A75&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A75,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C75" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A75),A75&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A75*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="14">
+        <f>IF(ISNUMBER(C75),A75*C75,IF(ISNUMBER(B75),A75*B75,""))</f>
+        <v/>
+      </c>
+      <c r="E75" s="14">
+        <f>IF(ISNUMBER(C75),IF(C75=0,0,A75*C75*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A75*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A75*$B$11)-1,$B$11-1,TRUE)/C75))),"")</f>
+        <v/>
+      </c>
+      <c r="F75" s="16">
+        <f>IF(ISNUMBER(C75),$B$9*C75+$B$11*(1-C75),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14">
+        <f>IF(ISNUMBER($B$48),26*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B76" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A76),A76&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A76,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C76" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A76),A76&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A76*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D76" s="14">
+        <f>IF(ISNUMBER(C76),A76*C76,IF(ISNUMBER(B76),A76*B76,""))</f>
+        <v/>
+      </c>
+      <c r="E76" s="14">
+        <f>IF(ISNUMBER(C76),IF(C76=0,0,A76*C76*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A76*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A76*$B$11)-1,$B$11-1,TRUE)/C76))),"")</f>
+        <v/>
+      </c>
+      <c r="F76" s="16">
+        <f>IF(ISNUMBER(C76),$B$9*C76+$B$11*(1-C76),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14">
+        <f>IF(ISNUMBER($B$48),27*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B77" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A77),A77&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A77,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A77),A77&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A77*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="14">
+        <f>IF(ISNUMBER(C77),A77*C77,IF(ISNUMBER(B77),A77*B77,""))</f>
+        <v/>
+      </c>
+      <c r="E77" s="14">
+        <f>IF(ISNUMBER(C77),IF(C77=0,0,A77*C77*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A77*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A77*$B$11)-1,$B$11-1,TRUE)/C77))),"")</f>
+        <v/>
+      </c>
+      <c r="F77" s="16">
+        <f>IF(ISNUMBER(C77),$B$9*C77+$B$11*(1-C77),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14">
+        <f>IF(ISNUMBER($B$48),28*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B78" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A78),A78&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A78,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A78),A78&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A78*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="14">
+        <f>IF(ISNUMBER(C78),A78*C78,IF(ISNUMBER(B78),A78*B78,""))</f>
+        <v/>
+      </c>
+      <c r="E78" s="14">
+        <f>IF(ISNUMBER(C78),IF(C78=0,0,A78*C78*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A78*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A78*$B$11)-1,$B$11-1,TRUE)/C78))),"")</f>
+        <v/>
+      </c>
+      <c r="F78" s="16">
+        <f>IF(ISNUMBER(C78),$B$9*C78+$B$11*(1-C78),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14">
+        <f>IF(ISNUMBER($B$48),29*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B79" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A79),A79&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A79,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A79),A79&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A79*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="14">
+        <f>IF(ISNUMBER(C79),A79*C79,IF(ISNUMBER(B79),A79*B79,""))</f>
+        <v/>
+      </c>
+      <c r="E79" s="14">
+        <f>IF(ISNUMBER(C79),IF(C79=0,0,A79*C79*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A79*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A79*$B$11)-1,$B$11-1,TRUE)/C79))),"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="16">
+        <f>IF(ISNUMBER(C79),$B$9*C79+$B$11*(1-C79),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14">
+        <f>IF(ISNUMBER($B$48),30*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B80" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A80),A80&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A80,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A80),A80&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A80*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="14">
+        <f>IF(ISNUMBER(C80),A80*C80,IF(ISNUMBER(B80),A80*B80,""))</f>
+        <v/>
+      </c>
+      <c r="E80" s="14">
+        <f>IF(ISNUMBER(C80),IF(C80=0,0,A80*C80*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A80*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A80*$B$11)-1,$B$11-1,TRUE)/C80))),"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="16">
+        <f>IF(ISNUMBER(C80),$B$9*C80+$B$11*(1-C80),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14">
+        <f>IF(ISNUMBER($B$48),31*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B81" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A81),A81&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A81,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A81),A81&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A81*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="14">
+        <f>IF(ISNUMBER(C81),A81*C81,IF(ISNUMBER(B81),A81*B81,""))</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>IF(ISNUMBER(C81),IF(C81=0,0,A81*C81*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A81*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A81*$B$11)-1,$B$11-1,TRUE)/C81))),"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="16">
+        <f>IF(ISNUMBER(C81),$B$9*C81+$B$11*(1-C81),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14">
+        <f>IF(ISNUMBER($B$48),32*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B82" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A82),A82&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A82,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A82),A82&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A82*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="14">
+        <f>IF(ISNUMBER(C82),A82*C82,IF(ISNUMBER(B82),A82*B82,""))</f>
+        <v/>
+      </c>
+      <c r="E82" s="14">
+        <f>IF(ISNUMBER(C82),IF(C82=0,0,A82*C82*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A82*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A82*$B$11)-1,$B$11-1,TRUE)/C82))),"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="16">
+        <f>IF(ISNUMBER(C82),$B$9*C82+$B$11*(1-C82),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14">
+        <f>IF(ISNUMBER($B$48),33*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B83" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A83),A83&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A83,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A83),A83&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A83*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="14">
+        <f>IF(ISNUMBER(C83),A83*C83,IF(ISNUMBER(B83),A83*B83,""))</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>IF(ISNUMBER(C83),IF(C83=0,0,A83*C83*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A83*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A83*$B$11)-1,$B$11-1,TRUE)/C83))),"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="16">
+        <f>IF(ISNUMBER(C83),$B$9*C83+$B$11*(1-C83),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14">
+        <f>IF(ISNUMBER($B$48),34*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B84" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A84),A84&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A84,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A84),A84&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A84*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="14">
+        <f>IF(ISNUMBER(C84),A84*C84,IF(ISNUMBER(B84),A84*B84,""))</f>
+        <v/>
+      </c>
+      <c r="E84" s="14">
+        <f>IF(ISNUMBER(C84),IF(C84=0,0,A84*C84*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A84*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A84*$B$11)-1,$B$11-1,TRUE)/C84))),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="16">
+        <f>IF(ISNUMBER(C84),$B$9*C84+$B$11*(1-C84),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14">
+        <f>IF(ISNUMBER($B$48),35*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B85" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A85),A85&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A85,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A85),A85&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A85*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="14">
+        <f>IF(ISNUMBER(C85),A85*C85,IF(ISNUMBER(B85),A85*B85,""))</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>IF(ISNUMBER(C85),IF(C85=0,0,A85*C85*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A85*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A85*$B$11)-1,$B$11-1,TRUE)/C85))),"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="16">
+        <f>IF(ISNUMBER(C85),$B$9*C85+$B$11*(1-C85),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14">
+        <f>IF(ISNUMBER($B$48),36*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B86" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A86),A86&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A86,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A86),A86&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A86*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="14">
+        <f>IF(ISNUMBER(C86),A86*C86,IF(ISNUMBER(B86),A86*B86,""))</f>
+        <v/>
+      </c>
+      <c r="E86" s="14">
+        <f>IF(ISNUMBER(C86),IF(C86=0,0,A86*C86*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A86*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A86*$B$11)-1,$B$11-1,TRUE)/C86))),"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="16">
+        <f>IF(ISNUMBER(C86),$B$9*C86+$B$11*(1-C86),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14">
+        <f>IF(ISNUMBER($B$48),37*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B87" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A87),A87&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A87,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A87),A87&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A87*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="14">
+        <f>IF(ISNUMBER(C87),A87*C87,IF(ISNUMBER(B87),A87*B87,""))</f>
+        <v/>
+      </c>
+      <c r="E87" s="14">
+        <f>IF(ISNUMBER(C87),IF(C87=0,0,A87*C87*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A87*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A87*$B$11)-1,$B$11-1,TRUE)/C87))),"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="16">
+        <f>IF(ISNUMBER(C87),$B$9*C87+$B$11*(1-C87),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14">
+        <f>IF(ISNUMBER($B$48),38*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B88" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A88),A88&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A88,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A88),A88&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A88*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="14">
+        <f>IF(ISNUMBER(C88),A88*C88,IF(ISNUMBER(B88),A88*B88,""))</f>
+        <v/>
+      </c>
+      <c r="E88" s="14">
+        <f>IF(ISNUMBER(C88),IF(C88=0,0,A88*C88*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A88*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A88*$B$11)-1,$B$11-1,TRUE)/C88))),"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="16">
+        <f>IF(ISNUMBER(C88),$B$9*C88+$B$11*(1-C88),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14">
+        <f>IF(ISNUMBER($B$48),39*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B89" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A89),A89&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A89,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A89),A89&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A89*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="14">
+        <f>IF(ISNUMBER(C89),A89*C89,IF(ISNUMBER(B89),A89*B89,""))</f>
+        <v/>
+      </c>
+      <c r="E89" s="14">
+        <f>IF(ISNUMBER(C89),IF(C89=0,0,A89*C89*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A89*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A89*$B$11)-1,$B$11-1,TRUE)/C89))),"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="16">
+        <f>IF(ISNUMBER(C89),$B$9*C89+$B$11*(1-C89),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14">
+        <f>IF(ISNUMBER($B$48),40*$B$48,"")</f>
+        <v/>
+      </c>
+      <c r="B90" s="14">
+        <f>IF(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A90),A90&lt;=1),_xlfn.BINOM.DIST($B$10,$B$9,A90,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="14">
+        <f>IF(AND(AND(AND(ISNUMBER($B$9),ISNUMBER($B$10),$B$9&gt;0,$B$10&gt;=0),ISNUMBER(A90),A90&lt;=1),AND(ISNUMBER($B$11),$B$11&gt;=$B$9)),_xlfn.HYPGEOM.DIST($B$10,$B$9,INT(A90*$B$11),$B$11,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="14">
+        <f>IF(ISNUMBER(C90),A90*C90,IF(ISNUMBER(B90),A90*B90,""))</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>IF(ISNUMBER(C90),IF(C90=0,0,A90*C90*(1-($B$9/$B$11)*IF(OR($B$10=0,INT(A90*$B$11)=0),0,_xlfn.HYPGEOM.DIST($B$10-1,$B$9-1,INT(A90*$B$11)-1,$B$11-1,TRUE)/C90))),"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="16">
+        <f>IF(ISNUMBER(C90),$B$9*C90+$B$11*(1-C90),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>Not calculated here: double, sequential (SPRT) and skip-lot plans (Further Reading p. 5-11), ISO 2859 / 3951 look-up (p. 12). Designing (n, c) needs the Peach table 'tabellen AS.pdf' (p. 4), which is not in the course files.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B9 B10 B11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="Type a whole number." type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12 B13 B14 B15 B27 B48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fraction" error="Type a fraction between 0 and 1." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2375,1327 +4000,1327 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="n">
+      <c r="A14" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="39" t="n">
+      <c r="B14" s="40" t="n">
         <v>2.121</v>
       </c>
-      <c r="C14" s="39" t="n">
+      <c r="C14" s="40" t="n">
         <v>3.76</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="40" t="n">
         <v>3.76</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="40" t="n">
         <v>1.88</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="41" t="n">
         <v>0.5642</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G14" s="41" t="n">
         <v>1.7725</v>
       </c>
-      <c r="H14" s="38" t="n">
+      <c r="H14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="39" t="n">
+      <c r="I14" s="40" t="n">
         <v>1.843</v>
       </c>
-      <c r="J14" s="38" t="n">
+      <c r="J14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="39" t="n">
+      <c r="K14" s="40" t="n">
         <v>3.267</v>
       </c>
-      <c r="L14" s="39" t="n">
+      <c r="L14" s="40" t="n">
         <v>1.128</v>
       </c>
-      <c r="M14" s="40" t="n">
+      <c r="M14" s="41" t="n">
         <v>0.8865</v>
       </c>
-      <c r="N14" s="38" t="n">
+      <c r="N14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="39" t="n">
+      <c r="O14" s="40" t="n">
         <v>3.686</v>
       </c>
-      <c r="P14" s="38" t="n">
+      <c r="P14" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="39" t="n">
+      <c r="Q14" s="40" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="n">
+      <c r="A15" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="39" t="n">
+      <c r="B15" s="40" t="n">
         <v>1.732</v>
       </c>
-      <c r="C15" s="39" t="n">
+      <c r="C15" s="40" t="n">
         <v>3.07</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>2.394</v>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="40" t="n">
         <v>1.023</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="41" t="n">
         <v>0.7236</v>
       </c>
-      <c r="G15" s="40" t="n">
+      <c r="G15" s="41" t="n">
         <v>1.382</v>
       </c>
-      <c r="H15" s="38" t="n">
+      <c r="H15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="39" t="n">
+      <c r="I15" s="40" t="n">
         <v>1.858</v>
       </c>
-      <c r="J15" s="38" t="n">
+      <c r="J15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="39" t="n">
+      <c r="K15" s="40" t="n">
         <v>2.568</v>
       </c>
-      <c r="L15" s="39" t="n">
+      <c r="L15" s="40" t="n">
         <v>1.693</v>
       </c>
-      <c r="M15" s="40" t="n">
+      <c r="M15" s="41" t="n">
         <v>0.5907</v>
       </c>
-      <c r="N15" s="38" t="n">
+      <c r="N15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="39" t="n">
+      <c r="O15" s="40" t="n">
         <v>4.358</v>
       </c>
-      <c r="P15" s="38" t="n">
+      <c r="P15" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="41" t="n">
+      <c r="Q15" s="42" t="n">
         <v>2.575</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="n">
+      <c r="A16" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="39" t="n">
+      <c r="B16" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="C16" s="39" t="n">
+      <c r="C16" s="40" t="n">
         <v>2.914</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>1.88</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="40" t="n">
         <v>0.729</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="41" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="G16" s="40" t="n">
+      <c r="G16" s="41" t="n">
         <v>1.2533</v>
       </c>
-      <c r="H16" s="38" t="n">
+      <c r="H16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="39" t="n">
+      <c r="I16" s="40" t="n">
         <v>1.808</v>
       </c>
-      <c r="J16" s="38" t="n">
+      <c r="J16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="39" t="n">
+      <c r="K16" s="40" t="n">
         <v>2.266</v>
       </c>
-      <c r="L16" s="39" t="n">
+      <c r="L16" s="40" t="n">
         <v>2.059</v>
       </c>
-      <c r="M16" s="40" t="n">
+      <c r="M16" s="41" t="n">
         <v>0.4857</v>
       </c>
-      <c r="N16" s="38" t="n">
+      <c r="N16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="39" t="n">
+      <c r="O16" s="40" t="n">
         <v>4.698</v>
       </c>
-      <c r="P16" s="38" t="n">
+      <c r="P16" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="39" t="n">
+      <c r="Q16" s="40" t="n">
         <v>2.282</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="38" t="n">
+      <c r="A17" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="39" t="n">
+      <c r="B17" s="40" t="n">
         <v>1.342</v>
       </c>
-      <c r="C17" s="39" t="n">
+      <c r="C17" s="40" t="n">
         <v>2.884</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="40" t="n">
         <v>1.596</v>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="40" t="n">
         <v>0.577</v>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="41" t="n">
         <v>0.8407</v>
       </c>
-      <c r="G17" s="40" t="n">
+      <c r="G17" s="41" t="n">
         <v>1.1894</v>
       </c>
-      <c r="H17" s="38" t="n">
+      <c r="H17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="39" t="n">
+      <c r="I17" s="40" t="n">
         <v>1.756</v>
       </c>
-      <c r="J17" s="38" t="n">
+      <c r="J17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="39" t="n">
+      <c r="K17" s="40" t="n">
         <v>2.089</v>
       </c>
-      <c r="L17" s="39" t="n">
+      <c r="L17" s="40" t="n">
         <v>2.326</v>
       </c>
-      <c r="M17" s="40" t="n">
+      <c r="M17" s="41" t="n">
         <v>0.4299</v>
       </c>
-      <c r="N17" s="38" t="n">
+      <c r="N17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="39" t="n">
+      <c r="O17" s="40" t="n">
         <v>4.918</v>
       </c>
-      <c r="P17" s="38" t="n">
+      <c r="P17" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="41" t="n">
+      <c r="Q17" s="42" t="n">
         <v>2.115</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="38" t="n">
+      <c r="A18" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="39" t="n">
+      <c r="B18" s="40" t="n">
         <v>1.225</v>
       </c>
-      <c r="C18" s="39" t="n">
+      <c r="C18" s="40" t="n">
         <v>2.899</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>1.41</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="40" t="n">
         <v>0.483</v>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="41" t="n">
         <v>0.8686</v>
       </c>
-      <c r="G18" s="40" t="n">
+      <c r="G18" s="41" t="n">
         <v>1.1512</v>
       </c>
-      <c r="H18" s="39" t="n">
+      <c r="H18" s="40" t="n">
         <v>0.026</v>
       </c>
-      <c r="I18" s="39" t="n">
+      <c r="I18" s="40" t="n">
         <v>1.711</v>
       </c>
-      <c r="J18" s="39" t="n">
+      <c r="J18" s="40" t="n">
         <v>0.03</v>
       </c>
-      <c r="K18" s="39" t="n">
+      <c r="K18" s="40" t="n">
         <v>1.97</v>
       </c>
-      <c r="L18" s="39" t="n">
+      <c r="L18" s="40" t="n">
         <v>2.534</v>
       </c>
-      <c r="M18" s="40" t="n">
+      <c r="M18" s="41" t="n">
         <v>0.3946</v>
       </c>
-      <c r="N18" s="38" t="n">
+      <c r="N18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="39" t="n">
+      <c r="O18" s="40" t="n">
         <v>5.078</v>
       </c>
-      <c r="P18" s="38" t="n">
+      <c r="P18" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="39" t="n">
+      <c r="Q18" s="40" t="n">
         <v>2.004</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="n">
+      <c r="A19" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="39" t="n">
+      <c r="B19" s="40" t="n">
         <v>1.134</v>
       </c>
-      <c r="C19" s="39" t="n">
+      <c r="C19" s="40" t="n">
         <v>2.935</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="40" t="n">
         <v>1.277</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="40" t="n">
         <v>0.419</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="41" t="n">
         <v>0.8882</v>
       </c>
-      <c r="G19" s="40" t="n">
+      <c r="G19" s="41" t="n">
         <v>1.1259</v>
       </c>
-      <c r="H19" s="39" t="n">
+      <c r="H19" s="40" t="n">
         <v>0.105</v>
       </c>
-      <c r="I19" s="39" t="n">
+      <c r="I19" s="40" t="n">
         <v>1.672</v>
       </c>
-      <c r="J19" s="39" t="n">
+      <c r="J19" s="40" t="n">
         <v>0.118</v>
       </c>
-      <c r="K19" s="39" t="n">
+      <c r="K19" s="40" t="n">
         <v>1.882</v>
       </c>
-      <c r="L19" s="39" t="n">
+      <c r="L19" s="40" t="n">
         <v>2.704</v>
       </c>
-      <c r="M19" s="40" t="n">
+      <c r="M19" s="41" t="n">
         <v>0.3698</v>
       </c>
-      <c r="N19" s="41" t="n">
+      <c r="N19" s="42" t="n">
         <v>0.205</v>
       </c>
-      <c r="O19" s="41" t="n">
+      <c r="O19" s="42" t="n">
         <v>5.203</v>
       </c>
-      <c r="P19" s="39" t="n">
+      <c r="P19" s="40" t="n">
         <v>0.076</v>
       </c>
-      <c r="Q19" s="39" t="n">
+      <c r="Q19" s="40" t="n">
         <v>1.924</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="n">
+      <c r="A20" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="39" t="n">
+      <c r="B20" s="40" t="n">
         <v>1.061</v>
       </c>
-      <c r="C20" s="39" t="n">
+      <c r="C20" s="40" t="n">
         <v>2.98</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D20" s="40" t="n">
         <v>1.175</v>
       </c>
-      <c r="E20" s="39" t="n">
+      <c r="E20" s="40" t="n">
         <v>0.373</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="41" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="G20" s="40" t="n">
+      <c r="G20" s="41" t="n">
         <v>1.1078</v>
       </c>
-      <c r="H20" s="39" t="n">
+      <c r="H20" s="40" t="n">
         <v>0.167</v>
       </c>
-      <c r="I20" s="39" t="n">
+      <c r="I20" s="40" t="n">
         <v>1.638</v>
       </c>
-      <c r="J20" s="39" t="n">
+      <c r="J20" s="40" t="n">
         <v>0.185</v>
       </c>
-      <c r="K20" s="39" t="n">
+      <c r="K20" s="40" t="n">
         <v>1.815</v>
       </c>
-      <c r="L20" s="39" t="n">
+      <c r="L20" s="40" t="n">
         <v>2.847</v>
       </c>
-      <c r="M20" s="40" t="n">
+      <c r="M20" s="41" t="n">
         <v>0.3512</v>
       </c>
-      <c r="N20" s="41" t="n">
+      <c r="N20" s="42" t="n">
         <v>0.387</v>
       </c>
-      <c r="O20" s="41" t="n">
+      <c r="O20" s="42" t="n">
         <v>5.307</v>
       </c>
-      <c r="P20" s="39" t="n">
+      <c r="P20" s="40" t="n">
         <v>0.136</v>
       </c>
-      <c r="Q20" s="39" t="n">
+      <c r="Q20" s="40" t="n">
         <v>1.864</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="38" t="n">
+      <c r="A21" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="39" t="n">
+      <c r="B21" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="39" t="n">
+      <c r="C21" s="40" t="n">
         <v>3.03</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D21" s="40" t="n">
         <v>1.094</v>
       </c>
-      <c r="E21" s="39" t="n">
+      <c r="E21" s="40" t="n">
         <v>0.337</v>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="41" t="n">
         <v>0.9139</v>
       </c>
-      <c r="G21" s="40" t="n">
+      <c r="G21" s="41" t="n">
         <v>1.0942</v>
       </c>
-      <c r="H21" s="39" t="n">
+      <c r="H21" s="40" t="n">
         <v>0.219</v>
       </c>
-      <c r="I21" s="39" t="n">
+      <c r="I21" s="40" t="n">
         <v>1.609</v>
       </c>
-      <c r="J21" s="39" t="n">
+      <c r="J21" s="40" t="n">
         <v>0.239</v>
       </c>
-      <c r="K21" s="39" t="n">
+      <c r="K21" s="40" t="n">
         <v>1.761</v>
       </c>
-      <c r="L21" s="39" t="n">
+      <c r="L21" s="40" t="n">
         <v>2.97</v>
       </c>
-      <c r="M21" s="40" t="n">
+      <c r="M21" s="41" t="n">
         <v>0.3367</v>
       </c>
-      <c r="N21" s="41" t="n">
+      <c r="N21" s="42" t="n">
         <v>0.546</v>
       </c>
-      <c r="O21" s="41" t="n">
+      <c r="O21" s="42" t="n">
         <v>5.394</v>
       </c>
-      <c r="P21" s="39" t="n">
+      <c r="P21" s="40" t="n">
         <v>0.184</v>
       </c>
-      <c r="Q21" s="39" t="n">
+      <c r="Q21" s="40" t="n">
         <v>1.816</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="38" t="n">
+      <c r="A22" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="39" t="n">
+      <c r="B22" s="40" t="n">
         <v>0.949</v>
       </c>
-      <c r="C22" s="39" t="n">
+      <c r="C22" s="40" t="n">
         <v>3.085</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D22" s="40" t="n">
         <v>1.028</v>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="40" t="n">
         <v>0.308</v>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="41" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G22" s="40" t="n">
+      <c r="G22" s="41" t="n">
         <v>1.0837</v>
       </c>
-      <c r="H22" s="39" t="n">
+      <c r="H22" s="40" t="n">
         <v>0.262</v>
       </c>
-      <c r="I22" s="39" t="n">
+      <c r="I22" s="40" t="n">
         <v>1.584</v>
       </c>
-      <c r="J22" s="39" t="n">
+      <c r="J22" s="40" t="n">
         <v>0.284</v>
       </c>
-      <c r="K22" s="39" t="n">
+      <c r="K22" s="40" t="n">
         <v>1.716</v>
       </c>
-      <c r="L22" s="39" t="n">
+      <c r="L22" s="40" t="n">
         <v>3.078</v>
       </c>
-      <c r="M22" s="40" t="n">
+      <c r="M22" s="41" t="n">
         <v>0.3249</v>
       </c>
-      <c r="N22" s="39" t="n">
+      <c r="N22" s="40" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="O22" s="39" t="n">
+      <c r="O22" s="40" t="n">
         <v>5.469</v>
       </c>
-      <c r="P22" s="39" t="n">
+      <c r="P22" s="40" t="n">
         <v>0.223</v>
       </c>
-      <c r="Q22" s="39" t="n">
+      <c r="Q22" s="40" t="n">
         <v>1.777</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="n">
+      <c r="A23" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="39" t="n">
+      <c r="B23" s="40" t="n">
         <v>0.905</v>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="40" t="n">
         <v>3.136</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D23" s="40" t="n">
         <v>0.973</v>
       </c>
-      <c r="E23" s="39" t="n">
+      <c r="E23" s="40" t="n">
         <v>0.285</v>
       </c>
-      <c r="F23" s="40" t="n">
+      <c r="F23" s="41" t="n">
         <v>0.93</v>
       </c>
-      <c r="G23" s="40" t="n">
+      <c r="G23" s="41" t="n">
         <v>1.0753</v>
       </c>
-      <c r="H23" s="39" t="n">
+      <c r="H23" s="40" t="n">
         <v>0.299</v>
       </c>
-      <c r="I23" s="39" t="n">
+      <c r="I23" s="40" t="n">
         <v>1.561</v>
       </c>
-      <c r="J23" s="39" t="n">
+      <c r="J23" s="40" t="n">
         <v>0.321</v>
       </c>
-      <c r="K23" s="39" t="n">
+      <c r="K23" s="40" t="n">
         <v>1.679</v>
       </c>
-      <c r="L23" s="39" t="n">
+      <c r="L23" s="40" t="n">
         <v>3.173</v>
       </c>
-      <c r="M23" s="40" t="n">
+      <c r="M23" s="41" t="n">
         <v>0.3152</v>
       </c>
-      <c r="N23" s="41" t="n">
+      <c r="N23" s="42" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="O23" s="41" t="n">
+      <c r="O23" s="42" t="n">
         <v>5.534</v>
       </c>
-      <c r="P23" s="39" t="n">
+      <c r="P23" s="40" t="n">
         <v>0.256</v>
       </c>
-      <c r="Q23" s="39" t="n">
+      <c r="Q23" s="40" t="n">
         <v>1.744</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="38" t="n">
+      <c r="A24" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="39" t="n">
+      <c r="B24" s="40" t="n">
         <v>0.866</v>
       </c>
-      <c r="C24" s="39" t="n">
+      <c r="C24" s="40" t="n">
         <v>3.189</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D24" s="40" t="n">
         <v>0.925</v>
       </c>
-      <c r="E24" s="39" t="n">
+      <c r="E24" s="40" t="n">
         <v>0.266</v>
       </c>
-      <c r="F24" s="40" t="n">
+      <c r="F24" s="41" t="n">
         <v>0.9359</v>
       </c>
-      <c r="G24" s="40" t="n">
+      <c r="G24" s="41" t="n">
         <v>1.0684</v>
       </c>
-      <c r="H24" s="39" t="n">
+      <c r="H24" s="40" t="n">
         <v>0.331</v>
       </c>
-      <c r="I24" s="39" t="n">
+      <c r="I24" s="40" t="n">
         <v>1.541</v>
       </c>
-      <c r="J24" s="39" t="n">
+      <c r="J24" s="40" t="n">
         <v>0.354</v>
       </c>
-      <c r="K24" s="39" t="n">
+      <c r="K24" s="40" t="n">
         <v>1.646</v>
       </c>
-      <c r="L24" s="39" t="n">
+      <c r="L24" s="40" t="n">
         <v>3.258</v>
       </c>
-      <c r="M24" s="40" t="n">
+      <c r="M24" s="41" t="n">
         <v>0.3069</v>
       </c>
-      <c r="N24" s="41" t="n">
+      <c r="N24" s="42" t="n">
         <v>0.924</v>
       </c>
-      <c r="O24" s="41" t="n">
+      <c r="O24" s="42" t="n">
         <v>5.592</v>
       </c>
-      <c r="P24" s="41" t="n">
+      <c r="P24" s="42" t="n">
         <v>0.284</v>
       </c>
-      <c r="Q24" s="41" t="n">
+      <c r="Q24" s="42" t="n">
         <v>1.716</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="38" t="n">
+      <c r="A25" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="39" t="n">
+      <c r="B25" s="40" t="n">
         <v>0.832</v>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="40" t="n">
         <v>3.242</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D25" s="40" t="n">
         <v>0.884</v>
       </c>
-      <c r="E25" s="39" t="n">
+      <c r="E25" s="40" t="n">
         <v>0.249</v>
       </c>
-      <c r="F25" s="40" t="n">
+      <c r="F25" s="41" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="G25" s="40" t="n">
+      <c r="G25" s="41" t="n">
         <v>1.0627</v>
       </c>
-      <c r="H25" s="39" t="n">
+      <c r="H25" s="40" t="n">
         <v>0.359</v>
       </c>
-      <c r="I25" s="39" t="n">
+      <c r="I25" s="40" t="n">
         <v>1.523</v>
       </c>
-      <c r="J25" s="39" t="n">
+      <c r="J25" s="40" t="n">
         <v>0.382</v>
       </c>
-      <c r="K25" s="39" t="n">
+      <c r="K25" s="40" t="n">
         <v>1.618</v>
       </c>
-      <c r="L25" s="39" t="n">
+      <c r="L25" s="40" t="n">
         <v>3.336</v>
       </c>
-      <c r="M25" s="40" t="n">
+      <c r="M25" s="41" t="n">
         <v>0.2998</v>
       </c>
-      <c r="N25" s="41" t="n">
+      <c r="N25" s="42" t="n">
         <v>1.026</v>
       </c>
-      <c r="O25" s="41" t="n">
+      <c r="O25" s="42" t="n">
         <v>5.646</v>
       </c>
-      <c r="P25" s="41" t="n">
+      <c r="P25" s="42" t="n">
         <v>0.308</v>
       </c>
-      <c r="Q25" s="41" t="n">
+      <c r="Q25" s="42" t="n">
         <v>1.692</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="38" t="n">
+      <c r="A26" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="39" t="n">
+      <c r="B26" s="40" t="n">
         <v>0.802</v>
       </c>
-      <c r="C26" s="39" t="n">
+      <c r="C26" s="40" t="n">
         <v>3.295</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D26" s="40" t="n">
         <v>0.848</v>
       </c>
-      <c r="E26" s="39" t="n">
+      <c r="E26" s="40" t="n">
         <v>0.235</v>
       </c>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="41" t="n">
         <v>0.9453</v>
       </c>
-      <c r="G26" s="40" t="n">
+      <c r="G26" s="41" t="n">
         <v>1.0579</v>
       </c>
-      <c r="H26" s="39" t="n">
+      <c r="H26" s="40" t="n">
         <v>0.384</v>
       </c>
-      <c r="I26" s="39" t="n">
+      <c r="I26" s="40" t="n">
         <v>1.507</v>
       </c>
-      <c r="J26" s="39" t="n">
+      <c r="J26" s="40" t="n">
         <v>0.406</v>
       </c>
-      <c r="K26" s="39" t="n">
+      <c r="K26" s="40" t="n">
         <v>1.594</v>
       </c>
-      <c r="L26" s="39" t="n">
+      <c r="L26" s="40" t="n">
         <v>3.407</v>
       </c>
-      <c r="M26" s="40" t="n">
+      <c r="M26" s="41" t="n">
         <v>0.2935</v>
       </c>
-      <c r="N26" s="41" t="n">
+      <c r="N26" s="42" t="n">
         <v>1.121</v>
       </c>
-      <c r="O26" s="41" t="n">
+      <c r="O26" s="42" t="n">
         <v>5.693</v>
       </c>
-      <c r="P26" s="41" t="n">
+      <c r="P26" s="42" t="n">
         <v>0.329</v>
       </c>
-      <c r="Q26" s="41" t="n">
+      <c r="Q26" s="42" t="n">
         <v>1.671</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="38" t="n">
+      <c r="A27" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="39" t="n">
+      <c r="B27" s="40" t="n">
         <v>0.775</v>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="40" t="n">
         <v>3.347</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D27" s="40" t="n">
         <v>0.8159999999999999</v>
       </c>
-      <c r="E27" s="39" t="n">
+      <c r="E27" s="40" t="n">
         <v>0.223</v>
       </c>
-      <c r="F27" s="40" t="n">
+      <c r="F27" s="41" t="n">
         <v>0.949</v>
       </c>
-      <c r="G27" s="40" t="n">
+      <c r="G27" s="41" t="n">
         <v>1.0537</v>
       </c>
-      <c r="H27" s="39" t="n">
+      <c r="H27" s="40" t="n">
         <v>0.406</v>
       </c>
-      <c r="I27" s="39" t="n">
+      <c r="I27" s="40" t="n">
         <v>1.492</v>
       </c>
-      <c r="J27" s="39" t="n">
+      <c r="J27" s="40" t="n">
         <v>0.428</v>
       </c>
-      <c r="K27" s="39" t="n">
+      <c r="K27" s="40" t="n">
         <v>1.572</v>
       </c>
-      <c r="L27" s="39" t="n">
+      <c r="L27" s="40" t="n">
         <v>3.472</v>
       </c>
-      <c r="M27" s="40" t="n">
+      <c r="M27" s="41" t="n">
         <v>0.288</v>
       </c>
-      <c r="N27" s="41" t="n">
+      <c r="N27" s="42" t="n">
         <v>1.207</v>
       </c>
-      <c r="O27" s="41" t="n">
+      <c r="O27" s="42" t="n">
         <v>5.737</v>
       </c>
-      <c r="P27" s="41" t="n">
+      <c r="P27" s="42" t="n">
         <v>0.348</v>
       </c>
-      <c r="Q27" s="41" t="n">
+      <c r="Q27" s="42" t="n">
         <v>1.652</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="38" t="n">
+      <c r="A28" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B28" s="39" t="n">
+      <c r="B28" s="40" t="n">
         <v>0.75</v>
       </c>
-      <c r="C28" s="39" t="n">
+      <c r="C28" s="40" t="n">
         <v>3.398</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D28" s="40" t="n">
         <v>0.788</v>
       </c>
-      <c r="E28" s="39" t="n">
+      <c r="E28" s="40" t="n">
         <v>0.212</v>
       </c>
-      <c r="F28" s="40" t="n">
+      <c r="F28" s="41" t="n">
         <v>0.9523</v>
       </c>
-      <c r="G28" s="40" t="n">
+      <c r="G28" s="41" t="n">
         <v>1.0501</v>
       </c>
-      <c r="H28" s="39" t="n">
+      <c r="H28" s="40" t="n">
         <v>0.427</v>
       </c>
-      <c r="I28" s="39" t="n">
+      <c r="I28" s="40" t="n">
         <v>1.478</v>
       </c>
-      <c r="J28" s="39" t="n">
+      <c r="J28" s="40" t="n">
         <v>0.448</v>
       </c>
-      <c r="K28" s="39" t="n">
+      <c r="K28" s="40" t="n">
         <v>1.552</v>
       </c>
-      <c r="L28" s="39" t="n">
+      <c r="L28" s="40" t="n">
         <v>3.532</v>
       </c>
-      <c r="M28" s="40" t="n">
+      <c r="M28" s="41" t="n">
         <v>0.2831</v>
       </c>
-      <c r="N28" s="41" t="n">
+      <c r="N28" s="42" t="n">
         <v>1.285</v>
       </c>
-      <c r="O28" s="41" t="n">
+      <c r="O28" s="42" t="n">
         <v>5.779</v>
       </c>
-      <c r="P28" s="41" t="n">
+      <c r="P28" s="42" t="n">
         <v>0.364</v>
       </c>
-      <c r="Q28" s="41" t="n">
+      <c r="Q28" s="42" t="n">
         <v>1.636</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="38" t="n">
+      <c r="A29" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="B29" s="39" t="n">
+      <c r="B29" s="40" t="n">
         <v>0.728</v>
       </c>
-      <c r="C29" s="39" t="n">
+      <c r="C29" s="40" t="n">
         <v>3.448</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D29" s="40" t="n">
         <v>0.762</v>
       </c>
-      <c r="E29" s="39" t="n">
+      <c r="E29" s="40" t="n">
         <v>0.203</v>
       </c>
-      <c r="F29" s="40" t="n">
+      <c r="F29" s="41" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="G29" s="40" t="n">
+      <c r="G29" s="41" t="n">
         <v>1.047</v>
       </c>
-      <c r="H29" s="39" t="n">
+      <c r="H29" s="40" t="n">
         <v>0.445</v>
       </c>
-      <c r="I29" s="39" t="n">
+      <c r="I29" s="40" t="n">
         <v>1.465</v>
       </c>
-      <c r="J29" s="39" t="n">
+      <c r="J29" s="40" t="n">
         <v>0.466</v>
       </c>
-      <c r="K29" s="39" t="n">
+      <c r="K29" s="40" t="n">
         <v>1.534</v>
       </c>
-      <c r="L29" s="39" t="n">
+      <c r="L29" s="40" t="n">
         <v>3.588</v>
       </c>
-      <c r="M29" s="40" t="n">
+      <c r="M29" s="41" t="n">
         <v>0.2787</v>
       </c>
-      <c r="N29" s="41" t="n">
+      <c r="N29" s="42" t="n">
         <v>1.359</v>
       </c>
-      <c r="O29" s="41" t="n">
+      <c r="O29" s="42" t="n">
         <v>5.817</v>
       </c>
-      <c r="P29" s="41" t="n">
+      <c r="P29" s="42" t="n">
         <v>0.379</v>
       </c>
-      <c r="Q29" s="41" t="n">
+      <c r="Q29" s="42" t="n">
         <v>1.621</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="38" t="n">
+      <c r="A30" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="39" t="n">
+      <c r="B30" s="40" t="n">
         <v>0.707</v>
       </c>
-      <c r="C30" s="39" t="n">
+      <c r="C30" s="40" t="n">
         <v>3.497</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D30" s="40" t="n">
         <v>0.738</v>
       </c>
-      <c r="E30" s="39" t="n">
+      <c r="E30" s="40" t="n">
         <v>0.194</v>
       </c>
-      <c r="F30" s="40" t="n">
+      <c r="F30" s="41" t="n">
         <v>0.9576</v>
       </c>
-      <c r="G30" s="40" t="n">
+      <c r="G30" s="41" t="n">
         <v>1.0442</v>
       </c>
-      <c r="H30" s="39" t="n">
+      <c r="H30" s="40" t="n">
         <v>0.461</v>
       </c>
-      <c r="I30" s="39" t="n">
+      <c r="I30" s="40" t="n">
         <v>1.454</v>
       </c>
-      <c r="J30" s="39" t="n">
+      <c r="J30" s="40" t="n">
         <v>0.482</v>
       </c>
-      <c r="K30" s="39" t="n">
+      <c r="K30" s="40" t="n">
         <v>1.518</v>
       </c>
-      <c r="L30" s="39" t="n">
+      <c r="L30" s="40" t="n">
         <v>3.64</v>
       </c>
-      <c r="M30" s="40" t="n">
+      <c r="M30" s="41" t="n">
         <v>0.2747</v>
       </c>
-      <c r="N30" s="41" t="n">
+      <c r="N30" s="42" t="n">
         <v>1.426</v>
       </c>
-      <c r="O30" s="41" t="n">
+      <c r="O30" s="42" t="n">
         <v>5.854</v>
       </c>
-      <c r="P30" s="41" t="n">
+      <c r="P30" s="42" t="n">
         <v>0.392</v>
       </c>
-      <c r="Q30" s="39" t="n">
+      <c r="Q30" s="40" t="n">
         <v>1.608</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="38" t="n">
+      <c r="A31" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="39" t="n">
+      <c r="B31" s="40" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C31" s="39" t="n">
+      <c r="C31" s="40" t="n">
         <v>3.545</v>
       </c>
-      <c r="D31" s="39" t="n">
+      <c r="D31" s="40" t="n">
         <v>0.717</v>
       </c>
-      <c r="E31" s="39" t="n">
+      <c r="E31" s="40" t="n">
         <v>0.187</v>
       </c>
-      <c r="F31" s="40" t="n">
+      <c r="F31" s="41" t="n">
         <v>0.9599</v>
       </c>
-      <c r="G31" s="40" t="n">
+      <c r="G31" s="41" t="n">
         <v>1.0418</v>
       </c>
-      <c r="H31" s="39" t="n">
+      <c r="H31" s="40" t="n">
         <v>0.477</v>
       </c>
-      <c r="I31" s="39" t="n">
+      <c r="I31" s="40" t="n">
         <v>1.443</v>
       </c>
-      <c r="J31" s="39" t="n">
+      <c r="J31" s="40" t="n">
         <v>0.497</v>
       </c>
-      <c r="K31" s="39" t="n">
+      <c r="K31" s="40" t="n">
         <v>1.503</v>
       </c>
-      <c r="L31" s="39" t="n">
+      <c r="L31" s="40" t="n">
         <v>3.689</v>
       </c>
-      <c r="M31" s="40" t="n">
+      <c r="M31" s="41" t="n">
         <v>0.2711</v>
       </c>
-      <c r="N31" s="41" t="n">
+      <c r="N31" s="42" t="n">
         <v>1.49</v>
       </c>
-      <c r="O31" s="41" t="n">
+      <c r="O31" s="42" t="n">
         <v>5.888</v>
       </c>
-      <c r="P31" s="41" t="n">
+      <c r="P31" s="42" t="n">
         <v>0.404</v>
       </c>
-      <c r="Q31" s="41" t="n">
+      <c r="Q31" s="42" t="n">
         <v>1.596</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="38" t="n">
+      <c r="A32" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="39" t="n">
+      <c r="B32" s="40" t="n">
         <v>0.671</v>
       </c>
-      <c r="C32" s="39" t="n">
+      <c r="C32" s="40" t="n">
         <v>3.592</v>
       </c>
-      <c r="D32" s="39" t="n">
+      <c r="D32" s="40" t="n">
         <v>0.697</v>
       </c>
-      <c r="E32" s="39" t="n">
+      <c r="E32" s="40" t="n">
         <v>0.18</v>
       </c>
-      <c r="F32" s="40" t="n">
+      <c r="F32" s="41" t="n">
         <v>0.9619</v>
       </c>
-      <c r="G32" s="40" t="n">
+      <c r="G32" s="41" t="n">
         <v>1.0396</v>
       </c>
-      <c r="H32" s="39" t="n">
+      <c r="H32" s="40" t="n">
         <v>0.491</v>
       </c>
-      <c r="I32" s="39" t="n">
+      <c r="I32" s="40" t="n">
         <v>1.433</v>
       </c>
-      <c r="J32" s="39" t="n">
+      <c r="J32" s="40" t="n">
         <v>0.51</v>
       </c>
-      <c r="K32" s="39" t="n">
+      <c r="K32" s="40" t="n">
         <v>1.49</v>
       </c>
-      <c r="L32" s="39" t="n">
+      <c r="L32" s="40" t="n">
         <v>3.735</v>
       </c>
-      <c r="M32" s="40" t="n">
+      <c r="M32" s="41" t="n">
         <v>0.2677</v>
       </c>
-      <c r="N32" s="41" t="n">
+      <c r="N32" s="42" t="n">
         <v>1.548</v>
       </c>
-      <c r="O32" s="41" t="n">
+      <c r="O32" s="42" t="n">
         <v>5.922</v>
       </c>
-      <c r="P32" s="41" t="n">
+      <c r="P32" s="42" t="n">
         <v>0.414</v>
       </c>
-      <c r="Q32" s="41" t="n">
+      <c r="Q32" s="42" t="n">
         <v>1.586</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="38" t="n">
+      <c r="A33" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="39" t="n">
+      <c r="B33" s="40" t="n">
         <v>0.655</v>
       </c>
-      <c r="C33" s="39" t="n">
+      <c r="C33" s="40" t="n">
         <v>3.639</v>
       </c>
-      <c r="D33" s="39" t="n">
+      <c r="D33" s="40" t="n">
         <v>0.679</v>
       </c>
-      <c r="E33" s="39" t="n">
+      <c r="E33" s="40" t="n">
         <v>0.173</v>
       </c>
-      <c r="F33" s="40" t="n">
+      <c r="F33" s="41" t="n">
         <v>0.9638</v>
       </c>
-      <c r="G33" s="40" t="n">
+      <c r="G33" s="41" t="n">
         <v>1.0376</v>
       </c>
-      <c r="H33" s="39" t="n">
+      <c r="H33" s="40" t="n">
         <v>0.504</v>
       </c>
-      <c r="I33" s="39" t="n">
+      <c r="I33" s="40" t="n">
         <v>1.424</v>
       </c>
-      <c r="J33" s="39" t="n">
+      <c r="J33" s="40" t="n">
         <v>0.523</v>
       </c>
-      <c r="K33" s="39" t="n">
+      <c r="K33" s="40" t="n">
         <v>1.477</v>
       </c>
-      <c r="L33" s="39" t="n">
+      <c r="L33" s="40" t="n">
         <v>3.778</v>
       </c>
-      <c r="M33" s="40" t="n">
+      <c r="M33" s="41" t="n">
         <v>0.2647</v>
       </c>
-      <c r="N33" s="41" t="n">
+      <c r="N33" s="42" t="n">
         <v>1.606</v>
       </c>
-      <c r="O33" s="41" t="n">
+      <c r="O33" s="42" t="n">
         <v>5.95</v>
       </c>
-      <c r="P33" s="39" t="n">
+      <c r="P33" s="40" t="n">
         <v>0.425</v>
       </c>
-      <c r="Q33" s="39" t="n">
+      <c r="Q33" s="40" t="n">
         <v>1.575</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="38" t="n">
+      <c r="A34" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="39" t="n">
+      <c r="B34" s="40" t="n">
         <v>0.64</v>
       </c>
-      <c r="C34" s="39" t="n">
+      <c r="C34" s="40" t="n">
         <v>3.684</v>
       </c>
-      <c r="D34" s="39" t="n">
+      <c r="D34" s="40" t="n">
         <v>0.662</v>
       </c>
-      <c r="E34" s="39" t="n">
+      <c r="E34" s="40" t="n">
         <v>0.167</v>
       </c>
-      <c r="F34" s="40" t="n">
+      <c r="F34" s="41" t="n">
         <v>0.9655</v>
       </c>
-      <c r="G34" s="40" t="n">
+      <c r="G34" s="41" t="n">
         <v>1.0358</v>
       </c>
-      <c r="H34" s="39" t="n">
+      <c r="H34" s="40" t="n">
         <v>0.516</v>
       </c>
-      <c r="I34" s="39" t="n">
+      <c r="I34" s="40" t="n">
         <v>1.415</v>
       </c>
-      <c r="J34" s="39" t="n">
+      <c r="J34" s="40" t="n">
         <v>0.534</v>
       </c>
-      <c r="K34" s="39" t="n">
+      <c r="K34" s="40" t="n">
         <v>1.466</v>
       </c>
-      <c r="L34" s="39" t="n">
+      <c r="L34" s="40" t="n">
         <v>3.819</v>
       </c>
-      <c r="M34" s="40" t="n">
+      <c r="M34" s="41" t="n">
         <v>0.2618</v>
       </c>
-      <c r="N34" s="39" t="n">
+      <c r="N34" s="40" t="n">
         <v>1.659</v>
       </c>
-      <c r="O34" s="39" t="n">
+      <c r="O34" s="40" t="n">
         <v>5.979</v>
       </c>
-      <c r="P34" s="39" t="n">
+      <c r="P34" s="40" t="n">
         <v>0.434</v>
       </c>
-      <c r="Q34" s="39" t="n">
+      <c r="Q34" s="40" t="n">
         <v>1.566</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="38" t="n">
+      <c r="A35" s="39" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="39" t="n">
+      <c r="B35" s="40" t="n">
         <v>0.626</v>
       </c>
-      <c r="C35" s="39" t="n">
+      <c r="C35" s="40" t="n">
         <v>3.729</v>
       </c>
-      <c r="D35" s="39" t="n">
+      <c r="D35" s="40" t="n">
         <v>0.647</v>
       </c>
-      <c r="E35" s="39" t="n">
+      <c r="E35" s="40" t="n">
         <v>0.162</v>
       </c>
-      <c r="F35" s="40" t="n">
+      <c r="F35" s="41" t="n">
         <v>0.967</v>
       </c>
-      <c r="G35" s="40" t="n">
+      <c r="G35" s="41" t="n">
         <v>1.0342</v>
       </c>
-      <c r="H35" s="39" t="n">
+      <c r="H35" s="40" t="n">
         <v>0.527</v>
       </c>
-      <c r="I35" s="39" t="n">
+      <c r="I35" s="40" t="n">
         <v>1.407</v>
       </c>
-      <c r="J35" s="39" t="n">
+      <c r="J35" s="40" t="n">
         <v>0.545</v>
       </c>
-      <c r="K35" s="39" t="n">
+      <c r="K35" s="40" t="n">
         <v>1.455</v>
       </c>
-      <c r="L35" s="39" t="n">
+      <c r="L35" s="40" t="n">
         <v>3.858</v>
       </c>
-      <c r="M35" s="40" t="n">
+      <c r="M35" s="41" t="n">
         <v>0.2592</v>
       </c>
-      <c r="N35" s="39" t="n">
+      <c r="N35" s="40" t="n">
         <v>1.71</v>
       </c>
-      <c r="O35" s="39" t="n">
+      <c r="O35" s="40" t="n">
         <v>6.006</v>
       </c>
-      <c r="P35" s="39" t="n">
+      <c r="P35" s="40" t="n">
         <v>0.443</v>
       </c>
-      <c r="Q35" s="39" t="n">
+      <c r="Q35" s="40" t="n">
         <v>1.557</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="n">
+      <c r="A36" s="39" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="39" t="n">
+      <c r="B36" s="40" t="n">
         <v>0.612</v>
       </c>
-      <c r="C36" s="39" t="n">
+      <c r="C36" s="40" t="n">
         <v>3.773</v>
       </c>
-      <c r="D36" s="39" t="n">
+      <c r="D36" s="40" t="n">
         <v>0.632</v>
       </c>
-      <c r="E36" s="39" t="n">
+      <c r="E36" s="40" t="n">
         <v>0.157</v>
       </c>
-      <c r="F36" s="40" t="n">
+      <c r="F36" s="41" t="n">
         <v>0.9684</v>
       </c>
-      <c r="G36" s="40" t="n">
+      <c r="G36" s="41" t="n">
         <v>1.0327</v>
       </c>
-      <c r="H36" s="39" t="n">
+      <c r="H36" s="40" t="n">
         <v>0.538</v>
       </c>
-      <c r="I36" s="39" t="n">
+      <c r="I36" s="40" t="n">
         <v>1.399</v>
       </c>
-      <c r="J36" s="39" t="n">
+      <c r="J36" s="40" t="n">
         <v>0.555</v>
       </c>
-      <c r="K36" s="39" t="n">
+      <c r="K36" s="40" t="n">
         <v>1.445</v>
       </c>
-      <c r="L36" s="39" t="n">
+      <c r="L36" s="40" t="n">
         <v>3.895</v>
       </c>
-      <c r="M36" s="40" t="n">
+      <c r="M36" s="41" t="n">
         <v>0.2567</v>
       </c>
-      <c r="N36" s="39" t="n">
+      <c r="N36" s="40" t="n">
         <v>1.759</v>
       </c>
-      <c r="O36" s="39" t="n">
+      <c r="O36" s="40" t="n">
         <v>6.031</v>
       </c>
-      <c r="P36" s="41" t="n">
+      <c r="P36" s="42" t="n">
         <v>0.452</v>
       </c>
-      <c r="Q36" s="39" t="n">
+      <c r="Q36" s="40" t="n">
         <v>1.548</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="38" t="n">
+      <c r="A37" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="39" t="n">
+      <c r="B37" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="C37" s="39" t="n">
+      <c r="C37" s="40" t="n">
         <v>3.816</v>
       </c>
-      <c r="D37" s="39" t="n">
+      <c r="D37" s="40" t="n">
         <v>0.619</v>
       </c>
-      <c r="E37" s="39" t="n">
+      <c r="E37" s="40" t="n">
         <v>0.153</v>
       </c>
-      <c r="F37" s="42" t="n">
+      <c r="F37" s="43" t="n">
         <v>0.9696</v>
       </c>
-      <c r="G37" s="40" t="n">
+      <c r="G37" s="41" t="n">
         <v>1.0313</v>
       </c>
-      <c r="H37" s="39" t="n">
+      <c r="H37" s="40" t="n">
         <v>0.548</v>
       </c>
-      <c r="I37" s="39" t="n">
+      <c r="I37" s="40" t="n">
         <v>1.392</v>
       </c>
-      <c r="J37" s="39" t="n">
+      <c r="J37" s="40" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="K37" s="39" t="n">
+      <c r="K37" s="40" t="n">
         <v>1.435</v>
       </c>
-      <c r="L37" s="39" t="n">
+      <c r="L37" s="40" t="n">
         <v>3.931</v>
       </c>
-      <c r="M37" s="40" t="n">
+      <c r="M37" s="41" t="n">
         <v>0.2544</v>
       </c>
-      <c r="N37" s="41" t="n">
+      <c r="N37" s="42" t="n">
         <v>1.804</v>
       </c>
-      <c r="O37" s="41" t="n">
+      <c r="O37" s="42" t="n">
         <v>6.058</v>
       </c>
-      <c r="P37" s="39" t="n">
+      <c r="P37" s="40" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q37" s="39" t="n">
+      <c r="Q37" s="40" t="n">
         <v>1.541</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="A38" s="44" t="inlineStr">
         <is>
           <t>&gt;25</t>
         </is>
       </c>
-      <c r="B38" s="43" t="inlineStr">
+      <c r="B38" s="44" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="C38" s="43" t="inlineStr"/>
-      <c r="D38" s="43" t="inlineStr">
+      <c r="C38" s="44" t="inlineStr"/>
+      <c r="D38" s="44" t="inlineStr">
         <is>
           <t>3/sqrt(n)</t>
         </is>
       </c>
-      <c r="E38" s="43" t="inlineStr"/>
-      <c r="F38" s="40" t="n">
+      <c r="E38" s="44" t="inlineStr"/>
+      <c r="F38" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="40" t="n">
+      <c r="G38" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="43" t="inlineStr">
+      <c r="H38" s="44" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="I38" s="43" t="inlineStr">
+      <c r="I38" s="44" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="J38" s="43" t="inlineStr">
+      <c r="J38" s="44" t="inlineStr">
         <is>
           <t>**</t>
         </is>
       </c>
-      <c r="K38" s="43" t="inlineStr">
+      <c r="K38" s="44" t="inlineStr">
         <is>
           <t>***</t>
         </is>
       </c>
-      <c r="L38" s="43" t="inlineStr"/>
-      <c r="M38" s="43" t="inlineStr"/>
-      <c r="N38" s="43" t="inlineStr"/>
-      <c r="O38" s="43" t="inlineStr"/>
-      <c r="P38" s="43" t="inlineStr"/>
-      <c r="Q38" s="43" t="inlineStr"/>
+      <c r="L38" s="44" t="inlineStr"/>
+      <c r="M38" s="44" t="inlineStr"/>
+      <c r="N38" s="44" t="inlineStr"/>
+      <c r="O38" s="44" t="inlineStr"/>
+      <c r="P38" s="44" t="inlineStr"/>
+      <c r="Q38" s="44" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="26" t="inlineStr">
@@ -3746,580 +5371,580 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="38" t="n">
+      <c r="A44" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B44" s="40" t="n">
         <v>1.128</v>
       </c>
-      <c r="C44" s="40" t="n">
+      <c r="C44" s="41" t="n">
         <v>0.5642</v>
       </c>
-      <c r="D44" s="40" t="n">
+      <c r="D44" s="41" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="E44" s="40" t="n">
+      <c r="E44" s="41" t="n">
         <v>0.8525</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="n">
+      <c r="A45" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B45" s="39" t="n">
+      <c r="B45" s="40" t="n">
         <v>1.693</v>
       </c>
-      <c r="C45" s="40" t="n">
+      <c r="C45" s="41" t="n">
         <v>0.7236</v>
       </c>
-      <c r="D45" s="40" t="n">
+      <c r="D45" s="41" t="n">
         <v>0.8862</v>
       </c>
-      <c r="E45" s="40" t="n">
+      <c r="E45" s="41" t="n">
         <v>0.8884</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38" t="n">
+      <c r="A46" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="39" t="n">
+      <c r="B46" s="40" t="n">
         <v>2.059</v>
       </c>
-      <c r="C46" s="40" t="n">
+      <c r="C46" s="41" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="D46" s="40" t="n">
+      <c r="D46" s="41" t="n">
         <v>0.9213</v>
       </c>
-      <c r="E46" s="40" t="n">
+      <c r="E46" s="41" t="n">
         <v>0.8798</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38" t="n">
+      <c r="A47" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B47" s="39" t="n">
+      <c r="B47" s="40" t="n">
         <v>2.326</v>
       </c>
-      <c r="C47" s="40" t="n">
+      <c r="C47" s="41" t="n">
         <v>0.8407</v>
       </c>
-      <c r="D47" s="40" t="n">
+      <c r="D47" s="41" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E47" s="40" t="n">
+      <c r="E47" s="41" t="n">
         <v>0.8641</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="n">
+      <c r="A48" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B48" s="39" t="n">
+      <c r="B48" s="40" t="n">
         <v>2.534</v>
       </c>
-      <c r="C48" s="40" t="n">
+      <c r="C48" s="41" t="n">
         <v>0.8686</v>
       </c>
-      <c r="D48" s="40" t="n">
+      <c r="D48" s="41" t="n">
         <v>0.9515</v>
       </c>
-      <c r="E48" s="40" t="n">
+      <c r="E48" s="41" t="n">
         <v>0.848</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="n">
+      <c r="A49" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B49" s="39" t="n">
+      <c r="B49" s="40" t="n">
         <v>2.704</v>
       </c>
-      <c r="C49" s="40" t="n">
+      <c r="C49" s="41" t="n">
         <v>0.8882</v>
       </c>
-      <c r="D49" s="40" t="n">
+      <c r="D49" s="41" t="n">
         <v>0.9594</v>
       </c>
-      <c r="E49" s="40" t="n">
+      <c r="E49" s="41" t="n">
         <v>0.8332000000000001</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38" t="n">
+      <c r="A50" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B50" s="39" t="n">
+      <c r="B50" s="40" t="n">
         <v>2.847</v>
       </c>
-      <c r="C50" s="40" t="n">
+      <c r="C50" s="41" t="n">
         <v>0.9026999999999999</v>
       </c>
-      <c r="D50" s="40" t="n">
+      <c r="D50" s="41" t="n">
         <v>0.965</v>
       </c>
-      <c r="E50" s="40" t="n">
+      <c r="E50" s="41" t="n">
         <v>0.8198</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="38" t="n">
+      <c r="A51" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B51" s="39" t="n">
+      <c r="B51" s="40" t="n">
         <v>2.97</v>
       </c>
-      <c r="C51" s="40" t="n">
+      <c r="C51" s="41" t="n">
         <v>0.9139</v>
       </c>
-      <c r="D51" s="40" t="n">
+      <c r="D51" s="41" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="E51" s="40" t="n">
+      <c r="E51" s="41" t="n">
         <v>0.8078</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="38" t="n">
+      <c r="A52" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="39" t="n">
+      <c r="B52" s="40" t="n">
         <v>3.078</v>
       </c>
-      <c r="C52" s="40" t="n">
+      <c r="C52" s="41" t="n">
         <v>0.9227</v>
       </c>
-      <c r="D52" s="40" t="n">
+      <c r="D52" s="41" t="n">
         <v>0.9727</v>
       </c>
-      <c r="E52" s="40" t="n">
+      <c r="E52" s="41" t="n">
         <v>0.7971</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="38" t="n">
+      <c r="A53" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B53" s="39" t="n">
+      <c r="B53" s="40" t="n">
         <v>3.173</v>
       </c>
-      <c r="C53" s="40" t="n">
+      <c r="C53" s="41" t="n">
         <v>0.93</v>
       </c>
-      <c r="D53" s="40" t="n">
+      <c r="D53" s="41" t="n">
         <v>0.9754</v>
       </c>
-      <c r="E53" s="40" t="n">
+      <c r="E53" s="41" t="n">
         <v>0.7873</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="38" t="n">
+      <c r="A54" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B54" s="39" t="n">
+      <c r="B54" s="40" t="n">
         <v>3.258</v>
       </c>
-      <c r="C54" s="40" t="n">
+      <c r="C54" s="41" t="n">
         <v>0.9359</v>
       </c>
-      <c r="D54" s="40" t="n">
+      <c r="D54" s="41" t="n">
         <v>0.9776</v>
       </c>
-      <c r="E54" s="42" t="n">
+      <c r="E54" s="43" t="n">
         <v>0.7785</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="38" t="n">
+      <c r="A55" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B55" s="39" t="n">
+      <c r="B55" s="40" t="n">
         <v>3.336</v>
       </c>
-      <c r="C55" s="40" t="n">
+      <c r="C55" s="41" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="D55" s="40" t="n">
+      <c r="D55" s="41" t="n">
         <v>0.9794</v>
       </c>
-      <c r="E55" s="40" t="n">
+      <c r="E55" s="41" t="n">
         <v>0.7704</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="38" t="n">
+      <c r="A56" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B56" s="39" t="n">
+      <c r="B56" s="40" t="n">
         <v>3.407</v>
       </c>
-      <c r="C56" s="40" t="n">
+      <c r="C56" s="41" t="n">
         <v>0.9453</v>
       </c>
-      <c r="D56" s="40" t="n">
+      <c r="D56" s="41" t="n">
         <v>0.981</v>
       </c>
-      <c r="E56" s="40" t="n">
+      <c r="E56" s="41" t="n">
         <v>0.763</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="38" t="n">
+      <c r="A57" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B57" s="39" t="n">
+      <c r="B57" s="40" t="n">
         <v>3.472</v>
       </c>
-      <c r="C57" s="40" t="n">
+      <c r="C57" s="41" t="n">
         <v>0.949</v>
       </c>
-      <c r="D57" s="40" t="n">
+      <c r="D57" s="41" t="n">
         <v>0.9823</v>
       </c>
-      <c r="E57" s="40" t="n">
+      <c r="E57" s="41" t="n">
         <v>0.7562</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="38" t="n">
+      <c r="A58" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B58" s="39" t="n">
+      <c r="B58" s="40" t="n">
         <v>3.532</v>
       </c>
-      <c r="C58" s="40" t="n">
+      <c r="C58" s="41" t="n">
         <v>0.9523</v>
       </c>
-      <c r="D58" s="40" t="n">
+      <c r="D58" s="41" t="n">
         <v>0.9835</v>
       </c>
-      <c r="E58" s="40" t="n">
+      <c r="E58" s="41" t="n">
         <v>0.7499</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="38" t="n">
+      <c r="A59" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="B59" s="39" t="n">
+      <c r="B59" s="40" t="n">
         <v>3.588</v>
       </c>
-      <c r="C59" s="40" t="n">
+      <c r="C59" s="41" t="n">
         <v>0.9550999999999999</v>
       </c>
-      <c r="D59" s="40" t="n">
+      <c r="D59" s="41" t="n">
         <v>0.9845</v>
       </c>
-      <c r="E59" s="40" t="n">
+      <c r="E59" s="41" t="n">
         <v>0.7441</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="38" t="n">
+      <c r="A60" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="B60" s="39" t="n">
+      <c r="B60" s="40" t="n">
         <v>3.64</v>
       </c>
-      <c r="C60" s="40" t="n">
+      <c r="C60" s="41" t="n">
         <v>0.9576</v>
       </c>
-      <c r="D60" s="40" t="n">
+      <c r="D60" s="41" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="E60" s="40" t="n">
+      <c r="E60" s="41" t="n">
         <v>0.7386</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="38" t="n">
+      <c r="A61" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="B61" s="39" t="n">
+      <c r="B61" s="40" t="n">
         <v>3.689</v>
       </c>
-      <c r="C61" s="40" t="n">
+      <c r="C61" s="41" t="n">
         <v>0.9599</v>
       </c>
-      <c r="D61" s="40" t="n">
+      <c r="D61" s="41" t="n">
         <v>0.9862</v>
       </c>
-      <c r="E61" s="40" t="n">
+      <c r="E61" s="41" t="n">
         <v>0.7335</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="38" t="n">
+      <c r="A62" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="B62" s="39" t="n">
+      <c r="B62" s="40" t="n">
         <v>3.735</v>
       </c>
-      <c r="C62" s="40" t="n">
+      <c r="C62" s="41" t="n">
         <v>0.9619</v>
       </c>
-      <c r="D62" s="40" t="n">
+      <c r="D62" s="41" t="n">
         <v>0.9869</v>
       </c>
-      <c r="E62" s="40" t="n">
+      <c r="E62" s="41" t="n">
         <v>0.7287</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="38" t="n">
+      <c r="A63" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="B63" s="39" t="n">
+      <c r="B63" s="40" t="n">
         <v>3.778</v>
       </c>
-      <c r="C63" s="40" t="n">
+      <c r="C63" s="41" t="n">
         <v>0.9638</v>
       </c>
-      <c r="D63" s="40" t="n">
+      <c r="D63" s="41" t="n">
         <v>0.9876</v>
       </c>
-      <c r="E63" s="42" t="n">
+      <c r="E63" s="43" t="n">
         <v>0.7272</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="38" t="n">
+      <c r="A64" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="B64" s="39" t="n">
+      <c r="B64" s="40" t="n">
         <v>3.819</v>
       </c>
-      <c r="C64" s="40" t="n">
+      <c r="C64" s="41" t="n">
         <v>0.9655</v>
       </c>
-      <c r="D64" s="40" t="n">
+      <c r="D64" s="41" t="n">
         <v>0.9882</v>
       </c>
-      <c r="E64" s="40" t="n">
+      <c r="E64" s="41" t="n">
         <v>0.7199</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="38" t="n">
+      <c r="A65" s="39" t="n">
         <v>23</v>
       </c>
-      <c r="B65" s="39" t="n">
+      <c r="B65" s="40" t="n">
         <v>3.858</v>
       </c>
-      <c r="C65" s="40" t="n">
+      <c r="C65" s="41" t="n">
         <v>0.967</v>
       </c>
-      <c r="D65" s="40" t="n">
+      <c r="D65" s="41" t="n">
         <v>0.9887</v>
       </c>
-      <c r="E65" s="40" t="n">
+      <c r="E65" s="41" t="n">
         <v>0.7159</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="38" t="n">
+      <c r="A66" s="39" t="n">
         <v>24</v>
       </c>
-      <c r="B66" s="39" t="n">
+      <c r="B66" s="40" t="n">
         <v>3.895</v>
       </c>
-      <c r="C66" s="40" t="n">
+      <c r="C66" s="41" t="n">
         <v>0.9684</v>
       </c>
-      <c r="D66" s="40" t="n">
+      <c r="D66" s="41" t="n">
         <v>0.9892</v>
       </c>
-      <c r="E66" s="40" t="n">
+      <c r="E66" s="41" t="n">
         <v>0.7121</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="38" t="n">
+      <c r="A67" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="B67" s="39" t="n">
+      <c r="B67" s="40" t="n">
         <v>3.931</v>
       </c>
-      <c r="C67" s="42" t="n">
+      <c r="C67" s="43" t="n">
         <v>0.9695</v>
       </c>
-      <c r="D67" s="40" t="n">
+      <c r="D67" s="41" t="n">
         <v>0.9896</v>
       </c>
-      <c r="E67" s="40" t="n">
+      <c r="E67" s="41" t="n">
         <v>0.7084</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="38" t="n">
+      <c r="A68" s="39" t="n">
         <v>30</v>
       </c>
-      <c r="B68" s="39" t="n">
+      <c r="B68" s="40" t="n">
         <v>4.086</v>
       </c>
-      <c r="C68" s="40" t="n">
+      <c r="C68" s="41" t="n">
         <v>0.9748</v>
       </c>
-      <c r="D68" s="40" t="n">
+      <c r="D68" s="41" t="n">
         <v>0.9915</v>
       </c>
-      <c r="E68" s="40" t="n">
+      <c r="E68" s="41" t="n">
         <v>0.6927</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="38" t="n">
+      <c r="A69" s="39" t="n">
         <v>35</v>
       </c>
-      <c r="B69" s="39" t="n">
+      <c r="B69" s="40" t="n">
         <v>4.213</v>
       </c>
-      <c r="C69" s="40" t="n">
+      <c r="C69" s="41" t="n">
         <v>0.9784</v>
       </c>
-      <c r="D69" s="40" t="n">
+      <c r="D69" s="41" t="n">
         <v>0.9927</v>
       </c>
-      <c r="E69" s="40" t="n">
+      <c r="E69" s="41" t="n">
         <v>0.6798999999999999</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="38" t="n">
+      <c r="A70" s="39" t="n">
         <v>40</v>
       </c>
-      <c r="B70" s="39" t="n">
+      <c r="B70" s="40" t="n">
         <v>4.322</v>
       </c>
-      <c r="C70" s="40" t="n">
+      <c r="C70" s="41" t="n">
         <v>0.9811</v>
       </c>
-      <c r="D70" s="40" t="n">
+      <c r="D70" s="41" t="n">
         <v>0.9936</v>
       </c>
-      <c r="E70" s="40" t="n">
+      <c r="E70" s="41" t="n">
         <v>0.6692</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="38" t="n">
+      <c r="A71" s="39" t="n">
         <v>45</v>
       </c>
-      <c r="B71" s="39" t="n">
+      <c r="B71" s="40" t="n">
         <v>4.415</v>
       </c>
-      <c r="C71" s="40" t="n">
+      <c r="C71" s="41" t="n">
         <v>0.9832</v>
       </c>
-      <c r="D71" s="40" t="n">
+      <c r="D71" s="41" t="n">
         <v>0.9943</v>
       </c>
-      <c r="E71" s="40" t="n">
+      <c r="E71" s="41" t="n">
         <v>0.6601</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="38" t="n">
+      <c r="A72" s="39" t="n">
         <v>50</v>
       </c>
-      <c r="B72" s="39" t="n">
+      <c r="B72" s="40" t="n">
         <v>4.498</v>
       </c>
-      <c r="C72" s="40" t="n">
+      <c r="C72" s="41" t="n">
         <v>0.9849</v>
       </c>
-      <c r="D72" s="40" t="n">
+      <c r="D72" s="41" t="n">
         <v>0.9949</v>
       </c>
-      <c r="E72" s="40" t="n">
+      <c r="E72" s="41" t="n">
         <v>0.6521</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="38" t="n">
+      <c r="A73" s="39" t="n">
         <v>60</v>
       </c>
-      <c r="B73" s="39" t="n">
+      <c r="B73" s="40" t="n">
         <v>4.639</v>
       </c>
-      <c r="C73" s="40" t="n">
+      <c r="C73" s="41" t="n">
         <v>0.9874000000000001</v>
       </c>
-      <c r="D73" s="40" t="n">
+      <c r="D73" s="41" t="n">
         <v>0.9957</v>
       </c>
-      <c r="E73" s="40" t="n">
+      <c r="E73" s="41" t="n">
         <v>0.6389</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="38" t="n">
+      <c r="A74" s="39" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="39" t="n">
+      <c r="B74" s="40" t="n">
         <v>4.755</v>
       </c>
-      <c r="C74" s="40" t="n">
+      <c r="C74" s="41" t="n">
         <v>0.9892</v>
       </c>
-      <c r="D74" s="40" t="n">
+      <c r="D74" s="41" t="n">
         <v>0.9963</v>
       </c>
-      <c r="E74" s="40" t="n">
+      <c r="E74" s="41" t="n">
         <v>0.6283</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="38" t="n">
+      <c r="A75" s="39" t="n">
         <v>80</v>
       </c>
-      <c r="B75" s="39" t="n">
+      <c r="B75" s="40" t="n">
         <v>4.854</v>
       </c>
-      <c r="C75" s="40" t="n">
+      <c r="C75" s="41" t="n">
         <v>0.9906</v>
       </c>
-      <c r="D75" s="40" t="n">
+      <c r="D75" s="41" t="n">
         <v>0.9968</v>
       </c>
-      <c r="E75" s="40" t="n">
+      <c r="E75" s="41" t="n">
         <v>0.6194</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="38" t="n">
+      <c r="A76" s="39" t="n">
         <v>90</v>
       </c>
-      <c r="B76" s="39" t="n">
+      <c r="B76" s="40" t="n">
         <v>4.939</v>
       </c>
-      <c r="C76" s="40" t="n">
+      <c r="C76" s="41" t="n">
         <v>0.9916</v>
       </c>
-      <c r="D76" s="40" t="n">
+      <c r="D76" s="41" t="n">
         <v>0.9972</v>
       </c>
-      <c r="E76" s="40" t="n">
+      <c r="E76" s="41" t="n">
         <v>0.6118</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="38" t="n">
+      <c r="A77" s="39" t="n">
         <v>100</v>
       </c>
-      <c r="B77" s="39" t="n">
+      <c r="B77" s="40" t="n">
         <v>5.015</v>
       </c>
-      <c r="C77" s="40" t="n">
+      <c r="C77" s="41" t="n">
         <v>0.9925</v>
       </c>
-      <c r="D77" s="40" t="n">
+      <c r="D77" s="41" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="E77" s="40" t="n">
+      <c r="E77" s="41" t="n">
         <v>0.6052</v>
       </c>
     </row>
@@ -4397,786 +6022,786 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="38" t="n">
+      <c r="A83" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B83" s="39" t="n">
+      <c r="B83" s="40" t="n">
         <v>2.121</v>
       </c>
-      <c r="C83" s="39" t="n">
+      <c r="C83" s="40" t="n">
         <v>1.88</v>
       </c>
-      <c r="D83" s="39" t="n">
+      <c r="D83" s="40" t="n">
         <v>2.659</v>
       </c>
-      <c r="E83" s="40" t="n">
+      <c r="E83" s="41" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="F83" s="40" t="n">
+      <c r="F83" s="41" t="n">
         <v>1.2533</v>
       </c>
-      <c r="G83" s="38" t="n">
+      <c r="G83" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="39" t="n">
+      <c r="H83" s="40" t="n">
         <v>3.267</v>
       </c>
-      <c r="I83" s="38" t="n">
+      <c r="I83" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="39" t="n">
+      <c r="J83" s="40" t="n">
         <v>3.267</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="38" t="n">
+      <c r="A84" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B84" s="39" t="n">
+      <c r="B84" s="40" t="n">
         <v>2.606</v>
       </c>
-      <c r="C84" s="43" t="inlineStr"/>
-      <c r="D84" s="43" t="inlineStr"/>
-      <c r="E84" s="43" t="inlineStr"/>
-      <c r="F84" s="43" t="inlineStr"/>
-      <c r="G84" s="43" t="inlineStr"/>
-      <c r="H84" s="43" t="inlineStr"/>
-      <c r="I84" s="43" t="inlineStr"/>
-      <c r="J84" s="43" t="inlineStr"/>
+      <c r="C84" s="44" t="inlineStr"/>
+      <c r="D84" s="44" t="inlineStr"/>
+      <c r="E84" s="44" t="inlineStr"/>
+      <c r="F84" s="44" t="inlineStr"/>
+      <c r="G84" s="44" t="inlineStr"/>
+      <c r="H84" s="44" t="inlineStr"/>
+      <c r="I84" s="44" t="inlineStr"/>
+      <c r="J84" s="44" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="38" t="n">
+      <c r="A85" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B85" s="39" t="n">
+      <c r="B85" s="40" t="n">
         <v>1.732</v>
       </c>
-      <c r="C85" s="39" t="n">
+      <c r="C85" s="40" t="n">
         <v>1.023</v>
       </c>
-      <c r="D85" s="39" t="n">
+      <c r="D85" s="40" t="n">
         <v>1.954</v>
       </c>
-      <c r="E85" s="40" t="n">
+      <c r="E85" s="41" t="n">
         <v>0.8862</v>
       </c>
-      <c r="F85" s="40" t="n">
+      <c r="F85" s="41" t="n">
         <v>1.1284</v>
       </c>
-      <c r="G85" s="38" t="n">
+      <c r="G85" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H85" s="39" t="n">
+      <c r="H85" s="40" t="n">
         <v>2.568</v>
       </c>
-      <c r="I85" s="38" t="n">
+      <c r="I85" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="39" t="n">
+      <c r="J85" s="40" t="n">
         <v>2.276</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="38" t="n">
+      <c r="A86" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B86" s="39" t="n">
+      <c r="B86" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="C86" s="39" t="n">
+      <c r="C86" s="40" t="n">
         <v>0.729</v>
       </c>
-      <c r="D86" s="39" t="n">
+      <c r="D86" s="40" t="n">
         <v>1.628</v>
       </c>
-      <c r="E86" s="40" t="n">
+      <c r="E86" s="41" t="n">
         <v>0.9213</v>
       </c>
-      <c r="F86" s="40" t="n">
+      <c r="F86" s="41" t="n">
         <v>1.0854</v>
       </c>
-      <c r="G86" s="38" t="n">
+      <c r="G86" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="39" t="n">
+      <c r="H86" s="40" t="n">
         <v>2.266</v>
       </c>
-      <c r="I86" s="38" t="n">
+      <c r="I86" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="39" t="n">
+      <c r="J86" s="40" t="n">
         <v>2.088</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="38" t="n">
+      <c r="A87" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B87" s="39" t="n">
+      <c r="B87" s="40" t="n">
         <v>1.342</v>
       </c>
-      <c r="C87" s="39" t="n">
+      <c r="C87" s="40" t="n">
         <v>0.577</v>
       </c>
-      <c r="D87" s="39" t="n">
+      <c r="D87" s="40" t="n">
         <v>1.427</v>
       </c>
-      <c r="E87" s="40" t="n">
+      <c r="E87" s="41" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F87" s="40" t="n">
+      <c r="F87" s="41" t="n">
         <v>1.0638</v>
       </c>
-      <c r="G87" s="38" t="n">
+      <c r="G87" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="39" t="n">
+      <c r="H87" s="40" t="n">
         <v>2.089</v>
       </c>
-      <c r="I87" s="38" t="n">
+      <c r="I87" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="39" t="n">
+      <c r="J87" s="40" t="n">
         <v>1.964</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="38" t="n">
+      <c r="A88" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B88" s="39" t="n">
+      <c r="B88" s="40" t="n">
         <v>1.225</v>
       </c>
-      <c r="C88" s="39" t="n">
+      <c r="C88" s="40" t="n">
         <v>0.483</v>
       </c>
-      <c r="D88" s="39" t="n">
+      <c r="D88" s="40" t="n">
         <v>1.287</v>
       </c>
-      <c r="E88" s="40" t="n">
+      <c r="E88" s="41" t="n">
         <v>0.9515</v>
       </c>
-      <c r="F88" s="40" t="n">
+      <c r="F88" s="41" t="n">
         <v>1.051</v>
       </c>
-      <c r="G88" s="39" t="n">
+      <c r="G88" s="40" t="n">
         <v>0.03</v>
       </c>
-      <c r="H88" s="39" t="n">
+      <c r="H88" s="40" t="n">
         <v>1.97</v>
       </c>
-      <c r="I88" s="39" t="n">
+      <c r="I88" s="40" t="n">
         <v>0.029</v>
       </c>
-      <c r="J88" s="39" t="n">
+      <c r="J88" s="40" t="n">
         <v>1.874</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="38" t="n">
+      <c r="A89" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B89" s="39" t="n">
+      <c r="B89" s="40" t="n">
         <v>1.134</v>
       </c>
-      <c r="C89" s="39" t="n">
+      <c r="C89" s="40" t="n">
         <v>0.419</v>
       </c>
-      <c r="D89" s="39" t="n">
+      <c r="D89" s="40" t="n">
         <v>1.182</v>
       </c>
-      <c r="E89" s="40" t="n">
+      <c r="E89" s="41" t="n">
         <v>0.9594</v>
       </c>
-      <c r="F89" s="40" t="n">
+      <c r="F89" s="41" t="n">
         <v>1.0423</v>
       </c>
-      <c r="G89" s="39" t="n">
+      <c r="G89" s="40" t="n">
         <v>0.118</v>
       </c>
-      <c r="H89" s="39" t="n">
+      <c r="H89" s="40" t="n">
         <v>1.882</v>
       </c>
-      <c r="I89" s="39" t="n">
+      <c r="I89" s="40" t="n">
         <v>0.113</v>
       </c>
-      <c r="J89" s="39" t="n">
+      <c r="J89" s="40" t="n">
         <v>1.806</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="38" t="n">
+      <c r="A90" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="39" t="n">
+      <c r="B90" s="40" t="n">
         <v>1.061</v>
       </c>
-      <c r="C90" s="39" t="n">
+      <c r="C90" s="40" t="n">
         <v>0.373</v>
       </c>
-      <c r="D90" s="39" t="n">
+      <c r="D90" s="40" t="n">
         <v>1.099</v>
       </c>
-      <c r="E90" s="40" t="n">
+      <c r="E90" s="41" t="n">
         <v>0.965</v>
       </c>
-      <c r="F90" s="40" t="n">
+      <c r="F90" s="41" t="n">
         <v>1.0363</v>
       </c>
-      <c r="G90" s="39" t="n">
+      <c r="G90" s="40" t="n">
         <v>0.185</v>
       </c>
-      <c r="H90" s="39" t="n">
+      <c r="H90" s="40" t="n">
         <v>1.815</v>
       </c>
-      <c r="I90" s="39" t="n">
+      <c r="I90" s="40" t="n">
         <v>0.179</v>
       </c>
-      <c r="J90" s="39" t="n">
+      <c r="J90" s="40" t="n">
         <v>1.751</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="38" t="n">
+      <c r="A91" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B91" s="39" t="n">
+      <c r="B91" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="39" t="n">
+      <c r="C91" s="40" t="n">
         <v>0.337</v>
       </c>
-      <c r="D91" s="39" t="n">
+      <c r="D91" s="40" t="n">
         <v>1.032</v>
       </c>
-      <c r="E91" s="40" t="n">
+      <c r="E91" s="41" t="n">
         <v>0.9693000000000001</v>
       </c>
-      <c r="F91" s="40" t="n">
+      <c r="F91" s="41" t="n">
         <v>1.0317</v>
       </c>
-      <c r="G91" s="39" t="n">
+      <c r="G91" s="40" t="n">
         <v>0.239</v>
       </c>
-      <c r="H91" s="39" t="n">
+      <c r="H91" s="40" t="n">
         <v>1.761</v>
       </c>
-      <c r="I91" s="39" t="n">
+      <c r="I91" s="40" t="n">
         <v>0.232</v>
       </c>
-      <c r="J91" s="39" t="n">
+      <c r="J91" s="40" t="n">
         <v>1.707</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="38" t="n">
+      <c r="A92" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B92" s="39" t="n">
+      <c r="B92" s="40" t="n">
         <v>0.949</v>
       </c>
-      <c r="C92" s="39" t="n">
+      <c r="C92" s="40" t="n">
         <v>0.308</v>
       </c>
-      <c r="D92" s="39" t="n">
+      <c r="D92" s="40" t="n">
         <v>0.975</v>
       </c>
-      <c r="E92" s="40" t="n">
+      <c r="E92" s="41" t="n">
         <v>0.9727</v>
       </c>
-      <c r="F92" s="40" t="n">
+      <c r="F92" s="41" t="n">
         <v>1.0281</v>
       </c>
-      <c r="G92" s="39" t="n">
+      <c r="G92" s="40" t="n">
         <v>0.284</v>
       </c>
-      <c r="H92" s="39" t="n">
+      <c r="H92" s="40" t="n">
         <v>1.716</v>
       </c>
-      <c r="I92" s="39" t="n">
+      <c r="I92" s="40" t="n">
         <v>0.276</v>
       </c>
-      <c r="J92" s="39" t="n">
+      <c r="J92" s="40" t="n">
         <v>1.669</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="38" t="n">
+      <c r="A93" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B93" s="39" t="n">
+      <c r="B93" s="40" t="n">
         <v>0.905</v>
       </c>
-      <c r="C93" s="39" t="n">
+      <c r="C93" s="40" t="n">
         <v>0.285</v>
       </c>
-      <c r="D93" s="39" t="n">
+      <c r="D93" s="40" t="n">
         <v>0.927</v>
       </c>
-      <c r="E93" s="40" t="n">
+      <c r="E93" s="41" t="n">
         <v>0.9754</v>
       </c>
-      <c r="F93" s="40" t="n">
+      <c r="F93" s="41" t="n">
         <v>1.0252</v>
       </c>
-      <c r="G93" s="39" t="n">
+      <c r="G93" s="40" t="n">
         <v>0.321</v>
       </c>
-      <c r="H93" s="39" t="n">
+      <c r="H93" s="40" t="n">
         <v>1.679</v>
       </c>
-      <c r="I93" s="39" t="n">
+      <c r="I93" s="40" t="n">
         <v>0.313</v>
       </c>
-      <c r="J93" s="39" t="n">
+      <c r="J93" s="40" t="n">
         <v>1.637</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="38" t="n">
+      <c r="A94" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B94" s="39" t="n">
+      <c r="B94" s="40" t="n">
         <v>0.866</v>
       </c>
-      <c r="C94" s="39" t="n">
+      <c r="C94" s="40" t="n">
         <v>0.266</v>
       </c>
-      <c r="D94" s="39" t="n">
+      <c r="D94" s="40" t="n">
         <v>0.886</v>
       </c>
-      <c r="E94" s="40" t="n">
+      <c r="E94" s="41" t="n">
         <v>0.9776</v>
       </c>
-      <c r="F94" s="40" t="n">
+      <c r="F94" s="41" t="n">
         <v>1.0229</v>
       </c>
-      <c r="G94" s="39" t="n">
+      <c r="G94" s="40" t="n">
         <v>0.354</v>
       </c>
-      <c r="H94" s="39" t="n">
+      <c r="H94" s="40" t="n">
         <v>1.646</v>
       </c>
-      <c r="I94" s="39" t="n">
+      <c r="I94" s="40" t="n">
         <v>0.346</v>
       </c>
-      <c r="J94" s="39" t="n">
+      <c r="J94" s="40" t="n">
         <v>1.61</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="38" t="n">
+      <c r="A95" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B95" s="39" t="n">
+      <c r="B95" s="40" t="n">
         <v>0.832</v>
       </c>
-      <c r="C95" s="39" t="n">
+      <c r="C95" s="40" t="n">
         <v>0.249</v>
       </c>
-      <c r="D95" s="39" t="n">
+      <c r="D95" s="40" t="n">
         <v>0.85</v>
       </c>
-      <c r="E95" s="40" t="n">
+      <c r="E95" s="41" t="n">
         <v>0.9794</v>
       </c>
-      <c r="F95" s="40" t="n">
+      <c r="F95" s="41" t="n">
         <v>1.021</v>
       </c>
-      <c r="G95" s="39" t="n">
+      <c r="G95" s="40" t="n">
         <v>0.382</v>
       </c>
-      <c r="H95" s="39" t="n">
+      <c r="H95" s="40" t="n">
         <v>1.618</v>
       </c>
-      <c r="I95" s="39" t="n">
+      <c r="I95" s="40" t="n">
         <v>0.374</v>
       </c>
-      <c r="J95" s="39" t="n">
+      <c r="J95" s="40" t="n">
         <v>1.585</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="38" t="n">
+      <c r="A96" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B96" s="39" t="n">
+      <c r="B96" s="40" t="n">
         <v>0.802</v>
       </c>
-      <c r="C96" s="39" t="n">
+      <c r="C96" s="40" t="n">
         <v>0.235</v>
       </c>
-      <c r="D96" s="39" t="n">
+      <c r="D96" s="40" t="n">
         <v>0.8169999999999999</v>
       </c>
-      <c r="E96" s="40" t="n">
+      <c r="E96" s="41" t="n">
         <v>0.981</v>
       </c>
-      <c r="F96" s="40" t="n">
+      <c r="F96" s="41" t="n">
         <v>1.0194</v>
       </c>
-      <c r="G96" s="39" t="n">
+      <c r="G96" s="40" t="n">
         <v>0.406</v>
       </c>
-      <c r="H96" s="39" t="n">
+      <c r="H96" s="40" t="n">
         <v>1.594</v>
       </c>
-      <c r="I96" s="39" t="n">
+      <c r="I96" s="40" t="n">
         <v>0.399</v>
       </c>
-      <c r="J96" s="39" t="n">
+      <c r="J96" s="40" t="n">
         <v>1.563</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="38" t="n">
+      <c r="A97" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B97" s="39" t="n">
+      <c r="B97" s="40" t="n">
         <v>0.775</v>
       </c>
-      <c r="C97" s="39" t="n">
+      <c r="C97" s="40" t="n">
         <v>0.223</v>
       </c>
-      <c r="D97" s="39" t="n">
+      <c r="D97" s="40" t="n">
         <v>0.789</v>
       </c>
-      <c r="E97" s="40" t="n">
+      <c r="E97" s="41" t="n">
         <v>0.9823</v>
       </c>
-      <c r="F97" s="40" t="n">
+      <c r="F97" s="41" t="n">
         <v>1.018</v>
       </c>
-      <c r="G97" s="39" t="n">
+      <c r="G97" s="40" t="n">
         <v>0.428</v>
       </c>
-      <c r="H97" s="39" t="n">
+      <c r="H97" s="40" t="n">
         <v>1.572</v>
       </c>
-      <c r="I97" s="39" t="n">
+      <c r="I97" s="40" t="n">
         <v>0.421</v>
       </c>
-      <c r="J97" s="39" t="n">
+      <c r="J97" s="40" t="n">
         <v>1.544</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="38" t="n">
+      <c r="A98" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B98" s="39" t="n">
+      <c r="B98" s="40" t="n">
         <v>0.75</v>
       </c>
-      <c r="C98" s="39" t="n">
+      <c r="C98" s="40" t="n">
         <v>0.212</v>
       </c>
-      <c r="D98" s="39" t="n">
+      <c r="D98" s="40" t="n">
         <v>0.763</v>
       </c>
-      <c r="E98" s="40" t="n">
+      <c r="E98" s="41" t="n">
         <v>0.9835</v>
       </c>
-      <c r="F98" s="40" t="n">
+      <c r="F98" s="41" t="n">
         <v>1.0168</v>
       </c>
-      <c r="G98" s="39" t="n">
+      <c r="G98" s="40" t="n">
         <v>0.448</v>
       </c>
-      <c r="H98" s="39" t="n">
+      <c r="H98" s="40" t="n">
         <v>1.552</v>
       </c>
-      <c r="I98" s="39" t="n">
+      <c r="I98" s="40" t="n">
         <v>0.44</v>
       </c>
-      <c r="J98" s="39" t="n">
+      <c r="J98" s="40" t="n">
         <v>1.526</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="38" t="n">
+      <c r="A99" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="B99" s="39" t="n">
+      <c r="B99" s="40" t="n">
         <v>0.728</v>
       </c>
-      <c r="C99" s="39" t="n">
+      <c r="C99" s="40" t="n">
         <v>0.203</v>
       </c>
-      <c r="D99" s="39" t="n">
+      <c r="D99" s="40" t="n">
         <v>0.739</v>
       </c>
-      <c r="E99" s="40" t="n">
+      <c r="E99" s="41" t="n">
         <v>0.9845</v>
       </c>
-      <c r="F99" s="40" t="n">
+      <c r="F99" s="41" t="n">
         <v>1.0157</v>
       </c>
-      <c r="G99" s="39" t="n">
+      <c r="G99" s="40" t="n">
         <v>0.466</v>
       </c>
-      <c r="H99" s="39" t="n">
+      <c r="H99" s="40" t="n">
         <v>1.534</v>
       </c>
-      <c r="I99" s="39" t="n">
+      <c r="I99" s="40" t="n">
         <v>0.458</v>
       </c>
-      <c r="J99" s="39" t="n">
+      <c r="J99" s="40" t="n">
         <v>1.511</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="38" t="n">
+      <c r="A100" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="B100" s="39" t="n">
+      <c r="B100" s="40" t="n">
         <v>0.707</v>
       </c>
-      <c r="C100" s="39" t="n">
+      <c r="C100" s="40" t="n">
         <v>0.194</v>
       </c>
-      <c r="D100" s="39" t="n">
+      <c r="D100" s="40" t="n">
         <v>0.718</v>
       </c>
-      <c r="E100" s="40" t="n">
+      <c r="E100" s="41" t="n">
         <v>0.9854000000000001</v>
       </c>
-      <c r="F100" s="40" t="n">
+      <c r="F100" s="41" t="n">
         <v>1.0148</v>
       </c>
-      <c r="G100" s="39" t="n">
+      <c r="G100" s="40" t="n">
         <v>0.482</v>
       </c>
-      <c r="H100" s="39" t="n">
+      <c r="H100" s="40" t="n">
         <v>1.518</v>
       </c>
-      <c r="I100" s="39" t="n">
+      <c r="I100" s="40" t="n">
         <v>0.475</v>
       </c>
-      <c r="J100" s="39" t="n">
+      <c r="J100" s="40" t="n">
         <v>1.496</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="38" t="n">
+      <c r="A101" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="B101" s="39" t="n">
+      <c r="B101" s="40" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="C101" s="39" t="n">
+      <c r="C101" s="40" t="n">
         <v>0.187</v>
       </c>
-      <c r="D101" s="39" t="n">
+      <c r="D101" s="40" t="n">
         <v>0.698</v>
       </c>
-      <c r="E101" s="40" t="n">
+      <c r="E101" s="41" t="n">
         <v>0.9862</v>
       </c>
-      <c r="F101" s="40" t="n">
+      <c r="F101" s="41" t="n">
         <v>1.014</v>
       </c>
-      <c r="G101" s="39" t="n">
+      <c r="G101" s="40" t="n">
         <v>0.497</v>
       </c>
-      <c r="H101" s="39" t="n">
+      <c r="H101" s="40" t="n">
         <v>1.503</v>
       </c>
-      <c r="I101" s="39" t="n">
+      <c r="I101" s="40" t="n">
         <v>0.49</v>
       </c>
-      <c r="J101" s="39" t="n">
+      <c r="J101" s="40" t="n">
         <v>1.483</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="38" t="n">
+      <c r="A102" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="B102" s="39" t="n">
+      <c r="B102" s="40" t="n">
         <v>0.671</v>
       </c>
-      <c r="C102" s="39" t="n">
+      <c r="C102" s="40" t="n">
         <v>0.18</v>
       </c>
-      <c r="D102" s="39" t="n">
+      <c r="D102" s="40" t="n">
         <v>0.68</v>
       </c>
-      <c r="E102" s="40" t="n">
+      <c r="E102" s="41" t="n">
         <v>0.9869</v>
       </c>
-      <c r="F102" s="40" t="n">
+      <c r="F102" s="41" t="n">
         <v>1.0133</v>
       </c>
-      <c r="G102" s="39" t="n">
+      <c r="G102" s="40" t="n">
         <v>0.51</v>
       </c>
-      <c r="H102" s="39" t="n">
+      <c r="H102" s="40" t="n">
         <v>1.49</v>
       </c>
-      <c r="I102" s="39" t="n">
+      <c r="I102" s="40" t="n">
         <v>0.504</v>
       </c>
-      <c r="J102" s="39" t="n">
+      <c r="J102" s="40" t="n">
         <v>1.47</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="38" t="n">
+      <c r="A103" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="B103" s="39" t="n">
+      <c r="B103" s="40" t="n">
         <v>0.655</v>
       </c>
-      <c r="C103" s="39" t="n">
+      <c r="C103" s="40" t="n">
         <v>0.173</v>
       </c>
-      <c r="D103" s="39" t="n">
+      <c r="D103" s="40" t="n">
         <v>0.663</v>
       </c>
-      <c r="E103" s="40" t="n">
+      <c r="E103" s="41" t="n">
         <v>0.9876</v>
       </c>
-      <c r="F103" s="40" t="n">
+      <c r="F103" s="41" t="n">
         <v>1.0126</v>
       </c>
-      <c r="G103" s="39" t="n">
+      <c r="G103" s="40" t="n">
         <v>0.523</v>
       </c>
-      <c r="H103" s="39" t="n">
+      <c r="H103" s="40" t="n">
         <v>1.477</v>
       </c>
-      <c r="I103" s="39" t="n">
+      <c r="I103" s="40" t="n">
         <v>0.516</v>
       </c>
-      <c r="J103" s="39" t="n">
+      <c r="J103" s="40" t="n">
         <v>1.459</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="38" t="n">
+      <c r="A104" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="B104" s="39" t="n">
+      <c r="B104" s="40" t="n">
         <v>0.64</v>
       </c>
-      <c r="C104" s="39" t="n">
+      <c r="C104" s="40" t="n">
         <v>0.167</v>
       </c>
-      <c r="D104" s="39" t="n">
+      <c r="D104" s="40" t="n">
         <v>0.647</v>
       </c>
-      <c r="E104" s="40" t="n">
+      <c r="E104" s="41" t="n">
         <v>0.9882</v>
       </c>
-      <c r="F104" s="40" t="n">
+      <c r="F104" s="41" t="n">
         <v>1.0119</v>
       </c>
-      <c r="G104" s="39" t="n">
+      <c r="G104" s="40" t="n">
         <v>0.534</v>
       </c>
-      <c r="H104" s="39" t="n">
+      <c r="H104" s="40" t="n">
         <v>1.466</v>
       </c>
-      <c r="I104" s="39" t="n">
+      <c r="I104" s="40" t="n">
         <v>0.528</v>
       </c>
-      <c r="J104" s="39" t="n">
+      <c r="J104" s="40" t="n">
         <v>1.448</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="38" t="n">
+      <c r="A105" s="39" t="n">
         <v>23</v>
       </c>
-      <c r="B105" s="39" t="n">
+      <c r="B105" s="40" t="n">
         <v>0.626</v>
       </c>
-      <c r="C105" s="39" t="n">
+      <c r="C105" s="40" t="n">
         <v>0.162</v>
       </c>
-      <c r="D105" s="39" t="n">
+      <c r="D105" s="40" t="n">
         <v>0.633</v>
       </c>
-      <c r="E105" s="40" t="n">
+      <c r="E105" s="41" t="n">
         <v>0.9887</v>
       </c>
-      <c r="F105" s="40" t="n">
+      <c r="F105" s="41" t="n">
         <v>1.0114</v>
       </c>
-      <c r="G105" s="39" t="n">
+      <c r="G105" s="40" t="n">
         <v>0.545</v>
       </c>
-      <c r="H105" s="39" t="n">
+      <c r="H105" s="40" t="n">
         <v>1.455</v>
       </c>
-      <c r="I105" s="39" t="n">
+      <c r="I105" s="40" t="n">
         <v>0.539</v>
       </c>
-      <c r="J105" s="39" t="n">
+      <c r="J105" s="40" t="n">
         <v>1.438</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="38" t="n">
+      <c r="A106" s="39" t="n">
         <v>24</v>
       </c>
-      <c r="B106" s="39" t="n">
+      <c r="B106" s="40" t="n">
         <v>0.612</v>
       </c>
-      <c r="C106" s="39" t="n">
+      <c r="C106" s="40" t="n">
         <v>0.157</v>
       </c>
-      <c r="D106" s="39" t="n">
+      <c r="D106" s="40" t="n">
         <v>0.619</v>
       </c>
-      <c r="E106" s="40" t="n">
+      <c r="E106" s="41" t="n">
         <v>0.9892</v>
       </c>
-      <c r="F106" s="40" t="n">
+      <c r="F106" s="41" t="n">
         <v>1.0109</v>
       </c>
-      <c r="G106" s="39" t="n">
+      <c r="G106" s="40" t="n">
         <v>0.555</v>
       </c>
-      <c r="H106" s="39" t="n">
+      <c r="H106" s="40" t="n">
         <v>1.445</v>
       </c>
-      <c r="I106" s="39" t="n">
+      <c r="I106" s="40" t="n">
         <v>0.549</v>
       </c>
-      <c r="J106" s="39" t="n">
+      <c r="J106" s="40" t="n">
         <v>1.429</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="38" t="n">
+      <c r="A107" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="B107" s="39" t="n">
+      <c r="B107" s="40" t="n">
         <v>0.6</v>
       </c>
-      <c r="C107" s="39" t="n">
+      <c r="C107" s="40" t="n">
         <v>0.153</v>
       </c>
-      <c r="D107" s="39" t="n">
+      <c r="D107" s="40" t="n">
         <v>0.606</v>
       </c>
-      <c r="E107" s="40" t="n">
+      <c r="E107" s="41" t="n">
         <v>0.9896</v>
       </c>
-      <c r="F107" s="40" t="n">
+      <c r="F107" s="41" t="n">
         <v>1.0105</v>
       </c>
-      <c r="G107" s="39" t="n">
+      <c r="G107" s="40" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="H107" s="39" t="n">
+      <c r="H107" s="40" t="n">
         <v>1.435</v>
       </c>
-      <c r="I107" s="39" t="n">
+      <c r="I107" s="40" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="J107" s="39" t="n">
+      <c r="J107" s="40" t="n">
         <v>1.42</v>
       </c>
     </row>
@@ -5249,698 +6874,698 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="38" t="n">
+      <c r="A113" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B113" s="39" t="n">
+      <c r="B113" s="40" t="n">
         <v>1.128</v>
       </c>
-      <c r="C113" s="40" t="n">
+      <c r="C113" s="41" t="n">
         <v>0.8865</v>
       </c>
-      <c r="D113" s="39" t="n">
+      <c r="D113" s="40" t="n">
         <v>0.853</v>
       </c>
-      <c r="E113" s="38" t="n">
+      <c r="E113" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="39" t="n">
+      <c r="F113" s="40" t="n">
         <v>3.686</v>
       </c>
-      <c r="G113" s="38" t="n">
+      <c r="G113" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="39" t="n">
+      <c r="H113" s="40" t="n">
         <v>3.267</v>
       </c>
-      <c r="I113" s="41" t="n">
+      <c r="I113" s="42" t="n">
         <v>2.66</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="38" t="n">
+      <c r="A114" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B114" s="39" t="n">
+      <c r="B114" s="40" t="n">
         <v>1.693</v>
       </c>
-      <c r="C114" s="40" t="n">
+      <c r="C114" s="41" t="n">
         <v>0.5907</v>
       </c>
-      <c r="D114" s="39" t="n">
+      <c r="D114" s="40" t="n">
         <v>0.888</v>
       </c>
-      <c r="E114" s="38" t="n">
+      <c r="E114" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="39" t="n">
+      <c r="F114" s="40" t="n">
         <v>4.358</v>
       </c>
-      <c r="G114" s="38" t="n">
+      <c r="G114" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="41" t="n">
+      <c r="H114" s="42" t="n">
         <v>2.574</v>
       </c>
-      <c r="I114" s="39" t="n">
+      <c r="I114" s="40" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="38" t="n">
+      <c r="A115" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B115" s="39" t="n">
+      <c r="B115" s="40" t="n">
         <v>2.059</v>
       </c>
-      <c r="C115" s="40" t="n">
+      <c r="C115" s="41" t="n">
         <v>0.4857</v>
       </c>
-      <c r="D115" s="39" t="n">
+      <c r="D115" s="40" t="n">
         <v>0.88</v>
       </c>
-      <c r="E115" s="38" t="n">
+      <c r="E115" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="39" t="n">
+      <c r="F115" s="40" t="n">
         <v>4.698</v>
       </c>
-      <c r="G115" s="38" t="n">
+      <c r="G115" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="39" t="n">
+      <c r="H115" s="40" t="n">
         <v>2.282</v>
       </c>
-      <c r="I115" s="39" t="n">
+      <c r="I115" s="40" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="38" t="n">
+      <c r="A116" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B116" s="39" t="n">
+      <c r="B116" s="40" t="n">
         <v>2.326</v>
       </c>
-      <c r="C116" s="40" t="n">
+      <c r="C116" s="41" t="n">
         <v>0.4299</v>
       </c>
-      <c r="D116" s="39" t="n">
+      <c r="D116" s="40" t="n">
         <v>0.864</v>
       </c>
-      <c r="E116" s="38" t="n">
+      <c r="E116" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="39" t="n">
+      <c r="F116" s="40" t="n">
         <v>4.918</v>
       </c>
-      <c r="G116" s="38" t="n">
+      <c r="G116" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="41" t="n">
+      <c r="H116" s="42" t="n">
         <v>2.114</v>
       </c>
-      <c r="I116" s="39" t="n">
+      <c r="I116" s="40" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="38" t="n">
+      <c r="A117" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B117" s="39" t="n">
+      <c r="B117" s="40" t="n">
         <v>2.534</v>
       </c>
-      <c r="C117" s="40" t="n">
+      <c r="C117" s="41" t="n">
         <v>0.3946</v>
       </c>
-      <c r="D117" s="39" t="n">
+      <c r="D117" s="40" t="n">
         <v>0.848</v>
       </c>
-      <c r="E117" s="38" t="n">
+      <c r="E117" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="39" t="n">
+      <c r="F117" s="40" t="n">
         <v>5.078</v>
       </c>
-      <c r="G117" s="38" t="n">
+      <c r="G117" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="39" t="n">
+      <c r="H117" s="40" t="n">
         <v>2.004</v>
       </c>
-      <c r="I117" s="39" t="n">
+      <c r="I117" s="40" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="38" t="n">
+      <c r="A118" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B118" s="39" t="n">
+      <c r="B118" s="40" t="n">
         <v>2.704</v>
       </c>
-      <c r="C118" s="40" t="n">
+      <c r="C118" s="41" t="n">
         <v>0.3698</v>
       </c>
-      <c r="D118" s="39" t="n">
+      <c r="D118" s="40" t="n">
         <v>0.833</v>
       </c>
-      <c r="E118" s="41" t="n">
+      <c r="E118" s="42" t="n">
         <v>0.204</v>
       </c>
-      <c r="F118" s="41" t="n">
+      <c r="F118" s="42" t="n">
         <v>5.204</v>
       </c>
-      <c r="G118" s="39" t="n">
+      <c r="G118" s="40" t="n">
         <v>0.076</v>
       </c>
-      <c r="H118" s="39" t="n">
+      <c r="H118" s="40" t="n">
         <v>1.924</v>
       </c>
-      <c r="I118" s="39" t="n">
+      <c r="I118" s="40" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="38" t="n">
+      <c r="A119" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B119" s="39" t="n">
+      <c r="B119" s="40" t="n">
         <v>2.847</v>
       </c>
-      <c r="C119" s="40" t="n">
+      <c r="C119" s="41" t="n">
         <v>0.3512</v>
       </c>
-      <c r="D119" s="39" t="n">
+      <c r="D119" s="40" t="n">
         <v>0.82</v>
       </c>
-      <c r="E119" s="41" t="n">
+      <c r="E119" s="42" t="n">
         <v>0.388</v>
       </c>
-      <c r="F119" s="41" t="n">
+      <c r="F119" s="42" t="n">
         <v>5.306</v>
       </c>
-      <c r="G119" s="39" t="n">
+      <c r="G119" s="40" t="n">
         <v>0.136</v>
       </c>
-      <c r="H119" s="39" t="n">
+      <c r="H119" s="40" t="n">
         <v>1.864</v>
       </c>
-      <c r="I119" s="39" t="n">
+      <c r="I119" s="40" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="38" t="n">
+      <c r="A120" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B120" s="39" t="n">
+      <c r="B120" s="40" t="n">
         <v>2.97</v>
       </c>
-      <c r="C120" s="40" t="n">
+      <c r="C120" s="41" t="n">
         <v>0.3367</v>
       </c>
-      <c r="D120" s="39" t="n">
+      <c r="D120" s="40" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="E120" s="41" t="n">
+      <c r="E120" s="42" t="n">
         <v>0.547</v>
       </c>
-      <c r="F120" s="41" t="n">
+      <c r="F120" s="42" t="n">
         <v>5.393</v>
       </c>
-      <c r="G120" s="39" t="n">
+      <c r="G120" s="40" t="n">
         <v>0.184</v>
       </c>
-      <c r="H120" s="39" t="n">
+      <c r="H120" s="40" t="n">
         <v>1.816</v>
       </c>
-      <c r="I120" s="39" t="n">
+      <c r="I120" s="40" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="38" t="n">
+      <c r="A121" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B121" s="39" t="n">
+      <c r="B121" s="40" t="n">
         <v>3.078</v>
       </c>
-      <c r="C121" s="40" t="n">
+      <c r="C121" s="41" t="n">
         <v>0.3249</v>
       </c>
-      <c r="D121" s="39" t="n">
+      <c r="D121" s="40" t="n">
         <v>0.797</v>
       </c>
-      <c r="E121" s="39" t="n">
+      <c r="E121" s="40" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="F121" s="39" t="n">
+      <c r="F121" s="40" t="n">
         <v>5.469</v>
       </c>
-      <c r="G121" s="39" t="n">
+      <c r="G121" s="40" t="n">
         <v>0.223</v>
       </c>
-      <c r="H121" s="39" t="n">
+      <c r="H121" s="40" t="n">
         <v>1.777</v>
       </c>
-      <c r="I121" s="39" t="n">
+      <c r="I121" s="40" t="n">
         <v>0.975</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="38" t="n">
+      <c r="A122" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B122" s="39" t="n">
+      <c r="B122" s="40" t="n">
         <v>3.173</v>
       </c>
-      <c r="C122" s="40" t="n">
+      <c r="C122" s="41" t="n">
         <v>0.3152</v>
       </c>
-      <c r="D122" s="39" t="n">
+      <c r="D122" s="40" t="n">
         <v>0.787</v>
       </c>
-      <c r="E122" s="41" t="n">
+      <c r="E122" s="42" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F122" s="41" t="n">
+      <c r="F122" s="42" t="n">
         <v>5.535</v>
       </c>
-      <c r="G122" s="39" t="n">
+      <c r="G122" s="40" t="n">
         <v>0.256</v>
       </c>
-      <c r="H122" s="39" t="n">
+      <c r="H122" s="40" t="n">
         <v>1.744</v>
       </c>
-      <c r="I122" s="39" t="n">
+      <c r="I122" s="40" t="n">
         <v>0.945</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="38" t="n">
+      <c r="A123" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B123" s="39" t="n">
+      <c r="B123" s="40" t="n">
         <v>3.258</v>
       </c>
-      <c r="C123" s="40" t="n">
+      <c r="C123" s="41" t="n">
         <v>0.3069</v>
       </c>
-      <c r="D123" s="41" t="n">
+      <c r="D123" s="42" t="n">
         <v>0.778</v>
       </c>
-      <c r="E123" s="41" t="n">
+      <c r="E123" s="42" t="n">
         <v>0.922</v>
       </c>
-      <c r="F123" s="41" t="n">
+      <c r="F123" s="42" t="n">
         <v>5.594</v>
       </c>
-      <c r="G123" s="41" t="n">
+      <c r="G123" s="42" t="n">
         <v>0.283</v>
       </c>
-      <c r="H123" s="41" t="n">
+      <c r="H123" s="42" t="n">
         <v>1.717</v>
       </c>
-      <c r="I123" s="39" t="n">
+      <c r="I123" s="40" t="n">
         <v>0.921</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="38" t="n">
+      <c r="A124" s="39" t="n">
         <v>13</v>
       </c>
-      <c r="B124" s="39" t="n">
+      <c r="B124" s="40" t="n">
         <v>3.336</v>
       </c>
-      <c r="C124" s="40" t="n">
+      <c r="C124" s="41" t="n">
         <v>0.2998</v>
       </c>
-      <c r="D124" s="39" t="n">
+      <c r="D124" s="40" t="n">
         <v>0.77</v>
       </c>
-      <c r="E124" s="41" t="n">
+      <c r="E124" s="42" t="n">
         <v>1.025</v>
       </c>
-      <c r="F124" s="41" t="n">
+      <c r="F124" s="42" t="n">
         <v>5.647</v>
       </c>
-      <c r="G124" s="41" t="n">
+      <c r="G124" s="42" t="n">
         <v>0.307</v>
       </c>
-      <c r="H124" s="41" t="n">
+      <c r="H124" s="42" t="n">
         <v>1.693</v>
       </c>
-      <c r="I124" s="39" t="n">
+      <c r="I124" s="40" t="n">
         <v>0.899</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="38" t="n">
+      <c r="A125" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="B125" s="39" t="n">
+      <c r="B125" s="40" t="n">
         <v>3.407</v>
       </c>
-      <c r="C125" s="40" t="n">
+      <c r="C125" s="41" t="n">
         <v>0.2935</v>
       </c>
-      <c r="D125" s="39" t="n">
+      <c r="D125" s="40" t="n">
         <v>0.763</v>
       </c>
-      <c r="E125" s="41" t="n">
+      <c r="E125" s="42" t="n">
         <v>1.118</v>
       </c>
-      <c r="F125" s="41" t="n">
+      <c r="F125" s="42" t="n">
         <v>5.696</v>
       </c>
-      <c r="G125" s="41" t="n">
+      <c r="G125" s="42" t="n">
         <v>0.328</v>
       </c>
-      <c r="H125" s="41" t="n">
+      <c r="H125" s="42" t="n">
         <v>1.672</v>
       </c>
-      <c r="I125" s="39" t="n">
+      <c r="I125" s="40" t="n">
         <v>0.881</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="38" t="n">
+      <c r="A126" s="39" t="n">
         <v>15</v>
       </c>
-      <c r="B126" s="39" t="n">
+      <c r="B126" s="40" t="n">
         <v>3.472</v>
       </c>
-      <c r="C126" s="40" t="n">
+      <c r="C126" s="41" t="n">
         <v>0.288</v>
       </c>
-      <c r="D126" s="39" t="n">
+      <c r="D126" s="40" t="n">
         <v>0.756</v>
       </c>
-      <c r="E126" s="41" t="n">
+      <c r="E126" s="42" t="n">
         <v>1.203</v>
       </c>
-      <c r="F126" s="41" t="n">
+      <c r="F126" s="42" t="n">
         <v>5.741</v>
       </c>
-      <c r="G126" s="41" t="n">
+      <c r="G126" s="42" t="n">
         <v>0.347</v>
       </c>
-      <c r="H126" s="41" t="n">
+      <c r="H126" s="42" t="n">
         <v>1.653</v>
       </c>
-      <c r="I126" s="39" t="n">
+      <c r="I126" s="40" t="n">
         <v>0.864</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="38" t="n">
+      <c r="A127" s="39" t="n">
         <v>16</v>
       </c>
-      <c r="B127" s="39" t="n">
+      <c r="B127" s="40" t="n">
         <v>3.532</v>
       </c>
-      <c r="C127" s="40" t="n">
+      <c r="C127" s="41" t="n">
         <v>0.2831</v>
       </c>
-      <c r="D127" s="39" t="n">
+      <c r="D127" s="40" t="n">
         <v>0.75</v>
       </c>
-      <c r="E127" s="41" t="n">
+      <c r="E127" s="42" t="n">
         <v>1.282</v>
       </c>
-      <c r="F127" s="41" t="n">
+      <c r="F127" s="42" t="n">
         <v>5.782</v>
       </c>
-      <c r="G127" s="41" t="n">
+      <c r="G127" s="42" t="n">
         <v>0.363</v>
       </c>
-      <c r="H127" s="41" t="n">
+      <c r="H127" s="42" t="n">
         <v>1.637</v>
       </c>
-      <c r="I127" s="39" t="n">
+      <c r="I127" s="40" t="n">
         <v>0.849</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="38" t="n">
+      <c r="A128" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="B128" s="39" t="n">
+      <c r="B128" s="40" t="n">
         <v>3.588</v>
       </c>
-      <c r="C128" s="40" t="n">
+      <c r="C128" s="41" t="n">
         <v>0.2787</v>
       </c>
-      <c r="D128" s="39" t="n">
+      <c r="D128" s="40" t="n">
         <v>0.744</v>
       </c>
-      <c r="E128" s="41" t="n">
+      <c r="E128" s="42" t="n">
         <v>1.356</v>
       </c>
-      <c r="F128" s="41" t="n">
+      <c r="F128" s="42" t="n">
         <v>5.82</v>
       </c>
-      <c r="G128" s="41" t="n">
+      <c r="G128" s="42" t="n">
         <v>0.378</v>
       </c>
-      <c r="H128" s="41" t="n">
+      <c r="H128" s="42" t="n">
         <v>1.622</v>
       </c>
-      <c r="I128" s="39" t="n">
+      <c r="I128" s="40" t="n">
         <v>0.836</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="38" t="n">
+      <c r="A129" s="39" t="n">
         <v>18</v>
       </c>
-      <c r="B129" s="39" t="n">
+      <c r="B129" s="40" t="n">
         <v>3.64</v>
       </c>
-      <c r="C129" s="40" t="n">
+      <c r="C129" s="41" t="n">
         <v>0.2747</v>
       </c>
-      <c r="D129" s="39" t="n">
+      <c r="D129" s="40" t="n">
         <v>0.739</v>
       </c>
-      <c r="E129" s="41" t="n">
+      <c r="E129" s="42" t="n">
         <v>1.424</v>
       </c>
-      <c r="F129" s="41" t="n">
+      <c r="F129" s="42" t="n">
         <v>5.856</v>
       </c>
-      <c r="G129" s="41" t="n">
+      <c r="G129" s="42" t="n">
         <v>0.391</v>
       </c>
-      <c r="H129" s="39" t="n">
+      <c r="H129" s="40" t="n">
         <v>1.608</v>
       </c>
-      <c r="I129" s="39" t="n">
+      <c r="I129" s="40" t="n">
         <v>0.824</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="38" t="n">
+      <c r="A130" s="39" t="n">
         <v>19</v>
       </c>
-      <c r="B130" s="39" t="n">
+      <c r="B130" s="40" t="n">
         <v>3.689</v>
       </c>
-      <c r="C130" s="40" t="n">
+      <c r="C130" s="41" t="n">
         <v>0.2711</v>
       </c>
-      <c r="D130" s="39" t="n">
+      <c r="D130" s="40" t="n">
         <v>0.734</v>
       </c>
-      <c r="E130" s="41" t="n">
+      <c r="E130" s="42" t="n">
         <v>1.487</v>
       </c>
-      <c r="F130" s="41" t="n">
+      <c r="F130" s="42" t="n">
         <v>5.891</v>
       </c>
-      <c r="G130" s="41" t="n">
+      <c r="G130" s="42" t="n">
         <v>0.403</v>
       </c>
-      <c r="H130" s="41" t="n">
+      <c r="H130" s="42" t="n">
         <v>1.597</v>
       </c>
-      <c r="I130" s="39" t="n">
+      <c r="I130" s="40" t="n">
         <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="38" t="n">
+      <c r="A131" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="39" t="n">
+      <c r="B131" s="40" t="n">
         <v>3.735</v>
       </c>
-      <c r="C131" s="40" t="n">
+      <c r="C131" s="41" t="n">
         <v>0.2677</v>
       </c>
-      <c r="D131" s="39" t="n">
+      <c r="D131" s="40" t="n">
         <v>0.729</v>
       </c>
-      <c r="E131" s="41" t="n">
+      <c r="E131" s="42" t="n">
         <v>1.549</v>
       </c>
-      <c r="F131" s="41" t="n">
+      <c r="F131" s="42" t="n">
         <v>5.921</v>
       </c>
-      <c r="G131" s="41" t="n">
+      <c r="G131" s="42" t="n">
         <v>0.415</v>
       </c>
-      <c r="H131" s="41" t="n">
+      <c r="H131" s="42" t="n">
         <v>1.585</v>
       </c>
-      <c r="I131" s="39" t="n">
+      <c r="I131" s="40" t="n">
         <v>0.803</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="38" t="n">
+      <c r="A132" s="39" t="n">
         <v>21</v>
       </c>
-      <c r="B132" s="39" t="n">
+      <c r="B132" s="40" t="n">
         <v>3.778</v>
       </c>
-      <c r="C132" s="40" t="n">
+      <c r="C132" s="41" t="n">
         <v>0.2647</v>
       </c>
-      <c r="D132" s="41" t="n">
+      <c r="D132" s="42" t="n">
         <v>0.724</v>
       </c>
-      <c r="E132" s="41" t="n">
+      <c r="E132" s="42" t="n">
         <v>1.605</v>
       </c>
-      <c r="F132" s="41" t="n">
+      <c r="F132" s="42" t="n">
         <v>5.951</v>
       </c>
-      <c r="G132" s="39" t="n">
+      <c r="G132" s="40" t="n">
         <v>0.425</v>
       </c>
-      <c r="H132" s="39" t="n">
+      <c r="H132" s="40" t="n">
         <v>1.575</v>
       </c>
-      <c r="I132" s="39" t="n">
+      <c r="I132" s="40" t="n">
         <v>0.794</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="38" t="n">
+      <c r="A133" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="B133" s="39" t="n">
+      <c r="B133" s="40" t="n">
         <v>3.819</v>
       </c>
-      <c r="C133" s="40" t="n">
+      <c r="C133" s="41" t="n">
         <v>0.2618</v>
       </c>
-      <c r="D133" s="39" t="n">
+      <c r="D133" s="40" t="n">
         <v>0.72</v>
       </c>
-      <c r="E133" s="39" t="n">
+      <c r="E133" s="40" t="n">
         <v>1.659</v>
       </c>
-      <c r="F133" s="39" t="n">
+      <c r="F133" s="40" t="n">
         <v>5.979</v>
       </c>
-      <c r="G133" s="39" t="n">
+      <c r="G133" s="40" t="n">
         <v>0.434</v>
       </c>
-      <c r="H133" s="39" t="n">
+      <c r="H133" s="40" t="n">
         <v>1.566</v>
       </c>
-      <c r="I133" s="39" t="n">
+      <c r="I133" s="40" t="n">
         <v>0.786</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="38" t="n">
+      <c r="A134" s="39" t="n">
         <v>23</v>
       </c>
-      <c r="B134" s="39" t="n">
+      <c r="B134" s="40" t="n">
         <v>3.858</v>
       </c>
-      <c r="C134" s="40" t="n">
+      <c r="C134" s="41" t="n">
         <v>0.2592</v>
       </c>
-      <c r="D134" s="39" t="n">
+      <c r="D134" s="40" t="n">
         <v>0.716</v>
       </c>
-      <c r="E134" s="39" t="n">
+      <c r="E134" s="40" t="n">
         <v>1.71</v>
       </c>
-      <c r="F134" s="39" t="n">
+      <c r="F134" s="40" t="n">
         <v>6.006</v>
       </c>
-      <c r="G134" s="39" t="n">
+      <c r="G134" s="40" t="n">
         <v>0.443</v>
       </c>
-      <c r="H134" s="39" t="n">
+      <c r="H134" s="40" t="n">
         <v>1.557</v>
       </c>
-      <c r="I134" s="39" t="n">
+      <c r="I134" s="40" t="n">
         <v>0.778</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="38" t="n">
+      <c r="A135" s="39" t="n">
         <v>24</v>
       </c>
-      <c r="B135" s="39" t="n">
+      <c r="B135" s="40" t="n">
         <v>3.895</v>
       </c>
-      <c r="C135" s="40" t="n">
+      <c r="C135" s="41" t="n">
         <v>0.2567</v>
       </c>
-      <c r="D135" s="39" t="n">
+      <c r="D135" s="40" t="n">
         <v>0.712</v>
       </c>
-      <c r="E135" s="39" t="n">
+      <c r="E135" s="40" t="n">
         <v>1.759</v>
       </c>
-      <c r="F135" s="39" t="n">
+      <c r="F135" s="40" t="n">
         <v>6.031</v>
       </c>
-      <c r="G135" s="41" t="n">
+      <c r="G135" s="42" t="n">
         <v>0.451</v>
       </c>
-      <c r="H135" s="39" t="n">
+      <c r="H135" s="40" t="n">
         <v>1.548</v>
       </c>
-      <c r="I135" s="39" t="n">
+      <c r="I135" s="40" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="38" t="n">
+      <c r="A136" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="B136" s="39" t="n">
+      <c r="B136" s="40" t="n">
         <v>3.931</v>
       </c>
-      <c r="C136" s="40" t="n">
+      <c r="C136" s="41" t="n">
         <v>0.2544</v>
       </c>
-      <c r="D136" s="39" t="n">
+      <c r="D136" s="40" t="n">
         <v>0.708</v>
       </c>
-      <c r="E136" s="41" t="n">
+      <c r="E136" s="42" t="n">
         <v>1.806</v>
       </c>
-      <c r="F136" s="41" t="n">
+      <c r="F136" s="42" t="n">
         <v>6.056</v>
       </c>
-      <c r="G136" s="39" t="n">
+      <c r="G136" s="40" t="n">
         <v>0.459</v>
       </c>
-      <c r="H136" s="39" t="n">
+      <c r="H136" s="40" t="n">
         <v>1.541</v>
       </c>
-      <c r="I136" s="39" t="n">
+      <c r="I136" s="40" t="n">
         <v>0.763</v>
       </c>
     </row>
@@ -6008,236 +7633,236 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="38" t="n">
+      <c r="A142" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B142" s="39" t="n">
+      <c r="B142" s="40" t="n">
         <v>1.88</v>
       </c>
-      <c r="C142" s="39" t="n">
+      <c r="C142" s="40" t="n">
         <v>2.659</v>
       </c>
-      <c r="D142" s="38" t="n">
+      <c r="D142" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E142" s="39" t="n">
+      <c r="E142" s="40" t="n">
         <v>3.267</v>
       </c>
-      <c r="F142" s="38" t="n">
+      <c r="F142" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="39" t="n">
+      <c r="G142" s="40" t="n">
         <v>3.267</v>
       </c>
-      <c r="H142" s="41" t="n">
+      <c r="H142" s="42" t="n">
         <v>2.659</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="38" t="n">
+      <c r="A143" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B143" s="39" t="n">
+      <c r="B143" s="40" t="n">
         <v>1.023</v>
       </c>
-      <c r="C143" s="39" t="n">
+      <c r="C143" s="40" t="n">
         <v>1.954</v>
       </c>
-      <c r="D143" s="38" t="n">
+      <c r="D143" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E143" s="39" t="n">
+      <c r="E143" s="40" t="n">
         <v>2.568</v>
       </c>
-      <c r="F143" s="38" t="n">
+      <c r="F143" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="41" t="n">
+      <c r="G143" s="42" t="n">
         <v>2.574</v>
       </c>
-      <c r="H143" s="39" t="n">
+      <c r="H143" s="40" t="n">
         <v>1.772</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="38" t="n">
+      <c r="A144" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B144" s="39" t="n">
+      <c r="B144" s="40" t="n">
         <v>0.729</v>
       </c>
-      <c r="C144" s="39" t="n">
+      <c r="C144" s="40" t="n">
         <v>1.628</v>
       </c>
-      <c r="D144" s="38" t="n">
+      <c r="D144" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E144" s="39" t="n">
+      <c r="E144" s="40" t="n">
         <v>2.266</v>
       </c>
-      <c r="F144" s="38" t="n">
+      <c r="F144" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G144" s="39" t="n">
+      <c r="G144" s="40" t="n">
         <v>2.282</v>
       </c>
-      <c r="H144" s="39" t="n">
+      <c r="H144" s="40" t="n">
         <v>1.457</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="38" t="n">
+      <c r="A145" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B145" s="39" t="n">
+      <c r="B145" s="40" t="n">
         <v>0.577</v>
       </c>
-      <c r="C145" s="39" t="n">
+      <c r="C145" s="40" t="n">
         <v>1.427</v>
       </c>
-      <c r="D145" s="38" t="n">
+      <c r="D145" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E145" s="39" t="n">
+      <c r="E145" s="40" t="n">
         <v>2.089</v>
       </c>
-      <c r="F145" s="38" t="n">
+      <c r="F145" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="41" t="n">
+      <c r="G145" s="42" t="n">
         <v>2.114</v>
       </c>
-      <c r="H145" s="39" t="n">
+      <c r="H145" s="40" t="n">
         <v>1.29</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="38" t="n">
+      <c r="A146" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B146" s="39" t="n">
+      <c r="B146" s="40" t="n">
         <v>0.483</v>
       </c>
-      <c r="C146" s="39" t="n">
+      <c r="C146" s="40" t="n">
         <v>1.287</v>
       </c>
-      <c r="D146" s="39" t="n">
+      <c r="D146" s="40" t="n">
         <v>0.03</v>
       </c>
-      <c r="E146" s="39" t="n">
+      <c r="E146" s="40" t="n">
         <v>1.97</v>
       </c>
-      <c r="F146" s="38" t="n">
+      <c r="F146" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="39" t="n">
+      <c r="G146" s="40" t="n">
         <v>2.004</v>
       </c>
-      <c r="H146" s="39" t="n">
+      <c r="H146" s="40" t="n">
         <v>1.184</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="38" t="n">
+      <c r="A147" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B147" s="39" t="n">
+      <c r="B147" s="40" t="n">
         <v>0.419</v>
       </c>
-      <c r="C147" s="39" t="n">
+      <c r="C147" s="40" t="n">
         <v>1.182</v>
       </c>
-      <c r="D147" s="39" t="n">
+      <c r="D147" s="40" t="n">
         <v>0.118</v>
       </c>
-      <c r="E147" s="39" t="n">
+      <c r="E147" s="40" t="n">
         <v>1.882</v>
       </c>
-      <c r="F147" s="39" t="n">
+      <c r="F147" s="40" t="n">
         <v>0.076</v>
       </c>
-      <c r="G147" s="39" t="n">
+      <c r="G147" s="40" t="n">
         <v>1.924</v>
       </c>
-      <c r="H147" s="39" t="n">
+      <c r="H147" s="40" t="n">
         <v>1.109</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="38" t="n">
+      <c r="A148" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B148" s="39" t="n">
+      <c r="B148" s="40" t="n">
         <v>0.373</v>
       </c>
-      <c r="C148" s="39" t="n">
+      <c r="C148" s="40" t="n">
         <v>1.099</v>
       </c>
-      <c r="D148" s="39" t="n">
+      <c r="D148" s="40" t="n">
         <v>0.185</v>
       </c>
-      <c r="E148" s="39" t="n">
+      <c r="E148" s="40" t="n">
         <v>1.815</v>
       </c>
-      <c r="F148" s="39" t="n">
+      <c r="F148" s="40" t="n">
         <v>0.136</v>
       </c>
-      <c r="G148" s="39" t="n">
+      <c r="G148" s="40" t="n">
         <v>1.864</v>
       </c>
-      <c r="H148" s="39" t="n">
+      <c r="H148" s="40" t="n">
         <v>1.054</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="38" t="n">
+      <c r="A149" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B149" s="39" t="n">
+      <c r="B149" s="40" t="n">
         <v>0.337</v>
       </c>
-      <c r="C149" s="39" t="n">
+      <c r="C149" s="40" t="n">
         <v>1.032</v>
       </c>
-      <c r="D149" s="39" t="n">
+      <c r="D149" s="40" t="n">
         <v>0.239</v>
       </c>
-      <c r="E149" s="39" t="n">
+      <c r="E149" s="40" t="n">
         <v>1.761</v>
       </c>
-      <c r="F149" s="39" t="n">
+      <c r="F149" s="40" t="n">
         <v>0.184</v>
       </c>
-      <c r="G149" s="39" t="n">
+      <c r="G149" s="40" t="n">
         <v>1.816</v>
       </c>
-      <c r="H149" s="39" t="n">
+      <c r="H149" s="40" t="n">
         <v>1.01</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="38" t="n">
+      <c r="A150" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B150" s="39" t="n">
+      <c r="B150" s="40" t="n">
         <v>0.308</v>
       </c>
-      <c r="C150" s="39" t="n">
+      <c r="C150" s="40" t="n">
         <v>0.975</v>
       </c>
-      <c r="D150" s="39" t="n">
+      <c r="D150" s="40" t="n">
         <v>0.284</v>
       </c>
-      <c r="E150" s="39" t="n">
+      <c r="E150" s="40" t="n">
         <v>1.716</v>
       </c>
-      <c r="F150" s="39" t="n">
+      <c r="F150" s="40" t="n">
         <v>0.223</v>
       </c>
-      <c r="G150" s="39" t="n">
+      <c r="G150" s="40" t="n">
         <v>1.777</v>
       </c>
-      <c r="H150" s="39" t="n">
+      <c r="H150" s="40" t="n">
         <v>0.975</v>
       </c>
     </row>
@@ -6327,1242 +7952,1242 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="44" t="n">
+      <c r="A156" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B156" s="45" t="n">
+      <c r="B156" s="46" t="n">
         <v>1.41421</v>
       </c>
-      <c r="C156" s="45" t="n">
+      <c r="C156" s="46" t="n">
         <v>1.91155</v>
       </c>
-      <c r="D156" s="45" t="n">
+      <c r="D156" s="46" t="n">
         <v>2.23887</v>
       </c>
-      <c r="E156" s="45" t="n">
+      <c r="E156" s="46" t="n">
         <v>2.48124</v>
       </c>
-      <c r="F156" s="45" t="n">
+      <c r="F156" s="46" t="n">
         <v>2.67253</v>
       </c>
-      <c r="G156" s="45" t="n">
+      <c r="G156" s="46" t="n">
         <v>2.82981</v>
       </c>
-      <c r="H156" s="45" t="n">
+      <c r="H156" s="46" t="n">
         <v>2.96288</v>
       </c>
-      <c r="I156" s="45" t="n">
+      <c r="I156" s="46" t="n">
         <v>3.07794</v>
       </c>
-      <c r="J156" s="45" t="n">
+      <c r="J156" s="46" t="n">
         <v>3.17905</v>
       </c>
-      <c r="K156" s="45" t="n">
+      <c r="K156" s="46" t="n">
         <v>3.26909</v>
       </c>
-      <c r="L156" s="45" t="n">
+      <c r="L156" s="46" t="n">
         <v>3.35016</v>
       </c>
-      <c r="M156" s="45" t="n">
+      <c r="M156" s="46" t="n">
         <v>3.42378</v>
       </c>
-      <c r="N156" s="45" t="n">
+      <c r="N156" s="46" t="n">
         <v>3.49116</v>
       </c>
-      <c r="O156" s="45" t="n">
+      <c r="O156" s="46" t="n">
         <v>3.55333</v>
       </c>
-      <c r="P156" s="45" t="n">
+      <c r="P156" s="46" t="n">
         <v>3.61071</v>
       </c>
-      <c r="Q156" s="45" t="n">
+      <c r="Q156" s="46" t="n">
         <v>3.66422</v>
       </c>
-      <c r="R156" s="45" t="n">
+      <c r="R156" s="46" t="n">
         <v>3.71424</v>
       </c>
-      <c r="S156" s="45" t="n">
+      <c r="S156" s="46" t="n">
         <v>3.76118</v>
       </c>
-      <c r="T156" s="45" t="n">
+      <c r="T156" s="46" t="n">
         <v>3.80537</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="44" t="n">
+      <c r="A157" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B157" s="45" t="n">
+      <c r="B157" s="46" t="n">
         <v>1.27931</v>
       </c>
-      <c r="C157" s="45" t="n">
+      <c r="C157" s="46" t="n">
         <v>1.80538</v>
       </c>
-      <c r="D157" s="45" t="n">
+      <c r="D157" s="46" t="n">
         <v>2.15069</v>
       </c>
-      <c r="E157" s="45" t="n">
+      <c r="E157" s="46" t="n">
         <v>2.40484</v>
       </c>
-      <c r="F157" s="45" t="n">
+      <c r="F157" s="46" t="n">
         <v>2.60438</v>
       </c>
-      <c r="G157" s="45" t="n">
+      <c r="G157" s="46" t="n">
         <v>2.76779</v>
       </c>
-      <c r="H157" s="45" t="n">
+      <c r="H157" s="46" t="n">
         <v>2.90562</v>
       </c>
-      <c r="I157" s="45" t="n">
+      <c r="I157" s="46" t="n">
         <v>3.02446</v>
       </c>
-      <c r="J157" s="45" t="n">
+      <c r="J157" s="46" t="n">
         <v>3.12869</v>
       </c>
-      <c r="K157" s="45" t="n">
+      <c r="K157" s="46" t="n">
         <v>3.22134</v>
       </c>
-      <c r="L157" s="45" t="n">
+      <c r="L157" s="46" t="n">
         <v>3.30463</v>
       </c>
-      <c r="M157" s="45" t="n">
+      <c r="M157" s="46" t="n">
         <v>3.38017</v>
       </c>
-      <c r="N157" s="45" t="n">
+      <c r="N157" s="46" t="n">
         <v>3.44922</v>
       </c>
-      <c r="O157" s="45" t="n">
+      <c r="O157" s="46" t="n">
         <v>3.51287</v>
       </c>
-      <c r="P157" s="45" t="n">
+      <c r="P157" s="46" t="n">
         <v>3.57156</v>
       </c>
-      <c r="Q157" s="45" t="n">
+      <c r="Q157" s="46" t="n">
         <v>3.62625</v>
       </c>
-      <c r="R157" s="45" t="n">
+      <c r="R157" s="46" t="n">
         <v>3.67734</v>
       </c>
-      <c r="S157" s="45" t="n">
+      <c r="S157" s="46" t="n">
         <v>3.72524</v>
       </c>
-      <c r="T157" s="45" t="n">
+      <c r="T157" s="46" t="n">
         <v>3.77032</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="44" t="n">
+      <c r="A158" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B158" s="45" t="n">
+      <c r="B158" s="46" t="n">
         <v>1.23105</v>
       </c>
-      <c r="C158" s="45" t="n">
+      <c r="C158" s="46" t="n">
         <v>1.76858</v>
       </c>
-      <c r="D158" s="45" t="n">
+      <c r="D158" s="46" t="n">
         <v>2.12049</v>
       </c>
-      <c r="E158" s="45" t="n">
+      <c r="E158" s="46" t="n">
         <v>2.37883</v>
       </c>
-      <c r="F158" s="45" t="n">
+      <c r="F158" s="46" t="n">
         <v>2.58127</v>
       </c>
-      <c r="G158" s="45" t="n">
+      <c r="G158" s="46" t="n">
         <v>2.74681</v>
       </c>
-      <c r="H158" s="45" t="n">
+      <c r="H158" s="46" t="n">
         <v>2.88628</v>
       </c>
-      <c r="I158" s="45" t="n">
+      <c r="I158" s="46" t="n">
         <v>3.00643</v>
       </c>
-      <c r="J158" s="45" t="n">
+      <c r="J158" s="46" t="n">
         <v>3.11173</v>
       </c>
-      <c r="K158" s="45" t="n">
+      <c r="K158" s="46" t="n">
         <v>3.20526</v>
       </c>
-      <c r="L158" s="45" t="n">
+      <c r="L158" s="46" t="n">
         <v>3.28931</v>
       </c>
-      <c r="M158" s="45" t="n">
+      <c r="M158" s="46" t="n">
         <v>3.3655</v>
       </c>
-      <c r="N158" s="45" t="n">
+      <c r="N158" s="46" t="n">
         <v>3.43512</v>
       </c>
-      <c r="O158" s="45" t="n">
+      <c r="O158" s="46" t="n">
         <v>3.49927</v>
       </c>
-      <c r="P158" s="45" t="n">
+      <c r="P158" s="46" t="n">
         <v>3.55842</v>
       </c>
-      <c r="Q158" s="45" t="n">
+      <c r="Q158" s="46" t="n">
         <v>3.61351</v>
       </c>
-      <c r="R158" s="45" t="n">
+      <c r="R158" s="46" t="n">
         <v>3.66495</v>
       </c>
-      <c r="S158" s="45" t="n">
+      <c r="S158" s="46" t="n">
         <v>3.71319</v>
       </c>
-      <c r="T158" s="45" t="n">
+      <c r="T158" s="46" t="n">
         <v>3.75857</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="44" t="n">
+      <c r="A159" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B159" s="45" t="n">
+      <c r="B159" s="46" t="n">
         <v>1.20621</v>
       </c>
-      <c r="C159" s="45" t="n">
+      <c r="C159" s="46" t="n">
         <v>1.74989</v>
       </c>
-      <c r="D159" s="45" t="n">
+      <c r="D159" s="46" t="n">
         <v>2.10522</v>
       </c>
-      <c r="E159" s="45" t="n">
+      <c r="E159" s="46" t="n">
         <v>2.36571</v>
       </c>
-      <c r="F159" s="45" t="n">
+      <c r="F159" s="46" t="n">
         <v>2.56964</v>
       </c>
-      <c r="G159" s="45" t="n">
+      <c r="G159" s="46" t="n">
         <v>2.73626</v>
       </c>
-      <c r="H159" s="45" t="n">
+      <c r="H159" s="46" t="n">
         <v>2.87656</v>
       </c>
-      <c r="I159" s="45" t="n">
+      <c r="I159" s="46" t="n">
         <v>2.99737</v>
       </c>
-      <c r="J159" s="45" t="n">
+      <c r="J159" s="46" t="n">
         <v>3.10321</v>
       </c>
-      <c r="K159" s="45" t="n">
+      <c r="K159" s="46" t="n">
         <v>3.1972</v>
       </c>
-      <c r="L159" s="45" t="n">
+      <c r="L159" s="46" t="n">
         <v>3.28163</v>
       </c>
-      <c r="M159" s="45" t="n">
+      <c r="M159" s="46" t="n">
         <v>3.35815</v>
       </c>
-      <c r="N159" s="45" t="n">
+      <c r="N159" s="46" t="n">
         <v>3.42805</v>
       </c>
-      <c r="O159" s="45" t="n">
+      <c r="O159" s="46" t="n">
         <v>3.49246</v>
       </c>
-      <c r="P159" s="45" t="n">
+      <c r="P159" s="46" t="n">
         <v>3.55183</v>
       </c>
-      <c r="Q159" s="45" t="n">
+      <c r="Q159" s="46" t="n">
         <v>3.60712</v>
       </c>
-      <c r="R159" s="45" t="n">
+      <c r="R159" s="46" t="n">
         <v>3.65875</v>
       </c>
-      <c r="S159" s="45" t="n">
+      <c r="S159" s="46" t="n">
         <v>3.70715</v>
       </c>
-      <c r="T159" s="45" t="n">
+      <c r="T159" s="46" t="n">
         <v>3.75268</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="44" t="n">
+      <c r="A160" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B160" s="45" t="n">
+      <c r="B160" s="46" t="n">
         <v>1.19105</v>
       </c>
-      <c r="C160" s="45" t="n">
+      <c r="C160" s="46" t="n">
         <v>1.73857</v>
       </c>
-      <c r="D160" s="45" t="n">
+      <c r="D160" s="46" t="n">
         <v>2.09601</v>
       </c>
-      <c r="E160" s="45" t="n">
+      <c r="E160" s="46" t="n">
         <v>2.35781</v>
       </c>
-      <c r="F160" s="45" t="n">
+      <c r="F160" s="46" t="n">
         <v>2.56263</v>
       </c>
-      <c r="G160" s="45" t="n">
+      <c r="G160" s="46" t="n">
         <v>2.72991</v>
       </c>
-      <c r="H160" s="45" t="n">
+      <c r="H160" s="46" t="n">
         <v>2.87071</v>
       </c>
-      <c r="I160" s="45" t="n">
+      <c r="I160" s="46" t="n">
         <v>2.99192</v>
       </c>
-      <c r="J160" s="45" t="n">
+      <c r="J160" s="46" t="n">
         <v>3.09808</v>
       </c>
-      <c r="K160" s="45" t="n">
+      <c r="K160" s="46" t="n">
         <v>3.19235</v>
       </c>
-      <c r="L160" s="45" t="n">
+      <c r="L160" s="46" t="n">
         <v>3.27701</v>
       </c>
-      <c r="M160" s="45" t="n">
+      <c r="M160" s="46" t="n">
         <v>3.35372</v>
       </c>
-      <c r="N160" s="45" t="n">
+      <c r="N160" s="46" t="n">
         <v>3.42381</v>
       </c>
-      <c r="O160" s="45" t="n">
+      <c r="O160" s="46" t="n">
         <v>3.48836</v>
       </c>
-      <c r="P160" s="45" t="n">
+      <c r="P160" s="46" t="n">
         <v>3.54787</v>
       </c>
-      <c r="Q160" s="45" t="n">
+      <c r="Q160" s="46" t="n">
         <v>3.60328</v>
       </c>
-      <c r="R160" s="45" t="n">
+      <c r="R160" s="46" t="n">
         <v>3.65502</v>
       </c>
-      <c r="S160" s="45" t="n">
+      <c r="S160" s="46" t="n">
         <v>3.70352</v>
       </c>
-      <c r="T160" s="45" t="n">
+      <c r="T160" s="46" t="n">
         <v>3.74914</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="44" t="n">
+      <c r="A161" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B161" s="45" t="n">
+      <c r="B161" s="46" t="n">
         <v>1.18083</v>
       </c>
-      <c r="C161" s="45" t="n">
+      <c r="C161" s="46" t="n">
         <v>1.73099</v>
       </c>
-      <c r="D161" s="45" t="n">
+      <c r="D161" s="46" t="n">
         <v>2.08985</v>
       </c>
-      <c r="E161" s="45" t="n">
+      <c r="E161" s="46" t="n">
         <v>2.35253</v>
       </c>
-      <c r="F161" s="45" t="n">
+      <c r="F161" s="46" t="n">
         <v>2.55795</v>
       </c>
-      <c r="G161" s="45" t="n">
+      <c r="G161" s="46" t="n">
         <v>2.72567</v>
       </c>
-      <c r="H161" s="45" t="n">
+      <c r="H161" s="46" t="n">
         <v>2.8668</v>
       </c>
-      <c r="I161" s="45" t="n">
+      <c r="I161" s="46" t="n">
         <v>2.98829</v>
       </c>
-      <c r="J161" s="45" t="n">
+      <c r="J161" s="46" t="n">
         <v>3.09467</v>
       </c>
-      <c r="K161" s="45" t="n">
+      <c r="K161" s="46" t="n">
         <v>3.18911</v>
       </c>
-      <c r="L161" s="45" t="n">
+      <c r="L161" s="46" t="n">
         <v>3.27392</v>
       </c>
-      <c r="M161" s="45" t="n">
+      <c r="M161" s="46" t="n">
         <v>3.35077</v>
       </c>
-      <c r="N161" s="45" t="n">
+      <c r="N161" s="46" t="n">
         <v>3.42097</v>
       </c>
-      <c r="O161" s="45" t="n">
+      <c r="O161" s="46" t="n">
         <v>3.48563</v>
       </c>
-      <c r="P161" s="45" t="n">
+      <c r="P161" s="46" t="n">
         <v>3.54522</v>
       </c>
-      <c r="Q161" s="45" t="n">
+      <c r="Q161" s="46" t="n">
         <v>3.60072</v>
       </c>
-      <c r="R161" s="45" t="n">
+      <c r="R161" s="46" t="n">
         <v>3.65253</v>
       </c>
-      <c r="S161" s="45" t="n">
+      <c r="S161" s="46" t="n">
         <v>3.70109</v>
       </c>
-      <c r="T161" s="45" t="n">
+      <c r="T161" s="46" t="n">
         <v>3.74678</v>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="44" t="n">
+      <c r="A162" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B162" s="45" t="n">
+      <c r="B162" s="46" t="n">
         <v>1.17348</v>
       </c>
-      <c r="C162" s="45" t="n">
+      <c r="C162" s="46" t="n">
         <v>1.72555</v>
       </c>
-      <c r="D162" s="45" t="n">
+      <c r="D162" s="46" t="n">
         <v>2.08543</v>
       </c>
-      <c r="E162" s="45" t="n">
+      <c r="E162" s="46" t="n">
         <v>2.34875</v>
       </c>
-      <c r="F162" s="45" t="n">
+      <c r="F162" s="46" t="n">
         <v>2.5546</v>
       </c>
-      <c r="G162" s="45" t="n">
+      <c r="G162" s="46" t="n">
         <v>2.72263</v>
       </c>
-      <c r="H162" s="45" t="n">
+      <c r="H162" s="46" t="n">
         <v>2.86401</v>
       </c>
-      <c r="I162" s="45" t="n">
+      <c r="I162" s="46" t="n">
         <v>2.98568</v>
       </c>
-      <c r="J162" s="45" t="n">
+      <c r="J162" s="46" t="n">
         <v>3.09222</v>
       </c>
-      <c r="K162" s="45" t="n">
+      <c r="K162" s="46" t="n">
         <v>3.18679</v>
       </c>
-      <c r="L162" s="45" t="n">
+      <c r="L162" s="46" t="n">
         <v>3.27172</v>
       </c>
-      <c r="M162" s="45" t="n">
+      <c r="M162" s="46" t="n">
         <v>3.34866</v>
       </c>
-      <c r="N162" s="45" t="n">
+      <c r="N162" s="46" t="n">
         <v>3.41894</v>
       </c>
-      <c r="O162" s="45" t="n">
+      <c r="O162" s="46" t="n">
         <v>3.48368</v>
       </c>
-      <c r="P162" s="45" t="n">
+      <c r="P162" s="46" t="n">
         <v>3.54333</v>
       </c>
-      <c r="Q162" s="45" t="n">
+      <c r="Q162" s="46" t="n">
         <v>3.59888</v>
       </c>
-      <c r="R162" s="45" t="n">
+      <c r="R162" s="46" t="n">
         <v>3.65075</v>
       </c>
-      <c r="S162" s="45" t="n">
+      <c r="S162" s="46" t="n">
         <v>3.69936</v>
       </c>
-      <c r="T162" s="45" t="n">
+      <c r="T162" s="46" t="n">
         <v>3.74509</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="44" t="n">
+      <c r="A163" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B163" s="45" t="n">
+      <c r="B163" s="46" t="n">
         <v>1.16794</v>
       </c>
-      <c r="C163" s="45" t="n">
+      <c r="C163" s="46" t="n">
         <v>1.72147</v>
       </c>
-      <c r="D163" s="45" t="n">
+      <c r="D163" s="46" t="n">
         <v>2.08212</v>
       </c>
-      <c r="E163" s="45" t="n">
+      <c r="E163" s="46" t="n">
         <v>2.34591</v>
       </c>
-      <c r="F163" s="45" t="n">
+      <c r="F163" s="46" t="n">
         <v>2.55208</v>
       </c>
-      <c r="G163" s="45" t="n">
+      <c r="G163" s="46" t="n">
         <v>2.72036</v>
       </c>
-      <c r="H163" s="45" t="n">
+      <c r="H163" s="46" t="n">
         <v>2.86192</v>
       </c>
-      <c r="I163" s="45" t="n">
+      <c r="I163" s="46" t="n">
         <v>2.98373</v>
       </c>
-      <c r="J163" s="45" t="n">
+      <c r="J163" s="46" t="n">
         <v>3.09039</v>
       </c>
-      <c r="K163" s="45" t="n">
+      <c r="K163" s="46" t="n">
         <v>3.18506</v>
       </c>
-      <c r="L163" s="45" t="n">
+      <c r="L163" s="46" t="n">
         <v>3.27006</v>
       </c>
-      <c r="M163" s="45" t="n">
+      <c r="M163" s="46" t="n">
         <v>3.34708</v>
       </c>
-      <c r="N163" s="45" t="n">
+      <c r="N163" s="46" t="n">
         <v>3.41742</v>
       </c>
-      <c r="O163" s="45" t="n">
+      <c r="O163" s="46" t="n">
         <v>3.48221</v>
       </c>
-      <c r="P163" s="45" t="n">
+      <c r="P163" s="46" t="n">
         <v>3.54192</v>
       </c>
-      <c r="Q163" s="45" t="n">
+      <c r="Q163" s="46" t="n">
         <v>3.59751</v>
       </c>
-      <c r="R163" s="45" t="n">
+      <c r="R163" s="46" t="n">
         <v>3.64941</v>
       </c>
-      <c r="S163" s="45" t="n">
+      <c r="S163" s="46" t="n">
         <v>3.69806</v>
       </c>
-      <c r="T163" s="45" t="n">
+      <c r="T163" s="46" t="n">
         <v>3.74382</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="44" t="n">
+      <c r="A164" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B164" s="45" t="n">
+      <c r="B164" s="46" t="n">
         <v>1.16361</v>
       </c>
-      <c r="C164" s="45" t="n">
+      <c r="C164" s="46" t="n">
         <v>1.71828</v>
       </c>
-      <c r="D164" s="45" t="n">
+      <c r="D164" s="46" t="n">
         <v>2.07953</v>
       </c>
-      <c r="E164" s="45" t="n">
+      <c r="E164" s="46" t="n">
         <v>2.3437</v>
       </c>
-      <c r="F164" s="45" t="n">
+      <c r="F164" s="46" t="n">
         <v>2.55013</v>
       </c>
-      <c r="G164" s="45" t="n">
+      <c r="G164" s="46" t="n">
         <v>2.71858</v>
       </c>
-      <c r="H164" s="45" t="n">
+      <c r="H164" s="46" t="n">
         <v>2.86028</v>
       </c>
-      <c r="I164" s="45" t="n">
+      <c r="I164" s="46" t="n">
         <v>2.98221</v>
       </c>
-      <c r="J164" s="45" t="n">
+      <c r="J164" s="46" t="n">
         <v>3.08896</v>
       </c>
-      <c r="K164" s="45" t="n">
+      <c r="K164" s="46" t="n">
         <v>3.1837</v>
       </c>
-      <c r="L164" s="45" t="n">
+      <c r="L164" s="46" t="n">
         <v>3.26878</v>
       </c>
-      <c r="M164" s="45" t="n">
+      <c r="M164" s="46" t="n">
         <v>3.34585</v>
       </c>
-      <c r="N164" s="45" t="n">
+      <c r="N164" s="46" t="n">
         <v>3.41624</v>
       </c>
-      <c r="O164" s="45" t="n">
+      <c r="O164" s="46" t="n">
         <v>3.48107</v>
       </c>
-      <c r="P164" s="45" t="n">
+      <c r="P164" s="46" t="n">
         <v>3.54081</v>
       </c>
-      <c r="Q164" s="45" t="n">
+      <c r="Q164" s="46" t="n">
         <v>3.59644</v>
       </c>
-      <c r="R164" s="45" t="n">
+      <c r="R164" s="46" t="n">
         <v>3.64838</v>
       </c>
-      <c r="S164" s="45" t="n">
+      <c r="S164" s="46" t="n">
         <v>3.69705</v>
       </c>
-      <c r="T164" s="45" t="n">
+      <c r="T164" s="46" t="n">
         <v>3.74284</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="44" t="n">
+      <c r="A165" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B165" s="45" t="n">
+      <c r="B165" s="46" t="n">
         <v>1.16014</v>
       </c>
-      <c r="C165" s="45" t="n">
+      <c r="C165" s="46" t="n">
         <v>1.71573</v>
       </c>
-      <c r="D165" s="45" t="n">
+      <c r="D165" s="46" t="n">
         <v>2.07746</v>
       </c>
-      <c r="E165" s="45" t="n">
+      <c r="E165" s="46" t="n">
         <v>2.34192</v>
       </c>
-      <c r="F165" s="45" t="n">
+      <c r="F165" s="46" t="n">
         <v>2.54856</v>
       </c>
-      <c r="G165" s="45" t="n">
+      <c r="G165" s="46" t="n">
         <v>2.71717</v>
       </c>
-      <c r="H165" s="45" t="n">
+      <c r="H165" s="46" t="n">
         <v>2.85898</v>
       </c>
-      <c r="I165" s="45" t="n">
+      <c r="I165" s="46" t="n">
         <v>2.981</v>
       </c>
-      <c r="J165" s="45" t="n">
+      <c r="J165" s="46" t="n">
         <v>3.08781</v>
       </c>
-      <c r="K165" s="45" t="n">
+      <c r="K165" s="46" t="n">
         <v>3.18262</v>
       </c>
-      <c r="L165" s="45" t="n">
+      <c r="L165" s="46" t="n">
         <v>3.26775</v>
       </c>
-      <c r="M165" s="45" t="n">
+      <c r="M165" s="46" t="n">
         <v>3.34486</v>
       </c>
-      <c r="N165" s="45" t="n">
+      <c r="N165" s="46" t="n">
         <v>3.41529</v>
       </c>
-      <c r="O165" s="45" t="n">
+      <c r="O165" s="46" t="n">
         <v>3.48016</v>
       </c>
-      <c r="P165" s="45" t="n">
+      <c r="P165" s="46" t="n">
         <v>3.53993</v>
       </c>
-      <c r="Q165" s="45" t="n">
+      <c r="Q165" s="46" t="n">
         <v>3.59559</v>
       </c>
-      <c r="R165" s="45" t="n">
+      <c r="R165" s="46" t="n">
         <v>3.64755</v>
       </c>
-      <c r="S165" s="45" t="n">
+      <c r="S165" s="46" t="n">
         <v>3.69625</v>
       </c>
-      <c r="T165" s="45" t="n">
+      <c r="T165" s="46" t="n">
         <v>3.74205</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="44" t="n">
+      <c r="A166" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="B166" s="45" t="n">
+      <c r="B166" s="46" t="n">
         <v>1.15729</v>
       </c>
-      <c r="C166" s="45" t="n">
+      <c r="C166" s="46" t="n">
         <v>1.71363</v>
       </c>
-      <c r="D166" s="45" t="n">
+      <c r="D166" s="46" t="n">
         <v>2.07577</v>
       </c>
-      <c r="E166" s="45" t="n">
+      <c r="E166" s="46" t="n">
         <v>2.34048</v>
       </c>
-      <c r="F166" s="45" t="n">
+      <c r="F166" s="46" t="n">
         <v>2.54728</v>
       </c>
-      <c r="G166" s="45" t="n">
+      <c r="G166" s="46" t="n">
         <v>2.716</v>
       </c>
-      <c r="H166" s="45" t="n">
+      <c r="H166" s="46" t="n">
         <v>2.85791</v>
       </c>
-      <c r="I166" s="45" t="n">
+      <c r="I166" s="46" t="n">
         <v>2.98</v>
       </c>
-      <c r="J166" s="45" t="n">
+      <c r="J166" s="46" t="n">
         <v>3.08688</v>
       </c>
-      <c r="K166" s="45" t="n">
+      <c r="K166" s="46" t="n">
         <v>3.18174</v>
       </c>
-      <c r="L166" s="45" t="n">
+      <c r="L166" s="46" t="n">
         <v>3.2669</v>
       </c>
-      <c r="M166" s="45" t="n">
+      <c r="M166" s="46" t="n">
         <v>3.34406</v>
       </c>
-      <c r="N166" s="45" t="n">
+      <c r="N166" s="46" t="n">
         <v>3.41452</v>
       </c>
-      <c r="O166" s="45" t="n">
+      <c r="O166" s="46" t="n">
         <v>3.47941</v>
       </c>
-      <c r="P166" s="45" t="n">
+      <c r="P166" s="46" t="n">
         <v>3.53921</v>
       </c>
-      <c r="Q166" s="45" t="n">
+      <c r="Q166" s="46" t="n">
         <v>3.59489</v>
       </c>
-      <c r="R166" s="45" t="n">
+      <c r="R166" s="46" t="n">
         <v>3.64687</v>
       </c>
-      <c r="S166" s="45" t="n">
+      <c r="S166" s="46" t="n">
         <v>3.69558</v>
       </c>
-      <c r="T166" s="45" t="n">
+      <c r="T166" s="46" t="n">
         <v>3.74141</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="44" t="n">
+      <c r="A167" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="B167" s="45" t="n">
+      <c r="B167" s="46" t="n">
         <v>1.1549</v>
       </c>
-      <c r="C167" s="45" t="n">
+      <c r="C167" s="46" t="n">
         <v>1.71189</v>
       </c>
-      <c r="D167" s="45" t="n">
+      <c r="D167" s="46" t="n">
         <v>2.07436</v>
       </c>
-      <c r="E167" s="45" t="n">
+      <c r="E167" s="46" t="n">
         <v>2.33927</v>
       </c>
-      <c r="F167" s="45" t="n">
+      <c r="F167" s="46" t="n">
         <v>2.54621</v>
       </c>
-      <c r="G167" s="45" t="n">
+      <c r="G167" s="46" t="n">
         <v>2.71504</v>
       </c>
-      <c r="H167" s="45" t="n">
+      <c r="H167" s="46" t="n">
         <v>2.85702</v>
       </c>
-      <c r="I167" s="45" t="n">
+      <c r="I167" s="46" t="n">
         <v>2.97917</v>
       </c>
-      <c r="J167" s="45" t="n">
+      <c r="J167" s="46" t="n">
         <v>3.0861</v>
       </c>
-      <c r="K167" s="45" t="n">
+      <c r="K167" s="46" t="n">
         <v>3.181</v>
       </c>
-      <c r="L167" s="45" t="n">
+      <c r="L167" s="46" t="n">
         <v>3.2662</v>
       </c>
-      <c r="M167" s="45" t="n">
+      <c r="M167" s="46" t="n">
         <v>3.34339</v>
       </c>
-      <c r="N167" s="45" t="n">
+      <c r="N167" s="46" t="n">
         <v>3.41387</v>
       </c>
-      <c r="O167" s="45" t="n">
+      <c r="O167" s="46" t="n">
         <v>3.47879</v>
       </c>
-      <c r="P167" s="45" t="n">
+      <c r="P167" s="46" t="n">
         <v>3.53861</v>
       </c>
-      <c r="Q167" s="45" t="n">
+      <c r="Q167" s="46" t="n">
         <v>3.5943</v>
       </c>
-      <c r="R167" s="45" t="n">
+      <c r="R167" s="46" t="n">
         <v>3.6463</v>
       </c>
-      <c r="S167" s="45" t="n">
+      <c r="S167" s="46" t="n">
         <v>3.69503</v>
       </c>
-      <c r="T167" s="45" t="n">
+      <c r="T167" s="46" t="n">
         <v>3.74087</v>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="44" t="n">
+      <c r="A168" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="B168" s="45" t="n">
+      <c r="B168" s="46" t="n">
         <v>1.15289</v>
       </c>
-      <c r="C168" s="45" t="n">
+      <c r="C168" s="46" t="n">
         <v>1.71041</v>
       </c>
-      <c r="D168" s="45" t="n">
+      <c r="D168" s="46" t="n">
         <v>2.07316</v>
       </c>
-      <c r="E168" s="45" t="n">
+      <c r="E168" s="46" t="n">
         <v>2.33824</v>
       </c>
-      <c r="F168" s="45" t="n">
+      <c r="F168" s="46" t="n">
         <v>2.5453</v>
       </c>
-      <c r="G168" s="45" t="n">
+      <c r="G168" s="46" t="n">
         <v>2.71422</v>
       </c>
-      <c r="H168" s="45" t="n">
+      <c r="H168" s="46" t="n">
         <v>2.85627</v>
       </c>
-      <c r="I168" s="45" t="n">
+      <c r="I168" s="46" t="n">
         <v>2.97847</v>
       </c>
-      <c r="J168" s="45" t="n">
+      <c r="J168" s="46" t="n">
         <v>3.08544</v>
       </c>
-      <c r="K168" s="45" t="n">
+      <c r="K168" s="46" t="n">
         <v>3.18037</v>
       </c>
-      <c r="L168" s="45" t="n">
+      <c r="L168" s="46" t="n">
         <v>3.26561</v>
       </c>
-      <c r="M168" s="45" t="n">
+      <c r="M168" s="46" t="n">
         <v>3.34282</v>
       </c>
-      <c r="N168" s="45" t="n">
+      <c r="N168" s="46" t="n">
         <v>3.41333</v>
       </c>
-      <c r="O168" s="45" t="n">
+      <c r="O168" s="46" t="n">
         <v>3.47826</v>
       </c>
-      <c r="P168" s="45" t="n">
+      <c r="P168" s="46" t="n">
         <v>3.5381</v>
       </c>
-      <c r="Q168" s="45" t="n">
+      <c r="Q168" s="46" t="n">
         <v>3.59381</v>
       </c>
-      <c r="R168" s="45" t="n">
+      <c r="R168" s="46" t="n">
         <v>3.64582</v>
       </c>
-      <c r="S168" s="45" t="n">
+      <c r="S168" s="46" t="n">
         <v>3.69457</v>
       </c>
-      <c r="T168" s="45" t="n">
+      <c r="T168" s="46" t="n">
         <v>3.74041</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="44" t="n">
+      <c r="A169" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="B169" s="45" t="n">
+      <c r="B169" s="46" t="n">
         <v>1.15115</v>
       </c>
-      <c r="C169" s="45" t="n">
+      <c r="C169" s="46" t="n">
         <v>1.70914</v>
       </c>
-      <c r="D169" s="45" t="n">
+      <c r="D169" s="46" t="n">
         <v>2.07213</v>
       </c>
-      <c r="E169" s="45" t="n">
+      <c r="E169" s="46" t="n">
         <v>2.33737</v>
       </c>
-      <c r="F169" s="45" t="n">
+      <c r="F169" s="46" t="n">
         <v>2.54452</v>
       </c>
-      <c r="G169" s="45" t="n">
+      <c r="G169" s="46" t="n">
         <v>2.71351</v>
       </c>
-      <c r="H169" s="45" t="n">
+      <c r="H169" s="46" t="n">
         <v>2.85562</v>
       </c>
-      <c r="I169" s="45" t="n">
+      <c r="I169" s="46" t="n">
         <v>2.97787</v>
       </c>
-      <c r="J169" s="45" t="n">
+      <c r="J169" s="46" t="n">
         <v>3.08487</v>
       </c>
-      <c r="K169" s="45" t="n">
+      <c r="K169" s="46" t="n">
         <v>3.17984</v>
       </c>
-      <c r="L169" s="45" t="n">
+      <c r="L169" s="46" t="n">
         <v>3.2651</v>
       </c>
-      <c r="M169" s="45" t="n">
+      <c r="M169" s="46" t="n">
         <v>3.34233</v>
       </c>
-      <c r="N169" s="45" t="n">
+      <c r="N169" s="46" t="n">
         <v>3.41286</v>
       </c>
-      <c r="O169" s="45" t="n">
+      <c r="O169" s="46" t="n">
         <v>3.47781</v>
       </c>
-      <c r="P169" s="45" t="n">
+      <c r="P169" s="46" t="n">
         <v>3.53766</v>
       </c>
-      <c r="Q169" s="45" t="n">
+      <c r="Q169" s="46" t="n">
         <v>3.59339</v>
       </c>
-      <c r="R169" s="45" t="n">
+      <c r="R169" s="46" t="n">
         <v>3.64541</v>
       </c>
-      <c r="S169" s="45" t="n">
+      <c r="S169" s="46" t="n">
         <v>3.69417</v>
       </c>
-      <c r="T169" s="45" t="n">
+      <c r="T169" s="46" t="n">
         <v>3.74002</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="44" t="n">
+      <c r="A170" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="B170" s="45" t="n">
+      <c r="B170" s="46" t="n">
         <v>1.14965</v>
       </c>
-      <c r="C170" s="45" t="n">
+      <c r="C170" s="46" t="n">
         <v>1.70804</v>
       </c>
-      <c r="D170" s="45" t="n">
+      <c r="D170" s="46" t="n">
         <v>2.07125</v>
       </c>
-      <c r="E170" s="45" t="n">
+      <c r="E170" s="46" t="n">
         <v>2.33661</v>
       </c>
-      <c r="F170" s="45" t="n">
+      <c r="F170" s="46" t="n">
         <v>2.54385</v>
       </c>
-      <c r="G170" s="45" t="n">
+      <c r="G170" s="46" t="n">
         <v>2.7129</v>
       </c>
-      <c r="H170" s="45" t="n">
+      <c r="H170" s="46" t="n">
         <v>2.85506</v>
       </c>
-      <c r="I170" s="45" t="n">
+      <c r="I170" s="46" t="n">
         <v>2.97735</v>
       </c>
-      <c r="J170" s="45" t="n">
+      <c r="J170" s="46" t="n">
         <v>3.08438</v>
       </c>
-      <c r="K170" s="45" t="n">
+      <c r="K170" s="46" t="n">
         <v>3.17938</v>
       </c>
-      <c r="L170" s="45" t="n">
+      <c r="L170" s="46" t="n">
         <v>3.26465</v>
       </c>
-      <c r="M170" s="45" t="n">
+      <c r="M170" s="46" t="n">
         <v>3.34191</v>
       </c>
-      <c r="N170" s="45" t="n">
+      <c r="N170" s="46" t="n">
         <v>3.41245</v>
       </c>
-      <c r="O170" s="45" t="n">
+      <c r="O170" s="46" t="n">
         <v>3.47742</v>
       </c>
-      <c r="P170" s="45" t="n">
+      <c r="P170" s="46" t="n">
         <v>3.53728</v>
       </c>
-      <c r="Q170" s="45" t="n">
+      <c r="Q170" s="46" t="n">
         <v>3.59302</v>
       </c>
-      <c r="R170" s="45" t="n">
+      <c r="R170" s="46" t="n">
         <v>3.64505</v>
       </c>
-      <c r="S170" s="45" t="n">
+      <c r="S170" s="46" t="n">
         <v>3.69382</v>
       </c>
-      <c r="T170" s="45" t="n">
+      <c r="T170" s="46" t="n">
         <v>3.73969</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="44" t="n">
+      <c r="A171" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="B171" s="45" t="n">
+      <c r="B171" s="46" t="n">
         <v>1.14833</v>
       </c>
-      <c r="C171" s="45" t="n">
+      <c r="C171" s="46" t="n">
         <v>1.70708</v>
       </c>
-      <c r="D171" s="45" t="n">
+      <c r="D171" s="46" t="n">
         <v>2.07047</v>
       </c>
-      <c r="E171" s="45" t="n">
+      <c r="E171" s="46" t="n">
         <v>2.33594</v>
       </c>
-      <c r="F171" s="45" t="n">
+      <c r="F171" s="46" t="n">
         <v>2.54326</v>
       </c>
-      <c r="G171" s="45" t="n">
+      <c r="G171" s="46" t="n">
         <v>2.71237</v>
       </c>
-      <c r="H171" s="45" t="n">
+      <c r="H171" s="46" t="n">
         <v>2.85457</v>
       </c>
-      <c r="I171" s="45" t="n">
+      <c r="I171" s="46" t="n">
         <v>2.97689</v>
       </c>
-      <c r="J171" s="45" t="n">
+      <c r="J171" s="46" t="n">
         <v>3.08395</v>
       </c>
-      <c r="K171" s="45" t="n">
+      <c r="K171" s="46" t="n">
         <v>3.17897</v>
       </c>
-      <c r="L171" s="45" t="n">
+      <c r="L171" s="46" t="n">
         <v>3.26427</v>
       </c>
-      <c r="M171" s="45" t="n">
+      <c r="M171" s="46" t="n">
         <v>3.34154</v>
       </c>
-      <c r="N171" s="45" t="n">
+      <c r="N171" s="46" t="n">
         <v>3.4121</v>
       </c>
-      <c r="O171" s="45" t="n">
+      <c r="O171" s="46" t="n">
         <v>3.47707</v>
       </c>
-      <c r="P171" s="45" t="n">
+      <c r="P171" s="46" t="n">
         <v>3.53695</v>
       </c>
-      <c r="Q171" s="45" t="n">
+      <c r="Q171" s="46" t="n">
         <v>3.5927</v>
       </c>
-      <c r="R171" s="45" t="n">
+      <c r="R171" s="46" t="n">
         <v>3.64474</v>
       </c>
-      <c r="S171" s="45" t="n">
+      <c r="S171" s="46" t="n">
         <v>3.69351</v>
       </c>
-      <c r="T171" s="45" t="n">
+      <c r="T171" s="46" t="n">
         <v>3.73939</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="44" t="n">
+      <c r="A172" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="B172" s="45" t="n">
+      <c r="B172" s="46" t="n">
         <v>1.14717</v>
       </c>
-      <c r="C172" s="45" t="n">
+      <c r="C172" s="46" t="n">
         <v>1.70623</v>
       </c>
-      <c r="D172" s="45" t="n">
+      <c r="D172" s="46" t="n">
         <v>2.06978</v>
       </c>
-      <c r="E172" s="45" t="n">
+      <c r="E172" s="46" t="n">
         <v>2.33535</v>
       </c>
-      <c r="F172" s="45" t="n">
+      <c r="F172" s="46" t="n">
         <v>2.54274</v>
       </c>
-      <c r="G172" s="45" t="n">
+      <c r="G172" s="46" t="n">
         <v>2.7119</v>
       </c>
-      <c r="H172" s="45" t="n">
+      <c r="H172" s="46" t="n">
         <v>2.85413</v>
       </c>
-      <c r="I172" s="45" t="n">
+      <c r="I172" s="46" t="n">
         <v>2.97649</v>
       </c>
-      <c r="J172" s="45" t="n">
+      <c r="J172" s="46" t="n">
         <v>3.08358</v>
       </c>
-      <c r="K172" s="45" t="n">
+      <c r="K172" s="46" t="n">
         <v>3.17861</v>
       </c>
-      <c r="L172" s="45" t="n">
+      <c r="L172" s="46" t="n">
         <v>3.26393</v>
       </c>
-      <c r="M172" s="45" t="n">
+      <c r="M172" s="46" t="n">
         <v>3.34121</v>
       </c>
-      <c r="N172" s="45" t="n">
+      <c r="N172" s="46" t="n">
         <v>3.41178</v>
       </c>
-      <c r="O172" s="45" t="n">
+      <c r="O172" s="46" t="n">
         <v>3.47677</v>
       </c>
-      <c r="P172" s="45" t="n">
+      <c r="P172" s="46" t="n">
         <v>3.53666</v>
       </c>
-      <c r="Q172" s="45" t="n">
+      <c r="Q172" s="46" t="n">
         <v>3.59242</v>
       </c>
-      <c r="R172" s="45" t="n">
+      <c r="R172" s="46" t="n">
         <v>3.64447</v>
       </c>
-      <c r="S172" s="45" t="n">
+      <c r="S172" s="46" t="n">
         <v>3.69325</v>
       </c>
-      <c r="T172" s="45" t="n">
+      <c r="T172" s="46" t="n">
         <v>3.73913</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="44" t="n">
+      <c r="A173" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="B173" s="45" t="n">
+      <c r="B173" s="46" t="n">
         <v>1.14613</v>
       </c>
-      <c r="C173" s="45" t="n">
+      <c r="C173" s="46" t="n">
         <v>1.70547</v>
       </c>
-      <c r="D173" s="45" t="n">
+      <c r="D173" s="46" t="n">
         <v>2.06917</v>
       </c>
-      <c r="E173" s="45" t="n">
+      <c r="E173" s="46" t="n">
         <v>2.33483</v>
       </c>
-      <c r="F173" s="45" t="n">
+      <c r="F173" s="46" t="n">
         <v>2.54228</v>
       </c>
-      <c r="G173" s="45" t="n">
+      <c r="G173" s="46" t="n">
         <v>2.71148</v>
       </c>
-      <c r="H173" s="45" t="n">
+      <c r="H173" s="46" t="n">
         <v>2.85375</v>
       </c>
-      <c r="I173" s="45" t="n">
+      <c r="I173" s="46" t="n">
         <v>2.97613</v>
       </c>
-      <c r="J173" s="45" t="n">
+      <c r="J173" s="46" t="n">
         <v>3.08324</v>
       </c>
-      <c r="K173" s="45" t="n">
+      <c r="K173" s="46" t="n">
         <v>3.17829</v>
       </c>
-      <c r="L173" s="45" t="n">
+      <c r="L173" s="46" t="n">
         <v>3.26362</v>
       </c>
-      <c r="M173" s="45" t="n">
+      <c r="M173" s="46" t="n">
         <v>3.34092</v>
       </c>
-      <c r="N173" s="45" t="n">
+      <c r="N173" s="46" t="n">
         <v>3.4115</v>
       </c>
-      <c r="O173" s="45" t="n">
+      <c r="O173" s="46" t="n">
         <v>3.4765</v>
       </c>
-      <c r="P173" s="45" t="n">
+      <c r="P173" s="46" t="n">
         <v>3.5364</v>
       </c>
-      <c r="Q173" s="45" t="n">
+      <c r="Q173" s="46" t="n">
         <v>3.59216</v>
       </c>
-      <c r="R173" s="45" t="n">
+      <c r="R173" s="46" t="n">
         <v>3.64422</v>
       </c>
-      <c r="S173" s="45" t="n">
+      <c r="S173" s="46" t="n">
         <v>3.69301</v>
       </c>
-      <c r="T173" s="45" t="n">
+      <c r="T173" s="46" t="n">
         <v>3.7389</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="44" t="n">
+      <c r="A174" s="45" t="n">
         <v>19</v>
       </c>
-      <c r="B174" s="45" t="n">
+      <c r="B174" s="46" t="n">
         <v>1.1452</v>
       </c>
-      <c r="C174" s="45" t="n">
+      <c r="C174" s="46" t="n">
         <v>1.7048</v>
       </c>
-      <c r="D174" s="45" t="n">
+      <c r="D174" s="46" t="n">
         <v>2.06862</v>
       </c>
-      <c r="E174" s="45" t="n">
+      <c r="E174" s="46" t="n">
         <v>2.33436</v>
       </c>
-      <c r="F174" s="45" t="n">
+      <c r="F174" s="46" t="n">
         <v>2.54187</v>
       </c>
-      <c r="G174" s="45" t="n">
+      <c r="G174" s="46" t="n">
         <v>2.71111</v>
       </c>
-      <c r="H174" s="45" t="n">
+      <c r="H174" s="46" t="n">
         <v>2.85341</v>
       </c>
-      <c r="I174" s="45" t="n">
+      <c r="I174" s="46" t="n">
         <v>2.97581</v>
       </c>
-      <c r="J174" s="45" t="n">
+      <c r="J174" s="46" t="n">
         <v>3.08294</v>
       </c>
-      <c r="K174" s="45" t="n">
+      <c r="K174" s="46" t="n">
         <v>3.17801</v>
       </c>
-      <c r="L174" s="45" t="n">
+      <c r="L174" s="46" t="n">
         <v>3.26335</v>
       </c>
-      <c r="M174" s="45" t="n">
+      <c r="M174" s="46" t="n">
         <v>3.34066</v>
       </c>
-      <c r="N174" s="45" t="n">
+      <c r="N174" s="46" t="n">
         <v>3.41125</v>
       </c>
-      <c r="O174" s="45" t="n">
+      <c r="O174" s="46" t="n">
         <v>3.47626</v>
       </c>
-      <c r="P174" s="45" t="n">
+      <c r="P174" s="46" t="n">
         <v>3.53617</v>
       </c>
-      <c r="Q174" s="45" t="n">
+      <c r="Q174" s="46" t="n">
         <v>3.59194</v>
       </c>
-      <c r="R174" s="45" t="n">
+      <c r="R174" s="46" t="n">
         <v>3.644</v>
       </c>
-      <c r="S174" s="45" t="n">
+      <c r="S174" s="46" t="n">
         <v>3.6928</v>
       </c>
-      <c r="T174" s="45" t="n">
+      <c r="T174" s="46" t="n">
         <v>3.73869</v>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="44" t="n">
+      <c r="A175" s="45" t="n">
         <v>20</v>
       </c>
-      <c r="B175" s="45" t="n">
+      <c r="B175" s="46" t="n">
         <v>1.14437</v>
       </c>
-      <c r="C175" s="45" t="n">
+      <c r="C175" s="46" t="n">
         <v>1.70419</v>
       </c>
-      <c r="D175" s="45" t="n">
+      <c r="D175" s="46" t="n">
         <v>2.06813</v>
       </c>
-      <c r="E175" s="45" t="n">
+      <c r="E175" s="46" t="n">
         <v>2.33394</v>
       </c>
-      <c r="F175" s="45" t="n">
+      <c r="F175" s="46" t="n">
         <v>2.54149</v>
       </c>
-      <c r="G175" s="45" t="n">
+      <c r="G175" s="46" t="n">
         <v>2.71077</v>
       </c>
-      <c r="H175" s="45" t="n">
+      <c r="H175" s="46" t="n">
         <v>2.8531</v>
       </c>
-      <c r="I175" s="45" t="n">
+      <c r="I175" s="46" t="n">
         <v>2.97552</v>
       </c>
-      <c r="J175" s="45" t="n">
+      <c r="J175" s="46" t="n">
         <v>3.08267</v>
       </c>
-      <c r="K175" s="45" t="n">
+      <c r="K175" s="46" t="n">
         <v>3.17775</v>
       </c>
-      <c r="L175" s="45" t="n">
+      <c r="L175" s="46" t="n">
         <v>3.26311</v>
       </c>
-      <c r="M175" s="45" t="n">
+      <c r="M175" s="46" t="n">
         <v>3.34042</v>
       </c>
-      <c r="N175" s="45" t="n">
+      <c r="N175" s="46" t="n">
         <v>3.41103</v>
       </c>
-      <c r="O175" s="45" t="n">
+      <c r="O175" s="46" t="n">
         <v>3.47605</v>
       </c>
-      <c r="P175" s="45" t="n">
+      <c r="P175" s="46" t="n">
         <v>3.53596</v>
       </c>
-      <c r="Q175" s="45" t="n">
+      <c r="Q175" s="46" t="n">
         <v>3.59174</v>
       </c>
-      <c r="R175" s="45" t="n">
+      <c r="R175" s="46" t="n">
         <v>3.6438</v>
       </c>
-      <c r="S175" s="45" t="n">
+      <c r="S175" s="46" t="n">
         <v>3.6926</v>
       </c>
-      <c r="T175" s="45" t="n">
+      <c r="T175" s="46" t="n">
         <v>3.7385</v>
       </c>
     </row>
@@ -7631,1242 +9256,1242 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="44" t="n">
+      <c r="A178" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="B178" s="46" t="n">
+      <c r="B178" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="C178" s="46" t="n">
+      <c r="C178" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="D178" s="46" t="n">
+      <c r="D178" s="47" t="n">
         <v>2.9</v>
       </c>
-      <c r="E178" s="46" t="n">
+      <c r="E178" s="47" t="n">
         <v>3.8</v>
       </c>
-      <c r="F178" s="46" t="n">
+      <c r="F178" s="47" t="n">
         <v>4.7</v>
       </c>
-      <c r="G178" s="46" t="n">
+      <c r="G178" s="47" t="n">
         <v>5.5</v>
       </c>
-      <c r="H178" s="46" t="n">
+      <c r="H178" s="47" t="n">
         <v>6.3</v>
       </c>
-      <c r="I178" s="46" t="n">
+      <c r="I178" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="J178" s="46" t="n">
+      <c r="J178" s="47" t="n">
         <v>7.7</v>
       </c>
-      <c r="K178" s="46" t="n">
+      <c r="K178" s="47" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L178" s="46" t="n">
+      <c r="L178" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="M178" s="46" t="n">
+      <c r="M178" s="47" t="n">
         <v>9.6</v>
       </c>
-      <c r="N178" s="46" t="n">
+      <c r="N178" s="47" t="n">
         <v>10.2</v>
       </c>
-      <c r="O178" s="46" t="n">
+      <c r="O178" s="47" t="n">
         <v>10.8</v>
       </c>
-      <c r="P178" s="46" t="n">
+      <c r="P178" s="47" t="n">
         <v>11.3</v>
       </c>
-      <c r="Q178" s="46" t="n">
+      <c r="Q178" s="47" t="n">
         <v>11.9</v>
       </c>
-      <c r="R178" s="46" t="n">
+      <c r="R178" s="47" t="n">
         <v>12.4</v>
       </c>
-      <c r="S178" s="46" t="n">
+      <c r="S178" s="47" t="n">
         <v>12.9</v>
       </c>
-      <c r="T178" s="46" t="n">
+      <c r="T178" s="47" t="n">
         <v>13.4</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="44" t="n">
+      <c r="A179" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="B179" s="46" t="n">
+      <c r="B179" s="47" t="n">
         <v>1.9</v>
       </c>
-      <c r="C179" s="46" t="n">
+      <c r="C179" s="47" t="n">
         <v>3.8</v>
       </c>
-      <c r="D179" s="46" t="n">
+      <c r="D179" s="47" t="n">
         <v>5.7</v>
       </c>
-      <c r="E179" s="46" t="n">
+      <c r="E179" s="47" t="n">
         <v>7.5</v>
       </c>
-      <c r="F179" s="46" t="n">
+      <c r="F179" s="47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G179" s="46" t="n">
+      <c r="G179" s="47" t="n">
         <v>10.8</v>
       </c>
-      <c r="H179" s="46" t="n">
+      <c r="H179" s="47" t="n">
         <v>12.3</v>
       </c>
-      <c r="I179" s="46" t="n">
+      <c r="I179" s="47" t="n">
         <v>13.8</v>
       </c>
-      <c r="J179" s="46" t="n">
+      <c r="J179" s="47" t="n">
         <v>15.1</v>
       </c>
-      <c r="K179" s="46" t="n">
+      <c r="K179" s="47" t="n">
         <v>16.5</v>
       </c>
-      <c r="L179" s="46" t="n">
+      <c r="L179" s="47" t="n">
         <v>17.8</v>
       </c>
-      <c r="M179" s="46" t="n">
+      <c r="M179" s="47" t="n">
         <v>19</v>
       </c>
-      <c r="N179" s="46" t="n">
+      <c r="N179" s="47" t="n">
         <v>20.2</v>
       </c>
-      <c r="O179" s="46" t="n">
+      <c r="O179" s="47" t="n">
         <v>21.3</v>
       </c>
-      <c r="P179" s="46" t="n">
+      <c r="P179" s="47" t="n">
         <v>22.4</v>
       </c>
-      <c r="Q179" s="46" t="n">
+      <c r="Q179" s="47" t="n">
         <v>23.5</v>
       </c>
-      <c r="R179" s="46" t="n">
+      <c r="R179" s="47" t="n">
         <v>24.5</v>
       </c>
-      <c r="S179" s="46" t="n">
+      <c r="S179" s="47" t="n">
         <v>25.5</v>
       </c>
-      <c r="T179" s="46" t="n">
+      <c r="T179" s="47" t="n">
         <v>26.5</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="44" t="n">
+      <c r="A180" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="B180" s="46" t="n">
+      <c r="B180" s="47" t="n">
         <v>2.8</v>
       </c>
-      <c r="C180" s="46" t="n">
+      <c r="C180" s="47" t="n">
         <v>5.7</v>
       </c>
-      <c r="D180" s="46" t="n">
+      <c r="D180" s="47" t="n">
         <v>8.4</v>
       </c>
-      <c r="E180" s="46" t="n">
+      <c r="E180" s="47" t="n">
         <v>11.1</v>
       </c>
-      <c r="F180" s="46" t="n">
+      <c r="F180" s="47" t="n">
         <v>13.6</v>
       </c>
-      <c r="G180" s="46" t="n">
+      <c r="G180" s="47" t="n">
         <v>16</v>
       </c>
-      <c r="H180" s="46" t="n">
+      <c r="H180" s="47" t="n">
         <v>18.3</v>
       </c>
-      <c r="I180" s="46" t="n">
+      <c r="I180" s="47" t="n">
         <v>20.5</v>
       </c>
-      <c r="J180" s="46" t="n">
+      <c r="J180" s="47" t="n">
         <v>22.6</v>
       </c>
-      <c r="K180" s="46" t="n">
+      <c r="K180" s="47" t="n">
         <v>24.6</v>
       </c>
-      <c r="L180" s="46" t="n">
+      <c r="L180" s="47" t="n">
         <v>26.5</v>
       </c>
-      <c r="M180" s="46" t="n">
+      <c r="M180" s="47" t="n">
         <v>28.4</v>
       </c>
-      <c r="N180" s="46" t="n">
+      <c r="N180" s="47" t="n">
         <v>30.1</v>
       </c>
-      <c r="O180" s="46" t="n">
+      <c r="O180" s="47" t="n">
         <v>31.9</v>
       </c>
-      <c r="P180" s="46" t="n">
+      <c r="P180" s="47" t="n">
         <v>33.5</v>
       </c>
-      <c r="Q180" s="46" t="n">
+      <c r="Q180" s="47" t="n">
         <v>35.1</v>
       </c>
-      <c r="R180" s="46" t="n">
+      <c r="R180" s="47" t="n">
         <v>36.7</v>
       </c>
-      <c r="S180" s="46" t="n">
+      <c r="S180" s="47" t="n">
         <v>38.2</v>
       </c>
-      <c r="T180" s="46" t="n">
+      <c r="T180" s="47" t="n">
         <v>39.7</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="44" t="n">
+      <c r="A181" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="B181" s="46" t="n">
+      <c r="B181" s="47" t="n">
         <v>3.7</v>
       </c>
-      <c r="C181" s="46" t="n">
+      <c r="C181" s="47" t="n">
         <v>7.5</v>
       </c>
-      <c r="D181" s="46" t="n">
+      <c r="D181" s="47" t="n">
         <v>11.2</v>
       </c>
-      <c r="E181" s="46" t="n">
+      <c r="E181" s="47" t="n">
         <v>14.7</v>
       </c>
-      <c r="F181" s="46" t="n">
+      <c r="F181" s="47" t="n">
         <v>18.1</v>
       </c>
-      <c r="G181" s="46" t="n">
+      <c r="G181" s="47" t="n">
         <v>21.3</v>
       </c>
-      <c r="H181" s="46" t="n">
+      <c r="H181" s="47" t="n">
         <v>24.4</v>
       </c>
-      <c r="I181" s="46" t="n">
+      <c r="I181" s="47" t="n">
         <v>27.3</v>
       </c>
-      <c r="J181" s="46" t="n">
+      <c r="J181" s="47" t="n">
         <v>30.1</v>
       </c>
-      <c r="K181" s="46" t="n">
+      <c r="K181" s="47" t="n">
         <v>32.7</v>
       </c>
-      <c r="L181" s="46" t="n">
+      <c r="L181" s="47" t="n">
         <v>35.3</v>
       </c>
-      <c r="M181" s="46" t="n">
+      <c r="M181" s="47" t="n">
         <v>37.7</v>
       </c>
-      <c r="N181" s="46" t="n">
+      <c r="N181" s="47" t="n">
         <v>40.1</v>
       </c>
-      <c r="O181" s="46" t="n">
+      <c r="O181" s="47" t="n">
         <v>42.4</v>
       </c>
-      <c r="P181" s="46" t="n">
+      <c r="P181" s="47" t="n">
         <v>44.6</v>
       </c>
-      <c r="Q181" s="46" t="n">
+      <c r="Q181" s="47" t="n">
         <v>46.7</v>
       </c>
-      <c r="R181" s="46" t="n">
+      <c r="R181" s="47" t="n">
         <v>48.8</v>
       </c>
-      <c r="S181" s="46" t="n">
+      <c r="S181" s="47" t="n">
         <v>50.8</v>
       </c>
-      <c r="T181" s="46" t="n">
+      <c r="T181" s="47" t="n">
         <v>52.8</v>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="44" t="n">
+      <c r="A182" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="B182" s="46" t="n">
+      <c r="B182" s="47" t="n">
         <v>4.6</v>
       </c>
-      <c r="C182" s="46" t="n">
+      <c r="C182" s="47" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="D182" s="46" t="n">
+      <c r="D182" s="47" t="n">
         <v>13.9</v>
       </c>
-      <c r="E182" s="46" t="n">
+      <c r="E182" s="47" t="n">
         <v>18.4</v>
       </c>
-      <c r="F182" s="46" t="n">
+      <c r="F182" s="47" t="n">
         <v>22.6</v>
       </c>
-      <c r="G182" s="46" t="n">
+      <c r="G182" s="47" t="n">
         <v>26.6</v>
       </c>
-      <c r="H182" s="46" t="n">
+      <c r="H182" s="47" t="n">
         <v>30.4</v>
       </c>
-      <c r="I182" s="46" t="n">
+      <c r="I182" s="47" t="n">
         <v>34</v>
       </c>
-      <c r="J182" s="46" t="n">
+      <c r="J182" s="47" t="n">
         <v>37.5</v>
       </c>
-      <c r="K182" s="46" t="n">
+      <c r="K182" s="47" t="n">
         <v>40.8</v>
       </c>
-      <c r="L182" s="46" t="n">
+      <c r="L182" s="47" t="n">
         <v>44</v>
       </c>
-      <c r="M182" s="46" t="n">
+      <c r="M182" s="47" t="n">
         <v>47.1</v>
       </c>
-      <c r="N182" s="46" t="n">
+      <c r="N182" s="47" t="n">
         <v>50.1</v>
       </c>
-      <c r="O182" s="46" t="n">
+      <c r="O182" s="47" t="n">
         <v>52.9</v>
       </c>
-      <c r="P182" s="46" t="n">
+      <c r="P182" s="47" t="n">
         <v>55.7</v>
       </c>
-      <c r="Q182" s="46" t="n">
+      <c r="Q182" s="47" t="n">
         <v>58.4</v>
       </c>
-      <c r="R182" s="46" t="n">
+      <c r="R182" s="47" t="n">
         <v>61</v>
       </c>
-      <c r="S182" s="46" t="n">
+      <c r="S182" s="47" t="n">
         <v>63.5</v>
       </c>
-      <c r="T182" s="46" t="n">
+      <c r="T182" s="47" t="n">
         <v>65.90000000000001</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="44" t="n">
+      <c r="A183" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="B183" s="46" t="n">
+      <c r="B183" s="47" t="n">
         <v>5.5</v>
       </c>
-      <c r="C183" s="46" t="n">
+      <c r="C183" s="47" t="n">
         <v>11.1</v>
       </c>
-      <c r="D183" s="46" t="n">
+      <c r="D183" s="47" t="n">
         <v>16.7</v>
       </c>
-      <c r="E183" s="46" t="n">
+      <c r="E183" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="F183" s="46" t="n">
+      <c r="F183" s="47" t="n">
         <v>27</v>
       </c>
-      <c r="G183" s="46" t="n">
+      <c r="G183" s="47" t="n">
         <v>31.8</v>
       </c>
-      <c r="H183" s="46" t="n">
+      <c r="H183" s="47" t="n">
         <v>36.4</v>
       </c>
-      <c r="I183" s="46" t="n">
+      <c r="I183" s="47" t="n">
         <v>40.8</v>
       </c>
-      <c r="J183" s="46" t="n">
+      <c r="J183" s="47" t="n">
         <v>45</v>
       </c>
-      <c r="K183" s="46" t="n">
+      <c r="K183" s="47" t="n">
         <v>49</v>
       </c>
-      <c r="L183" s="46" t="n">
+      <c r="L183" s="47" t="n">
         <v>52.8</v>
       </c>
-      <c r="M183" s="46" t="n">
+      <c r="M183" s="47" t="n">
         <v>56.5</v>
       </c>
-      <c r="N183" s="46" t="n">
+      <c r="N183" s="47" t="n">
         <v>60.1</v>
       </c>
-      <c r="O183" s="46" t="n">
+      <c r="O183" s="47" t="n">
         <v>63.5</v>
       </c>
-      <c r="P183" s="46" t="n">
+      <c r="P183" s="47" t="n">
         <v>66.8</v>
       </c>
-      <c r="Q183" s="46" t="n">
+      <c r="Q183" s="47" t="n">
         <v>70</v>
       </c>
-      <c r="R183" s="46" t="n">
+      <c r="R183" s="47" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="S183" s="46" t="n">
+      <c r="S183" s="47" t="n">
         <v>76.09999999999999</v>
       </c>
-      <c r="T183" s="46" t="n">
+      <c r="T183" s="47" t="n">
         <v>79.09999999999999</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="44" t="n">
+      <c r="A184" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="B184" s="46" t="n">
+      <c r="B184" s="47" t="n">
         <v>6.4</v>
       </c>
-      <c r="C184" s="46" t="n">
+      <c r="C184" s="47" t="n">
         <v>12.9</v>
       </c>
-      <c r="D184" s="46" t="n">
+      <c r="D184" s="47" t="n">
         <v>19.4</v>
       </c>
-      <c r="E184" s="46" t="n">
+      <c r="E184" s="47" t="n">
         <v>25.6</v>
       </c>
-      <c r="F184" s="46" t="n">
+      <c r="F184" s="47" t="n">
         <v>31.5</v>
       </c>
-      <c r="G184" s="46" t="n">
+      <c r="G184" s="47" t="n">
         <v>37.1</v>
       </c>
-      <c r="H184" s="46" t="n">
+      <c r="H184" s="47" t="n">
         <v>42.5</v>
       </c>
-      <c r="I184" s="46" t="n">
+      <c r="I184" s="47" t="n">
         <v>47.6</v>
       </c>
-      <c r="J184" s="46" t="n">
+      <c r="J184" s="47" t="n">
         <v>52.4</v>
       </c>
-      <c r="K184" s="46" t="n">
+      <c r="K184" s="47" t="n">
         <v>57.1</v>
       </c>
-      <c r="L184" s="46" t="n">
+      <c r="L184" s="47" t="n">
         <v>61.6</v>
       </c>
-      <c r="M184" s="46" t="n">
+      <c r="M184" s="47" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="N184" s="46" t="n">
+      <c r="N184" s="47" t="n">
         <v>70</v>
       </c>
-      <c r="O184" s="46" t="n">
+      <c r="O184" s="47" t="n">
         <v>74</v>
       </c>
-      <c r="P184" s="46" t="n">
+      <c r="P184" s="47" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="Q184" s="46" t="n">
+      <c r="Q184" s="47" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="R184" s="46" t="n">
+      <c r="R184" s="47" t="n">
         <v>85.3</v>
       </c>
-      <c r="S184" s="46" t="n">
+      <c r="S184" s="47" t="n">
         <v>88.8</v>
       </c>
-      <c r="T184" s="46" t="n">
+      <c r="T184" s="47" t="n">
         <v>92.2</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="44" t="n">
+      <c r="A185" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="B185" s="46" t="n">
+      <c r="B185" s="47" t="n">
         <v>7.2</v>
       </c>
-      <c r="C185" s="46" t="n">
+      <c r="C185" s="47" t="n">
         <v>14.8</v>
       </c>
-      <c r="D185" s="46" t="n">
+      <c r="D185" s="47" t="n">
         <v>22.1</v>
       </c>
-      <c r="E185" s="46" t="n">
+      <c r="E185" s="47" t="n">
         <v>29.2</v>
       </c>
-      <c r="F185" s="46" t="n">
+      <c r="F185" s="47" t="n">
         <v>36</v>
       </c>
-      <c r="G185" s="46" t="n">
+      <c r="G185" s="47" t="n">
         <v>42.4</v>
       </c>
-      <c r="H185" s="46" t="n">
+      <c r="H185" s="47" t="n">
         <v>48.5</v>
       </c>
-      <c r="I185" s="46" t="n">
+      <c r="I185" s="47" t="n">
         <v>54.3</v>
       </c>
-      <c r="J185" s="46" t="n">
+      <c r="J185" s="47" t="n">
         <v>59.9</v>
       </c>
-      <c r="K185" s="46" t="n">
+      <c r="K185" s="47" t="n">
         <v>65.2</v>
       </c>
-      <c r="L185" s="46" t="n">
+      <c r="L185" s="47" t="n">
         <v>70.3</v>
       </c>
-      <c r="M185" s="46" t="n">
+      <c r="M185" s="47" t="n">
         <v>75.2</v>
       </c>
-      <c r="N185" s="46" t="n">
+      <c r="N185" s="47" t="n">
         <v>80</v>
       </c>
-      <c r="O185" s="46" t="n">
+      <c r="O185" s="47" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="P185" s="46" t="n">
+      <c r="P185" s="47" t="n">
         <v>89</v>
       </c>
-      <c r="Q185" s="46" t="n">
+      <c r="Q185" s="47" t="n">
         <v>93.3</v>
       </c>
-      <c r="R185" s="46" t="n">
+      <c r="R185" s="47" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="S185" s="46" t="n">
+      <c r="S185" s="47" t="n">
         <v>101.4</v>
       </c>
-      <c r="T185" s="46" t="n">
+      <c r="T185" s="47" t="n">
         <v>105.3</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="44" t="n">
+      <c r="A186" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="B186" s="46" t="n">
+      <c r="B186" s="47" t="n">
         <v>8.1</v>
       </c>
-      <c r="C186" s="46" t="n">
+      <c r="C186" s="47" t="n">
         <v>16.6</v>
       </c>
-      <c r="D186" s="46" t="n">
+      <c r="D186" s="47" t="n">
         <v>24.9</v>
       </c>
-      <c r="E186" s="46" t="n">
+      <c r="E186" s="47" t="n">
         <v>32.9</v>
       </c>
-      <c r="F186" s="46" t="n">
+      <c r="F186" s="47" t="n">
         <v>40.4</v>
       </c>
-      <c r="G186" s="46" t="n">
+      <c r="G186" s="47" t="n">
         <v>47.7</v>
       </c>
-      <c r="H186" s="46" t="n">
+      <c r="H186" s="47" t="n">
         <v>54.5</v>
       </c>
-      <c r="I186" s="46" t="n">
+      <c r="I186" s="47" t="n">
         <v>61.1</v>
       </c>
-      <c r="J186" s="46" t="n">
+      <c r="J186" s="47" t="n">
         <v>67.3</v>
       </c>
-      <c r="K186" s="46" t="n">
+      <c r="K186" s="47" t="n">
         <v>73.3</v>
       </c>
-      <c r="L186" s="46" t="n">
+      <c r="L186" s="47" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="M186" s="46" t="n">
+      <c r="M186" s="47" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="N186" s="46" t="n">
+      <c r="N186" s="47" t="n">
         <v>90</v>
       </c>
-      <c r="O186" s="46" t="n">
+      <c r="O186" s="47" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="P186" s="46" t="n">
+      <c r="P186" s="47" t="n">
         <v>100.1</v>
       </c>
-      <c r="Q186" s="46" t="n">
+      <c r="Q186" s="47" t="n">
         <v>104.9</v>
       </c>
-      <c r="R186" s="46" t="n">
+      <c r="R186" s="47" t="n">
         <v>109.5</v>
       </c>
-      <c r="S186" s="46" t="n">
+      <c r="S186" s="47" t="n">
         <v>114.1</v>
       </c>
-      <c r="T186" s="46" t="n">
+      <c r="T186" s="47" t="n">
         <v>118.5</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="44" t="n">
+      <c r="A187" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="B187" s="46" t="n">
+      <c r="B187" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C187" s="46" t="n">
+      <c r="C187" s="47" t="n">
         <v>18.4</v>
       </c>
-      <c r="D187" s="46" t="n">
+      <c r="D187" s="47" t="n">
         <v>27.6</v>
       </c>
-      <c r="E187" s="46" t="n">
+      <c r="E187" s="47" t="n">
         <v>36.5</v>
       </c>
-      <c r="F187" s="46" t="n">
+      <c r="F187" s="47" t="n">
         <v>44.9</v>
       </c>
-      <c r="G187" s="46" t="n">
+      <c r="G187" s="47" t="n">
         <v>52.9</v>
       </c>
-      <c r="H187" s="46" t="n">
+      <c r="H187" s="47" t="n">
         <v>60.6</v>
       </c>
-      <c r="I187" s="46" t="n">
+      <c r="I187" s="47" t="n">
         <v>67.8</v>
       </c>
-      <c r="J187" s="46" t="n">
+      <c r="J187" s="47" t="n">
         <v>74.8</v>
       </c>
-      <c r="K187" s="46" t="n">
+      <c r="K187" s="47" t="n">
         <v>81.5</v>
       </c>
-      <c r="L187" s="46" t="n">
+      <c r="L187" s="47" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="M187" s="46" t="n">
+      <c r="M187" s="47" t="n">
         <v>94</v>
       </c>
-      <c r="N187" s="46" t="n">
+      <c r="N187" s="47" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="O187" s="46" t="n">
+      <c r="O187" s="47" t="n">
         <v>105.6</v>
       </c>
-      <c r="P187" s="46" t="n">
+      <c r="P187" s="47" t="n">
         <v>111.2</v>
       </c>
-      <c r="Q187" s="46" t="n">
+      <c r="Q187" s="47" t="n">
         <v>116.5</v>
       </c>
-      <c r="R187" s="46" t="n">
+      <c r="R187" s="47" t="n">
         <v>121.7</v>
       </c>
-      <c r="S187" s="46" t="n">
+      <c r="S187" s="47" t="n">
         <v>126.7</v>
       </c>
-      <c r="T187" s="46" t="n">
+      <c r="T187" s="47" t="n">
         <v>131.6</v>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="44" t="n">
+      <c r="A188" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="B188" s="46" t="n">
+      <c r="B188" s="47" t="n">
         <v>9.9</v>
       </c>
-      <c r="C188" s="46" t="n">
+      <c r="C188" s="47" t="n">
         <v>20.2</v>
       </c>
-      <c r="D188" s="46" t="n">
+      <c r="D188" s="47" t="n">
         <v>30.4</v>
       </c>
-      <c r="E188" s="46" t="n">
+      <c r="E188" s="47" t="n">
         <v>40.1</v>
       </c>
-      <c r="F188" s="46" t="n">
+      <c r="F188" s="47" t="n">
         <v>49.4</v>
       </c>
-      <c r="G188" s="46" t="n">
+      <c r="G188" s="47" t="n">
         <v>58.2</v>
       </c>
-      <c r="H188" s="46" t="n">
+      <c r="H188" s="47" t="n">
         <v>66.59999999999999</v>
       </c>
-      <c r="I188" s="46" t="n">
+      <c r="I188" s="47" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="J188" s="46" t="n">
+      <c r="J188" s="47" t="n">
         <v>82.2</v>
       </c>
-      <c r="K188" s="46" t="n">
+      <c r="K188" s="47" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="L188" s="46" t="n">
+      <c r="L188" s="47" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="M188" s="46" t="n">
+      <c r="M188" s="47" t="n">
         <v>103.4</v>
       </c>
-      <c r="N188" s="46" t="n">
+      <c r="N188" s="47" t="n">
         <v>109.9</v>
       </c>
-      <c r="O188" s="46" t="n">
+      <c r="O188" s="47" t="n">
         <v>116.2</v>
       </c>
-      <c r="P188" s="46" t="n">
+      <c r="P188" s="47" t="n">
         <v>122.3</v>
       </c>
-      <c r="Q188" s="46" t="n">
+      <c r="Q188" s="47" t="n">
         <v>128.1</v>
       </c>
-      <c r="R188" s="46" t="n">
+      <c r="R188" s="47" t="n">
         <v>133.8</v>
       </c>
-      <c r="S188" s="46" t="n">
+      <c r="S188" s="47" t="n">
         <v>139.4</v>
       </c>
-      <c r="T188" s="46" t="n">
+      <c r="T188" s="47" t="n">
         <v>144.7</v>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="44" t="n">
+      <c r="A189" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="B189" s="46" t="n">
+      <c r="B189" s="47" t="n">
         <v>10.7</v>
       </c>
-      <c r="C189" s="46" t="n">
+      <c r="C189" s="47" t="n">
         <v>22</v>
       </c>
-      <c r="D189" s="46" t="n">
+      <c r="D189" s="47" t="n">
         <v>33.1</v>
       </c>
-      <c r="E189" s="46" t="n">
+      <c r="E189" s="47" t="n">
         <v>43.7</v>
       </c>
-      <c r="F189" s="46" t="n">
+      <c r="F189" s="47" t="n">
         <v>53.8</v>
       </c>
-      <c r="G189" s="46" t="n">
+      <c r="G189" s="47" t="n">
         <v>63.5</v>
       </c>
-      <c r="H189" s="46" t="n">
+      <c r="H189" s="47" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="I189" s="46" t="n">
+      <c r="I189" s="47" t="n">
         <v>81.3</v>
       </c>
-      <c r="J189" s="46" t="n">
+      <c r="J189" s="47" t="n">
         <v>89.7</v>
       </c>
-      <c r="K189" s="46" t="n">
+      <c r="K189" s="47" t="n">
         <v>97.7</v>
       </c>
-      <c r="L189" s="46" t="n">
+      <c r="L189" s="47" t="n">
         <v>105.4</v>
       </c>
-      <c r="M189" s="46" t="n">
+      <c r="M189" s="47" t="n">
         <v>112.7</v>
       </c>
-      <c r="N189" s="46" t="n">
+      <c r="N189" s="47" t="n">
         <v>119.9</v>
       </c>
-      <c r="O189" s="46" t="n">
+      <c r="O189" s="47" t="n">
         <v>126.7</v>
       </c>
-      <c r="P189" s="46" t="n">
+      <c r="P189" s="47" t="n">
         <v>133.3</v>
       </c>
-      <c r="Q189" s="46" t="n">
+      <c r="Q189" s="47" t="n">
         <v>139.8</v>
       </c>
-      <c r="R189" s="46" t="n">
+      <c r="R189" s="47" t="n">
         <v>146</v>
       </c>
-      <c r="S189" s="46" t="n">
+      <c r="S189" s="47" t="n">
         <v>152</v>
       </c>
-      <c r="T189" s="46" t="n">
+      <c r="T189" s="47" t="n">
         <v>157.9</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="44" t="n">
+      <c r="A190" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="B190" s="46" t="n">
+      <c r="B190" s="47" t="n">
         <v>11.6</v>
       </c>
-      <c r="C190" s="46" t="n">
+      <c r="C190" s="47" t="n">
         <v>23.8</v>
       </c>
-      <c r="D190" s="46" t="n">
+      <c r="D190" s="47" t="n">
         <v>35.8</v>
       </c>
-      <c r="E190" s="46" t="n">
+      <c r="E190" s="47" t="n">
         <v>47.3</v>
       </c>
-      <c r="F190" s="46" t="n">
+      <c r="F190" s="47" t="n">
         <v>58.3</v>
       </c>
-      <c r="G190" s="46" t="n">
+      <c r="G190" s="47" t="n">
         <v>68.7</v>
       </c>
-      <c r="H190" s="46" t="n">
+      <c r="H190" s="47" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="I190" s="46" t="n">
+      <c r="I190" s="47" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="J190" s="46" t="n">
+      <c r="J190" s="47" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="K190" s="46" t="n">
+      <c r="K190" s="47" t="n">
         <v>105.8</v>
       </c>
-      <c r="L190" s="46" t="n">
+      <c r="L190" s="47" t="n">
         <v>114.1</v>
       </c>
-      <c r="M190" s="46" t="n">
+      <c r="M190" s="47" t="n">
         <v>122.1</v>
       </c>
-      <c r="N190" s="46" t="n">
+      <c r="N190" s="47" t="n">
         <v>129.8</v>
       </c>
-      <c r="O190" s="46" t="n">
+      <c r="O190" s="47" t="n">
         <v>137.3</v>
       </c>
-      <c r="P190" s="46" t="n">
+      <c r="P190" s="47" t="n">
         <v>144.4</v>
       </c>
-      <c r="Q190" s="46" t="n">
+      <c r="Q190" s="47" t="n">
         <v>151.4</v>
       </c>
-      <c r="R190" s="46" t="n">
+      <c r="R190" s="47" t="n">
         <v>158.1</v>
       </c>
-      <c r="S190" s="46" t="n">
+      <c r="S190" s="47" t="n">
         <v>164.7</v>
       </c>
-      <c r="T190" s="46" t="n">
+      <c r="T190" s="47" t="n">
         <v>171</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="44" t="n">
+      <c r="A191" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="B191" s="46" t="n">
+      <c r="B191" s="47" t="n">
         <v>12.5</v>
       </c>
-      <c r="C191" s="46" t="n">
+      <c r="C191" s="47" t="n">
         <v>25.7</v>
       </c>
-      <c r="D191" s="46" t="n">
+      <c r="D191" s="47" t="n">
         <v>38.6</v>
       </c>
-      <c r="E191" s="46" t="n">
+      <c r="E191" s="47" t="n">
         <v>51</v>
       </c>
-      <c r="F191" s="46" t="n">
+      <c r="F191" s="47" t="n">
         <v>62.8</v>
       </c>
-      <c r="G191" s="46" t="n">
+      <c r="G191" s="47" t="n">
         <v>74</v>
       </c>
-      <c r="H191" s="46" t="n">
+      <c r="H191" s="47" t="n">
         <v>84.7</v>
       </c>
-      <c r="I191" s="46" t="n">
+      <c r="I191" s="47" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="J191" s="46" t="n">
+      <c r="J191" s="47" t="n">
         <v>104.6</v>
       </c>
-      <c r="K191" s="46" t="n">
+      <c r="K191" s="47" t="n">
         <v>113.9</v>
       </c>
-      <c r="L191" s="46" t="n">
+      <c r="L191" s="47" t="n">
         <v>122.9</v>
       </c>
-      <c r="M191" s="46" t="n">
+      <c r="M191" s="47" t="n">
         <v>131.5</v>
       </c>
-      <c r="N191" s="46" t="n">
+      <c r="N191" s="47" t="n">
         <v>139.8</v>
       </c>
-      <c r="O191" s="46" t="n">
+      <c r="O191" s="47" t="n">
         <v>147.8</v>
       </c>
-      <c r="P191" s="46" t="n">
+      <c r="P191" s="47" t="n">
         <v>155.5</v>
       </c>
-      <c r="Q191" s="46" t="n">
+      <c r="Q191" s="47" t="n">
         <v>163</v>
       </c>
-      <c r="R191" s="46" t="n">
+      <c r="R191" s="47" t="n">
         <v>170.3</v>
       </c>
-      <c r="S191" s="46" t="n">
+      <c r="S191" s="47" t="n">
         <v>177.3</v>
       </c>
-      <c r="T191" s="46" t="n">
+      <c r="T191" s="47" t="n">
         <v>184.2</v>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="44" t="n">
+      <c r="A192" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="B192" s="46" t="n">
+      <c r="B192" s="47" t="n">
         <v>13.4</v>
       </c>
-      <c r="C192" s="46" t="n">
+      <c r="C192" s="47" t="n">
         <v>27.5</v>
       </c>
-      <c r="D192" s="46" t="n">
+      <c r="D192" s="47" t="n">
         <v>41.3</v>
       </c>
-      <c r="E192" s="46" t="n">
+      <c r="E192" s="47" t="n">
         <v>54.6</v>
       </c>
-      <c r="F192" s="46" t="n">
+      <c r="F192" s="47" t="n">
         <v>67.2</v>
       </c>
-      <c r="G192" s="46" t="n">
+      <c r="G192" s="47" t="n">
         <v>79.3</v>
       </c>
-      <c r="H192" s="46" t="n">
+      <c r="H192" s="47" t="n">
         <v>90.7</v>
       </c>
-      <c r="I192" s="46" t="n">
+      <c r="I192" s="47" t="n">
         <v>101.6</v>
       </c>
-      <c r="J192" s="46" t="n">
+      <c r="J192" s="47" t="n">
         <v>112.1</v>
       </c>
-      <c r="K192" s="46" t="n">
+      <c r="K192" s="47" t="n">
         <v>122.1</v>
       </c>
-      <c r="L192" s="46" t="n">
+      <c r="L192" s="47" t="n">
         <v>131.7</v>
       </c>
-      <c r="M192" s="46" t="n">
+      <c r="M192" s="47" t="n">
         <v>140.9</v>
       </c>
-      <c r="N192" s="46" t="n">
+      <c r="N192" s="47" t="n">
         <v>149.8</v>
       </c>
-      <c r="O192" s="46" t="n">
+      <c r="O192" s="47" t="n">
         <v>158.3</v>
       </c>
-      <c r="P192" s="46" t="n">
+      <c r="P192" s="47" t="n">
         <v>166.6</v>
       </c>
-      <c r="Q192" s="46" t="n">
+      <c r="Q192" s="47" t="n">
         <v>174.6</v>
       </c>
-      <c r="R192" s="46" t="n">
+      <c r="R192" s="47" t="n">
         <v>182.4</v>
       </c>
-      <c r="S192" s="46" t="n">
+      <c r="S192" s="47" t="n">
         <v>190</v>
       </c>
-      <c r="T192" s="46" t="n">
+      <c r="T192" s="47" t="n">
         <v>197.3</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="44" t="n">
+      <c r="A193" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="B193" s="46" t="n">
+      <c r="B193" s="47" t="n">
         <v>14.3</v>
       </c>
-      <c r="C193" s="46" t="n">
+      <c r="C193" s="47" t="n">
         <v>29.3</v>
       </c>
-      <c r="D193" s="46" t="n">
+      <c r="D193" s="47" t="n">
         <v>44.1</v>
       </c>
-      <c r="E193" s="46" t="n">
+      <c r="E193" s="47" t="n">
         <v>58.2</v>
       </c>
-      <c r="F193" s="46" t="n">
+      <c r="F193" s="47" t="n">
         <v>71.7</v>
       </c>
-      <c r="G193" s="46" t="n">
+      <c r="G193" s="47" t="n">
         <v>84.5</v>
       </c>
-      <c r="H193" s="46" t="n">
+      <c r="H193" s="47" t="n">
         <v>96.7</v>
       </c>
-      <c r="I193" s="46" t="n">
+      <c r="I193" s="47" t="n">
         <v>108.4</v>
       </c>
-      <c r="J193" s="46" t="n">
+      <c r="J193" s="47" t="n">
         <v>119.5</v>
       </c>
-      <c r="K193" s="46" t="n">
+      <c r="K193" s="47" t="n">
         <v>130.2</v>
       </c>
-      <c r="L193" s="46" t="n">
+      <c r="L193" s="47" t="n">
         <v>140.4</v>
       </c>
-      <c r="M193" s="46" t="n">
+      <c r="M193" s="47" t="n">
         <v>150.2</v>
       </c>
-      <c r="N193" s="46" t="n">
+      <c r="N193" s="47" t="n">
         <v>159.7</v>
       </c>
-      <c r="O193" s="46" t="n">
+      <c r="O193" s="47" t="n">
         <v>168.9</v>
       </c>
-      <c r="P193" s="46" t="n">
+      <c r="P193" s="47" t="n">
         <v>177.7</v>
       </c>
-      <c r="Q193" s="46" t="n">
+      <c r="Q193" s="47" t="n">
         <v>186.3</v>
       </c>
-      <c r="R193" s="46" t="n">
+      <c r="R193" s="47" t="n">
         <v>194.6</v>
       </c>
-      <c r="S193" s="46" t="n">
+      <c r="S193" s="47" t="n">
         <v>202.6</v>
       </c>
-      <c r="T193" s="46" t="n">
+      <c r="T193" s="47" t="n">
         <v>210.4</v>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="44" t="n">
+      <c r="A194" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="B194" s="46" t="n">
+      <c r="B194" s="47" t="n">
         <v>15.1</v>
       </c>
-      <c r="C194" s="46" t="n">
+      <c r="C194" s="47" t="n">
         <v>31.1</v>
       </c>
-      <c r="D194" s="46" t="n">
+      <c r="D194" s="47" t="n">
         <v>46.8</v>
       </c>
-      <c r="E194" s="46" t="n">
+      <c r="E194" s="47" t="n">
         <v>61.8</v>
       </c>
-      <c r="F194" s="46" t="n">
+      <c r="F194" s="47" t="n">
         <v>76.2</v>
       </c>
-      <c r="G194" s="46" t="n">
+      <c r="G194" s="47" t="n">
         <v>89.8</v>
       </c>
-      <c r="H194" s="46" t="n">
+      <c r="H194" s="47" t="n">
         <v>102.8</v>
       </c>
-      <c r="I194" s="46" t="n">
+      <c r="I194" s="47" t="n">
         <v>115.1</v>
       </c>
-      <c r="J194" s="46" t="n">
+      <c r="J194" s="47" t="n">
         <v>127</v>
       </c>
-      <c r="K194" s="46" t="n">
+      <c r="K194" s="47" t="n">
         <v>138.3</v>
       </c>
-      <c r="L194" s="46" t="n">
+      <c r="L194" s="47" t="n">
         <v>149.2</v>
       </c>
-      <c r="M194" s="46" t="n">
+      <c r="M194" s="47" t="n">
         <v>159.6</v>
       </c>
-      <c r="N194" s="46" t="n">
+      <c r="N194" s="47" t="n">
         <v>169.7</v>
       </c>
-      <c r="O194" s="46" t="n">
+      <c r="O194" s="47" t="n">
         <v>179.4</v>
       </c>
-      <c r="P194" s="46" t="n">
+      <c r="P194" s="47" t="n">
         <v>188.8</v>
       </c>
-      <c r="Q194" s="46" t="n">
+      <c r="Q194" s="47" t="n">
         <v>197.9</v>
       </c>
-      <c r="R194" s="46" t="n">
+      <c r="R194" s="47" t="n">
         <v>206.7</v>
       </c>
-      <c r="S194" s="46" t="n">
+      <c r="S194" s="47" t="n">
         <v>215.2</v>
       </c>
-      <c r="T194" s="46" t="n">
+      <c r="T194" s="47" t="n">
         <v>223.6</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="44" t="n">
+      <c r="A195" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="B195" s="46" t="n">
+      <c r="B195" s="47" t="n">
         <v>16</v>
       </c>
-      <c r="C195" s="46" t="n">
+      <c r="C195" s="47" t="n">
         <v>32.9</v>
       </c>
-      <c r="D195" s="46" t="n">
+      <c r="D195" s="47" t="n">
         <v>49.5</v>
       </c>
-      <c r="E195" s="46" t="n">
+      <c r="E195" s="47" t="n">
         <v>65.5</v>
       </c>
-      <c r="F195" s="46" t="n">
+      <c r="F195" s="47" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="G195" s="46" t="n">
+      <c r="G195" s="47" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="H195" s="46" t="n">
+      <c r="H195" s="47" t="n">
         <v>108.8</v>
       </c>
-      <c r="I195" s="46" t="n">
+      <c r="I195" s="47" t="n">
         <v>121.9</v>
       </c>
-      <c r="J195" s="46" t="n">
+      <c r="J195" s="47" t="n">
         <v>134.4</v>
       </c>
-      <c r="K195" s="46" t="n">
+      <c r="K195" s="47" t="n">
         <v>146.4</v>
       </c>
-      <c r="L195" s="46" t="n">
+      <c r="L195" s="47" t="n">
         <v>157.9</v>
       </c>
-      <c r="M195" s="46" t="n">
+      <c r="M195" s="47" t="n">
         <v>169</v>
       </c>
-      <c r="N195" s="46" t="n">
+      <c r="N195" s="47" t="n">
         <v>179.7</v>
       </c>
-      <c r="O195" s="46" t="n">
+      <c r="O195" s="47" t="n">
         <v>190</v>
       </c>
-      <c r="P195" s="46" t="n">
+      <c r="P195" s="47" t="n">
         <v>199.9</v>
       </c>
-      <c r="Q195" s="46" t="n">
+      <c r="Q195" s="47" t="n">
         <v>209.5</v>
       </c>
-      <c r="R195" s="46" t="n">
+      <c r="R195" s="47" t="n">
         <v>218.8</v>
       </c>
-      <c r="S195" s="46" t="n">
+      <c r="S195" s="47" t="n">
         <v>227.9</v>
       </c>
-      <c r="T195" s="46" t="n">
+      <c r="T195" s="47" t="n">
         <v>236.7</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="44" t="n">
+      <c r="A196" s="45" t="n">
         <v>19</v>
       </c>
-      <c r="B196" s="46" t="n">
+      <c r="B196" s="47" t="n">
         <v>16.9</v>
       </c>
-      <c r="C196" s="46" t="n">
+      <c r="C196" s="47" t="n">
         <v>34.7</v>
       </c>
-      <c r="D196" s="46" t="n">
+      <c r="D196" s="47" t="n">
         <v>52.3</v>
       </c>
-      <c r="E196" s="46" t="n">
+      <c r="E196" s="47" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="F196" s="46" t="n">
+      <c r="F196" s="47" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="G196" s="46" t="n">
+      <c r="G196" s="47" t="n">
         <v>100.3</v>
       </c>
-      <c r="H196" s="46" t="n">
+      <c r="H196" s="47" t="n">
         <v>114.8</v>
       </c>
-      <c r="I196" s="46" t="n">
+      <c r="I196" s="47" t="n">
         <v>128.7</v>
       </c>
-      <c r="J196" s="46" t="n">
+      <c r="J196" s="47" t="n">
         <v>141.9</v>
       </c>
-      <c r="K196" s="46" t="n">
+      <c r="K196" s="47" t="n">
         <v>154.5</v>
       </c>
-      <c r="L196" s="46" t="n">
+      <c r="L196" s="47" t="n">
         <v>166.7</v>
       </c>
-      <c r="M196" s="46" t="n">
+      <c r="M196" s="47" t="n">
         <v>178.4</v>
       </c>
-      <c r="N196" s="46" t="n">
+      <c r="N196" s="47" t="n">
         <v>189.6</v>
       </c>
-      <c r="O196" s="46" t="n">
+      <c r="O196" s="47" t="n">
         <v>200.5</v>
       </c>
-      <c r="P196" s="46" t="n">
+      <c r="P196" s="47" t="n">
         <v>211</v>
       </c>
-      <c r="Q196" s="46" t="n">
+      <c r="Q196" s="47" t="n">
         <v>221.1</v>
       </c>
-      <c r="R196" s="46" t="n">
+      <c r="R196" s="47" t="n">
         <v>231</v>
       </c>
-      <c r="S196" s="46" t="n">
+      <c r="S196" s="47" t="n">
         <v>240.5</v>
       </c>
-      <c r="T196" s="46" t="n">
+      <c r="T196" s="47" t="n">
         <v>249.8</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="44" t="n">
+      <c r="A197" s="45" t="n">
         <v>20</v>
       </c>
-      <c r="B197" s="46" t="n">
+      <c r="B197" s="47" t="n">
         <v>17.8</v>
       </c>
-      <c r="C197" s="46" t="n">
+      <c r="C197" s="47" t="n">
         <v>36.5</v>
       </c>
-      <c r="D197" s="46" t="n">
+      <c r="D197" s="47" t="n">
         <v>55</v>
       </c>
-      <c r="E197" s="46" t="n">
+      <c r="E197" s="47" t="n">
         <v>72.7</v>
       </c>
-      <c r="F197" s="46" t="n">
+      <c r="F197" s="47" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="G197" s="46" t="n">
+      <c r="G197" s="47" t="n">
         <v>105.6</v>
       </c>
-      <c r="H197" s="46" t="n">
+      <c r="H197" s="47" t="n">
         <v>120.9</v>
       </c>
-      <c r="I197" s="46" t="n">
+      <c r="I197" s="47" t="n">
         <v>135.4</v>
       </c>
-      <c r="J197" s="46" t="n">
+      <c r="J197" s="47" t="n">
         <v>149.3</v>
       </c>
-      <c r="K197" s="46" t="n">
+      <c r="K197" s="47" t="n">
         <v>162.7</v>
       </c>
-      <c r="L197" s="46" t="n">
+      <c r="L197" s="47" t="n">
         <v>175.5</v>
       </c>
-      <c r="M197" s="46" t="n">
+      <c r="M197" s="47" t="n">
         <v>187.8</v>
       </c>
-      <c r="N197" s="46" t="n">
+      <c r="N197" s="47" t="n">
         <v>199.6</v>
       </c>
-      <c r="O197" s="46" t="n">
+      <c r="O197" s="47" t="n">
         <v>211</v>
       </c>
-      <c r="P197" s="46" t="n">
+      <c r="P197" s="47" t="n">
         <v>222.1</v>
       </c>
-      <c r="Q197" s="46" t="n">
+      <c r="Q197" s="47" t="n">
         <v>232.8</v>
       </c>
-      <c r="R197" s="46" t="n">
+      <c r="R197" s="47" t="n">
         <v>243.1</v>
       </c>
-      <c r="S197" s="46" t="n">
+      <c r="S197" s="47" t="n">
         <v>253.2</v>
       </c>
-      <c r="T197" s="46" t="n">
+      <c r="T197" s="47" t="n">
         <v>263</v>
       </c>
     </row>
@@ -8876,61 +10501,61 @@
           <t>d2 (g → ∞)</t>
         </is>
       </c>
-      <c r="B199" s="45" t="n">
+      <c r="B199" s="46" t="n">
         <v>1.12838</v>
       </c>
-      <c r="C199" s="45" t="n">
+      <c r="C199" s="46" t="n">
         <v>1.69257</v>
       </c>
-      <c r="D199" s="45" t="n">
+      <c r="D199" s="46" t="n">
         <v>2.05875</v>
       </c>
-      <c r="E199" s="45" t="n">
+      <c r="E199" s="46" t="n">
         <v>2.32593</v>
       </c>
-      <c r="F199" s="45" t="n">
+      <c r="F199" s="46" t="n">
         <v>2.53441</v>
       </c>
-      <c r="G199" s="45" t="n">
+      <c r="G199" s="46" t="n">
         <v>2.70436</v>
       </c>
-      <c r="H199" s="40" t="n">
+      <c r="H199" s="41" t="n">
         <v>2.8472</v>
       </c>
-      <c r="I199" s="45" t="n">
+      <c r="I199" s="46" t="n">
         <v>2.97003</v>
       </c>
-      <c r="J199" s="45" t="n">
+      <c r="J199" s="46" t="n">
         <v>3.07751</v>
       </c>
-      <c r="K199" s="45" t="n">
+      <c r="K199" s="46" t="n">
         <v>3.17287</v>
       </c>
-      <c r="L199" s="45" t="n">
+      <c r="L199" s="46" t="n">
         <v>3.25846</v>
       </c>
-      <c r="M199" s="45" t="n">
+      <c r="M199" s="46" t="n">
         <v>3.33598</v>
       </c>
-      <c r="N199" s="45" t="n">
+      <c r="N199" s="46" t="n">
         <v>3.40676</v>
       </c>
-      <c r="O199" s="45" t="n">
+      <c r="O199" s="46" t="n">
         <v>3.47193</v>
       </c>
-      <c r="P199" s="45" t="n">
+      <c r="P199" s="46" t="n">
         <v>3.53198</v>
       </c>
-      <c r="Q199" s="45" t="n">
+      <c r="Q199" s="46" t="n">
         <v>3.58788</v>
       </c>
-      <c r="R199" s="45" t="n">
+      <c r="R199" s="46" t="n">
         <v>3.64006</v>
       </c>
-      <c r="S199" s="45" t="n">
+      <c r="S199" s="46" t="n">
         <v>3.68896</v>
       </c>
-      <c r="T199" s="39" t="n">
+      <c r="T199" s="40" t="n">
         <v>3.735</v>
       </c>
     </row>
@@ -8940,61 +10565,61 @@
           <t>cd</t>
         </is>
       </c>
-      <c r="B200" s="39" t="n">
+      <c r="B200" s="40" t="n">
         <v>0.876</v>
       </c>
-      <c r="C200" s="39" t="n">
+      <c r="C200" s="40" t="n">
         <v>1.815</v>
       </c>
-      <c r="D200" s="40" t="n">
+      <c r="D200" s="41" t="n">
         <v>2.7378</v>
       </c>
-      <c r="E200" s="39" t="n">
+      <c r="E200" s="40" t="n">
         <v>3.623</v>
       </c>
-      <c r="F200" s="40" t="n">
+      <c r="F200" s="41" t="n">
         <v>4.4658</v>
       </c>
-      <c r="G200" s="40" t="n">
+      <c r="G200" s="41" t="n">
         <v>5.2673</v>
       </c>
-      <c r="H200" s="40" t="n">
+      <c r="H200" s="41" t="n">
         <v>6.0305</v>
       </c>
-      <c r="I200" s="40" t="n">
+      <c r="I200" s="41" t="n">
         <v>6.7582</v>
       </c>
-      <c r="J200" s="40" t="n">
+      <c r="J200" s="41" t="n">
         <v>7.4539</v>
       </c>
-      <c r="K200" s="40" t="n">
+      <c r="K200" s="41" t="n">
         <v>8.120699999999999</v>
       </c>
-      <c r="L200" s="40" t="n">
+      <c r="L200" s="41" t="n">
         <v>8.760199999999999</v>
       </c>
-      <c r="M200" s="40" t="n">
+      <c r="M200" s="41" t="n">
         <v>9.3751</v>
       </c>
-      <c r="N200" s="40" t="n">
+      <c r="N200" s="41" t="n">
         <v>9.9679</v>
       </c>
-      <c r="O200" s="40" t="n">
+      <c r="O200" s="41" t="n">
         <v>10.5396</v>
       </c>
-      <c r="P200" s="40" t="n">
+      <c r="P200" s="41" t="n">
         <v>11.0913</v>
       </c>
-      <c r="Q200" s="40" t="n">
+      <c r="Q200" s="41" t="n">
         <v>11.6259</v>
       </c>
-      <c r="R200" s="39" t="n">
+      <c r="R200" s="40" t="n">
         <v>12.144</v>
       </c>
-      <c r="S200" s="40" t="n">
+      <c r="S200" s="41" t="n">
         <v>12.6468</v>
       </c>
-      <c r="T200" s="40" t="n">
+      <c r="T200" s="41" t="n">
         <v>13.1362</v>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 18-20, 32-46, 64; Six Sigma For Dummies.pdf p. 114-116, 159-165; ___4.1 tabellen SPC.pdf p. 1-2</t>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 18-21, 32-47, 50, 64, 83; Six Sigma For Dummies.pdf p. 114-116, 159-165; ___4.1 tabellen SPC.pdf p. 1-2</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S06-WE01, S06-WE02, S06-WE04, S06-WE07, S06-WE08, S06-WE12, S06-WE13; a few printed values on deck p. 46 and 49 disagree with the computation (listed in build/README.md)</t>
+          <t>VERIFIED: tested against course worked examples S06-WE01, S06-WE02, S06-WE04, S06-WE07, S06-WE08, S06-WE12, S06-WE13; a few printed values on deck p. 46 and 50 disagree with the computation (listed in build/README.md)</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Cp level (deck p. 39)</t>
+          <t>Cp level (deck p. 40)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1536,7 +1536,7 @@
         <v/>
       </c>
       <c r="D23" s="13">
-        <f>IF(ISNUMBER(C23),IF(C23&gt;=$B$43,"6 Sigma kwaliteitsniveau",IF(C23&gt;=$B$42,"goed",IF(C23&gt;=$B$41,"acceptabel",IF(C23&gt;=$B$40,"net capabel","niet capabel")))),"")</f>
+        <f>IF(ISNUMBER(C23),IF(C23&gt;=$B$43,"6 Sigma quality level",IF(C23&gt;=$B$42,"good",IF(C23&gt;=$B$41,"acceptable",IF(C23&gt;=$B$40,"just capable","not capable")))),"")</f>
         <v/>
       </c>
       <c r="E23" s="12">
@@ -1601,7 +1601,7 @@
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>IF(ISNUMBER(C24),IF(C24&gt;=$B$43,"6 Sigma kwaliteitsniveau",IF(C24&gt;=$B$42,"goed",IF(C24&gt;=$B$41,"acceptabel",IF(C24&gt;=$B$40,"net capabel","niet capabel")))),"")</f>
+        <f>IF(ISNUMBER(C24),IF(C24&gt;=$B$43,"6 Sigma quality level",IF(C24&gt;=$B$42,"good",IF(C24&gt;=$B$41,"acceptable",IF(C24&gt;=$B$40,"just capable","not capable")))),"")</f>
         <v/>
       </c>
       <c r="E24" s="12">
@@ -1674,7 +1674,7 @@
         <v/>
       </c>
       <c r="D25" s="13">
-        <f>IF(ISNUMBER(C25),IF(C25&gt;=$B$43,"6 Sigma kwaliteitsniveau",IF(C25&gt;=$B$42,"goed",IF(C25&gt;=$B$41,"acceptabel",IF(C25&gt;=$B$40,"net capabel","niet capabel")))),"")</f>
+        <f>IF(ISNUMBER(C25),IF(C25&gt;=$B$43,"6 Sigma quality level",IF(C25&gt;=$B$42,"good",IF(C25&gt;=$B$41,"acceptable",IF(C25&gt;=$B$40,"just capable","not capable")))),"")</f>
         <v/>
       </c>
       <c r="E25" s="12">
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="D26" s="13">
-        <f>IF(ISNUMBER(C26),IF(C26&gt;=$B$43,"6 Sigma kwaliteitsniveau",IF(C26&gt;=$B$42,"goed",IF(C26&gt;=$B$41,"acceptabel",IF(C26&gt;=$B$40,"net capabel","niet capabel")))),"")</f>
+        <f>IF(ISNUMBER(C26),IF(C26&gt;=$B$43,"6 Sigma quality level",IF(C26&gt;=$B$42,"good",IF(C26&gt;=$B$41,"acceptable",IF(C26&gt;=$B$40,"just capable","not capable")))),"")</f>
         <v/>
       </c>
       <c r="E26" s="12">
@@ -1812,7 +1812,7 @@
         <v/>
       </c>
       <c r="D27" s="13">
-        <f>IF(ISNUMBER(C27),IF(C27&gt;=$B$43,"6 Sigma kwaliteitsniveau",IF(C27&gt;=$B$42,"goed",IF(C27&gt;=$B$41,"acceptabel",IF(C27&gt;=$B$40,"net capabel","niet capabel")))),"")</f>
+        <f>IF(ISNUMBER(C27),IF(C27&gt;=$B$43,"6 Sigma quality level",IF(C27&gt;=$B$42,"good",IF(C27&gt;=$B$41,"acceptable",IF(C27&gt;=$B$40,"just capable","not capable")))),"")</f>
         <v/>
       </c>
       <c r="E27" s="12">
@@ -1885,7 +1885,7 @@
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>IF(ISNUMBER(C28),IF(C28&gt;=$B$43,"6 Sigma kwaliteitsniveau",IF(C28&gt;=$B$42,"goed",IF(C28&gt;=$B$41,"acceptabel",IF(C28&gt;=$B$40,"net capabel","niet capabel")))),"")</f>
+        <f>IF(ISNUMBER(C28),IF(C28&gt;=$B$43,"6 Sigma quality level",IF(C28&gt;=$B$42,"good",IF(C28&gt;=$B$41,"acceptable",IF(C28&gt;=$B$40,"just capable","not capable")))),"")</f>
         <v/>
       </c>
       <c r="E28" s="12">
@@ -1931,7 +1931,7 @@
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>deck p. 32; Six Sigma For Dummies.pdf p. 164-165</t>
+          <t>deck p. 33; Six Sigma For Dummies.pdf p. 164-165</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>deck p. 20 (table: 6 -&gt; 3.4 DPMO), 36-37 (notes); Dummies p. 27, 159-160; Harry &amp; Schroeder summary p. 2 (3.4 dpm)</t>
+          <t>deck p. 21 (table: 6 -&gt; 3.4 DPMO), 37 (+ notes); Dummies p. 27, 159-160; Harry &amp; Schroeder summary p. 2 (3.4 dpm)</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39: 'Cp = 2: 6 Sigma kwaliteitsniveau - 2 defect per miljard' (short term)</t>
+          <t>deck p. 40: 'CP = 2  6 Sigma quality level – 2 defect per billion of opportunities (short term)'</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>deck p. 36; Dummies p. 159 ('Zlt = Zst - 1.5')</t>
+          <t>deck p. 37; Dummies p. 159 ('Zlt = Zst - 1.5')</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39 (Cp = 2: 6 Sigma kwaliteitsniveau)</t>
+          <t>deck p. 40 (CP = 2: 6 Sigma quality level)</t>
         </is>
       </c>
     </row>
@@ -2057,14 +2057,14 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Cp &lt; 1: niet capabel</t>
+          <t>CP &lt; 1: the process is not capable</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Cp ≥ this: net capabel</t>
+          <t>Cp ≥ this: just capable</t>
         </is>
       </c>
       <c r="B40" s="19" t="n">
@@ -2072,14 +2072,14 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39 ('Cp=1: net capabel')</t>
+          <t>deck p. 40 ('CP = 1 The process is just capable')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Cp ≥ this: acceptabel</t>
+          <t>Cp ≥ this: acceptable</t>
         </is>
       </c>
       <c r="B41" s="19" t="n">
@@ -2087,14 +2087,14 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39 ('Cp&gt;=1,33: acceptabel')</t>
+          <t>deck p. 40 ('CP &gt;= 1.33 The capability of the process is acceptable')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Cp ≥ this: goed</t>
+          <t>Cp ≥ this: good</t>
         </is>
       </c>
       <c r="B42" s="19" t="n">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39 ('Cp&gt;=1,67: goed')</t>
+          <t>deck p. 40 ('CP &gt;= 1.67 The capability of the process is good')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Cp ≥ this: 6 Sigma kwaliteitsniveau</t>
+          <t>Cp ≥ this: 6 Sigma quality level</t>
         </is>
       </c>
       <c r="B43" s="19" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39 ('Cp=2: 6 Sigma kwaliteitsniveau')</t>
+          <t>deck p. 40 ('CP = 2 6 Sigma quality level')</t>
         </is>
       </c>
     </row>
@@ -2146,14 +2146,14 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Centre the process (mean to the middle of LSL and USL): Cpk rises to Cp. Deck p. 35, 41-44, 46.</t>
+          <t>Centre the process (mean to the middle of LSL and USL): Cpk rises to Cp. Deck p. 36, 42-45, 46.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Reduce the variation (σ): Cp and Cpk both rise. Deck p. 21-22, 35; Dummies p. 165-166.</t>
+          <t>Reduce the variation (σ): Cp and Cpk both rise. Deck p. 22, 36; Dummies p. 165-166.</t>
         </is>
       </c>
     </row>
@@ -20319,7 +20319,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 16-19, 26; ___1.1 Ztable.pdf; ___1.2 statistische functionaliteit in excel.pdf p. 1-3; __NormVerdeling Excel functies.xlsx</t>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 16-19, 27; ___1.1 Ztable.pdf; ___1.2 statistische functionaliteit in excel.pdf p. 1-3; __NormVerdeling Excel functies.xlsx</t>
         </is>
       </c>
     </row>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S06-WE09 (NORM.INV / NORM.VERD workbook) and S06-WE10 (deck p. 19 notes), the 68-95-99.7 rule (deck p. 18) and the course Z table</t>
+          <t>VERIFIED: tested against course worked examples S06-WE09 (NORM.INV / NORM.VERD workbook) and S06-WE10 (deck p. 19 notes), the 68-95-99.7 rule (deck p. 19) and the course Z table</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>deck p. 18; Excel NORMALISEREN (STANDARDIZE)</t>
+          <t>deck p. 19; Excel NORMALISEREN (STANDARDIZE)</t>
         </is>
       </c>
     </row>
@@ -20673,7 +20673,7 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>6. The 68 - 95 - 99.7 rule (deck p. 18)</t>
+          <t>6. The 68 - 95 - 99.7 rule (deck p. 19)</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>deck p. 18: ≈ 68 %</t>
+          <t>deck p. 19: ≈ 68 %</t>
         </is>
       </c>
     </row>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>deck p. 18: ≈ 95 %</t>
+          <t>deck p. 19: ≈ 95 %</t>
         </is>
       </c>
     </row>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>deck p. 18: ≈ 99.7 %</t>
+          <t>deck p. 19: ≈ 99.7 %</t>
         </is>
       </c>
     </row>
@@ -20898,7 +20898,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 19-20, 36-39; Six Sigma For Dummies.pdf p. 42, 147-161; Six-Sigma Mikel Harry - Richard Schroeder.pdf p. 3-5; 20260521_van volsem.pdf p. 7</t>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 20-21, 37-40; Six Sigma For Dummies.pdf p. 42, 147-161; Six-Sigma Mikel Harry - Richard Schroeder.pdf p. 3-5; 20260521_van volsem.pdf p. 7</t>
         </is>
       </c>
     </row>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>deck p. 19; Dummies p. 153</t>
+          <t>deck p. 20; Dummies p. 153</t>
         </is>
       </c>
     </row>
@@ -21035,7 +21035,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>deck p. 19; Dummies p. 155</t>
+          <t>deck p. 20; Dummies p. 155</t>
         </is>
       </c>
     </row>
@@ -21051,7 +21051,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>deck p. 19</t>
+          <t>deck p. 20</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>deck p. 20; Dummies Table 6-3 p. 160 ('long-term DPMO, short-term Z'); Harry &amp; Schroeder p. 5</t>
+          <t>deck p. 21; Dummies Table 6-3 p. 160 ('long-term DPMO, short-term Z'); Harry &amp; Schroeder p. 5</t>
         </is>
       </c>
     </row>
@@ -21193,7 +21193,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>deck p. 20; Dummies p. 42, 160; Van Volsem p. 7: 6 -&gt; 3.4</t>
+          <t>deck p. 21; Dummies p. 42, 160; Van Volsem p. 7: 6 -&gt; 3.4</t>
         </is>
       </c>
     </row>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>deck p. 39: Cp = 2 (Z = 6) -&gt; 2 per billion</t>
+          <t>deck p. 40: CP = 2 (Z = 6) -&gt; 2 defect per billion</t>
         </is>
       </c>
     </row>
@@ -21236,7 +21236,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>deck p. 20; Van Volsem p. 7</t>
+          <t>deck p. 21; Van Volsem p. 7</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21729,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>deck p. 36; Dummies p. 159-160 ('Zlt = Zst - 1.5')</t>
+          <t>deck p. 37; Dummies p. 159-160 ('Zlt = Zst - 1.5')</t>
         </is>
       </c>
     </row>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: binomial and hypergeometric blocks tested against course worked examples S04-WE02, S03-WE19, S03-WE21; Bernoulli, Poisson, exponential and uniform blocks have no course example (audited)</t>
+          <t>VERIFIED: binomial and hypergeometric blocks tested against course worked examples S04-WE02, S03-WE19, S03-WE21, the Poisson block against S02-WE09; Bernoulli, Poisson, exponential and uniform use standard definitions not printed in the course (decision 20; audited)</t>
         </is>
       </c>
     </row>
@@ -25709,7 +25709,7 @@
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
-          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+          <t>standard definition, not printed in the course (decision 20); no course worked example (checked by the stats-auditor, build/README.md)</t>
         </is>
       </c>
     </row>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
-          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+          <t>standard definition, not printed in the course (decision 20); course example Naert Les 1 p. 9-10 (λ = 2.959) tested</t>
         </is>
       </c>
     </row>
@@ -25990,7 +25990,7 @@
       <c r="B36" s="7" t="n"/>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Naert Les 1 p. 9: λ = 2.959 customers / minute</t>
+          <t>Naert Les 1 p. 9-10: λ = 2.959 customers / minute</t>
         </is>
       </c>
     </row>
@@ -26014,7 +26014,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Naert Les 1 p. 7-9 (Poisson for counts)</t>
+          <t>Naert Les 1 p. 7-9 names Poisson for counts</t>
         </is>
       </c>
     </row>
@@ -26075,7 +26075,7 @@
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+          <t>standard definition, not printed in the course (decision 20); no course worked example (checked by the stats-auditor, build/README.md)</t>
         </is>
       </c>
     </row>
@@ -26112,7 +26112,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Naert Les 1 p. 7 (exponential for waiting times)</t>
+          <t>Naert Les 1 p. 7 names exponential for waiting times</t>
         </is>
       </c>
     </row>
@@ -26139,7 +26139,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Excel EXPON.DIST(t; λ; WAAR) (Acceptance Sampling.xlsm 'distributions')</t>
+          <t>Excel EXPON.DIST(t; λ; WAAR); the course workbook uses EXPON.DIST with a rate (Acceptance Sampling.xlsm)</t>
         </is>
       </c>
     </row>
@@ -26162,7 +26162,7 @@
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
-          <t>no course worked example for this block (checked by the stats-auditor, build/README.md)</t>
+          <t>standard definition, not printed in the course (decision 20); no course worked example (checked by the stats-auditor, build/README.md)</t>
         </is>
       </c>
     </row>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Acceptance Sampling.xlsm 'distributions'</t>
+          <t>Acceptance Sampling.xlsm 'distributions' (uniform density on [1, 2])</t>
         </is>
       </c>
     </row>
@@ -32053,7 +32053,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 55, 62-73; ___4.1 tabellen SPC.pdf p. 1-2; Six Sigma For Dummies.pdf p. 239-256; Les 5/20260619_ottoy_Rheostat Knob Data.xls</t>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 54-58, 62-74; ___4.1 tabellen SPC.pdf p. 1-2; Six Sigma For Dummies.pdf p. 239-256; Les 5/20260619_ottoy_Rheostat Knob Data.xls</t>
         </is>
       </c>
     </row>
@@ -32161,7 +32161,7 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>IF(COUNT(O30:O79)&gt;0,IF(MIN(O30:O79)=MAX(O30:O79),"yes","NO: limits use the largest n (deck p. 73: variable sample size)"),"")</f>
+        <f>IF(COUNT(O30:O79)&gt;0,IF(MIN(O30:O79)=MAX(O30:O79),"yes","NO: limits use the largest n (deck p. 74: variable sample size)"),"")</f>
         <v/>
       </c>
     </row>
@@ -32325,7 +32325,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>deck p. 73; Dummies p. 249</t>
+          <t>deck p. 74; Dummies p. 249</t>
         </is>
       </c>
     </row>
@@ -32362,7 +32362,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>deck p. 73</t>
+          <t>deck p. 74</t>
         </is>
       </c>
     </row>
@@ -32395,7 +32395,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>deck p. 73 (preferred for n &gt; 10)</t>
+          <t>deck p. 74; notes p. 73: s preferred for n &gt; 10</t>
         </is>
       </c>
     </row>
@@ -32432,7 +32432,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>deck p. 73</t>
+          <t>deck p. 74</t>
         </is>
       </c>
     </row>
@@ -39528,7 +39528,7 @@
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
         <is>
-          <t>5. Reading the chart: Western Electric rules (deck p. 67-68)</t>
+          <t>5. Reading the chart: Western Electric rules (deck p. 68-69)</t>
         </is>
       </c>
     </row>
@@ -39563,7 +39563,7 @@
     <row r="316">
       <c r="A316" s="8" t="inlineStr">
         <is>
-          <t>More sensitizing rules, zones A/B/C and tampering vs. under-reacting: deck p. 64-69; Dummies p. 245-247.</t>
+          <t>More sensitizing rules, zones A/B/C and tampering vs. under-reacting: deck p. 65-70; Dummies p. 245-247.</t>
         </is>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -20898,7 +20898,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 20-21, 37-40; Six Sigma For Dummies.pdf p. 42, 147-161; Six-Sigma Mikel Harry - Richard Schroeder.pdf p. 3-5; 20260521_van volsem.pdf p. 7</t>
+          <t>source/course/Les 4/2026 Lean - Six Sigma v13 - Capabiliteit - SPC.pdf p. 20-21, 37-40; Six Sigma For Dummies.pdf p. 41, 147-161; Six-Sigma Mikel Harry - Richard Schroeder.pdf p. 3-5; 20260521_van volsem.pdf p. 7</t>
         </is>
       </c>
     </row>
@@ -21193,7 +21193,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>deck p. 21; Dummies p. 42, 160; Van Volsem p. 7: 6 -&gt; 3.4</t>
+          <t>deck p. 21; Dummies p. 41, 160; Van Volsem p. 7: 6 -&gt; 3.4</t>
         </is>
       </c>
     </row>
@@ -41091,7 +41091,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Other course thresholds: 'Gauge R&amp;R ≤ 20 % of tolerance' (deck Les 4 p. 60); σ²_measure / σ²_observed ≤ 0.1 good, 0.1-0.3 marginal, ≥ 0.3 unacceptable (Dummies p. 178).</t>
+          <t>Other course thresholds: 'Gauge R&amp;R ≤ 20 % of tolerance' (deck Les 4 p. 61); σ²_measure / σ²_observed ≤ 0.1 good, 0.1-0.3 marginal, ≥ 0.3 unacceptable (Dummies p. 178).</t>
         </is>
       </c>
     </row>

--- a/build/bb_toolkit.xlsx
+++ b/build/bb_toolkit.xlsx
@@ -1235,7 +1235,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1264,31 +1264,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S06-WE01, S06-WE02, S06-WE04, S06-WE07, S06-WE08, S06-WE12, S06-WE13; a few printed values on deck p. 46 and 50 disagree with the computation (listed in build/README.md)</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S06-WE01, S06-WE02, S06-WE04, S06-WE07, S06-WE08, S06-WE12, S06-WE13; a few printed values on deck p. 46 and 50 disagree with the computation (listed in build/README.md)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2227,31 +2227,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S03-WE06, S03-WE07, S03-WE20, S03-WE21, S04-WE12, S04-WE16, S04-WE18</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S03-WE06, S03-WE07, S03-WE20, S03-WE21, S04-WE12, S04-WE16, S04-WE18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3873,7 +3873,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3890,31 +3890,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S05-WE01, S05-WE02, S05-WE05 to S05-WE09, S05-WE17, S05-WE18, S08-WE16; printed values that disagree are listed in build/README.md</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S05-WE01, S05-WE02, S05-WE05 to S05-WE09, S05-WE17, S05-WE18, S08-WE16; printed values that disagree are listed in build/README.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13487,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -13499,7 +13499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -13516,31 +13516,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: transcriptions of both scanned tables double-checked cell by cell; values compared with their mathematical definitions in tests/test_constants.py</t>
+          <t>GEVERIFIEERD (VERIFIED): transcriptions of both scanned tables double-checked cell by cell; values compared with their mathematical definitions in tests/test_constants.py</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -20314,7 +20314,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -20326,7 +20326,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -20343,31 +20343,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S06-WE09 (NORM.INV / NORM.VERD workbook) and S06-WE10 (deck p. 19 notes), the 68-95-99.7 rule (deck p. 19) and the course Z table</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S06-WE09 (NORM.INV / NORM.VERD workbook) and S06-WE10 (deck p. 19 notes), the 68-95-99.7 rule (deck p. 19) and the course Z table</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -20905,7 +20905,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -20922,31 +20922,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S07-WE01, S08-WE01 to S08-WE08, S09-WE01, S09-WE03 to S09-WE06 and the course sigma tables; a few printed values disagree (listed in build/README.md)</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S07-WE01, S08-WE01 to S08-WE08, S09-WE01, S09-WE03 to S09-WE06 and the course sigma tables; a few printed values disagree (listed in build/README.md)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -21774,7 +21774,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -21786,7 +21786,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -21803,31 +21803,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S03-WE03, S03-WE05, S08-WE10 and the Dummies χ² and F tables (p. 194, 196); the Dummies F-interval example S08-WE11 disagrees (build/README.md)</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S03-WE03, S03-WE05, S08-WE10 and the Dummies χ² and F tables (p. 194, 196); the Dummies F-interval example S08-WE11 disagrees (build/README.md)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -24542,7 +24542,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -24554,7 +24554,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -24571,31 +24571,31 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>UNVERIFIED: no course worked example prints these metrics; checked against an independent computation and by the stats-auditor (build/README.md)</t>
+          <t>NIET GEVERIFIEERD (UNVERIFIED): no course worked example prints these metrics; checked against an independent computation and by the stats-auditor (build/README.md)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -25644,7 +25644,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -25656,7 +25656,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -25673,31 +25673,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: binomial and hypergeometric blocks tested against course worked examples S04-WE02, S03-WE19, S03-WE21, the Poisson block against S02-WE09; Bernoulli, Poisson, exponential and uniform use standard definitions not printed in the course (decision 20; audited)</t>
+          <t>GEVERIFIEERD (VERIFIED): binomial and hypergeometric blocks tested against course worked examples S04-WE02, S03-WE19, S03-WE21, the Poisson block against S02-WE09; Bernoulli, Poisson, exponential and uniform use standard definitions not printed in the course (decision 20; audited)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -26282,7 +26282,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -26294,7 +26294,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -26311,31 +26311,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S03-WE01, S03-WE02, S03-WE04, S03-WE10, S03-WE13, S03-WE14, S03-WE15, S08-WE12, S08-WE13</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S03-WE01, S03-WE02, S03-WE04, S03-WE10, S03-WE13, S03-WE14, S03-WE15, S08-WE12, S08-WE13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -32048,7 +32048,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -32060,7 +32060,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -32077,31 +32077,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S06-WE03, S06-WE05, S06-WE06, S08-WE18, S08-WE21, S10-WE04a, S10-WE04b; a few printed values disagree (build/README.md)</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S06-WE03, S06-WE05, S06-WE06, S08-WE18, S08-WE21, S10-WE04a, S10-WE04b; a few printed values disagree (build/README.md)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
@@ -39611,7 +39611,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Course source</t>
+          <t>Bron in de cursus</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -39623,7 +39623,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Convention used</t>
+          <t>Gebruikte conventie</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -39640,31 +39640,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>VERIFIED: tested against course worked examples S10-WE02 (ANOVA) and S10-WE03 (average and range) on the course's own study data</t>
+          <t>GEVERIFIEERD (VERIFIED): tested against course worked examples S10-WE02 (ANOVA) and S10-WE03 (average and range) on the course's own study data</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Legende</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yellow cell = type your input here.  Green cell = result, do not type.  Orange cell (Tables) = disagrees with another printed source.</t>
+          <t>Gele cel = vul hier in (invoer).  Groene cel = resultaat, niet overtypen.  Oranje cel (Tabellen) = verschilt van een andere gedrukte bron.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>If a green cell shows nothing, an input it needs is still empty.</t>
+          <t>Blijft een groene cel leeg, dan ontbreekt nog een invoer die ze nodig heeft.</t>
         </is>
       </c>
     </row>
